--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="337">
   <si>
     <t xml:space="preserve">BETTING TEST ACCOUNT — ROLL-UP DASHBOARD</t>
   </si>
@@ -123,7 +123,7 @@
     <t xml:space="preserve">2026-07-12</t>
   </si>
   <si>
-    <t xml:space="preserve">Tab: MLB Jul 12 · 1-0 so far (Pirates +$135.20)</t>
+    <t xml:space="preserve">Tab: MLB Jul 12 · 2-5 thru 7 of 8 graded (-$326.80), Giants ML pending</t>
   </si>
   <si>
     <t xml:space="preserve">NASCAR Quaker State 400</t>
@@ -582,7 +582,7 @@
     <t xml:space="preserve">TEST 3 — MLB SUNDAY SLATE · JULY 12, 2026</t>
   </si>
   <si>
-    <t xml:space="preserve">STATUS: ACTIVE — 1 of 8 settled (Pirates ✓ +$135.20)</t>
+    <t xml:space="preserve">STATUS: ACTIVE — 7 of 8 settled (2-5, -$326.80), Giants ML pending (in progress)</t>
   </si>
   <si>
     <t xml:space="preserve">15-game slate, 8 bets · Source: mlb-jul12-betting-card.html · Lines: ESPN consensus board, Sunday AM · Research: VSiN, PickDawgz, DK Network</t>
@@ -612,7 +612,7 @@
     <t xml:space="preserve">@ White Sox · Ginn (2.49 road ERA) vs Schultz (5.4 BB/9)</t>
   </si>
   <si>
-    <t xml:space="preserve">Clearest starter mismatch priced near even</t>
+    <t xml:space="preserve">Clearest starter mismatch priced near even · RESULT: CWS 9-1 F — Ginn 8 ER in 4.1 IP, six-run 1st; Sox complete sweep</t>
   </si>
   <si>
     <t xml:space="preserve">Tigers ML</t>
@@ -621,7 +621,7 @@
     <t xml:space="preserve">vs Phillies · Skubal vs Wheeler ace duel</t>
   </si>
   <si>
-    <t xml:space="preserve">Bullpen edge: DET 3.10 ERA (3rd) vs PHI 5.41 (26th) since Jun 1</t>
+    <t xml:space="preserve">Bullpen edge: DET 3.10 ERA (3rd) vs PHI 5.41 (26th) since Jun 1 · RESULT: PHI 5-0 F — Wheeler 10 K, Realmuto 3-run 2B; DET pen never got a lead</t>
   </si>
   <si>
     <t xml:space="preserve">Royals @ Orioles Under 9.5</t>
@@ -630,7 +630,7 @@
     <t xml:space="preserve">Totals · Lugo vs Baz</t>
   </si>
   <si>
-    <t xml:space="preserve">KC last in road scoring 3.8 R/G; Baz 3.78 FIP</t>
+    <t xml:space="preserve">KC last in road scoring 3.8 R/G; Baz 3.78 FIP · RESULT: BAL 8-2 F — 10 combined runs, Over by half a run</t>
   </si>
   <si>
     <t xml:space="preserve">Pirates ML</t>
@@ -648,7 +648,7 @@
     <t xml:space="preserve">vs Cubs · Abbott ≤3 ER in 14 straight starts</t>
   </si>
   <si>
-    <t xml:space="preserve">Home dog with the more reliable starter</t>
+    <t xml:space="preserve">Home dog with the more reliable starter · RESULT: CHC 8-4 F — home-dog value didn't land</t>
   </si>
   <si>
     <t xml:space="preserve">Mariners ML</t>
@@ -657,7 +657,7 @@
     <t xml:space="preserve">@ Rays · Hancock 3.23 vs Seymour 4.11</t>
   </si>
   <si>
-    <t xml:space="preserve">Seymour's 6-1 record masks a 4.11 ERA</t>
+    <t xml:space="preserve">Seymour's 6-1 record masks a 4.11 ERA · RESULT: SEA 8-2 F — Crawford 3 RBI; Hancock exited 2nd (finger) but pen held</t>
   </si>
   <si>
     <t xml:space="preserve">Longshot: 3-Leg ML Parlay</t>
@@ -666,7 +666,7 @@
     <t xml:space="preserve">Pirates ML +104 / Reds ML +108 / Athletics ML -104</t>
   </si>
   <si>
-    <t xml:space="preserve">The mandatory longshot — stacks our three value legs</t>
+    <t xml:space="preserve">The mandatory longshot — stacks our three value legs · RESULT: Loss — Reds &amp; A's legs both failed after Pirates leg hit</t>
   </si>
   <si>
     <t xml:space="preserve">Expected Wins (model)</t>
@@ -693,6 +693,12 @@
     <t xml:space="preserve">NYY -114</t>
   </si>
   <si>
+    <t xml:space="preserve">Yankees 5-3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Would have won (NYY -114)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Red Sox @ Mets</t>
   </si>
   <si>
@@ -702,6 +708,12 @@
     <t xml:space="preserve">BOS -126</t>
   </si>
   <si>
+    <t xml:space="preserve">Red Sox 3-2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Would have won (BOS -126)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Guardians @ Marlins</t>
   </si>
   <si>
@@ -711,6 +723,12 @@
     <t xml:space="preserve">MIA -115</t>
   </si>
   <si>
+    <t xml:space="preserve">Guardians 3-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Good skip — MIA -115 lost</t>
+  </si>
+  <si>
     <t xml:space="preserve">Angels @ Twins</t>
   </si>
   <si>
@@ -727,6 +745,12 @@
   </si>
   <si>
     <t xml:space="preserve">STL -136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Braves 4-3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Good skip — STL -136 lost</t>
   </si>
   <si>
     <t xml:space="preserve">Astros @ Rangers</t>
@@ -1018,20 +1042,17 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="13">
+  <numFmts count="10">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="\$#,##0"/>
     <numFmt numFmtId="166" formatCode="\$#,##0.00;&quot;($&quot;#,##0.00\);\-"/>
     <numFmt numFmtId="167" formatCode="\$#,##0.00"/>
     <numFmt numFmtId="168" formatCode="\+0;\-0"/>
-    <numFmt numFmtId="169" formatCode="\$#,##0"/>
-    <numFmt numFmtId="170" formatCode="\$#,##0.00"/>
-    <numFmt numFmtId="171" formatCode="\$#,##0.00;&quot;($&quot;#,##0.00\);\-"/>
-    <numFmt numFmtId="172" formatCode="0"/>
-    <numFmt numFmtId="173" formatCode="0.0%"/>
-    <numFmt numFmtId="174" formatCode="0%"/>
-    <numFmt numFmtId="175" formatCode="0.0&quot; exp. wins&quot;"/>
-    <numFmt numFmtId="176" formatCode="0.0"/>
+    <numFmt numFmtId="169" formatCode="0"/>
+    <numFmt numFmtId="170" formatCode="0.0%"/>
+    <numFmt numFmtId="171" formatCode="0%"/>
+    <numFmt numFmtId="172" formatCode="0.0&quot; exp. wins&quot;"/>
+    <numFmt numFmtId="173" formatCode="0.0"/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -1310,20 +1331,24 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="66">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1443,11 +1468,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1455,15 +1476,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1483,7 +1496,39 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1491,51 +1536,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="171" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="171" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="172" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="173" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1547,11 +1548,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1559,15 +1556,15 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="174" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="171" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="175" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="172" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="176" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1608,35 +1605,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="4">
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <charset val="1"/>
-        <family val="0"/>
-        <b val="1"/>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <charset val="1"/>
-        <family val="0"/>
-        <b val="1"/>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="2">
     <dxf>
       <font>
         <name val="Arial"/>
@@ -1913,315 +1882,315 @@
   <dimension ref="A1:J24"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="6" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="6" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="44"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="5" t="n">
+      <c r="B5" s="6" t="n">
         <v>5000</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="6" t="n">
+      <c r="B6" s="7" t="n">
         <f aca="false">H20</f>
-        <v>300.310372831303</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+        <v>-161.689627168697</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="7" t="n">
+      <c r="B7" s="8" t="n">
         <f aca="false">I19</f>
-        <v>5300.3103728313</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
+        <v>4838.3103728313</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="8" t="n">
+      <c r="B8" s="9" t="n">
         <f aca="false">F20</f>
-        <v>2870</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="7" t="n">
+      <c r="B9" s="8" t="n">
         <f aca="false">B7-B8</f>
-        <v>2430.3103728313</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
+        <v>2638.3103728313</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="9" t="str">
+      <c r="B10" s="10" t="str">
         <f aca="false">COUNTIF(D16:D19,"ACTIVE")&amp;" of 4 max"</f>
         <v>3 of 4 max</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="11" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="4" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="11" t="s">
+      <c r="A15" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B15" s="11" t="s">
+      <c r="B15" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="11" t="s">
+      <c r="C15" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="D15" s="11" t="s">
+      <c r="D15" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="E15" s="11" t="s">
+      <c r="E15" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="F15" s="11" t="s">
+      <c r="F15" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G15" s="11" t="s">
+      <c r="G15" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="H15" s="11" t="s">
+      <c r="H15" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="I15" s="11" t="s">
+      <c r="I15" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="J15" s="11" t="s">
+      <c r="J15" s="12" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="12" t="n">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="B16" s="13" t="s">
+      <c r="B16" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="C16" s="12" t="s">
+      <c r="C16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="D16" s="14" t="s">
+      <c r="D16" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="E16" s="15" t="n">
+      <c r="E16" s="16" t="n">
         <f aca="false">SUM('UFC 329'!F7:F15)</f>
         <v>1050</v>
       </c>
-      <c r="F16" s="15" t="n">
+      <c r="F16" s="16" t="n">
         <f aca="false">SUMIF('UFC 329'!I7:I15,"Pending",'UFC 329'!F7:F15)</f>
         <v>0</v>
       </c>
-      <c r="G16" s="16" t="n">
+      <c r="G16" s="17" t="n">
         <f aca="false">SUM('UFC 329'!J7:J15)</f>
         <v>1215.1103728313</v>
       </c>
-      <c r="H16" s="17" t="n">
+      <c r="H16" s="18" t="n">
         <f aca="false">SUM('UFC 329'!K7:K15)</f>
         <v>165.110372831303</v>
       </c>
-      <c r="I16" s="18" t="n">
+      <c r="I16" s="19" t="n">
         <f aca="false">B5+SUM($H$16:H16)</f>
         <v>5165.1103728313</v>
       </c>
-      <c r="J16" s="19" t="s">
+      <c r="J16" s="20" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="20" t="n">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="B17" s="21" t="s">
+      <c r="B17" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="C17" s="20" t="s">
+      <c r="C17" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="D17" s="22" t="s">
+      <c r="D17" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="E17" s="23" t="n">
+      <c r="E17" s="24" t="n">
         <f aca="false">SUM('World Cup 2026'!F7:F13)</f>
         <v>1000</v>
       </c>
-      <c r="F17" s="23" t="n">
+      <c r="F17" s="24" t="n">
         <f aca="false">SUMIF('World Cup 2026'!I7:I13,"Pending",'World Cup 2026'!F7:F13)</f>
         <v>1000</v>
       </c>
-      <c r="G17" s="24" t="n">
+      <c r="G17" s="25" t="n">
         <f aca="false">SUM('World Cup 2026'!J7:J13)</f>
         <v>0</v>
       </c>
-      <c r="H17" s="25" t="n">
+      <c r="H17" s="26" t="n">
         <f aca="false">SUM('World Cup 2026'!K7:K13)</f>
         <v>0</v>
       </c>
-      <c r="I17" s="26" t="n">
+      <c r="I17" s="27" t="n">
         <f aca="false">I16+H17</f>
         <v>5165.1103728313</v>
       </c>
-      <c r="J17" s="27" t="s">
+      <c r="J17" s="28" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="20" t="n">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="B18" s="21" t="s">
+      <c r="B18" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="C18" s="20" t="s">
+      <c r="C18" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="D18" s="22" t="s">
+      <c r="D18" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="E18" s="23" t="n">
+      <c r="E18" s="24" t="n">
         <f aca="false">SUM('MLB Jul 12'!F7:F14)</f>
         <v>1000</v>
       </c>
-      <c r="F18" s="23" t="n">
+      <c r="F18" s="24" t="n">
         <f aca="false">SUMIF('MLB Jul 12'!I7:I14,"Pending",'MLB Jul 12'!F7:F14)</f>
-        <v>870</v>
-      </c>
-      <c r="G18" s="24" t="n">
+        <v>200</v>
+      </c>
+      <c r="G18" s="25" t="n">
         <f aca="false">SUM('MLB Jul 12'!J7:J14)</f>
-        <v>265.2</v>
-      </c>
-      <c r="H18" s="25" t="n">
+        <v>473.2</v>
+      </c>
+      <c r="H18" s="26" t="n">
         <f aca="false">SUM('MLB Jul 12'!K7:K14)</f>
-        <v>135.2</v>
-      </c>
-      <c r="I18" s="26" t="n">
+        <v>-326.8</v>
+      </c>
+      <c r="I18" s="27" t="n">
         <f aca="false">I17+H18</f>
-        <v>5300.3103728313</v>
-      </c>
-      <c r="J18" s="27" t="s">
+        <v>4838.3103728313</v>
+      </c>
+      <c r="J18" s="28" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="20" t="n">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="B19" s="21" t="s">
+      <c r="B19" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="C19" s="20" t="s">
+      <c r="C19" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="D19" s="22" t="s">
+      <c r="D19" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="E19" s="23" t="n">
+      <c r="E19" s="24" t="n">
         <f aca="false">SUM('NASCAR Jul 12'!F7:F13)</f>
         <v>1000</v>
       </c>
-      <c r="F19" s="23" t="n">
+      <c r="F19" s="24" t="n">
         <f aca="false">SUMIF('NASCAR Jul 12'!I7:I13,"Pending",'NASCAR Jul 12'!F7:F13)</f>
         <v>1000</v>
       </c>
-      <c r="G19" s="24" t="n">
+      <c r="G19" s="25" t="n">
         <f aca="false">SUM('NASCAR Jul 12'!J7:J13)</f>
         <v>0</v>
       </c>
-      <c r="H19" s="25" t="n">
+      <c r="H19" s="26" t="n">
         <f aca="false">SUM('NASCAR Jul 12'!K7:K13)</f>
         <v>0</v>
       </c>
-      <c r="I19" s="26" t="n">
+      <c r="I19" s="27" t="n">
         <f aca="false">I18+H19</f>
-        <v>5300.3103728313</v>
-      </c>
-      <c r="J19" s="27" t="s">
+        <v>4838.3103728313</v>
+      </c>
+      <c r="J19" s="28" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="28"/>
-      <c r="B20" s="29" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="29"/>
+      <c r="B20" s="30" t="s">
         <v>35</v>
       </c>
-      <c r="C20" s="28"/>
-      <c r="D20" s="28"/>
-      <c r="E20" s="30" t="n">
+      <c r="C20" s="29"/>
+      <c r="D20" s="29"/>
+      <c r="E20" s="31" t="n">
         <f aca="false">SUM(E16:E19)</f>
         <v>4050</v>
       </c>
-      <c r="F20" s="30" t="n">
+      <c r="F20" s="31" t="n">
         <f aca="false">SUM(F16:F19)</f>
-        <v>2870</v>
-      </c>
-      <c r="G20" s="31" t="n">
+        <v>2200</v>
+      </c>
+      <c r="G20" s="32" t="n">
         <f aca="false">SUM(G16:G19)</f>
-        <v>1480.3103728313</v>
-      </c>
-      <c r="H20" s="32" t="n">
+        <v>1688.3103728313</v>
+      </c>
+      <c r="H20" s="33" t="n">
         <f aca="false">SUM(H16:H19)</f>
-        <v>300.310372831303</v>
-      </c>
-      <c r="I20" s="28"/>
-      <c r="J20" s="28"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="33" t="s">
+        <v>-161.689627168697</v>
+      </c>
+      <c r="I20" s="29"/>
+      <c r="J20" s="29"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="34" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="33" t="s">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="34" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="33" t="s">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="34" t="s">
         <v>38</v>
       </c>
     </row>
@@ -2277,16 +2246,16 @@
   <dimension ref="A1:L41"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="34" width="5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="34" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="34" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="34" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="34" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="34" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="34" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="34" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="9" style="34" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="34" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="9" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="40"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2298,736 +2267,736 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="3" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="37" t="s">
+      <c r="A3" s="3" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="38" t="s">
+      <c r="A5" s="4" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D6" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="E6" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="F6" s="11" t="s">
+      <c r="F6" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="G6" s="11" t="s">
+      <c r="G6" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="H6" s="11" t="s">
+      <c r="H6" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="I6" s="11" t="s">
+      <c r="I6" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="J6" s="11" t="s">
+      <c r="J6" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="K6" s="11" t="s">
+      <c r="K6" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="L6" s="11" t="s">
+      <c r="L6" s="12" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="39" t="n">
+      <c r="A7" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="40" t="s">
+      <c r="B7" s="38" t="s">
         <v>55</v>
       </c>
-      <c r="C7" s="41" t="s">
+      <c r="C7" s="39" t="s">
         <v>56</v>
       </c>
-      <c r="D7" s="39" t="s">
+      <c r="D7" s="37" t="s">
         <v>57</v>
       </c>
-      <c r="E7" s="42" t="n">
+      <c r="E7" s="40" t="n">
         <v>-265</v>
       </c>
-      <c r="F7" s="43" t="n">
+      <c r="F7" s="41" t="n">
         <v>265</v>
       </c>
-      <c r="G7" s="44" t="n">
+      <c r="G7" s="42" t="n">
         <f aca="false">IF(E7&gt;0,F7*E7/100,F7*100/ABS(E7))</f>
         <v>100</v>
       </c>
-      <c r="H7" s="44" t="n">
+      <c r="H7" s="42" t="n">
         <f aca="false">F7+G7</f>
         <v>365</v>
       </c>
-      <c r="I7" s="45" t="s">
+      <c r="I7" s="43" t="s">
         <v>58</v>
       </c>
-      <c r="J7" s="44" t="n">
+      <c r="J7" s="42" t="n">
         <f aca="false">IF(I7="Win",F7+G7,IF(I7="Push",F7,IF(I7="Loss",0,0)))</f>
         <v>365</v>
       </c>
-      <c r="K7" s="46" t="n">
+      <c r="K7" s="44" t="n">
         <f aca="false">IF(I7="Pending",0,J7-F7)</f>
         <v>100</v>
       </c>
-      <c r="L7" s="47" t="s">
+      <c r="L7" s="45" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="39" t="n">
+      <c r="A8" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="40" t="s">
+      <c r="B8" s="38" t="s">
         <v>60</v>
       </c>
-      <c r="C8" s="41" t="s">
+      <c r="C8" s="39" t="s">
         <v>61</v>
       </c>
-      <c r="D8" s="39" t="s">
+      <c r="D8" s="37" t="s">
         <v>62</v>
       </c>
-      <c r="E8" s="42" t="n">
+      <c r="E8" s="40" t="n">
         <v>-140</v>
       </c>
-      <c r="F8" s="43" t="n">
+      <c r="F8" s="41" t="n">
         <v>200</v>
       </c>
-      <c r="G8" s="44" t="n">
+      <c r="G8" s="42" t="n">
         <f aca="false">IF(E8&gt;0,F8*E8/100,F8*100/ABS(E8))</f>
         <v>142.857142857143</v>
       </c>
-      <c r="H8" s="44" t="n">
+      <c r="H8" s="42" t="n">
         <f aca="false">F8+G8</f>
         <v>342.857142857143</v>
       </c>
-      <c r="I8" s="45" t="s">
+      <c r="I8" s="43" t="s">
         <v>58</v>
       </c>
-      <c r="J8" s="44" t="n">
+      <c r="J8" s="42" t="n">
         <f aca="false">IF(I8="Win",F8+G8,IF(I8="Push",F8,IF(I8="Loss",0,0)))</f>
         <v>342.857142857143</v>
       </c>
-      <c r="K8" s="46" t="n">
+      <c r="K8" s="44" t="n">
         <f aca="false">IF(I8="Pending",0,J8-F8)</f>
         <v>142.857142857143</v>
       </c>
-      <c r="L8" s="47" t="s">
+      <c r="L8" s="45" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="39" t="n">
+      <c r="A9" s="37" t="n">
         <v>3</v>
       </c>
-      <c r="B9" s="40" t="s">
+      <c r="B9" s="38" t="s">
         <v>64</v>
       </c>
-      <c r="C9" s="41" t="s">
+      <c r="C9" s="39" t="s">
         <v>65</v>
       </c>
-      <c r="D9" s="39" t="s">
+      <c r="D9" s="37" t="s">
         <v>57</v>
       </c>
-      <c r="E9" s="42" t="n">
+      <c r="E9" s="40" t="n">
         <v>-148</v>
       </c>
-      <c r="F9" s="43" t="n">
+      <c r="F9" s="41" t="n">
         <v>148</v>
       </c>
-      <c r="G9" s="44" t="n">
+      <c r="G9" s="42" t="n">
         <f aca="false">IF(E9&gt;0,F9*E9/100,F9*100/ABS(E9))</f>
         <v>100</v>
       </c>
-      <c r="H9" s="44" t="n">
+      <c r="H9" s="42" t="n">
         <f aca="false">F9+G9</f>
         <v>248</v>
       </c>
-      <c r="I9" s="48" t="s">
+      <c r="I9" s="46" t="s">
         <v>66</v>
       </c>
-      <c r="J9" s="44" t="n">
+      <c r="J9" s="42" t="n">
         <f aca="false">IF(I9="Win",F9+G9,IF(I9="Push",F9,IF(I9="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K9" s="46" t="n">
+      <c r="K9" s="44" t="n">
         <f aca="false">IF(I9="Pending",0,J9-F9)</f>
         <v>-148</v>
       </c>
-      <c r="L9" s="47" t="s">
+      <c r="L9" s="45" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="39" t="n">
+      <c r="A10" s="37" t="n">
         <v>4</v>
       </c>
-      <c r="B10" s="40" t="s">
+      <c r="B10" s="38" t="s">
         <v>68</v>
       </c>
-      <c r="C10" s="41" t="s">
+      <c r="C10" s="39" t="s">
         <v>69</v>
       </c>
-      <c r="D10" s="39" t="s">
+      <c r="D10" s="37" t="s">
         <v>57</v>
       </c>
-      <c r="E10" s="42" t="n">
+      <c r="E10" s="40" t="n">
         <v>114</v>
       </c>
-      <c r="F10" s="43" t="n">
+      <c r="F10" s="41" t="n">
         <v>100</v>
       </c>
-      <c r="G10" s="44" t="n">
+      <c r="G10" s="42" t="n">
         <f aca="false">IF(E10&gt;0,F10*E10/100,F10*100/ABS(E10))</f>
         <v>114</v>
       </c>
-      <c r="H10" s="44" t="n">
+      <c r="H10" s="42" t="n">
         <f aca="false">F10+G10</f>
         <v>214</v>
       </c>
-      <c r="I10" s="45" t="s">
+      <c r="I10" s="43" t="s">
         <v>58</v>
       </c>
-      <c r="J10" s="44" t="n">
+      <c r="J10" s="42" t="n">
         <f aca="false">IF(I10="Win",F10+G10,IF(I10="Push",F10,IF(I10="Loss",0,0)))</f>
         <v>214</v>
       </c>
-      <c r="K10" s="46" t="n">
+      <c r="K10" s="44" t="n">
         <f aca="false">IF(I10="Pending",0,J10-F10)</f>
         <v>114</v>
       </c>
-      <c r="L10" s="47" t="s">
+      <c r="L10" s="45" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="39" t="n">
+      <c r="A11" s="37" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="40" t="s">
+      <c r="B11" s="38" t="s">
         <v>71</v>
       </c>
-      <c r="C11" s="41" t="s">
+      <c r="C11" s="39" t="s">
         <v>72</v>
       </c>
-      <c r="D11" s="39" t="s">
+      <c r="D11" s="37" t="s">
         <v>57</v>
       </c>
-      <c r="E11" s="42" t="n">
+      <c r="E11" s="40" t="n">
         <v>-218</v>
       </c>
-      <c r="F11" s="43" t="n">
+      <c r="F11" s="41" t="n">
         <v>100</v>
       </c>
-      <c r="G11" s="44" t="n">
+      <c r="G11" s="42" t="n">
         <f aca="false">IF(E11&gt;0,F11*E11/100,F11*100/ABS(E11))</f>
         <v>45.8715596330275</v>
       </c>
-      <c r="H11" s="44" t="n">
+      <c r="H11" s="42" t="n">
         <f aca="false">F11+G11</f>
         <v>145.871559633028</v>
       </c>
-      <c r="I11" s="48" t="s">
+      <c r="I11" s="46" t="s">
         <v>66</v>
       </c>
-      <c r="J11" s="44" t="n">
+      <c r="J11" s="42" t="n">
         <f aca="false">IF(I11="Win",F11+G11,IF(I11="Push",F11,IF(I11="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K11" s="46" t="n">
+      <c r="K11" s="44" t="n">
         <f aca="false">IF(I11="Pending",0,J11-F11)</f>
         <v>-100</v>
       </c>
-      <c r="L11" s="47" t="s">
+      <c r="L11" s="45" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="39" t="n">
+      <c r="A12" s="37" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="40" t="s">
+      <c r="B12" s="38" t="s">
         <v>74</v>
       </c>
-      <c r="C12" s="41" t="s">
+      <c r="C12" s="39" t="s">
         <v>75</v>
       </c>
-      <c r="D12" s="39" t="s">
+      <c r="D12" s="37" t="s">
         <v>57</v>
       </c>
-      <c r="E12" s="42" t="n">
+      <c r="E12" s="40" t="n">
         <v>-125</v>
       </c>
-      <c r="F12" s="43" t="n">
+      <c r="F12" s="41" t="n">
         <v>75</v>
       </c>
-      <c r="G12" s="44" t="n">
+      <c r="G12" s="42" t="n">
         <f aca="false">IF(E12&gt;0,F12*E12/100,F12*100/ABS(E12))</f>
         <v>60</v>
       </c>
-      <c r="H12" s="44" t="n">
+      <c r="H12" s="42" t="n">
         <f aca="false">F12+G12</f>
         <v>135</v>
       </c>
-      <c r="I12" s="45" t="s">
+      <c r="I12" s="43" t="s">
         <v>58</v>
       </c>
-      <c r="J12" s="44" t="n">
+      <c r="J12" s="42" t="n">
         <f aca="false">IF(I12="Win",F12+G12,IF(I12="Push",F12,IF(I12="Loss",0,0)))</f>
         <v>135</v>
       </c>
-      <c r="K12" s="46" t="n">
+      <c r="K12" s="44" t="n">
         <f aca="false">IF(I12="Pending",0,J12-F12)</f>
         <v>60</v>
       </c>
-      <c r="L12" s="47" t="s">
+      <c r="L12" s="45" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="39" t="n">
+      <c r="A13" s="37" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="40" t="s">
+      <c r="B13" s="38" t="s">
         <v>77</v>
       </c>
-      <c r="C13" s="41" t="s">
+      <c r="C13" s="39" t="s">
         <v>78</v>
       </c>
-      <c r="D13" s="39" t="s">
+      <c r="D13" s="37" t="s">
         <v>57</v>
       </c>
-      <c r="E13" s="42" t="n">
+      <c r="E13" s="40" t="n">
         <v>-225</v>
       </c>
-      <c r="F13" s="43" t="n">
+      <c r="F13" s="41" t="n">
         <v>50</v>
       </c>
-      <c r="G13" s="44" t="n">
+      <c r="G13" s="42" t="n">
         <f aca="false">IF(E13&gt;0,F13*E13/100,F13*100/ABS(E13))</f>
         <v>22.2222222222222</v>
       </c>
-      <c r="H13" s="44" t="n">
+      <c r="H13" s="42" t="n">
         <f aca="false">F13+G13</f>
         <v>72.2222222222222</v>
       </c>
-      <c r="I13" s="45" t="s">
+      <c r="I13" s="43" t="s">
         <v>58</v>
       </c>
-      <c r="J13" s="44" t="n">
+      <c r="J13" s="42" t="n">
         <f aca="false">IF(I13="Win",F13+G13,IF(I13="Push",F13,IF(I13="Loss",0,0)))</f>
         <v>72.2222222222222</v>
       </c>
-      <c r="K13" s="46" t="n">
+      <c r="K13" s="44" t="n">
         <f aca="false">IF(I13="Pending",0,J13-F13)</f>
         <v>22.2222222222222</v>
       </c>
-      <c r="L13" s="47" t="s">
+      <c r="L13" s="45" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="39" t="n">
+      <c r="A14" s="37" t="n">
         <v>8</v>
       </c>
-      <c r="B14" s="40" t="s">
+      <c r="B14" s="38" t="s">
         <v>80</v>
       </c>
-      <c r="C14" s="41" t="s">
+      <c r="C14" s="39" t="s">
         <v>81</v>
       </c>
-      <c r="D14" s="39" t="s">
+      <c r="D14" s="37" t="s">
         <v>57</v>
       </c>
-      <c r="E14" s="42" t="n">
+      <c r="E14" s="40" t="n">
         <v>-258</v>
       </c>
-      <c r="F14" s="43" t="n">
+      <c r="F14" s="41" t="n">
         <v>62</v>
       </c>
-      <c r="G14" s="44" t="n">
+      <c r="G14" s="42" t="n">
         <f aca="false">IF(E14&gt;0,F14*E14/100,F14*100/ABS(E14))</f>
         <v>24.031007751938</v>
       </c>
-      <c r="H14" s="44" t="n">
+      <c r="H14" s="42" t="n">
         <f aca="false">F14+G14</f>
         <v>86.031007751938</v>
       </c>
-      <c r="I14" s="45" t="s">
+      <c r="I14" s="43" t="s">
         <v>58</v>
       </c>
-      <c r="J14" s="44" t="n">
+      <c r="J14" s="42" t="n">
         <f aca="false">IF(I14="Win",F14+G14,IF(I14="Push",F14,IF(I14="Loss",0,0)))</f>
         <v>86.031007751938</v>
       </c>
-      <c r="K14" s="46" t="n">
+      <c r="K14" s="44" t="n">
         <f aca="false">IF(I14="Pending",0,J14-F14)</f>
         <v>24.031007751938</v>
       </c>
-      <c r="L14" s="47" t="s">
+      <c r="L14" s="45" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="39" t="n">
+      <c r="A15" s="37" t="n">
         <v>9</v>
       </c>
-      <c r="B15" s="40" t="s">
+      <c r="B15" s="38" t="s">
         <v>83</v>
       </c>
-      <c r="C15" s="41" t="s">
+      <c r="C15" s="39" t="s">
         <v>84</v>
       </c>
-      <c r="D15" s="39" t="s">
+      <c r="D15" s="37" t="s">
         <v>85</v>
       </c>
-      <c r="E15" s="42" t="n">
+      <c r="E15" s="40" t="n">
         <v>443</v>
       </c>
-      <c r="F15" s="43" t="n">
+      <c r="F15" s="41" t="n">
         <v>50</v>
       </c>
-      <c r="G15" s="44" t="n">
+      <c r="G15" s="42" t="n">
         <f aca="false">IF(E15&gt;0,F15*E15/100,F15*100/ABS(E15))</f>
         <v>221.5</v>
       </c>
-      <c r="H15" s="44" t="n">
+      <c r="H15" s="42" t="n">
         <f aca="false">F15+G15</f>
         <v>271.5</v>
       </c>
-      <c r="I15" s="48" t="s">
+      <c r="I15" s="46" t="s">
         <v>66</v>
       </c>
-      <c r="J15" s="44" t="n">
+      <c r="J15" s="42" t="n">
         <f aca="false">IF(I15="Win",F15+G15,IF(I15="Push",F15,IF(I15="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K15" s="46" t="n">
+      <c r="K15" s="44" t="n">
         <f aca="false">IF(I15="Pending",0,J15-F15)</f>
         <v>-50</v>
       </c>
-      <c r="L15" s="47" t="s">
+      <c r="L15" s="45" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="49"/>
-      <c r="B16" s="50" t="s">
+      <c r="A16" s="47"/>
+      <c r="B16" s="48" t="s">
         <v>35</v>
       </c>
-      <c r="C16" s="49"/>
-      <c r="D16" s="49"/>
-      <c r="E16" s="49"/>
-      <c r="F16" s="51" t="n">
+      <c r="C16" s="47"/>
+      <c r="D16" s="47"/>
+      <c r="E16" s="47"/>
+      <c r="F16" s="31" t="n">
         <f aca="false">SUM(F7:F15)</f>
         <v>1050</v>
       </c>
-      <c r="G16" s="52" t="n">
+      <c r="G16" s="32" t="n">
         <f aca="false">SUM(G7:G15)</f>
         <v>830.481932464331</v>
       </c>
-      <c r="H16" s="52" t="n">
+      <c r="H16" s="32" t="n">
         <f aca="false">SUM(H7:H15)</f>
         <v>1880.48193246433</v>
       </c>
-      <c r="I16" s="49"/>
-      <c r="J16" s="52" t="n">
+      <c r="I16" s="47"/>
+      <c r="J16" s="32" t="n">
         <f aca="false">SUM(J7:J15)</f>
         <v>1215.1103728313</v>
       </c>
-      <c r="K16" s="53" t="n">
+      <c r="K16" s="33" t="n">
         <f aca="false">SUM(K7:K15)</f>
         <v>165.110372831303</v>
       </c>
-      <c r="L16" s="49"/>
+      <c r="L16" s="47"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="38" t="s">
+      <c r="B18" s="4" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="40" t="s">
+      <c r="B19" s="38" t="s">
         <v>88</v>
       </c>
-      <c r="C19" s="54" t="n">
+      <c r="C19" s="49" t="n">
         <f aca="false">COUNTIF(I7:I15,"Win")</f>
         <v>6</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="40" t="s">
+      <c r="B20" s="38" t="s">
         <v>89</v>
       </c>
-      <c r="C20" s="54" t="n">
+      <c r="C20" s="49" t="n">
         <f aca="false">COUNTIF(I7:I15,"Loss")</f>
         <v>3</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="40" t="s">
+      <c r="B21" s="38" t="s">
         <v>90</v>
       </c>
-      <c r="C21" s="54" t="n">
+      <c r="C21" s="49" t="n">
         <f aca="false">COUNTIF(I7:I15,"Push")</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="40" t="s">
+      <c r="B22" s="38" t="s">
         <v>91</v>
       </c>
-      <c r="C22" s="54" t="n">
+      <c r="C22" s="49" t="n">
         <f aca="false">COUNTIF(I7:I15,"Pending")</f>
         <v>0</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="40" t="s">
+      <c r="B23" s="38" t="s">
         <v>92</v>
       </c>
-      <c r="C23" s="55" t="n">
+      <c r="C23" s="50" t="n">
         <f aca="false">IF(COUNTIF(I7:I15,"Win")+COUNTIF(I7:I15,"Loss")=0,"—",COUNTIF(I7:I15,"Win")/(COUNTIF(I7:I15,"Win")+COUNTIF(I7:I15,"Loss")))</f>
         <v>0.666666666666667</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="40" t="s">
+      <c r="B24" s="38" t="s">
         <v>93</v>
       </c>
-      <c r="C24" s="56" t="n">
+      <c r="C24" s="51" t="n">
         <f aca="false">SUM(F7:F15)</f>
         <v>1050</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="40" t="s">
+      <c r="B25" s="38" t="s">
         <v>94</v>
       </c>
-      <c r="C25" s="44" t="n">
+      <c r="C25" s="42" t="n">
         <f aca="false">SUM(J7:J15)</f>
         <v>1215.1103728313</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="40" t="s">
+      <c r="B26" s="38" t="s">
         <v>95</v>
       </c>
-      <c r="C26" s="46" t="n">
+      <c r="C26" s="44" t="n">
         <f aca="false">SUM(K7:K15)</f>
         <v>165.110372831303</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="40" t="s">
+      <c r="B27" s="38" t="s">
         <v>96</v>
       </c>
-      <c r="C27" s="55" t="n">
+      <c r="C27" s="50" t="n">
         <f aca="false">IF(SUM(F7:F15)=0,"—",SUM(K7:K15)/SUM(F7:F15))</f>
         <v>0.157247974125051</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="40" t="s">
+      <c r="B28" s="38" t="s">
         <v>97</v>
       </c>
-      <c r="C28" s="44" t="n">
+      <c r="C28" s="42" t="n">
         <f aca="false">SUM(H7:H15)</f>
         <v>1880.48193246433</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="38" t="s">
+      <c r="A30" s="4" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="11" t="s">
+      <c r="A31" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B31" s="11" t="s">
+      <c r="B31" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="C31" s="11" t="s">
+      <c r="C31" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="D31" s="11" t="s">
+      <c r="D31" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="E31" s="11" t="s">
+      <c r="E31" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="F31" s="11" t="s">
+      <c r="F31" s="12" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="39" t="n">
+      <c r="A32" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="B32" s="40" t="s">
+      <c r="B32" s="38" t="s">
         <v>104</v>
       </c>
-      <c r="C32" s="47" t="s">
+      <c r="C32" s="45" t="s">
         <v>105</v>
       </c>
-      <c r="D32" s="57" t="s">
+      <c r="D32" s="52" t="s">
         <v>106</v>
       </c>
-      <c r="E32" s="58" t="s">
+      <c r="E32" s="53" t="s">
         <v>107</v>
       </c>
-      <c r="F32" s="58" t="s">
+      <c r="F32" s="53" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="39" t="n">
+      <c r="A33" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="B33" s="40" t="s">
+      <c r="B33" s="38" t="s">
         <v>109</v>
       </c>
-      <c r="C33" s="47" t="s">
+      <c r="C33" s="45" t="s">
         <v>110</v>
       </c>
-      <c r="D33" s="57" t="s">
+      <c r="D33" s="52" t="s">
         <v>111</v>
       </c>
-      <c r="E33" s="58" t="s">
+      <c r="E33" s="53" t="s">
         <v>112</v>
       </c>
-      <c r="F33" s="58" t="s">
+      <c r="F33" s="53" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="39" t="n">
+      <c r="A34" s="37" t="n">
         <v>3</v>
       </c>
-      <c r="B34" s="40" t="s">
+      <c r="B34" s="38" t="s">
         <v>114</v>
       </c>
-      <c r="C34" s="47" t="s">
+      <c r="C34" s="45" t="s">
         <v>115</v>
       </c>
-      <c r="D34" s="57" t="s">
+      <c r="D34" s="52" t="s">
         <v>116</v>
       </c>
-      <c r="E34" s="58" t="s">
+      <c r="E34" s="53" t="s">
         <v>117</v>
       </c>
-      <c r="F34" s="58" t="s">
+      <c r="F34" s="53" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="39" t="n">
+      <c r="A35" s="37" t="n">
         <v>4</v>
       </c>
-      <c r="B35" s="40" t="s">
+      <c r="B35" s="38" t="s">
         <v>119</v>
       </c>
-      <c r="C35" s="47" t="s">
+      <c r="C35" s="45" t="s">
         <v>120</v>
       </c>
-      <c r="D35" s="57" t="s">
+      <c r="D35" s="52" t="s">
         <v>121</v>
       </c>
-      <c r="E35" s="58" t="s">
+      <c r="E35" s="53" t="s">
         <v>122</v>
       </c>
-      <c r="F35" s="58" t="s">
+      <c r="F35" s="53" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="39" t="n">
+      <c r="A36" s="37" t="n">
         <v>5</v>
       </c>
-      <c r="B36" s="40" t="s">
+      <c r="B36" s="38" t="s">
         <v>124</v>
       </c>
-      <c r="C36" s="47" t="s">
+      <c r="C36" s="45" t="s">
         <v>125</v>
       </c>
-      <c r="D36" s="57" t="s">
+      <c r="D36" s="52" t="s">
         <v>126</v>
       </c>
-      <c r="E36" s="58" t="s">
+      <c r="E36" s="53" t="s">
         <v>127</v>
       </c>
-      <c r="F36" s="58" t="s">
+      <c r="F36" s="53" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="39" t="n">
+      <c r="A37" s="37" t="n">
         <v>6</v>
       </c>
-      <c r="B37" s="40" t="s">
+      <c r="B37" s="38" t="s">
         <v>129</v>
       </c>
-      <c r="C37" s="47" t="s">
+      <c r="C37" s="45" t="s">
         <v>130</v>
       </c>
-      <c r="D37" s="57" t="s">
+      <c r="D37" s="52" t="s">
         <v>131</v>
       </c>
-      <c r="E37" s="58" t="s">
+      <c r="E37" s="53" t="s">
         <v>132</v>
       </c>
-      <c r="F37" s="58" t="s">
+      <c r="F37" s="53" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="59" t="s">
+      <c r="A39" s="34" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="59" t="s">
+      <c r="A40" s="34" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="59" t="s">
+      <c r="A41" s="34" t="s">
         <v>136</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="K7:K16">
-    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>AND(ISNUMBER(K7),K7&gt;0)</formula>
     </cfRule>
-    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>AND(ISNUMBER(K7),K7&lt;0)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C26:C27">
-    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>AND(ISNUMBER(C26),C26&gt;0)</formula>
     </cfRule>
-    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>AND(ISNUMBER(C26),C26&lt;0)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3056,606 +3025,606 @@
   <dimension ref="A1:L35"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="34" width="5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="34" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="34" width="42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="34" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="34" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="34" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="34" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="9" style="34" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="34" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="9" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="44"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="35" t="s">
         <v>137</v>
       </c>
-      <c r="H1" s="60" t="s">
+      <c r="H1" s="54" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="3" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="37" t="s">
+      <c r="A3" s="3" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="38" t="s">
+      <c r="A5" s="4" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D6" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="E6" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="F6" s="11" t="s">
+      <c r="F6" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="G6" s="11" t="s">
+      <c r="G6" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="H6" s="11" t="s">
+      <c r="H6" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="I6" s="11" t="s">
+      <c r="I6" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="J6" s="11" t="s">
+      <c r="J6" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="K6" s="11" t="s">
+      <c r="K6" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="L6" s="11" t="s">
+      <c r="L6" s="12" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="39" t="n">
+      <c r="A7" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="40" t="s">
+      <c r="B7" s="38" t="s">
         <v>142</v>
       </c>
-      <c r="C7" s="41" t="s">
+      <c r="C7" s="39" t="s">
         <v>143</v>
       </c>
-      <c r="D7" s="39" t="s">
+      <c r="D7" s="37" t="s">
         <v>144</v>
       </c>
-      <c r="E7" s="42" t="n">
+      <c r="E7" s="40" t="n">
         <v>-144</v>
       </c>
-      <c r="F7" s="43" t="n">
+      <c r="F7" s="41" t="n">
         <v>300</v>
       </c>
-      <c r="G7" s="44" t="n">
+      <c r="G7" s="42" t="n">
         <f aca="false">IF(E7&gt;0,F7*E7/100,F7*100/ABS(E7))</f>
         <v>208.333333333333</v>
       </c>
-      <c r="H7" s="44" t="n">
+      <c r="H7" s="42" t="n">
         <f aca="false">F7+G7</f>
         <v>508.333333333333</v>
       </c>
-      <c r="I7" s="61" t="s">
+      <c r="I7" s="55" t="s">
         <v>91</v>
       </c>
-      <c r="J7" s="44" t="n">
+      <c r="J7" s="42" t="n">
         <f aca="false">IF(I7="Win",F7+G7,IF(I7="Push",F7,IF(I7="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K7" s="46" t="n">
+      <c r="K7" s="44" t="n">
         <f aca="false">IF(I7="Pending",0,J7-F7)</f>
         <v>0</v>
       </c>
-      <c r="L7" s="47" t="s">
+      <c r="L7" s="45" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="39" t="n">
+      <c r="A8" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="40" t="s">
+      <c r="B8" s="38" t="s">
         <v>146</v>
       </c>
-      <c r="C8" s="41" t="s">
+      <c r="C8" s="39" t="s">
         <v>147</v>
       </c>
-      <c r="D8" s="39" t="s">
+      <c r="D8" s="37" t="s">
         <v>148</v>
       </c>
-      <c r="E8" s="42" t="n">
+      <c r="E8" s="40" t="n">
         <v>-122</v>
       </c>
-      <c r="F8" s="43" t="n">
+      <c r="F8" s="41" t="n">
         <v>120</v>
       </c>
-      <c r="G8" s="44" t="n">
+      <c r="G8" s="42" t="n">
         <f aca="false">IF(E8&gt;0,F8*E8/100,F8*100/ABS(E8))</f>
         <v>98.3606557377049</v>
       </c>
-      <c r="H8" s="44" t="n">
+      <c r="H8" s="42" t="n">
         <f aca="false">F8+G8</f>
         <v>218.360655737705</v>
       </c>
-      <c r="I8" s="61" t="s">
+      <c r="I8" s="55" t="s">
         <v>91</v>
       </c>
-      <c r="J8" s="44" t="n">
+      <c r="J8" s="42" t="n">
         <f aca="false">IF(I8="Win",F8+G8,IF(I8="Push",F8,IF(I8="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K8" s="46" t="n">
+      <c r="K8" s="44" t="n">
         <f aca="false">IF(I8="Pending",0,J8-F8)</f>
         <v>0</v>
       </c>
-      <c r="L8" s="47" t="s">
+      <c r="L8" s="45" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="39" t="n">
+      <c r="A9" s="37" t="n">
         <v>3</v>
       </c>
-      <c r="B9" s="40" t="s">
+      <c r="B9" s="38" t="s">
         <v>150</v>
       </c>
-      <c r="C9" s="41" t="s">
+      <c r="C9" s="39" t="s">
         <v>151</v>
       </c>
-      <c r="D9" s="39" t="s">
+      <c r="D9" s="37" t="s">
         <v>152</v>
       </c>
-      <c r="E9" s="42" t="n">
+      <c r="E9" s="40" t="n">
         <v>175</v>
       </c>
-      <c r="F9" s="43" t="n">
+      <c r="F9" s="41" t="n">
         <v>150</v>
       </c>
-      <c r="G9" s="44" t="n">
+      <c r="G9" s="42" t="n">
         <f aca="false">IF(E9&gt;0,F9*E9/100,F9*100/ABS(E9))</f>
         <v>262.5</v>
       </c>
-      <c r="H9" s="44" t="n">
+      <c r="H9" s="42" t="n">
         <f aca="false">F9+G9</f>
         <v>412.5</v>
       </c>
-      <c r="I9" s="61" t="s">
+      <c r="I9" s="55" t="s">
         <v>91</v>
       </c>
-      <c r="J9" s="44" t="n">
+      <c r="J9" s="42" t="n">
         <f aca="false">IF(I9="Win",F9+G9,IF(I9="Push",F9,IF(I9="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K9" s="46" t="n">
+      <c r="K9" s="44" t="n">
         <f aca="false">IF(I9="Pending",0,J9-F9)</f>
         <v>0</v>
       </c>
-      <c r="L9" s="47" t="s">
+      <c r="L9" s="45" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="39" t="n">
+      <c r="A10" s="37" t="n">
         <v>4</v>
       </c>
-      <c r="B10" s="40" t="s">
+      <c r="B10" s="38" t="s">
         <v>154</v>
       </c>
-      <c r="C10" s="41" t="s">
+      <c r="C10" s="39" t="s">
         <v>155</v>
       </c>
-      <c r="D10" s="39" t="s">
+      <c r="D10" s="37" t="s">
         <v>152</v>
       </c>
-      <c r="E10" s="42" t="n">
+      <c r="E10" s="40" t="n">
         <v>205</v>
       </c>
-      <c r="F10" s="43" t="n">
+      <c r="F10" s="41" t="n">
         <v>80</v>
       </c>
-      <c r="G10" s="44" t="n">
+      <c r="G10" s="42" t="n">
         <f aca="false">IF(E10&gt;0,F10*E10/100,F10*100/ABS(E10))</f>
         <v>164</v>
       </c>
-      <c r="H10" s="44" t="n">
+      <c r="H10" s="42" t="n">
         <f aca="false">F10+G10</f>
         <v>244</v>
       </c>
-      <c r="I10" s="61" t="s">
+      <c r="I10" s="55" t="s">
         <v>91</v>
       </c>
-      <c r="J10" s="44" t="n">
+      <c r="J10" s="42" t="n">
         <f aca="false">IF(I10="Win",F10+G10,IF(I10="Push",F10,IF(I10="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K10" s="46" t="n">
+      <c r="K10" s="44" t="n">
         <f aca="false">IF(I10="Pending",0,J10-F10)</f>
         <v>0</v>
       </c>
-      <c r="L10" s="47" t="s">
+      <c r="L10" s="45" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="39" t="n">
+      <c r="A11" s="37" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="40" t="s">
+      <c r="B11" s="38" t="s">
         <v>157</v>
       </c>
-      <c r="C11" s="41" t="s">
+      <c r="C11" s="39" t="s">
         <v>158</v>
       </c>
-      <c r="D11" s="39" t="s">
+      <c r="D11" s="37" t="s">
         <v>159</v>
       </c>
-      <c r="E11" s="42" t="n">
+      <c r="E11" s="40" t="n">
         <v>160</v>
       </c>
-      <c r="F11" s="43" t="n">
+      <c r="F11" s="41" t="n">
         <v>250</v>
       </c>
-      <c r="G11" s="44" t="n">
+      <c r="G11" s="42" t="n">
         <f aca="false">IF(E11&gt;0,F11*E11/100,F11*100/ABS(E11))</f>
         <v>400</v>
       </c>
-      <c r="H11" s="44" t="n">
+      <c r="H11" s="42" t="n">
         <f aca="false">F11+G11</f>
         <v>650</v>
       </c>
-      <c r="I11" s="61" t="s">
+      <c r="I11" s="55" t="s">
         <v>91</v>
       </c>
-      <c r="J11" s="44" t="n">
+      <c r="J11" s="42" t="n">
         <f aca="false">IF(I11="Win",F11+G11,IF(I11="Push",F11,IF(I11="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K11" s="46" t="n">
+      <c r="K11" s="44" t="n">
         <f aca="false">IF(I11="Pending",0,J11-F11)</f>
         <v>0</v>
       </c>
-      <c r="L11" s="47" t="s">
+      <c r="L11" s="45" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="39" t="n">
+      <c r="A12" s="37" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="40" t="s">
+      <c r="B12" s="38" t="s">
         <v>161</v>
       </c>
-      <c r="C12" s="41" t="s">
+      <c r="C12" s="39" t="s">
         <v>162</v>
       </c>
-      <c r="D12" s="39" t="s">
+      <c r="D12" s="37" t="s">
         <v>159</v>
       </c>
-      <c r="E12" s="42" t="n">
+      <c r="E12" s="40" t="n">
         <v>500</v>
       </c>
-      <c r="F12" s="43" t="n">
+      <c r="F12" s="41" t="n">
         <v>50</v>
       </c>
-      <c r="G12" s="44" t="n">
+      <c r="G12" s="42" t="n">
         <f aca="false">IF(E12&gt;0,F12*E12/100,F12*100/ABS(E12))</f>
         <v>250</v>
       </c>
-      <c r="H12" s="44" t="n">
+      <c r="H12" s="42" t="n">
         <f aca="false">F12+G12</f>
         <v>300</v>
       </c>
-      <c r="I12" s="61" t="s">
+      <c r="I12" s="55" t="s">
         <v>91</v>
       </c>
-      <c r="J12" s="44" t="n">
+      <c r="J12" s="42" t="n">
         <f aca="false">IF(I12="Win",F12+G12,IF(I12="Push",F12,IF(I12="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K12" s="46" t="n">
+      <c r="K12" s="44" t="n">
         <f aca="false">IF(I12="Pending",0,J12-F12)</f>
         <v>0</v>
       </c>
-      <c r="L12" s="47" t="s">
+      <c r="L12" s="45" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="39" t="n">
+      <c r="A13" s="37" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="40" t="s">
+      <c r="B13" s="38" t="s">
         <v>164</v>
       </c>
-      <c r="C13" s="41" t="s">
+      <c r="C13" s="39" t="s">
         <v>165</v>
       </c>
-      <c r="D13" s="39" t="s">
+      <c r="D13" s="37" t="s">
         <v>85</v>
       </c>
-      <c r="E13" s="42" t="n">
+      <c r="E13" s="40" t="n">
         <v>179</v>
       </c>
-      <c r="F13" s="43" t="n">
+      <c r="F13" s="41" t="n">
         <v>50</v>
       </c>
-      <c r="G13" s="44" t="n">
+      <c r="G13" s="42" t="n">
         <f aca="false">IF(E13&gt;0,F13*E13/100,F13*100/ABS(E13))</f>
         <v>89.5</v>
       </c>
-      <c r="H13" s="44" t="n">
+      <c r="H13" s="42" t="n">
         <f aca="false">F13+G13</f>
         <v>139.5</v>
       </c>
-      <c r="I13" s="61" t="s">
+      <c r="I13" s="55" t="s">
         <v>91</v>
       </c>
-      <c r="J13" s="44" t="n">
+      <c r="J13" s="42" t="n">
         <f aca="false">IF(I13="Win",F13+G13,IF(I13="Push",F13,IF(I13="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K13" s="46" t="n">
+      <c r="K13" s="44" t="n">
         <f aca="false">IF(I13="Pending",0,J13-F13)</f>
         <v>0</v>
       </c>
-      <c r="L13" s="47" t="s">
+      <c r="L13" s="45" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="49"/>
-      <c r="B14" s="50" t="s">
+      <c r="A14" s="47"/>
+      <c r="B14" s="48" t="s">
         <v>35</v>
       </c>
-      <c r="C14" s="49"/>
-      <c r="D14" s="49"/>
-      <c r="E14" s="49"/>
-      <c r="F14" s="51" t="n">
+      <c r="C14" s="47"/>
+      <c r="D14" s="47"/>
+      <c r="E14" s="47"/>
+      <c r="F14" s="31" t="n">
         <f aca="false">SUM(F7:F13)</f>
         <v>1000</v>
       </c>
-      <c r="G14" s="52" t="n">
+      <c r="G14" s="32" t="n">
         <f aca="false">SUM(G7:G13)</f>
         <v>1472.69398907104</v>
       </c>
-      <c r="H14" s="52" t="n">
+      <c r="H14" s="32" t="n">
         <f aca="false">SUM(H7:H13)</f>
         <v>2472.69398907104</v>
       </c>
-      <c r="I14" s="49"/>
-      <c r="J14" s="52" t="n">
+      <c r="I14" s="47"/>
+      <c r="J14" s="32" t="n">
         <f aca="false">SUM(J7:J13)</f>
         <v>0</v>
       </c>
-      <c r="K14" s="53" t="n">
+      <c r="K14" s="33" t="n">
         <f aca="false">SUM(K7:K13)</f>
         <v>0</v>
       </c>
-      <c r="L14" s="49"/>
+      <c r="L14" s="47"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="38" t="s">
+      <c r="B16" s="4" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="40" t="s">
+      <c r="B17" s="38" t="s">
         <v>88</v>
       </c>
-      <c r="C17" s="54" t="n">
+      <c r="C17" s="49" t="n">
         <f aca="false">COUNTIF(I7:I13,"Win")</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="40" t="s">
+      <c r="B18" s="38" t="s">
         <v>89</v>
       </c>
-      <c r="C18" s="54" t="n">
+      <c r="C18" s="49" t="n">
         <f aca="false">COUNTIF(I7:I13,"Loss")</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="40" t="s">
+      <c r="B19" s="38" t="s">
         <v>90</v>
       </c>
-      <c r="C19" s="54" t="n">
+      <c r="C19" s="49" t="n">
         <f aca="false">COUNTIF(I7:I13,"Push")</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="40" t="s">
+      <c r="B20" s="38" t="s">
         <v>91</v>
       </c>
-      <c r="C20" s="54" t="n">
+      <c r="C20" s="49" t="n">
         <f aca="false">COUNTIF(I7:I13,"Pending")</f>
         <v>7</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="40" t="s">
+      <c r="B21" s="38" t="s">
         <v>92</v>
       </c>
-      <c r="C21" s="55" t="str">
+      <c r="C21" s="50" t="str">
         <f aca="false">IF(COUNTIF(I7:I13,"Win")+COUNTIF(I7:I13,"Loss")=0,"—",COUNTIF(I7:I13,"Win")/(COUNTIF(I7:I13,"Win")+COUNTIF(I7:I13,"Loss")))</f>
         <v>—</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="40" t="s">
+      <c r="B22" s="38" t="s">
         <v>93</v>
       </c>
-      <c r="C22" s="56" t="n">
+      <c r="C22" s="51" t="n">
         <f aca="false">SUM(F7:F13)</f>
         <v>1000</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="40" t="s">
+      <c r="B23" s="38" t="s">
         <v>94</v>
       </c>
-      <c r="C23" s="44" t="n">
+      <c r="C23" s="42" t="n">
         <f aca="false">SUM(J7:J13)</f>
         <v>0</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="40" t="s">
+      <c r="B24" s="38" t="s">
         <v>95</v>
       </c>
-      <c r="C24" s="46" t="n">
+      <c r="C24" s="44" t="n">
         <f aca="false">SUM(K7:K13)</f>
         <v>0</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="40" t="s">
+      <c r="B25" s="38" t="s">
         <v>96</v>
       </c>
-      <c r="C25" s="55" t="n">
+      <c r="C25" s="50" t="n">
         <f aca="false">IF(SUM(F7:F13)=0,"—",SUM(K7:K13)/SUM(F7:F13))</f>
         <v>0</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="40" t="s">
+      <c r="B26" s="38" t="s">
         <v>167</v>
       </c>
-      <c r="C26" s="56" t="n">
+      <c r="C26" s="51" t="n">
         <f aca="false">929</f>
         <v>929</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="38" t="s">
+      <c r="A28" s="4" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="11" t="s">
+      <c r="A29" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B29" s="11" t="s">
+      <c r="B29" s="12" t="s">
         <v>169</v>
       </c>
-      <c r="C29" s="11" t="s">
+      <c r="C29" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="D29" s="11" t="s">
+      <c r="D29" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="E29" s="11" t="s">
+      <c r="E29" s="12" t="s">
         <v>170</v>
       </c>
-      <c r="F29" s="11" t="s">
+      <c r="F29" s="12" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="39" t="n">
+      <c r="A30" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="B30" s="40" t="s">
+      <c r="B30" s="38" t="s">
         <v>171</v>
       </c>
-      <c r="C30" s="47" t="s">
+      <c r="C30" s="45" t="s">
         <v>172</v>
       </c>
-      <c r="D30" s="57" t="s">
+      <c r="D30" s="52" t="s">
         <v>173</v>
       </c>
-      <c r="E30" s="61"/>
-      <c r="F30" s="61"/>
+      <c r="E30" s="55"/>
+      <c r="F30" s="55"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="39" t="n">
+      <c r="A31" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="B31" s="40" t="s">
+      <c r="B31" s="38" t="s">
         <v>174</v>
       </c>
-      <c r="C31" s="47" t="s">
+      <c r="C31" s="45" t="s">
         <v>175</v>
       </c>
-      <c r="D31" s="57" t="s">
+      <c r="D31" s="52" t="s">
         <v>176</v>
       </c>
-      <c r="E31" s="61"/>
-      <c r="F31" s="61"/>
+      <c r="E31" s="55"/>
+      <c r="F31" s="55"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="39" t="n">
+      <c r="A32" s="37" t="n">
         <v>3</v>
       </c>
-      <c r="B32" s="40" t="s">
+      <c r="B32" s="38" t="s">
         <v>177</v>
       </c>
-      <c r="C32" s="47" t="s">
+      <c r="C32" s="45" t="s">
         <v>178</v>
       </c>
-      <c r="D32" s="57" t="s">
+      <c r="D32" s="52" t="s">
         <v>179</v>
       </c>
-      <c r="E32" s="61"/>
-      <c r="F32" s="61"/>
+      <c r="E32" s="55"/>
+      <c r="F32" s="55"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="39" t="n">
+      <c r="A33" s="37" t="n">
         <v>4</v>
       </c>
-      <c r="B33" s="40" t="s">
+      <c r="B33" s="38" t="s">
         <v>180</v>
       </c>
-      <c r="C33" s="47" t="s">
+      <c r="C33" s="45" t="s">
         <v>181</v>
       </c>
-      <c r="D33" s="57" t="s">
+      <c r="D33" s="52" t="s">
         <v>182</v>
       </c>
-      <c r="E33" s="61"/>
-      <c r="F33" s="61"/>
+      <c r="E33" s="55"/>
+      <c r="F33" s="55"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="59" t="s">
+      <c r="A35" s="34" t="s">
         <v>183</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="K7:K14">
-    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>AND(ISNUMBER(K7),K7&gt;0)</formula>
     </cfRule>
-    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>AND(ISNUMBER(K7),K7&lt;0)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C24:C25">
-    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>AND(ISNUMBER(C24),C24&gt;0)</formula>
     </cfRule>
-    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>AND(ISNUMBER(C24),C24&lt;0)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3684,770 +3653,786 @@
   <dimension ref="A1:M42"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="34" width="5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="34" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="34" width="46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="34" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="34" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="34" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="34" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="9" style="34" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="34" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="34" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="9" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="46"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="35" t="s">
         <v>184</v>
       </c>
-      <c r="H1" s="60" t="s">
+      <c r="H1" s="54" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="3" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="37" t="s">
+      <c r="A3" s="3" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="38" t="s">
+      <c r="A5" s="4" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="12" t="s">
         <v>188</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D6" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="E6" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="F6" s="11" t="s">
+      <c r="F6" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="G6" s="11" t="s">
+      <c r="G6" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="H6" s="11" t="s">
+      <c r="H6" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="I6" s="11" t="s">
+      <c r="I6" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="J6" s="11" t="s">
+      <c r="J6" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="K6" s="11" t="s">
+      <c r="K6" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="L6" s="11" t="s">
+      <c r="L6" s="12" t="s">
         <v>189</v>
       </c>
-      <c r="M6" s="11" t="s">
+      <c r="M6" s="12" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="39" t="n">
+      <c r="A7" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="40" t="s">
+      <c r="B7" s="38" t="s">
         <v>190</v>
       </c>
-      <c r="C7" s="41" t="s">
+      <c r="C7" s="39" t="s">
         <v>191</v>
       </c>
-      <c r="D7" s="39" t="s">
+      <c r="D7" s="37" t="s">
         <v>57</v>
       </c>
-      <c r="E7" s="42" t="n">
+      <c r="E7" s="40" t="n">
         <v>-155</v>
       </c>
-      <c r="F7" s="43" t="n">
+      <c r="F7" s="41" t="n">
         <v>200</v>
       </c>
-      <c r="G7" s="44" t="n">
+      <c r="G7" s="42" t="n">
         <f aca="false">IF(E7&gt;0,F7*E7/100,F7*100/ABS(E7))</f>
         <v>129.032258064516</v>
       </c>
-      <c r="H7" s="44" t="n">
+      <c r="H7" s="42" t="n">
         <f aca="false">F7+G7</f>
         <v>329.032258064516</v>
       </c>
-      <c r="I7" s="61" t="s">
+      <c r="I7" s="55" t="s">
         <v>91</v>
       </c>
-      <c r="J7" s="44" t="n">
+      <c r="J7" s="42" t="n">
         <f aca="false">IF(I7="Win",F7+G7,IF(I7="Push",F7,IF(I7="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K7" s="46" t="n">
+      <c r="K7" s="44" t="n">
         <f aca="false">IF(I7="Pending",0,J7-F7)</f>
         <v>0</v>
       </c>
-      <c r="L7" s="62" t="n">
+      <c r="L7" s="56" t="n">
         <v>0.62</v>
       </c>
-      <c r="M7" s="47" t="s">
+      <c r="M7" s="45" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="39" t="n">
+      <c r="A8" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="40" t="s">
+      <c r="B8" s="38" t="s">
         <v>193</v>
       </c>
-      <c r="C8" s="41" t="s">
+      <c r="C8" s="39" t="s">
         <v>194</v>
       </c>
-      <c r="D8" s="39" t="s">
+      <c r="D8" s="37" t="s">
         <v>57</v>
       </c>
-      <c r="E8" s="42" t="n">
+      <c r="E8" s="40" t="n">
         <v>-104</v>
       </c>
-      <c r="F8" s="43" t="n">
+      <c r="F8" s="41" t="n">
         <v>150</v>
       </c>
-      <c r="G8" s="44" t="n">
+      <c r="G8" s="42" t="n">
         <f aca="false">IF(E8&gt;0,F8*E8/100,F8*100/ABS(E8))</f>
         <v>144.230769230769</v>
       </c>
-      <c r="H8" s="44" t="n">
+      <c r="H8" s="42" t="n">
         <f aca="false">F8+G8</f>
         <v>294.230769230769</v>
       </c>
-      <c r="I8" s="61" t="s">
-        <v>91</v>
-      </c>
-      <c r="J8" s="44" t="n">
+      <c r="I8" s="55" t="s">
+        <v>66</v>
+      </c>
+      <c r="J8" s="42" t="n">
         <f aca="false">IF(I8="Win",F8+G8,IF(I8="Push",F8,IF(I8="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K8" s="46" t="n">
+      <c r="K8" s="44" t="n">
         <f aca="false">IF(I8="Pending",0,J8-F8)</f>
-        <v>0</v>
-      </c>
-      <c r="L8" s="62" t="n">
+        <v>-150</v>
+      </c>
+      <c r="L8" s="56" t="n">
         <v>0.54</v>
       </c>
-      <c r="M8" s="47" t="s">
+      <c r="M8" s="45" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="39" t="n">
+      <c r="A9" s="37" t="n">
         <v>3</v>
       </c>
-      <c r="B9" s="40" t="s">
+      <c r="B9" s="38" t="s">
         <v>196</v>
       </c>
-      <c r="C9" s="41" t="s">
+      <c r="C9" s="39" t="s">
         <v>197</v>
       </c>
-      <c r="D9" s="39" t="s">
+      <c r="D9" s="37" t="s">
         <v>57</v>
       </c>
-      <c r="E9" s="42" t="n">
+      <c r="E9" s="40" t="n">
         <v>-115</v>
       </c>
-      <c r="F9" s="43" t="n">
+      <c r="F9" s="41" t="n">
         <v>150</v>
       </c>
-      <c r="G9" s="44" t="n">
+      <c r="G9" s="42" t="n">
         <f aca="false">IF(E9&gt;0,F9*E9/100,F9*100/ABS(E9))</f>
         <v>130.434782608696</v>
       </c>
-      <c r="H9" s="44" t="n">
+      <c r="H9" s="42" t="n">
         <f aca="false">F9+G9</f>
         <v>280.434782608696</v>
       </c>
-      <c r="I9" s="61" t="s">
-        <v>91</v>
-      </c>
-      <c r="J9" s="44" t="n">
+      <c r="I9" s="55" t="s">
+        <v>66</v>
+      </c>
+      <c r="J9" s="42" t="n">
         <f aca="false">IF(I9="Win",F9+G9,IF(I9="Push",F9,IF(I9="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K9" s="46" t="n">
+      <c r="K9" s="44" t="n">
         <f aca="false">IF(I9="Pending",0,J9-F9)</f>
-        <v>0</v>
-      </c>
-      <c r="L9" s="62" t="n">
+        <v>-150</v>
+      </c>
+      <c r="L9" s="56" t="n">
         <v>0.55</v>
       </c>
-      <c r="M9" s="47" t="s">
+      <c r="M9" s="45" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="39" t="n">
+      <c r="A10" s="37" t="n">
         <v>4</v>
       </c>
-      <c r="B10" s="40" t="s">
+      <c r="B10" s="38" t="s">
         <v>199</v>
       </c>
-      <c r="C10" s="41" t="s">
+      <c r="C10" s="39" t="s">
         <v>200</v>
       </c>
-      <c r="D10" s="39" t="s">
+      <c r="D10" s="37" t="s">
         <v>148</v>
       </c>
-      <c r="E10" s="42" t="n">
+      <c r="E10" s="40" t="n">
         <v>-114</v>
       </c>
-      <c r="F10" s="43" t="n">
+      <c r="F10" s="41" t="n">
         <v>120</v>
       </c>
-      <c r="G10" s="44" t="n">
+      <c r="G10" s="42" t="n">
         <f aca="false">IF(E10&gt;0,F10*E10/100,F10*100/ABS(E10))</f>
         <v>105.263157894737</v>
       </c>
-      <c r="H10" s="44" t="n">
+      <c r="H10" s="42" t="n">
         <f aca="false">F10+G10</f>
         <v>225.263157894737</v>
       </c>
-      <c r="I10" s="61" t="s">
-        <v>91</v>
-      </c>
-      <c r="J10" s="44" t="n">
+      <c r="I10" s="55" t="s">
+        <v>66</v>
+      </c>
+      <c r="J10" s="42" t="n">
         <f aca="false">IF(I10="Win",F10+G10,IF(I10="Push",F10,IF(I10="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K10" s="46" t="n">
+      <c r="K10" s="44" t="n">
         <f aca="false">IF(I10="Pending",0,J10-F10)</f>
-        <v>0</v>
-      </c>
-      <c r="L10" s="62" t="n">
+        <v>-120</v>
+      </c>
+      <c r="L10" s="56" t="n">
         <v>0.55</v>
       </c>
-      <c r="M10" s="47" t="s">
+      <c r="M10" s="45" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="39" t="n">
+      <c r="A11" s="37" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="40" t="s">
+      <c r="B11" s="38" t="s">
         <v>202</v>
       </c>
-      <c r="C11" s="41" t="s">
+      <c r="C11" s="39" t="s">
         <v>203</v>
       </c>
-      <c r="D11" s="39" t="s">
+      <c r="D11" s="37" t="s">
         <v>57</v>
       </c>
-      <c r="E11" s="42" t="n">
+      <c r="E11" s="40" t="n">
         <v>104</v>
       </c>
-      <c r="F11" s="43" t="n">
+      <c r="F11" s="41" t="n">
         <v>130</v>
       </c>
-      <c r="G11" s="44" t="n">
+      <c r="G11" s="42" t="n">
         <f aca="false">IF(E11&gt;0,F11*E11/100,F11*100/ABS(E11))</f>
         <v>135.2</v>
       </c>
-      <c r="H11" s="44" t="n">
+      <c r="H11" s="42" t="n">
         <f aca="false">F11+G11</f>
         <v>265.2</v>
       </c>
-      <c r="I11" s="45" t="s">
+      <c r="I11" s="43" t="s">
         <v>58</v>
       </c>
-      <c r="J11" s="44" t="n">
+      <c r="J11" s="42" t="n">
         <f aca="false">IF(I11="Win",F11+G11,IF(I11="Push",F11,IF(I11="Loss",0,0)))</f>
         <v>265.2</v>
       </c>
-      <c r="K11" s="46" t="n">
+      <c r="K11" s="44" t="n">
         <f aca="false">IF(I11="Pending",0,J11-F11)</f>
         <v>135.2</v>
       </c>
-      <c r="L11" s="62" t="n">
+      <c r="L11" s="56" t="n">
         <v>0.52</v>
       </c>
-      <c r="M11" s="47" t="s">
+      <c r="M11" s="45" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="39" t="n">
+      <c r="A12" s="37" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="40" t="s">
+      <c r="B12" s="38" t="s">
         <v>205</v>
       </c>
-      <c r="C12" s="41" t="s">
+      <c r="C12" s="39" t="s">
         <v>206</v>
       </c>
-      <c r="D12" s="39" t="s">
+      <c r="D12" s="37" t="s">
         <v>57</v>
       </c>
-      <c r="E12" s="42" t="n">
+      <c r="E12" s="40" t="n">
         <v>108</v>
       </c>
-      <c r="F12" s="43" t="n">
+      <c r="F12" s="41" t="n">
         <v>100</v>
       </c>
-      <c r="G12" s="44" t="n">
+      <c r="G12" s="42" t="n">
         <f aca="false">IF(E12&gt;0,F12*E12/100,F12*100/ABS(E12))</f>
         <v>108</v>
       </c>
-      <c r="H12" s="44" t="n">
+      <c r="H12" s="42" t="n">
         <f aca="false">F12+G12</f>
         <v>208</v>
       </c>
-      <c r="I12" s="61" t="s">
-        <v>91</v>
-      </c>
-      <c r="J12" s="44" t="n">
+      <c r="I12" s="55" t="s">
+        <v>66</v>
+      </c>
+      <c r="J12" s="42" t="n">
         <f aca="false">IF(I12="Win",F12+G12,IF(I12="Push",F12,IF(I12="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K12" s="46" t="n">
+      <c r="K12" s="44" t="n">
         <f aca="false">IF(I12="Pending",0,J12-F12)</f>
-        <v>0</v>
-      </c>
-      <c r="L12" s="62" t="n">
+        <v>-100</v>
+      </c>
+      <c r="L12" s="56" t="n">
         <v>0.5</v>
       </c>
-      <c r="M12" s="47" t="s">
+      <c r="M12" s="45" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="39" t="n">
+      <c r="A13" s="37" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="40" t="s">
+      <c r="B13" s="38" t="s">
         <v>208</v>
       </c>
-      <c r="C13" s="41" t="s">
+      <c r="C13" s="39" t="s">
         <v>209</v>
       </c>
-      <c r="D13" s="39" t="s">
+      <c r="D13" s="37" t="s">
         <v>57</v>
       </c>
-      <c r="E13" s="42" t="n">
+      <c r="E13" s="40" t="n">
         <v>108</v>
       </c>
-      <c r="F13" s="43" t="n">
+      <c r="F13" s="41" t="n">
         <v>100</v>
       </c>
-      <c r="G13" s="44" t="n">
+      <c r="G13" s="42" t="n">
         <f aca="false">IF(E13&gt;0,F13*E13/100,F13*100/ABS(E13))</f>
         <v>108</v>
       </c>
-      <c r="H13" s="44" t="n">
+      <c r="H13" s="42" t="n">
         <f aca="false">F13+G13</f>
         <v>208</v>
       </c>
-      <c r="I13" s="61" t="s">
-        <v>91</v>
-      </c>
-      <c r="J13" s="44" t="n">
+      <c r="I13" s="55" t="s">
+        <v>58</v>
+      </c>
+      <c r="J13" s="42" t="n">
         <f aca="false">IF(I13="Win",F13+G13,IF(I13="Push",F13,IF(I13="Loss",0,0)))</f>
-        <v>0</v>
-      </c>
-      <c r="K13" s="46" t="n">
+        <v>208</v>
+      </c>
+      <c r="K13" s="44" t="n">
         <f aca="false">IF(I13="Pending",0,J13-F13)</f>
-        <v>0</v>
-      </c>
-      <c r="L13" s="62" t="n">
+        <v>108</v>
+      </c>
+      <c r="L13" s="56" t="n">
         <v>0.5</v>
       </c>
-      <c r="M13" s="47" t="s">
+      <c r="M13" s="45" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="39" t="n">
+      <c r="A14" s="37" t="n">
         <v>8</v>
       </c>
-      <c r="B14" s="40" t="s">
+      <c r="B14" s="38" t="s">
         <v>211</v>
       </c>
-      <c r="C14" s="41" t="s">
+      <c r="C14" s="39" t="s">
         <v>212</v>
       </c>
-      <c r="D14" s="39" t="s">
+      <c r="D14" s="37" t="s">
         <v>85</v>
       </c>
-      <c r="E14" s="42" t="n">
+      <c r="E14" s="40" t="n">
         <v>732</v>
       </c>
-      <c r="F14" s="43" t="n">
+      <c r="F14" s="41" t="n">
         <v>50</v>
       </c>
-      <c r="G14" s="44" t="n">
+      <c r="G14" s="42" t="n">
         <f aca="false">IF(E14&gt;0,F14*E14/100,F14*100/ABS(E14))</f>
         <v>366</v>
       </c>
-      <c r="H14" s="44" t="n">
+      <c r="H14" s="42" t="n">
         <f aca="false">F14+G14</f>
         <v>416</v>
       </c>
-      <c r="I14" s="61" t="s">
-        <v>91</v>
-      </c>
-      <c r="J14" s="44" t="n">
+      <c r="I14" s="55" t="s">
+        <v>66</v>
+      </c>
+      <c r="J14" s="42" t="n">
         <f aca="false">IF(I14="Win",F14+G14,IF(I14="Push",F14,IF(I14="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K14" s="46" t="n">
+      <c r="K14" s="44" t="n">
         <f aca="false">IF(I14="Pending",0,J14-F14)</f>
-        <v>0</v>
-      </c>
-      <c r="L14" s="62" t="n">
+        <v>-50</v>
+      </c>
+      <c r="L14" s="56" t="n">
         <v>0.14</v>
       </c>
-      <c r="M14" s="47" t="s">
+      <c r="M14" s="45" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="49"/>
-      <c r="B15" s="50" t="s">
+      <c r="A15" s="47"/>
+      <c r="B15" s="48" t="s">
         <v>35</v>
       </c>
-      <c r="C15" s="49"/>
-      <c r="D15" s="49"/>
-      <c r="E15" s="49"/>
-      <c r="F15" s="51" t="n">
+      <c r="C15" s="47"/>
+      <c r="D15" s="47"/>
+      <c r="E15" s="47"/>
+      <c r="F15" s="31" t="n">
         <f aca="false">SUM(F7:F14)</f>
         <v>1000</v>
       </c>
-      <c r="G15" s="52" t="n">
+      <c r="G15" s="32" t="n">
         <f aca="false">SUM(G7:G14)</f>
         <v>1226.16096779872</v>
       </c>
-      <c r="H15" s="52" t="n">
+      <c r="H15" s="32" t="n">
         <f aca="false">SUM(H7:H14)</f>
         <v>2226.16096779872</v>
       </c>
-      <c r="I15" s="49"/>
-      <c r="J15" s="52" t="n">
+      <c r="I15" s="47"/>
+      <c r="J15" s="32" t="n">
         <f aca="false">SUM(J7:J14)</f>
-        <v>265.2</v>
-      </c>
-      <c r="K15" s="53" t="n">
+        <v>473.2</v>
+      </c>
+      <c r="K15" s="33" t="n">
         <f aca="false">SUM(K7:K14)</f>
-        <v>135.2</v>
-      </c>
-      <c r="L15" s="63" t="n">
+        <v>-326.8</v>
+      </c>
+      <c r="L15" s="57" t="n">
         <f aca="false">SUM(L7:L14)</f>
         <v>3.92</v>
       </c>
-      <c r="M15" s="49"/>
+      <c r="M15" s="47"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="38" t="s">
+      <c r="B17" s="4" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="40" t="s">
+      <c r="B18" s="38" t="s">
         <v>88</v>
       </c>
-      <c r="C18" s="54" t="n">
+      <c r="C18" s="49" t="n">
         <f aca="false">COUNTIF(I7:I14,"Win")</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B19" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="C19" s="49" t="n">
+        <f aca="false">COUNTIF(I7:I14,"Loss")</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B20" s="38" t="s">
+        <v>90</v>
+      </c>
+      <c r="C20" s="49" t="n">
+        <f aca="false">COUNTIF(I7:I14,"Push")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B21" s="38" t="s">
+        <v>91</v>
+      </c>
+      <c r="C21" s="49" t="n">
+        <f aca="false">COUNTIF(I7:I14,"Pending")</f>
         <v>1</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="40" t="s">
-        <v>89</v>
-      </c>
-      <c r="C19" s="54" t="n">
-        <f aca="false">COUNTIF(I7:I14,"Loss")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="40" t="s">
-        <v>90</v>
-      </c>
-      <c r="C20" s="54" t="n">
-        <f aca="false">COUNTIF(I7:I14,"Push")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="40" t="s">
-        <v>91</v>
-      </c>
-      <c r="C21" s="54" t="n">
-        <f aca="false">COUNTIF(I7:I14,"Pending")</f>
-        <v>7</v>
-      </c>
-    </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="40" t="s">
+      <c r="B22" s="38" t="s">
         <v>92</v>
       </c>
-      <c r="C22" s="55" t="n">
+      <c r="C22" s="50" t="n">
         <f aca="false">IF(COUNTIF(I7:I14,"Win")+COUNTIF(I7:I14,"Loss")=0,"—",COUNTIF(I7:I14,"Win")/(COUNTIF(I7:I14,"Win")+COUNTIF(I7:I14,"Loss")))</f>
-        <v>1</v>
+        <v>0.285714285714286</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="40" t="s">
+      <c r="B23" s="38" t="s">
         <v>93</v>
       </c>
-      <c r="C23" s="56" t="n">
+      <c r="C23" s="51" t="n">
         <f aca="false">SUM(F7:F14)</f>
         <v>1000</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="40" t="s">
+      <c r="B24" s="38" t="s">
         <v>94</v>
       </c>
-      <c r="C24" s="44" t="n">
+      <c r="C24" s="42" t="n">
         <f aca="false">SUM(J7:J14)</f>
-        <v>265.2</v>
+        <v>473.2</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="40" t="s">
+      <c r="B25" s="38" t="s">
         <v>95</v>
       </c>
-      <c r="C25" s="46" t="n">
+      <c r="C25" s="44" t="n">
         <f aca="false">SUM(K7:K14)</f>
-        <v>135.2</v>
+        <v>-326.8</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="40" t="s">
+      <c r="B26" s="38" t="s">
         <v>96</v>
       </c>
-      <c r="C26" s="55" t="n">
+      <c r="C26" s="50" t="n">
         <f aca="false">IF(SUM(F7:F14)=0,"—",SUM(K7:K14)/SUM(F7:F14))</f>
-        <v>0.1352</v>
+        <v>-0.3268</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="40" t="s">
+      <c r="B27" s="38" t="s">
         <v>97</v>
       </c>
-      <c r="C27" s="44" t="n">
+      <c r="C27" s="42" t="n">
         <f aca="false">SUM(H7:H14)</f>
         <v>2226.16096779872</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="40" t="s">
+      <c r="B28" s="38" t="s">
         <v>214</v>
       </c>
-      <c r="C28" s="64" t="n">
+      <c r="C28" s="58" t="n">
         <f aca="false">SUM(L7:L14)</f>
         <v>3.92</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="40" t="s">
+      <c r="B29" s="38" t="s">
         <v>215</v>
       </c>
-      <c r="C29" s="46" t="n">
+      <c r="C29" s="44" t="n">
         <f aca="false">SUMPRODUCT(L7:L14,G7:G14)-SUMPRODUCT(1-L7:L14,F7:F14)</f>
         <v>45.1624826615033</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="38" t="s">
+      <c r="A31" s="4" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="11" t="s">
+      <c r="A32" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B32" s="11" t="s">
+      <c r="B32" s="12" t="s">
         <v>217</v>
       </c>
-      <c r="C32" s="11" t="s">
+      <c r="C32" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="D32" s="11" t="s">
+      <c r="D32" s="12" t="s">
         <v>218</v>
       </c>
-      <c r="E32" s="11" t="s">
+      <c r="E32" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="F32" s="11" t="s">
+      <c r="F32" s="12" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="39" t="n">
+      <c r="A33" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="B33" s="40" t="s">
+      <c r="B33" s="38" t="s">
         <v>219</v>
       </c>
-      <c r="C33" s="47" t="s">
+      <c r="C33" s="45" t="s">
         <v>220</v>
       </c>
-      <c r="D33" s="57" t="s">
+      <c r="D33" s="52" t="s">
         <v>221</v>
       </c>
-      <c r="E33" s="61"/>
-      <c r="F33" s="61"/>
+      <c r="E33" s="55" t="s">
+        <v>222</v>
+      </c>
+      <c r="F33" s="55" t="s">
+        <v>223</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="39" t="n">
+      <c r="A34" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="B34" s="40" t="s">
-        <v>222</v>
-      </c>
-      <c r="C34" s="47" t="s">
-        <v>223</v>
-      </c>
-      <c r="D34" s="57" t="s">
+      <c r="B34" s="38" t="s">
         <v>224</v>
       </c>
-      <c r="E34" s="61"/>
-      <c r="F34" s="61"/>
+      <c r="C34" s="45" t="s">
+        <v>225</v>
+      </c>
+      <c r="D34" s="52" t="s">
+        <v>226</v>
+      </c>
+      <c r="E34" s="55" t="s">
+        <v>227</v>
+      </c>
+      <c r="F34" s="55" t="s">
+        <v>228</v>
+      </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="39" t="n">
+      <c r="A35" s="37" t="n">
         <v>3</v>
       </c>
-      <c r="B35" s="40" t="s">
-        <v>225</v>
-      </c>
-      <c r="C35" s="47" t="s">
-        <v>226</v>
-      </c>
-      <c r="D35" s="57" t="s">
-        <v>227</v>
-      </c>
-      <c r="E35" s="61"/>
-      <c r="F35" s="61"/>
+      <c r="B35" s="38" t="s">
+        <v>229</v>
+      </c>
+      <c r="C35" s="45" t="s">
+        <v>230</v>
+      </c>
+      <c r="D35" s="52" t="s">
+        <v>231</v>
+      </c>
+      <c r="E35" s="55" t="s">
+        <v>232</v>
+      </c>
+      <c r="F35" s="55" t="s">
+        <v>233</v>
+      </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="39" t="n">
+      <c r="A36" s="37" t="n">
         <v>4</v>
       </c>
-      <c r="B36" s="40" t="s">
-        <v>228</v>
-      </c>
-      <c r="C36" s="47" t="s">
-        <v>229</v>
-      </c>
-      <c r="D36" s="57" t="s">
-        <v>230</v>
-      </c>
-      <c r="E36" s="61"/>
-      <c r="F36" s="61"/>
+      <c r="B36" s="38" t="s">
+        <v>234</v>
+      </c>
+      <c r="C36" s="45" t="s">
+        <v>235</v>
+      </c>
+      <c r="D36" s="52" t="s">
+        <v>236</v>
+      </c>
+      <c r="E36" s="55"/>
+      <c r="F36" s="55"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="39" t="n">
+      <c r="A37" s="37" t="n">
         <v>5</v>
       </c>
-      <c r="B37" s="40" t="s">
-        <v>231</v>
-      </c>
-      <c r="C37" s="47" t="s">
-        <v>232</v>
-      </c>
-      <c r="D37" s="57" t="s">
-        <v>233</v>
-      </c>
-      <c r="E37" s="61"/>
-      <c r="F37" s="61"/>
+      <c r="B37" s="38" t="s">
+        <v>237</v>
+      </c>
+      <c r="C37" s="45" t="s">
+        <v>238</v>
+      </c>
+      <c r="D37" s="52" t="s">
+        <v>239</v>
+      </c>
+      <c r="E37" s="55" t="s">
+        <v>240</v>
+      </c>
+      <c r="F37" s="55" t="s">
+        <v>241</v>
+      </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="39" t="n">
+      <c r="A38" s="37" t="n">
         <v>6</v>
       </c>
-      <c r="B38" s="40" t="s">
-        <v>234</v>
-      </c>
-      <c r="C38" s="47" t="s">
-        <v>235</v>
-      </c>
-      <c r="D38" s="57" t="s">
-        <v>236</v>
-      </c>
-      <c r="E38" s="61"/>
-      <c r="F38" s="61"/>
+      <c r="B38" s="38" t="s">
+        <v>242</v>
+      </c>
+      <c r="C38" s="45" t="s">
+        <v>243</v>
+      </c>
+      <c r="D38" s="52" t="s">
+        <v>244</v>
+      </c>
+      <c r="E38" s="55"/>
+      <c r="F38" s="55"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="39" t="n">
+      <c r="A39" s="37" t="n">
         <v>7</v>
       </c>
-      <c r="B39" s="40" t="s">
-        <v>237</v>
-      </c>
-      <c r="C39" s="47" t="s">
-        <v>238</v>
-      </c>
-      <c r="D39" s="57" t="s">
-        <v>239</v>
-      </c>
-      <c r="E39" s="61"/>
-      <c r="F39" s="61"/>
+      <c r="B39" s="38" t="s">
+        <v>245</v>
+      </c>
+      <c r="C39" s="45" t="s">
+        <v>246</v>
+      </c>
+      <c r="D39" s="52" t="s">
+        <v>247</v>
+      </c>
+      <c r="E39" s="55"/>
+      <c r="F39" s="55"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="39" t="n">
+      <c r="A40" s="37" t="n">
         <v>8</v>
       </c>
-      <c r="B40" s="40" t="s">
-        <v>240</v>
-      </c>
-      <c r="C40" s="47" t="s">
-        <v>241</v>
-      </c>
-      <c r="D40" s="57" t="s">
-        <v>242</v>
-      </c>
-      <c r="E40" s="61"/>
-      <c r="F40" s="61"/>
+      <c r="B40" s="38" t="s">
+        <v>248</v>
+      </c>
+      <c r="C40" s="45" t="s">
+        <v>249</v>
+      </c>
+      <c r="D40" s="52" t="s">
+        <v>250</v>
+      </c>
+      <c r="E40" s="55"/>
+      <c r="F40" s="55"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="59" t="s">
-        <v>243</v>
+      <c r="A42" s="34" t="s">
+        <v>251</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="K7:K15">
-    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>AND(ISNUMBER(K7),K7&gt;0)</formula>
     </cfRule>
-    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>AND(ISNUMBER(K7),K7&lt;0)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C25:C26">
-    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>AND(ISNUMBER(C25),C25&gt;0)</formula>
     </cfRule>
-    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>AND(ISNUMBER(C25),C25&lt;0)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C29">
-    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>AND(ISNUMBER(C29),C29&gt;0)</formula>
     </cfRule>
-    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>AND(ISNUMBER(C29),C29&lt;0)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4476,555 +4461,555 @@
   <dimension ref="A1:M29"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="34" width="5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="34" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="34" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="34" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="34" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="34" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="34" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="9" style="34" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="34" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="34" width="50"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="9" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="50"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="35" t="s">
-        <v>244</v>
-      </c>
-      <c r="H1" s="60" t="s">
-        <v>245</v>
+        <v>252</v>
+      </c>
+      <c r="H1" s="54" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="37" t="s">
-        <v>246</v>
+      <c r="A2" s="3" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="65" t="s">
-        <v>247</v>
+      <c r="A3" s="59" t="s">
+        <v>255</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="38" t="s">
+      <c r="A5" s="4" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="12" t="s">
         <v>169</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D6" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="E6" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="F6" s="11" t="s">
+      <c r="F6" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="G6" s="11" t="s">
+      <c r="G6" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="H6" s="11" t="s">
+      <c r="H6" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="I6" s="11" t="s">
+      <c r="I6" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="J6" s="11" t="s">
+      <c r="J6" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="K6" s="11" t="s">
+      <c r="K6" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="L6" s="11" t="s">
+      <c r="L6" s="12" t="s">
         <v>189</v>
       </c>
-      <c r="M6" s="11" t="s">
+      <c r="M6" s="12" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="39" t="n">
+      <c r="A7" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>248</v>
-      </c>
-      <c r="C7" s="66" t="s">
-        <v>249</v>
-      </c>
-      <c r="D7" s="39" t="s">
-        <v>250</v>
-      </c>
-      <c r="E7" s="42" t="n">
+      <c r="B7" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="C7" s="60" t="s">
+        <v>257</v>
+      </c>
+      <c r="D7" s="37" t="s">
+        <v>258</v>
+      </c>
+      <c r="E7" s="40" t="n">
         <v>-113</v>
       </c>
-      <c r="F7" s="43" t="n">
+      <c r="F7" s="41" t="n">
         <v>300</v>
       </c>
-      <c r="G7" s="44" t="n">
+      <c r="G7" s="42" t="n">
         <f aca="false">IF(E7&gt;0,F7*E7/100,F7*100/ABS(E7))</f>
         <v>265.486725663717</v>
       </c>
-      <c r="H7" s="44" t="n">
+      <c r="H7" s="42" t="n">
         <f aca="false">F7+G7</f>
         <v>565.486725663717</v>
       </c>
-      <c r="I7" s="61" t="s">
+      <c r="I7" s="55" t="s">
         <v>91</v>
       </c>
-      <c r="J7" s="44" t="n">
+      <c r="J7" s="42" t="n">
         <f aca="false">IF(I7="Win",F7+G7,IF(I7="Push",F7,IF(I7="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K7" s="46" t="n">
+      <c r="K7" s="44" t="n">
         <f aca="false">IF(I7="Pending",0,J7-F7)</f>
         <v>0</v>
       </c>
-      <c r="L7" s="62" t="n">
+      <c r="L7" s="56" t="n">
         <v>0.58</v>
       </c>
-      <c r="M7" s="67" t="s">
-        <v>251</v>
+      <c r="M7" s="61" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="39" t="n">
+      <c r="A8" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="C8" s="66" t="s">
-        <v>253</v>
-      </c>
-      <c r="D8" s="39" t="s">
+      <c r="B8" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="C8" s="60" t="s">
+        <v>261</v>
+      </c>
+      <c r="D8" s="37" t="s">
         <v>62</v>
       </c>
-      <c r="E8" s="42" t="n">
+      <c r="E8" s="40" t="n">
         <v>456</v>
       </c>
-      <c r="F8" s="43" t="n">
+      <c r="F8" s="41" t="n">
         <v>200</v>
       </c>
-      <c r="G8" s="44" t="n">
+      <c r="G8" s="42" t="n">
         <f aca="false">IF(E8&gt;0,F8*E8/100,F8*100/ABS(E8))</f>
         <v>912</v>
       </c>
-      <c r="H8" s="44" t="n">
+      <c r="H8" s="42" t="n">
         <f aca="false">F8+G8</f>
         <v>1112</v>
       </c>
-      <c r="I8" s="61" t="s">
+      <c r="I8" s="55" t="s">
         <v>91</v>
       </c>
-      <c r="J8" s="44" t="n">
+      <c r="J8" s="42" t="n">
         <f aca="false">IF(I8="Win",F8+G8,IF(I8="Push",F8,IF(I8="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K8" s="46" t="n">
+      <c r="K8" s="44" t="n">
         <f aca="false">IF(I8="Pending",0,J8-F8)</f>
         <v>0</v>
       </c>
-      <c r="L8" s="62" t="n">
+      <c r="L8" s="56" t="n">
         <v>0.24</v>
       </c>
-      <c r="M8" s="67" t="s">
-        <v>254</v>
+      <c r="M8" s="61" t="s">
+        <v>262</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="39" t="n">
+      <c r="A9" s="37" t="n">
         <v>3</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>255</v>
-      </c>
-      <c r="C9" s="66" t="s">
-        <v>256</v>
-      </c>
-      <c r="D9" s="39" t="s">
+      <c r="B9" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="C9" s="60" t="s">
+        <v>264</v>
+      </c>
+      <c r="D9" s="37" t="s">
         <v>159</v>
       </c>
-      <c r="E9" s="42" t="n">
+      <c r="E9" s="40" t="n">
         <v>1150</v>
       </c>
-      <c r="F9" s="43" t="n">
+      <c r="F9" s="41" t="n">
         <v>150</v>
       </c>
-      <c r="G9" s="44" t="n">
+      <c r="G9" s="42" t="n">
         <f aca="false">IF(E9&gt;0,F9*E9/100,F9*100/ABS(E9))</f>
         <v>1725</v>
       </c>
-      <c r="H9" s="44" t="n">
+      <c r="H9" s="42" t="n">
         <f aca="false">F9+G9</f>
         <v>1875</v>
       </c>
-      <c r="I9" s="61" t="s">
+      <c r="I9" s="55" t="s">
         <v>91</v>
       </c>
-      <c r="J9" s="44" t="n">
+      <c r="J9" s="42" t="n">
         <f aca="false">IF(I9="Win",F9+G9,IF(I9="Push",F9,IF(I9="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K9" s="46" t="n">
+      <c r="K9" s="44" t="n">
         <f aca="false">IF(I9="Pending",0,J9-F9)</f>
         <v>0</v>
       </c>
-      <c r="L9" s="62" t="n">
+      <c r="L9" s="56" t="n">
         <v>0.1</v>
       </c>
-      <c r="M9" s="67" t="s">
-        <v>257</v>
+      <c r="M9" s="61" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="39" t="n">
+      <c r="A10" s="37" t="n">
         <v>4</v>
       </c>
-      <c r="B10" s="4" t="s">
-        <v>258</v>
-      </c>
-      <c r="C10" s="66" t="s">
-        <v>256</v>
-      </c>
-      <c r="D10" s="39" t="s">
+      <c r="B10" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="C10" s="60" t="s">
+        <v>264</v>
+      </c>
+      <c r="D10" s="37" t="s">
         <v>159</v>
       </c>
-      <c r="E10" s="42" t="n">
+      <c r="E10" s="40" t="n">
         <v>1567</v>
       </c>
-      <c r="F10" s="43" t="n">
+      <c r="F10" s="41" t="n">
         <v>120</v>
       </c>
-      <c r="G10" s="44" t="n">
+      <c r="G10" s="42" t="n">
         <f aca="false">IF(E10&gt;0,F10*E10/100,F10*100/ABS(E10))</f>
         <v>1880.4</v>
       </c>
-      <c r="H10" s="44" t="n">
+      <c r="H10" s="42" t="n">
         <f aca="false">F10+G10</f>
         <v>2000.4</v>
       </c>
-      <c r="I10" s="61" t="s">
+      <c r="I10" s="55" t="s">
         <v>91</v>
       </c>
-      <c r="J10" s="44" t="n">
+      <c r="J10" s="42" t="n">
         <f aca="false">IF(I10="Win",F10+G10,IF(I10="Push",F10,IF(I10="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K10" s="46" t="n">
+      <c r="K10" s="44" t="n">
         <f aca="false">IF(I10="Pending",0,J10-F10)</f>
         <v>0</v>
       </c>
-      <c r="L10" s="62" t="n">
+      <c r="L10" s="56" t="n">
         <v>0.08</v>
       </c>
-      <c r="M10" s="67" t="s">
-        <v>259</v>
+      <c r="M10" s="61" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="39" t="n">
+      <c r="A11" s="37" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="4" t="s">
-        <v>260</v>
-      </c>
-      <c r="C11" s="66" t="s">
-        <v>256</v>
-      </c>
-      <c r="D11" s="39" t="s">
+      <c r="B11" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="C11" s="60" t="s">
+        <v>264</v>
+      </c>
+      <c r="D11" s="37" t="s">
         <v>159</v>
       </c>
-      <c r="E11" s="42" t="n">
+      <c r="E11" s="40" t="n">
         <v>1800</v>
       </c>
-      <c r="F11" s="43" t="n">
+      <c r="F11" s="41" t="n">
         <v>100</v>
       </c>
-      <c r="G11" s="44" t="n">
+      <c r="G11" s="42" t="n">
         <f aca="false">IF(E11&gt;0,F11*E11/100,F11*100/ABS(E11))</f>
         <v>1800</v>
       </c>
-      <c r="H11" s="44" t="n">
+      <c r="H11" s="42" t="n">
         <f aca="false">F11+G11</f>
         <v>1900</v>
       </c>
-      <c r="I11" s="61" t="s">
+      <c r="I11" s="55" t="s">
         <v>91</v>
       </c>
-      <c r="J11" s="44" t="n">
+      <c r="J11" s="42" t="n">
         <f aca="false">IF(I11="Win",F11+G11,IF(I11="Push",F11,IF(I11="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K11" s="46" t="n">
+      <c r="K11" s="44" t="n">
         <f aca="false">IF(I11="Pending",0,J11-F11)</f>
         <v>0</v>
       </c>
-      <c r="L11" s="62" t="n">
+      <c r="L11" s="56" t="n">
         <v>0.07</v>
       </c>
-      <c r="M11" s="67" t="s">
-        <v>261</v>
+      <c r="M11" s="61" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="39" t="n">
+      <c r="A12" s="37" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="C12" s="66" t="s">
-        <v>256</v>
-      </c>
-      <c r="D12" s="39" t="s">
+      <c r="B12" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="C12" s="60" t="s">
+        <v>264</v>
+      </c>
+      <c r="D12" s="37" t="s">
         <v>159</v>
       </c>
-      <c r="E12" s="42" t="n">
+      <c r="E12" s="40" t="n">
         <v>1150</v>
       </c>
-      <c r="F12" s="43" t="n">
+      <c r="F12" s="41" t="n">
         <v>90</v>
       </c>
-      <c r="G12" s="44" t="n">
+      <c r="G12" s="42" t="n">
         <f aca="false">IF(E12&gt;0,F12*E12/100,F12*100/ABS(E12))</f>
         <v>1035</v>
       </c>
-      <c r="H12" s="44" t="n">
+      <c r="H12" s="42" t="n">
         <f aca="false">F12+G12</f>
         <v>1125</v>
       </c>
-      <c r="I12" s="61" t="s">
+      <c r="I12" s="55" t="s">
         <v>91</v>
       </c>
-      <c r="J12" s="44" t="n">
+      <c r="J12" s="42" t="n">
         <f aca="false">IF(I12="Win",F12+G12,IF(I12="Push",F12,IF(I12="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K12" s="46" t="n">
+      <c r="K12" s="44" t="n">
         <f aca="false">IF(I12="Pending",0,J12-F12)</f>
         <v>0</v>
       </c>
-      <c r="L12" s="62" t="n">
+      <c r="L12" s="56" t="n">
         <v>0.08</v>
       </c>
-      <c r="M12" s="67" t="s">
-        <v>263</v>
+      <c r="M12" s="61" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="39" t="n">
+      <c r="A13" s="37" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="C13" s="60" t="s">
         <v>264</v>
       </c>
-      <c r="C13" s="66" t="s">
-        <v>256</v>
-      </c>
-      <c r="D13" s="39" t="s">
+      <c r="D13" s="37" t="s">
         <v>159</v>
       </c>
-      <c r="E13" s="42" t="n">
+      <c r="E13" s="40" t="n">
         <v>1900</v>
       </c>
-      <c r="F13" s="43" t="n">
+      <c r="F13" s="41" t="n">
         <v>40</v>
       </c>
-      <c r="G13" s="44" t="n">
+      <c r="G13" s="42" t="n">
         <f aca="false">IF(E13&gt;0,F13*E13/100,F13*100/ABS(E13))</f>
         <v>760</v>
       </c>
-      <c r="H13" s="44" t="n">
+      <c r="H13" s="42" t="n">
         <f aca="false">F13+G13</f>
         <v>800</v>
       </c>
-      <c r="I13" s="61" t="s">
+      <c r="I13" s="55" t="s">
         <v>91</v>
       </c>
-      <c r="J13" s="44" t="n">
+      <c r="J13" s="42" t="n">
         <f aca="false">IF(I13="Win",F13+G13,IF(I13="Push",F13,IF(I13="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K13" s="46" t="n">
+      <c r="K13" s="44" t="n">
         <f aca="false">IF(I13="Pending",0,J13-F13)</f>
         <v>0</v>
       </c>
-      <c r="L13" s="62" t="n">
+      <c r="L13" s="56" t="n">
         <v>0.05</v>
       </c>
-      <c r="M13" s="67" t="s">
-        <v>265</v>
+      <c r="M13" s="61" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="28"/>
-      <c r="B14" s="29" t="s">
+      <c r="A14" s="29"/>
+      <c r="B14" s="30" t="s">
         <v>35</v>
       </c>
-      <c r="C14" s="28"/>
-      <c r="D14" s="28"/>
-      <c r="E14" s="28"/>
-      <c r="F14" s="51" t="n">
+      <c r="C14" s="29"/>
+      <c r="D14" s="29"/>
+      <c r="E14" s="29"/>
+      <c r="F14" s="31" t="n">
         <f aca="false">SUM(F7:F13)</f>
         <v>1000</v>
       </c>
-      <c r="G14" s="52" t="n">
+      <c r="G14" s="32" t="n">
         <f aca="false">SUM(G7:G13)</f>
         <v>8377.88672566372</v>
       </c>
-      <c r="H14" s="52" t="n">
+      <c r="H14" s="32" t="n">
         <f aca="false">SUM(H7:H13)</f>
         <v>9377.88672566372</v>
       </c>
-      <c r="I14" s="28"/>
-      <c r="J14" s="52" t="n">
+      <c r="I14" s="29"/>
+      <c r="J14" s="32" t="n">
         <f aca="false">SUM(J7:J13)</f>
         <v>0</v>
       </c>
-      <c r="K14" s="53" t="n">
+      <c r="K14" s="33" t="n">
         <f aca="false">SUM(K7:K13)</f>
         <v>0</v>
       </c>
-      <c r="L14" s="63" t="n">
+      <c r="L14" s="57" t="n">
         <f aca="false">SUM(L7:L13)</f>
         <v>1.2</v>
       </c>
-      <c r="M14" s="28"/>
+      <c r="M14" s="29"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="38" t="s">
+      <c r="B16" s="4" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="C17" s="54" t="n">
+      <c r="C17" s="49" t="n">
         <f aca="false">COUNTIF(I7:I13,"Win")</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="C18" s="54" t="n">
+      <c r="C18" s="49" t="n">
         <f aca="false">COUNTIF(I7:I13,"Loss")</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="C19" s="54" t="n">
+      <c r="C19" s="49" t="n">
         <f aca="false">COUNTIF(I7:I13,"Push")</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="C20" s="54" t="n">
+      <c r="C20" s="49" t="n">
         <f aca="false">COUNTIF(I7:I13,"Pending")</f>
         <v>7</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="C21" s="55" t="str">
+      <c r="C21" s="50" t="str">
         <f aca="false">IF(COUNTIF(I7:I13,"Win")+COUNTIF(I7:I13,"Loss")=0,"—",COUNTIF(I7:I13,"Win")/(COUNTIF(I7:I13,"Win")+COUNTIF(I7:I13,"Loss")))</f>
         <v>—</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="C22" s="56" t="n">
+      <c r="C22" s="51" t="n">
         <f aca="false">SUM(F7:F13)</f>
         <v>1000</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="C23" s="44" t="n">
+      <c r="C23" s="42" t="n">
         <f aca="false">SUM(J7:J13)</f>
         <v>0</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="C24" s="46" t="n">
+      <c r="C24" s="44" t="n">
         <f aca="false">SUM(K7:K13)</f>
         <v>0</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="C25" s="55" t="n">
+      <c r="C25" s="50" t="n">
         <f aca="false">IF(SUM(F7:F13)=0,"—",SUM(K7:K13)/SUM(F7:F13))</f>
         <v>0</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="4" t="s">
+      <c r="B26" s="5" t="s">
         <v>214</v>
       </c>
-      <c r="C26" s="64" t="n">
+      <c r="C26" s="58" t="n">
         <f aca="false">SUM(L7:L13)</f>
         <v>1.2</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="4" t="s">
-        <v>266</v>
-      </c>
-      <c r="C27" s="56" t="n">
+      <c r="B27" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="C27" s="51" t="n">
         <f aca="false">2678</f>
         <v>2678</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="59" t="s">
-        <v>267</v>
+      <c r="A29" s="34" t="s">
+        <v>275</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="K7:K14">
-    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>AND(ISNUMBER(K7),K7&gt;0)</formula>
     </cfRule>
-    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>AND(ISNUMBER(K7),K7&lt;0)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C24:C25">
-    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>AND(ISNUMBER(C24),C24&gt;0)</formula>
     </cfRule>
-    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>AND(ISNUMBER(C24),C24&lt;0)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5052,346 +5037,346 @@
   <dimension ref="A1:G25"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="34" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="34" width="38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="34" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="34" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="34" width="48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="48"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="35" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="37" t="s">
-        <v>269</v>
+      <c r="A2" s="3" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="11" t="s">
-        <v>270</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>271</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>272</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>273</v>
-      </c>
-      <c r="E4" s="11" t="s">
-        <v>274</v>
-      </c>
-      <c r="F4" s="11" t="s">
-        <v>275</v>
-      </c>
-      <c r="G4" s="11" t="s">
+      <c r="A4" s="12" t="s">
+        <v>278</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>279</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>280</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>281</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>282</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>283</v>
+      </c>
+      <c r="G4" s="12" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
-        <v>276</v>
-      </c>
-      <c r="B5" s="68" t="s">
-        <v>277</v>
-      </c>
-      <c r="C5" s="69"/>
-      <c r="D5" s="69" t="s">
-        <v>278</v>
-      </c>
-      <c r="E5" s="69" t="s">
-        <v>278</v>
-      </c>
-      <c r="F5" s="69"/>
-      <c r="G5" s="70" t="s">
-        <v>279</v>
+      <c r="A5" s="5" t="s">
+        <v>284</v>
+      </c>
+      <c r="B5" s="62" t="s">
+        <v>285</v>
+      </c>
+      <c r="C5" s="63"/>
+      <c r="D5" s="63" t="s">
+        <v>286</v>
+      </c>
+      <c r="E5" s="63" t="s">
+        <v>286</v>
+      </c>
+      <c r="F5" s="63"/>
+      <c r="G5" s="64" t="s">
+        <v>287</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
-        <v>280</v>
-      </c>
-      <c r="B6" s="68" t="s">
-        <v>281</v>
-      </c>
-      <c r="C6" s="69" t="s">
-        <v>278</v>
-      </c>
-      <c r="D6" s="69"/>
-      <c r="E6" s="69"/>
-      <c r="F6" s="69"/>
-      <c r="G6" s="70" t="s">
-        <v>282</v>
+      <c r="A6" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="B6" s="62" t="s">
+        <v>289</v>
+      </c>
+      <c r="C6" s="63" t="s">
+        <v>286</v>
+      </c>
+      <c r="D6" s="63"/>
+      <c r="E6" s="63"/>
+      <c r="F6" s="63"/>
+      <c r="G6" s="64" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
-        <v>283</v>
-      </c>
-      <c r="B7" s="68" t="s">
-        <v>284</v>
-      </c>
-      <c r="C7" s="69" t="s">
-        <v>278</v>
-      </c>
-      <c r="D7" s="69"/>
-      <c r="E7" s="69"/>
-      <c r="F7" s="69"/>
-      <c r="G7" s="70" t="s">
-        <v>285</v>
+      <c r="A7" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="B7" s="62" t="s">
+        <v>292</v>
+      </c>
+      <c r="C7" s="63" t="s">
+        <v>286</v>
+      </c>
+      <c r="D7" s="63"/>
+      <c r="E7" s="63"/>
+      <c r="F7" s="63"/>
+      <c r="G7" s="64" t="s">
+        <v>293</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="B8" s="62" t="s">
+        <v>295</v>
+      </c>
+      <c r="C8" s="63"/>
+      <c r="D8" s="63" t="s">
         <v>286</v>
       </c>
-      <c r="B8" s="68" t="s">
-        <v>287</v>
-      </c>
-      <c r="C8" s="69"/>
-      <c r="D8" s="69" t="s">
-        <v>278</v>
-      </c>
-      <c r="E8" s="69"/>
-      <c r="F8" s="69"/>
-      <c r="G8" s="70" t="s">
-        <v>288</v>
+      <c r="E8" s="63"/>
+      <c r="F8" s="63"/>
+      <c r="G8" s="64" t="s">
+        <v>296</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
-        <v>289</v>
-      </c>
-      <c r="B9" s="68" t="s">
-        <v>290</v>
-      </c>
-      <c r="C9" s="69"/>
-      <c r="D9" s="69" t="s">
-        <v>278</v>
-      </c>
-      <c r="E9" s="69"/>
-      <c r="F9" s="69" t="s">
-        <v>278</v>
-      </c>
-      <c r="G9" s="70" t="s">
-        <v>291</v>
+      <c r="A9" s="5" t="s">
+        <v>297</v>
+      </c>
+      <c r="B9" s="62" t="s">
+        <v>298</v>
+      </c>
+      <c r="C9" s="63"/>
+      <c r="D9" s="63" t="s">
+        <v>286</v>
+      </c>
+      <c r="E9" s="63"/>
+      <c r="F9" s="63" t="s">
+        <v>286</v>
+      </c>
+      <c r="G9" s="64" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
-        <v>292</v>
-      </c>
-      <c r="B10" s="68" t="s">
-        <v>293</v>
-      </c>
-      <c r="C10" s="69"/>
-      <c r="D10" s="69" t="s">
-        <v>278</v>
-      </c>
-      <c r="E10" s="69" t="s">
-        <v>278</v>
-      </c>
-      <c r="F10" s="69"/>
-      <c r="G10" s="70" t="s">
-        <v>294</v>
+      <c r="A10" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="B10" s="62" t="s">
+        <v>301</v>
+      </c>
+      <c r="C10" s="63"/>
+      <c r="D10" s="63" t="s">
+        <v>286</v>
+      </c>
+      <c r="E10" s="63" t="s">
+        <v>286</v>
+      </c>
+      <c r="F10" s="63"/>
+      <c r="G10" s="64" t="s">
+        <v>302</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
-        <v>295</v>
-      </c>
-      <c r="B11" s="68" t="s">
-        <v>296</v>
-      </c>
-      <c r="C11" s="69"/>
-      <c r="D11" s="69" t="s">
-        <v>278</v>
-      </c>
-      <c r="E11" s="69"/>
-      <c r="F11" s="69"/>
-      <c r="G11" s="70" t="s">
-        <v>297</v>
+      <c r="A11" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="B11" s="62" t="s">
+        <v>304</v>
+      </c>
+      <c r="C11" s="63"/>
+      <c r="D11" s="63" t="s">
+        <v>286</v>
+      </c>
+      <c r="E11" s="63"/>
+      <c r="F11" s="63"/>
+      <c r="G11" s="64" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="s">
-        <v>298</v>
-      </c>
-      <c r="B12" s="68" t="s">
-        <v>299</v>
-      </c>
-      <c r="C12" s="69"/>
-      <c r="D12" s="69" t="s">
-        <v>278</v>
-      </c>
-      <c r="E12" s="69"/>
-      <c r="F12" s="69" t="s">
-        <v>278</v>
-      </c>
-      <c r="G12" s="70" t="s">
-        <v>300</v>
+      <c r="A12" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="B12" s="62" t="s">
+        <v>307</v>
+      </c>
+      <c r="C12" s="63"/>
+      <c r="D12" s="63" t="s">
+        <v>286</v>
+      </c>
+      <c r="E12" s="63"/>
+      <c r="F12" s="63" t="s">
+        <v>286</v>
+      </c>
+      <c r="G12" s="64" t="s">
+        <v>308</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="s">
-        <v>301</v>
-      </c>
-      <c r="B13" s="68" t="s">
-        <v>302</v>
-      </c>
-      <c r="C13" s="69"/>
-      <c r="D13" s="69" t="s">
-        <v>278</v>
-      </c>
-      <c r="E13" s="69"/>
-      <c r="F13" s="69"/>
-      <c r="G13" s="70" t="s">
-        <v>303</v>
+      <c r="A13" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="B13" s="62" t="s">
+        <v>310</v>
+      </c>
+      <c r="C13" s="63"/>
+      <c r="D13" s="63" t="s">
+        <v>286</v>
+      </c>
+      <c r="E13" s="63"/>
+      <c r="F13" s="63"/>
+      <c r="G13" s="64" t="s">
+        <v>311</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="s">
-        <v>304</v>
-      </c>
-      <c r="B14" s="68" t="s">
-        <v>305</v>
-      </c>
-      <c r="C14" s="69"/>
-      <c r="D14" s="69" t="s">
-        <v>278</v>
-      </c>
-      <c r="E14" s="69"/>
-      <c r="F14" s="69"/>
-      <c r="G14" s="70" t="s">
-        <v>306</v>
+      <c r="A14" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="B14" s="62" t="s">
+        <v>313</v>
+      </c>
+      <c r="C14" s="63"/>
+      <c r="D14" s="63" t="s">
+        <v>286</v>
+      </c>
+      <c r="E14" s="63"/>
+      <c r="F14" s="63"/>
+      <c r="G14" s="64" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="s">
-        <v>307</v>
-      </c>
-      <c r="B15" s="68" t="s">
-        <v>308</v>
-      </c>
-      <c r="C15" s="69"/>
-      <c r="D15" s="69" t="s">
-        <v>278</v>
-      </c>
-      <c r="E15" s="69"/>
-      <c r="F15" s="69"/>
-      <c r="G15" s="70" t="s">
-        <v>309</v>
+      <c r="A15" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="B15" s="62" t="s">
+        <v>316</v>
+      </c>
+      <c r="C15" s="63"/>
+      <c r="D15" s="63" t="s">
+        <v>286</v>
+      </c>
+      <c r="E15" s="63"/>
+      <c r="F15" s="63"/>
+      <c r="G15" s="64" t="s">
+        <v>317</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="s">
-        <v>310</v>
-      </c>
-      <c r="B16" s="68" t="s">
-        <v>311</v>
-      </c>
-      <c r="C16" s="69"/>
-      <c r="D16" s="69" t="s">
-        <v>278</v>
-      </c>
-      <c r="E16" s="69"/>
-      <c r="F16" s="69"/>
-      <c r="G16" s="70" t="s">
-        <v>312</v>
+      <c r="A16" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="B16" s="62" t="s">
+        <v>319</v>
+      </c>
+      <c r="C16" s="63"/>
+      <c r="D16" s="63" t="s">
+        <v>286</v>
+      </c>
+      <c r="E16" s="63"/>
+      <c r="F16" s="63"/>
+      <c r="G16" s="64" t="s">
+        <v>320</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="s">
-        <v>313</v>
-      </c>
-      <c r="B17" s="68" t="s">
-        <v>314</v>
-      </c>
-      <c r="C17" s="69"/>
-      <c r="D17" s="69"/>
-      <c r="E17" s="69" t="s">
-        <v>278</v>
-      </c>
-      <c r="F17" s="69" t="s">
-        <v>278</v>
-      </c>
-      <c r="G17" s="70" t="s">
-        <v>315</v>
+      <c r="A17" s="5" t="s">
+        <v>321</v>
+      </c>
+      <c r="B17" s="62" t="s">
+        <v>322</v>
+      </c>
+      <c r="C17" s="63"/>
+      <c r="D17" s="63"/>
+      <c r="E17" s="63" t="s">
+        <v>286</v>
+      </c>
+      <c r="F17" s="63" t="s">
+        <v>286</v>
+      </c>
+      <c r="G17" s="64" t="s">
+        <v>323</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4" t="s">
-        <v>316</v>
-      </c>
-      <c r="B18" s="68" t="s">
-        <v>317</v>
-      </c>
-      <c r="C18" s="69"/>
-      <c r="D18" s="69"/>
-      <c r="E18" s="69" t="s">
-        <v>278</v>
-      </c>
-      <c r="F18" s="69"/>
-      <c r="G18" s="70" t="s">
-        <v>318</v>
+      <c r="A18" s="5" t="s">
+        <v>324</v>
+      </c>
+      <c r="B18" s="62" t="s">
+        <v>325</v>
+      </c>
+      <c r="C18" s="63"/>
+      <c r="D18" s="63"/>
+      <c r="E18" s="63" t="s">
+        <v>286</v>
+      </c>
+      <c r="F18" s="63"/>
+      <c r="G18" s="64" t="s">
+        <v>326</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4" t="s">
-        <v>319</v>
-      </c>
-      <c r="B19" s="68" t="s">
-        <v>320</v>
-      </c>
-      <c r="C19" s="69"/>
-      <c r="D19" s="69"/>
-      <c r="E19" s="69" t="s">
-        <v>278</v>
-      </c>
-      <c r="F19" s="69"/>
-      <c r="G19" s="70" t="s">
-        <v>321</v>
+      <c r="A19" s="5" t="s">
+        <v>327</v>
+      </c>
+      <c r="B19" s="62" t="s">
+        <v>328</v>
+      </c>
+      <c r="C19" s="63"/>
+      <c r="D19" s="63"/>
+      <c r="E19" s="63" t="s">
+        <v>286</v>
+      </c>
+      <c r="F19" s="63"/>
+      <c r="G19" s="64" t="s">
+        <v>329</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="4" t="s">
-        <v>322</v>
-      </c>
-      <c r="B20" s="68" t="s">
-        <v>323</v>
-      </c>
-      <c r="C20" s="69"/>
-      <c r="D20" s="69"/>
-      <c r="E20" s="69"/>
-      <c r="F20" s="69" t="s">
-        <v>278</v>
-      </c>
-      <c r="G20" s="70" t="s">
-        <v>324</v>
+      <c r="A20" s="5" t="s">
+        <v>330</v>
+      </c>
+      <c r="B20" s="62" t="s">
+        <v>331</v>
+      </c>
+      <c r="C20" s="63"/>
+      <c r="D20" s="63"/>
+      <c r="E20" s="63"/>
+      <c r="F20" s="63" t="s">
+        <v>286</v>
+      </c>
+      <c r="G20" s="64" t="s">
+        <v>332</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="71" t="s">
-        <v>325</v>
+      <c r="A22" s="65" t="s">
+        <v>333</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="37" t="s">
-        <v>326</v>
+      <c r="A23" s="3" t="s">
+        <v>334</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="37" t="s">
-        <v>327</v>
+      <c r="A24" s="3" t="s">
+        <v>335</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="37" t="s">
-        <v>328</v>
+      <c r="A25" s="3" t="s">
+        <v>336</v>
       </c>
     </row>
   </sheetData>

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -14,6 +14,7 @@
     <sheet name="MLB Jul 12" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="NASCAR Jul 12" sheetId="5" state="visible" r:id="rId7"/>
     <sheet name="References" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="WNBA Jul 12" sheetId="7" state="visible" r:id="rId9"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="587" uniqueCount="376">
   <si>
     <t xml:space="preserve">BETTING TEST ACCOUNT — ROLL-UP DASHBOARD</t>
   </si>
@@ -123,7 +124,7 @@
     <t xml:space="preserve">2026-07-12</t>
   </si>
   <si>
-    <t xml:space="preserve">Tab: MLB Jul 12 · 2-5 thru 7 of 8 graded (-$326.80), Giants ML pending</t>
+    <t xml:space="preserve">Tab: MLB Jul 12 · 2-5 thru 7 of 8 · Giants ML still live</t>
   </si>
   <si>
     <t xml:space="preserve">NASCAR Quaker State 400</t>
@@ -132,13 +133,79 @@
     <t xml:space="preserve">Tab: NASCAR Jul 12 · race ~7 PM ET</t>
   </si>
   <si>
+    <t xml:space="preserve">WNBA Sunday Doubleheader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tab: WNBA Jul 12 · Sky@Wings 7 ET, Fever@Aces 9 ET</t>
+  </si>
+  <si>
     <t xml:space="preserve">TOTALS</t>
   </si>
   <si>
-    <t xml:space="preserve">Legend: GREEN-tinted rows = ACTIVE cards · GREY-tinted rows = SETTLED/ARCHIVE (drop off 7 days after settling). Tab colors match (green tabs = active).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">'Net P/L to Date' includes partially-graded cards, so the account balance moves as individual bets settle, not just when a whole card closes.</t>
+    <t xml:space="preserve">🎲 LONGSHOT TRACKER — one per card, hit/miss record</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Card</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Longshot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Odds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test 1 · UFC 329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">McGregor KO/TKO/Sub R1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+250</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MISS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test 3 · MLB Jul 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3-leg ML parlay (PIT+CIN+ATH)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test 4 · NASCAR Jul 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kyle Larson to win</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+1900</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test 5 · WNBA Jul 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4-leg cross-game parlay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LONGSHOT HIT RATE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Note: WC card carries an England hedge ticket, not a longshot — excluded from this record. UFC longshot was flagged at $0 stake and missed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legend: GREEN-tinted rows = ACTIVE cards · GREY-tinted rows = SETTLED/ARCHIVE (drop off 7 days after settling). Tab colors match.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">'Net P/L to Date' includes partially-graded cards, so the account balance moves as individual bets settle.</t>
   </si>
   <si>
     <t xml:space="preserve">Blue = manual input · Black = formula. Status column is set manually when a card fully settles.</t>
@@ -171,9 +238,6 @@
     <t xml:space="preserve">Odds (Am.)</t>
   </si>
   <si>
-    <t xml:space="preserve">Stake</t>
-  </si>
-  <si>
     <t xml:space="preserve">To Win</t>
   </si>
   <si>
@@ -420,9 +484,6 @@
     <t xml:space="preserve">$0 stake — flagged as fun play only at +250</t>
   </si>
   <si>
-    <t xml:space="preserve">+250</t>
-  </si>
-  <si>
     <t xml:space="preserve">Did not hit — McGregor lost R1</t>
   </si>
   <si>
@@ -582,7 +643,7 @@
     <t xml:space="preserve">TEST 3 — MLB SUNDAY SLATE · JULY 12, 2026</t>
   </si>
   <si>
-    <t xml:space="preserve">STATUS: ACTIVE — 7 of 8 settled (2-5, -$326.80), Giants ML pending (in progress)</t>
+    <t xml:space="preserve">STATUS: ACTIVE — 1 of 8 settled (Pirates ✓ +$135.20)</t>
   </si>
   <si>
     <t xml:space="preserve">15-game slate, 8 bets · Source: mlb-jul12-betting-card.html · Lines: ESPN consensus board, Sunday AM · Research: VSiN, PickDawgz, DK Network</t>
@@ -612,7 +673,7 @@
     <t xml:space="preserve">@ White Sox · Ginn (2.49 road ERA) vs Schultz (5.4 BB/9)</t>
   </si>
   <si>
-    <t xml:space="preserve">Clearest starter mismatch priced near even · RESULT: CWS 9-1 F — Ginn 8 ER in 4.1 IP, six-run 1st; Sox complete sweep</t>
+    <t xml:space="preserve">Clearest starter mismatch priced near even · RESULT: CWS 9-1 · Ginn 8 ER in 4.1, six-run 1st</t>
   </si>
   <si>
     <t xml:space="preserve">Tigers ML</t>
@@ -621,7 +682,7 @@
     <t xml:space="preserve">vs Phillies · Skubal vs Wheeler ace duel</t>
   </si>
   <si>
-    <t xml:space="preserve">Bullpen edge: DET 3.10 ERA (3rd) vs PHI 5.41 (26th) since Jun 1 · RESULT: PHI 5-0 F — Wheeler 10 K, Realmuto 3-run 2B; DET pen never got a lead</t>
+    <t xml:space="preserve">Bullpen edge: DET 3.10 ERA (3rd) vs PHI 5.41 (26th) since Jun 1 · RESULT: PHI 5-0 · Wheeler 10 K shutout; pen edge moot</t>
   </si>
   <si>
     <t xml:space="preserve">Royals @ Orioles Under 9.5</t>
@@ -630,7 +691,7 @@
     <t xml:space="preserve">Totals · Lugo vs Baz</t>
   </si>
   <si>
-    <t xml:space="preserve">KC last in road scoring 3.8 R/G; Baz 3.78 FIP · RESULT: BAL 8-2 F — 10 combined runs, Over by half a run</t>
+    <t xml:space="preserve">KC last in road scoring 3.8 R/G; Baz 3.78 FIP · RESULT: BAL 8-2 · 10 combined runs, over by half a run</t>
   </si>
   <si>
     <t xml:space="preserve">Pirates ML</t>
@@ -648,7 +709,7 @@
     <t xml:space="preserve">vs Cubs · Abbott ≤3 ER in 14 straight starts</t>
   </si>
   <si>
-    <t xml:space="preserve">Home dog with the more reliable starter · RESULT: CHC 8-4 F — home-dog value didn't land</t>
+    <t xml:space="preserve">Home dog with the more reliable starter · RESULT: CHC 8-4 · home-dog value didn't land</t>
   </si>
   <si>
     <t xml:space="preserve">Mariners ML</t>
@@ -657,7 +718,7 @@
     <t xml:space="preserve">@ Rays · Hancock 3.23 vs Seymour 4.11</t>
   </si>
   <si>
-    <t xml:space="preserve">Seymour's 6-1 record masks a 4.11 ERA · RESULT: SEA 8-2 F — Crawford 3 RBI; Hancock exited 2nd (finger) but pen held</t>
+    <t xml:space="preserve">Seymour's 6-1 record masks a 4.11 ERA · RESULT: SEA 8-2 · Crawford 3 RBI; pen covered Hancock's exit</t>
   </si>
   <si>
     <t xml:space="preserve">Longshot: 3-Leg ML Parlay</t>
@@ -666,7 +727,7 @@
     <t xml:space="preserve">Pirates ML +104 / Reds ML +108 / Athletics ML -104</t>
   </si>
   <si>
-    <t xml:space="preserve">The mandatory longshot — stacks our three value legs · RESULT: Loss — Reds &amp; A's legs both failed after Pirates leg hit</t>
+    <t xml:space="preserve">The mandatory longshot — stacks our three value legs · RESULT: Parlay dead — Reds &amp; A's legs lost (PIT leg won)</t>
   </si>
   <si>
     <t xml:space="preserve">Expected Wins (model)</t>
@@ -693,12 +754,6 @@
     <t xml:space="preserve">NYY -114</t>
   </si>
   <si>
-    <t xml:space="preserve">Yankees 5-3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Would have won (NYY -114)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Red Sox @ Mets</t>
   </si>
   <si>
@@ -708,12 +763,6 @@
     <t xml:space="preserve">BOS -126</t>
   </si>
   <si>
-    <t xml:space="preserve">Red Sox 3-2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Would have won (BOS -126)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Guardians @ Marlins</t>
   </si>
   <si>
@@ -723,12 +772,6 @@
     <t xml:space="preserve">MIA -115</t>
   </si>
   <si>
-    <t xml:space="preserve">Guardians 3-1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Good skip — MIA -115 lost</t>
-  </si>
-  <si>
     <t xml:space="preserve">Angels @ Twins</t>
   </si>
   <si>
@@ -747,12 +790,6 @@
     <t xml:space="preserve">STL -136</t>
   </si>
   <si>
-    <t xml:space="preserve">Braves 4-3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Good skip — STL -136 lost</t>
-  </si>
-  <si>
     <t xml:space="preserve">Astros @ Rangers</t>
   </si>
   <si>
@@ -924,7 +961,7 @@
     <t xml:space="preserve">Odds, picks, prediction-market data</t>
   </si>
   <si>
-    <t xml:space="preserve">WC: Kalshi probabilities (SEE CAUTION BELOW) · NASCAR: outrights, H2H, props</t>
+    <t xml:space="preserve">WC: Kalshi probabilities (SEE CAUTION BELOW) · NASCAR: outrights, H2H, props · WNBA: Fever-Aces picks/props (T5)</t>
   </si>
   <si>
     <t xml:space="preserve">dknetwork.draftkings.com</t>
@@ -936,94 +973,94 @@
     <t xml:space="preserve">WC semifinal openers; MLB parlay research</t>
   </si>
   <si>
+    <t xml:space="preserve">sports.yahoo.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brackets, schedules, lineups, reports</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WC bracket; NASCAR starting lineup/race info</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vavel.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Live match blogs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Live Argentina-Switzerland score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">foxsports.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Odds stories, score pages</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WC title odds context</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nbcsports.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Match previews &amp; broadcast info</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argentina-Switzerland preview</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wikipedia.org</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tournament format &amp; structure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WC knockout format/dates</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vsin.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Expert betting analysis &amp; picks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MLB Sunday card; NASCAR top-5 picks &amp; longshots</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pickdawgz.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Game predictions with stats</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brewers-Pirates deep dive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mlb.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Official schedules &amp; probable pitchers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Probable-pitcher confirmation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cbssports.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Model-based picks &amp; odds (FanDuel)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SportsLine model: Keselowski call, Blaney fade</t>
+  </si>
+  <si>
     <t xml:space="preserve">si.com</t>
   </si>
   <si>
-    <t xml:space="preserve">Betting lines &amp; analysis (FanDuel)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">France-Spain lines</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sports.yahoo.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brackets, schedules, lineups, reports</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WC bracket; NASCAR starting lineup/race info</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vavel.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Live match blogs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Live Argentina-Switzerland score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">foxsports.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Odds stories, score pages</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WC title odds context</t>
-  </si>
-  <si>
-    <t xml:space="preserve">nbcsports.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Match previews &amp; broadcast info</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argentina-Switzerland preview</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wikipedia.org</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tournament format &amp; structure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WC knockout format/dates</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vsin.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Expert betting analysis &amp; picks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MLB Sunday card; NASCAR top-5 picks &amp; longshots</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pickdawgz.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Game predictions with stats</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brewers-Pirates deep dive</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mlb.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Official schedules &amp; probable pitchers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Probable-pitcher confirmation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cbssports.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Model-based picks &amp; odds (FanDuel)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SportsLine model: Keselowski call, Blaney fade</t>
+    <t xml:space="preserve">Betting lines, picks &amp; player props (FanDuel)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T2: France-Spain lines · T5 WNBA: all game lines &amp; props</t>
   </si>
   <si>
     <t xml:space="preserve">⚠ SOURCE CAUTION — KALSHI (per John, 2026-07-12): prediction-market prices can be manipulated ('market rigging'). Kalshi probabilities are used for CONTEXT/comparison only, never as a primary betting basis. Primary basis = sportsbook consensus + our own stats analysis.</t>
@@ -1036,6 +1073,87 @@
   </si>
   <si>
     <t xml:space="preserve">Sites queried but returning no usable facts (blocked/empty) are not listed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEST 5 — WNBA SUNDAY NIGHT DOUBLEHEADER · JULY 12, 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STATUS: ACTIVE — games 7 &amp; 9 PM ET tonight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sky @ Wings 7 PM ET (ESPN) · Fever @ Aces 9 PM ET (NBC) · Source: wnba-jul12-betting-card.html · Lines: FanDuel via SI Betting / Covers, ~5 PM CT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Budget $1,000 · 6 core bets + 1 longshot (counts toward the account longshot record). EV ≈ +$81, expected wins ≈ 3.6 of 7.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wings -9.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vs Sky · 7 PM ET</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spread</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sky missing Carrington + Diggins; Wings 15-8, 2nd in O-rating last 10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sky @ Wings Over 177.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Game 1 total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">185 &amp; 188 combined in first two meetings; Sky 3rd in pace, over 8 of last 10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paige Bueckers 20+ Points</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wings G · player prop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22+ in 6 of last 7; 20.6 PPG; Sky 10th in D-rating</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aces -4.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vs Fever · 9 PM ET</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+41 differential last 7 home w/ Wilson; rested off 48-pt blowout Sat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A'ja Wilson Double-Double (Yes)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aces F · player prop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DD in 5 straight career games vs Clark; 10.8 reb/game at home; 11 DDs (3rd in W)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kelsey Mitchell Over 2.5 Threes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fever G · player prop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3+ threes in 6 straight, 8 of 10; 41.1% from deep; LV 12th vs opp threes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LONGSHOT: 4-Leg Parlay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wings -9.5 / Aces -4.5 / Bueckers 20+ / Mitchell 3+ threes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stacks our four highest-confidence legs · counts in longshot record</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yellow = fill in results (dropdown). Blue = inputs. Black = formulas. Parlay odds +971 = (-115 × -108 × -159 × -121) compounded; grades as one bet.</t>
   </si>
 </sst>
 </file>
@@ -1054,7 +1172,7 @@
     <numFmt numFmtId="172" formatCode="0.0&quot; exp. wins&quot;"/>
     <numFmt numFmtId="173" formatCode="0.0"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1154,6 +1272,13 @@
       <charset val="1"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <sz val="9"/>
       <color rgb="FF666666"/>
       <name val="Arial"/>
@@ -1163,13 +1288,6 @@
     <font>
       <b val="true"/>
       <sz val="13"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF0000FF"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -1201,6 +1319,19 @@
       <i val="true"/>
       <sz val="9"/>
       <color rgb="FF9C6500"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -1331,7 +1462,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="70">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1468,14 +1599,30 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1492,11 +1639,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1540,10 +1683,6 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="19" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1552,11 +1691,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="171" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1572,10 +1711,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1588,11 +1723,23 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1879,7 +2026,7 @@
     <tabColor rgb="FF1F2A44"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:J34"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30"/>
@@ -1920,7 +2067,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="7" t="n">
-        <f aca="false">H20</f>
+        <f aca="false">H21</f>
         <v>-161.689627168697</v>
       </c>
     </row>
@@ -1929,7 +2076,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="8" t="n">
-        <f aca="false">I19</f>
+        <f aca="false">I20</f>
         <v>4838.3103728313</v>
       </c>
     </row>
@@ -1938,8 +2085,8 @@
         <v>6</v>
       </c>
       <c r="B8" s="9" t="n">
-        <f aca="false">F20</f>
-        <v>2200</v>
+        <f aca="false">F21</f>
+        <v>3200</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1948,7 +2095,7 @@
       </c>
       <c r="B9" s="8" t="n">
         <f aca="false">B7-B8</f>
-        <v>2638.3103728313</v>
+        <v>1638.3103728313</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1956,8 +2103,8 @@
         <v>8</v>
       </c>
       <c r="B10" s="10" t="str">
-        <f aca="false">COUNTIF(D16:D19,"ACTIVE")&amp;" of 4 max"</f>
-        <v>3 of 4 max</v>
+        <f aca="false">COUNTIF(D16:D20,"ACTIVE")&amp;" of 4 max"</f>
+        <v>4 of 4 max</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2035,7 +2182,7 @@
         <v>165.110372831303</v>
       </c>
       <c r="I16" s="19" t="n">
-        <f aca="false">B5+SUM($H$16:H16)</f>
+        <f aca="false">B5+H16</f>
         <v>5165.1103728313</v>
       </c>
       <c r="J16" s="20" t="s">
@@ -2154,48 +2301,195 @@
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="29"/>
-      <c r="B20" s="30" t="s">
+      <c r="A20" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="B20" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="C20" s="29"/>
-      <c r="D20" s="29"/>
-      <c r="E20" s="31" t="n">
-        <f aca="false">SUM(E16:E19)</f>
-        <v>4050</v>
-      </c>
-      <c r="F20" s="31" t="n">
-        <f aca="false">SUM(F16:F19)</f>
-        <v>2200</v>
-      </c>
-      <c r="G20" s="32" t="n">
-        <f aca="false">SUM(G16:G19)</f>
+      <c r="C20" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="D20" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="E20" s="24" t="n">
+        <f aca="false">SUM('WNBA Jul 12'!F7:F13)</f>
+        <v>1000</v>
+      </c>
+      <c r="F20" s="24" t="n">
+        <f aca="false">SUMIF('WNBA Jul 12'!I7:I13,"Pending",'WNBA Jul 12'!F7:F13)</f>
+        <v>1000</v>
+      </c>
+      <c r="G20" s="25" t="n">
+        <f aca="false">SUM('WNBA Jul 12'!J7:J13)</f>
+        <v>0</v>
+      </c>
+      <c r="H20" s="26" t="n">
+        <f aca="false">SUM('WNBA Jul 12'!K7:K13)</f>
+        <v>0</v>
+      </c>
+      <c r="I20" s="27" t="n">
+        <f aca="false">I19+H20</f>
+        <v>4838.3103728313</v>
+      </c>
+      <c r="J20" s="28" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="29"/>
+      <c r="B21" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="C21" s="29"/>
+      <c r="D21" s="29"/>
+      <c r="E21" s="31" t="n">
+        <f aca="false">SUM(E16:E20)</f>
+        <v>5050</v>
+      </c>
+      <c r="F21" s="31" t="n">
+        <f aca="false">SUM(F16:F20)</f>
+        <v>3200</v>
+      </c>
+      <c r="G21" s="32" t="n">
+        <f aca="false">SUM(G16:G20)</f>
         <v>1688.3103728313</v>
       </c>
-      <c r="H20" s="33" t="n">
-        <f aca="false">SUM(H16:H19)</f>
+      <c r="H21" s="33" t="n">
+        <f aca="false">SUM(H16:H20)</f>
         <v>-161.689627168697</v>
       </c>
-      <c r="I20" s="29"/>
-      <c r="J20" s="29"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="34" t="s">
-        <v>36</v>
-      </c>
+      <c r="I21" s="29"/>
+      <c r="J21" s="29"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="34" t="s">
-        <v>37</v>
+      <c r="A23" s="4" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="34" t="s">
-        <v>38</v>
+      <c r="A24" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="C24" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="D24" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="E24" s="12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B25" s="34" t="s">
+        <v>44</v>
+      </c>
+      <c r="C25" s="35" t="s">
+        <v>45</v>
+      </c>
+      <c r="D25" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="10" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B26" s="34" t="s">
+        <v>48</v>
+      </c>
+      <c r="C26" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="D26" s="36" t="n">
+        <v>50</v>
+      </c>
+      <c r="E26" s="10" t="str">
+        <f aca="false">IF('MLB Jul 12'!I14="Win","HIT",IF('MLB Jul 12'!I14="Loss","MISS","Pending"))</f>
+        <v>MISS</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B27" s="34" t="s">
+        <v>51</v>
+      </c>
+      <c r="C27" s="35" t="s">
+        <v>52</v>
+      </c>
+      <c r="D27" s="36" t="n">
+        <v>40</v>
+      </c>
+      <c r="E27" s="10" t="str">
+        <f aca="false">IF('NASCAR Jul 12'!I13="Win","HIT",IF('NASCAR Jul 12'!I13="Loss","MISS","Pending"))</f>
+        <v>Pending</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B28" s="34" t="s">
+        <v>54</v>
+      </c>
+      <c r="C28" s="35" t="s">
+        <v>55</v>
+      </c>
+      <c r="D28" s="36" t="n">
+        <v>100</v>
+      </c>
+      <c r="E28" s="10" t="str">
+        <f aca="false">IF('WNBA Jul 12'!I13="Win","HIT",IF('WNBA Jul 12'!I13="Loss","MISS","Pending"))</f>
+        <v>Pending</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="30" t="s">
+        <v>56</v>
+      </c>
+      <c r="B29" s="29"/>
+      <c r="C29" s="29"/>
+      <c r="D29" s="29"/>
+      <c r="E29" s="37" t="str">
+        <f aca="false">IF(COUNTIF(E25:E28,"HIT")+COUNTIF(E25:E28,"MISS")=0,"—",COUNTIF(E25:E28,"HIT")&amp;"-for-"&amp;(COUNTIF(E25:E28,"HIT")+COUNTIF(E25:E28,"MISS"))&amp;" ("&amp;TEXT(COUNTIF(E25:E28,"HIT")/(COUNTIF(E25:E28,"HIT")+COUNTIF(E25:E28,"MISS")),"0%")&amp;")")</f>
+        <v>0-for-2 (0%)</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="38" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="38" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="38" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="38" t="s">
+        <v>60</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="H16:H20">
+  <conditionalFormatting sqref="H16:H21">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>AND(ISNUMBER(H16),H16&gt;0)</formula>
     </cfRule>
@@ -2203,7 +2497,7 @@
       <formula>AND(ISNUMBER(H16),H16&lt;0)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I16:I19">
+  <conditionalFormatting sqref="I16:I20">
     <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>AND(ISNUMBER(I16),I16&gt;5000)</formula>
     </cfRule>
@@ -2259,26 +2553,26 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="35" t="s">
-        <v>39</v>
-      </c>
-      <c r="H1" s="36" t="s">
-        <v>40</v>
+      <c r="A1" s="39" t="s">
+        <v>61</v>
+      </c>
+      <c r="H1" s="40" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>42</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2286,425 +2580,425 @@
         <v>12</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="G6" s="12" t="s">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="H6" s="12" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="I6" s="12" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="J6" s="12" t="s">
-        <v>52</v>
+        <v>73</v>
       </c>
       <c r="K6" s="12" t="s">
-        <v>53</v>
+        <v>74</v>
       </c>
       <c r="L6" s="12" t="s">
-        <v>54</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="37" t="n">
+      <c r="A7" s="41" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="38" t="s">
-        <v>55</v>
-      </c>
-      <c r="C7" s="39" t="s">
-        <v>56</v>
-      </c>
-      <c r="D7" s="37" t="s">
-        <v>57</v>
-      </c>
-      <c r="E7" s="40" t="n">
+      <c r="B7" s="42" t="s">
+        <v>76</v>
+      </c>
+      <c r="C7" s="43" t="s">
+        <v>77</v>
+      </c>
+      <c r="D7" s="41" t="s">
+        <v>78</v>
+      </c>
+      <c r="E7" s="44" t="n">
         <v>-265</v>
       </c>
-      <c r="F7" s="41" t="n">
+      <c r="F7" s="36" t="n">
         <v>265</v>
       </c>
-      <c r="G7" s="42" t="n">
+      <c r="G7" s="45" t="n">
         <f aca="false">IF(E7&gt;0,F7*E7/100,F7*100/ABS(E7))</f>
         <v>100</v>
       </c>
-      <c r="H7" s="42" t="n">
+      <c r="H7" s="45" t="n">
         <f aca="false">F7+G7</f>
         <v>365</v>
       </c>
-      <c r="I7" s="43" t="s">
-        <v>58</v>
-      </c>
-      <c r="J7" s="42" t="n">
+      <c r="I7" s="46" t="s">
+        <v>79</v>
+      </c>
+      <c r="J7" s="45" t="n">
         <f aca="false">IF(I7="Win",F7+G7,IF(I7="Push",F7,IF(I7="Loss",0,0)))</f>
         <v>365</v>
       </c>
-      <c r="K7" s="44" t="n">
+      <c r="K7" s="47" t="n">
         <f aca="false">IF(I7="Pending",0,J7-F7)</f>
         <v>100</v>
       </c>
-      <c r="L7" s="45" t="s">
-        <v>59</v>
+      <c r="L7" s="48" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="37" t="n">
+      <c r="A8" s="41" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="38" t="s">
-        <v>60</v>
-      </c>
-      <c r="C8" s="39" t="s">
-        <v>61</v>
-      </c>
-      <c r="D8" s="37" t="s">
-        <v>62</v>
-      </c>
-      <c r="E8" s="40" t="n">
+      <c r="B8" s="42" t="s">
+        <v>81</v>
+      </c>
+      <c r="C8" s="43" t="s">
+        <v>82</v>
+      </c>
+      <c r="D8" s="41" t="s">
+        <v>83</v>
+      </c>
+      <c r="E8" s="44" t="n">
         <v>-140</v>
       </c>
-      <c r="F8" s="41" t="n">
+      <c r="F8" s="36" t="n">
         <v>200</v>
       </c>
-      <c r="G8" s="42" t="n">
+      <c r="G8" s="45" t="n">
         <f aca="false">IF(E8&gt;0,F8*E8/100,F8*100/ABS(E8))</f>
         <v>142.857142857143</v>
       </c>
-      <c r="H8" s="42" t="n">
+      <c r="H8" s="45" t="n">
         <f aca="false">F8+G8</f>
         <v>342.857142857143</v>
       </c>
-      <c r="I8" s="43" t="s">
-        <v>58</v>
-      </c>
-      <c r="J8" s="42" t="n">
+      <c r="I8" s="46" t="s">
+        <v>79</v>
+      </c>
+      <c r="J8" s="45" t="n">
         <f aca="false">IF(I8="Win",F8+G8,IF(I8="Push",F8,IF(I8="Loss",0,0)))</f>
         <v>342.857142857143</v>
       </c>
-      <c r="K8" s="44" t="n">
+      <c r="K8" s="47" t="n">
         <f aca="false">IF(I8="Pending",0,J8-F8)</f>
         <v>142.857142857143</v>
       </c>
-      <c r="L8" s="45" t="s">
-        <v>63</v>
+      <c r="L8" s="48" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="37" t="n">
+      <c r="A9" s="41" t="n">
         <v>3</v>
       </c>
-      <c r="B9" s="38" t="s">
-        <v>64</v>
-      </c>
-      <c r="C9" s="39" t="s">
-        <v>65</v>
-      </c>
-      <c r="D9" s="37" t="s">
-        <v>57</v>
-      </c>
-      <c r="E9" s="40" t="n">
+      <c r="B9" s="42" t="s">
+        <v>85</v>
+      </c>
+      <c r="C9" s="43" t="s">
+        <v>86</v>
+      </c>
+      <c r="D9" s="41" t="s">
+        <v>78</v>
+      </c>
+      <c r="E9" s="44" t="n">
         <v>-148</v>
       </c>
-      <c r="F9" s="41" t="n">
+      <c r="F9" s="36" t="n">
         <v>148</v>
       </c>
-      <c r="G9" s="42" t="n">
+      <c r="G9" s="45" t="n">
         <f aca="false">IF(E9&gt;0,F9*E9/100,F9*100/ABS(E9))</f>
         <v>100</v>
       </c>
-      <c r="H9" s="42" t="n">
+      <c r="H9" s="45" t="n">
         <f aca="false">F9+G9</f>
         <v>248</v>
       </c>
-      <c r="I9" s="46" t="s">
-        <v>66</v>
-      </c>
-      <c r="J9" s="42" t="n">
+      <c r="I9" s="49" t="s">
+        <v>87</v>
+      </c>
+      <c r="J9" s="45" t="n">
         <f aca="false">IF(I9="Win",F9+G9,IF(I9="Push",F9,IF(I9="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K9" s="44" t="n">
+      <c r="K9" s="47" t="n">
         <f aca="false">IF(I9="Pending",0,J9-F9)</f>
         <v>-148</v>
       </c>
-      <c r="L9" s="45" t="s">
-        <v>67</v>
+      <c r="L9" s="48" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="37" t="n">
+      <c r="A10" s="41" t="n">
         <v>4</v>
       </c>
-      <c r="B10" s="38" t="s">
-        <v>68</v>
-      </c>
-      <c r="C10" s="39" t="s">
-        <v>69</v>
-      </c>
-      <c r="D10" s="37" t="s">
-        <v>57</v>
-      </c>
-      <c r="E10" s="40" t="n">
+      <c r="B10" s="42" t="s">
+        <v>89</v>
+      </c>
+      <c r="C10" s="43" t="s">
+        <v>90</v>
+      </c>
+      <c r="D10" s="41" t="s">
+        <v>78</v>
+      </c>
+      <c r="E10" s="44" t="n">
         <v>114</v>
       </c>
-      <c r="F10" s="41" t="n">
+      <c r="F10" s="36" t="n">
         <v>100</v>
       </c>
-      <c r="G10" s="42" t="n">
+      <c r="G10" s="45" t="n">
         <f aca="false">IF(E10&gt;0,F10*E10/100,F10*100/ABS(E10))</f>
         <v>114</v>
       </c>
-      <c r="H10" s="42" t="n">
+      <c r="H10" s="45" t="n">
         <f aca="false">F10+G10</f>
         <v>214</v>
       </c>
-      <c r="I10" s="43" t="s">
-        <v>58</v>
-      </c>
-      <c r="J10" s="42" t="n">
+      <c r="I10" s="46" t="s">
+        <v>79</v>
+      </c>
+      <c r="J10" s="45" t="n">
         <f aca="false">IF(I10="Win",F10+G10,IF(I10="Push",F10,IF(I10="Loss",0,0)))</f>
         <v>214</v>
       </c>
-      <c r="K10" s="44" t="n">
+      <c r="K10" s="47" t="n">
         <f aca="false">IF(I10="Pending",0,J10-F10)</f>
         <v>114</v>
       </c>
-      <c r="L10" s="45" t="s">
-        <v>70</v>
+      <c r="L10" s="48" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="37" t="n">
+      <c r="A11" s="41" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="38" t="s">
-        <v>71</v>
-      </c>
-      <c r="C11" s="39" t="s">
-        <v>72</v>
-      </c>
-      <c r="D11" s="37" t="s">
-        <v>57</v>
-      </c>
-      <c r="E11" s="40" t="n">
+      <c r="B11" s="42" t="s">
+        <v>92</v>
+      </c>
+      <c r="C11" s="43" t="s">
+        <v>93</v>
+      </c>
+      <c r="D11" s="41" t="s">
+        <v>78</v>
+      </c>
+      <c r="E11" s="44" t="n">
         <v>-218</v>
       </c>
-      <c r="F11" s="41" t="n">
+      <c r="F11" s="36" t="n">
         <v>100</v>
       </c>
-      <c r="G11" s="42" t="n">
+      <c r="G11" s="45" t="n">
         <f aca="false">IF(E11&gt;0,F11*E11/100,F11*100/ABS(E11))</f>
         <v>45.8715596330275</v>
       </c>
-      <c r="H11" s="42" t="n">
+      <c r="H11" s="45" t="n">
         <f aca="false">F11+G11</f>
         <v>145.871559633028</v>
       </c>
-      <c r="I11" s="46" t="s">
-        <v>66</v>
-      </c>
-      <c r="J11" s="42" t="n">
+      <c r="I11" s="49" t="s">
+        <v>87</v>
+      </c>
+      <c r="J11" s="45" t="n">
         <f aca="false">IF(I11="Win",F11+G11,IF(I11="Push",F11,IF(I11="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K11" s="44" t="n">
+      <c r="K11" s="47" t="n">
         <f aca="false">IF(I11="Pending",0,J11-F11)</f>
         <v>-100</v>
       </c>
-      <c r="L11" s="45" t="s">
-        <v>73</v>
+      <c r="L11" s="48" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="37" t="n">
+      <c r="A12" s="41" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="38" t="s">
-        <v>74</v>
-      </c>
-      <c r="C12" s="39" t="s">
+      <c r="B12" s="42" t="s">
+        <v>95</v>
+      </c>
+      <c r="C12" s="43" t="s">
+        <v>96</v>
+      </c>
+      <c r="D12" s="41" t="s">
+        <v>78</v>
+      </c>
+      <c r="E12" s="44" t="n">
+        <v>-125</v>
+      </c>
+      <c r="F12" s="36" t="n">
         <v>75</v>
       </c>
-      <c r="D12" s="37" t="s">
-        <v>57</v>
-      </c>
-      <c r="E12" s="40" t="n">
-        <v>-125</v>
-      </c>
-      <c r="F12" s="41" t="n">
-        <v>75</v>
-      </c>
-      <c r="G12" s="42" t="n">
+      <c r="G12" s="45" t="n">
         <f aca="false">IF(E12&gt;0,F12*E12/100,F12*100/ABS(E12))</f>
         <v>60</v>
       </c>
-      <c r="H12" s="42" t="n">
+      <c r="H12" s="45" t="n">
         <f aca="false">F12+G12</f>
         <v>135</v>
       </c>
-      <c r="I12" s="43" t="s">
-        <v>58</v>
-      </c>
-      <c r="J12" s="42" t="n">
+      <c r="I12" s="46" t="s">
+        <v>79</v>
+      </c>
+      <c r="J12" s="45" t="n">
         <f aca="false">IF(I12="Win",F12+G12,IF(I12="Push",F12,IF(I12="Loss",0,0)))</f>
         <v>135</v>
       </c>
-      <c r="K12" s="44" t="n">
+      <c r="K12" s="47" t="n">
         <f aca="false">IF(I12="Pending",0,J12-F12)</f>
         <v>60</v>
       </c>
-      <c r="L12" s="45" t="s">
-        <v>76</v>
+      <c r="L12" s="48" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="37" t="n">
+      <c r="A13" s="41" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="38" t="s">
-        <v>77</v>
-      </c>
-      <c r="C13" s="39" t="s">
+      <c r="B13" s="42" t="s">
+        <v>98</v>
+      </c>
+      <c r="C13" s="43" t="s">
+        <v>99</v>
+      </c>
+      <c r="D13" s="41" t="s">
         <v>78</v>
       </c>
-      <c r="D13" s="37" t="s">
-        <v>57</v>
-      </c>
-      <c r="E13" s="40" t="n">
+      <c r="E13" s="44" t="n">
         <v>-225</v>
       </c>
-      <c r="F13" s="41" t="n">
+      <c r="F13" s="36" t="n">
         <v>50</v>
       </c>
-      <c r="G13" s="42" t="n">
+      <c r="G13" s="45" t="n">
         <f aca="false">IF(E13&gt;0,F13*E13/100,F13*100/ABS(E13))</f>
         <v>22.2222222222222</v>
       </c>
-      <c r="H13" s="42" t="n">
+      <c r="H13" s="45" t="n">
         <f aca="false">F13+G13</f>
         <v>72.2222222222222</v>
       </c>
-      <c r="I13" s="43" t="s">
-        <v>58</v>
-      </c>
-      <c r="J13" s="42" t="n">
+      <c r="I13" s="46" t="s">
+        <v>79</v>
+      </c>
+      <c r="J13" s="45" t="n">
         <f aca="false">IF(I13="Win",F13+G13,IF(I13="Push",F13,IF(I13="Loss",0,0)))</f>
         <v>72.2222222222222</v>
       </c>
-      <c r="K13" s="44" t="n">
+      <c r="K13" s="47" t="n">
         <f aca="false">IF(I13="Pending",0,J13-F13)</f>
         <v>22.2222222222222</v>
       </c>
-      <c r="L13" s="45" t="s">
-        <v>79</v>
+      <c r="L13" s="48" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="37" t="n">
+      <c r="A14" s="41" t="n">
         <v>8</v>
       </c>
-      <c r="B14" s="38" t="s">
-        <v>80</v>
-      </c>
-      <c r="C14" s="39" t="s">
-        <v>81</v>
-      </c>
-      <c r="D14" s="37" t="s">
-        <v>57</v>
-      </c>
-      <c r="E14" s="40" t="n">
+      <c r="B14" s="42" t="s">
+        <v>101</v>
+      </c>
+      <c r="C14" s="43" t="s">
+        <v>102</v>
+      </c>
+      <c r="D14" s="41" t="s">
+        <v>78</v>
+      </c>
+      <c r="E14" s="44" t="n">
         <v>-258</v>
       </c>
-      <c r="F14" s="41" t="n">
+      <c r="F14" s="36" t="n">
         <v>62</v>
       </c>
-      <c r="G14" s="42" t="n">
+      <c r="G14" s="45" t="n">
         <f aca="false">IF(E14&gt;0,F14*E14/100,F14*100/ABS(E14))</f>
         <v>24.031007751938</v>
       </c>
-      <c r="H14" s="42" t="n">
+      <c r="H14" s="45" t="n">
         <f aca="false">F14+G14</f>
         <v>86.031007751938</v>
       </c>
-      <c r="I14" s="43" t="s">
-        <v>58</v>
-      </c>
-      <c r="J14" s="42" t="n">
+      <c r="I14" s="46" t="s">
+        <v>79</v>
+      </c>
+      <c r="J14" s="45" t="n">
         <f aca="false">IF(I14="Win",F14+G14,IF(I14="Push",F14,IF(I14="Loss",0,0)))</f>
         <v>86.031007751938</v>
       </c>
-      <c r="K14" s="44" t="n">
+      <c r="K14" s="47" t="n">
         <f aca="false">IF(I14="Pending",0,J14-F14)</f>
         <v>24.031007751938</v>
       </c>
-      <c r="L14" s="45" t="s">
-        <v>82</v>
+      <c r="L14" s="48" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="37" t="n">
+      <c r="A15" s="41" t="n">
         <v>9</v>
       </c>
-      <c r="B15" s="38" t="s">
-        <v>83</v>
-      </c>
-      <c r="C15" s="39" t="s">
-        <v>84</v>
-      </c>
-      <c r="D15" s="37" t="s">
-        <v>85</v>
-      </c>
-      <c r="E15" s="40" t="n">
+      <c r="B15" s="42" t="s">
+        <v>104</v>
+      </c>
+      <c r="C15" s="43" t="s">
+        <v>105</v>
+      </c>
+      <c r="D15" s="41" t="s">
+        <v>106</v>
+      </c>
+      <c r="E15" s="44" t="n">
         <v>443</v>
       </c>
-      <c r="F15" s="41" t="n">
+      <c r="F15" s="36" t="n">
         <v>50</v>
       </c>
-      <c r="G15" s="42" t="n">
+      <c r="G15" s="45" t="n">
         <f aca="false">IF(E15&gt;0,F15*E15/100,F15*100/ABS(E15))</f>
         <v>221.5</v>
       </c>
-      <c r="H15" s="42" t="n">
+      <c r="H15" s="45" t="n">
         <f aca="false">F15+G15</f>
         <v>271.5</v>
       </c>
-      <c r="I15" s="46" t="s">
-        <v>66</v>
-      </c>
-      <c r="J15" s="42" t="n">
+      <c r="I15" s="49" t="s">
+        <v>87</v>
+      </c>
+      <c r="J15" s="45" t="n">
         <f aca="false">IF(I15="Win",F15+G15,IF(I15="Push",F15,IF(I15="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K15" s="44" t="n">
+      <c r="K15" s="47" t="n">
         <f aca="false">IF(I15="Pending",0,J15-F15)</f>
         <v>-50</v>
       </c>
-      <c r="L15" s="45" t="s">
-        <v>86</v>
+      <c r="L15" s="48" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="47"/>
-      <c r="B16" s="48" t="s">
-        <v>35</v>
-      </c>
-      <c r="C16" s="47"/>
-      <c r="D16" s="47"/>
-      <c r="E16" s="47"/>
+      <c r="A16" s="50"/>
+      <c r="B16" s="51" t="s">
+        <v>37</v>
+      </c>
+      <c r="C16" s="50"/>
+      <c r="D16" s="50"/>
+      <c r="E16" s="50"/>
       <c r="F16" s="31" t="n">
         <f aca="false">SUM(F7:F15)</f>
         <v>1050</v>
@@ -2717,7 +3011,7 @@
         <f aca="false">SUM(H7:H15)</f>
         <v>1880.48193246433</v>
       </c>
-      <c r="I16" s="47"/>
+      <c r="I16" s="50"/>
       <c r="J16" s="32" t="n">
         <f aca="false">SUM(J7:J15)</f>
         <v>1215.1103728313</v>
@@ -2726,106 +3020,106 @@
         <f aca="false">SUM(K7:K15)</f>
         <v>165.110372831303</v>
       </c>
-      <c r="L16" s="47"/>
+      <c r="L16" s="50"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="4" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="38" t="s">
-        <v>88</v>
-      </c>
-      <c r="C19" s="49" t="n">
+      <c r="B19" s="42" t="s">
+        <v>109</v>
+      </c>
+      <c r="C19" s="52" t="n">
         <f aca="false">COUNTIF(I7:I15,"Win")</f>
         <v>6</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="38" t="s">
-        <v>89</v>
-      </c>
-      <c r="C20" s="49" t="n">
+      <c r="B20" s="42" t="s">
+        <v>110</v>
+      </c>
+      <c r="C20" s="52" t="n">
         <f aca="false">COUNTIF(I7:I15,"Loss")</f>
         <v>3</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="38" t="s">
-        <v>90</v>
-      </c>
-      <c r="C21" s="49" t="n">
+      <c r="B21" s="42" t="s">
+        <v>111</v>
+      </c>
+      <c r="C21" s="52" t="n">
         <f aca="false">COUNTIF(I7:I15,"Push")</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="38" t="s">
-        <v>91</v>
-      </c>
-      <c r="C22" s="49" t="n">
+      <c r="B22" s="42" t="s">
+        <v>112</v>
+      </c>
+      <c r="C22" s="52" t="n">
         <f aca="false">COUNTIF(I7:I15,"Pending")</f>
         <v>0</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="38" t="s">
-        <v>92</v>
-      </c>
-      <c r="C23" s="50" t="n">
+      <c r="B23" s="42" t="s">
+        <v>113</v>
+      </c>
+      <c r="C23" s="53" t="n">
         <f aca="false">IF(COUNTIF(I7:I15,"Win")+COUNTIF(I7:I15,"Loss")=0,"—",COUNTIF(I7:I15,"Win")/(COUNTIF(I7:I15,"Win")+COUNTIF(I7:I15,"Loss")))</f>
         <v>0.666666666666667</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="38" t="s">
-        <v>93</v>
-      </c>
-      <c r="C24" s="51" t="n">
+      <c r="B24" s="42" t="s">
+        <v>114</v>
+      </c>
+      <c r="C24" s="54" t="n">
         <f aca="false">SUM(F7:F15)</f>
         <v>1050</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="38" t="s">
-        <v>94</v>
-      </c>
-      <c r="C25" s="42" t="n">
+      <c r="B25" s="42" t="s">
+        <v>115</v>
+      </c>
+      <c r="C25" s="45" t="n">
         <f aca="false">SUM(J7:J15)</f>
         <v>1215.1103728313</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="38" t="s">
-        <v>95</v>
-      </c>
-      <c r="C26" s="44" t="n">
+      <c r="B26" s="42" t="s">
+        <v>116</v>
+      </c>
+      <c r="C26" s="47" t="n">
         <f aca="false">SUM(K7:K15)</f>
         <v>165.110372831303</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="38" t="s">
-        <v>96</v>
-      </c>
-      <c r="C27" s="50" t="n">
+      <c r="B27" s="42" t="s">
+        <v>117</v>
+      </c>
+      <c r="C27" s="53" t="n">
         <f aca="false">IF(SUM(F7:F15)=0,"—",SUM(K7:K15)/SUM(F7:F15))</f>
         <v>0.157247974125051</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="38" t="s">
-        <v>97</v>
-      </c>
-      <c r="C28" s="42" t="n">
+      <c r="B28" s="42" t="s">
+        <v>118</v>
+      </c>
+      <c r="C28" s="45" t="n">
         <f aca="false">SUM(H7:H15)</f>
         <v>1880.48193246433</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
-        <v>98</v>
+        <v>119</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2833,154 +3127,154 @@
         <v>12</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>99</v>
+        <v>120</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>100</v>
+        <v>121</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>101</v>
+        <v>122</v>
       </c>
       <c r="E31" s="12" t="s">
-        <v>102</v>
+        <v>123</v>
       </c>
       <c r="F31" s="12" t="s">
-        <v>103</v>
+        <v>124</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="37" t="n">
+      <c r="A32" s="41" t="n">
         <v>1</v>
       </c>
-      <c r="B32" s="38" t="s">
-        <v>104</v>
-      </c>
-      <c r="C32" s="45" t="s">
-        <v>105</v>
-      </c>
-      <c r="D32" s="52" t="s">
-        <v>106</v>
-      </c>
-      <c r="E32" s="53" t="s">
-        <v>107</v>
-      </c>
-      <c r="F32" s="53" t="s">
-        <v>108</v>
+      <c r="B32" s="42" t="s">
+        <v>125</v>
+      </c>
+      <c r="C32" s="48" t="s">
+        <v>126</v>
+      </c>
+      <c r="D32" s="35" t="s">
+        <v>127</v>
+      </c>
+      <c r="E32" s="55" t="s">
+        <v>128</v>
+      </c>
+      <c r="F32" s="55" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="37" t="n">
+      <c r="A33" s="41" t="n">
         <v>2</v>
       </c>
-      <c r="B33" s="38" t="s">
-        <v>109</v>
-      </c>
-      <c r="C33" s="45" t="s">
-        <v>110</v>
-      </c>
-      <c r="D33" s="52" t="s">
-        <v>111</v>
-      </c>
-      <c r="E33" s="53" t="s">
-        <v>112</v>
-      </c>
-      <c r="F33" s="53" t="s">
-        <v>113</v>
+      <c r="B33" s="42" t="s">
+        <v>130</v>
+      </c>
+      <c r="C33" s="48" t="s">
+        <v>131</v>
+      </c>
+      <c r="D33" s="35" t="s">
+        <v>132</v>
+      </c>
+      <c r="E33" s="55" t="s">
+        <v>133</v>
+      </c>
+      <c r="F33" s="55" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="37" t="n">
+      <c r="A34" s="41" t="n">
         <v>3</v>
       </c>
-      <c r="B34" s="38" t="s">
-        <v>114</v>
-      </c>
-      <c r="C34" s="45" t="s">
-        <v>115</v>
-      </c>
-      <c r="D34" s="52" t="s">
-        <v>116</v>
-      </c>
-      <c r="E34" s="53" t="s">
-        <v>117</v>
-      </c>
-      <c r="F34" s="53" t="s">
-        <v>118</v>
+      <c r="B34" s="42" t="s">
+        <v>135</v>
+      </c>
+      <c r="C34" s="48" t="s">
+        <v>136</v>
+      </c>
+      <c r="D34" s="35" t="s">
+        <v>137</v>
+      </c>
+      <c r="E34" s="55" t="s">
+        <v>138</v>
+      </c>
+      <c r="F34" s="55" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="37" t="n">
+      <c r="A35" s="41" t="n">
         <v>4</v>
       </c>
-      <c r="B35" s="38" t="s">
-        <v>119</v>
-      </c>
-      <c r="C35" s="45" t="s">
-        <v>120</v>
-      </c>
-      <c r="D35" s="52" t="s">
-        <v>121</v>
-      </c>
-      <c r="E35" s="53" t="s">
-        <v>122</v>
-      </c>
-      <c r="F35" s="53" t="s">
-        <v>123</v>
+      <c r="B35" s="42" t="s">
+        <v>140</v>
+      </c>
+      <c r="C35" s="48" t="s">
+        <v>141</v>
+      </c>
+      <c r="D35" s="35" t="s">
+        <v>142</v>
+      </c>
+      <c r="E35" s="55" t="s">
+        <v>143</v>
+      </c>
+      <c r="F35" s="55" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="37" t="n">
+      <c r="A36" s="41" t="n">
         <v>5</v>
       </c>
-      <c r="B36" s="38" t="s">
-        <v>124</v>
-      </c>
-      <c r="C36" s="45" t="s">
-        <v>125</v>
-      </c>
-      <c r="D36" s="52" t="s">
-        <v>126</v>
-      </c>
-      <c r="E36" s="53" t="s">
-        <v>127</v>
-      </c>
-      <c r="F36" s="53" t="s">
-        <v>128</v>
+      <c r="B36" s="42" t="s">
+        <v>145</v>
+      </c>
+      <c r="C36" s="48" t="s">
+        <v>146</v>
+      </c>
+      <c r="D36" s="35" t="s">
+        <v>147</v>
+      </c>
+      <c r="E36" s="55" t="s">
+        <v>148</v>
+      </c>
+      <c r="F36" s="55" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="37" t="n">
+      <c r="A37" s="41" t="n">
         <v>6</v>
       </c>
-      <c r="B37" s="38" t="s">
-        <v>129</v>
-      </c>
-      <c r="C37" s="45" t="s">
-        <v>130</v>
-      </c>
-      <c r="D37" s="52" t="s">
-        <v>131</v>
-      </c>
-      <c r="E37" s="53" t="s">
-        <v>132</v>
-      </c>
-      <c r="F37" s="53" t="s">
-        <v>133</v>
+      <c r="B37" s="42" t="s">
+        <v>150</v>
+      </c>
+      <c r="C37" s="48" t="s">
+        <v>151</v>
+      </c>
+      <c r="D37" s="35" t="s">
+        <v>45</v>
+      </c>
+      <c r="E37" s="55" t="s">
+        <v>152</v>
+      </c>
+      <c r="F37" s="55" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="34" t="s">
-        <v>134</v>
+      <c r="A39" s="38" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="34" t="s">
-        <v>135</v>
+      <c r="A40" s="38" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="34" t="s">
-        <v>136</v>
+      <c r="A41" s="38" t="s">
+        <v>156</v>
       </c>
     </row>
   </sheetData>
@@ -3037,26 +3331,26 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="35" t="s">
-        <v>137</v>
-      </c>
-      <c r="H1" s="54" t="s">
-        <v>138</v>
+      <c r="A1" s="39" t="s">
+        <v>157</v>
+      </c>
+      <c r="H1" s="56" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>139</v>
+        <v>159</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>140</v>
+        <v>160</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3064,341 +3358,341 @@
         <v>12</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>141</v>
+        <v>161</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="G6" s="12" t="s">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="H6" s="12" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="I6" s="12" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="J6" s="12" t="s">
-        <v>52</v>
+        <v>73</v>
       </c>
       <c r="K6" s="12" t="s">
-        <v>53</v>
+        <v>74</v>
       </c>
       <c r="L6" s="12" t="s">
-        <v>54</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="37" t="n">
+      <c r="A7" s="41" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="38" t="s">
-        <v>142</v>
-      </c>
-      <c r="C7" s="39" t="s">
-        <v>143</v>
-      </c>
-      <c r="D7" s="37" t="s">
-        <v>144</v>
-      </c>
-      <c r="E7" s="40" t="n">
+      <c r="B7" s="42" t="s">
+        <v>162</v>
+      </c>
+      <c r="C7" s="43" t="s">
+        <v>163</v>
+      </c>
+      <c r="D7" s="41" t="s">
+        <v>164</v>
+      </c>
+      <c r="E7" s="44" t="n">
         <v>-144</v>
       </c>
-      <c r="F7" s="41" t="n">
+      <c r="F7" s="36" t="n">
         <v>300</v>
       </c>
-      <c r="G7" s="42" t="n">
+      <c r="G7" s="45" t="n">
         <f aca="false">IF(E7&gt;0,F7*E7/100,F7*100/ABS(E7))</f>
         <v>208.333333333333</v>
       </c>
-      <c r="H7" s="42" t="n">
+      <c r="H7" s="45" t="n">
         <f aca="false">F7+G7</f>
         <v>508.333333333333</v>
       </c>
-      <c r="I7" s="55" t="s">
-        <v>91</v>
-      </c>
-      <c r="J7" s="42" t="n">
+      <c r="I7" s="57" t="s">
+        <v>112</v>
+      </c>
+      <c r="J7" s="45" t="n">
         <f aca="false">IF(I7="Win",F7+G7,IF(I7="Push",F7,IF(I7="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K7" s="44" t="n">
+      <c r="K7" s="47" t="n">
         <f aca="false">IF(I7="Pending",0,J7-F7)</f>
         <v>0</v>
       </c>
-      <c r="L7" s="45" t="s">
-        <v>145</v>
+      <c r="L7" s="48" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="37" t="n">
+      <c r="A8" s="41" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="38" t="s">
-        <v>146</v>
-      </c>
-      <c r="C8" s="39" t="s">
-        <v>147</v>
-      </c>
-      <c r="D8" s="37" t="s">
-        <v>148</v>
-      </c>
-      <c r="E8" s="40" t="n">
+      <c r="B8" s="42" t="s">
+        <v>166</v>
+      </c>
+      <c r="C8" s="43" t="s">
+        <v>167</v>
+      </c>
+      <c r="D8" s="41" t="s">
+        <v>168</v>
+      </c>
+      <c r="E8" s="44" t="n">
         <v>-122</v>
       </c>
-      <c r="F8" s="41" t="n">
+      <c r="F8" s="36" t="n">
         <v>120</v>
       </c>
-      <c r="G8" s="42" t="n">
+      <c r="G8" s="45" t="n">
         <f aca="false">IF(E8&gt;0,F8*E8/100,F8*100/ABS(E8))</f>
         <v>98.3606557377049</v>
       </c>
-      <c r="H8" s="42" t="n">
+      <c r="H8" s="45" t="n">
         <f aca="false">F8+G8</f>
         <v>218.360655737705</v>
       </c>
-      <c r="I8" s="55" t="s">
-        <v>91</v>
-      </c>
-      <c r="J8" s="42" t="n">
+      <c r="I8" s="57" t="s">
+        <v>112</v>
+      </c>
+      <c r="J8" s="45" t="n">
         <f aca="false">IF(I8="Win",F8+G8,IF(I8="Push",F8,IF(I8="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K8" s="44" t="n">
+      <c r="K8" s="47" t="n">
         <f aca="false">IF(I8="Pending",0,J8-F8)</f>
         <v>0</v>
       </c>
-      <c r="L8" s="45" t="s">
-        <v>149</v>
+      <c r="L8" s="48" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="37" t="n">
+      <c r="A9" s="41" t="n">
         <v>3</v>
       </c>
-      <c r="B9" s="38" t="s">
+      <c r="B9" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="C9" s="43" t="s">
+        <v>171</v>
+      </c>
+      <c r="D9" s="41" t="s">
+        <v>172</v>
+      </c>
+      <c r="E9" s="44" t="n">
+        <v>175</v>
+      </c>
+      <c r="F9" s="36" t="n">
         <v>150</v>
       </c>
-      <c r="C9" s="39" t="s">
-        <v>151</v>
-      </c>
-      <c r="D9" s="37" t="s">
-        <v>152</v>
-      </c>
-      <c r="E9" s="40" t="n">
-        <v>175</v>
-      </c>
-      <c r="F9" s="41" t="n">
-        <v>150</v>
-      </c>
-      <c r="G9" s="42" t="n">
+      <c r="G9" s="45" t="n">
         <f aca="false">IF(E9&gt;0,F9*E9/100,F9*100/ABS(E9))</f>
         <v>262.5</v>
       </c>
-      <c r="H9" s="42" t="n">
+      <c r="H9" s="45" t="n">
         <f aca="false">F9+G9</f>
         <v>412.5</v>
       </c>
-      <c r="I9" s="55" t="s">
-        <v>91</v>
-      </c>
-      <c r="J9" s="42" t="n">
+      <c r="I9" s="57" t="s">
+        <v>112</v>
+      </c>
+      <c r="J9" s="45" t="n">
         <f aca="false">IF(I9="Win",F9+G9,IF(I9="Push",F9,IF(I9="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K9" s="44" t="n">
+      <c r="K9" s="47" t="n">
         <f aca="false">IF(I9="Pending",0,J9-F9)</f>
         <v>0</v>
       </c>
-      <c r="L9" s="45" t="s">
-        <v>153</v>
+      <c r="L9" s="48" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="37" t="n">
+      <c r="A10" s="41" t="n">
         <v>4</v>
       </c>
-      <c r="B10" s="38" t="s">
-        <v>154</v>
-      </c>
-      <c r="C10" s="39" t="s">
-        <v>155</v>
-      </c>
-      <c r="D10" s="37" t="s">
-        <v>152</v>
-      </c>
-      <c r="E10" s="40" t="n">
+      <c r="B10" s="42" t="s">
+        <v>174</v>
+      </c>
+      <c r="C10" s="43" t="s">
+        <v>175</v>
+      </c>
+      <c r="D10" s="41" t="s">
+        <v>172</v>
+      </c>
+      <c r="E10" s="44" t="n">
         <v>205</v>
       </c>
-      <c r="F10" s="41" t="n">
+      <c r="F10" s="36" t="n">
         <v>80</v>
       </c>
-      <c r="G10" s="42" t="n">
+      <c r="G10" s="45" t="n">
         <f aca="false">IF(E10&gt;0,F10*E10/100,F10*100/ABS(E10))</f>
         <v>164</v>
       </c>
-      <c r="H10" s="42" t="n">
+      <c r="H10" s="45" t="n">
         <f aca="false">F10+G10</f>
         <v>244</v>
       </c>
-      <c r="I10" s="55" t="s">
-        <v>91</v>
-      </c>
-      <c r="J10" s="42" t="n">
+      <c r="I10" s="57" t="s">
+        <v>112</v>
+      </c>
+      <c r="J10" s="45" t="n">
         <f aca="false">IF(I10="Win",F10+G10,IF(I10="Push",F10,IF(I10="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K10" s="44" t="n">
+      <c r="K10" s="47" t="n">
         <f aca="false">IF(I10="Pending",0,J10-F10)</f>
         <v>0</v>
       </c>
-      <c r="L10" s="45" t="s">
-        <v>156</v>
+      <c r="L10" s="48" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="37" t="n">
+      <c r="A11" s="41" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="38" t="s">
-        <v>157</v>
-      </c>
-      <c r="C11" s="39" t="s">
-        <v>158</v>
-      </c>
-      <c r="D11" s="37" t="s">
-        <v>159</v>
-      </c>
-      <c r="E11" s="40" t="n">
+      <c r="B11" s="42" t="s">
+        <v>177</v>
+      </c>
+      <c r="C11" s="43" t="s">
+        <v>178</v>
+      </c>
+      <c r="D11" s="41" t="s">
+        <v>179</v>
+      </c>
+      <c r="E11" s="44" t="n">
         <v>160</v>
       </c>
-      <c r="F11" s="41" t="n">
+      <c r="F11" s="36" t="n">
         <v>250</v>
       </c>
-      <c r="G11" s="42" t="n">
+      <c r="G11" s="45" t="n">
         <f aca="false">IF(E11&gt;0,F11*E11/100,F11*100/ABS(E11))</f>
         <v>400</v>
       </c>
-      <c r="H11" s="42" t="n">
+      <c r="H11" s="45" t="n">
         <f aca="false">F11+G11</f>
         <v>650</v>
       </c>
-      <c r="I11" s="55" t="s">
-        <v>91</v>
-      </c>
-      <c r="J11" s="42" t="n">
+      <c r="I11" s="57" t="s">
+        <v>112</v>
+      </c>
+      <c r="J11" s="45" t="n">
         <f aca="false">IF(I11="Win",F11+G11,IF(I11="Push",F11,IF(I11="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K11" s="44" t="n">
+      <c r="K11" s="47" t="n">
         <f aca="false">IF(I11="Pending",0,J11-F11)</f>
         <v>0</v>
       </c>
-      <c r="L11" s="45" t="s">
-        <v>160</v>
+      <c r="L11" s="48" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="37" t="n">
+      <c r="A12" s="41" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="38" t="s">
-        <v>161</v>
-      </c>
-      <c r="C12" s="39" t="s">
-        <v>162</v>
-      </c>
-      <c r="D12" s="37" t="s">
-        <v>159</v>
-      </c>
-      <c r="E12" s="40" t="n">
+      <c r="B12" s="42" t="s">
+        <v>181</v>
+      </c>
+      <c r="C12" s="43" t="s">
+        <v>182</v>
+      </c>
+      <c r="D12" s="41" t="s">
+        <v>179</v>
+      </c>
+      <c r="E12" s="44" t="n">
         <v>500</v>
       </c>
-      <c r="F12" s="41" t="n">
+      <c r="F12" s="36" t="n">
         <v>50</v>
       </c>
-      <c r="G12" s="42" t="n">
+      <c r="G12" s="45" t="n">
         <f aca="false">IF(E12&gt;0,F12*E12/100,F12*100/ABS(E12))</f>
         <v>250</v>
       </c>
-      <c r="H12" s="42" t="n">
+      <c r="H12" s="45" t="n">
         <f aca="false">F12+G12</f>
         <v>300</v>
       </c>
-      <c r="I12" s="55" t="s">
-        <v>91</v>
-      </c>
-      <c r="J12" s="42" t="n">
+      <c r="I12" s="57" t="s">
+        <v>112</v>
+      </c>
+      <c r="J12" s="45" t="n">
         <f aca="false">IF(I12="Win",F12+G12,IF(I12="Push",F12,IF(I12="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K12" s="44" t="n">
+      <c r="K12" s="47" t="n">
         <f aca="false">IF(I12="Pending",0,J12-F12)</f>
         <v>0</v>
       </c>
-      <c r="L12" s="45" t="s">
-        <v>163</v>
+      <c r="L12" s="48" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="37" t="n">
+      <c r="A13" s="41" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="38" t="s">
-        <v>164</v>
-      </c>
-      <c r="C13" s="39" t="s">
-        <v>165</v>
-      </c>
-      <c r="D13" s="37" t="s">
-        <v>85</v>
-      </c>
-      <c r="E13" s="40" t="n">
+      <c r="B13" s="42" t="s">
+        <v>184</v>
+      </c>
+      <c r="C13" s="43" t="s">
+        <v>185</v>
+      </c>
+      <c r="D13" s="41" t="s">
+        <v>106</v>
+      </c>
+      <c r="E13" s="44" t="n">
         <v>179</v>
       </c>
-      <c r="F13" s="41" t="n">
+      <c r="F13" s="36" t="n">
         <v>50</v>
       </c>
-      <c r="G13" s="42" t="n">
+      <c r="G13" s="45" t="n">
         <f aca="false">IF(E13&gt;0,F13*E13/100,F13*100/ABS(E13))</f>
         <v>89.5</v>
       </c>
-      <c r="H13" s="42" t="n">
+      <c r="H13" s="45" t="n">
         <f aca="false">F13+G13</f>
         <v>139.5</v>
       </c>
-      <c r="I13" s="55" t="s">
-        <v>91</v>
-      </c>
-      <c r="J13" s="42" t="n">
+      <c r="I13" s="57" t="s">
+        <v>112</v>
+      </c>
+      <c r="J13" s="45" t="n">
         <f aca="false">IF(I13="Win",F13+G13,IF(I13="Push",F13,IF(I13="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K13" s="44" t="n">
+      <c r="K13" s="47" t="n">
         <f aca="false">IF(I13="Pending",0,J13-F13)</f>
         <v>0</v>
       </c>
-      <c r="L13" s="45" t="s">
-        <v>166</v>
+      <c r="L13" s="48" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="47"/>
-      <c r="B14" s="48" t="s">
-        <v>35</v>
-      </c>
-      <c r="C14" s="47"/>
-      <c r="D14" s="47"/>
-      <c r="E14" s="47"/>
+      <c r="A14" s="50"/>
+      <c r="B14" s="51" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" s="50"/>
+      <c r="D14" s="50"/>
+      <c r="E14" s="50"/>
       <c r="F14" s="31" t="n">
         <f aca="false">SUM(F7:F13)</f>
         <v>1000</v>
@@ -3411,7 +3705,7 @@
         <f aca="false">SUM(H7:H13)</f>
         <v>2472.69398907104</v>
       </c>
-      <c r="I14" s="47"/>
+      <c r="I14" s="50"/>
       <c r="J14" s="32" t="n">
         <f aca="false">SUM(J7:J13)</f>
         <v>0</v>
@@ -3420,106 +3714,106 @@
         <f aca="false">SUM(K7:K13)</f>
         <v>0</v>
       </c>
-      <c r="L14" s="47"/>
+      <c r="L14" s="50"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="4" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="38" t="s">
-        <v>88</v>
-      </c>
-      <c r="C17" s="49" t="n">
+      <c r="B17" s="42" t="s">
+        <v>109</v>
+      </c>
+      <c r="C17" s="52" t="n">
         <f aca="false">COUNTIF(I7:I13,"Win")</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="38" t="s">
-        <v>89</v>
-      </c>
-      <c r="C18" s="49" t="n">
+      <c r="B18" s="42" t="s">
+        <v>110</v>
+      </c>
+      <c r="C18" s="52" t="n">
         <f aca="false">COUNTIF(I7:I13,"Loss")</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="38" t="s">
-        <v>90</v>
-      </c>
-      <c r="C19" s="49" t="n">
+      <c r="B19" s="42" t="s">
+        <v>111</v>
+      </c>
+      <c r="C19" s="52" t="n">
         <f aca="false">COUNTIF(I7:I13,"Push")</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="38" t="s">
-        <v>91</v>
-      </c>
-      <c r="C20" s="49" t="n">
+      <c r="B20" s="42" t="s">
+        <v>112</v>
+      </c>
+      <c r="C20" s="52" t="n">
         <f aca="false">COUNTIF(I7:I13,"Pending")</f>
         <v>7</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="38" t="s">
-        <v>92</v>
-      </c>
-      <c r="C21" s="50" t="str">
+      <c r="B21" s="42" t="s">
+        <v>113</v>
+      </c>
+      <c r="C21" s="53" t="str">
         <f aca="false">IF(COUNTIF(I7:I13,"Win")+COUNTIF(I7:I13,"Loss")=0,"—",COUNTIF(I7:I13,"Win")/(COUNTIF(I7:I13,"Win")+COUNTIF(I7:I13,"Loss")))</f>
         <v>—</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="38" t="s">
-        <v>93</v>
-      </c>
-      <c r="C22" s="51" t="n">
+      <c r="B22" s="42" t="s">
+        <v>114</v>
+      </c>
+      <c r="C22" s="54" t="n">
         <f aca="false">SUM(F7:F13)</f>
         <v>1000</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="38" t="s">
-        <v>94</v>
-      </c>
-      <c r="C23" s="42" t="n">
+      <c r="B23" s="42" t="s">
+        <v>115</v>
+      </c>
+      <c r="C23" s="45" t="n">
         <f aca="false">SUM(J7:J13)</f>
         <v>0</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="38" t="s">
-        <v>95</v>
-      </c>
-      <c r="C24" s="44" t="n">
+      <c r="B24" s="42" t="s">
+        <v>116</v>
+      </c>
+      <c r="C24" s="47" t="n">
         <f aca="false">SUM(K7:K13)</f>
         <v>0</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="38" t="s">
-        <v>96</v>
-      </c>
-      <c r="C25" s="50" t="n">
+      <c r="B25" s="42" t="s">
+        <v>117</v>
+      </c>
+      <c r="C25" s="53" t="n">
         <f aca="false">IF(SUM(F7:F13)=0,"—",SUM(K7:K13)/SUM(F7:F13))</f>
         <v>0</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="38" t="s">
-        <v>167</v>
-      </c>
-      <c r="C26" s="51" t="n">
+      <c r="B26" s="42" t="s">
+        <v>187</v>
+      </c>
+      <c r="C26" s="54" t="n">
         <f aca="false">929</f>
         <v>929</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
-        <v>168</v>
+        <v>188</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3527,88 +3821,88 @@
         <v>12</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>100</v>
+        <v>121</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>101</v>
+        <v>122</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="F29" s="12" t="s">
-        <v>103</v>
+        <v>124</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="37" t="n">
+      <c r="A30" s="41" t="n">
         <v>1</v>
       </c>
-      <c r="B30" s="38" t="s">
-        <v>171</v>
-      </c>
-      <c r="C30" s="45" t="s">
-        <v>172</v>
-      </c>
-      <c r="D30" s="52" t="s">
-        <v>173</v>
-      </c>
-      <c r="E30" s="55"/>
-      <c r="F30" s="55"/>
+      <c r="B30" s="42" t="s">
+        <v>191</v>
+      </c>
+      <c r="C30" s="48" t="s">
+        <v>192</v>
+      </c>
+      <c r="D30" s="35" t="s">
+        <v>193</v>
+      </c>
+      <c r="E30" s="57"/>
+      <c r="F30" s="57"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="37" t="n">
+      <c r="A31" s="41" t="n">
         <v>2</v>
       </c>
-      <c r="B31" s="38" t="s">
-        <v>174</v>
-      </c>
-      <c r="C31" s="45" t="s">
-        <v>175</v>
-      </c>
-      <c r="D31" s="52" t="s">
-        <v>176</v>
-      </c>
-      <c r="E31" s="55"/>
-      <c r="F31" s="55"/>
+      <c r="B31" s="42" t="s">
+        <v>194</v>
+      </c>
+      <c r="C31" s="48" t="s">
+        <v>195</v>
+      </c>
+      <c r="D31" s="35" t="s">
+        <v>196</v>
+      </c>
+      <c r="E31" s="57"/>
+      <c r="F31" s="57"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="37" t="n">
+      <c r="A32" s="41" t="n">
         <v>3</v>
       </c>
-      <c r="B32" s="38" t="s">
-        <v>177</v>
-      </c>
-      <c r="C32" s="45" t="s">
-        <v>178</v>
-      </c>
-      <c r="D32" s="52" t="s">
-        <v>179</v>
-      </c>
-      <c r="E32" s="55"/>
-      <c r="F32" s="55"/>
+      <c r="B32" s="42" t="s">
+        <v>197</v>
+      </c>
+      <c r="C32" s="48" t="s">
+        <v>198</v>
+      </c>
+      <c r="D32" s="35" t="s">
+        <v>199</v>
+      </c>
+      <c r="E32" s="57"/>
+      <c r="F32" s="57"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="37" t="n">
+      <c r="A33" s="41" t="n">
         <v>4</v>
       </c>
-      <c r="B33" s="38" t="s">
-        <v>180</v>
-      </c>
-      <c r="C33" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="D33" s="52" t="s">
-        <v>182</v>
-      </c>
-      <c r="E33" s="55"/>
-      <c r="F33" s="55"/>
+      <c r="B33" s="42" t="s">
+        <v>200</v>
+      </c>
+      <c r="C33" s="48" t="s">
+        <v>201</v>
+      </c>
+      <c r="D33" s="35" t="s">
+        <v>202</v>
+      </c>
+      <c r="E33" s="57"/>
+      <c r="F33" s="57"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="34" t="s">
-        <v>183</v>
+      <c r="A35" s="38" t="s">
+        <v>203</v>
       </c>
     </row>
   </sheetData>
@@ -3666,26 +3960,26 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="35" t="s">
-        <v>184</v>
-      </c>
-      <c r="H1" s="54" t="s">
-        <v>185</v>
+      <c r="A1" s="39" t="s">
+        <v>204</v>
+      </c>
+      <c r="H1" s="56" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>186</v>
+        <v>206</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>187</v>
+        <v>207</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3693,410 +3987,410 @@
         <v>12</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>188</v>
+        <v>208</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="G6" s="12" t="s">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="H6" s="12" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="I6" s="12" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="J6" s="12" t="s">
-        <v>52</v>
+        <v>73</v>
       </c>
       <c r="K6" s="12" t="s">
-        <v>53</v>
+        <v>74</v>
       </c>
       <c r="L6" s="12" t="s">
-        <v>189</v>
+        <v>209</v>
       </c>
       <c r="M6" s="12" t="s">
-        <v>54</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="37" t="n">
+      <c r="A7" s="41" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="38" t="s">
-        <v>190</v>
-      </c>
-      <c r="C7" s="39" t="s">
-        <v>191</v>
-      </c>
-      <c r="D7" s="37" t="s">
-        <v>57</v>
-      </c>
-      <c r="E7" s="40" t="n">
+      <c r="B7" s="42" t="s">
+        <v>210</v>
+      </c>
+      <c r="C7" s="43" t="s">
+        <v>211</v>
+      </c>
+      <c r="D7" s="41" t="s">
+        <v>78</v>
+      </c>
+      <c r="E7" s="44" t="n">
         <v>-155</v>
       </c>
-      <c r="F7" s="41" t="n">
+      <c r="F7" s="36" t="n">
         <v>200</v>
       </c>
-      <c r="G7" s="42" t="n">
+      <c r="G7" s="45" t="n">
         <f aca="false">IF(E7&gt;0,F7*E7/100,F7*100/ABS(E7))</f>
         <v>129.032258064516</v>
       </c>
-      <c r="H7" s="42" t="n">
+      <c r="H7" s="45" t="n">
         <f aca="false">F7+G7</f>
         <v>329.032258064516</v>
       </c>
-      <c r="I7" s="55" t="s">
-        <v>91</v>
-      </c>
-      <c r="J7" s="42" t="n">
+      <c r="I7" s="57" t="s">
+        <v>112</v>
+      </c>
+      <c r="J7" s="45" t="n">
         <f aca="false">IF(I7="Win",F7+G7,IF(I7="Push",F7,IF(I7="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K7" s="44" t="n">
+      <c r="K7" s="47" t="n">
         <f aca="false">IF(I7="Pending",0,J7-F7)</f>
         <v>0</v>
       </c>
-      <c r="L7" s="56" t="n">
+      <c r="L7" s="58" t="n">
         <v>0.62</v>
       </c>
-      <c r="M7" s="45" t="s">
-        <v>192</v>
+      <c r="M7" s="48" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="37" t="n">
+      <c r="A8" s="41" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="38" t="s">
-        <v>193</v>
-      </c>
-      <c r="C8" s="39" t="s">
-        <v>194</v>
-      </c>
-      <c r="D8" s="37" t="s">
-        <v>57</v>
-      </c>
-      <c r="E8" s="40" t="n">
+      <c r="B8" s="42" t="s">
+        <v>213</v>
+      </c>
+      <c r="C8" s="43" t="s">
+        <v>214</v>
+      </c>
+      <c r="D8" s="41" t="s">
+        <v>78</v>
+      </c>
+      <c r="E8" s="44" t="n">
         <v>-104</v>
       </c>
-      <c r="F8" s="41" t="n">
+      <c r="F8" s="36" t="n">
         <v>150</v>
       </c>
-      <c r="G8" s="42" t="n">
+      <c r="G8" s="45" t="n">
         <f aca="false">IF(E8&gt;0,F8*E8/100,F8*100/ABS(E8))</f>
         <v>144.230769230769</v>
       </c>
-      <c r="H8" s="42" t="n">
+      <c r="H8" s="45" t="n">
         <f aca="false">F8+G8</f>
         <v>294.230769230769</v>
       </c>
-      <c r="I8" s="55" t="s">
-        <v>66</v>
-      </c>
-      <c r="J8" s="42" t="n">
+      <c r="I8" s="49" t="s">
+        <v>87</v>
+      </c>
+      <c r="J8" s="45" t="n">
         <f aca="false">IF(I8="Win",F8+G8,IF(I8="Push",F8,IF(I8="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K8" s="44" t="n">
+      <c r="K8" s="47" t="n">
         <f aca="false">IF(I8="Pending",0,J8-F8)</f>
         <v>-150</v>
       </c>
-      <c r="L8" s="56" t="n">
+      <c r="L8" s="58" t="n">
         <v>0.54</v>
       </c>
-      <c r="M8" s="45" t="s">
-        <v>195</v>
+      <c r="M8" s="48" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="37" t="n">
+      <c r="A9" s="41" t="n">
         <v>3</v>
       </c>
-      <c r="B9" s="38" t="s">
-        <v>196</v>
-      </c>
-      <c r="C9" s="39" t="s">
-        <v>197</v>
-      </c>
-      <c r="D9" s="37" t="s">
-        <v>57</v>
-      </c>
-      <c r="E9" s="40" t="n">
+      <c r="B9" s="42" t="s">
+        <v>216</v>
+      </c>
+      <c r="C9" s="43" t="s">
+        <v>217</v>
+      </c>
+      <c r="D9" s="41" t="s">
+        <v>78</v>
+      </c>
+      <c r="E9" s="44" t="n">
         <v>-115</v>
       </c>
-      <c r="F9" s="41" t="n">
+      <c r="F9" s="36" t="n">
         <v>150</v>
       </c>
-      <c r="G9" s="42" t="n">
+      <c r="G9" s="45" t="n">
         <f aca="false">IF(E9&gt;0,F9*E9/100,F9*100/ABS(E9))</f>
         <v>130.434782608696</v>
       </c>
-      <c r="H9" s="42" t="n">
+      <c r="H9" s="45" t="n">
         <f aca="false">F9+G9</f>
         <v>280.434782608696</v>
       </c>
-      <c r="I9" s="55" t="s">
-        <v>66</v>
-      </c>
-      <c r="J9" s="42" t="n">
+      <c r="I9" s="49" t="s">
+        <v>87</v>
+      </c>
+      <c r="J9" s="45" t="n">
         <f aca="false">IF(I9="Win",F9+G9,IF(I9="Push",F9,IF(I9="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K9" s="44" t="n">
+      <c r="K9" s="47" t="n">
         <f aca="false">IF(I9="Pending",0,J9-F9)</f>
         <v>-150</v>
       </c>
-      <c r="L9" s="56" t="n">
+      <c r="L9" s="58" t="n">
         <v>0.55</v>
       </c>
-      <c r="M9" s="45" t="s">
-        <v>198</v>
+      <c r="M9" s="48" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="37" t="n">
+      <c r="A10" s="41" t="n">
         <v>4</v>
       </c>
-      <c r="B10" s="38" t="s">
-        <v>199</v>
-      </c>
-      <c r="C10" s="39" t="s">
-        <v>200</v>
-      </c>
-      <c r="D10" s="37" t="s">
-        <v>148</v>
-      </c>
-      <c r="E10" s="40" t="n">
+      <c r="B10" s="42" t="s">
+        <v>219</v>
+      </c>
+      <c r="C10" s="43" t="s">
+        <v>220</v>
+      </c>
+      <c r="D10" s="41" t="s">
+        <v>168</v>
+      </c>
+      <c r="E10" s="44" t="n">
         <v>-114</v>
       </c>
-      <c r="F10" s="41" t="n">
+      <c r="F10" s="36" t="n">
         <v>120</v>
       </c>
-      <c r="G10" s="42" t="n">
+      <c r="G10" s="45" t="n">
         <f aca="false">IF(E10&gt;0,F10*E10/100,F10*100/ABS(E10))</f>
         <v>105.263157894737</v>
       </c>
-      <c r="H10" s="42" t="n">
+      <c r="H10" s="45" t="n">
         <f aca="false">F10+G10</f>
         <v>225.263157894737</v>
       </c>
-      <c r="I10" s="55" t="s">
-        <v>66</v>
-      </c>
-      <c r="J10" s="42" t="n">
+      <c r="I10" s="49" t="s">
+        <v>87</v>
+      </c>
+      <c r="J10" s="45" t="n">
         <f aca="false">IF(I10="Win",F10+G10,IF(I10="Push",F10,IF(I10="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K10" s="44" t="n">
+      <c r="K10" s="47" t="n">
         <f aca="false">IF(I10="Pending",0,J10-F10)</f>
         <v>-120</v>
       </c>
-      <c r="L10" s="56" t="n">
+      <c r="L10" s="58" t="n">
         <v>0.55</v>
       </c>
-      <c r="M10" s="45" t="s">
-        <v>201</v>
+      <c r="M10" s="48" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="37" t="n">
+      <c r="A11" s="41" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="38" t="s">
-        <v>202</v>
-      </c>
-      <c r="C11" s="39" t="s">
-        <v>203</v>
-      </c>
-      <c r="D11" s="37" t="s">
-        <v>57</v>
-      </c>
-      <c r="E11" s="40" t="n">
+      <c r="B11" s="42" t="s">
+        <v>222</v>
+      </c>
+      <c r="C11" s="43" t="s">
+        <v>223</v>
+      </c>
+      <c r="D11" s="41" t="s">
+        <v>78</v>
+      </c>
+      <c r="E11" s="44" t="n">
         <v>104</v>
       </c>
-      <c r="F11" s="41" t="n">
+      <c r="F11" s="36" t="n">
         <v>130</v>
       </c>
-      <c r="G11" s="42" t="n">
+      <c r="G11" s="45" t="n">
         <f aca="false">IF(E11&gt;0,F11*E11/100,F11*100/ABS(E11))</f>
         <v>135.2</v>
       </c>
-      <c r="H11" s="42" t="n">
+      <c r="H11" s="45" t="n">
         <f aca="false">F11+G11</f>
         <v>265.2</v>
       </c>
-      <c r="I11" s="43" t="s">
-        <v>58</v>
-      </c>
-      <c r="J11" s="42" t="n">
+      <c r="I11" s="46" t="s">
+        <v>79</v>
+      </c>
+      <c r="J11" s="45" t="n">
         <f aca="false">IF(I11="Win",F11+G11,IF(I11="Push",F11,IF(I11="Loss",0,0)))</f>
         <v>265.2</v>
       </c>
-      <c r="K11" s="44" t="n">
+      <c r="K11" s="47" t="n">
         <f aca="false">IF(I11="Pending",0,J11-F11)</f>
         <v>135.2</v>
       </c>
-      <c r="L11" s="56" t="n">
+      <c r="L11" s="58" t="n">
         <v>0.52</v>
       </c>
-      <c r="M11" s="45" t="s">
-        <v>204</v>
+      <c r="M11" s="48" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="37" t="n">
+      <c r="A12" s="41" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="38" t="s">
-        <v>205</v>
-      </c>
-      <c r="C12" s="39" t="s">
-        <v>206</v>
-      </c>
-      <c r="D12" s="37" t="s">
-        <v>57</v>
-      </c>
-      <c r="E12" s="40" t="n">
+      <c r="B12" s="42" t="s">
+        <v>225</v>
+      </c>
+      <c r="C12" s="43" t="s">
+        <v>226</v>
+      </c>
+      <c r="D12" s="41" t="s">
+        <v>78</v>
+      </c>
+      <c r="E12" s="44" t="n">
         <v>108</v>
       </c>
-      <c r="F12" s="41" t="n">
+      <c r="F12" s="36" t="n">
         <v>100</v>
       </c>
-      <c r="G12" s="42" t="n">
+      <c r="G12" s="45" t="n">
         <f aca="false">IF(E12&gt;0,F12*E12/100,F12*100/ABS(E12))</f>
         <v>108</v>
       </c>
-      <c r="H12" s="42" t="n">
+      <c r="H12" s="45" t="n">
         <f aca="false">F12+G12</f>
         <v>208</v>
       </c>
-      <c r="I12" s="55" t="s">
-        <v>66</v>
-      </c>
-      <c r="J12" s="42" t="n">
+      <c r="I12" s="49" t="s">
+        <v>87</v>
+      </c>
+      <c r="J12" s="45" t="n">
         <f aca="false">IF(I12="Win",F12+G12,IF(I12="Push",F12,IF(I12="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K12" s="44" t="n">
+      <c r="K12" s="47" t="n">
         <f aca="false">IF(I12="Pending",0,J12-F12)</f>
         <v>-100</v>
       </c>
-      <c r="L12" s="56" t="n">
+      <c r="L12" s="58" t="n">
         <v>0.5</v>
       </c>
-      <c r="M12" s="45" t="s">
-        <v>207</v>
+      <c r="M12" s="48" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="37" t="n">
+      <c r="A13" s="41" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="38" t="s">
-        <v>208</v>
-      </c>
-      <c r="C13" s="39" t="s">
-        <v>209</v>
-      </c>
-      <c r="D13" s="37" t="s">
-        <v>57</v>
-      </c>
-      <c r="E13" s="40" t="n">
+      <c r="B13" s="42" t="s">
+        <v>228</v>
+      </c>
+      <c r="C13" s="43" t="s">
+        <v>229</v>
+      </c>
+      <c r="D13" s="41" t="s">
+        <v>78</v>
+      </c>
+      <c r="E13" s="44" t="n">
         <v>108</v>
       </c>
-      <c r="F13" s="41" t="n">
+      <c r="F13" s="36" t="n">
         <v>100</v>
       </c>
-      <c r="G13" s="42" t="n">
+      <c r="G13" s="45" t="n">
         <f aca="false">IF(E13&gt;0,F13*E13/100,F13*100/ABS(E13))</f>
         <v>108</v>
       </c>
-      <c r="H13" s="42" t="n">
+      <c r="H13" s="45" t="n">
         <f aca="false">F13+G13</f>
         <v>208</v>
       </c>
-      <c r="I13" s="55" t="s">
-        <v>58</v>
-      </c>
-      <c r="J13" s="42" t="n">
+      <c r="I13" s="46" t="s">
+        <v>79</v>
+      </c>
+      <c r="J13" s="45" t="n">
         <f aca="false">IF(I13="Win",F13+G13,IF(I13="Push",F13,IF(I13="Loss",0,0)))</f>
         <v>208</v>
       </c>
-      <c r="K13" s="44" t="n">
+      <c r="K13" s="47" t="n">
         <f aca="false">IF(I13="Pending",0,J13-F13)</f>
         <v>108</v>
       </c>
-      <c r="L13" s="56" t="n">
+      <c r="L13" s="58" t="n">
         <v>0.5</v>
       </c>
-      <c r="M13" s="45" t="s">
-        <v>210</v>
+      <c r="M13" s="48" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="37" t="n">
+      <c r="A14" s="41" t="n">
         <v>8</v>
       </c>
-      <c r="B14" s="38" t="s">
-        <v>211</v>
-      </c>
-      <c r="C14" s="39" t="s">
-        <v>212</v>
-      </c>
-      <c r="D14" s="37" t="s">
-        <v>85</v>
-      </c>
-      <c r="E14" s="40" t="n">
+      <c r="B14" s="42" t="s">
+        <v>231</v>
+      </c>
+      <c r="C14" s="43" t="s">
+        <v>232</v>
+      </c>
+      <c r="D14" s="41" t="s">
+        <v>106</v>
+      </c>
+      <c r="E14" s="44" t="n">
         <v>732</v>
       </c>
-      <c r="F14" s="41" t="n">
+      <c r="F14" s="36" t="n">
         <v>50</v>
       </c>
-      <c r="G14" s="42" t="n">
+      <c r="G14" s="45" t="n">
         <f aca="false">IF(E14&gt;0,F14*E14/100,F14*100/ABS(E14))</f>
         <v>366</v>
       </c>
-      <c r="H14" s="42" t="n">
+      <c r="H14" s="45" t="n">
         <f aca="false">F14+G14</f>
         <v>416</v>
       </c>
-      <c r="I14" s="55" t="s">
-        <v>66</v>
-      </c>
-      <c r="J14" s="42" t="n">
+      <c r="I14" s="49" t="s">
+        <v>87</v>
+      </c>
+      <c r="J14" s="45" t="n">
         <f aca="false">IF(I14="Win",F14+G14,IF(I14="Push",F14,IF(I14="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K14" s="44" t="n">
+      <c r="K14" s="47" t="n">
         <f aca="false">IF(I14="Pending",0,J14-F14)</f>
         <v>-50</v>
       </c>
-      <c r="L14" s="56" t="n">
+      <c r="L14" s="58" t="n">
         <v>0.14</v>
       </c>
-      <c r="M14" s="45" t="s">
-        <v>213</v>
+      <c r="M14" s="48" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="47"/>
-      <c r="B15" s="48" t="s">
-        <v>35</v>
-      </c>
-      <c r="C15" s="47"/>
-      <c r="D15" s="47"/>
-      <c r="E15" s="47"/>
+      <c r="A15" s="50"/>
+      <c r="B15" s="51" t="s">
+        <v>37</v>
+      </c>
+      <c r="C15" s="50"/>
+      <c r="D15" s="50"/>
+      <c r="E15" s="50"/>
       <c r="F15" s="31" t="n">
         <f aca="false">SUM(F7:F14)</f>
         <v>1000</v>
@@ -4109,7 +4403,7 @@
         <f aca="false">SUM(H7:H14)</f>
         <v>2226.16096779872</v>
       </c>
-      <c r="I15" s="47"/>
+      <c r="I15" s="50"/>
       <c r="J15" s="32" t="n">
         <f aca="false">SUM(J7:J14)</f>
         <v>473.2</v>
@@ -4118,128 +4412,128 @@
         <f aca="false">SUM(K7:K14)</f>
         <v>-326.8</v>
       </c>
-      <c r="L15" s="57" t="n">
+      <c r="L15" s="59" t="n">
         <f aca="false">SUM(L7:L14)</f>
         <v>3.92</v>
       </c>
-      <c r="M15" s="47"/>
+      <c r="M15" s="50"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="4" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="38" t="s">
-        <v>88</v>
-      </c>
-      <c r="C18" s="49" t="n">
+      <c r="B18" s="42" t="s">
+        <v>109</v>
+      </c>
+      <c r="C18" s="52" t="n">
         <f aca="false">COUNTIF(I7:I14,"Win")</f>
         <v>2</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="38" t="s">
-        <v>89</v>
-      </c>
-      <c r="C19" s="49" t="n">
+      <c r="B19" s="42" t="s">
+        <v>110</v>
+      </c>
+      <c r="C19" s="52" t="n">
         <f aca="false">COUNTIF(I7:I14,"Loss")</f>
         <v>5</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="38" t="s">
-        <v>90</v>
-      </c>
-      <c r="C20" s="49" t="n">
+      <c r="B20" s="42" t="s">
+        <v>111</v>
+      </c>
+      <c r="C20" s="52" t="n">
         <f aca="false">COUNTIF(I7:I14,"Push")</f>
         <v>0</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="38" t="s">
-        <v>91</v>
-      </c>
-      <c r="C21" s="49" t="n">
+      <c r="B21" s="42" t="s">
+        <v>112</v>
+      </c>
+      <c r="C21" s="52" t="n">
         <f aca="false">COUNTIF(I7:I14,"Pending")</f>
         <v>1</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="38" t="s">
-        <v>92</v>
-      </c>
-      <c r="C22" s="50" t="n">
+      <c r="B22" s="42" t="s">
+        <v>113</v>
+      </c>
+      <c r="C22" s="53" t="n">
         <f aca="false">IF(COUNTIF(I7:I14,"Win")+COUNTIF(I7:I14,"Loss")=0,"—",COUNTIF(I7:I14,"Win")/(COUNTIF(I7:I14,"Win")+COUNTIF(I7:I14,"Loss")))</f>
         <v>0.285714285714286</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="38" t="s">
-        <v>93</v>
-      </c>
-      <c r="C23" s="51" t="n">
+      <c r="B23" s="42" t="s">
+        <v>114</v>
+      </c>
+      <c r="C23" s="54" t="n">
         <f aca="false">SUM(F7:F14)</f>
         <v>1000</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="38" t="s">
-        <v>94</v>
-      </c>
-      <c r="C24" s="42" t="n">
+      <c r="B24" s="42" t="s">
+        <v>115</v>
+      </c>
+      <c r="C24" s="45" t="n">
         <f aca="false">SUM(J7:J14)</f>
         <v>473.2</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="38" t="s">
-        <v>95</v>
-      </c>
-      <c r="C25" s="44" t="n">
+      <c r="B25" s="42" t="s">
+        <v>116</v>
+      </c>
+      <c r="C25" s="47" t="n">
         <f aca="false">SUM(K7:K14)</f>
         <v>-326.8</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="38" t="s">
-        <v>96</v>
-      </c>
-      <c r="C26" s="50" t="n">
+      <c r="B26" s="42" t="s">
+        <v>117</v>
+      </c>
+      <c r="C26" s="53" t="n">
         <f aca="false">IF(SUM(F7:F14)=0,"—",SUM(K7:K14)/SUM(F7:F14))</f>
         <v>-0.3268</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="38" t="s">
-        <v>97</v>
-      </c>
-      <c r="C27" s="42" t="n">
+      <c r="B27" s="42" t="s">
+        <v>118</v>
+      </c>
+      <c r="C27" s="45" t="n">
         <f aca="false">SUM(H7:H14)</f>
         <v>2226.16096779872</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="38" t="s">
-        <v>214</v>
-      </c>
-      <c r="C28" s="58" t="n">
+      <c r="B28" s="42" t="s">
+        <v>234</v>
+      </c>
+      <c r="C28" s="60" t="n">
         <f aca="false">SUM(L7:L14)</f>
         <v>3.92</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="38" t="s">
-        <v>215</v>
-      </c>
-      <c r="C29" s="44" t="n">
+      <c r="B29" s="42" t="s">
+        <v>235</v>
+      </c>
+      <c r="C29" s="47" t="n">
         <f aca="false">SUMPRODUCT(L7:L14,G7:G14)-SUMPRODUCT(1-L7:L14,F7:F14)</f>
         <v>45.1624826615033</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>216</v>
+        <v>236</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4247,168 +4541,152 @@
         <v>12</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>217</v>
+        <v>237</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>100</v>
+        <v>121</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>218</v>
+        <v>238</v>
       </c>
       <c r="E32" s="12" t="s">
-        <v>102</v>
+        <v>123</v>
       </c>
       <c r="F32" s="12" t="s">
-        <v>103</v>
+        <v>124</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="37" t="n">
+      <c r="A33" s="41" t="n">
         <v>1</v>
       </c>
-      <c r="B33" s="38" t="s">
-        <v>219</v>
-      </c>
-      <c r="C33" s="45" t="s">
-        <v>220</v>
-      </c>
-      <c r="D33" s="52" t="s">
-        <v>221</v>
-      </c>
-      <c r="E33" s="55" t="s">
-        <v>222</v>
-      </c>
-      <c r="F33" s="55" t="s">
-        <v>223</v>
-      </c>
+      <c r="B33" s="42" t="s">
+        <v>239</v>
+      </c>
+      <c r="C33" s="48" t="s">
+        <v>240</v>
+      </c>
+      <c r="D33" s="35" t="s">
+        <v>241</v>
+      </c>
+      <c r="E33" s="57"/>
+      <c r="F33" s="57"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="37" t="n">
+      <c r="A34" s="41" t="n">
         <v>2</v>
       </c>
-      <c r="B34" s="38" t="s">
-        <v>224</v>
-      </c>
-      <c r="C34" s="45" t="s">
-        <v>225</v>
-      </c>
-      <c r="D34" s="52" t="s">
-        <v>226</v>
-      </c>
-      <c r="E34" s="55" t="s">
-        <v>227</v>
-      </c>
-      <c r="F34" s="55" t="s">
-        <v>228</v>
-      </c>
+      <c r="B34" s="42" t="s">
+        <v>242</v>
+      </c>
+      <c r="C34" s="48" t="s">
+        <v>243</v>
+      </c>
+      <c r="D34" s="35" t="s">
+        <v>244</v>
+      </c>
+      <c r="E34" s="57"/>
+      <c r="F34" s="57"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="37" t="n">
+      <c r="A35" s="41" t="n">
         <v>3</v>
       </c>
-      <c r="B35" s="38" t="s">
-        <v>229</v>
-      </c>
-      <c r="C35" s="45" t="s">
-        <v>230</v>
-      </c>
-      <c r="D35" s="52" t="s">
-        <v>231</v>
-      </c>
-      <c r="E35" s="55" t="s">
-        <v>232</v>
-      </c>
-      <c r="F35" s="55" t="s">
-        <v>233</v>
-      </c>
+      <c r="B35" s="42" t="s">
+        <v>245</v>
+      </c>
+      <c r="C35" s="48" t="s">
+        <v>246</v>
+      </c>
+      <c r="D35" s="35" t="s">
+        <v>247</v>
+      </c>
+      <c r="E35" s="57"/>
+      <c r="F35" s="57"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="37" t="n">
+      <c r="A36" s="41" t="n">
         <v>4</v>
       </c>
-      <c r="B36" s="38" t="s">
-        <v>234</v>
-      </c>
-      <c r="C36" s="45" t="s">
-        <v>235</v>
-      </c>
-      <c r="D36" s="52" t="s">
-        <v>236</v>
-      </c>
-      <c r="E36" s="55"/>
-      <c r="F36" s="55"/>
+      <c r="B36" s="42" t="s">
+        <v>248</v>
+      </c>
+      <c r="C36" s="48" t="s">
+        <v>249</v>
+      </c>
+      <c r="D36" s="35" t="s">
+        <v>250</v>
+      </c>
+      <c r="E36" s="57"/>
+      <c r="F36" s="57"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="37" t="n">
+      <c r="A37" s="41" t="n">
         <v>5</v>
       </c>
-      <c r="B37" s="38" t="s">
-        <v>237</v>
-      </c>
-      <c r="C37" s="45" t="s">
-        <v>238</v>
-      </c>
-      <c r="D37" s="52" t="s">
-        <v>239</v>
-      </c>
-      <c r="E37" s="55" t="s">
-        <v>240</v>
-      </c>
-      <c r="F37" s="55" t="s">
-        <v>241</v>
-      </c>
+      <c r="B37" s="42" t="s">
+        <v>251</v>
+      </c>
+      <c r="C37" s="48" t="s">
+        <v>252</v>
+      </c>
+      <c r="D37" s="35" t="s">
+        <v>253</v>
+      </c>
+      <c r="E37" s="57"/>
+      <c r="F37" s="57"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="37" t="n">
+      <c r="A38" s="41" t="n">
         <v>6</v>
       </c>
-      <c r="B38" s="38" t="s">
-        <v>242</v>
-      </c>
-      <c r="C38" s="45" t="s">
-        <v>243</v>
-      </c>
-      <c r="D38" s="52" t="s">
-        <v>244</v>
-      </c>
-      <c r="E38" s="55"/>
-      <c r="F38" s="55"/>
+      <c r="B38" s="42" t="s">
+        <v>254</v>
+      </c>
+      <c r="C38" s="48" t="s">
+        <v>255</v>
+      </c>
+      <c r="D38" s="35" t="s">
+        <v>256</v>
+      </c>
+      <c r="E38" s="57"/>
+      <c r="F38" s="57"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="37" t="n">
+      <c r="A39" s="41" t="n">
         <v>7</v>
       </c>
-      <c r="B39" s="38" t="s">
-        <v>245</v>
-      </c>
-      <c r="C39" s="45" t="s">
-        <v>246</v>
-      </c>
-      <c r="D39" s="52" t="s">
-        <v>247</v>
-      </c>
-      <c r="E39" s="55"/>
-      <c r="F39" s="55"/>
+      <c r="B39" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="C39" s="48" t="s">
+        <v>258</v>
+      </c>
+      <c r="D39" s="35" t="s">
+        <v>259</v>
+      </c>
+      <c r="E39" s="57"/>
+      <c r="F39" s="57"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="37" t="n">
+      <c r="A40" s="41" t="n">
         <v>8</v>
       </c>
-      <c r="B40" s="38" t="s">
-        <v>248</v>
-      </c>
-      <c r="C40" s="45" t="s">
-        <v>249</v>
-      </c>
-      <c r="D40" s="52" t="s">
-        <v>250</v>
-      </c>
-      <c r="E40" s="55"/>
-      <c r="F40" s="55"/>
+      <c r="B40" s="42" t="s">
+        <v>260</v>
+      </c>
+      <c r="C40" s="48" t="s">
+        <v>261</v>
+      </c>
+      <c r="D40" s="35" t="s">
+        <v>262</v>
+      </c>
+      <c r="E40" s="57"/>
+      <c r="F40" s="57"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="34" t="s">
-        <v>251</v>
+      <c r="A42" s="38" t="s">
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -4474,26 +4752,26 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="35" t="s">
-        <v>252</v>
-      </c>
-      <c r="H1" s="54" t="s">
-        <v>253</v>
+      <c r="A1" s="39" t="s">
+        <v>264</v>
+      </c>
+      <c r="H1" s="56" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>254</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="59" t="s">
-        <v>255</v>
+      <c r="A3" s="61" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4501,361 +4779,361 @@
         <v>12</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="G6" s="12" t="s">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="H6" s="12" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="I6" s="12" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="J6" s="12" t="s">
-        <v>52</v>
+        <v>73</v>
       </c>
       <c r="K6" s="12" t="s">
-        <v>53</v>
+        <v>74</v>
       </c>
       <c r="L6" s="12" t="s">
-        <v>189</v>
+        <v>209</v>
       </c>
       <c r="M6" s="12" t="s">
-        <v>54</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="37" t="n">
+      <c r="A7" s="41" t="n">
         <v>1</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>256</v>
-      </c>
-      <c r="C7" s="60" t="s">
-        <v>257</v>
-      </c>
-      <c r="D7" s="37" t="s">
-        <v>258</v>
-      </c>
-      <c r="E7" s="40" t="n">
+        <v>268</v>
+      </c>
+      <c r="C7" s="34" t="s">
+        <v>269</v>
+      </c>
+      <c r="D7" s="41" t="s">
+        <v>270</v>
+      </c>
+      <c r="E7" s="44" t="n">
         <v>-113</v>
       </c>
-      <c r="F7" s="41" t="n">
+      <c r="F7" s="36" t="n">
         <v>300</v>
       </c>
-      <c r="G7" s="42" t="n">
+      <c r="G7" s="45" t="n">
         <f aca="false">IF(E7&gt;0,F7*E7/100,F7*100/ABS(E7))</f>
         <v>265.486725663717</v>
       </c>
-      <c r="H7" s="42" t="n">
+      <c r="H7" s="45" t="n">
         <f aca="false">F7+G7</f>
         <v>565.486725663717</v>
       </c>
-      <c r="I7" s="55" t="s">
-        <v>91</v>
-      </c>
-      <c r="J7" s="42" t="n">
+      <c r="I7" s="57" t="s">
+        <v>112</v>
+      </c>
+      <c r="J7" s="45" t="n">
         <f aca="false">IF(I7="Win",F7+G7,IF(I7="Push",F7,IF(I7="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K7" s="44" t="n">
+      <c r="K7" s="47" t="n">
         <f aca="false">IF(I7="Pending",0,J7-F7)</f>
         <v>0</v>
       </c>
-      <c r="L7" s="56" t="n">
+      <c r="L7" s="58" t="n">
         <v>0.58</v>
       </c>
-      <c r="M7" s="61" t="s">
-        <v>259</v>
+      <c r="M7" s="62" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="37" t="n">
+      <c r="A8" s="41" t="n">
         <v>2</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>260</v>
-      </c>
-      <c r="C8" s="60" t="s">
-        <v>261</v>
-      </c>
-      <c r="D8" s="37" t="s">
-        <v>62</v>
-      </c>
-      <c r="E8" s="40" t="n">
+        <v>272</v>
+      </c>
+      <c r="C8" s="34" t="s">
+        <v>273</v>
+      </c>
+      <c r="D8" s="41" t="s">
+        <v>83</v>
+      </c>
+      <c r="E8" s="44" t="n">
         <v>456</v>
       </c>
-      <c r="F8" s="41" t="n">
+      <c r="F8" s="36" t="n">
         <v>200</v>
       </c>
-      <c r="G8" s="42" t="n">
+      <c r="G8" s="45" t="n">
         <f aca="false">IF(E8&gt;0,F8*E8/100,F8*100/ABS(E8))</f>
         <v>912</v>
       </c>
-      <c r="H8" s="42" t="n">
+      <c r="H8" s="45" t="n">
         <f aca="false">F8+G8</f>
         <v>1112</v>
       </c>
-      <c r="I8" s="55" t="s">
-        <v>91</v>
-      </c>
-      <c r="J8" s="42" t="n">
+      <c r="I8" s="57" t="s">
+        <v>112</v>
+      </c>
+      <c r="J8" s="45" t="n">
         <f aca="false">IF(I8="Win",F8+G8,IF(I8="Push",F8,IF(I8="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K8" s="44" t="n">
+      <c r="K8" s="47" t="n">
         <f aca="false">IF(I8="Pending",0,J8-F8)</f>
         <v>0</v>
       </c>
-      <c r="L8" s="56" t="n">
+      <c r="L8" s="58" t="n">
         <v>0.24</v>
       </c>
-      <c r="M8" s="61" t="s">
-        <v>262</v>
+      <c r="M8" s="62" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="37" t="n">
+      <c r="A9" s="41" t="n">
         <v>3</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>263</v>
-      </c>
-      <c r="C9" s="60" t="s">
-        <v>264</v>
-      </c>
-      <c r="D9" s="37" t="s">
-        <v>159</v>
-      </c>
-      <c r="E9" s="40" t="n">
+        <v>275</v>
+      </c>
+      <c r="C9" s="34" t="s">
+        <v>276</v>
+      </c>
+      <c r="D9" s="41" t="s">
+        <v>179</v>
+      </c>
+      <c r="E9" s="44" t="n">
         <v>1150</v>
       </c>
-      <c r="F9" s="41" t="n">
+      <c r="F9" s="36" t="n">
         <v>150</v>
       </c>
-      <c r="G9" s="42" t="n">
+      <c r="G9" s="45" t="n">
         <f aca="false">IF(E9&gt;0,F9*E9/100,F9*100/ABS(E9))</f>
         <v>1725</v>
       </c>
-      <c r="H9" s="42" t="n">
+      <c r="H9" s="45" t="n">
         <f aca="false">F9+G9</f>
         <v>1875</v>
       </c>
-      <c r="I9" s="55" t="s">
-        <v>91</v>
-      </c>
-      <c r="J9" s="42" t="n">
+      <c r="I9" s="57" t="s">
+        <v>112</v>
+      </c>
+      <c r="J9" s="45" t="n">
         <f aca="false">IF(I9="Win",F9+G9,IF(I9="Push",F9,IF(I9="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K9" s="44" t="n">
+      <c r="K9" s="47" t="n">
         <f aca="false">IF(I9="Pending",0,J9-F9)</f>
         <v>0</v>
       </c>
-      <c r="L9" s="56" t="n">
+      <c r="L9" s="58" t="n">
         <v>0.1</v>
       </c>
-      <c r="M9" s="61" t="s">
-        <v>265</v>
+      <c r="M9" s="62" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="37" t="n">
+      <c r="A10" s="41" t="n">
         <v>4</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="C10" s="60" t="s">
-        <v>264</v>
-      </c>
-      <c r="D10" s="37" t="s">
-        <v>159</v>
-      </c>
-      <c r="E10" s="40" t="n">
+        <v>278</v>
+      </c>
+      <c r="C10" s="34" t="s">
+        <v>276</v>
+      </c>
+      <c r="D10" s="41" t="s">
+        <v>179</v>
+      </c>
+      <c r="E10" s="44" t="n">
         <v>1567</v>
       </c>
-      <c r="F10" s="41" t="n">
+      <c r="F10" s="36" t="n">
         <v>120</v>
       </c>
-      <c r="G10" s="42" t="n">
+      <c r="G10" s="45" t="n">
         <f aca="false">IF(E10&gt;0,F10*E10/100,F10*100/ABS(E10))</f>
         <v>1880.4</v>
       </c>
-      <c r="H10" s="42" t="n">
+      <c r="H10" s="45" t="n">
         <f aca="false">F10+G10</f>
         <v>2000.4</v>
       </c>
-      <c r="I10" s="55" t="s">
-        <v>91</v>
-      </c>
-      <c r="J10" s="42" t="n">
+      <c r="I10" s="57" t="s">
+        <v>112</v>
+      </c>
+      <c r="J10" s="45" t="n">
         <f aca="false">IF(I10="Win",F10+G10,IF(I10="Push",F10,IF(I10="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K10" s="44" t="n">
+      <c r="K10" s="47" t="n">
         <f aca="false">IF(I10="Pending",0,J10-F10)</f>
         <v>0</v>
       </c>
-      <c r="L10" s="56" t="n">
+      <c r="L10" s="58" t="n">
         <v>0.08</v>
       </c>
-      <c r="M10" s="61" t="s">
-        <v>267</v>
+      <c r="M10" s="62" t="s">
+        <v>279</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="37" t="n">
+      <c r="A11" s="41" t="n">
         <v>5</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>268</v>
-      </c>
-      <c r="C11" s="60" t="s">
-        <v>264</v>
-      </c>
-      <c r="D11" s="37" t="s">
-        <v>159</v>
-      </c>
-      <c r="E11" s="40" t="n">
+        <v>280</v>
+      </c>
+      <c r="C11" s="34" t="s">
+        <v>276</v>
+      </c>
+      <c r="D11" s="41" t="s">
+        <v>179</v>
+      </c>
+      <c r="E11" s="44" t="n">
         <v>1800</v>
       </c>
-      <c r="F11" s="41" t="n">
+      <c r="F11" s="36" t="n">
         <v>100</v>
       </c>
-      <c r="G11" s="42" t="n">
+      <c r="G11" s="45" t="n">
         <f aca="false">IF(E11&gt;0,F11*E11/100,F11*100/ABS(E11))</f>
         <v>1800</v>
       </c>
-      <c r="H11" s="42" t="n">
+      <c r="H11" s="45" t="n">
         <f aca="false">F11+G11</f>
         <v>1900</v>
       </c>
-      <c r="I11" s="55" t="s">
-        <v>91</v>
-      </c>
-      <c r="J11" s="42" t="n">
+      <c r="I11" s="57" t="s">
+        <v>112</v>
+      </c>
+      <c r="J11" s="45" t="n">
         <f aca="false">IF(I11="Win",F11+G11,IF(I11="Push",F11,IF(I11="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K11" s="44" t="n">
+      <c r="K11" s="47" t="n">
         <f aca="false">IF(I11="Pending",0,J11-F11)</f>
         <v>0</v>
       </c>
-      <c r="L11" s="56" t="n">
+      <c r="L11" s="58" t="n">
         <v>0.07</v>
       </c>
-      <c r="M11" s="61" t="s">
-        <v>269</v>
+      <c r="M11" s="62" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="37" t="n">
+      <c r="A12" s="41" t="n">
         <v>6</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>270</v>
-      </c>
-      <c r="C12" s="60" t="s">
-        <v>264</v>
-      </c>
-      <c r="D12" s="37" t="s">
-        <v>159</v>
-      </c>
-      <c r="E12" s="40" t="n">
+        <v>282</v>
+      </c>
+      <c r="C12" s="34" t="s">
+        <v>276</v>
+      </c>
+      <c r="D12" s="41" t="s">
+        <v>179</v>
+      </c>
+      <c r="E12" s="44" t="n">
         <v>1150</v>
       </c>
-      <c r="F12" s="41" t="n">
+      <c r="F12" s="36" t="n">
         <v>90</v>
       </c>
-      <c r="G12" s="42" t="n">
+      <c r="G12" s="45" t="n">
         <f aca="false">IF(E12&gt;0,F12*E12/100,F12*100/ABS(E12))</f>
         <v>1035</v>
       </c>
-      <c r="H12" s="42" t="n">
+      <c r="H12" s="45" t="n">
         <f aca="false">F12+G12</f>
         <v>1125</v>
       </c>
-      <c r="I12" s="55" t="s">
-        <v>91</v>
-      </c>
-      <c r="J12" s="42" t="n">
+      <c r="I12" s="57" t="s">
+        <v>112</v>
+      </c>
+      <c r="J12" s="45" t="n">
         <f aca="false">IF(I12="Win",F12+G12,IF(I12="Push",F12,IF(I12="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K12" s="44" t="n">
+      <c r="K12" s="47" t="n">
         <f aca="false">IF(I12="Pending",0,J12-F12)</f>
         <v>0</v>
       </c>
-      <c r="L12" s="56" t="n">
+      <c r="L12" s="58" t="n">
         <v>0.08</v>
       </c>
-      <c r="M12" s="61" t="s">
-        <v>271</v>
+      <c r="M12" s="62" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="37" t="n">
+      <c r="A13" s="41" t="n">
         <v>7</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>272</v>
-      </c>
-      <c r="C13" s="60" t="s">
-        <v>264</v>
-      </c>
-      <c r="D13" s="37" t="s">
-        <v>159</v>
-      </c>
-      <c r="E13" s="40" t="n">
+        <v>284</v>
+      </c>
+      <c r="C13" s="34" t="s">
+        <v>276</v>
+      </c>
+      <c r="D13" s="41" t="s">
+        <v>179</v>
+      </c>
+      <c r="E13" s="44" t="n">
         <v>1900</v>
       </c>
-      <c r="F13" s="41" t="n">
+      <c r="F13" s="36" t="n">
         <v>40</v>
       </c>
-      <c r="G13" s="42" t="n">
+      <c r="G13" s="45" t="n">
         <f aca="false">IF(E13&gt;0,F13*E13/100,F13*100/ABS(E13))</f>
         <v>760</v>
       </c>
-      <c r="H13" s="42" t="n">
+      <c r="H13" s="45" t="n">
         <f aca="false">F13+G13</f>
         <v>800</v>
       </c>
-      <c r="I13" s="55" t="s">
-        <v>91</v>
-      </c>
-      <c r="J13" s="42" t="n">
+      <c r="I13" s="57" t="s">
+        <v>112</v>
+      </c>
+      <c r="J13" s="45" t="n">
         <f aca="false">IF(I13="Win",F13+G13,IF(I13="Push",F13,IF(I13="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K13" s="44" t="n">
+      <c r="K13" s="47" t="n">
         <f aca="false">IF(I13="Pending",0,J13-F13)</f>
         <v>0</v>
       </c>
-      <c r="L13" s="56" t="n">
+      <c r="L13" s="58" t="n">
         <v>0.05</v>
       </c>
-      <c r="M13" s="61" t="s">
-        <v>273</v>
+      <c r="M13" s="62" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="29"/>
       <c r="B14" s="30" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C14" s="29"/>
       <c r="D14" s="29"/>
@@ -4881,7 +5159,7 @@
         <f aca="false">SUM(K7:K13)</f>
         <v>0</v>
       </c>
-      <c r="L14" s="57" t="n">
+      <c r="L14" s="59" t="n">
         <f aca="false">SUM(L7:L13)</f>
         <v>1.2</v>
       </c>
@@ -4889,111 +5167,111 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="4" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="C17" s="49" t="n">
+        <v>109</v>
+      </c>
+      <c r="C17" s="52" t="n">
         <f aca="false">COUNTIF(I7:I13,"Win")</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="C18" s="49" t="n">
+        <v>110</v>
+      </c>
+      <c r="C18" s="52" t="n">
         <f aca="false">COUNTIF(I7:I13,"Loss")</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="C19" s="49" t="n">
+        <v>111</v>
+      </c>
+      <c r="C19" s="52" t="n">
         <f aca="false">COUNTIF(I7:I13,"Push")</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="C20" s="49" t="n">
+        <v>112</v>
+      </c>
+      <c r="C20" s="52" t="n">
         <f aca="false">COUNTIF(I7:I13,"Pending")</f>
         <v>7</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="C21" s="50" t="str">
+        <v>113</v>
+      </c>
+      <c r="C21" s="53" t="str">
         <f aca="false">IF(COUNTIF(I7:I13,"Win")+COUNTIF(I7:I13,"Loss")=0,"—",COUNTIF(I7:I13,"Win")/(COUNTIF(I7:I13,"Win")+COUNTIF(I7:I13,"Loss")))</f>
         <v>—</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="C22" s="51" t="n">
+        <v>114</v>
+      </c>
+      <c r="C22" s="54" t="n">
         <f aca="false">SUM(F7:F13)</f>
         <v>1000</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="C23" s="42" t="n">
+        <v>115</v>
+      </c>
+      <c r="C23" s="45" t="n">
         <f aca="false">SUM(J7:J13)</f>
         <v>0</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="C24" s="44" t="n">
+        <v>116</v>
+      </c>
+      <c r="C24" s="47" t="n">
         <f aca="false">SUM(K7:K13)</f>
         <v>0</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="C25" s="50" t="n">
+        <v>117</v>
+      </c>
+      <c r="C25" s="53" t="n">
         <f aca="false">IF(SUM(F7:F13)=0,"—",SUM(K7:K13)/SUM(F7:F13))</f>
         <v>0</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="5" t="s">
-        <v>214</v>
-      </c>
-      <c r="C26" s="58" t="n">
+        <v>234</v>
+      </c>
+      <c r="C26" s="60" t="n">
         <f aca="false">SUM(L7:L13)</f>
         <v>1.2</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="5" t="s">
-        <v>274</v>
-      </c>
-      <c r="C27" s="51" t="n">
+        <v>286</v>
+      </c>
+      <c r="C27" s="54" t="n">
         <f aca="false">2678</f>
         <v>2678</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="34" t="s">
-        <v>275</v>
+      <c r="A29" s="38" t="s">
+        <v>287</v>
       </c>
     </row>
   </sheetData>
@@ -5045,338 +5323,338 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="35" t="s">
-        <v>276</v>
+      <c r="A1" s="39" t="s">
+        <v>288</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>277</v>
+        <v>289</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>281</v>
+        <v>293</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>54</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>284</v>
-      </c>
-      <c r="B5" s="62" t="s">
-        <v>285</v>
-      </c>
-      <c r="C5" s="63"/>
-      <c r="D5" s="63" t="s">
-        <v>286</v>
-      </c>
-      <c r="E5" s="63" t="s">
-        <v>286</v>
-      </c>
-      <c r="F5" s="63"/>
-      <c r="G5" s="64" t="s">
-        <v>287</v>
+        <v>296</v>
+      </c>
+      <c r="B5" s="63" t="s">
+        <v>297</v>
+      </c>
+      <c r="C5" s="64"/>
+      <c r="D5" s="64" t="s">
+        <v>298</v>
+      </c>
+      <c r="E5" s="64" t="s">
+        <v>298</v>
+      </c>
+      <c r="F5" s="64"/>
+      <c r="G5" s="65" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>288</v>
-      </c>
-      <c r="B6" s="62" t="s">
-        <v>289</v>
-      </c>
-      <c r="C6" s="63" t="s">
-        <v>286</v>
-      </c>
-      <c r="D6" s="63"/>
-      <c r="E6" s="63"/>
-      <c r="F6" s="63"/>
-      <c r="G6" s="64" t="s">
-        <v>290</v>
+        <v>300</v>
+      </c>
+      <c r="B6" s="63" t="s">
+        <v>301</v>
+      </c>
+      <c r="C6" s="64" t="s">
+        <v>298</v>
+      </c>
+      <c r="D6" s="64"/>
+      <c r="E6" s="64"/>
+      <c r="F6" s="64"/>
+      <c r="G6" s="65" t="s">
+        <v>302</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>291</v>
-      </c>
-      <c r="B7" s="62" t="s">
-        <v>292</v>
-      </c>
-      <c r="C7" s="63" t="s">
-        <v>286</v>
-      </c>
-      <c r="D7" s="63"/>
-      <c r="E7" s="63"/>
-      <c r="F7" s="63"/>
-      <c r="G7" s="64" t="s">
-        <v>293</v>
+        <v>303</v>
+      </c>
+      <c r="B7" s="63" t="s">
+        <v>304</v>
+      </c>
+      <c r="C7" s="64" t="s">
+        <v>298</v>
+      </c>
+      <c r="D7" s="64"/>
+      <c r="E7" s="64"/>
+      <c r="F7" s="64"/>
+      <c r="G7" s="65" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>294</v>
-      </c>
-      <c r="B8" s="62" t="s">
-        <v>295</v>
-      </c>
-      <c r="C8" s="63"/>
-      <c r="D8" s="63" t="s">
-        <v>286</v>
-      </c>
-      <c r="E8" s="63"/>
-      <c r="F8" s="63"/>
-      <c r="G8" s="64" t="s">
-        <v>296</v>
+        <v>306</v>
+      </c>
+      <c r="B8" s="63" t="s">
+        <v>307</v>
+      </c>
+      <c r="C8" s="64"/>
+      <c r="D8" s="64" t="s">
+        <v>298</v>
+      </c>
+      <c r="E8" s="64"/>
+      <c r="F8" s="64"/>
+      <c r="G8" s="65" t="s">
+        <v>308</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>297</v>
-      </c>
-      <c r="B9" s="62" t="s">
+        <v>309</v>
+      </c>
+      <c r="B9" s="63" t="s">
+        <v>310</v>
+      </c>
+      <c r="C9" s="64"/>
+      <c r="D9" s="64" t="s">
         <v>298</v>
       </c>
-      <c r="C9" s="63"/>
-      <c r="D9" s="63" t="s">
-        <v>286</v>
-      </c>
-      <c r="E9" s="63"/>
-      <c r="F9" s="63" t="s">
-        <v>286</v>
-      </c>
-      <c r="G9" s="64" t="s">
-        <v>299</v>
+      <c r="E9" s="64"/>
+      <c r="F9" s="64" t="s">
+        <v>298</v>
+      </c>
+      <c r="G9" s="65" t="s">
+        <v>311</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>300</v>
-      </c>
-      <c r="B10" s="62" t="s">
-        <v>301</v>
-      </c>
-      <c r="C10" s="63"/>
-      <c r="D10" s="63" t="s">
-        <v>286</v>
-      </c>
-      <c r="E10" s="63" t="s">
-        <v>286</v>
-      </c>
-      <c r="F10" s="63"/>
-      <c r="G10" s="64" t="s">
-        <v>302</v>
+        <v>312</v>
+      </c>
+      <c r="B10" s="63" t="s">
+        <v>313</v>
+      </c>
+      <c r="C10" s="64"/>
+      <c r="D10" s="64" t="s">
+        <v>298</v>
+      </c>
+      <c r="E10" s="64" t="s">
+        <v>298</v>
+      </c>
+      <c r="F10" s="64"/>
+      <c r="G10" s="65" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>303</v>
-      </c>
-      <c r="B11" s="62" t="s">
-        <v>304</v>
-      </c>
-      <c r="C11" s="63"/>
-      <c r="D11" s="63" t="s">
-        <v>286</v>
-      </c>
-      <c r="E11" s="63"/>
-      <c r="F11" s="63"/>
-      <c r="G11" s="64" t="s">
-        <v>305</v>
+        <v>315</v>
+      </c>
+      <c r="B11" s="63" t="s">
+        <v>316</v>
+      </c>
+      <c r="C11" s="64"/>
+      <c r="D11" s="64" t="s">
+        <v>298</v>
+      </c>
+      <c r="E11" s="64"/>
+      <c r="F11" s="64" t="s">
+        <v>298</v>
+      </c>
+      <c r="G11" s="65" t="s">
+        <v>317</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>306</v>
-      </c>
-      <c r="B12" s="62" t="s">
-        <v>307</v>
-      </c>
-      <c r="C12" s="63"/>
-      <c r="D12" s="63" t="s">
-        <v>286</v>
-      </c>
-      <c r="E12" s="63"/>
-      <c r="F12" s="63" t="s">
-        <v>286</v>
-      </c>
-      <c r="G12" s="64" t="s">
-        <v>308</v>
+        <v>318</v>
+      </c>
+      <c r="B12" s="63" t="s">
+        <v>319</v>
+      </c>
+      <c r="C12" s="64"/>
+      <c r="D12" s="64" t="s">
+        <v>298</v>
+      </c>
+      <c r="E12" s="64"/>
+      <c r="F12" s="64"/>
+      <c r="G12" s="65" t="s">
+        <v>320</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="B13" s="62" t="s">
-        <v>310</v>
-      </c>
-      <c r="C13" s="63"/>
-      <c r="D13" s="63" t="s">
-        <v>286</v>
-      </c>
-      <c r="E13" s="63"/>
-      <c r="F13" s="63"/>
-      <c r="G13" s="64" t="s">
-        <v>311</v>
+        <v>321</v>
+      </c>
+      <c r="B13" s="63" t="s">
+        <v>322</v>
+      </c>
+      <c r="C13" s="64"/>
+      <c r="D13" s="64" t="s">
+        <v>298</v>
+      </c>
+      <c r="E13" s="64"/>
+      <c r="F13" s="64"/>
+      <c r="G13" s="65" t="s">
+        <v>323</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="B14" s="62" t="s">
-        <v>313</v>
-      </c>
-      <c r="C14" s="63"/>
-      <c r="D14" s="63" t="s">
-        <v>286</v>
-      </c>
-      <c r="E14" s="63"/>
-      <c r="F14" s="63"/>
-      <c r="G14" s="64" t="s">
-        <v>314</v>
+        <v>324</v>
+      </c>
+      <c r="B14" s="63" t="s">
+        <v>325</v>
+      </c>
+      <c r="C14" s="64"/>
+      <c r="D14" s="64" t="s">
+        <v>298</v>
+      </c>
+      <c r="E14" s="64"/>
+      <c r="F14" s="64"/>
+      <c r="G14" s="65" t="s">
+        <v>326</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>315</v>
-      </c>
-      <c r="B15" s="62" t="s">
-        <v>316</v>
-      </c>
-      <c r="C15" s="63"/>
-      <c r="D15" s="63" t="s">
-        <v>286</v>
-      </c>
-      <c r="E15" s="63"/>
-      <c r="F15" s="63"/>
-      <c r="G15" s="64" t="s">
-        <v>317</v>
+        <v>327</v>
+      </c>
+      <c r="B15" s="63" t="s">
+        <v>328</v>
+      </c>
+      <c r="C15" s="64"/>
+      <c r="D15" s="64" t="s">
+        <v>298</v>
+      </c>
+      <c r="E15" s="64"/>
+      <c r="F15" s="64"/>
+      <c r="G15" s="65" t="s">
+        <v>329</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>318</v>
-      </c>
-      <c r="B16" s="62" t="s">
-        <v>319</v>
-      </c>
-      <c r="C16" s="63"/>
-      <c r="D16" s="63" t="s">
-        <v>286</v>
-      </c>
-      <c r="E16" s="63"/>
-      <c r="F16" s="63"/>
-      <c r="G16" s="64" t="s">
-        <v>320</v>
+        <v>330</v>
+      </c>
+      <c r="B16" s="63" t="s">
+        <v>331</v>
+      </c>
+      <c r="C16" s="64"/>
+      <c r="D16" s="64"/>
+      <c r="E16" s="64" t="s">
+        <v>298</v>
+      </c>
+      <c r="F16" s="64" t="s">
+        <v>298</v>
+      </c>
+      <c r="G16" s="65" t="s">
+        <v>332</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>321</v>
-      </c>
-      <c r="B17" s="62" t="s">
-        <v>322</v>
-      </c>
-      <c r="C17" s="63"/>
-      <c r="D17" s="63"/>
-      <c r="E17" s="63" t="s">
-        <v>286</v>
-      </c>
-      <c r="F17" s="63" t="s">
-        <v>286</v>
-      </c>
-      <c r="G17" s="64" t="s">
-        <v>323</v>
+        <v>333</v>
+      </c>
+      <c r="B17" s="63" t="s">
+        <v>334</v>
+      </c>
+      <c r="C17" s="64"/>
+      <c r="D17" s="64"/>
+      <c r="E17" s="64" t="s">
+        <v>298</v>
+      </c>
+      <c r="F17" s="64"/>
+      <c r="G17" s="65" t="s">
+        <v>335</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>324</v>
-      </c>
-      <c r="B18" s="62" t="s">
-        <v>325</v>
-      </c>
-      <c r="C18" s="63"/>
-      <c r="D18" s="63"/>
-      <c r="E18" s="63" t="s">
-        <v>286</v>
-      </c>
-      <c r="F18" s="63"/>
-      <c r="G18" s="64" t="s">
-        <v>326</v>
+        <v>336</v>
+      </c>
+      <c r="B18" s="63" t="s">
+        <v>337</v>
+      </c>
+      <c r="C18" s="64"/>
+      <c r="D18" s="64"/>
+      <c r="E18" s="64" t="s">
+        <v>298</v>
+      </c>
+      <c r="F18" s="64"/>
+      <c r="G18" s="65" t="s">
+        <v>338</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>327</v>
-      </c>
-      <c r="B19" s="62" t="s">
-        <v>328</v>
-      </c>
-      <c r="C19" s="63"/>
-      <c r="D19" s="63"/>
-      <c r="E19" s="63" t="s">
-        <v>286</v>
-      </c>
-      <c r="F19" s="63"/>
-      <c r="G19" s="64" t="s">
-        <v>329</v>
+        <v>339</v>
+      </c>
+      <c r="B19" s="63" t="s">
+        <v>340</v>
+      </c>
+      <c r="C19" s="64"/>
+      <c r="D19" s="64"/>
+      <c r="E19" s="64"/>
+      <c r="F19" s="64" t="s">
+        <v>298</v>
+      </c>
+      <c r="G19" s="65" t="s">
+        <v>341</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="5" t="s">
-        <v>330</v>
-      </c>
-      <c r="B20" s="62" t="s">
-        <v>331</v>
-      </c>
-      <c r="C20" s="63"/>
-      <c r="D20" s="63"/>
-      <c r="E20" s="63"/>
-      <c r="F20" s="63" t="s">
-        <v>286</v>
-      </c>
-      <c r="G20" s="64" t="s">
-        <v>332</v>
+      <c r="A20" s="66" t="s">
+        <v>342</v>
+      </c>
+      <c r="B20" s="67" t="s">
+        <v>343</v>
+      </c>
+      <c r="D20" s="68" t="s">
+        <v>298</v>
+      </c>
+      <c r="F20" s="68" t="s">
+        <v>298</v>
+      </c>
+      <c r="G20" s="38" t="s">
+        <v>344</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="65" t="s">
-        <v>333</v>
+      <c r="A22" s="69" t="s">
+        <v>345</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>334</v>
+        <v>346</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>335</v>
+        <v>347</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>336</v>
+        <v>348</v>
       </c>
     </row>
   </sheetData>
@@ -5388,4 +5666,590 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FF1B7A3D"/>
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:M30"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="9" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="50"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="39" t="s">
+        <v>349</v>
+      </c>
+      <c r="H1" s="56" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>208</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="G6" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="H6" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="I6" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="J6" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="K6" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="L6" s="12" t="s">
+        <v>209</v>
+      </c>
+      <c r="M6" s="12" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="C7" s="34" t="s">
+        <v>354</v>
+      </c>
+      <c r="D7" s="41" t="s">
+        <v>355</v>
+      </c>
+      <c r="E7" s="44" t="n">
+        <v>-115</v>
+      </c>
+      <c r="F7" s="36" t="n">
+        <v>200</v>
+      </c>
+      <c r="G7" s="45" t="n">
+        <f aca="false">IF(E7&gt;0,F7*E7/100,F7*100/ABS(E7))</f>
+        <v>173.913043478261</v>
+      </c>
+      <c r="H7" s="45" t="n">
+        <f aca="false">F7+G7</f>
+        <v>373.913043478261</v>
+      </c>
+      <c r="I7" s="57" t="s">
+        <v>112</v>
+      </c>
+      <c r="J7" s="45" t="n">
+        <f aca="false">IF(I7="Win",F7+G7,IF(I7="Push",F7,IF(I7="Loss",0,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="K7" s="47" t="n">
+        <f aca="false">IF(I7="Pending",0,J7-F7)</f>
+        <v>0</v>
+      </c>
+      <c r="L7" s="58" t="n">
+        <v>0.56</v>
+      </c>
+      <c r="M7" s="62" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="C8" s="34" t="s">
+        <v>358</v>
+      </c>
+      <c r="D8" s="41" t="s">
+        <v>168</v>
+      </c>
+      <c r="E8" s="44" t="n">
+        <v>-112</v>
+      </c>
+      <c r="F8" s="36" t="n">
+        <v>150</v>
+      </c>
+      <c r="G8" s="45" t="n">
+        <f aca="false">IF(E8&gt;0,F8*E8/100,F8*100/ABS(E8))</f>
+        <v>133.928571428571</v>
+      </c>
+      <c r="H8" s="45" t="n">
+        <f aca="false">F8+G8</f>
+        <v>283.928571428571</v>
+      </c>
+      <c r="I8" s="57" t="s">
+        <v>112</v>
+      </c>
+      <c r="J8" s="45" t="n">
+        <f aca="false">IF(I8="Win",F8+G8,IF(I8="Push",F8,IF(I8="Loss",0,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="K8" s="47" t="n">
+        <f aca="false">IF(I8="Pending",0,J8-F8)</f>
+        <v>0</v>
+      </c>
+      <c r="L8" s="58" t="n">
+        <v>0.56</v>
+      </c>
+      <c r="M8" s="62" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="41" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="C9" s="34" t="s">
+        <v>361</v>
+      </c>
+      <c r="D9" s="41" t="s">
+        <v>83</v>
+      </c>
+      <c r="E9" s="44" t="n">
+        <v>-159</v>
+      </c>
+      <c r="F9" s="36" t="n">
+        <v>150</v>
+      </c>
+      <c r="G9" s="45" t="n">
+        <f aca="false">IF(E9&gt;0,F9*E9/100,F9*100/ABS(E9))</f>
+        <v>94.3396226415094</v>
+      </c>
+      <c r="H9" s="45" t="n">
+        <f aca="false">F9+G9</f>
+        <v>244.339622641509</v>
+      </c>
+      <c r="I9" s="57" t="s">
+        <v>112</v>
+      </c>
+      <c r="J9" s="45" t="n">
+        <f aca="false">IF(I9="Win",F9+G9,IF(I9="Push",F9,IF(I9="Loss",0,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="K9" s="47" t="n">
+        <f aca="false">IF(I9="Pending",0,J9-F9)</f>
+        <v>0</v>
+      </c>
+      <c r="L9" s="58" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="M9" s="62" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="41" t="n">
+        <v>4</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="C10" s="34" t="s">
+        <v>364</v>
+      </c>
+      <c r="D10" s="41" t="s">
+        <v>355</v>
+      </c>
+      <c r="E10" s="44" t="n">
+        <v>-108</v>
+      </c>
+      <c r="F10" s="36" t="n">
+        <v>150</v>
+      </c>
+      <c r="G10" s="45" t="n">
+        <f aca="false">IF(E10&gt;0,F10*E10/100,F10*100/ABS(E10))</f>
+        <v>138.888888888889</v>
+      </c>
+      <c r="H10" s="45" t="n">
+        <f aca="false">F10+G10</f>
+        <v>288.888888888889</v>
+      </c>
+      <c r="I10" s="57" t="s">
+        <v>112</v>
+      </c>
+      <c r="J10" s="45" t="n">
+        <f aca="false">IF(I10="Win",F10+G10,IF(I10="Push",F10,IF(I10="Loss",0,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="K10" s="47" t="n">
+        <f aca="false">IF(I10="Pending",0,J10-F10)</f>
+        <v>0</v>
+      </c>
+      <c r="L10" s="58" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="M10" s="62" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="41" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>366</v>
+      </c>
+      <c r="C11" s="34" t="s">
+        <v>367</v>
+      </c>
+      <c r="D11" s="41" t="s">
+        <v>83</v>
+      </c>
+      <c r="E11" s="44" t="n">
+        <v>-120</v>
+      </c>
+      <c r="F11" s="36" t="n">
+        <v>130</v>
+      </c>
+      <c r="G11" s="45" t="n">
+        <f aca="false">IF(E11&gt;0,F11*E11/100,F11*100/ABS(E11))</f>
+        <v>108.333333333333</v>
+      </c>
+      <c r="H11" s="45" t="n">
+        <f aca="false">F11+G11</f>
+        <v>238.333333333333</v>
+      </c>
+      <c r="I11" s="57" t="s">
+        <v>112</v>
+      </c>
+      <c r="J11" s="45" t="n">
+        <f aca="false">IF(I11="Win",F11+G11,IF(I11="Push",F11,IF(I11="Loss",0,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="K11" s="47" t="n">
+        <f aca="false">IF(I11="Pending",0,J11-F11)</f>
+        <v>0</v>
+      </c>
+      <c r="L11" s="58" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M11" s="62" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="41" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="C12" s="34" t="s">
+        <v>370</v>
+      </c>
+      <c r="D12" s="41" t="s">
+        <v>83</v>
+      </c>
+      <c r="E12" s="44" t="n">
+        <v>-121</v>
+      </c>
+      <c r="F12" s="36" t="n">
+        <v>120</v>
+      </c>
+      <c r="G12" s="45" t="n">
+        <f aca="false">IF(E12&gt;0,F12*E12/100,F12*100/ABS(E12))</f>
+        <v>99.1735537190083</v>
+      </c>
+      <c r="H12" s="45" t="n">
+        <f aca="false">F12+G12</f>
+        <v>219.173553719008</v>
+      </c>
+      <c r="I12" s="57" t="s">
+        <v>112</v>
+      </c>
+      <c r="J12" s="45" t="n">
+        <f aca="false">IF(I12="Win",F12+G12,IF(I12="Push",F12,IF(I12="Loss",0,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="K12" s="47" t="n">
+        <f aca="false">IF(I12="Pending",0,J12-F12)</f>
+        <v>0</v>
+      </c>
+      <c r="L12" s="58" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="M12" s="62" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="41" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>372</v>
+      </c>
+      <c r="C13" s="34" t="s">
+        <v>373</v>
+      </c>
+      <c r="D13" s="41" t="s">
+        <v>106</v>
+      </c>
+      <c r="E13" s="44" t="n">
+        <v>971</v>
+      </c>
+      <c r="F13" s="36" t="n">
+        <v>100</v>
+      </c>
+      <c r="G13" s="45" t="n">
+        <f aca="false">IF(E13&gt;0,F13*E13/100,F13*100/ABS(E13))</f>
+        <v>971</v>
+      </c>
+      <c r="H13" s="45" t="n">
+        <f aca="false">F13+G13</f>
+        <v>1071</v>
+      </c>
+      <c r="I13" s="57" t="s">
+        <v>112</v>
+      </c>
+      <c r="J13" s="45" t="n">
+        <f aca="false">IF(I13="Win",F13+G13,IF(I13="Push",F13,IF(I13="Loss",0,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="K13" s="47" t="n">
+        <f aca="false">IF(I13="Pending",0,J13-F13)</f>
+        <v>0</v>
+      </c>
+      <c r="L13" s="58" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="M13" s="62" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="29"/>
+      <c r="B14" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" s="29"/>
+      <c r="D14" s="29"/>
+      <c r="E14" s="29"/>
+      <c r="F14" s="31" t="n">
+        <f aca="false">SUM(F7:F13)</f>
+        <v>1000</v>
+      </c>
+      <c r="G14" s="32" t="n">
+        <f aca="false">SUM(G7:G13)</f>
+        <v>1719.57701348957</v>
+      </c>
+      <c r="H14" s="32" t="n">
+        <f aca="false">SUM(H7:H13)</f>
+        <v>2719.57701348957</v>
+      </c>
+      <c r="I14" s="29"/>
+      <c r="J14" s="32" t="n">
+        <f aca="false">SUM(J7:J13)</f>
+        <v>0</v>
+      </c>
+      <c r="K14" s="33" t="n">
+        <f aca="false">SUM(K7:K13)</f>
+        <v>0</v>
+      </c>
+      <c r="L14" s="59" t="n">
+        <f aca="false">SUM(L7:L13)</f>
+        <v>3.62</v>
+      </c>
+      <c r="M14" s="29"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B16" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B17" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="C17" s="52" t="n">
+        <f aca="false">COUNTIF(I7:I13,"Win")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B18" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="C18" s="52" t="n">
+        <f aca="false">COUNTIF(I7:I13,"Loss")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B19" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="C19" s="52" t="n">
+        <f aca="false">COUNTIF(I7:I13,"Push")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B20" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="C20" s="52" t="n">
+        <f aca="false">COUNTIF(I7:I13,"Pending")</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B21" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="C21" s="53" t="str">
+        <f aca="false">IF(COUNTIF(I7:I13,"Win")+COUNTIF(I7:I13,"Loss")=0,"—",COUNTIF(I7:I13,"Win")/(COUNTIF(I7:I13,"Win")+COUNTIF(I7:I13,"Loss")))</f>
+        <v>—</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B22" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="C22" s="54" t="n">
+        <f aca="false">SUM(F7:F13)</f>
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B23" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="C23" s="45" t="n">
+        <f aca="false">SUM(J7:J13)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B24" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="C24" s="47" t="n">
+        <f aca="false">SUM(K7:K13)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B25" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="C25" s="53" t="n">
+        <f aca="false">IF(SUM(F7:F13)=0,"—",SUM(K7:K13)/SUM(F7:F13))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B26" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="C26" s="45" t="n">
+        <f aca="false">SUM(H7:H13)</f>
+        <v>2719.57701348957</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B27" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="C27" s="60" t="n">
+        <f aca="false">SUM(L7:L13)</f>
+        <v>3.62</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B28" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="C28" s="47" t="n">
+        <f aca="false">SUMPRODUCT(L7:L13,G7:G13)-SUMPRODUCT(1-L7:L13,F7:F13)</f>
+        <v>84.7416091107209</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="38" t="s">
+        <v>375</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="K7:K14">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>AND(ISNUMBER(K7),K7&gt;0)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+      <formula>AND(ISNUMBER(K7),K7&lt;0)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C24:C25">
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>AND(ISNUMBER(C24),C24&gt;0)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+      <formula>AND(ISNUMBER(C24),C24&lt;0)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="I7:I13" type="list">
+      <formula1>"Pending,Win,Loss,Push"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
 </file>
--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -88,12 +88,45 @@
     <t xml:space="preserve">Net P/L to Date</t>
   </si>
   <si>
-    <t xml:space="preserve">Account Balance After</t>
+    <t xml:space="preserve">Running Balance (display order)</t>
   </si>
   <si>
     <t xml:space="preserve">Detail Tab / Notes</t>
   </si>
   <si>
+    <t xml:space="preserve">MLB Sunday Slate (15 games)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACTIVE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tab: MLB Jul 12 · LIVE — 2-5 thru 7, Giants ML remaining</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WNBA Sunday Doubleheader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tab: WNBA Jul 12 · Sky@Wings 7 ET, Fever@Aces 9 ET</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NASCAR Quaker State 400</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tab: NASCAR Jul 12 · race ~7 PM ET</t>
+  </si>
+  <si>
+    <t xml:space="preserve">World Cup 2026 — Final Four</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jul 14-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tab: World Cup 2026 · semis Tue/Wed, final Sun</t>
+  </si>
+  <si>
     <t xml:space="preserve">UFC 329: McGregor vs Holloway 2</t>
   </si>
   <si>
@@ -104,39 +137,6 @@
   </si>
   <si>
     <t xml:space="preserve">Tab: UFC 329 · 6-3, settled Jul 11 · archives Jul 18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">World Cup 2026 — Final Four</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jul 14-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACTIVE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tab: World Cup 2026 · semis Tue/Wed, final Sun</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MLB Sunday Slate (15 games)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tab: MLB Jul 12 · 2-5 thru 7 of 8 · Giants ML still live</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NASCAR Quaker State 400</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tab: NASCAR Jul 12 · race ~7 PM ET</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WNBA Sunday Doubleheader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tab: WNBA Jul 12 · Sky@Wings 7 ET, Fever@Aces 9 ET</t>
   </si>
   <si>
     <t xml:space="preserve">TOTALS</t>
@@ -1160,17 +1160,20 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="10">
+  <numFmts count="13">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="\$#,##0"/>
     <numFmt numFmtId="166" formatCode="\$#,##0.00;&quot;($&quot;#,##0.00\);\-"/>
     <numFmt numFmtId="167" formatCode="\$#,##0.00"/>
-    <numFmt numFmtId="168" formatCode="\+0;\-0"/>
-    <numFmt numFmtId="169" formatCode="0"/>
-    <numFmt numFmtId="170" formatCode="0.0%"/>
-    <numFmt numFmtId="171" formatCode="0%"/>
-    <numFmt numFmtId="172" formatCode="0.0&quot; exp. wins&quot;"/>
-    <numFmt numFmtId="173" formatCode="0.0"/>
+    <numFmt numFmtId="168" formatCode="\$#,##0"/>
+    <numFmt numFmtId="169" formatCode="\$#,##0.00"/>
+    <numFmt numFmtId="170" formatCode="\$#,##0.00;&quot;($&quot;#,##0.00\);\-"/>
+    <numFmt numFmtId="171" formatCode="\+0;\-0"/>
+    <numFmt numFmtId="172" formatCode="0"/>
+    <numFmt numFmtId="173" formatCode="0.0%"/>
+    <numFmt numFmtId="174" formatCode="0%"/>
+    <numFmt numFmtId="175" formatCode="0.0&quot; exp. wins&quot;"/>
+    <numFmt numFmtId="176" formatCode="0.0"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -1251,7 +1254,7 @@
     <font>
       <b val="true"/>
       <sz val="10"/>
-      <color rgb="FF808080"/>
+      <color rgb="FF1B7A3D"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -1266,7 +1269,7 @@
     <font>
       <b val="true"/>
       <sz val="10"/>
-      <color rgb="FF1B7A3D"/>
+      <color rgb="FF808080"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -1360,14 +1363,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE7E6E6"/>
-        <bgColor rgb="FFE2F0D9"/>
+        <fgColor rgb="FFE2F0D9"/>
+        <bgColor rgb="FFE7E6E6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE2F0D9"/>
-        <bgColor rgb="FFE7E6E6"/>
+        <fgColor rgb="FFE7E6E6"/>
+        <bgColor rgb="FFE2F0D9"/>
       </patternFill>
     </fill>
     <fill>
@@ -1527,19 +1530,19 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1559,19 +1562,19 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1639,7 +1642,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="171" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1671,11 +1674,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="172" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1695,15 +1698,15 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="174" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="175" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="176" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1719,7 +1722,7 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1735,7 +1738,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2154,7 +2157,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B16" s="14" t="s">
         <v>22</v>
@@ -2166,168 +2169,168 @@
         <v>24</v>
       </c>
       <c r="E16" s="16" t="n">
+        <f aca="false">SUM('MLB Jul 12'!F7:F14)</f>
+        <v>1000</v>
+      </c>
+      <c r="F16" s="16" t="n">
+        <f aca="false">SUMIF('MLB Jul 12'!I7:I14,"Pending",'MLB Jul 12'!F7:F14)</f>
+        <v>200</v>
+      </c>
+      <c r="G16" s="17" t="n">
+        <f aca="false">SUM('MLB Jul 12'!J7:J14)</f>
+        <v>473.2</v>
+      </c>
+      <c r="H16" s="18" t="n">
+        <f aca="false">SUM('MLB Jul 12'!K7:K14)</f>
+        <v>-326.8</v>
+      </c>
+      <c r="I16" s="19" t="n">
+        <f aca="false">B5+H16</f>
+        <v>4673.2</v>
+      </c>
+      <c r="J16" s="20" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="B17" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="C17" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D17" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="E17" s="16" t="n">
+        <f aca="false">SUM('WNBA Jul 12'!F7:F13)</f>
+        <v>1000</v>
+      </c>
+      <c r="F17" s="16" t="n">
+        <f aca="false">SUMIF('WNBA Jul 12'!I7:I13,"Pending",'WNBA Jul 12'!F7:F13)</f>
+        <v>1000</v>
+      </c>
+      <c r="G17" s="17" t="n">
+        <f aca="false">SUM('WNBA Jul 12'!J7:J13)</f>
+        <v>0</v>
+      </c>
+      <c r="H17" s="18" t="n">
+        <f aca="false">SUM('WNBA Jul 12'!K7:K13)</f>
+        <v>0</v>
+      </c>
+      <c r="I17" s="19" t="n">
+        <f aca="false">I16+H17</f>
+        <v>4673.2</v>
+      </c>
+      <c r="J17" s="20" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D18" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="E18" s="16" t="n">
+        <f aca="false">SUM('NASCAR Jul 12'!F7:F13)</f>
+        <v>1000</v>
+      </c>
+      <c r="F18" s="16" t="n">
+        <f aca="false">SUMIF('NASCAR Jul 12'!I7:I13,"Pending",'NASCAR Jul 12'!F7:F13)</f>
+        <v>1000</v>
+      </c>
+      <c r="G18" s="17" t="n">
+        <f aca="false">SUM('NASCAR Jul 12'!J7:J13)</f>
+        <v>0</v>
+      </c>
+      <c r="H18" s="18" t="n">
+        <f aca="false">SUM('NASCAR Jul 12'!K7:K13)</f>
+        <v>0</v>
+      </c>
+      <c r="I18" s="19" t="n">
+        <f aca="false">I17+H18</f>
+        <v>4673.2</v>
+      </c>
+      <c r="J18" s="20" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B19" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="C19" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="D19" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="E19" s="16" t="n">
+        <f aca="false">SUM('World Cup 2026'!F7:F13)</f>
+        <v>1000</v>
+      </c>
+      <c r="F19" s="16" t="n">
+        <f aca="false">SUMIF('World Cup 2026'!I7:I13,"Pending",'World Cup 2026'!F7:F13)</f>
+        <v>1000</v>
+      </c>
+      <c r="G19" s="17" t="n">
+        <f aca="false">SUM('World Cup 2026'!J7:J13)</f>
+        <v>0</v>
+      </c>
+      <c r="H19" s="18" t="n">
+        <f aca="false">SUM('World Cup 2026'!K7:K13)</f>
+        <v>0</v>
+      </c>
+      <c r="I19" s="19" t="n">
+        <f aca="false">I18+H19</f>
+        <v>4673.2</v>
+      </c>
+      <c r="J19" s="20" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="B20" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="C20" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="D20" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="E20" s="24" t="n">
         <f aca="false">SUM('UFC 329'!F7:F15)</f>
         <v>1050</v>
       </c>
-      <c r="F16" s="16" t="n">
+      <c r="F20" s="24" t="n">
         <f aca="false">SUMIF('UFC 329'!I7:I15,"Pending",'UFC 329'!F7:F15)</f>
         <v>0</v>
       </c>
-      <c r="G16" s="17" t="n">
+      <c r="G20" s="25" t="n">
         <f aca="false">SUM('UFC 329'!J7:J15)</f>
         <v>1215.1103728313</v>
       </c>
-      <c r="H16" s="18" t="n">
+      <c r="H20" s="26" t="n">
         <f aca="false">SUM('UFC 329'!K7:K15)</f>
         <v>165.110372831303</v>
-      </c>
-      <c r="I16" s="19" t="n">
-        <f aca="false">B5+H16</f>
-        <v>5165.1103728313</v>
-      </c>
-      <c r="J16" s="20" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="B17" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="C17" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="D17" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="E17" s="24" t="n">
-        <f aca="false">SUM('World Cup 2026'!F7:F13)</f>
-        <v>1000</v>
-      </c>
-      <c r="F17" s="24" t="n">
-        <f aca="false">SUMIF('World Cup 2026'!I7:I13,"Pending",'World Cup 2026'!F7:F13)</f>
-        <v>1000</v>
-      </c>
-      <c r="G17" s="25" t="n">
-        <f aca="false">SUM('World Cup 2026'!J7:J13)</f>
-        <v>0</v>
-      </c>
-      <c r="H17" s="26" t="n">
-        <f aca="false">SUM('World Cup 2026'!K7:K13)</f>
-        <v>0</v>
-      </c>
-      <c r="I17" s="27" t="n">
-        <f aca="false">I16+H17</f>
-        <v>5165.1103728313</v>
-      </c>
-      <c r="J17" s="28" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="21" t="n">
-        <v>3</v>
-      </c>
-      <c r="B18" s="22" t="s">
-        <v>30</v>
-      </c>
-      <c r="C18" s="21" t="s">
-        <v>31</v>
-      </c>
-      <c r="D18" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="E18" s="24" t="n">
-        <f aca="false">SUM('MLB Jul 12'!F7:F14)</f>
-        <v>1000</v>
-      </c>
-      <c r="F18" s="24" t="n">
-        <f aca="false">SUMIF('MLB Jul 12'!I7:I14,"Pending",'MLB Jul 12'!F7:F14)</f>
-        <v>200</v>
-      </c>
-      <c r="G18" s="25" t="n">
-        <f aca="false">SUM('MLB Jul 12'!J7:J14)</f>
-        <v>473.2</v>
-      </c>
-      <c r="H18" s="26" t="n">
-        <f aca="false">SUM('MLB Jul 12'!K7:K14)</f>
-        <v>-326.8</v>
-      </c>
-      <c r="I18" s="27" t="n">
-        <f aca="false">I17+H18</f>
-        <v>4838.3103728313</v>
-      </c>
-      <c r="J18" s="28" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="21" t="n">
-        <v>4</v>
-      </c>
-      <c r="B19" s="22" t="s">
-        <v>33</v>
-      </c>
-      <c r="C19" s="21" t="s">
-        <v>31</v>
-      </c>
-      <c r="D19" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="E19" s="24" t="n">
-        <f aca="false">SUM('NASCAR Jul 12'!F7:F13)</f>
-        <v>1000</v>
-      </c>
-      <c r="F19" s="24" t="n">
-        <f aca="false">SUMIF('NASCAR Jul 12'!I7:I13,"Pending",'NASCAR Jul 12'!F7:F13)</f>
-        <v>1000</v>
-      </c>
-      <c r="G19" s="25" t="n">
-        <f aca="false">SUM('NASCAR Jul 12'!J7:J13)</f>
-        <v>0</v>
-      </c>
-      <c r="H19" s="26" t="n">
-        <f aca="false">SUM('NASCAR Jul 12'!K7:K13)</f>
-        <v>0</v>
-      </c>
-      <c r="I19" s="27" t="n">
-        <f aca="false">I18+H19</f>
-        <v>4838.3103728313</v>
-      </c>
-      <c r="J19" s="28" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="B20" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="C20" s="21" t="s">
-        <v>31</v>
-      </c>
-      <c r="D20" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="E20" s="24" t="n">
-        <f aca="false">SUM('WNBA Jul 12'!F7:F13)</f>
-        <v>1000</v>
-      </c>
-      <c r="F20" s="24" t="n">
-        <f aca="false">SUMIF('WNBA Jul 12'!I7:I13,"Pending",'WNBA Jul 12'!F7:F13)</f>
-        <v>1000</v>
-      </c>
-      <c r="G20" s="25" t="n">
-        <f aca="false">SUM('WNBA Jul 12'!J7:J13)</f>
-        <v>0</v>
-      </c>
-      <c r="H20" s="26" t="n">
-        <f aca="false">SUM('WNBA Jul 12'!K7:K13)</f>
-        <v>0</v>
       </c>
       <c r="I20" s="27" t="n">
         <f aca="false">I19+H20</f>

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -100,15 +100,18 @@
     <t xml:space="preserve">2026-07-12</t>
   </si>
   <si>
+    <t xml:space="preserve">SETTLED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tab: MLB Jul 12 · SETTLED 3-5 (37.5%), -$197.77 · Giants ML won</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WNBA Sunday Doubleheader</t>
+  </si>
+  <si>
     <t xml:space="preserve">ACTIVE</t>
   </si>
   <si>
-    <t xml:space="preserve">Tab: MLB Jul 12 · LIVE — 2-5 thru 7, Giants ML remaining</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WNBA Sunday Doubleheader</t>
-  </si>
-  <si>
     <t xml:space="preserve">Tab: WNBA Jul 12 · Sky@Wings 7 ET, Fever@Aces 9 ET</t>
   </si>
   <si>
@@ -133,9 +136,6 @@
     <t xml:space="preserve">2026-07-11</t>
   </si>
   <si>
-    <t xml:space="preserve">SETTLED</t>
-  </si>
-  <si>
     <t xml:space="preserve">Tab: UFC 329 · 6-3, settled Jul 11 · archives Jul 18</t>
   </si>
   <si>
@@ -643,7 +643,7 @@
     <t xml:space="preserve">TEST 3 — MLB SUNDAY SLATE · JULY 12, 2026</t>
   </si>
   <si>
-    <t xml:space="preserve">STATUS: ACTIVE — 1 of 8 settled (Pirates ✓ +$135.20)</t>
+    <t xml:space="preserve">STATUS: ARCHIVED — settled Jul 12 (3-5, -$197.77)</t>
   </si>
   <si>
     <t xml:space="preserve">15-game slate, 8 bets · Source: mlb-jul12-betting-card.html · Lines: ESPN consensus board, Sunday AM · Research: VSiN, PickDawgz, DK Network</t>
@@ -664,7 +664,7 @@
     <t xml:space="preserve">vs Rockies · McDonald vs Lorenzen (6.46 ERA)</t>
   </si>
   <si>
-    <t xml:space="preserve">Safest play — Lorenzen 1.4 HR/9, Rockies worst road team</t>
+    <t xml:space="preserve">Safest play — Lorenzen 1.4 HR/9, Rockies worst road team · RESULT: SF 3-1 · Lorenzen fade lands</t>
   </si>
   <si>
     <t xml:space="preserve">Athletics ML</t>
@@ -1160,20 +1160,17 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="13">
+  <numFmts count="10">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="\$#,##0"/>
     <numFmt numFmtId="166" formatCode="\$#,##0.00;&quot;($&quot;#,##0.00\);\-"/>
     <numFmt numFmtId="167" formatCode="\$#,##0.00"/>
-    <numFmt numFmtId="168" formatCode="\$#,##0"/>
-    <numFmt numFmtId="169" formatCode="\$#,##0.00"/>
-    <numFmt numFmtId="170" formatCode="\$#,##0.00;&quot;($&quot;#,##0.00\);\-"/>
-    <numFmt numFmtId="171" formatCode="\+0;\-0"/>
-    <numFmt numFmtId="172" formatCode="0"/>
-    <numFmt numFmtId="173" formatCode="0.0%"/>
-    <numFmt numFmtId="174" formatCode="0%"/>
-    <numFmt numFmtId="175" formatCode="0.0&quot; exp. wins&quot;"/>
-    <numFmt numFmtId="176" formatCode="0.0"/>
+    <numFmt numFmtId="168" formatCode="\+0;\-0"/>
+    <numFmt numFmtId="169" formatCode="0"/>
+    <numFmt numFmtId="170" formatCode="0.0%"/>
+    <numFmt numFmtId="171" formatCode="0%"/>
+    <numFmt numFmtId="172" formatCode="0.0&quot; exp. wins&quot;"/>
+    <numFmt numFmtId="173" formatCode="0.0"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -1254,7 +1251,7 @@
     <font>
       <b val="true"/>
       <sz val="10"/>
-      <color rgb="FF1B7A3D"/>
+      <color rgb="FF808080"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -1269,7 +1266,7 @@
     <font>
       <b val="true"/>
       <sz val="10"/>
-      <color rgb="FF808080"/>
+      <color rgb="FF1B7A3D"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -1363,14 +1360,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE2F0D9"/>
-        <bgColor rgb="FFE7E6E6"/>
+        <fgColor rgb="FFE7E6E6"/>
+        <bgColor rgb="FFE2F0D9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE7E6E6"/>
-        <bgColor rgb="FFE2F0D9"/>
+        <fgColor rgb="FFE2F0D9"/>
+        <bgColor rgb="FFE7E6E6"/>
       </patternFill>
     </fill>
     <fill>
@@ -1530,19 +1527,19 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1562,19 +1559,19 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1642,39 +1639,67 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="168" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="171" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="172" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="172" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1682,34 +1707,6 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="174" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="175" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="176" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1722,7 +1719,7 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1738,7 +1735,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2071,7 +2068,7 @@
       </c>
       <c r="B6" s="7" t="n">
         <f aca="false">H21</f>
-        <v>-161.689627168697</v>
+        <v>-32.6573691041808</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2080,7 +2077,7 @@
       </c>
       <c r="B7" s="8" t="n">
         <f aca="false">I20</f>
-        <v>4838.3103728313</v>
+        <v>4967.34263089582</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2089,7 +2086,7 @@
       </c>
       <c r="B8" s="9" t="n">
         <f aca="false">F21</f>
-        <v>3200</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2098,7 +2095,7 @@
       </c>
       <c r="B9" s="8" t="n">
         <f aca="false">B7-B8</f>
-        <v>1638.3103728313</v>
+        <v>1967.34263089582</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2107,7 +2104,7 @@
       </c>
       <c r="B10" s="10" t="str">
         <f aca="false">COUNTIF(D16:D20,"ACTIVE")&amp;" of 4 max"</f>
-        <v>4 of 4 max</v>
+        <v>3 of 4 max</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2174,169 +2171,169 @@
       </c>
       <c r="F16" s="16" t="n">
         <f aca="false">SUMIF('MLB Jul 12'!I7:I14,"Pending",'MLB Jul 12'!F7:F14)</f>
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G16" s="17" t="n">
         <f aca="false">SUM('MLB Jul 12'!J7:J14)</f>
-        <v>473.2</v>
+        <v>802.232258064516</v>
       </c>
       <c r="H16" s="18" t="n">
         <f aca="false">SUM('MLB Jul 12'!K7:K14)</f>
-        <v>-326.8</v>
+        <v>-197.767741935484</v>
       </c>
       <c r="I16" s="19" t="n">
         <f aca="false">B5+H16</f>
-        <v>4673.2</v>
+        <v>4802.23225806452</v>
       </c>
       <c r="J16" s="20" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="13" t="n">
+      <c r="A17" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="B17" s="14" t="s">
+      <c r="B17" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="C17" s="13" t="s">
+      <c r="C17" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="D17" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="E17" s="16" t="n">
+      <c r="D17" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="E17" s="24" t="n">
         <f aca="false">SUM('WNBA Jul 12'!F7:F13)</f>
         <v>1000</v>
       </c>
-      <c r="F17" s="16" t="n">
+      <c r="F17" s="24" t="n">
         <f aca="false">SUMIF('WNBA Jul 12'!I7:I13,"Pending",'WNBA Jul 12'!F7:F13)</f>
         <v>1000</v>
       </c>
-      <c r="G17" s="17" t="n">
+      <c r="G17" s="25" t="n">
         <f aca="false">SUM('WNBA Jul 12'!J7:J13)</f>
         <v>0</v>
       </c>
-      <c r="H17" s="18" t="n">
+      <c r="H17" s="26" t="n">
         <f aca="false">SUM('WNBA Jul 12'!K7:K13)</f>
         <v>0</v>
       </c>
-      <c r="I17" s="19" t="n">
+      <c r="I17" s="27" t="n">
         <f aca="false">I16+H17</f>
-        <v>4673.2</v>
-      </c>
-      <c r="J17" s="20" t="s">
+        <v>4802.23225806452</v>
+      </c>
+      <c r="J17" s="28" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="B18" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="C18" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="D18" s="23" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="13" t="n">
-        <v>4</v>
-      </c>
-      <c r="B18" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="C18" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="D18" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="E18" s="16" t="n">
+      <c r="E18" s="24" t="n">
         <f aca="false">SUM('NASCAR Jul 12'!F7:F13)</f>
         <v>1000</v>
       </c>
-      <c r="F18" s="16" t="n">
+      <c r="F18" s="24" t="n">
         <f aca="false">SUMIF('NASCAR Jul 12'!I7:I13,"Pending",'NASCAR Jul 12'!F7:F13)</f>
         <v>1000</v>
       </c>
-      <c r="G18" s="17" t="n">
+      <c r="G18" s="25" t="n">
         <f aca="false">SUM('NASCAR Jul 12'!J7:J13)</f>
         <v>0</v>
       </c>
-      <c r="H18" s="18" t="n">
+      <c r="H18" s="26" t="n">
         <f aca="false">SUM('NASCAR Jul 12'!K7:K13)</f>
         <v>0</v>
       </c>
-      <c r="I18" s="19" t="n">
+      <c r="I18" s="27" t="n">
         <f aca="false">I17+H18</f>
-        <v>4673.2</v>
-      </c>
-      <c r="J18" s="20" t="s">
-        <v>29</v>
+        <v>4802.23225806452</v>
+      </c>
+      <c r="J18" s="28" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="13" t="n">
+      <c r="A19" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="B19" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="C19" s="13" t="s">
+      <c r="B19" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="D19" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="E19" s="16" t="n">
+      <c r="C19" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="D19" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="E19" s="24" t="n">
         <f aca="false">SUM('World Cup 2026'!F7:F13)</f>
         <v>1000</v>
       </c>
-      <c r="F19" s="16" t="n">
+      <c r="F19" s="24" t="n">
         <f aca="false">SUMIF('World Cup 2026'!I7:I13,"Pending",'World Cup 2026'!F7:F13)</f>
         <v>1000</v>
       </c>
-      <c r="G19" s="17" t="n">
+      <c r="G19" s="25" t="n">
         <f aca="false">SUM('World Cup 2026'!J7:J13)</f>
         <v>0</v>
       </c>
-      <c r="H19" s="18" t="n">
+      <c r="H19" s="26" t="n">
         <f aca="false">SUM('World Cup 2026'!K7:K13)</f>
         <v>0</v>
       </c>
-      <c r="I19" s="19" t="n">
+      <c r="I19" s="27" t="n">
         <f aca="false">I18+H19</f>
-        <v>4673.2</v>
-      </c>
-      <c r="J19" s="20" t="s">
-        <v>32</v>
+        <v>4802.23225806452</v>
+      </c>
+      <c r="J19" s="28" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="21" t="n">
+      <c r="A20" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="B20" s="22" t="s">
-        <v>33</v>
-      </c>
-      <c r="C20" s="21" t="s">
+      <c r="B20" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="D20" s="23" t="s">
+      <c r="C20" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="E20" s="24" t="n">
+      <c r="D20" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="E20" s="16" t="n">
         <f aca="false">SUM('UFC 329'!F7:F15)</f>
         <v>1050</v>
       </c>
-      <c r="F20" s="24" t="n">
+      <c r="F20" s="16" t="n">
         <f aca="false">SUMIF('UFC 329'!I7:I15,"Pending",'UFC 329'!F7:F15)</f>
         <v>0</v>
       </c>
-      <c r="G20" s="25" t="n">
+      <c r="G20" s="17" t="n">
         <f aca="false">SUM('UFC 329'!J7:J15)</f>
         <v>1215.1103728313</v>
       </c>
-      <c r="H20" s="26" t="n">
+      <c r="H20" s="18" t="n">
         <f aca="false">SUM('UFC 329'!K7:K15)</f>
         <v>165.110372831303</v>
       </c>
-      <c r="I20" s="27" t="n">
+      <c r="I20" s="19" t="n">
         <f aca="false">I19+H20</f>
-        <v>4838.3103728313</v>
-      </c>
-      <c r="J20" s="28" t="s">
+        <v>4967.34263089582</v>
+      </c>
+      <c r="J20" s="20" t="s">
         <v>36</v>
       </c>
     </row>
@@ -2353,15 +2350,15 @@
       </c>
       <c r="F21" s="31" t="n">
         <f aca="false">SUM(F16:F20)</f>
-        <v>3200</v>
+        <v>3000</v>
       </c>
       <c r="G21" s="32" t="n">
         <f aca="false">SUM(G16:G20)</f>
-        <v>1688.3103728313</v>
+        <v>2017.34263089582</v>
       </c>
       <c r="H21" s="33" t="n">
         <f aca="false">SUM(H16:H20)</f>
-        <v>-161.689627168697</v>
+        <v>-32.6573691041808</v>
       </c>
       <c r="I21" s="29"/>
       <c r="J21" s="29"/>
@@ -3944,7 +3941,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <tabColor rgb="FF1B7A3D"/>
+    <tabColor rgb="FF808080"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:M42"/>
@@ -3966,7 +3963,7 @@
       <c r="A1" s="39" t="s">
         <v>204</v>
       </c>
-      <c r="H1" s="56" t="s">
+      <c r="H1" s="40" t="s">
         <v>205</v>
       </c>
     </row>
@@ -4053,16 +4050,16 @@
         <f aca="false">F7+G7</f>
         <v>329.032258064516</v>
       </c>
-      <c r="I7" s="57" t="s">
-        <v>112</v>
+      <c r="I7" s="46" t="s">
+        <v>79</v>
       </c>
       <c r="J7" s="45" t="n">
         <f aca="false">IF(I7="Win",F7+G7,IF(I7="Push",F7,IF(I7="Loss",0,0)))</f>
-        <v>0</v>
+        <v>329.032258064516</v>
       </c>
       <c r="K7" s="47" t="n">
         <f aca="false">IF(I7="Pending",0,J7-F7)</f>
-        <v>0</v>
+        <v>129.032258064516</v>
       </c>
       <c r="L7" s="58" t="n">
         <v>0.62</v>
@@ -4409,11 +4406,11 @@
       <c r="I15" s="50"/>
       <c r="J15" s="32" t="n">
         <f aca="false">SUM(J7:J14)</f>
-        <v>473.2</v>
+        <v>802.232258064516</v>
       </c>
       <c r="K15" s="33" t="n">
         <f aca="false">SUM(K7:K14)</f>
-        <v>-326.8</v>
+        <v>-197.767741935484</v>
       </c>
       <c r="L15" s="59" t="n">
         <f aca="false">SUM(L7:L14)</f>
@@ -4432,7 +4429,7 @@
       </c>
       <c r="C18" s="52" t="n">
         <f aca="false">COUNTIF(I7:I14,"Win")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4459,7 +4456,7 @@
       </c>
       <c r="C21" s="52" t="n">
         <f aca="false">COUNTIF(I7:I14,"Pending")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4468,7 +4465,7 @@
       </c>
       <c r="C22" s="53" t="n">
         <f aca="false">IF(COUNTIF(I7:I14,"Win")+COUNTIF(I7:I14,"Loss")=0,"—",COUNTIF(I7:I14,"Win")/(COUNTIF(I7:I14,"Win")+COUNTIF(I7:I14,"Loss")))</f>
-        <v>0.285714285714286</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4486,7 +4483,7 @@
       </c>
       <c r="C24" s="45" t="n">
         <f aca="false">SUM(J7:J14)</f>
-        <v>473.2</v>
+        <v>802.232258064516</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4495,7 +4492,7 @@
       </c>
       <c r="C25" s="47" t="n">
         <f aca="false">SUM(K7:K14)</f>
-        <v>-326.8</v>
+        <v>-197.767741935484</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4504,7 +4501,7 @@
       </c>
       <c r="C26" s="53" t="n">
         <f aca="false">IF(SUM(F7:F14)=0,"—",SUM(K7:K14)/SUM(F7:F14))</f>
-        <v>-0.3268</v>
+        <v>-0.197767741935484</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -15,6 +15,7 @@
     <sheet name="NASCAR Jul 12" sheetId="5" state="visible" r:id="rId7"/>
     <sheet name="References" sheetId="6" state="visible" r:id="rId8"/>
     <sheet name="WNBA Jul 12" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="The Open" sheetId="8" state="visible" r:id="rId10"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -26,12 +27,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="587" uniqueCount="376">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="673" uniqueCount="421">
   <si>
     <t xml:space="preserve">BETTING TEST ACCOUNT — ROLL-UP DASHBOARD</t>
   </si>
   <si>
-    <t xml:space="preserve">Account rules: $5,000 total account · max $1,000 staked per card · max 4 cards active at any time. Cards archive off this dashboard 7 days after settling.</t>
+    <t xml:space="preserve">Account rules: $5,000 total account · max $1,000 staked per card · max 4 cards active at any time. QUEUED cards hold no money and don't count against the cap. Settled cards archive after 7 days.</t>
   </si>
   <si>
     <t xml:space="preserve">ACCOUNT SUMMARY</t>
@@ -61,7 +62,7 @@
     <t xml:space="preserve">$1,000 (UFC card staked $1,050 — pre-dates rule; grandfathered)</t>
   </si>
   <si>
-    <t xml:space="preserve">CARD TIMELINE — ACCOUNT IMPACT OVER TIME</t>
+    <t xml:space="preserve">CARD TIMELINE — SORTED BY NEXT ACTION (settled at bottom)</t>
   </si>
   <si>
     <t xml:space="preserve">#</t>
@@ -88,46 +89,67 @@
     <t xml:space="preserve">Net P/L to Date</t>
   </si>
   <si>
-    <t xml:space="preserve">Running Balance (display order)</t>
+    <t xml:space="preserve">Running Balance</t>
   </si>
   <si>
     <t xml:space="preserve">Detail Tab / Notes</t>
   </si>
   <si>
+    <t xml:space="preserve">WNBA Sunday Doubleheader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACTIVE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tab: WNBA Jul 12 · Sky@Wings 7 ET, Fever@Aces 9 ET</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NASCAR Quaker State 400</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tab: NASCAR Jul 12 · race ~7 PM ET tonight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">World Cup 2026 — Final Four</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jul 14-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tab: World Cup 2026 · semis Tue/Wed, final Sun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Open Championship (golf)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jul 16-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tab: The Open · $600 outrights + $400 props Wed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rugby Nations Cup — Final Rd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QUEUED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Draft card built · odds post ~Fri · $0 at risk</t>
+  </si>
+  <si>
     <t xml:space="preserve">MLB Sunday Slate (15 games)</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-12</t>
-  </si>
-  <si>
     <t xml:space="preserve">SETTLED</t>
   </si>
   <si>
-    <t xml:space="preserve">Tab: MLB Jul 12 · SETTLED 3-5 (37.5%), -$197.77 · Giants ML won</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WNBA Sunday Doubleheader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACTIVE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tab: WNBA Jul 12 · Sky@Wings 7 ET, Fever@Aces 9 ET</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NASCAR Quaker State 400</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tab: NASCAR Jul 12 · race ~7 PM ET</t>
-  </si>
-  <si>
-    <t xml:space="preserve">World Cup 2026 — Final Four</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jul 14-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tab: World Cup 2026 · semis Tue/Wed, final Sun</t>
+    <t xml:space="preserve">Tab: MLB Jul 12 · SETTLED 3-5 (37.5%), -$197.77</t>
   </si>
   <si>
     <t xml:space="preserve">UFC 329: McGregor vs Holloway 2</t>
@@ -136,7 +158,7 @@
     <t xml:space="preserve">2026-07-11</t>
   </si>
   <si>
-    <t xml:space="preserve">Tab: UFC 329 · 6-3, settled Jul 11 · archives Jul 18</t>
+    <t xml:space="preserve">Tab: UFC 329 · 6-3, +$165.11 · archives Jul 18</t>
   </si>
   <si>
     <t xml:space="preserve">TOTALS</t>
@@ -196,19 +218,40 @@
     <t xml:space="preserve">+971</t>
   </si>
   <si>
+    <t xml:space="preserve">Test 6 · The Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brooks Koepka outright</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+5000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test 7 · Rugby Jul 18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TBD at finalization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TBD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Queued</t>
+  </si>
+  <si>
     <t xml:space="preserve">LONGSHOT HIT RATE</t>
   </si>
   <si>
-    <t xml:space="preserve">Note: WC card carries an England hedge ticket, not a longshot — excluded from this record. UFC longshot was flagged at $0 stake and missed.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Legend: GREEN-tinted rows = ACTIVE cards · GREY-tinted rows = SETTLED/ARCHIVE (drop off 7 days after settling). Tab colors match.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">'Net P/L to Date' includes partially-graded cards, so the account balance moves as individual bets settle.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blue = manual input · Black = formula. Status column is set manually when a card fully settles.</t>
+    <t xml:space="preserve">Note: WC card carries an England hedge, not a longshot — excluded. UFC longshot was $0-stake and missed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legend: GREEN rows = ACTIVE · YELLOW = QUEUED (no money) · GREY = SETTLED/ARCHIVE. Tab colors match.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">'Net P/L to Date' includes partially-graded cards; Running Balance applies P/L top-to-bottom in display order (bottom row = current balance).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blue = manual input · Black = formula.</t>
   </si>
   <si>
     <t xml:space="preserve">TEST 1 — UFC 329: McGREGOR vs HOLLOWAY 2</t>
@@ -1063,6 +1106,33 @@
     <t xml:space="preserve">T2: France-Spain lines · T5 WNBA: all game lines &amp; props</t>
   </si>
   <si>
+    <t xml:space="preserve">golfdigest.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Golf major picks &amp; player analysis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T6 Open: 13-best-bets breakdown, form/course fit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sportsbettingdime.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Odds tracking (DraftKings)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T6 Open: outright board · also WC SF openers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">all.rugby</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rugby fixtures &amp; results</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T7 Rugby: Nations Cup rounds 1-2 results, Rd 3 fixtures</t>
+  </si>
+  <si>
     <t xml:space="preserve">⚠ SOURCE CAUTION — KALSHI (per John, 2026-07-12): prediction-market prices can be manipulated ('market rigging'). Kalshi probabilities are used for CONTEXT/comparison only, never as a primary betting basis. Primary basis = sportsbook consensus + our own stats analysis.</t>
   </si>
   <si>
@@ -1154,25 +1224,95 @@
   </si>
   <si>
     <t xml:space="preserve">Yellow = fill in results (dropdown). Blue = inputs. Black = formulas. Parlay odds +971 = (-115 × -108 × -159 × -121) compounded; grades as one bet.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEST 6 — THE 154th OPEN CHAMPIONSHIP · ROYAL BIRKDALE · JULY 16-19, 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STATUS: ACTIVE — first tee Thu Jul 16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source: open2026-betting-card.html · Odds: DraftKings/consensus + Golf Digest, locked Sun Jul 12 · Phase 2 props ($400) added Wed Jul 15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Outright basket is mutually exclusive — max one cashes. Basket coverage ≈ 44%. $600 deployed now; $400 reserved (not yet at risk).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scottie Scheffler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anchor — defending champ, drought discount on world No. 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jon Rahm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two majors, near-misses all season, wind player</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tommy Fleetwood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Southport native — Birkdale is his home course</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matt Fitzpatrick</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 wins this season, English home major</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Collin Morikawa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021 Open champ, Sunday 61 at Travelers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brooks Koepka (LONGSHOT)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 majors, career-long price · counts in longshot record</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RESERVED — Phase 2 props (Wed)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Top-10s / H2H matchups / make-cut — lines post midweek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$400 reserved, not yet at risk; converts Wed Jul 15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOTALS (deployed)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total Staked (Phase 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Basket Coverage (one wins)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="10">
+  <numFmts count="14">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="\$#,##0"/>
     <numFmt numFmtId="166" formatCode="\$#,##0.00;&quot;($&quot;#,##0.00\);\-"/>
     <numFmt numFmtId="167" formatCode="\$#,##0.00"/>
     <numFmt numFmtId="168" formatCode="\+0;\-0"/>
-    <numFmt numFmtId="169" formatCode="0"/>
-    <numFmt numFmtId="170" formatCode="0.0%"/>
-    <numFmt numFmtId="171" formatCode="0%"/>
-    <numFmt numFmtId="172" formatCode="0.0&quot; exp. wins&quot;"/>
-    <numFmt numFmtId="173" formatCode="0.0"/>
+    <numFmt numFmtId="169" formatCode="\$#,##0"/>
+    <numFmt numFmtId="170" formatCode="\$#,##0.00"/>
+    <numFmt numFmtId="171" formatCode="\$#,##0.00;&quot;($&quot;#,##0.00\);\-"/>
+    <numFmt numFmtId="172" formatCode="0"/>
+    <numFmt numFmtId="173" formatCode="0.0%"/>
+    <numFmt numFmtId="174" formatCode="0%"/>
+    <numFmt numFmtId="175" formatCode="0.0&quot; exp. wins&quot;"/>
+    <numFmt numFmtId="176" formatCode="0.0"/>
+    <numFmt numFmtId="177" formatCode="0.00&quot; exp. wins&quot;"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1251,7 +1391,7 @@
     <font>
       <b val="true"/>
       <sz val="10"/>
-      <color rgb="FF808080"/>
+      <color rgb="FF1B7A3D"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -1266,7 +1406,15 @@
     <font>
       <b val="true"/>
       <sz val="10"/>
-      <color rgb="FF1B7A3D"/>
+      <color rgb="FF9C6500"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF808080"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -1360,14 +1508,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE7E6E6"/>
-        <bgColor rgb="FFE2F0D9"/>
+        <fgColor rgb="FFE2F0D9"/>
+        <bgColor rgb="FFE7E6E6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE2F0D9"/>
-        <bgColor rgb="FFE7E6E6"/>
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7E6E6"/>
+        <bgColor rgb="FFE2F0D9"/>
       </patternFill>
     </fill>
     <fill>
@@ -1406,12 +1560,6 @@
         <bgColor rgb="FF008080"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFF2F2F2"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border diagonalUp="false" diagonalDown="false">
@@ -1462,16 +1610,200 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="94">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1483,264 +1815,176 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="18" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="171" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="171" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="172" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="174" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="175" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="176" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="167" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="166" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="177" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="171" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="172" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="173" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="23" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1752,7 +1996,35 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="4">
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <family val="0"/>
+        <b val="1"/>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <family val="0"/>
+        <b val="1"/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <name val="Arial"/>
@@ -2026,470 +2298,575 @@
     <tabColor rgb="FF1F2A44"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J34"/>
+  <dimension ref="A1:J38"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="6" style="1" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="6" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="46"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="B5" s="5" t="n">
         <v>5000</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="7" t="n">
-        <f aca="false">H21</f>
+      <c r="B6" s="6" t="n">
+        <f aca="false">H23</f>
         <v>-32.6573691041808</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="8" t="n">
-        <f aca="false">I20</f>
+      <c r="B7" s="7" t="n">
+        <f aca="false">B5+B6</f>
         <v>4967.34263089582</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="9" t="n">
-        <f aca="false">F21</f>
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5" t="s">
+      <c r="B8" s="8" t="n">
+        <f aca="false">F23</f>
+        <v>3600</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="8" t="n">
+      <c r="B9" s="7" t="n">
         <f aca="false">B7-B8</f>
-        <v>1967.34263089582</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5" t="s">
+        <v>1367.34263089582</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="10" t="str">
-        <f aca="false">COUNTIF(D16:D20,"ACTIVE")&amp;" of 4 max"</f>
-        <v>3 of 4 max</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="5" t="s">
+      <c r="B10" s="9" t="str">
+        <f aca="false">COUNTIF(D16:D22,"ACTIVE")&amp;" of 4 max"</f>
+        <v>4 of 4 max</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="11" t="s">
+      <c r="B11" s="10" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="3" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="12" t="s">
+      <c r="A15" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="B15" s="12" t="s">
+      <c r="B15" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="12" t="s">
+      <c r="C15" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D15" s="12" t="s">
+      <c r="D15" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="E15" s="12" t="s">
+      <c r="E15" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="F15" s="12" t="s">
+      <c r="F15" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="G15" s="12" t="s">
+      <c r="G15" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="H15" s="12" t="s">
+      <c r="H15" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="I15" s="12" t="s">
+      <c r="I15" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="J15" s="12" t="s">
+      <c r="J15" s="11" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="13" t="n">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="D16" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="E16" s="15" t="n">
+        <f aca="false">SUM('WNBA Jul 12'!F7:F13)</f>
+        <v>1000</v>
+      </c>
+      <c r="F16" s="15" t="n">
+        <f aca="false">SUMIF('WNBA Jul 12'!I7:I13,"Pending",'WNBA Jul 12'!F7:F13)</f>
+        <v>1000</v>
+      </c>
+      <c r="G16" s="16" t="n">
+        <f aca="false">SUM('WNBA Jul 12'!J7:J13)</f>
+        <v>0</v>
+      </c>
+      <c r="H16" s="17" t="n">
+        <f aca="false">SUM('WNBA Jul 12'!K7:K13)</f>
+        <v>0</v>
+      </c>
+      <c r="I16" s="18" t="n">
+        <f aca="false">B5+H16</f>
+        <v>5000</v>
+      </c>
+      <c r="J16" s="19" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="D17" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="E17" s="15" t="n">
+        <f aca="false">SUM('NASCAR Jul 12'!F7:F13)</f>
+        <v>1000</v>
+      </c>
+      <c r="F17" s="15" t="n">
+        <f aca="false">SUMIF('NASCAR Jul 12'!I7:I13,"Pending",'NASCAR Jul 12'!F7:F13)</f>
+        <v>1000</v>
+      </c>
+      <c r="G17" s="16" t="n">
+        <f aca="false">SUM('NASCAR Jul 12'!J7:J13)</f>
+        <v>0</v>
+      </c>
+      <c r="H17" s="17" t="n">
+        <f aca="false">SUM('NASCAR Jul 12'!K7:K13)</f>
+        <v>0</v>
+      </c>
+      <c r="I17" s="18" t="n">
+        <f aca="false">I16+H17</f>
+        <v>5000</v>
+      </c>
+      <c r="J17" s="19" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D18" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="E18" s="15" t="n">
+        <f aca="false">SUM('World Cup 2026'!F7:F13)</f>
+        <v>1000</v>
+      </c>
+      <c r="F18" s="15" t="n">
+        <f aca="false">SUMIF('World Cup 2026'!I7:I13,"Pending",'World Cup 2026'!F7:F13)</f>
+        <v>1000</v>
+      </c>
+      <c r="G18" s="16" t="n">
+        <f aca="false">SUM('World Cup 2026'!J7:J13)</f>
+        <v>0</v>
+      </c>
+      <c r="H18" s="17" t="n">
+        <f aca="false">SUM('World Cup 2026'!K7:K13)</f>
+        <v>0</v>
+      </c>
+      <c r="I18" s="18" t="n">
+        <f aca="false">I17+H18</f>
+        <v>5000</v>
+      </c>
+      <c r="J18" s="19" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D19" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="E19" s="15" t="n">
+        <f aca="false">SUM('The Open'!F7:F12)</f>
+        <v>600</v>
+      </c>
+      <c r="F19" s="15" t="n">
+        <f aca="false">SUMIF('The Open'!I7:I12,"Pending",'The Open'!F7:F12)</f>
+        <v>600</v>
+      </c>
+      <c r="G19" s="16" t="n">
+        <f aca="false">SUM('The Open'!J7:J12)</f>
+        <v>0</v>
+      </c>
+      <c r="H19" s="17" t="n">
+        <f aca="false">SUM('The Open'!K7:K12)</f>
+        <v>0</v>
+      </c>
+      <c r="I19" s="18" t="n">
+        <f aca="false">I18+H19</f>
+        <v>5000</v>
+      </c>
+      <c r="J19" s="19" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="20" t="n">
+        <v>7</v>
+      </c>
+      <c r="B20" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="C20" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="D20" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="E20" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="26" t="n">
+        <f aca="false">I19+H20</f>
+        <v>5000</v>
+      </c>
+      <c r="J20" s="27" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="28" t="n">
         <v>3</v>
       </c>
-      <c r="B16" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="C16" s="13" t="s">
+      <c r="B21" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="C21" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="D16" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="E16" s="16" t="n">
+      <c r="D21" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="E21" s="31" t="n">
         <f aca="false">SUM('MLB Jul 12'!F7:F14)</f>
         <v>1000</v>
       </c>
-      <c r="F16" s="16" t="n">
+      <c r="F21" s="31" t="n">
         <f aca="false">SUMIF('MLB Jul 12'!I7:I14,"Pending",'MLB Jul 12'!F7:F14)</f>
         <v>0</v>
       </c>
-      <c r="G16" s="17" t="n">
+      <c r="G21" s="32" t="n">
         <f aca="false">SUM('MLB Jul 12'!J7:J14)</f>
         <v>802.232258064516</v>
       </c>
-      <c r="H16" s="18" t="n">
+      <c r="H21" s="33" t="n">
         <f aca="false">SUM('MLB Jul 12'!K7:K14)</f>
         <v>-197.767741935484</v>
       </c>
-      <c r="I16" s="19" t="n">
-        <f aca="false">B5+H16</f>
+      <c r="I21" s="34" t="n">
+        <f aca="false">I20+H21</f>
         <v>4802.23225806452</v>
       </c>
-      <c r="J16" s="20" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="B17" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="C17" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="D17" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="E17" s="24" t="n">
-        <f aca="false">SUM('WNBA Jul 12'!F7:F13)</f>
-        <v>1000</v>
-      </c>
-      <c r="F17" s="24" t="n">
-        <f aca="false">SUMIF('WNBA Jul 12'!I7:I13,"Pending",'WNBA Jul 12'!F7:F13)</f>
-        <v>1000</v>
-      </c>
-      <c r="G17" s="25" t="n">
-        <f aca="false">SUM('WNBA Jul 12'!J7:J13)</f>
-        <v>0</v>
-      </c>
-      <c r="H17" s="26" t="n">
-        <f aca="false">SUM('WNBA Jul 12'!K7:K13)</f>
-        <v>0</v>
-      </c>
-      <c r="I17" s="27" t="n">
-        <f aca="false">I16+H17</f>
-        <v>4802.23225806452</v>
-      </c>
-      <c r="J17" s="28" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="21" t="n">
-        <v>4</v>
-      </c>
-      <c r="B18" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="C18" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="D18" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="E18" s="24" t="n">
-        <f aca="false">SUM('NASCAR Jul 12'!F7:F13)</f>
-        <v>1000</v>
-      </c>
-      <c r="F18" s="24" t="n">
-        <f aca="false">SUMIF('NASCAR Jul 12'!I7:I13,"Pending",'NASCAR Jul 12'!F7:F13)</f>
-        <v>1000</v>
-      </c>
-      <c r="G18" s="25" t="n">
-        <f aca="false">SUM('NASCAR Jul 12'!J7:J13)</f>
-        <v>0</v>
-      </c>
-      <c r="H18" s="26" t="n">
-        <f aca="false">SUM('NASCAR Jul 12'!K7:K13)</f>
-        <v>0</v>
-      </c>
-      <c r="I18" s="27" t="n">
-        <f aca="false">I17+H18</f>
-        <v>4802.23225806452</v>
-      </c>
-      <c r="J18" s="28" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="B19" s="22" t="s">
-        <v>31</v>
-      </c>
-      <c r="C19" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="D19" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="E19" s="24" t="n">
-        <f aca="false">SUM('World Cup 2026'!F7:F13)</f>
-        <v>1000</v>
-      </c>
-      <c r="F19" s="24" t="n">
-        <f aca="false">SUMIF('World Cup 2026'!I7:I13,"Pending",'World Cup 2026'!F7:F13)</f>
-        <v>1000</v>
-      </c>
-      <c r="G19" s="25" t="n">
-        <f aca="false">SUM('World Cup 2026'!J7:J13)</f>
-        <v>0</v>
-      </c>
-      <c r="H19" s="26" t="n">
-        <f aca="false">SUM('World Cup 2026'!K7:K13)</f>
-        <v>0</v>
-      </c>
-      <c r="I19" s="27" t="n">
-        <f aca="false">I18+H19</f>
-        <v>4802.23225806452</v>
-      </c>
-      <c r="J19" s="28" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="13" t="n">
+      <c r="J21" s="35" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="B20" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="C20" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="D20" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="E20" s="16" t="n">
+      <c r="B22" s="29" t="s">
+        <v>41</v>
+      </c>
+      <c r="C22" s="28" t="s">
+        <v>42</v>
+      </c>
+      <c r="D22" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="E22" s="31" t="n">
         <f aca="false">SUM('UFC 329'!F7:F15)</f>
         <v>1050</v>
       </c>
-      <c r="F20" s="16" t="n">
+      <c r="F22" s="31" t="n">
         <f aca="false">SUMIF('UFC 329'!I7:I15,"Pending",'UFC 329'!F7:F15)</f>
         <v>0</v>
       </c>
-      <c r="G20" s="17" t="n">
+      <c r="G22" s="32" t="n">
         <f aca="false">SUM('UFC 329'!J7:J15)</f>
         <v>1215.1103728313</v>
       </c>
-      <c r="H20" s="18" t="n">
+      <c r="H22" s="33" t="n">
         <f aca="false">SUM('UFC 329'!K7:K15)</f>
         <v>165.110372831303</v>
       </c>
-      <c r="I20" s="19" t="n">
-        <f aca="false">I19+H20</f>
+      <c r="I22" s="34" t="n">
+        <f aca="false">I21+H22</f>
         <v>4967.34263089582</v>
       </c>
-      <c r="J20" s="20" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="29"/>
-      <c r="B21" s="30" t="s">
-        <v>37</v>
-      </c>
-      <c r="C21" s="29"/>
-      <c r="D21" s="29"/>
-      <c r="E21" s="31" t="n">
-        <f aca="false">SUM(E16:E20)</f>
-        <v>5050</v>
-      </c>
-      <c r="F21" s="31" t="n">
-        <f aca="false">SUM(F16:F20)</f>
-        <v>3000</v>
-      </c>
-      <c r="G21" s="32" t="n">
-        <f aca="false">SUM(G16:G20)</f>
+      <c r="J22" s="35" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="36"/>
+      <c r="B23" s="37" t="s">
+        <v>44</v>
+      </c>
+      <c r="C23" s="36"/>
+      <c r="D23" s="36"/>
+      <c r="E23" s="38" t="n">
+        <f aca="false">SUM(E16:E22)</f>
+        <v>5650</v>
+      </c>
+      <c r="F23" s="38" t="n">
+        <f aca="false">SUM(F16:F22)</f>
+        <v>3600</v>
+      </c>
+      <c r="G23" s="39" t="n">
+        <f aca="false">SUM(G16:G22)</f>
         <v>2017.34263089582</v>
       </c>
-      <c r="H21" s="33" t="n">
-        <f aca="false">SUM(H16:H20)</f>
+      <c r="H23" s="40" t="n">
+        <f aca="false">SUM(H16:H22)</f>
         <v>-32.6573691041808</v>
       </c>
-      <c r="I21" s="29"/>
-      <c r="J21" s="29"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="B24" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="C24" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="D24" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="E24" s="12" t="s">
+      <c r="I23" s="36"/>
+      <c r="J23" s="36"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="D26" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="E26" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B25" s="34" t="s">
-        <v>44</v>
-      </c>
-      <c r="C25" s="35" t="s">
-        <v>45</v>
-      </c>
-      <c r="D25" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" s="10" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="B26" s="34" t="s">
-        <v>48</v>
-      </c>
-      <c r="C26" s="35" t="s">
-        <v>49</v>
-      </c>
-      <c r="D26" s="36" t="n">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="E26" s="10" t="str">
+      <c r="B27" s="41" t="s">
+        <v>51</v>
+      </c>
+      <c r="C27" s="42" t="s">
+        <v>52</v>
+      </c>
+      <c r="D27" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="9" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B28" s="41" t="s">
+        <v>55</v>
+      </c>
+      <c r="C28" s="42" t="s">
+        <v>56</v>
+      </c>
+      <c r="D28" s="43" t="n">
+        <v>50</v>
+      </c>
+      <c r="E28" s="9" t="str">
         <f aca="false">IF('MLB Jul 12'!I14="Win","HIT",IF('MLB Jul 12'!I14="Loss","MISS","Pending"))</f>
         <v>MISS</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="B27" s="34" t="s">
-        <v>51</v>
-      </c>
-      <c r="C27" s="35" t="s">
-        <v>52</v>
-      </c>
-      <c r="D27" s="36" t="n">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B29" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="C29" s="42" t="s">
+        <v>59</v>
+      </c>
+      <c r="D29" s="43" t="n">
         <v>40</v>
       </c>
-      <c r="E27" s="10" t="str">
+      <c r="E29" s="9" t="str">
         <f aca="false">IF('NASCAR Jul 12'!I13="Win","HIT",IF('NASCAR Jul 12'!I13="Loss","MISS","Pending"))</f>
         <v>Pending</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="B28" s="34" t="s">
-        <v>54</v>
-      </c>
-      <c r="C28" s="35" t="s">
-        <v>55</v>
-      </c>
-      <c r="D28" s="36" t="n">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B30" s="41" t="s">
+        <v>61</v>
+      </c>
+      <c r="C30" s="42" t="s">
+        <v>62</v>
+      </c>
+      <c r="D30" s="43" t="n">
         <v>100</v>
       </c>
-      <c r="E28" s="10" t="str">
+      <c r="E30" s="9" t="str">
         <f aca="false">IF('WNBA Jul 12'!I13="Win","HIT",IF('WNBA Jul 12'!I13="Loss","MISS","Pending"))</f>
         <v>Pending</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="30" t="s">
-        <v>56</v>
-      </c>
-      <c r="B29" s="29"/>
-      <c r="C29" s="29"/>
-      <c r="D29" s="29"/>
-      <c r="E29" s="37" t="str">
-        <f aca="false">IF(COUNTIF(E25:E28,"HIT")+COUNTIF(E25:E28,"MISS")=0,"—",COUNTIF(E25:E28,"HIT")&amp;"-for-"&amp;(COUNTIF(E25:E28,"HIT")+COUNTIF(E25:E28,"MISS"))&amp;" ("&amp;TEXT(COUNTIF(E25:E28,"HIT")/(COUNTIF(E25:E28,"HIT")+COUNTIF(E25:E28,"MISS")),"0%")&amp;")")</f>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B31" s="41" t="s">
+        <v>64</v>
+      </c>
+      <c r="C31" s="42" t="s">
+        <v>65</v>
+      </c>
+      <c r="D31" s="43" t="n">
+        <v>50</v>
+      </c>
+      <c r="E31" s="9" t="str">
+        <f aca="false">IF('The Open'!I12="Win","HIT",IF('The Open'!I12="Loss","MISS","Pending"))</f>
+        <v>Pending</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B32" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="C32" s="42" t="s">
+        <v>68</v>
+      </c>
+      <c r="D32" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="9" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="37" t="s">
+        <v>70</v>
+      </c>
+      <c r="B33" s="36"/>
+      <c r="C33" s="36"/>
+      <c r="D33" s="36"/>
+      <c r="E33" s="44" t="str">
+        <f aca="false">IF(COUNTIF(E27:E32,"HIT")+COUNTIF(E27:E32,"MISS")=0,"—",COUNTIF(E27:E32,"HIT")&amp;"-for-"&amp;(COUNTIF(E27:E32,"HIT")+COUNTIF(E27:E32,"MISS"))&amp;" ("&amp;TEXT(COUNTIF(E27:E32,"HIT")/(COUNTIF(E27:E32,"HIT")+COUNTIF(E27:E32,"MISS")),"0%")&amp;")")</f>
         <v>0-for-2 (0%)</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="38" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="38" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="38" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="38" t="s">
-        <v>60</v>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="45" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="45" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="45" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="45" t="s">
+        <v>74</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="H16:H21">
+  <conditionalFormatting sqref="H16:H23">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>AND(ISNUMBER(H16),H16&gt;0)</formula>
     </cfRule>
@@ -2497,7 +2874,7 @@
       <formula>AND(ISNUMBER(H16),H16&lt;0)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I16:I20">
+  <conditionalFormatting sqref="I16:I22">
     <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>AND(ISNUMBER(I16),I16&gt;5000)</formula>
     </cfRule>
@@ -2540,757 +2917,757 @@
   <dimension ref="A1:L41"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="9" style="1" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="46" width="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="46" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="46" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="46" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="46" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="46" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="46" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="46" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="9" style="46" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="46" width="40"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="39" t="s">
-        <v>61</v>
-      </c>
-      <c r="H1" s="40" t="s">
-        <v>62</v>
+      <c r="A1" s="47" t="s">
+        <v>75</v>
+      </c>
+      <c r="H1" s="48" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
-        <v>63</v>
+      <c r="A2" s="49" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
-        <v>64</v>
+      <c r="A3" s="49" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
-        <v>65</v>
+      <c r="A5" s="50" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="C6" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="D6" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="E6" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="F6" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="G6" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="H6" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="I6" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="J6" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="K6" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="L6" s="12" t="s">
-        <v>75</v>
+      <c r="B6" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="G6" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="I6" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="J6" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="K6" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="L6" s="11" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="41" t="n">
+      <c r="A7" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="42" t="s">
-        <v>76</v>
-      </c>
-      <c r="C7" s="43" t="s">
-        <v>77</v>
-      </c>
-      <c r="D7" s="41" t="s">
-        <v>78</v>
-      </c>
-      <c r="E7" s="44" t="n">
+      <c r="B7" s="52" t="s">
+        <v>90</v>
+      </c>
+      <c r="C7" s="53" t="s">
+        <v>91</v>
+      </c>
+      <c r="D7" s="51" t="s">
+        <v>92</v>
+      </c>
+      <c r="E7" s="54" t="n">
         <v>-265</v>
       </c>
-      <c r="F7" s="36" t="n">
+      <c r="F7" s="55" t="n">
         <v>265</v>
       </c>
-      <c r="G7" s="45" t="n">
+      <c r="G7" s="56" t="n">
         <f aca="false">IF(E7&gt;0,F7*E7/100,F7*100/ABS(E7))</f>
         <v>100</v>
       </c>
-      <c r="H7" s="45" t="n">
+      <c r="H7" s="56" t="n">
         <f aca="false">F7+G7</f>
         <v>365</v>
       </c>
-      <c r="I7" s="46" t="s">
-        <v>79</v>
-      </c>
-      <c r="J7" s="45" t="n">
+      <c r="I7" s="57" t="s">
+        <v>93</v>
+      </c>
+      <c r="J7" s="56" t="n">
         <f aca="false">IF(I7="Win",F7+G7,IF(I7="Push",F7,IF(I7="Loss",0,0)))</f>
         <v>365</v>
       </c>
-      <c r="K7" s="47" t="n">
+      <c r="K7" s="58" t="n">
         <f aca="false">IF(I7="Pending",0,J7-F7)</f>
         <v>100</v>
       </c>
-      <c r="L7" s="48" t="s">
-        <v>80</v>
+      <c r="L7" s="59" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="41" t="n">
+      <c r="A8" s="51" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="42" t="s">
-        <v>81</v>
-      </c>
-      <c r="C8" s="43" t="s">
-        <v>82</v>
-      </c>
-      <c r="D8" s="41" t="s">
-        <v>83</v>
-      </c>
-      <c r="E8" s="44" t="n">
+      <c r="B8" s="52" t="s">
+        <v>95</v>
+      </c>
+      <c r="C8" s="53" t="s">
+        <v>96</v>
+      </c>
+      <c r="D8" s="51" t="s">
+        <v>97</v>
+      </c>
+      <c r="E8" s="54" t="n">
         <v>-140</v>
       </c>
-      <c r="F8" s="36" t="n">
+      <c r="F8" s="55" t="n">
         <v>200</v>
       </c>
-      <c r="G8" s="45" t="n">
+      <c r="G8" s="56" t="n">
         <f aca="false">IF(E8&gt;0,F8*E8/100,F8*100/ABS(E8))</f>
         <v>142.857142857143</v>
       </c>
-      <c r="H8" s="45" t="n">
+      <c r="H8" s="56" t="n">
         <f aca="false">F8+G8</f>
         <v>342.857142857143</v>
       </c>
-      <c r="I8" s="46" t="s">
-        <v>79</v>
-      </c>
-      <c r="J8" s="45" t="n">
+      <c r="I8" s="57" t="s">
+        <v>93</v>
+      </c>
+      <c r="J8" s="56" t="n">
         <f aca="false">IF(I8="Win",F8+G8,IF(I8="Push",F8,IF(I8="Loss",0,0)))</f>
         <v>342.857142857143</v>
       </c>
-      <c r="K8" s="47" t="n">
+      <c r="K8" s="58" t="n">
         <f aca="false">IF(I8="Pending",0,J8-F8)</f>
         <v>142.857142857143</v>
       </c>
-      <c r="L8" s="48" t="s">
-        <v>84</v>
+      <c r="L8" s="59" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="41" t="n">
+      <c r="A9" s="51" t="n">
         <v>3</v>
       </c>
-      <c r="B9" s="42" t="s">
-        <v>85</v>
-      </c>
-      <c r="C9" s="43" t="s">
-        <v>86</v>
-      </c>
-      <c r="D9" s="41" t="s">
-        <v>78</v>
-      </c>
-      <c r="E9" s="44" t="n">
+      <c r="B9" s="52" t="s">
+        <v>99</v>
+      </c>
+      <c r="C9" s="53" t="s">
+        <v>100</v>
+      </c>
+      <c r="D9" s="51" t="s">
+        <v>92</v>
+      </c>
+      <c r="E9" s="54" t="n">
         <v>-148</v>
       </c>
-      <c r="F9" s="36" t="n">
+      <c r="F9" s="55" t="n">
         <v>148</v>
       </c>
-      <c r="G9" s="45" t="n">
+      <c r="G9" s="56" t="n">
         <f aca="false">IF(E9&gt;0,F9*E9/100,F9*100/ABS(E9))</f>
         <v>100</v>
       </c>
-      <c r="H9" s="45" t="n">
+      <c r="H9" s="56" t="n">
         <f aca="false">F9+G9</f>
         <v>248</v>
       </c>
-      <c r="I9" s="49" t="s">
-        <v>87</v>
-      </c>
-      <c r="J9" s="45" t="n">
+      <c r="I9" s="60" t="s">
+        <v>101</v>
+      </c>
+      <c r="J9" s="56" t="n">
         <f aca="false">IF(I9="Win",F9+G9,IF(I9="Push",F9,IF(I9="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K9" s="47" t="n">
+      <c r="K9" s="58" t="n">
         <f aca="false">IF(I9="Pending",0,J9-F9)</f>
         <v>-148</v>
       </c>
-      <c r="L9" s="48" t="s">
-        <v>88</v>
+      <c r="L9" s="59" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="41" t="n">
+      <c r="A10" s="51" t="n">
         <v>4</v>
       </c>
-      <c r="B10" s="42" t="s">
-        <v>89</v>
-      </c>
-      <c r="C10" s="43" t="s">
-        <v>90</v>
-      </c>
-      <c r="D10" s="41" t="s">
-        <v>78</v>
-      </c>
-      <c r="E10" s="44" t="n">
+      <c r="B10" s="52" t="s">
+        <v>103</v>
+      </c>
+      <c r="C10" s="53" t="s">
+        <v>104</v>
+      </c>
+      <c r="D10" s="51" t="s">
+        <v>92</v>
+      </c>
+      <c r="E10" s="54" t="n">
         <v>114</v>
       </c>
-      <c r="F10" s="36" t="n">
+      <c r="F10" s="55" t="n">
         <v>100</v>
       </c>
-      <c r="G10" s="45" t="n">
+      <c r="G10" s="56" t="n">
         <f aca="false">IF(E10&gt;0,F10*E10/100,F10*100/ABS(E10))</f>
         <v>114</v>
       </c>
-      <c r="H10" s="45" t="n">
+      <c r="H10" s="56" t="n">
         <f aca="false">F10+G10</f>
         <v>214</v>
       </c>
-      <c r="I10" s="46" t="s">
-        <v>79</v>
-      </c>
-      <c r="J10" s="45" t="n">
+      <c r="I10" s="57" t="s">
+        <v>93</v>
+      </c>
+      <c r="J10" s="56" t="n">
         <f aca="false">IF(I10="Win",F10+G10,IF(I10="Push",F10,IF(I10="Loss",0,0)))</f>
         <v>214</v>
       </c>
-      <c r="K10" s="47" t="n">
+      <c r="K10" s="58" t="n">
         <f aca="false">IF(I10="Pending",0,J10-F10)</f>
         <v>114</v>
       </c>
-      <c r="L10" s="48" t="s">
-        <v>91</v>
+      <c r="L10" s="59" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="41" t="n">
+      <c r="A11" s="51" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="42" t="s">
+      <c r="B11" s="52" t="s">
+        <v>106</v>
+      </c>
+      <c r="C11" s="53" t="s">
+        <v>107</v>
+      </c>
+      <c r="D11" s="51" t="s">
         <v>92</v>
       </c>
-      <c r="C11" s="43" t="s">
-        <v>93</v>
-      </c>
-      <c r="D11" s="41" t="s">
-        <v>78</v>
-      </c>
-      <c r="E11" s="44" t="n">
+      <c r="E11" s="54" t="n">
         <v>-218</v>
       </c>
-      <c r="F11" s="36" t="n">
+      <c r="F11" s="55" t="n">
         <v>100</v>
       </c>
-      <c r="G11" s="45" t="n">
+      <c r="G11" s="56" t="n">
         <f aca="false">IF(E11&gt;0,F11*E11/100,F11*100/ABS(E11))</f>
         <v>45.8715596330275</v>
       </c>
-      <c r="H11" s="45" t="n">
+      <c r="H11" s="56" t="n">
         <f aca="false">F11+G11</f>
         <v>145.871559633028</v>
       </c>
-      <c r="I11" s="49" t="s">
-        <v>87</v>
-      </c>
-      <c r="J11" s="45" t="n">
+      <c r="I11" s="60" t="s">
+        <v>101</v>
+      </c>
+      <c r="J11" s="56" t="n">
         <f aca="false">IF(I11="Win",F11+G11,IF(I11="Push",F11,IF(I11="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K11" s="47" t="n">
+      <c r="K11" s="58" t="n">
         <f aca="false">IF(I11="Pending",0,J11-F11)</f>
         <v>-100</v>
       </c>
-      <c r="L11" s="48" t="s">
-        <v>94</v>
+      <c r="L11" s="59" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="41" t="n">
+      <c r="A12" s="51" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="42" t="s">
-        <v>95</v>
-      </c>
-      <c r="C12" s="43" t="s">
-        <v>96</v>
-      </c>
-      <c r="D12" s="41" t="s">
-        <v>78</v>
-      </c>
-      <c r="E12" s="44" t="n">
+      <c r="B12" s="52" t="s">
+        <v>109</v>
+      </c>
+      <c r="C12" s="53" t="s">
+        <v>110</v>
+      </c>
+      <c r="D12" s="51" t="s">
+        <v>92</v>
+      </c>
+      <c r="E12" s="54" t="n">
         <v>-125</v>
       </c>
-      <c r="F12" s="36" t="n">
+      <c r="F12" s="55" t="n">
         <v>75</v>
       </c>
-      <c r="G12" s="45" t="n">
+      <c r="G12" s="56" t="n">
         <f aca="false">IF(E12&gt;0,F12*E12/100,F12*100/ABS(E12))</f>
         <v>60</v>
       </c>
-      <c r="H12" s="45" t="n">
+      <c r="H12" s="56" t="n">
         <f aca="false">F12+G12</f>
         <v>135</v>
       </c>
-      <c r="I12" s="46" t="s">
-        <v>79</v>
-      </c>
-      <c r="J12" s="45" t="n">
+      <c r="I12" s="57" t="s">
+        <v>93</v>
+      </c>
+      <c r="J12" s="56" t="n">
         <f aca="false">IF(I12="Win",F12+G12,IF(I12="Push",F12,IF(I12="Loss",0,0)))</f>
         <v>135</v>
       </c>
-      <c r="K12" s="47" t="n">
+      <c r="K12" s="58" t="n">
         <f aca="false">IF(I12="Pending",0,J12-F12)</f>
         <v>60</v>
       </c>
-      <c r="L12" s="48" t="s">
-        <v>97</v>
+      <c r="L12" s="59" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="41" t="n">
+      <c r="A13" s="51" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="42" t="s">
-        <v>98</v>
-      </c>
-      <c r="C13" s="43" t="s">
-        <v>99</v>
-      </c>
-      <c r="D13" s="41" t="s">
-        <v>78</v>
-      </c>
-      <c r="E13" s="44" t="n">
+      <c r="B13" s="52" t="s">
+        <v>112</v>
+      </c>
+      <c r="C13" s="53" t="s">
+        <v>113</v>
+      </c>
+      <c r="D13" s="51" t="s">
+        <v>92</v>
+      </c>
+      <c r="E13" s="54" t="n">
         <v>-225</v>
       </c>
-      <c r="F13" s="36" t="n">
+      <c r="F13" s="55" t="n">
         <v>50</v>
       </c>
-      <c r="G13" s="45" t="n">
+      <c r="G13" s="56" t="n">
         <f aca="false">IF(E13&gt;0,F13*E13/100,F13*100/ABS(E13))</f>
         <v>22.2222222222222</v>
       </c>
-      <c r="H13" s="45" t="n">
+      <c r="H13" s="56" t="n">
         <f aca="false">F13+G13</f>
         <v>72.2222222222222</v>
       </c>
-      <c r="I13" s="46" t="s">
-        <v>79</v>
-      </c>
-      <c r="J13" s="45" t="n">
+      <c r="I13" s="57" t="s">
+        <v>93</v>
+      </c>
+      <c r="J13" s="56" t="n">
         <f aca="false">IF(I13="Win",F13+G13,IF(I13="Push",F13,IF(I13="Loss",0,0)))</f>
         <v>72.2222222222222</v>
       </c>
-      <c r="K13" s="47" t="n">
+      <c r="K13" s="58" t="n">
         <f aca="false">IF(I13="Pending",0,J13-F13)</f>
         <v>22.2222222222222</v>
       </c>
-      <c r="L13" s="48" t="s">
-        <v>100</v>
+      <c r="L13" s="59" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="41" t="n">
+      <c r="A14" s="51" t="n">
         <v>8</v>
       </c>
-      <c r="B14" s="42" t="s">
-        <v>101</v>
-      </c>
-      <c r="C14" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="D14" s="41" t="s">
-        <v>78</v>
-      </c>
-      <c r="E14" s="44" t="n">
+      <c r="B14" s="52" t="s">
+        <v>115</v>
+      </c>
+      <c r="C14" s="53" t="s">
+        <v>116</v>
+      </c>
+      <c r="D14" s="51" t="s">
+        <v>92</v>
+      </c>
+      <c r="E14" s="54" t="n">
         <v>-258</v>
       </c>
-      <c r="F14" s="36" t="n">
+      <c r="F14" s="55" t="n">
         <v>62</v>
       </c>
-      <c r="G14" s="45" t="n">
+      <c r="G14" s="56" t="n">
         <f aca="false">IF(E14&gt;0,F14*E14/100,F14*100/ABS(E14))</f>
         <v>24.031007751938</v>
       </c>
-      <c r="H14" s="45" t="n">
+      <c r="H14" s="56" t="n">
         <f aca="false">F14+G14</f>
         <v>86.031007751938</v>
       </c>
-      <c r="I14" s="46" t="s">
-        <v>79</v>
-      </c>
-      <c r="J14" s="45" t="n">
+      <c r="I14" s="57" t="s">
+        <v>93</v>
+      </c>
+      <c r="J14" s="56" t="n">
         <f aca="false">IF(I14="Win",F14+G14,IF(I14="Push",F14,IF(I14="Loss",0,0)))</f>
         <v>86.031007751938</v>
       </c>
-      <c r="K14" s="47" t="n">
+      <c r="K14" s="58" t="n">
         <f aca="false">IF(I14="Pending",0,J14-F14)</f>
         <v>24.031007751938</v>
       </c>
-      <c r="L14" s="48" t="s">
-        <v>103</v>
+      <c r="L14" s="59" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="41" t="n">
+      <c r="A15" s="51" t="n">
         <v>9</v>
       </c>
-      <c r="B15" s="42" t="s">
-        <v>104</v>
-      </c>
-      <c r="C15" s="43" t="s">
-        <v>105</v>
-      </c>
-      <c r="D15" s="41" t="s">
-        <v>106</v>
-      </c>
-      <c r="E15" s="44" t="n">
+      <c r="B15" s="52" t="s">
+        <v>118</v>
+      </c>
+      <c r="C15" s="53" t="s">
+        <v>119</v>
+      </c>
+      <c r="D15" s="51" t="s">
+        <v>120</v>
+      </c>
+      <c r="E15" s="54" t="n">
         <v>443</v>
       </c>
-      <c r="F15" s="36" t="n">
+      <c r="F15" s="55" t="n">
         <v>50</v>
       </c>
-      <c r="G15" s="45" t="n">
+      <c r="G15" s="56" t="n">
         <f aca="false">IF(E15&gt;0,F15*E15/100,F15*100/ABS(E15))</f>
         <v>221.5</v>
       </c>
-      <c r="H15" s="45" t="n">
+      <c r="H15" s="56" t="n">
         <f aca="false">F15+G15</f>
         <v>271.5</v>
       </c>
-      <c r="I15" s="49" t="s">
-        <v>87</v>
-      </c>
-      <c r="J15" s="45" t="n">
+      <c r="I15" s="60" t="s">
+        <v>101</v>
+      </c>
+      <c r="J15" s="56" t="n">
         <f aca="false">IF(I15="Win",F15+G15,IF(I15="Push",F15,IF(I15="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K15" s="47" t="n">
+      <c r="K15" s="58" t="n">
         <f aca="false">IF(I15="Pending",0,J15-F15)</f>
         <v>-50</v>
       </c>
-      <c r="L15" s="48" t="s">
-        <v>107</v>
+      <c r="L15" s="59" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="50"/>
-      <c r="B16" s="51" t="s">
-        <v>37</v>
-      </c>
-      <c r="C16" s="50"/>
-      <c r="D16" s="50"/>
-      <c r="E16" s="50"/>
-      <c r="F16" s="31" t="n">
+      <c r="A16" s="61"/>
+      <c r="B16" s="62" t="s">
+        <v>44</v>
+      </c>
+      <c r="C16" s="61"/>
+      <c r="D16" s="61"/>
+      <c r="E16" s="61"/>
+      <c r="F16" s="63" t="n">
         <f aca="false">SUM(F7:F15)</f>
         <v>1050</v>
       </c>
-      <c r="G16" s="32" t="n">
+      <c r="G16" s="64" t="n">
         <f aca="false">SUM(G7:G15)</f>
         <v>830.481932464331</v>
       </c>
-      <c r="H16" s="32" t="n">
+      <c r="H16" s="64" t="n">
         <f aca="false">SUM(H7:H15)</f>
         <v>1880.48193246433</v>
       </c>
-      <c r="I16" s="50"/>
-      <c r="J16" s="32" t="n">
+      <c r="I16" s="61"/>
+      <c r="J16" s="64" t="n">
         <f aca="false">SUM(J7:J15)</f>
         <v>1215.1103728313</v>
       </c>
-      <c r="K16" s="33" t="n">
+      <c r="K16" s="65" t="n">
         <f aca="false">SUM(K7:K15)</f>
         <v>165.110372831303</v>
       </c>
-      <c r="L16" s="50"/>
+      <c r="L16" s="61"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="4" t="s">
-        <v>108</v>
+      <c r="B18" s="50" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="42" t="s">
-        <v>109</v>
-      </c>
-      <c r="C19" s="52" t="n">
+      <c r="B19" s="52" t="s">
+        <v>123</v>
+      </c>
+      <c r="C19" s="66" t="n">
         <f aca="false">COUNTIF(I7:I15,"Win")</f>
         <v>6</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="42" t="s">
-        <v>110</v>
-      </c>
-      <c r="C20" s="52" t="n">
+      <c r="B20" s="52" t="s">
+        <v>124</v>
+      </c>
+      <c r="C20" s="66" t="n">
         <f aca="false">COUNTIF(I7:I15,"Loss")</f>
         <v>3</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="42" t="s">
-        <v>111</v>
-      </c>
-      <c r="C21" s="52" t="n">
+      <c r="B21" s="52" t="s">
+        <v>125</v>
+      </c>
+      <c r="C21" s="66" t="n">
         <f aca="false">COUNTIF(I7:I15,"Push")</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="42" t="s">
-        <v>112</v>
-      </c>
-      <c r="C22" s="52" t="n">
+      <c r="B22" s="52" t="s">
+        <v>126</v>
+      </c>
+      <c r="C22" s="66" t="n">
         <f aca="false">COUNTIF(I7:I15,"Pending")</f>
         <v>0</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="42" t="s">
-        <v>113</v>
-      </c>
-      <c r="C23" s="53" t="n">
+      <c r="B23" s="52" t="s">
+        <v>127</v>
+      </c>
+      <c r="C23" s="67" t="n">
         <f aca="false">IF(COUNTIF(I7:I15,"Win")+COUNTIF(I7:I15,"Loss")=0,"—",COUNTIF(I7:I15,"Win")/(COUNTIF(I7:I15,"Win")+COUNTIF(I7:I15,"Loss")))</f>
         <v>0.666666666666667</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="42" t="s">
-        <v>114</v>
-      </c>
-      <c r="C24" s="54" t="n">
+      <c r="B24" s="52" t="s">
+        <v>128</v>
+      </c>
+      <c r="C24" s="68" t="n">
         <f aca="false">SUM(F7:F15)</f>
         <v>1050</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="42" t="s">
-        <v>115</v>
-      </c>
-      <c r="C25" s="45" t="n">
+      <c r="B25" s="52" t="s">
+        <v>129</v>
+      </c>
+      <c r="C25" s="56" t="n">
         <f aca="false">SUM(J7:J15)</f>
         <v>1215.1103728313</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="42" t="s">
-        <v>116</v>
-      </c>
-      <c r="C26" s="47" t="n">
+      <c r="B26" s="52" t="s">
+        <v>130</v>
+      </c>
+      <c r="C26" s="58" t="n">
         <f aca="false">SUM(K7:K15)</f>
         <v>165.110372831303</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="42" t="s">
-        <v>117</v>
-      </c>
-      <c r="C27" s="53" t="n">
+      <c r="B27" s="52" t="s">
+        <v>131</v>
+      </c>
+      <c r="C27" s="67" t="n">
         <f aca="false">IF(SUM(F7:F15)=0,"—",SUM(K7:K15)/SUM(F7:F15))</f>
         <v>0.157247974125051</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="42" t="s">
-        <v>118</v>
-      </c>
-      <c r="C28" s="45" t="n">
+      <c r="B28" s="52" t="s">
+        <v>132</v>
+      </c>
+      <c r="C28" s="56" t="n">
         <f aca="false">SUM(H7:H15)</f>
         <v>1880.48193246433</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="4" t="s">
-        <v>119</v>
+      <c r="A30" s="50" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="12" t="s">
+      <c r="A31" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="B31" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="C31" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="D31" s="12" t="s">
-        <v>122</v>
-      </c>
-      <c r="E31" s="12" t="s">
-        <v>123</v>
-      </c>
-      <c r="F31" s="12" t="s">
-        <v>124</v>
+      <c r="B31" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="C31" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="D31" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="E31" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="F31" s="11" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="41" t="n">
+      <c r="A32" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="B32" s="42" t="s">
-        <v>125</v>
-      </c>
-      <c r="C32" s="48" t="s">
-        <v>126</v>
-      </c>
-      <c r="D32" s="35" t="s">
-        <v>127</v>
-      </c>
-      <c r="E32" s="55" t="s">
-        <v>128</v>
-      </c>
-      <c r="F32" s="55" t="s">
-        <v>129</v>
+      <c r="B32" s="52" t="s">
+        <v>139</v>
+      </c>
+      <c r="C32" s="59" t="s">
+        <v>140</v>
+      </c>
+      <c r="D32" s="42" t="s">
+        <v>141</v>
+      </c>
+      <c r="E32" s="69" t="s">
+        <v>142</v>
+      </c>
+      <c r="F32" s="69" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="41" t="n">
+      <c r="A33" s="51" t="n">
         <v>2</v>
       </c>
-      <c r="B33" s="42" t="s">
-        <v>130</v>
-      </c>
-      <c r="C33" s="48" t="s">
-        <v>131</v>
-      </c>
-      <c r="D33" s="35" t="s">
-        <v>132</v>
-      </c>
-      <c r="E33" s="55" t="s">
-        <v>133</v>
-      </c>
-      <c r="F33" s="55" t="s">
-        <v>134</v>
+      <c r="B33" s="52" t="s">
+        <v>144</v>
+      </c>
+      <c r="C33" s="59" t="s">
+        <v>145</v>
+      </c>
+      <c r="D33" s="42" t="s">
+        <v>146</v>
+      </c>
+      <c r="E33" s="69" t="s">
+        <v>147</v>
+      </c>
+      <c r="F33" s="69" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="41" t="n">
+      <c r="A34" s="51" t="n">
         <v>3</v>
       </c>
-      <c r="B34" s="42" t="s">
-        <v>135</v>
-      </c>
-      <c r="C34" s="48" t="s">
-        <v>136</v>
-      </c>
-      <c r="D34" s="35" t="s">
-        <v>137</v>
-      </c>
-      <c r="E34" s="55" t="s">
-        <v>138</v>
-      </c>
-      <c r="F34" s="55" t="s">
-        <v>139</v>
+      <c r="B34" s="52" t="s">
+        <v>149</v>
+      </c>
+      <c r="C34" s="59" t="s">
+        <v>150</v>
+      </c>
+      <c r="D34" s="42" t="s">
+        <v>151</v>
+      </c>
+      <c r="E34" s="69" t="s">
+        <v>152</v>
+      </c>
+      <c r="F34" s="69" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="41" t="n">
+      <c r="A35" s="51" t="n">
         <v>4</v>
       </c>
-      <c r="B35" s="42" t="s">
-        <v>140</v>
-      </c>
-      <c r="C35" s="48" t="s">
-        <v>141</v>
-      </c>
-      <c r="D35" s="35" t="s">
-        <v>142</v>
-      </c>
-      <c r="E35" s="55" t="s">
-        <v>143</v>
-      </c>
-      <c r="F35" s="55" t="s">
-        <v>144</v>
+      <c r="B35" s="52" t="s">
+        <v>154</v>
+      </c>
+      <c r="C35" s="59" t="s">
+        <v>155</v>
+      </c>
+      <c r="D35" s="42" t="s">
+        <v>156</v>
+      </c>
+      <c r="E35" s="69" t="s">
+        <v>157</v>
+      </c>
+      <c r="F35" s="69" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="41" t="n">
+      <c r="A36" s="51" t="n">
         <v>5</v>
       </c>
-      <c r="B36" s="42" t="s">
-        <v>145</v>
-      </c>
-      <c r="C36" s="48" t="s">
-        <v>146</v>
-      </c>
-      <c r="D36" s="35" t="s">
-        <v>147</v>
-      </c>
-      <c r="E36" s="55" t="s">
-        <v>148</v>
-      </c>
-      <c r="F36" s="55" t="s">
-        <v>149</v>
+      <c r="B36" s="52" t="s">
+        <v>159</v>
+      </c>
+      <c r="C36" s="59" t="s">
+        <v>160</v>
+      </c>
+      <c r="D36" s="42" t="s">
+        <v>161</v>
+      </c>
+      <c r="E36" s="69" t="s">
+        <v>162</v>
+      </c>
+      <c r="F36" s="69" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="41" t="n">
+      <c r="A37" s="51" t="n">
         <v>6</v>
       </c>
-      <c r="B37" s="42" t="s">
-        <v>150</v>
-      </c>
-      <c r="C37" s="48" t="s">
-        <v>151</v>
-      </c>
-      <c r="D37" s="35" t="s">
-        <v>45</v>
-      </c>
-      <c r="E37" s="55" t="s">
-        <v>152</v>
-      </c>
-      <c r="F37" s="55" t="s">
-        <v>153</v>
+      <c r="B37" s="52" t="s">
+        <v>164</v>
+      </c>
+      <c r="C37" s="59" t="s">
+        <v>165</v>
+      </c>
+      <c r="D37" s="42" t="s">
+        <v>52</v>
+      </c>
+      <c r="E37" s="69" t="s">
+        <v>166</v>
+      </c>
+      <c r="F37" s="69" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="38" t="s">
-        <v>154</v>
+      <c r="A39" s="70" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="38" t="s">
-        <v>155</v>
+      <c r="A40" s="70" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="38" t="s">
-        <v>156</v>
+      <c r="A41" s="70" t="s">
+        <v>170</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="K7:K16">
-    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>AND(ISNUMBER(K7),K7&gt;0)</formula>
     </cfRule>
-    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>AND(ISNUMBER(K7),K7&lt;0)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C26:C27">
-    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>AND(ISNUMBER(C26),C26&gt;0)</formula>
     </cfRule>
-    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>AND(ISNUMBER(C26),C26&lt;0)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3319,606 +3696,606 @@
   <dimension ref="A1:L35"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="9" style="1" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="46" width="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="46" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="46" width="42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="46" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="46" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="46" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="46" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="9" style="46" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="46" width="44"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="39" t="s">
-        <v>157</v>
-      </c>
-      <c r="H1" s="56" t="s">
-        <v>158</v>
+      <c r="A1" s="47" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1" s="71" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
-        <v>159</v>
+      <c r="A2" s="49" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
-        <v>160</v>
+      <c r="A3" s="49" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
-        <v>65</v>
+      <c r="A5" s="50" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="C6" s="12" t="s">
-        <v>161</v>
-      </c>
-      <c r="D6" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="E6" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="F6" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="G6" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="H6" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="I6" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="J6" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="K6" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="L6" s="12" t="s">
-        <v>75</v>
+      <c r="B6" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="G6" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="I6" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="J6" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="K6" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="L6" s="11" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="41" t="n">
+      <c r="A7" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="42" t="s">
-        <v>162</v>
-      </c>
-      <c r="C7" s="43" t="s">
-        <v>163</v>
-      </c>
-      <c r="D7" s="41" t="s">
-        <v>164</v>
-      </c>
-      <c r="E7" s="44" t="n">
+      <c r="B7" s="52" t="s">
+        <v>176</v>
+      </c>
+      <c r="C7" s="53" t="s">
+        <v>177</v>
+      </c>
+      <c r="D7" s="51" t="s">
+        <v>178</v>
+      </c>
+      <c r="E7" s="54" t="n">
         <v>-144</v>
       </c>
-      <c r="F7" s="36" t="n">
+      <c r="F7" s="55" t="n">
         <v>300</v>
       </c>
-      <c r="G7" s="45" t="n">
+      <c r="G7" s="56" t="n">
         <f aca="false">IF(E7&gt;0,F7*E7/100,F7*100/ABS(E7))</f>
         <v>208.333333333333</v>
       </c>
-      <c r="H7" s="45" t="n">
+      <c r="H7" s="56" t="n">
         <f aca="false">F7+G7</f>
         <v>508.333333333333</v>
       </c>
-      <c r="I7" s="57" t="s">
-        <v>112</v>
-      </c>
-      <c r="J7" s="45" t="n">
+      <c r="I7" s="72" t="s">
+        <v>126</v>
+      </c>
+      <c r="J7" s="56" t="n">
         <f aca="false">IF(I7="Win",F7+G7,IF(I7="Push",F7,IF(I7="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K7" s="47" t="n">
+      <c r="K7" s="58" t="n">
         <f aca="false">IF(I7="Pending",0,J7-F7)</f>
         <v>0</v>
       </c>
-      <c r="L7" s="48" t="s">
-        <v>165</v>
+      <c r="L7" s="59" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="41" t="n">
+      <c r="A8" s="51" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="42" t="s">
-        <v>166</v>
-      </c>
-      <c r="C8" s="43" t="s">
-        <v>167</v>
-      </c>
-      <c r="D8" s="41" t="s">
-        <v>168</v>
-      </c>
-      <c r="E8" s="44" t="n">
+      <c r="B8" s="52" t="s">
+        <v>180</v>
+      </c>
+      <c r="C8" s="53" t="s">
+        <v>181</v>
+      </c>
+      <c r="D8" s="51" t="s">
+        <v>182</v>
+      </c>
+      <c r="E8" s="54" t="n">
         <v>-122</v>
       </c>
-      <c r="F8" s="36" t="n">
+      <c r="F8" s="55" t="n">
         <v>120</v>
       </c>
-      <c r="G8" s="45" t="n">
+      <c r="G8" s="56" t="n">
         <f aca="false">IF(E8&gt;0,F8*E8/100,F8*100/ABS(E8))</f>
         <v>98.3606557377049</v>
       </c>
-      <c r="H8" s="45" t="n">
+      <c r="H8" s="56" t="n">
         <f aca="false">F8+G8</f>
         <v>218.360655737705</v>
       </c>
-      <c r="I8" s="57" t="s">
-        <v>112</v>
-      </c>
-      <c r="J8" s="45" t="n">
+      <c r="I8" s="72" t="s">
+        <v>126</v>
+      </c>
+      <c r="J8" s="56" t="n">
         <f aca="false">IF(I8="Win",F8+G8,IF(I8="Push",F8,IF(I8="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K8" s="47" t="n">
+      <c r="K8" s="58" t="n">
         <f aca="false">IF(I8="Pending",0,J8-F8)</f>
         <v>0</v>
       </c>
-      <c r="L8" s="48" t="s">
-        <v>169</v>
+      <c r="L8" s="59" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="41" t="n">
+      <c r="A9" s="51" t="n">
         <v>3</v>
       </c>
-      <c r="B9" s="42" t="s">
-        <v>170</v>
-      </c>
-      <c r="C9" s="43" t="s">
-        <v>171</v>
-      </c>
-      <c r="D9" s="41" t="s">
-        <v>172</v>
-      </c>
-      <c r="E9" s="44" t="n">
+      <c r="B9" s="52" t="s">
+        <v>184</v>
+      </c>
+      <c r="C9" s="53" t="s">
+        <v>185</v>
+      </c>
+      <c r="D9" s="51" t="s">
+        <v>186</v>
+      </c>
+      <c r="E9" s="54" t="n">
         <v>175</v>
       </c>
-      <c r="F9" s="36" t="n">
+      <c r="F9" s="55" t="n">
         <v>150</v>
       </c>
-      <c r="G9" s="45" t="n">
+      <c r="G9" s="56" t="n">
         <f aca="false">IF(E9&gt;0,F9*E9/100,F9*100/ABS(E9))</f>
         <v>262.5</v>
       </c>
-      <c r="H9" s="45" t="n">
+      <c r="H9" s="56" t="n">
         <f aca="false">F9+G9</f>
         <v>412.5</v>
       </c>
-      <c r="I9" s="57" t="s">
-        <v>112</v>
-      </c>
-      <c r="J9" s="45" t="n">
+      <c r="I9" s="72" t="s">
+        <v>126</v>
+      </c>
+      <c r="J9" s="56" t="n">
         <f aca="false">IF(I9="Win",F9+G9,IF(I9="Push",F9,IF(I9="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K9" s="47" t="n">
+      <c r="K9" s="58" t="n">
         <f aca="false">IF(I9="Pending",0,J9-F9)</f>
         <v>0</v>
       </c>
-      <c r="L9" s="48" t="s">
-        <v>173</v>
+      <c r="L9" s="59" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="41" t="n">
+      <c r="A10" s="51" t="n">
         <v>4</v>
       </c>
-      <c r="B10" s="42" t="s">
-        <v>174</v>
-      </c>
-      <c r="C10" s="43" t="s">
-        <v>175</v>
-      </c>
-      <c r="D10" s="41" t="s">
-        <v>172</v>
-      </c>
-      <c r="E10" s="44" t="n">
+      <c r="B10" s="52" t="s">
+        <v>188</v>
+      </c>
+      <c r="C10" s="53" t="s">
+        <v>189</v>
+      </c>
+      <c r="D10" s="51" t="s">
+        <v>186</v>
+      </c>
+      <c r="E10" s="54" t="n">
         <v>205</v>
       </c>
-      <c r="F10" s="36" t="n">
+      <c r="F10" s="55" t="n">
         <v>80</v>
       </c>
-      <c r="G10" s="45" t="n">
+      <c r="G10" s="56" t="n">
         <f aca="false">IF(E10&gt;0,F10*E10/100,F10*100/ABS(E10))</f>
         <v>164</v>
       </c>
-      <c r="H10" s="45" t="n">
+      <c r="H10" s="56" t="n">
         <f aca="false">F10+G10</f>
         <v>244</v>
       </c>
-      <c r="I10" s="57" t="s">
-        <v>112</v>
-      </c>
-      <c r="J10" s="45" t="n">
+      <c r="I10" s="72" t="s">
+        <v>126</v>
+      </c>
+      <c r="J10" s="56" t="n">
         <f aca="false">IF(I10="Win",F10+G10,IF(I10="Push",F10,IF(I10="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K10" s="47" t="n">
+      <c r="K10" s="58" t="n">
         <f aca="false">IF(I10="Pending",0,J10-F10)</f>
         <v>0</v>
       </c>
-      <c r="L10" s="48" t="s">
-        <v>176</v>
+      <c r="L10" s="59" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="41" t="n">
+      <c r="A11" s="51" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="42" t="s">
-        <v>177</v>
-      </c>
-      <c r="C11" s="43" t="s">
-        <v>178</v>
-      </c>
-      <c r="D11" s="41" t="s">
-        <v>179</v>
-      </c>
-      <c r="E11" s="44" t="n">
+      <c r="B11" s="52" t="s">
+        <v>191</v>
+      </c>
+      <c r="C11" s="53" t="s">
+        <v>192</v>
+      </c>
+      <c r="D11" s="51" t="s">
+        <v>193</v>
+      </c>
+      <c r="E11" s="54" t="n">
         <v>160</v>
       </c>
-      <c r="F11" s="36" t="n">
+      <c r="F11" s="55" t="n">
         <v>250</v>
       </c>
-      <c r="G11" s="45" t="n">
+      <c r="G11" s="56" t="n">
         <f aca="false">IF(E11&gt;0,F11*E11/100,F11*100/ABS(E11))</f>
         <v>400</v>
       </c>
-      <c r="H11" s="45" t="n">
+      <c r="H11" s="56" t="n">
         <f aca="false">F11+G11</f>
         <v>650</v>
       </c>
-      <c r="I11" s="57" t="s">
-        <v>112</v>
-      </c>
-      <c r="J11" s="45" t="n">
+      <c r="I11" s="72" t="s">
+        <v>126</v>
+      </c>
+      <c r="J11" s="56" t="n">
         <f aca="false">IF(I11="Win",F11+G11,IF(I11="Push",F11,IF(I11="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K11" s="47" t="n">
+      <c r="K11" s="58" t="n">
         <f aca="false">IF(I11="Pending",0,J11-F11)</f>
         <v>0</v>
       </c>
-      <c r="L11" s="48" t="s">
-        <v>180</v>
+      <c r="L11" s="59" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="41" t="n">
+      <c r="A12" s="51" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="42" t="s">
-        <v>181</v>
-      </c>
-      <c r="C12" s="43" t="s">
-        <v>182</v>
-      </c>
-      <c r="D12" s="41" t="s">
-        <v>179</v>
-      </c>
-      <c r="E12" s="44" t="n">
+      <c r="B12" s="52" t="s">
+        <v>195</v>
+      </c>
+      <c r="C12" s="53" t="s">
+        <v>196</v>
+      </c>
+      <c r="D12" s="51" t="s">
+        <v>193</v>
+      </c>
+      <c r="E12" s="54" t="n">
         <v>500</v>
       </c>
-      <c r="F12" s="36" t="n">
+      <c r="F12" s="55" t="n">
         <v>50</v>
       </c>
-      <c r="G12" s="45" t="n">
+      <c r="G12" s="56" t="n">
         <f aca="false">IF(E12&gt;0,F12*E12/100,F12*100/ABS(E12))</f>
         <v>250</v>
       </c>
-      <c r="H12" s="45" t="n">
+      <c r="H12" s="56" t="n">
         <f aca="false">F12+G12</f>
         <v>300</v>
       </c>
-      <c r="I12" s="57" t="s">
-        <v>112</v>
-      </c>
-      <c r="J12" s="45" t="n">
+      <c r="I12" s="72" t="s">
+        <v>126</v>
+      </c>
+      <c r="J12" s="56" t="n">
         <f aca="false">IF(I12="Win",F12+G12,IF(I12="Push",F12,IF(I12="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K12" s="47" t="n">
+      <c r="K12" s="58" t="n">
         <f aca="false">IF(I12="Pending",0,J12-F12)</f>
         <v>0</v>
       </c>
-      <c r="L12" s="48" t="s">
-        <v>183</v>
+      <c r="L12" s="59" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="41" t="n">
+      <c r="A13" s="51" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="42" t="s">
-        <v>184</v>
-      </c>
-      <c r="C13" s="43" t="s">
-        <v>185</v>
-      </c>
-      <c r="D13" s="41" t="s">
-        <v>106</v>
-      </c>
-      <c r="E13" s="44" t="n">
+      <c r="B13" s="52" t="s">
+        <v>198</v>
+      </c>
+      <c r="C13" s="53" t="s">
+        <v>199</v>
+      </c>
+      <c r="D13" s="51" t="s">
+        <v>120</v>
+      </c>
+      <c r="E13" s="54" t="n">
         <v>179</v>
       </c>
-      <c r="F13" s="36" t="n">
+      <c r="F13" s="55" t="n">
         <v>50</v>
       </c>
-      <c r="G13" s="45" t="n">
+      <c r="G13" s="56" t="n">
         <f aca="false">IF(E13&gt;0,F13*E13/100,F13*100/ABS(E13))</f>
         <v>89.5</v>
       </c>
-      <c r="H13" s="45" t="n">
+      <c r="H13" s="56" t="n">
         <f aca="false">F13+G13</f>
         <v>139.5</v>
       </c>
-      <c r="I13" s="57" t="s">
-        <v>112</v>
-      </c>
-      <c r="J13" s="45" t="n">
+      <c r="I13" s="72" t="s">
+        <v>126</v>
+      </c>
+      <c r="J13" s="56" t="n">
         <f aca="false">IF(I13="Win",F13+G13,IF(I13="Push",F13,IF(I13="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K13" s="47" t="n">
+      <c r="K13" s="58" t="n">
         <f aca="false">IF(I13="Pending",0,J13-F13)</f>
         <v>0</v>
       </c>
-      <c r="L13" s="48" t="s">
-        <v>186</v>
+      <c r="L13" s="59" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="50"/>
-      <c r="B14" s="51" t="s">
-        <v>37</v>
-      </c>
-      <c r="C14" s="50"/>
-      <c r="D14" s="50"/>
-      <c r="E14" s="50"/>
-      <c r="F14" s="31" t="n">
+      <c r="A14" s="61"/>
+      <c r="B14" s="62" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14" s="61"/>
+      <c r="D14" s="61"/>
+      <c r="E14" s="61"/>
+      <c r="F14" s="63" t="n">
         <f aca="false">SUM(F7:F13)</f>
         <v>1000</v>
       </c>
-      <c r="G14" s="32" t="n">
+      <c r="G14" s="64" t="n">
         <f aca="false">SUM(G7:G13)</f>
         <v>1472.69398907104</v>
       </c>
-      <c r="H14" s="32" t="n">
+      <c r="H14" s="64" t="n">
         <f aca="false">SUM(H7:H13)</f>
         <v>2472.69398907104</v>
       </c>
-      <c r="I14" s="50"/>
-      <c r="J14" s="32" t="n">
+      <c r="I14" s="61"/>
+      <c r="J14" s="64" t="n">
         <f aca="false">SUM(J7:J13)</f>
         <v>0</v>
       </c>
-      <c r="K14" s="33" t="n">
+      <c r="K14" s="65" t="n">
         <f aca="false">SUM(K7:K13)</f>
         <v>0</v>
       </c>
-      <c r="L14" s="50"/>
+      <c r="L14" s="61"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="4" t="s">
-        <v>108</v>
+      <c r="B16" s="50" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="42" t="s">
-        <v>109</v>
-      </c>
-      <c r="C17" s="52" t="n">
+      <c r="B17" s="52" t="s">
+        <v>123</v>
+      </c>
+      <c r="C17" s="66" t="n">
         <f aca="false">COUNTIF(I7:I13,"Win")</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="42" t="s">
-        <v>110</v>
-      </c>
-      <c r="C18" s="52" t="n">
+      <c r="B18" s="52" t="s">
+        <v>124</v>
+      </c>
+      <c r="C18" s="66" t="n">
         <f aca="false">COUNTIF(I7:I13,"Loss")</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="42" t="s">
-        <v>111</v>
-      </c>
-      <c r="C19" s="52" t="n">
+      <c r="B19" s="52" t="s">
+        <v>125</v>
+      </c>
+      <c r="C19" s="66" t="n">
         <f aca="false">COUNTIF(I7:I13,"Push")</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="42" t="s">
-        <v>112</v>
-      </c>
-      <c r="C20" s="52" t="n">
+      <c r="B20" s="52" t="s">
+        <v>126</v>
+      </c>
+      <c r="C20" s="66" t="n">
         <f aca="false">COUNTIF(I7:I13,"Pending")</f>
         <v>7</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="42" t="s">
-        <v>113</v>
-      </c>
-      <c r="C21" s="53" t="str">
+      <c r="B21" s="52" t="s">
+        <v>127</v>
+      </c>
+      <c r="C21" s="67" t="str">
         <f aca="false">IF(COUNTIF(I7:I13,"Win")+COUNTIF(I7:I13,"Loss")=0,"—",COUNTIF(I7:I13,"Win")/(COUNTIF(I7:I13,"Win")+COUNTIF(I7:I13,"Loss")))</f>
         <v>—</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="42" t="s">
-        <v>114</v>
-      </c>
-      <c r="C22" s="54" t="n">
+      <c r="B22" s="52" t="s">
+        <v>128</v>
+      </c>
+      <c r="C22" s="68" t="n">
         <f aca="false">SUM(F7:F13)</f>
         <v>1000</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="42" t="s">
-        <v>115</v>
-      </c>
-      <c r="C23" s="45" t="n">
+      <c r="B23" s="52" t="s">
+        <v>129</v>
+      </c>
+      <c r="C23" s="56" t="n">
         <f aca="false">SUM(J7:J13)</f>
         <v>0</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="42" t="s">
-        <v>116</v>
-      </c>
-      <c r="C24" s="47" t="n">
+      <c r="B24" s="52" t="s">
+        <v>130</v>
+      </c>
+      <c r="C24" s="58" t="n">
         <f aca="false">SUM(K7:K13)</f>
         <v>0</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="42" t="s">
-        <v>117</v>
-      </c>
-      <c r="C25" s="53" t="n">
+      <c r="B25" s="52" t="s">
+        <v>131</v>
+      </c>
+      <c r="C25" s="67" t="n">
         <f aca="false">IF(SUM(F7:F13)=0,"—",SUM(K7:K13)/SUM(F7:F13))</f>
         <v>0</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="42" t="s">
-        <v>187</v>
-      </c>
-      <c r="C26" s="54" t="n">
+      <c r="B26" s="52" t="s">
+        <v>201</v>
+      </c>
+      <c r="C26" s="68" t="n">
         <f aca="false">929</f>
         <v>929</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="4" t="s">
-        <v>188</v>
+      <c r="A28" s="50" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="12" t="s">
+      <c r="A29" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="B29" s="12" t="s">
-        <v>189</v>
-      </c>
-      <c r="C29" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="D29" s="12" t="s">
-        <v>122</v>
-      </c>
-      <c r="E29" s="12" t="s">
-        <v>190</v>
-      </c>
-      <c r="F29" s="12" t="s">
-        <v>124</v>
+      <c r="B29" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="C29" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="D29" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="E29" s="11" t="s">
+        <v>204</v>
+      </c>
+      <c r="F29" s="11" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="41" t="n">
+      <c r="A30" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="B30" s="42" t="s">
-        <v>191</v>
-      </c>
-      <c r="C30" s="48" t="s">
-        <v>192</v>
-      </c>
-      <c r="D30" s="35" t="s">
-        <v>193</v>
-      </c>
-      <c r="E30" s="57"/>
-      <c r="F30" s="57"/>
+      <c r="B30" s="52" t="s">
+        <v>205</v>
+      </c>
+      <c r="C30" s="59" t="s">
+        <v>206</v>
+      </c>
+      <c r="D30" s="42" t="s">
+        <v>207</v>
+      </c>
+      <c r="E30" s="72"/>
+      <c r="F30" s="72"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="41" t="n">
+      <c r="A31" s="51" t="n">
         <v>2</v>
       </c>
-      <c r="B31" s="42" t="s">
-        <v>194</v>
-      </c>
-      <c r="C31" s="48" t="s">
-        <v>195</v>
-      </c>
-      <c r="D31" s="35" t="s">
-        <v>196</v>
-      </c>
-      <c r="E31" s="57"/>
-      <c r="F31" s="57"/>
+      <c r="B31" s="52" t="s">
+        <v>208</v>
+      </c>
+      <c r="C31" s="59" t="s">
+        <v>209</v>
+      </c>
+      <c r="D31" s="42" t="s">
+        <v>210</v>
+      </c>
+      <c r="E31" s="72"/>
+      <c r="F31" s="72"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="41" t="n">
+      <c r="A32" s="51" t="n">
         <v>3</v>
       </c>
-      <c r="B32" s="42" t="s">
-        <v>197</v>
-      </c>
-      <c r="C32" s="48" t="s">
-        <v>198</v>
-      </c>
-      <c r="D32" s="35" t="s">
-        <v>199</v>
-      </c>
-      <c r="E32" s="57"/>
-      <c r="F32" s="57"/>
+      <c r="B32" s="52" t="s">
+        <v>211</v>
+      </c>
+      <c r="C32" s="59" t="s">
+        <v>212</v>
+      </c>
+      <c r="D32" s="42" t="s">
+        <v>213</v>
+      </c>
+      <c r="E32" s="72"/>
+      <c r="F32" s="72"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="41" t="n">
+      <c r="A33" s="51" t="n">
         <v>4</v>
       </c>
-      <c r="B33" s="42" t="s">
-        <v>200</v>
-      </c>
-      <c r="C33" s="48" t="s">
-        <v>201</v>
-      </c>
-      <c r="D33" s="35" t="s">
-        <v>202</v>
-      </c>
-      <c r="E33" s="57"/>
-      <c r="F33" s="57"/>
+      <c r="B33" s="52" t="s">
+        <v>214</v>
+      </c>
+      <c r="C33" s="59" t="s">
+        <v>215</v>
+      </c>
+      <c r="D33" s="42" t="s">
+        <v>216</v>
+      </c>
+      <c r="E33" s="72"/>
+      <c r="F33" s="72"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="38" t="s">
-        <v>203</v>
+      <c r="A35" s="70" t="s">
+        <v>217</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="K7:K14">
-    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>AND(ISNUMBER(K7),K7&gt;0)</formula>
     </cfRule>
-    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>AND(ISNUMBER(K7),K7&lt;0)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C24:C25">
-    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>AND(ISNUMBER(C24),C24&gt;0)</formula>
     </cfRule>
-    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>AND(ISNUMBER(C24),C24&lt;0)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3947,770 +4324,770 @@
   <dimension ref="A1:M42"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="9" style="1" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="46" width="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="46" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="46" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="46" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="46" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="46" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="46" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="9" style="46" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="46" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="46" width="46"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="39" t="s">
-        <v>204</v>
-      </c>
-      <c r="H1" s="40" t="s">
-        <v>205</v>
+      <c r="A1" s="47" t="s">
+        <v>218</v>
+      </c>
+      <c r="H1" s="48" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
-        <v>206</v>
+      <c r="A2" s="49" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
-        <v>207</v>
+      <c r="A3" s="49" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
-        <v>65</v>
+      <c r="A5" s="50" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="C6" s="12" t="s">
-        <v>208</v>
-      </c>
-      <c r="D6" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="E6" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="F6" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="G6" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="H6" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="I6" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="J6" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="K6" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="L6" s="12" t="s">
-        <v>209</v>
-      </c>
-      <c r="M6" s="12" t="s">
-        <v>75</v>
+      <c r="B6" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="G6" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="I6" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="J6" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="K6" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="L6" s="11" t="s">
+        <v>223</v>
+      </c>
+      <c r="M6" s="11" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="41" t="n">
+      <c r="A7" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="42" t="s">
-        <v>210</v>
-      </c>
-      <c r="C7" s="43" t="s">
-        <v>211</v>
-      </c>
-      <c r="D7" s="41" t="s">
-        <v>78</v>
-      </c>
-      <c r="E7" s="44" t="n">
+      <c r="B7" s="52" t="s">
+        <v>224</v>
+      </c>
+      <c r="C7" s="53" t="s">
+        <v>225</v>
+      </c>
+      <c r="D7" s="51" t="s">
+        <v>92</v>
+      </c>
+      <c r="E7" s="54" t="n">
         <v>-155</v>
       </c>
-      <c r="F7" s="36" t="n">
+      <c r="F7" s="55" t="n">
         <v>200</v>
       </c>
-      <c r="G7" s="45" t="n">
+      <c r="G7" s="56" t="n">
         <f aca="false">IF(E7&gt;0,F7*E7/100,F7*100/ABS(E7))</f>
         <v>129.032258064516</v>
       </c>
-      <c r="H7" s="45" t="n">
+      <c r="H7" s="56" t="n">
         <f aca="false">F7+G7</f>
         <v>329.032258064516</v>
       </c>
-      <c r="I7" s="46" t="s">
-        <v>79</v>
-      </c>
-      <c r="J7" s="45" t="n">
+      <c r="I7" s="57" t="s">
+        <v>93</v>
+      </c>
+      <c r="J7" s="56" t="n">
         <f aca="false">IF(I7="Win",F7+G7,IF(I7="Push",F7,IF(I7="Loss",0,0)))</f>
         <v>329.032258064516</v>
       </c>
-      <c r="K7" s="47" t="n">
+      <c r="K7" s="58" t="n">
         <f aca="false">IF(I7="Pending",0,J7-F7)</f>
         <v>129.032258064516</v>
       </c>
-      <c r="L7" s="58" t="n">
+      <c r="L7" s="73" t="n">
         <v>0.62</v>
       </c>
-      <c r="M7" s="48" t="s">
-        <v>212</v>
+      <c r="M7" s="59" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="41" t="n">
+      <c r="A8" s="51" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="42" t="s">
-        <v>213</v>
-      </c>
-      <c r="C8" s="43" t="s">
-        <v>214</v>
-      </c>
-      <c r="D8" s="41" t="s">
-        <v>78</v>
-      </c>
-      <c r="E8" s="44" t="n">
+      <c r="B8" s="52" t="s">
+        <v>227</v>
+      </c>
+      <c r="C8" s="53" t="s">
+        <v>228</v>
+      </c>
+      <c r="D8" s="51" t="s">
+        <v>92</v>
+      </c>
+      <c r="E8" s="54" t="n">
         <v>-104</v>
       </c>
-      <c r="F8" s="36" t="n">
+      <c r="F8" s="55" t="n">
         <v>150</v>
       </c>
-      <c r="G8" s="45" t="n">
+      <c r="G8" s="56" t="n">
         <f aca="false">IF(E8&gt;0,F8*E8/100,F8*100/ABS(E8))</f>
         <v>144.230769230769</v>
       </c>
-      <c r="H8" s="45" t="n">
+      <c r="H8" s="56" t="n">
         <f aca="false">F8+G8</f>
         <v>294.230769230769</v>
       </c>
-      <c r="I8" s="49" t="s">
-        <v>87</v>
-      </c>
-      <c r="J8" s="45" t="n">
+      <c r="I8" s="60" t="s">
+        <v>101</v>
+      </c>
+      <c r="J8" s="56" t="n">
         <f aca="false">IF(I8="Win",F8+G8,IF(I8="Push",F8,IF(I8="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K8" s="47" t="n">
+      <c r="K8" s="58" t="n">
         <f aca="false">IF(I8="Pending",0,J8-F8)</f>
         <v>-150</v>
       </c>
-      <c r="L8" s="58" t="n">
+      <c r="L8" s="73" t="n">
         <v>0.54</v>
       </c>
-      <c r="M8" s="48" t="s">
-        <v>215</v>
+      <c r="M8" s="59" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="41" t="n">
+      <c r="A9" s="51" t="n">
         <v>3</v>
       </c>
-      <c r="B9" s="42" t="s">
-        <v>216</v>
-      </c>
-      <c r="C9" s="43" t="s">
-        <v>217</v>
-      </c>
-      <c r="D9" s="41" t="s">
-        <v>78</v>
-      </c>
-      <c r="E9" s="44" t="n">
+      <c r="B9" s="52" t="s">
+        <v>230</v>
+      </c>
+      <c r="C9" s="53" t="s">
+        <v>231</v>
+      </c>
+      <c r="D9" s="51" t="s">
+        <v>92</v>
+      </c>
+      <c r="E9" s="54" t="n">
         <v>-115</v>
       </c>
-      <c r="F9" s="36" t="n">
+      <c r="F9" s="55" t="n">
         <v>150</v>
       </c>
-      <c r="G9" s="45" t="n">
+      <c r="G9" s="56" t="n">
         <f aca="false">IF(E9&gt;0,F9*E9/100,F9*100/ABS(E9))</f>
         <v>130.434782608696</v>
       </c>
-      <c r="H9" s="45" t="n">
+      <c r="H9" s="56" t="n">
         <f aca="false">F9+G9</f>
         <v>280.434782608696</v>
       </c>
-      <c r="I9" s="49" t="s">
-        <v>87</v>
-      </c>
-      <c r="J9" s="45" t="n">
+      <c r="I9" s="60" t="s">
+        <v>101</v>
+      </c>
+      <c r="J9" s="56" t="n">
         <f aca="false">IF(I9="Win",F9+G9,IF(I9="Push",F9,IF(I9="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K9" s="47" t="n">
+      <c r="K9" s="58" t="n">
         <f aca="false">IF(I9="Pending",0,J9-F9)</f>
         <v>-150</v>
       </c>
-      <c r="L9" s="58" t="n">
+      <c r="L9" s="73" t="n">
         <v>0.55</v>
       </c>
-      <c r="M9" s="48" t="s">
-        <v>218</v>
+      <c r="M9" s="59" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="41" t="n">
+      <c r="A10" s="51" t="n">
         <v>4</v>
       </c>
-      <c r="B10" s="42" t="s">
-        <v>219</v>
-      </c>
-      <c r="C10" s="43" t="s">
-        <v>220</v>
-      </c>
-      <c r="D10" s="41" t="s">
-        <v>168</v>
-      </c>
-      <c r="E10" s="44" t="n">
+      <c r="B10" s="52" t="s">
+        <v>233</v>
+      </c>
+      <c r="C10" s="53" t="s">
+        <v>234</v>
+      </c>
+      <c r="D10" s="51" t="s">
+        <v>182</v>
+      </c>
+      <c r="E10" s="54" t="n">
         <v>-114</v>
       </c>
-      <c r="F10" s="36" t="n">
+      <c r="F10" s="55" t="n">
         <v>120</v>
       </c>
-      <c r="G10" s="45" t="n">
+      <c r="G10" s="56" t="n">
         <f aca="false">IF(E10&gt;0,F10*E10/100,F10*100/ABS(E10))</f>
         <v>105.263157894737</v>
       </c>
-      <c r="H10" s="45" t="n">
+      <c r="H10" s="56" t="n">
         <f aca="false">F10+G10</f>
         <v>225.263157894737</v>
       </c>
-      <c r="I10" s="49" t="s">
-        <v>87</v>
-      </c>
-      <c r="J10" s="45" t="n">
+      <c r="I10" s="60" t="s">
+        <v>101</v>
+      </c>
+      <c r="J10" s="56" t="n">
         <f aca="false">IF(I10="Win",F10+G10,IF(I10="Push",F10,IF(I10="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K10" s="47" t="n">
+      <c r="K10" s="58" t="n">
         <f aca="false">IF(I10="Pending",0,J10-F10)</f>
         <v>-120</v>
       </c>
-      <c r="L10" s="58" t="n">
+      <c r="L10" s="73" t="n">
         <v>0.55</v>
       </c>
-      <c r="M10" s="48" t="s">
-        <v>221</v>
+      <c r="M10" s="59" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="41" t="n">
+      <c r="A11" s="51" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="42" t="s">
-        <v>222</v>
-      </c>
-      <c r="C11" s="43" t="s">
-        <v>223</v>
-      </c>
-      <c r="D11" s="41" t="s">
-        <v>78</v>
-      </c>
-      <c r="E11" s="44" t="n">
+      <c r="B11" s="52" t="s">
+        <v>236</v>
+      </c>
+      <c r="C11" s="53" t="s">
+        <v>237</v>
+      </c>
+      <c r="D11" s="51" t="s">
+        <v>92</v>
+      </c>
+      <c r="E11" s="54" t="n">
         <v>104</v>
       </c>
-      <c r="F11" s="36" t="n">
+      <c r="F11" s="55" t="n">
         <v>130</v>
       </c>
-      <c r="G11" s="45" t="n">
+      <c r="G11" s="56" t="n">
         <f aca="false">IF(E11&gt;0,F11*E11/100,F11*100/ABS(E11))</f>
         <v>135.2</v>
       </c>
-      <c r="H11" s="45" t="n">
+      <c r="H11" s="56" t="n">
         <f aca="false">F11+G11</f>
         <v>265.2</v>
       </c>
-      <c r="I11" s="46" t="s">
-        <v>79</v>
-      </c>
-      <c r="J11" s="45" t="n">
+      <c r="I11" s="57" t="s">
+        <v>93</v>
+      </c>
+      <c r="J11" s="56" t="n">
         <f aca="false">IF(I11="Win",F11+G11,IF(I11="Push",F11,IF(I11="Loss",0,0)))</f>
         <v>265.2</v>
       </c>
-      <c r="K11" s="47" t="n">
+      <c r="K11" s="58" t="n">
         <f aca="false">IF(I11="Pending",0,J11-F11)</f>
         <v>135.2</v>
       </c>
-      <c r="L11" s="58" t="n">
+      <c r="L11" s="73" t="n">
         <v>0.52</v>
       </c>
-      <c r="M11" s="48" t="s">
-        <v>224</v>
+      <c r="M11" s="59" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="41" t="n">
+      <c r="A12" s="51" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="42" t="s">
-        <v>225</v>
-      </c>
-      <c r="C12" s="43" t="s">
-        <v>226</v>
-      </c>
-      <c r="D12" s="41" t="s">
-        <v>78</v>
-      </c>
-      <c r="E12" s="44" t="n">
+      <c r="B12" s="52" t="s">
+        <v>239</v>
+      </c>
+      <c r="C12" s="53" t="s">
+        <v>240</v>
+      </c>
+      <c r="D12" s="51" t="s">
+        <v>92</v>
+      </c>
+      <c r="E12" s="54" t="n">
         <v>108</v>
       </c>
-      <c r="F12" s="36" t="n">
+      <c r="F12" s="55" t="n">
         <v>100</v>
       </c>
-      <c r="G12" s="45" t="n">
+      <c r="G12" s="56" t="n">
         <f aca="false">IF(E12&gt;0,F12*E12/100,F12*100/ABS(E12))</f>
         <v>108</v>
       </c>
-      <c r="H12" s="45" t="n">
+      <c r="H12" s="56" t="n">
         <f aca="false">F12+G12</f>
         <v>208</v>
       </c>
-      <c r="I12" s="49" t="s">
-        <v>87</v>
-      </c>
-      <c r="J12" s="45" t="n">
+      <c r="I12" s="60" t="s">
+        <v>101</v>
+      </c>
+      <c r="J12" s="56" t="n">
         <f aca="false">IF(I12="Win",F12+G12,IF(I12="Push",F12,IF(I12="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K12" s="47" t="n">
+      <c r="K12" s="58" t="n">
         <f aca="false">IF(I12="Pending",0,J12-F12)</f>
         <v>-100</v>
       </c>
-      <c r="L12" s="58" t="n">
+      <c r="L12" s="73" t="n">
         <v>0.5</v>
       </c>
-      <c r="M12" s="48" t="s">
-        <v>227</v>
+      <c r="M12" s="59" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="41" t="n">
+      <c r="A13" s="51" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="42" t="s">
-        <v>228</v>
-      </c>
-      <c r="C13" s="43" t="s">
-        <v>229</v>
-      </c>
-      <c r="D13" s="41" t="s">
-        <v>78</v>
-      </c>
-      <c r="E13" s="44" t="n">
+      <c r="B13" s="52" t="s">
+        <v>242</v>
+      </c>
+      <c r="C13" s="53" t="s">
+        <v>243</v>
+      </c>
+      <c r="D13" s="51" t="s">
+        <v>92</v>
+      </c>
+      <c r="E13" s="54" t="n">
         <v>108</v>
       </c>
-      <c r="F13" s="36" t="n">
+      <c r="F13" s="55" t="n">
         <v>100</v>
       </c>
-      <c r="G13" s="45" t="n">
+      <c r="G13" s="56" t="n">
         <f aca="false">IF(E13&gt;0,F13*E13/100,F13*100/ABS(E13))</f>
         <v>108</v>
       </c>
-      <c r="H13" s="45" t="n">
+      <c r="H13" s="56" t="n">
         <f aca="false">F13+G13</f>
         <v>208</v>
       </c>
-      <c r="I13" s="46" t="s">
-        <v>79</v>
-      </c>
-      <c r="J13" s="45" t="n">
+      <c r="I13" s="57" t="s">
+        <v>93</v>
+      </c>
+      <c r="J13" s="56" t="n">
         <f aca="false">IF(I13="Win",F13+G13,IF(I13="Push",F13,IF(I13="Loss",0,0)))</f>
         <v>208</v>
       </c>
-      <c r="K13" s="47" t="n">
+      <c r="K13" s="58" t="n">
         <f aca="false">IF(I13="Pending",0,J13-F13)</f>
         <v>108</v>
       </c>
-      <c r="L13" s="58" t="n">
+      <c r="L13" s="73" t="n">
         <v>0.5</v>
       </c>
-      <c r="M13" s="48" t="s">
-        <v>230</v>
+      <c r="M13" s="59" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="41" t="n">
+      <c r="A14" s="51" t="n">
         <v>8</v>
       </c>
-      <c r="B14" s="42" t="s">
-        <v>231</v>
-      </c>
-      <c r="C14" s="43" t="s">
-        <v>232</v>
-      </c>
-      <c r="D14" s="41" t="s">
-        <v>106</v>
-      </c>
-      <c r="E14" s="44" t="n">
+      <c r="B14" s="52" t="s">
+        <v>245</v>
+      </c>
+      <c r="C14" s="53" t="s">
+        <v>246</v>
+      </c>
+      <c r="D14" s="51" t="s">
+        <v>120</v>
+      </c>
+      <c r="E14" s="54" t="n">
         <v>732</v>
       </c>
-      <c r="F14" s="36" t="n">
+      <c r="F14" s="55" t="n">
         <v>50</v>
       </c>
-      <c r="G14" s="45" t="n">
+      <c r="G14" s="56" t="n">
         <f aca="false">IF(E14&gt;0,F14*E14/100,F14*100/ABS(E14))</f>
         <v>366</v>
       </c>
-      <c r="H14" s="45" t="n">
+      <c r="H14" s="56" t="n">
         <f aca="false">F14+G14</f>
         <v>416</v>
       </c>
-      <c r="I14" s="49" t="s">
-        <v>87</v>
-      </c>
-      <c r="J14" s="45" t="n">
+      <c r="I14" s="60" t="s">
+        <v>101</v>
+      </c>
+      <c r="J14" s="56" t="n">
         <f aca="false">IF(I14="Win",F14+G14,IF(I14="Push",F14,IF(I14="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K14" s="47" t="n">
+      <c r="K14" s="58" t="n">
         <f aca="false">IF(I14="Pending",0,J14-F14)</f>
         <v>-50</v>
       </c>
-      <c r="L14" s="58" t="n">
+      <c r="L14" s="73" t="n">
         <v>0.14</v>
       </c>
-      <c r="M14" s="48" t="s">
-        <v>233</v>
+      <c r="M14" s="59" t="s">
+        <v>247</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="50"/>
-      <c r="B15" s="51" t="s">
-        <v>37</v>
-      </c>
-      <c r="C15" s="50"/>
-      <c r="D15" s="50"/>
-      <c r="E15" s="50"/>
-      <c r="F15" s="31" t="n">
+      <c r="A15" s="61"/>
+      <c r="B15" s="62" t="s">
+        <v>44</v>
+      </c>
+      <c r="C15" s="61"/>
+      <c r="D15" s="61"/>
+      <c r="E15" s="61"/>
+      <c r="F15" s="63" t="n">
         <f aca="false">SUM(F7:F14)</f>
         <v>1000</v>
       </c>
-      <c r="G15" s="32" t="n">
+      <c r="G15" s="64" t="n">
         <f aca="false">SUM(G7:G14)</f>
         <v>1226.16096779872</v>
       </c>
-      <c r="H15" s="32" t="n">
+      <c r="H15" s="64" t="n">
         <f aca="false">SUM(H7:H14)</f>
         <v>2226.16096779872</v>
       </c>
-      <c r="I15" s="50"/>
-      <c r="J15" s="32" t="n">
+      <c r="I15" s="61"/>
+      <c r="J15" s="64" t="n">
         <f aca="false">SUM(J7:J14)</f>
         <v>802.232258064516</v>
       </c>
-      <c r="K15" s="33" t="n">
+      <c r="K15" s="65" t="n">
         <f aca="false">SUM(K7:K14)</f>
         <v>-197.767741935484</v>
       </c>
-      <c r="L15" s="59" t="n">
+      <c r="L15" s="74" t="n">
         <f aca="false">SUM(L7:L14)</f>
         <v>3.92</v>
       </c>
-      <c r="M15" s="50"/>
+      <c r="M15" s="61"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="4" t="s">
-        <v>108</v>
+      <c r="B17" s="50" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="42" t="s">
-        <v>109</v>
-      </c>
-      <c r="C18" s="52" t="n">
+      <c r="B18" s="52" t="s">
+        <v>123</v>
+      </c>
+      <c r="C18" s="66" t="n">
         <f aca="false">COUNTIF(I7:I14,"Win")</f>
         <v>3</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="42" t="s">
-        <v>110</v>
-      </c>
-      <c r="C19" s="52" t="n">
+      <c r="B19" s="52" t="s">
+        <v>124</v>
+      </c>
+      <c r="C19" s="66" t="n">
         <f aca="false">COUNTIF(I7:I14,"Loss")</f>
         <v>5</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="42" t="s">
-        <v>111</v>
-      </c>
-      <c r="C20" s="52" t="n">
+      <c r="B20" s="52" t="s">
+        <v>125</v>
+      </c>
+      <c r="C20" s="66" t="n">
         <f aca="false">COUNTIF(I7:I14,"Push")</f>
         <v>0</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="42" t="s">
-        <v>112</v>
-      </c>
-      <c r="C21" s="52" t="n">
+      <c r="B21" s="52" t="s">
+        <v>126</v>
+      </c>
+      <c r="C21" s="66" t="n">
         <f aca="false">COUNTIF(I7:I14,"Pending")</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="42" t="s">
-        <v>113</v>
-      </c>
-      <c r="C22" s="53" t="n">
+      <c r="B22" s="52" t="s">
+        <v>127</v>
+      </c>
+      <c r="C22" s="67" t="n">
         <f aca="false">IF(COUNTIF(I7:I14,"Win")+COUNTIF(I7:I14,"Loss")=0,"—",COUNTIF(I7:I14,"Win")/(COUNTIF(I7:I14,"Win")+COUNTIF(I7:I14,"Loss")))</f>
         <v>0.375</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="42" t="s">
-        <v>114</v>
-      </c>
-      <c r="C23" s="54" t="n">
+      <c r="B23" s="52" t="s">
+        <v>128</v>
+      </c>
+      <c r="C23" s="68" t="n">
         <f aca="false">SUM(F7:F14)</f>
         <v>1000</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="42" t="s">
-        <v>115</v>
-      </c>
-      <c r="C24" s="45" t="n">
+      <c r="B24" s="52" t="s">
+        <v>129</v>
+      </c>
+      <c r="C24" s="56" t="n">
         <f aca="false">SUM(J7:J14)</f>
         <v>802.232258064516</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="42" t="s">
-        <v>116</v>
-      </c>
-      <c r="C25" s="47" t="n">
+      <c r="B25" s="52" t="s">
+        <v>130</v>
+      </c>
+      <c r="C25" s="58" t="n">
         <f aca="false">SUM(K7:K14)</f>
         <v>-197.767741935484</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="42" t="s">
-        <v>117</v>
-      </c>
-      <c r="C26" s="53" t="n">
+      <c r="B26" s="52" t="s">
+        <v>131</v>
+      </c>
+      <c r="C26" s="67" t="n">
         <f aca="false">IF(SUM(F7:F14)=0,"—",SUM(K7:K14)/SUM(F7:F14))</f>
         <v>-0.197767741935484</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="42" t="s">
-        <v>118</v>
-      </c>
-      <c r="C27" s="45" t="n">
+      <c r="B27" s="52" t="s">
+        <v>132</v>
+      </c>
+      <c r="C27" s="56" t="n">
         <f aca="false">SUM(H7:H14)</f>
         <v>2226.16096779872</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="42" t="s">
-        <v>234</v>
-      </c>
-      <c r="C28" s="60" t="n">
+      <c r="B28" s="52" t="s">
+        <v>248</v>
+      </c>
+      <c r="C28" s="75" t="n">
         <f aca="false">SUM(L7:L14)</f>
         <v>3.92</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="42" t="s">
-        <v>235</v>
-      </c>
-      <c r="C29" s="47" t="n">
+      <c r="B29" s="52" t="s">
+        <v>249</v>
+      </c>
+      <c r="C29" s="58" t="n">
         <f aca="false">SUMPRODUCT(L7:L14,G7:G14)-SUMPRODUCT(1-L7:L14,F7:F14)</f>
         <v>45.1624826615033</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="4" t="s">
-        <v>236</v>
+      <c r="A31" s="50" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="12" t="s">
+      <c r="A32" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="B32" s="12" t="s">
-        <v>237</v>
-      </c>
-      <c r="C32" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="D32" s="12" t="s">
-        <v>238</v>
-      </c>
-      <c r="E32" s="12" t="s">
-        <v>123</v>
-      </c>
-      <c r="F32" s="12" t="s">
-        <v>124</v>
+      <c r="B32" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="C32" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="D32" s="11" t="s">
+        <v>252</v>
+      </c>
+      <c r="E32" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="F32" s="11" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="41" t="n">
+      <c r="A33" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="B33" s="42" t="s">
-        <v>239</v>
-      </c>
-      <c r="C33" s="48" t="s">
-        <v>240</v>
-      </c>
-      <c r="D33" s="35" t="s">
-        <v>241</v>
-      </c>
-      <c r="E33" s="57"/>
-      <c r="F33" s="57"/>
+      <c r="B33" s="52" t="s">
+        <v>253</v>
+      </c>
+      <c r="C33" s="59" t="s">
+        <v>254</v>
+      </c>
+      <c r="D33" s="42" t="s">
+        <v>255</v>
+      </c>
+      <c r="E33" s="72"/>
+      <c r="F33" s="72"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="41" t="n">
+      <c r="A34" s="51" t="n">
         <v>2</v>
       </c>
-      <c r="B34" s="42" t="s">
-        <v>242</v>
-      </c>
-      <c r="C34" s="48" t="s">
-        <v>243</v>
-      </c>
-      <c r="D34" s="35" t="s">
-        <v>244</v>
-      </c>
-      <c r="E34" s="57"/>
-      <c r="F34" s="57"/>
+      <c r="B34" s="52" t="s">
+        <v>256</v>
+      </c>
+      <c r="C34" s="59" t="s">
+        <v>257</v>
+      </c>
+      <c r="D34" s="42" t="s">
+        <v>258</v>
+      </c>
+      <c r="E34" s="72"/>
+      <c r="F34" s="72"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="41" t="n">
+      <c r="A35" s="51" t="n">
         <v>3</v>
       </c>
-      <c r="B35" s="42" t="s">
-        <v>245</v>
-      </c>
-      <c r="C35" s="48" t="s">
-        <v>246</v>
-      </c>
-      <c r="D35" s="35" t="s">
-        <v>247</v>
-      </c>
-      <c r="E35" s="57"/>
-      <c r="F35" s="57"/>
+      <c r="B35" s="52" t="s">
+        <v>259</v>
+      </c>
+      <c r="C35" s="59" t="s">
+        <v>260</v>
+      </c>
+      <c r="D35" s="42" t="s">
+        <v>261</v>
+      </c>
+      <c r="E35" s="72"/>
+      <c r="F35" s="72"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="41" t="n">
+      <c r="A36" s="51" t="n">
         <v>4</v>
       </c>
-      <c r="B36" s="42" t="s">
-        <v>248</v>
-      </c>
-      <c r="C36" s="48" t="s">
-        <v>249</v>
-      </c>
-      <c r="D36" s="35" t="s">
-        <v>250</v>
-      </c>
-      <c r="E36" s="57"/>
-      <c r="F36" s="57"/>
+      <c r="B36" s="52" t="s">
+        <v>262</v>
+      </c>
+      <c r="C36" s="59" t="s">
+        <v>263</v>
+      </c>
+      <c r="D36" s="42" t="s">
+        <v>264</v>
+      </c>
+      <c r="E36" s="72"/>
+      <c r="F36" s="72"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="41" t="n">
+      <c r="A37" s="51" t="n">
         <v>5</v>
       </c>
-      <c r="B37" s="42" t="s">
-        <v>251</v>
-      </c>
-      <c r="C37" s="48" t="s">
-        <v>252</v>
-      </c>
-      <c r="D37" s="35" t="s">
-        <v>253</v>
-      </c>
-      <c r="E37" s="57"/>
-      <c r="F37" s="57"/>
+      <c r="B37" s="52" t="s">
+        <v>265</v>
+      </c>
+      <c r="C37" s="59" t="s">
+        <v>266</v>
+      </c>
+      <c r="D37" s="42" t="s">
+        <v>267</v>
+      </c>
+      <c r="E37" s="72"/>
+      <c r="F37" s="72"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="41" t="n">
+      <c r="A38" s="51" t="n">
         <v>6</v>
       </c>
-      <c r="B38" s="42" t="s">
-        <v>254</v>
-      </c>
-      <c r="C38" s="48" t="s">
-        <v>255</v>
-      </c>
-      <c r="D38" s="35" t="s">
-        <v>256</v>
-      </c>
-      <c r="E38" s="57"/>
-      <c r="F38" s="57"/>
+      <c r="B38" s="52" t="s">
+        <v>268</v>
+      </c>
+      <c r="C38" s="59" t="s">
+        <v>269</v>
+      </c>
+      <c r="D38" s="42" t="s">
+        <v>270</v>
+      </c>
+      <c r="E38" s="72"/>
+      <c r="F38" s="72"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="41" t="n">
+      <c r="A39" s="51" t="n">
         <v>7</v>
       </c>
-      <c r="B39" s="42" t="s">
-        <v>257</v>
-      </c>
-      <c r="C39" s="48" t="s">
-        <v>258</v>
-      </c>
-      <c r="D39" s="35" t="s">
-        <v>259</v>
-      </c>
-      <c r="E39" s="57"/>
-      <c r="F39" s="57"/>
+      <c r="B39" s="52" t="s">
+        <v>271</v>
+      </c>
+      <c r="C39" s="59" t="s">
+        <v>272</v>
+      </c>
+      <c r="D39" s="42" t="s">
+        <v>273</v>
+      </c>
+      <c r="E39" s="72"/>
+      <c r="F39" s="72"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="41" t="n">
+      <c r="A40" s="51" t="n">
         <v>8</v>
       </c>
-      <c r="B40" s="42" t="s">
-        <v>260</v>
-      </c>
-      <c r="C40" s="48" t="s">
-        <v>261</v>
-      </c>
-      <c r="D40" s="35" t="s">
-        <v>262</v>
-      </c>
-      <c r="E40" s="57"/>
-      <c r="F40" s="57"/>
+      <c r="B40" s="52" t="s">
+        <v>274</v>
+      </c>
+      <c r="C40" s="59" t="s">
+        <v>275</v>
+      </c>
+      <c r="D40" s="42" t="s">
+        <v>276</v>
+      </c>
+      <c r="E40" s="72"/>
+      <c r="F40" s="72"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="38" t="s">
-        <v>263</v>
+      <c r="A42" s="70" t="s">
+        <v>277</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="K7:K15">
-    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>AND(ISNUMBER(K7),K7&gt;0)</formula>
     </cfRule>
-    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>AND(ISNUMBER(K7),K7&lt;0)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C25:C26">
-    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>AND(ISNUMBER(C25),C25&gt;0)</formula>
     </cfRule>
-    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>AND(ISNUMBER(C25),C25&lt;0)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C29">
-    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>AND(ISNUMBER(C29),C29&gt;0)</formula>
     </cfRule>
-    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>AND(ISNUMBER(C29),C29&lt;0)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4739,555 +5116,555 @@
   <dimension ref="A1:M29"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="9" style="1" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="50"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="46" width="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="46" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="46" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="46" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="46" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="46" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="46" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="9" style="46" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="46" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="46" width="50"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="39" t="s">
-        <v>264</v>
-      </c>
-      <c r="H1" s="56" t="s">
-        <v>265</v>
+      <c r="A1" s="47" t="s">
+        <v>278</v>
+      </c>
+      <c r="H1" s="71" t="s">
+        <v>279</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
-        <v>266</v>
+      <c r="A2" s="49" t="s">
+        <v>280</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="61" t="s">
-        <v>267</v>
+      <c r="A3" s="76" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
-        <v>65</v>
+      <c r="A5" s="50" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="C6" s="12" t="s">
-        <v>189</v>
-      </c>
-      <c r="D6" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="E6" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="F6" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="G6" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="H6" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="I6" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="J6" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="K6" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="L6" s="12" t="s">
-        <v>209</v>
-      </c>
-      <c r="M6" s="12" t="s">
-        <v>75</v>
+      <c r="B6" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="G6" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="I6" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="J6" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="K6" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="L6" s="11" t="s">
+        <v>223</v>
+      </c>
+      <c r="M6" s="11" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="41" t="n">
+      <c r="A7" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>268</v>
-      </c>
-      <c r="C7" s="34" t="s">
-        <v>269</v>
-      </c>
-      <c r="D7" s="41" t="s">
-        <v>270</v>
-      </c>
-      <c r="E7" s="44" t="n">
+      <c r="B7" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="C7" s="41" t="s">
+        <v>283</v>
+      </c>
+      <c r="D7" s="51" t="s">
+        <v>284</v>
+      </c>
+      <c r="E7" s="54" t="n">
         <v>-113</v>
       </c>
-      <c r="F7" s="36" t="n">
+      <c r="F7" s="55" t="n">
         <v>300</v>
       </c>
-      <c r="G7" s="45" t="n">
+      <c r="G7" s="56" t="n">
         <f aca="false">IF(E7&gt;0,F7*E7/100,F7*100/ABS(E7))</f>
         <v>265.486725663717</v>
       </c>
-      <c r="H7" s="45" t="n">
+      <c r="H7" s="56" t="n">
         <f aca="false">F7+G7</f>
         <v>565.486725663717</v>
       </c>
-      <c r="I7" s="57" t="s">
-        <v>112</v>
-      </c>
-      <c r="J7" s="45" t="n">
+      <c r="I7" s="72" t="s">
+        <v>126</v>
+      </c>
+      <c r="J7" s="56" t="n">
         <f aca="false">IF(I7="Win",F7+G7,IF(I7="Push",F7,IF(I7="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K7" s="47" t="n">
+      <c r="K7" s="58" t="n">
         <f aca="false">IF(I7="Pending",0,J7-F7)</f>
         <v>0</v>
       </c>
-      <c r="L7" s="58" t="n">
+      <c r="L7" s="73" t="n">
         <v>0.58</v>
       </c>
-      <c r="M7" s="62" t="s">
-        <v>271</v>
+      <c r="M7" s="77" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="41" t="n">
+      <c r="A8" s="51" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>272</v>
-      </c>
-      <c r="C8" s="34" t="s">
-        <v>273</v>
-      </c>
-      <c r="D8" s="41" t="s">
-        <v>83</v>
-      </c>
-      <c r="E8" s="44" t="n">
+      <c r="B8" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="C8" s="41" t="s">
+        <v>287</v>
+      </c>
+      <c r="D8" s="51" t="s">
+        <v>97</v>
+      </c>
+      <c r="E8" s="54" t="n">
         <v>456</v>
       </c>
-      <c r="F8" s="36" t="n">
+      <c r="F8" s="55" t="n">
         <v>200</v>
       </c>
-      <c r="G8" s="45" t="n">
+      <c r="G8" s="56" t="n">
         <f aca="false">IF(E8&gt;0,F8*E8/100,F8*100/ABS(E8))</f>
         <v>912</v>
       </c>
-      <c r="H8" s="45" t="n">
+      <c r="H8" s="56" t="n">
         <f aca="false">F8+G8</f>
         <v>1112</v>
       </c>
-      <c r="I8" s="57" t="s">
-        <v>112</v>
-      </c>
-      <c r="J8" s="45" t="n">
+      <c r="I8" s="72" t="s">
+        <v>126</v>
+      </c>
+      <c r="J8" s="56" t="n">
         <f aca="false">IF(I8="Win",F8+G8,IF(I8="Push",F8,IF(I8="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K8" s="47" t="n">
+      <c r="K8" s="58" t="n">
         <f aca="false">IF(I8="Pending",0,J8-F8)</f>
         <v>0</v>
       </c>
-      <c r="L8" s="58" t="n">
+      <c r="L8" s="73" t="n">
         <v>0.24</v>
       </c>
-      <c r="M8" s="62" t="s">
-        <v>274</v>
+      <c r="M8" s="77" t="s">
+        <v>288</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="41" t="n">
+      <c r="A9" s="51" t="n">
         <v>3</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>275</v>
-      </c>
-      <c r="C9" s="34" t="s">
-        <v>276</v>
-      </c>
-      <c r="D9" s="41" t="s">
-        <v>179</v>
-      </c>
-      <c r="E9" s="44" t="n">
+      <c r="B9" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="C9" s="41" t="s">
+        <v>290</v>
+      </c>
+      <c r="D9" s="51" t="s">
+        <v>193</v>
+      </c>
+      <c r="E9" s="54" t="n">
         <v>1150</v>
       </c>
-      <c r="F9" s="36" t="n">
+      <c r="F9" s="55" t="n">
         <v>150</v>
       </c>
-      <c r="G9" s="45" t="n">
+      <c r="G9" s="56" t="n">
         <f aca="false">IF(E9&gt;0,F9*E9/100,F9*100/ABS(E9))</f>
         <v>1725</v>
       </c>
-      <c r="H9" s="45" t="n">
+      <c r="H9" s="56" t="n">
         <f aca="false">F9+G9</f>
         <v>1875</v>
       </c>
-      <c r="I9" s="57" t="s">
-        <v>112</v>
-      </c>
-      <c r="J9" s="45" t="n">
+      <c r="I9" s="72" t="s">
+        <v>126</v>
+      </c>
+      <c r="J9" s="56" t="n">
         <f aca="false">IF(I9="Win",F9+G9,IF(I9="Push",F9,IF(I9="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K9" s="47" t="n">
+      <c r="K9" s="58" t="n">
         <f aca="false">IF(I9="Pending",0,J9-F9)</f>
         <v>0</v>
       </c>
-      <c r="L9" s="58" t="n">
+      <c r="L9" s="73" t="n">
         <v>0.1</v>
       </c>
-      <c r="M9" s="62" t="s">
-        <v>277</v>
+      <c r="M9" s="77" t="s">
+        <v>291</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="41" t="n">
+      <c r="A10" s="51" t="n">
         <v>4</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>278</v>
-      </c>
-      <c r="C10" s="34" t="s">
-        <v>276</v>
-      </c>
-      <c r="D10" s="41" t="s">
-        <v>179</v>
-      </c>
-      <c r="E10" s="44" t="n">
+      <c r="B10" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="C10" s="41" t="s">
+        <v>290</v>
+      </c>
+      <c r="D10" s="51" t="s">
+        <v>193</v>
+      </c>
+      <c r="E10" s="54" t="n">
         <v>1567</v>
       </c>
-      <c r="F10" s="36" t="n">
+      <c r="F10" s="55" t="n">
         <v>120</v>
       </c>
-      <c r="G10" s="45" t="n">
+      <c r="G10" s="56" t="n">
         <f aca="false">IF(E10&gt;0,F10*E10/100,F10*100/ABS(E10))</f>
         <v>1880.4</v>
       </c>
-      <c r="H10" s="45" t="n">
+      <c r="H10" s="56" t="n">
         <f aca="false">F10+G10</f>
         <v>2000.4</v>
       </c>
-      <c r="I10" s="57" t="s">
-        <v>112</v>
-      </c>
-      <c r="J10" s="45" t="n">
+      <c r="I10" s="72" t="s">
+        <v>126</v>
+      </c>
+      <c r="J10" s="56" t="n">
         <f aca="false">IF(I10="Win",F10+G10,IF(I10="Push",F10,IF(I10="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K10" s="47" t="n">
+      <c r="K10" s="58" t="n">
         <f aca="false">IF(I10="Pending",0,J10-F10)</f>
         <v>0</v>
       </c>
-      <c r="L10" s="58" t="n">
+      <c r="L10" s="73" t="n">
         <v>0.08</v>
       </c>
-      <c r="M10" s="62" t="s">
-        <v>279</v>
+      <c r="M10" s="77" t="s">
+        <v>293</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="41" t="n">
+      <c r="A11" s="51" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>280</v>
-      </c>
-      <c r="C11" s="34" t="s">
-        <v>276</v>
-      </c>
-      <c r="D11" s="41" t="s">
-        <v>179</v>
-      </c>
-      <c r="E11" s="44" t="n">
+      <c r="B11" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="C11" s="41" t="s">
+        <v>290</v>
+      </c>
+      <c r="D11" s="51" t="s">
+        <v>193</v>
+      </c>
+      <c r="E11" s="54" t="n">
         <v>1800</v>
       </c>
-      <c r="F11" s="36" t="n">
+      <c r="F11" s="55" t="n">
         <v>100</v>
       </c>
-      <c r="G11" s="45" t="n">
+      <c r="G11" s="56" t="n">
         <f aca="false">IF(E11&gt;0,F11*E11/100,F11*100/ABS(E11))</f>
         <v>1800</v>
       </c>
-      <c r="H11" s="45" t="n">
+      <c r="H11" s="56" t="n">
         <f aca="false">F11+G11</f>
         <v>1900</v>
       </c>
-      <c r="I11" s="57" t="s">
-        <v>112</v>
-      </c>
-      <c r="J11" s="45" t="n">
+      <c r="I11" s="72" t="s">
+        <v>126</v>
+      </c>
+      <c r="J11" s="56" t="n">
         <f aca="false">IF(I11="Win",F11+G11,IF(I11="Push",F11,IF(I11="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K11" s="47" t="n">
+      <c r="K11" s="58" t="n">
         <f aca="false">IF(I11="Pending",0,J11-F11)</f>
         <v>0</v>
       </c>
-      <c r="L11" s="58" t="n">
+      <c r="L11" s="73" t="n">
         <v>0.07</v>
       </c>
-      <c r="M11" s="62" t="s">
-        <v>281</v>
+      <c r="M11" s="77" t="s">
+        <v>295</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="41" t="n">
+      <c r="A12" s="51" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>282</v>
-      </c>
-      <c r="C12" s="34" t="s">
-        <v>276</v>
-      </c>
-      <c r="D12" s="41" t="s">
-        <v>179</v>
-      </c>
-      <c r="E12" s="44" t="n">
+      <c r="B12" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="C12" s="41" t="s">
+        <v>290</v>
+      </c>
+      <c r="D12" s="51" t="s">
+        <v>193</v>
+      </c>
+      <c r="E12" s="54" t="n">
         <v>1150</v>
       </c>
-      <c r="F12" s="36" t="n">
+      <c r="F12" s="55" t="n">
         <v>90</v>
       </c>
-      <c r="G12" s="45" t="n">
+      <c r="G12" s="56" t="n">
         <f aca="false">IF(E12&gt;0,F12*E12/100,F12*100/ABS(E12))</f>
         <v>1035</v>
       </c>
-      <c r="H12" s="45" t="n">
+      <c r="H12" s="56" t="n">
         <f aca="false">F12+G12</f>
         <v>1125</v>
       </c>
-      <c r="I12" s="57" t="s">
-        <v>112</v>
-      </c>
-      <c r="J12" s="45" t="n">
+      <c r="I12" s="72" t="s">
+        <v>126</v>
+      </c>
+      <c r="J12" s="56" t="n">
         <f aca="false">IF(I12="Win",F12+G12,IF(I12="Push",F12,IF(I12="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K12" s="47" t="n">
+      <c r="K12" s="58" t="n">
         <f aca="false">IF(I12="Pending",0,J12-F12)</f>
         <v>0</v>
       </c>
-      <c r="L12" s="58" t="n">
+      <c r="L12" s="73" t="n">
         <v>0.08</v>
       </c>
-      <c r="M12" s="62" t="s">
-        <v>283</v>
+      <c r="M12" s="77" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="41" t="n">
+      <c r="A13" s="51" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>284</v>
-      </c>
-      <c r="C13" s="34" t="s">
-        <v>276</v>
-      </c>
-      <c r="D13" s="41" t="s">
-        <v>179</v>
-      </c>
-      <c r="E13" s="44" t="n">
+      <c r="B13" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="C13" s="41" t="s">
+        <v>290</v>
+      </c>
+      <c r="D13" s="51" t="s">
+        <v>193</v>
+      </c>
+      <c r="E13" s="54" t="n">
         <v>1900</v>
       </c>
-      <c r="F13" s="36" t="n">
+      <c r="F13" s="55" t="n">
         <v>40</v>
       </c>
-      <c r="G13" s="45" t="n">
+      <c r="G13" s="56" t="n">
         <f aca="false">IF(E13&gt;0,F13*E13/100,F13*100/ABS(E13))</f>
         <v>760</v>
       </c>
-      <c r="H13" s="45" t="n">
+      <c r="H13" s="56" t="n">
         <f aca="false">F13+G13</f>
         <v>800</v>
       </c>
-      <c r="I13" s="57" t="s">
-        <v>112</v>
-      </c>
-      <c r="J13" s="45" t="n">
+      <c r="I13" s="72" t="s">
+        <v>126</v>
+      </c>
+      <c r="J13" s="56" t="n">
         <f aca="false">IF(I13="Win",F13+G13,IF(I13="Push",F13,IF(I13="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K13" s="47" t="n">
+      <c r="K13" s="58" t="n">
         <f aca="false">IF(I13="Pending",0,J13-F13)</f>
         <v>0</v>
       </c>
-      <c r="L13" s="58" t="n">
+      <c r="L13" s="73" t="n">
         <v>0.05</v>
       </c>
-      <c r="M13" s="62" t="s">
-        <v>285</v>
+      <c r="M13" s="77" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="29"/>
-      <c r="B14" s="30" t="s">
-        <v>37</v>
-      </c>
-      <c r="C14" s="29"/>
-      <c r="D14" s="29"/>
-      <c r="E14" s="29"/>
-      <c r="F14" s="31" t="n">
+      <c r="A14" s="36"/>
+      <c r="B14" s="37" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14" s="36"/>
+      <c r="D14" s="36"/>
+      <c r="E14" s="36"/>
+      <c r="F14" s="63" t="n">
         <f aca="false">SUM(F7:F13)</f>
         <v>1000</v>
       </c>
-      <c r="G14" s="32" t="n">
+      <c r="G14" s="64" t="n">
         <f aca="false">SUM(G7:G13)</f>
         <v>8377.88672566372</v>
       </c>
-      <c r="H14" s="32" t="n">
+      <c r="H14" s="64" t="n">
         <f aca="false">SUM(H7:H13)</f>
         <v>9377.88672566372</v>
       </c>
-      <c r="I14" s="29"/>
-      <c r="J14" s="32" t="n">
+      <c r="I14" s="36"/>
+      <c r="J14" s="64" t="n">
         <f aca="false">SUM(J7:J13)</f>
         <v>0</v>
       </c>
-      <c r="K14" s="33" t="n">
+      <c r="K14" s="65" t="n">
         <f aca="false">SUM(K7:K13)</f>
         <v>0</v>
       </c>
-      <c r="L14" s="59" t="n">
+      <c r="L14" s="74" t="n">
         <f aca="false">SUM(L7:L13)</f>
         <v>1.2</v>
       </c>
-      <c r="M14" s="29"/>
+      <c r="M14" s="36"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="4" t="s">
-        <v>108</v>
+      <c r="B16" s="50" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="C17" s="52" t="n">
+      <c r="B17" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="C17" s="66" t="n">
         <f aca="false">COUNTIF(I7:I13,"Win")</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="C18" s="52" t="n">
+      <c r="B18" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="C18" s="66" t="n">
         <f aca="false">COUNTIF(I7:I13,"Loss")</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="C19" s="52" t="n">
+      <c r="B19" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="C19" s="66" t="n">
         <f aca="false">COUNTIF(I7:I13,"Push")</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="C20" s="52" t="n">
+      <c r="B20" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="C20" s="66" t="n">
         <f aca="false">COUNTIF(I7:I13,"Pending")</f>
         <v>7</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="C21" s="53" t="str">
+      <c r="B21" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="C21" s="67" t="str">
         <f aca="false">IF(COUNTIF(I7:I13,"Win")+COUNTIF(I7:I13,"Loss")=0,"—",COUNTIF(I7:I13,"Win")/(COUNTIF(I7:I13,"Win")+COUNTIF(I7:I13,"Loss")))</f>
         <v>—</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="C22" s="54" t="n">
+      <c r="B22" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="C22" s="68" t="n">
         <f aca="false">SUM(F7:F13)</f>
         <v>1000</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="C23" s="45" t="n">
+      <c r="B23" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="C23" s="56" t="n">
         <f aca="false">SUM(J7:J13)</f>
         <v>0</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="C24" s="47" t="n">
+      <c r="B24" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="C24" s="58" t="n">
         <f aca="false">SUM(K7:K13)</f>
         <v>0</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="C25" s="53" t="n">
+      <c r="B25" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="C25" s="67" t="n">
         <f aca="false">IF(SUM(F7:F13)=0,"—",SUM(K7:K13)/SUM(F7:F13))</f>
         <v>0</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="5" t="s">
-        <v>234</v>
-      </c>
-      <c r="C26" s="60" t="n">
+      <c r="B26" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="C26" s="75" t="n">
         <f aca="false">SUM(L7:L13)</f>
         <v>1.2</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="5" t="s">
-        <v>286</v>
-      </c>
-      <c r="C27" s="54" t="n">
+      <c r="B27" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="C27" s="68" t="n">
         <f aca="false">2678</f>
         <v>2678</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="38" t="s">
-        <v>287</v>
+      <c r="A29" s="70" t="s">
+        <v>301</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="K7:K14">
-    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>AND(ISNUMBER(K7),K7&gt;0)</formula>
     </cfRule>
-    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>AND(ISNUMBER(K7),K7&lt;0)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C24:C25">
-    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>AND(ISNUMBER(C24),C24&gt;0)</formula>
     </cfRule>
-    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>AND(ISNUMBER(C24),C24&lt;0)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5312,349 +5689,383 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="1" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="46" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="46" width="38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="46" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="46" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="46" width="48"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="39" t="s">
-        <v>288</v>
+      <c r="A1" s="47" t="s">
+        <v>302</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
-        <v>289</v>
+      <c r="A2" s="49" t="s">
+        <v>303</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="12" t="s">
-        <v>290</v>
-      </c>
-      <c r="B4" s="12" t="s">
-        <v>291</v>
-      </c>
-      <c r="C4" s="12" t="s">
-        <v>292</v>
-      </c>
-      <c r="D4" s="12" t="s">
-        <v>293</v>
-      </c>
-      <c r="E4" s="12" t="s">
-        <v>294</v>
-      </c>
-      <c r="F4" s="12" t="s">
-        <v>295</v>
-      </c>
-      <c r="G4" s="12" t="s">
-        <v>75</v>
+      <c r="A4" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>305</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>306</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>307</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>309</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="s">
-        <v>296</v>
-      </c>
-      <c r="B5" s="63" t="s">
-        <v>297</v>
-      </c>
-      <c r="C5" s="64"/>
-      <c r="D5" s="64" t="s">
-        <v>298</v>
-      </c>
-      <c r="E5" s="64" t="s">
-        <v>298</v>
-      </c>
-      <c r="F5" s="64"/>
-      <c r="G5" s="65" t="s">
-        <v>299</v>
+      <c r="A5" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="B5" s="78" t="s">
+        <v>311</v>
+      </c>
+      <c r="C5" s="79"/>
+      <c r="D5" s="79" t="s">
+        <v>312</v>
+      </c>
+      <c r="E5" s="79" t="s">
+        <v>312</v>
+      </c>
+      <c r="F5" s="79"/>
+      <c r="G5" s="80" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="s">
-        <v>300</v>
-      </c>
-      <c r="B6" s="63" t="s">
-        <v>301</v>
-      </c>
-      <c r="C6" s="64" t="s">
-        <v>298</v>
-      </c>
-      <c r="D6" s="64"/>
-      <c r="E6" s="64"/>
-      <c r="F6" s="64"/>
-      <c r="G6" s="65" t="s">
-        <v>302</v>
+      <c r="A6" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="B6" s="78" t="s">
+        <v>315</v>
+      </c>
+      <c r="C6" s="79" t="s">
+        <v>312</v>
+      </c>
+      <c r="D6" s="79"/>
+      <c r="E6" s="79"/>
+      <c r="F6" s="79"/>
+      <c r="G6" s="80" t="s">
+        <v>316</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="s">
-        <v>303</v>
-      </c>
-      <c r="B7" s="63" t="s">
-        <v>304</v>
-      </c>
-      <c r="C7" s="64" t="s">
-        <v>298</v>
-      </c>
-      <c r="D7" s="64"/>
-      <c r="E7" s="64"/>
-      <c r="F7" s="64"/>
-      <c r="G7" s="65" t="s">
-        <v>305</v>
+      <c r="A7" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="B7" s="78" t="s">
+        <v>318</v>
+      </c>
+      <c r="C7" s="79" t="s">
+        <v>312</v>
+      </c>
+      <c r="D7" s="79"/>
+      <c r="E7" s="79"/>
+      <c r="F7" s="79"/>
+      <c r="G7" s="80" t="s">
+        <v>319</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="s">
-        <v>306</v>
-      </c>
-      <c r="B8" s="63" t="s">
-        <v>307</v>
-      </c>
-      <c r="C8" s="64"/>
-      <c r="D8" s="64" t="s">
-        <v>298</v>
-      </c>
-      <c r="E8" s="64"/>
-      <c r="F8" s="64"/>
-      <c r="G8" s="65" t="s">
-        <v>308</v>
+      <c r="A8" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="B8" s="78" t="s">
+        <v>321</v>
+      </c>
+      <c r="C8" s="79"/>
+      <c r="D8" s="79" t="s">
+        <v>312</v>
+      </c>
+      <c r="E8" s="79"/>
+      <c r="F8" s="79"/>
+      <c r="G8" s="80" t="s">
+        <v>322</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="B9" s="63" t="s">
-        <v>310</v>
-      </c>
-      <c r="C9" s="64"/>
-      <c r="D9" s="64" t="s">
-        <v>298</v>
-      </c>
-      <c r="E9" s="64"/>
-      <c r="F9" s="64" t="s">
-        <v>298</v>
-      </c>
-      <c r="G9" s="65" t="s">
-        <v>311</v>
+      <c r="A9" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="B9" s="78" t="s">
+        <v>324</v>
+      </c>
+      <c r="C9" s="79"/>
+      <c r="D9" s="79" t="s">
+        <v>312</v>
+      </c>
+      <c r="E9" s="79"/>
+      <c r="F9" s="79" t="s">
+        <v>312</v>
+      </c>
+      <c r="G9" s="80" t="s">
+        <v>325</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="B10" s="78" t="s">
+        <v>327</v>
+      </c>
+      <c r="C10" s="79"/>
+      <c r="D10" s="79" t="s">
         <v>312</v>
       </c>
-      <c r="B10" s="63" t="s">
-        <v>313</v>
-      </c>
-      <c r="C10" s="64"/>
-      <c r="D10" s="64" t="s">
-        <v>298</v>
-      </c>
-      <c r="E10" s="64" t="s">
-        <v>298</v>
-      </c>
-      <c r="F10" s="64"/>
-      <c r="G10" s="65" t="s">
-        <v>314</v>
+      <c r="E10" s="79" t="s">
+        <v>312</v>
+      </c>
+      <c r="F10" s="79"/>
+      <c r="G10" s="80" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="5" t="s">
-        <v>315</v>
-      </c>
-      <c r="B11" s="63" t="s">
-        <v>316</v>
-      </c>
-      <c r="C11" s="64"/>
-      <c r="D11" s="64" t="s">
-        <v>298</v>
-      </c>
-      <c r="E11" s="64"/>
-      <c r="F11" s="64" t="s">
-        <v>298</v>
-      </c>
-      <c r="G11" s="65" t="s">
-        <v>317</v>
+      <c r="A11" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="B11" s="78" t="s">
+        <v>330</v>
+      </c>
+      <c r="C11" s="79"/>
+      <c r="D11" s="79" t="s">
+        <v>312</v>
+      </c>
+      <c r="E11" s="79"/>
+      <c r="F11" s="79" t="s">
+        <v>312</v>
+      </c>
+      <c r="G11" s="80" t="s">
+        <v>331</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="5" t="s">
-        <v>318</v>
-      </c>
-      <c r="B12" s="63" t="s">
-        <v>319</v>
-      </c>
-      <c r="C12" s="64"/>
-      <c r="D12" s="64" t="s">
-        <v>298</v>
-      </c>
-      <c r="E12" s="64"/>
-      <c r="F12" s="64"/>
-      <c r="G12" s="65" t="s">
-        <v>320</v>
+      <c r="A12" s="4" t="s">
+        <v>332</v>
+      </c>
+      <c r="B12" s="78" t="s">
+        <v>333</v>
+      </c>
+      <c r="C12" s="79"/>
+      <c r="D12" s="79" t="s">
+        <v>312</v>
+      </c>
+      <c r="E12" s="79"/>
+      <c r="F12" s="79"/>
+      <c r="G12" s="80" t="s">
+        <v>334</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="5" t="s">
-        <v>321</v>
-      </c>
-      <c r="B13" s="63" t="s">
-        <v>322</v>
-      </c>
-      <c r="C13" s="64"/>
-      <c r="D13" s="64" t="s">
-        <v>298</v>
-      </c>
-      <c r="E13" s="64"/>
-      <c r="F13" s="64"/>
-      <c r="G13" s="65" t="s">
-        <v>323</v>
+      <c r="A13" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="B13" s="78" t="s">
+        <v>336</v>
+      </c>
+      <c r="C13" s="79"/>
+      <c r="D13" s="79" t="s">
+        <v>312</v>
+      </c>
+      <c r="E13" s="79"/>
+      <c r="F13" s="79"/>
+      <c r="G13" s="80" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="5" t="s">
-        <v>324</v>
-      </c>
-      <c r="B14" s="63" t="s">
-        <v>325</v>
-      </c>
-      <c r="C14" s="64"/>
-      <c r="D14" s="64" t="s">
-        <v>298</v>
-      </c>
-      <c r="E14" s="64"/>
-      <c r="F14" s="64"/>
-      <c r="G14" s="65" t="s">
-        <v>326</v>
+      <c r="A14" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="B14" s="78" t="s">
+        <v>339</v>
+      </c>
+      <c r="C14" s="79"/>
+      <c r="D14" s="79" t="s">
+        <v>312</v>
+      </c>
+      <c r="E14" s="79"/>
+      <c r="F14" s="79"/>
+      <c r="G14" s="80" t="s">
+        <v>340</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="5" t="s">
-        <v>327</v>
-      </c>
-      <c r="B15" s="63" t="s">
-        <v>328</v>
-      </c>
-      <c r="C15" s="64"/>
-      <c r="D15" s="64" t="s">
-        <v>298</v>
-      </c>
-      <c r="E15" s="64"/>
-      <c r="F15" s="64"/>
-      <c r="G15" s="65" t="s">
-        <v>329</v>
+      <c r="A15" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="B15" s="78" t="s">
+        <v>342</v>
+      </c>
+      <c r="C15" s="79"/>
+      <c r="D15" s="79" t="s">
+        <v>312</v>
+      </c>
+      <c r="E15" s="79"/>
+      <c r="F15" s="79"/>
+      <c r="G15" s="80" t="s">
+        <v>343</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="5" t="s">
-        <v>330</v>
-      </c>
-      <c r="B16" s="63" t="s">
-        <v>331</v>
-      </c>
-      <c r="C16" s="64"/>
-      <c r="D16" s="64"/>
-      <c r="E16" s="64" t="s">
-        <v>298</v>
-      </c>
-      <c r="F16" s="64" t="s">
-        <v>298</v>
-      </c>
-      <c r="G16" s="65" t="s">
-        <v>332</v>
+      <c r="A16" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="B16" s="78" t="s">
+        <v>345</v>
+      </c>
+      <c r="C16" s="79"/>
+      <c r="D16" s="79"/>
+      <c r="E16" s="79" t="s">
+        <v>312</v>
+      </c>
+      <c r="F16" s="79" t="s">
+        <v>312</v>
+      </c>
+      <c r="G16" s="80" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="5" t="s">
-        <v>333</v>
-      </c>
-      <c r="B17" s="63" t="s">
-        <v>334</v>
-      </c>
-      <c r="C17" s="64"/>
-      <c r="D17" s="64"/>
-      <c r="E17" s="64" t="s">
-        <v>298</v>
-      </c>
-      <c r="F17" s="64"/>
-      <c r="G17" s="65" t="s">
-        <v>335</v>
+      <c r="A17" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="B17" s="78" t="s">
+        <v>348</v>
+      </c>
+      <c r="C17" s="79"/>
+      <c r="D17" s="79"/>
+      <c r="E17" s="79" t="s">
+        <v>312</v>
+      </c>
+      <c r="F17" s="79"/>
+      <c r="G17" s="80" t="s">
+        <v>349</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="5" t="s">
-        <v>336</v>
-      </c>
-      <c r="B18" s="63" t="s">
-        <v>337</v>
-      </c>
-      <c r="C18" s="64"/>
-      <c r="D18" s="64"/>
-      <c r="E18" s="64" t="s">
-        <v>298</v>
-      </c>
-      <c r="F18" s="64"/>
-      <c r="G18" s="65" t="s">
-        <v>338</v>
+      <c r="A18" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="B18" s="78" t="s">
+        <v>351</v>
+      </c>
+      <c r="C18" s="79"/>
+      <c r="D18" s="79"/>
+      <c r="E18" s="79" t="s">
+        <v>312</v>
+      </c>
+      <c r="F18" s="79"/>
+      <c r="G18" s="80" t="s">
+        <v>352</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="5" t="s">
-        <v>339</v>
-      </c>
-      <c r="B19" s="63" t="s">
-        <v>340</v>
-      </c>
-      <c r="C19" s="64"/>
-      <c r="D19" s="64"/>
-      <c r="E19" s="64"/>
-      <c r="F19" s="64" t="s">
-        <v>298</v>
-      </c>
-      <c r="G19" s="65" t="s">
-        <v>341</v>
+      <c r="A19" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="B19" s="78" t="s">
+        <v>354</v>
+      </c>
+      <c r="C19" s="79"/>
+      <c r="D19" s="79"/>
+      <c r="E19" s="79"/>
+      <c r="F19" s="79" t="s">
+        <v>312</v>
+      </c>
+      <c r="G19" s="80" t="s">
+        <v>355</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="66" t="s">
-        <v>342</v>
-      </c>
-      <c r="B20" s="67" t="s">
-        <v>343</v>
-      </c>
-      <c r="D20" s="68" t="s">
-        <v>298</v>
-      </c>
-      <c r="F20" s="68" t="s">
-        <v>298</v>
-      </c>
-      <c r="G20" s="38" t="s">
-        <v>344</v>
+      <c r="A20" s="81" t="s">
+        <v>356</v>
+      </c>
+      <c r="B20" s="82" t="s">
+        <v>357</v>
+      </c>
+      <c r="D20" s="83" t="s">
+        <v>312</v>
+      </c>
+      <c r="F20" s="83" t="s">
+        <v>312</v>
+      </c>
+      <c r="G20" s="70" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="84" t="s">
+        <v>359</v>
+      </c>
+      <c r="B21" s="85" t="s">
+        <v>360</v>
+      </c>
+      <c r="G21" s="45" t="s">
+        <v>361</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="69" t="s">
-        <v>345</v>
+      <c r="A22" s="84" t="s">
+        <v>362</v>
+      </c>
+      <c r="B22" s="85" t="s">
+        <v>363</v>
+      </c>
+      <c r="G22" s="45" t="s">
+        <v>364</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="3" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="3" t="s">
-        <v>347</v>
-      </c>
-    </row>
+      <c r="A23" s="84" t="s">
+        <v>365</v>
+      </c>
+      <c r="B23" s="85" t="s">
+        <v>366</v>
+      </c>
+      <c r="G23" s="45" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="3" t="s">
-        <v>348</v>
+      <c r="A25" s="86" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="49" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="49" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="49" t="s">
+        <v>371</v>
       </c>
     </row>
   </sheetData>
@@ -5677,564 +6088,564 @@
   <dimension ref="A1:M30"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="9" style="1" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="50"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="46" width="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="46" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="46" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="46" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="46" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="46" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="46" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="9" style="46" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="46" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="46" width="50"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="39" t="s">
-        <v>349</v>
-      </c>
-      <c r="H1" s="56" t="s">
-        <v>350</v>
+      <c r="A1" s="47" t="s">
+        <v>372</v>
+      </c>
+      <c r="H1" s="71" t="s">
+        <v>373</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
-        <v>351</v>
+      <c r="A2" s="49" t="s">
+        <v>374</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
-        <v>352</v>
+      <c r="A3" s="49" t="s">
+        <v>375</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
-        <v>65</v>
+      <c r="A5" s="50" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="C6" s="12" t="s">
-        <v>208</v>
-      </c>
-      <c r="D6" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="E6" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="F6" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="G6" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="H6" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="I6" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="J6" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="K6" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="L6" s="12" t="s">
-        <v>209</v>
-      </c>
-      <c r="M6" s="12" t="s">
-        <v>75</v>
+      <c r="B6" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="G6" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="I6" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="J6" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="K6" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="L6" s="11" t="s">
+        <v>223</v>
+      </c>
+      <c r="M6" s="11" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="41" t="n">
+      <c r="A7" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>353</v>
-      </c>
-      <c r="C7" s="34" t="s">
-        <v>354</v>
-      </c>
-      <c r="D7" s="41" t="s">
-        <v>355</v>
-      </c>
-      <c r="E7" s="44" t="n">
+      <c r="B7" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="C7" s="41" t="s">
+        <v>377</v>
+      </c>
+      <c r="D7" s="51" t="s">
+        <v>378</v>
+      </c>
+      <c r="E7" s="54" t="n">
         <v>-115</v>
       </c>
-      <c r="F7" s="36" t="n">
+      <c r="F7" s="55" t="n">
         <v>200</v>
       </c>
-      <c r="G7" s="45" t="n">
+      <c r="G7" s="56" t="n">
         <f aca="false">IF(E7&gt;0,F7*E7/100,F7*100/ABS(E7))</f>
         <v>173.913043478261</v>
       </c>
-      <c r="H7" s="45" t="n">
+      <c r="H7" s="56" t="n">
         <f aca="false">F7+G7</f>
         <v>373.913043478261</v>
       </c>
-      <c r="I7" s="57" t="s">
-        <v>112</v>
-      </c>
-      <c r="J7" s="45" t="n">
+      <c r="I7" s="72" t="s">
+        <v>126</v>
+      </c>
+      <c r="J7" s="56" t="n">
         <f aca="false">IF(I7="Win",F7+G7,IF(I7="Push",F7,IF(I7="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K7" s="47" t="n">
+      <c r="K7" s="58" t="n">
         <f aca="false">IF(I7="Pending",0,J7-F7)</f>
         <v>0</v>
       </c>
-      <c r="L7" s="58" t="n">
+      <c r="L7" s="73" t="n">
         <v>0.56</v>
       </c>
-      <c r="M7" s="62" t="s">
-        <v>356</v>
+      <c r="M7" s="77" t="s">
+        <v>379</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="41" t="n">
+      <c r="A8" s="51" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>357</v>
-      </c>
-      <c r="C8" s="34" t="s">
-        <v>358</v>
-      </c>
-      <c r="D8" s="41" t="s">
-        <v>168</v>
-      </c>
-      <c r="E8" s="44" t="n">
+      <c r="B8" s="4" t="s">
+        <v>380</v>
+      </c>
+      <c r="C8" s="41" t="s">
+        <v>381</v>
+      </c>
+      <c r="D8" s="51" t="s">
+        <v>182</v>
+      </c>
+      <c r="E8" s="54" t="n">
         <v>-112</v>
       </c>
-      <c r="F8" s="36" t="n">
+      <c r="F8" s="55" t="n">
         <v>150</v>
       </c>
-      <c r="G8" s="45" t="n">
+      <c r="G8" s="56" t="n">
         <f aca="false">IF(E8&gt;0,F8*E8/100,F8*100/ABS(E8))</f>
         <v>133.928571428571</v>
       </c>
-      <c r="H8" s="45" t="n">
+      <c r="H8" s="56" t="n">
         <f aca="false">F8+G8</f>
         <v>283.928571428571</v>
       </c>
-      <c r="I8" s="57" t="s">
-        <v>112</v>
-      </c>
-      <c r="J8" s="45" t="n">
+      <c r="I8" s="72" t="s">
+        <v>126</v>
+      </c>
+      <c r="J8" s="56" t="n">
         <f aca="false">IF(I8="Win",F8+G8,IF(I8="Push",F8,IF(I8="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K8" s="47" t="n">
+      <c r="K8" s="58" t="n">
         <f aca="false">IF(I8="Pending",0,J8-F8)</f>
         <v>0</v>
       </c>
-      <c r="L8" s="58" t="n">
+      <c r="L8" s="73" t="n">
         <v>0.56</v>
       </c>
-      <c r="M8" s="62" t="s">
-        <v>359</v>
+      <c r="M8" s="77" t="s">
+        <v>382</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="41" t="n">
+      <c r="A9" s="51" t="n">
         <v>3</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>360</v>
-      </c>
-      <c r="C9" s="34" t="s">
-        <v>361</v>
-      </c>
-      <c r="D9" s="41" t="s">
-        <v>83</v>
-      </c>
-      <c r="E9" s="44" t="n">
+      <c r="B9" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="C9" s="41" t="s">
+        <v>384</v>
+      </c>
+      <c r="D9" s="51" t="s">
+        <v>97</v>
+      </c>
+      <c r="E9" s="54" t="n">
         <v>-159</v>
       </c>
-      <c r="F9" s="36" t="n">
+      <c r="F9" s="55" t="n">
         <v>150</v>
       </c>
-      <c r="G9" s="45" t="n">
+      <c r="G9" s="56" t="n">
         <f aca="false">IF(E9&gt;0,F9*E9/100,F9*100/ABS(E9))</f>
         <v>94.3396226415094</v>
       </c>
-      <c r="H9" s="45" t="n">
+      <c r="H9" s="56" t="n">
         <f aca="false">F9+G9</f>
         <v>244.339622641509</v>
       </c>
-      <c r="I9" s="57" t="s">
-        <v>112</v>
-      </c>
-      <c r="J9" s="45" t="n">
+      <c r="I9" s="72" t="s">
+        <v>126</v>
+      </c>
+      <c r="J9" s="56" t="n">
         <f aca="false">IF(I9="Win",F9+G9,IF(I9="Push",F9,IF(I9="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K9" s="47" t="n">
+      <c r="K9" s="58" t="n">
         <f aca="false">IF(I9="Pending",0,J9-F9)</f>
         <v>0</v>
       </c>
-      <c r="L9" s="58" t="n">
+      <c r="L9" s="73" t="n">
         <v>0.65</v>
       </c>
-      <c r="M9" s="62" t="s">
-        <v>362</v>
+      <c r="M9" s="77" t="s">
+        <v>385</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="41" t="n">
+      <c r="A10" s="51" t="n">
         <v>4</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>363</v>
-      </c>
-      <c r="C10" s="34" t="s">
-        <v>364</v>
-      </c>
-      <c r="D10" s="41" t="s">
-        <v>355</v>
-      </c>
-      <c r="E10" s="44" t="n">
+      <c r="B10" s="4" t="s">
+        <v>386</v>
+      </c>
+      <c r="C10" s="41" t="s">
+        <v>387</v>
+      </c>
+      <c r="D10" s="51" t="s">
+        <v>378</v>
+      </c>
+      <c r="E10" s="54" t="n">
         <v>-108</v>
       </c>
-      <c r="F10" s="36" t="n">
+      <c r="F10" s="55" t="n">
         <v>150</v>
       </c>
-      <c r="G10" s="45" t="n">
+      <c r="G10" s="56" t="n">
         <f aca="false">IF(E10&gt;0,F10*E10/100,F10*100/ABS(E10))</f>
         <v>138.888888888889</v>
       </c>
-      <c r="H10" s="45" t="n">
+      <c r="H10" s="56" t="n">
         <f aca="false">F10+G10</f>
         <v>288.888888888889</v>
       </c>
-      <c r="I10" s="57" t="s">
-        <v>112</v>
-      </c>
-      <c r="J10" s="45" t="n">
+      <c r="I10" s="72" t="s">
+        <v>126</v>
+      </c>
+      <c r="J10" s="56" t="n">
         <f aca="false">IF(I10="Win",F10+G10,IF(I10="Push",F10,IF(I10="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K10" s="47" t="n">
+      <c r="K10" s="58" t="n">
         <f aca="false">IF(I10="Pending",0,J10-F10)</f>
         <v>0</v>
       </c>
-      <c r="L10" s="58" t="n">
+      <c r="L10" s="73" t="n">
         <v>0.55</v>
       </c>
-      <c r="M10" s="62" t="s">
-        <v>365</v>
+      <c r="M10" s="77" t="s">
+        <v>388</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="41" t="n">
+      <c r="A11" s="51" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>366</v>
-      </c>
-      <c r="C11" s="34" t="s">
-        <v>367</v>
-      </c>
-      <c r="D11" s="41" t="s">
-        <v>83</v>
-      </c>
-      <c r="E11" s="44" t="n">
+      <c r="B11" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="C11" s="41" t="s">
+        <v>390</v>
+      </c>
+      <c r="D11" s="51" t="s">
+        <v>97</v>
+      </c>
+      <c r="E11" s="54" t="n">
         <v>-120</v>
       </c>
-      <c r="F11" s="36" t="n">
+      <c r="F11" s="55" t="n">
         <v>130</v>
       </c>
-      <c r="G11" s="45" t="n">
+      <c r="G11" s="56" t="n">
         <f aca="false">IF(E11&gt;0,F11*E11/100,F11*100/ABS(E11))</f>
         <v>108.333333333333</v>
       </c>
-      <c r="H11" s="45" t="n">
+      <c r="H11" s="56" t="n">
         <f aca="false">F11+G11</f>
         <v>238.333333333333</v>
       </c>
-      <c r="I11" s="57" t="s">
-        <v>112</v>
-      </c>
-      <c r="J11" s="45" t="n">
+      <c r="I11" s="72" t="s">
+        <v>126</v>
+      </c>
+      <c r="J11" s="56" t="n">
         <f aca="false">IF(I11="Win",F11+G11,IF(I11="Push",F11,IF(I11="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K11" s="47" t="n">
+      <c r="K11" s="58" t="n">
         <f aca="false">IF(I11="Pending",0,J11-F11)</f>
         <v>0</v>
       </c>
-      <c r="L11" s="58" t="n">
+      <c r="L11" s="73" t="n">
         <v>0.6</v>
       </c>
-      <c r="M11" s="62" t="s">
-        <v>368</v>
+      <c r="M11" s="77" t="s">
+        <v>391</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="41" t="n">
+      <c r="A12" s="51" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>369</v>
-      </c>
-      <c r="C12" s="34" t="s">
-        <v>370</v>
-      </c>
-      <c r="D12" s="41" t="s">
-        <v>83</v>
-      </c>
-      <c r="E12" s="44" t="n">
+      <c r="B12" s="4" t="s">
+        <v>392</v>
+      </c>
+      <c r="C12" s="41" t="s">
+        <v>393</v>
+      </c>
+      <c r="D12" s="51" t="s">
+        <v>97</v>
+      </c>
+      <c r="E12" s="54" t="n">
         <v>-121</v>
       </c>
-      <c r="F12" s="36" t="n">
+      <c r="F12" s="55" t="n">
         <v>120</v>
       </c>
-      <c r="G12" s="45" t="n">
+      <c r="G12" s="56" t="n">
         <f aca="false">IF(E12&gt;0,F12*E12/100,F12*100/ABS(E12))</f>
         <v>99.1735537190083</v>
       </c>
-      <c r="H12" s="45" t="n">
+      <c r="H12" s="56" t="n">
         <f aca="false">F12+G12</f>
         <v>219.173553719008</v>
       </c>
-      <c r="I12" s="57" t="s">
-        <v>112</v>
-      </c>
-      <c r="J12" s="45" t="n">
+      <c r="I12" s="72" t="s">
+        <v>126</v>
+      </c>
+      <c r="J12" s="56" t="n">
         <f aca="false">IF(I12="Win",F12+G12,IF(I12="Push",F12,IF(I12="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K12" s="47" t="n">
+      <c r="K12" s="58" t="n">
         <f aca="false">IF(I12="Pending",0,J12-F12)</f>
         <v>0</v>
       </c>
-      <c r="L12" s="58" t="n">
+      <c r="L12" s="73" t="n">
         <v>0.58</v>
       </c>
-      <c r="M12" s="62" t="s">
-        <v>371</v>
+      <c r="M12" s="77" t="s">
+        <v>394</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="41" t="n">
+      <c r="A13" s="51" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>372</v>
-      </c>
-      <c r="C13" s="34" t="s">
-        <v>373</v>
-      </c>
-      <c r="D13" s="41" t="s">
-        <v>106</v>
-      </c>
-      <c r="E13" s="44" t="n">
+      <c r="B13" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="C13" s="41" t="s">
+        <v>396</v>
+      </c>
+      <c r="D13" s="51" t="s">
+        <v>120</v>
+      </c>
+      <c r="E13" s="54" t="n">
         <v>971</v>
       </c>
-      <c r="F13" s="36" t="n">
+      <c r="F13" s="55" t="n">
         <v>100</v>
       </c>
-      <c r="G13" s="45" t="n">
+      <c r="G13" s="56" t="n">
         <f aca="false">IF(E13&gt;0,F13*E13/100,F13*100/ABS(E13))</f>
         <v>971</v>
       </c>
-      <c r="H13" s="45" t="n">
+      <c r="H13" s="56" t="n">
         <f aca="false">F13+G13</f>
         <v>1071</v>
       </c>
-      <c r="I13" s="57" t="s">
-        <v>112</v>
-      </c>
-      <c r="J13" s="45" t="n">
+      <c r="I13" s="72" t="s">
+        <v>126</v>
+      </c>
+      <c r="J13" s="56" t="n">
         <f aca="false">IF(I13="Win",F13+G13,IF(I13="Push",F13,IF(I13="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K13" s="47" t="n">
+      <c r="K13" s="58" t="n">
         <f aca="false">IF(I13="Pending",0,J13-F13)</f>
         <v>0</v>
       </c>
-      <c r="L13" s="58" t="n">
+      <c r="L13" s="73" t="n">
         <v>0.12</v>
       </c>
-      <c r="M13" s="62" t="s">
-        <v>374</v>
+      <c r="M13" s="77" t="s">
+        <v>397</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="29"/>
-      <c r="B14" s="30" t="s">
-        <v>37</v>
-      </c>
-      <c r="C14" s="29"/>
-      <c r="D14" s="29"/>
-      <c r="E14" s="29"/>
-      <c r="F14" s="31" t="n">
+      <c r="A14" s="36"/>
+      <c r="B14" s="37" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14" s="36"/>
+      <c r="D14" s="36"/>
+      <c r="E14" s="36"/>
+      <c r="F14" s="63" t="n">
         <f aca="false">SUM(F7:F13)</f>
         <v>1000</v>
       </c>
-      <c r="G14" s="32" t="n">
+      <c r="G14" s="64" t="n">
         <f aca="false">SUM(G7:G13)</f>
         <v>1719.57701348957</v>
       </c>
-      <c r="H14" s="32" t="n">
+      <c r="H14" s="64" t="n">
         <f aca="false">SUM(H7:H13)</f>
         <v>2719.57701348957</v>
       </c>
-      <c r="I14" s="29"/>
-      <c r="J14" s="32" t="n">
+      <c r="I14" s="36"/>
+      <c r="J14" s="64" t="n">
         <f aca="false">SUM(J7:J13)</f>
         <v>0</v>
       </c>
-      <c r="K14" s="33" t="n">
+      <c r="K14" s="65" t="n">
         <f aca="false">SUM(K7:K13)</f>
         <v>0</v>
       </c>
-      <c r="L14" s="59" t="n">
+      <c r="L14" s="74" t="n">
         <f aca="false">SUM(L7:L13)</f>
         <v>3.62</v>
       </c>
-      <c r="M14" s="29"/>
+      <c r="M14" s="36"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="4" t="s">
-        <v>108</v>
+      <c r="B16" s="50" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="C17" s="52" t="n">
+      <c r="B17" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="C17" s="66" t="n">
         <f aca="false">COUNTIF(I7:I13,"Win")</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="C18" s="52" t="n">
+      <c r="B18" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="C18" s="66" t="n">
         <f aca="false">COUNTIF(I7:I13,"Loss")</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="C19" s="52" t="n">
+      <c r="B19" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="C19" s="66" t="n">
         <f aca="false">COUNTIF(I7:I13,"Push")</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="C20" s="52" t="n">
+      <c r="B20" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="C20" s="66" t="n">
         <f aca="false">COUNTIF(I7:I13,"Pending")</f>
         <v>7</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="C21" s="53" t="str">
+      <c r="B21" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="C21" s="67" t="str">
         <f aca="false">IF(COUNTIF(I7:I13,"Win")+COUNTIF(I7:I13,"Loss")=0,"—",COUNTIF(I7:I13,"Win")/(COUNTIF(I7:I13,"Win")+COUNTIF(I7:I13,"Loss")))</f>
         <v>—</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="C22" s="54" t="n">
+      <c r="B22" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="C22" s="68" t="n">
         <f aca="false">SUM(F7:F13)</f>
         <v>1000</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="C23" s="45" t="n">
+      <c r="B23" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="C23" s="56" t="n">
         <f aca="false">SUM(J7:J13)</f>
         <v>0</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="C24" s="47" t="n">
+      <c r="B24" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="C24" s="58" t="n">
         <f aca="false">SUM(K7:K13)</f>
         <v>0</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="C25" s="53" t="n">
+      <c r="B25" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="C25" s="67" t="n">
         <f aca="false">IF(SUM(F7:F13)=0,"—",SUM(K7:K13)/SUM(F7:F13))</f>
         <v>0</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="C26" s="45" t="n">
+      <c r="B26" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C26" s="56" t="n">
         <f aca="false">SUM(H7:H13)</f>
         <v>2719.57701348957</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="5" t="s">
-        <v>234</v>
-      </c>
-      <c r="C27" s="60" t="n">
+      <c r="B27" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="C27" s="75" t="n">
         <f aca="false">SUM(L7:L13)</f>
         <v>3.62</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="C28" s="47" t="n">
+      <c r="B28" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="C28" s="58" t="n">
         <f aca="false">SUMPRODUCT(L7:L13,G7:G13)-SUMPRODUCT(1-L7:L13,F7:F13)</f>
         <v>84.7416091107209</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="38" t="s">
-        <v>375</v>
+      <c r="A30" s="70" t="s">
+        <v>398</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="K7:K14">
-    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>AND(ISNUMBER(K7),K7&gt;0)</formula>
     </cfRule>
-    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>AND(ISNUMBER(K7),K7&lt;0)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C24:C25">
-    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>AND(ISNUMBER(C24),C24&gt;0)</formula>
     </cfRule>
-    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>AND(ISNUMBER(C24),C24&lt;0)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6252,4 +6663,529 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FF1B7A3D"/>
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:M24"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="9" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="50"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="87" t="s">
+        <v>399</v>
+      </c>
+      <c r="H1" s="88" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="G6" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="I6" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="J6" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="K6" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="L6" s="11" t="s">
+        <v>223</v>
+      </c>
+      <c r="M6" s="11" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>403</v>
+      </c>
+      <c r="C7" s="41" t="s">
+        <v>290</v>
+      </c>
+      <c r="D7" s="51" t="s">
+        <v>193</v>
+      </c>
+      <c r="E7" s="54" t="n">
+        <v>450</v>
+      </c>
+      <c r="F7" s="43" t="n">
+        <v>200</v>
+      </c>
+      <c r="G7" s="89" t="n">
+        <f aca="false">IF(E7&gt;0,F7*E7/100,F7*100/ABS(E7))</f>
+        <v>900</v>
+      </c>
+      <c r="H7" s="89" t="n">
+        <f aca="false">F7+G7</f>
+        <v>1100</v>
+      </c>
+      <c r="I7" s="72" t="s">
+        <v>126</v>
+      </c>
+      <c r="J7" s="89" t="n">
+        <f aca="false">IF(I7="Win",F7+G7,IF(I7="Push",F7,IF(I7="Loss",0,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="K7" s="90" t="n">
+        <f aca="false">IF(I7="Pending",0,J7-F7)</f>
+        <v>0</v>
+      </c>
+      <c r="L7" s="91" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="M7" s="77" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="51" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>405</v>
+      </c>
+      <c r="C8" s="41" t="s">
+        <v>290</v>
+      </c>
+      <c r="D8" s="51" t="s">
+        <v>193</v>
+      </c>
+      <c r="E8" s="54" t="n">
+        <v>1600</v>
+      </c>
+      <c r="F8" s="43" t="n">
+        <v>100</v>
+      </c>
+      <c r="G8" s="89" t="n">
+        <f aca="false">IF(E8&gt;0,F8*E8/100,F8*100/ABS(E8))</f>
+        <v>1600</v>
+      </c>
+      <c r="H8" s="89" t="n">
+        <f aca="false">F8+G8</f>
+        <v>1700</v>
+      </c>
+      <c r="I8" s="72" t="s">
+        <v>126</v>
+      </c>
+      <c r="J8" s="89" t="n">
+        <f aca="false">IF(I8="Win",F8+G8,IF(I8="Push",F8,IF(I8="Loss",0,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="K8" s="90" t="n">
+        <f aca="false">IF(I8="Pending",0,J8-F8)</f>
+        <v>0</v>
+      </c>
+      <c r="L8" s="91" t="n">
+        <v>0.07</v>
+      </c>
+      <c r="M8" s="77" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="51" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>407</v>
+      </c>
+      <c r="C9" s="41" t="s">
+        <v>290</v>
+      </c>
+      <c r="D9" s="51" t="s">
+        <v>193</v>
+      </c>
+      <c r="E9" s="54" t="n">
+        <v>1600</v>
+      </c>
+      <c r="F9" s="43" t="n">
+        <v>100</v>
+      </c>
+      <c r="G9" s="89" t="n">
+        <f aca="false">IF(E9&gt;0,F9*E9/100,F9*100/ABS(E9))</f>
+        <v>1600</v>
+      </c>
+      <c r="H9" s="89" t="n">
+        <f aca="false">F9+G9</f>
+        <v>1700</v>
+      </c>
+      <c r="I9" s="72" t="s">
+        <v>126</v>
+      </c>
+      <c r="J9" s="89" t="n">
+        <f aca="false">IF(I9="Win",F9+G9,IF(I9="Push",F9,IF(I9="Loss",0,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="K9" s="90" t="n">
+        <f aca="false">IF(I9="Pending",0,J9-F9)</f>
+        <v>0</v>
+      </c>
+      <c r="L9" s="91" t="n">
+        <v>0.07</v>
+      </c>
+      <c r="M9" s="77" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="51" t="n">
+        <v>4</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>409</v>
+      </c>
+      <c r="C10" s="41" t="s">
+        <v>290</v>
+      </c>
+      <c r="D10" s="51" t="s">
+        <v>193</v>
+      </c>
+      <c r="E10" s="54" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F10" s="43" t="n">
+        <v>80</v>
+      </c>
+      <c r="G10" s="89" t="n">
+        <f aca="false">IF(E10&gt;0,F10*E10/100,F10*100/ABS(E10))</f>
+        <v>1600</v>
+      </c>
+      <c r="H10" s="89" t="n">
+        <f aca="false">F10+G10</f>
+        <v>1680</v>
+      </c>
+      <c r="I10" s="72" t="s">
+        <v>126</v>
+      </c>
+      <c r="J10" s="89" t="n">
+        <f aca="false">IF(I10="Win",F10+G10,IF(I10="Push",F10,IF(I10="Loss",0,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="K10" s="90" t="n">
+        <f aca="false">IF(I10="Pending",0,J10-F10)</f>
+        <v>0</v>
+      </c>
+      <c r="L10" s="91" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="M10" s="77" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="51" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>411</v>
+      </c>
+      <c r="C11" s="41" t="s">
+        <v>290</v>
+      </c>
+      <c r="D11" s="51" t="s">
+        <v>193</v>
+      </c>
+      <c r="E11" s="54" t="n">
+        <v>2800</v>
+      </c>
+      <c r="F11" s="43" t="n">
+        <v>70</v>
+      </c>
+      <c r="G11" s="89" t="n">
+        <f aca="false">IF(E11&gt;0,F11*E11/100,F11*100/ABS(E11))</f>
+        <v>1960</v>
+      </c>
+      <c r="H11" s="89" t="n">
+        <f aca="false">F11+G11</f>
+        <v>2030</v>
+      </c>
+      <c r="I11" s="72" t="s">
+        <v>126</v>
+      </c>
+      <c r="J11" s="89" t="n">
+        <f aca="false">IF(I11="Win",F11+G11,IF(I11="Push",F11,IF(I11="Loss",0,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="K11" s="90" t="n">
+        <f aca="false">IF(I11="Pending",0,J11-F11)</f>
+        <v>0</v>
+      </c>
+      <c r="L11" s="91" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="M11" s="77" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="51" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>413</v>
+      </c>
+      <c r="C12" s="41" t="s">
+        <v>290</v>
+      </c>
+      <c r="D12" s="51" t="s">
+        <v>193</v>
+      </c>
+      <c r="E12" s="54" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F12" s="43" t="n">
+        <v>50</v>
+      </c>
+      <c r="G12" s="89" t="n">
+        <f aca="false">IF(E12&gt;0,F12*E12/100,F12*100/ABS(E12))</f>
+        <v>2500</v>
+      </c>
+      <c r="H12" s="89" t="n">
+        <f aca="false">F12+G12</f>
+        <v>2550</v>
+      </c>
+      <c r="I12" s="72" t="s">
+        <v>126</v>
+      </c>
+      <c r="J12" s="89" t="n">
+        <f aca="false">IF(I12="Win",F12+G12,IF(I12="Push",F12,IF(I12="Loss",0,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="K12" s="90" t="n">
+        <f aca="false">IF(I12="Pending",0,J12-F12)</f>
+        <v>0</v>
+      </c>
+      <c r="L12" s="91" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="M12" s="77" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="27" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" s="21" t="s">
+        <v>415</v>
+      </c>
+      <c r="C13" s="27" t="s">
+        <v>416</v>
+      </c>
+      <c r="D13" s="27" t="s">
+        <v>68</v>
+      </c>
+      <c r="E13" s="27"/>
+      <c r="F13" s="27"/>
+      <c r="G13" s="27"/>
+      <c r="H13" s="27"/>
+      <c r="I13" s="27"/>
+      <c r="J13" s="27"/>
+      <c r="K13" s="27"/>
+      <c r="L13" s="27"/>
+      <c r="M13" s="27" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="36"/>
+      <c r="B14" s="37" t="s">
+        <v>418</v>
+      </c>
+      <c r="C14" s="36"/>
+      <c r="D14" s="36"/>
+      <c r="E14" s="36"/>
+      <c r="F14" s="38" t="n">
+        <f aca="false">SUM(F7:F13)</f>
+        <v>600</v>
+      </c>
+      <c r="G14" s="39" t="n">
+        <f aca="false">SUM(G7:G12)</f>
+        <v>10160</v>
+      </c>
+      <c r="H14" s="39" t="n">
+        <f aca="false">SUM(H7:H12)</f>
+        <v>10760</v>
+      </c>
+      <c r="I14" s="36"/>
+      <c r="J14" s="39" t="n">
+        <f aca="false">SUM(J7:J12)</f>
+        <v>0</v>
+      </c>
+      <c r="K14" s="40" t="n">
+        <f aca="false">SUM(K7:K12)</f>
+        <v>0</v>
+      </c>
+      <c r="L14" s="92" t="n">
+        <f aca="false">SUM(L7:L12)</f>
+        <v>0.445</v>
+      </c>
+      <c r="M14" s="36"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="3" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="C17" s="66" t="n">
+        <f aca="false">COUNTIF(I7:I12,"Win")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="C18" s="66" t="n">
+        <f aca="false">COUNTIF(I7:I12,"Loss")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="C19" s="66" t="n">
+        <f aca="false">COUNTIF(I7:I12,"Pending")</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="C20" s="67" t="str">
+        <f aca="false">IF(COUNTIF(I7:I12,"Win")+COUNTIF(I7:I12,"Loss")=0,"—",COUNTIF(I7:I12,"Win")/(COUNTIF(I7:I12,"Win")+COUNTIF(I7:I12,"Loss")))</f>
+        <v>—</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="4" t="s">
+        <v>419</v>
+      </c>
+      <c r="C21" s="93" t="n">
+        <f aca="false">SUM(F7:F12)</f>
+        <v>600</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="C22" s="89" t="n">
+        <f aca="false">SUM(J7:J12)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="C23" s="90" t="n">
+        <f aca="false">SUM(K7:K12)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="4" t="s">
+        <v>420</v>
+      </c>
+      <c r="C24" s="67" t="n">
+        <f aca="false">SUM(L7:L12)</f>
+        <v>0.445</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="K7:K14">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>AND(ISNUMBER(K7),K7&gt;0)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+      <formula>AND(ISNUMBER(K7),K7&lt;0)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C23">
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>AND(ISNUMBER(C23),C23&gt;0)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+      <formula>AND(ISNUMBER(C23),C23&lt;0)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="I7:I12" type="list">
+      <formula1>"Pending,Win,Loss,Push"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
 </file>
--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -104,7 +104,7 @@
     <t xml:space="preserve">ACTIVE</t>
   </si>
   <si>
-    <t xml:space="preserve">Tab: WNBA Jul 12 · Sky@Wings 7 ET, Fever@Aces 9 ET</t>
+    <t xml:space="preserve">Tab: WNBA Jul 12 · Game 1: 1-3 incl. parlay (-$355.66) · Aces game live</t>
   </si>
   <si>
     <t xml:space="preserve">NASCAR Quaker State 400</t>
@@ -1148,7 +1148,7 @@
     <t xml:space="preserve">TEST 5 — WNBA SUNDAY NIGHT DOUBLEHEADER · JULY 12, 2026</t>
   </si>
   <si>
-    <t xml:space="preserve">STATUS: ACTIVE — games 7 &amp; 9 PM ET tonight</t>
+    <t xml:space="preserve">STATUS: ACTIVE — Game 1 graded 1-2; Fever@Aces in progress</t>
   </si>
   <si>
     <t xml:space="preserve">Sky @ Wings 7 PM ET (ESPN) · Fever @ Aces 9 PM ET (NBC) · Source: wnba-jul12-betting-card.html · Lines: FanDuel via SI Betting / Covers, ~5 PM CT</t>
@@ -1166,7 +1166,7 @@
     <t xml:space="preserve">Spread</t>
   </si>
   <si>
-    <t xml:space="preserve">Sky missing Carrington + Diggins; Wings 15-8, 2nd in O-rating last 10</t>
+    <t xml:space="preserve">Sky missing Carrington + Diggins; Wings 15-8, 2nd in O-rating last 10 · RESULT: DAL 82-79 — won by 3, spread dead</t>
   </si>
   <si>
     <t xml:space="preserve">Sky @ Wings Over 177.5</t>
@@ -1175,7 +1175,7 @@
     <t xml:space="preserve">Game 1 total</t>
   </si>
   <si>
-    <t xml:space="preserve">185 &amp; 188 combined in first two meetings; Sky 3rd in pace, over 8 of last 10</t>
+    <t xml:space="preserve">185 &amp; 188 combined in first two meetings; Sky 3rd in pace, over 8 of last 10 · RESULT: 161 combined — 16.5 under the number</t>
   </si>
   <si>
     <t xml:space="preserve">Paige Bueckers 20+ Points</t>
@@ -1184,7 +1184,7 @@
     <t xml:space="preserve">Wings G · player prop</t>
   </si>
   <si>
-    <t xml:space="preserve">22+ in 6 of last 7; 20.6 PPG; Sky 10th in D-rating</t>
+    <t xml:space="preserve">22+ in 6 of last 7; 20.6 PPG; Sky 10th in D-rating · RESULT: Bueckers 20 pts (6-13 FG, 7-8 FT) — cleared at the buzzer of our line</t>
   </si>
   <si>
     <t xml:space="preserve">Aces -4.5</t>
@@ -1220,7 +1220,7 @@
     <t xml:space="preserve">Wings -9.5 / Aces -4.5 / Bueckers 20+ / Mitchell 3+ threes</t>
   </si>
   <si>
-    <t xml:space="preserve">Stacks our four highest-confidence legs · counts in longshot record</t>
+    <t xml:space="preserve">Stacks our four highest-confidence legs · counts in longshot record · RESULT: Wings -9.5 leg dead → parlay dead (longshot MISS)</t>
   </si>
   <si>
     <t xml:space="preserve">Yellow = fill in results (dropdown). Blue = inputs. Black = formulas. Parlay odds +971 = (-115 × -108 × -159 × -121) compounded; grades as one bet.</t>
@@ -1296,21 +1296,18 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="14">
+  <numFmts count="11">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="\$#,##0"/>
     <numFmt numFmtId="166" formatCode="\$#,##0.00;&quot;($&quot;#,##0.00\);\-"/>
     <numFmt numFmtId="167" formatCode="\$#,##0.00"/>
     <numFmt numFmtId="168" formatCode="\+0;\-0"/>
-    <numFmt numFmtId="169" formatCode="\$#,##0"/>
-    <numFmt numFmtId="170" formatCode="\$#,##0.00"/>
-    <numFmt numFmtId="171" formatCode="\$#,##0.00;&quot;($&quot;#,##0.00\);\-"/>
-    <numFmt numFmtId="172" formatCode="0"/>
-    <numFmt numFmtId="173" formatCode="0.0%"/>
-    <numFmt numFmtId="174" formatCode="0%"/>
-    <numFmt numFmtId="175" formatCode="0.0&quot; exp. wins&quot;"/>
-    <numFmt numFmtId="176" formatCode="0.0"/>
-    <numFmt numFmtId="177" formatCode="0.00&quot; exp. wins&quot;"/>
+    <numFmt numFmtId="169" formatCode="0"/>
+    <numFmt numFmtId="170" formatCode="0.0%"/>
+    <numFmt numFmtId="171" formatCode="0%"/>
+    <numFmt numFmtId="172" formatCode="0.0&quot; exp. wins&quot;"/>
+    <numFmt numFmtId="173" formatCode="0.0"/>
+    <numFmt numFmtId="174" formatCode="0.00&quot; exp. wins&quot;"/>
   </numFmts>
   <fonts count="25">
     <font>
@@ -1610,20 +1607,24 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="94">
+  <cellXfs count="80">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1791,11 +1792,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1807,14 +1804,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1831,7 +1820,35 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1839,43 +1856,27 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="171" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="171" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="172" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="172" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1883,38 +1884,6 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="174" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="175" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="176" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1947,43 +1916,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="24" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="173" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="177" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="174" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1996,35 +1937,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="4">
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <charset val="1"/>
-        <family val="0"/>
-        <b val="1"/>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <charset val="1"/>
-        <family val="0"/>
-        <b val="1"/>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="2">
     <dxf>
       <font>
         <name val="Arial"/>
@@ -2301,567 +2214,567 @@
   <dimension ref="A1:J38"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="6" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="6" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="46"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="5" t="n">
+      <c r="B5" s="6" t="n">
         <v>5000</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="6" t="n">
+      <c r="B6" s="7" t="n">
         <f aca="false">H23</f>
-        <v>-32.6573691041808</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+        <v>-388.317746462671</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="7" t="n">
+      <c r="B7" s="8" t="n">
         <f aca="false">B5+B6</f>
-        <v>4967.34263089582</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
+        <v>4611.68225353733</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="8" t="n">
+      <c r="B8" s="9" t="n">
         <f aca="false">F23</f>
-        <v>3600</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="7" t="n">
+      <c r="B9" s="8" t="n">
         <f aca="false">B7-B8</f>
-        <v>1367.34263089582</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
+        <v>1611.68225353733</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="9" t="str">
+      <c r="B10" s="10" t="str">
         <f aca="false">COUNTIF(D16:D22,"ACTIVE")&amp;" of 4 max"</f>
         <v>4 of 4 max</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="11" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="4" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="11" t="s">
+      <c r="A15" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B15" s="11" t="s">
+      <c r="B15" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="11" t="s">
+      <c r="C15" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="D15" s="11" t="s">
+      <c r="D15" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="E15" s="11" t="s">
+      <c r="E15" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="F15" s="11" t="s">
+      <c r="F15" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G15" s="11" t="s">
+      <c r="G15" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="H15" s="11" t="s">
+      <c r="H15" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="I15" s="11" t="s">
+      <c r="I15" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="J15" s="11" t="s">
+      <c r="J15" s="12" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="12" t="n">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="B16" s="13" t="s">
+      <c r="B16" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="C16" s="12" t="s">
+      <c r="C16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="D16" s="14" t="s">
+      <c r="D16" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="E16" s="15" t="n">
+      <c r="E16" s="16" t="n">
         <f aca="false">SUM('WNBA Jul 12'!F7:F13)</f>
         <v>1000</v>
       </c>
-      <c r="F16" s="15" t="n">
+      <c r="F16" s="16" t="n">
         <f aca="false">SUMIF('WNBA Jul 12'!I7:I13,"Pending",'WNBA Jul 12'!F7:F13)</f>
-        <v>1000</v>
-      </c>
-      <c r="G16" s="16" t="n">
+        <v>400</v>
+      </c>
+      <c r="G16" s="17" t="n">
         <f aca="false">SUM('WNBA Jul 12'!J7:J13)</f>
-        <v>0</v>
-      </c>
-      <c r="H16" s="17" t="n">
+        <v>244.339622641509</v>
+      </c>
+      <c r="H16" s="18" t="n">
         <f aca="false">SUM('WNBA Jul 12'!K7:K13)</f>
-        <v>0</v>
-      </c>
-      <c r="I16" s="18" t="n">
+        <v>-355.660377358491</v>
+      </c>
+      <c r="I16" s="19" t="n">
         <f aca="false">B5+H16</f>
-        <v>5000</v>
-      </c>
-      <c r="J16" s="19" t="s">
+        <v>4644.33962264151</v>
+      </c>
+      <c r="J16" s="20" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="12" t="n">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="B17" s="13" t="s">
+      <c r="B17" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="C17" s="12" t="s">
+      <c r="C17" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="D17" s="14" t="s">
+      <c r="D17" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="E17" s="15" t="n">
+      <c r="E17" s="16" t="n">
         <f aca="false">SUM('NASCAR Jul 12'!F7:F13)</f>
         <v>1000</v>
       </c>
-      <c r="F17" s="15" t="n">
+      <c r="F17" s="16" t="n">
         <f aca="false">SUMIF('NASCAR Jul 12'!I7:I13,"Pending",'NASCAR Jul 12'!F7:F13)</f>
         <v>1000</v>
       </c>
-      <c r="G17" s="16" t="n">
+      <c r="G17" s="17" t="n">
         <f aca="false">SUM('NASCAR Jul 12'!J7:J13)</f>
         <v>0</v>
       </c>
-      <c r="H17" s="17" t="n">
+      <c r="H17" s="18" t="n">
         <f aca="false">SUM('NASCAR Jul 12'!K7:K13)</f>
         <v>0</v>
       </c>
-      <c r="I17" s="18" t="n">
+      <c r="I17" s="19" t="n">
         <f aca="false">I16+H17</f>
-        <v>5000</v>
-      </c>
-      <c r="J17" s="19" t="s">
+        <v>4644.33962264151</v>
+      </c>
+      <c r="J17" s="20" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="12" t="n">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="B18" s="13" t="s">
+      <c r="B18" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="C18" s="12" t="s">
+      <c r="C18" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="D18" s="14" t="s">
+      <c r="D18" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="E18" s="15" t="n">
+      <c r="E18" s="16" t="n">
         <f aca="false">SUM('World Cup 2026'!F7:F13)</f>
         <v>1000</v>
       </c>
-      <c r="F18" s="15" t="n">
+      <c r="F18" s="16" t="n">
         <f aca="false">SUMIF('World Cup 2026'!I7:I13,"Pending",'World Cup 2026'!F7:F13)</f>
         <v>1000</v>
       </c>
-      <c r="G18" s="16" t="n">
+      <c r="G18" s="17" t="n">
         <f aca="false">SUM('World Cup 2026'!J7:J13)</f>
         <v>0</v>
       </c>
-      <c r="H18" s="17" t="n">
+      <c r="H18" s="18" t="n">
         <f aca="false">SUM('World Cup 2026'!K7:K13)</f>
         <v>0</v>
       </c>
-      <c r="I18" s="18" t="n">
+      <c r="I18" s="19" t="n">
         <f aca="false">I17+H18</f>
-        <v>5000</v>
-      </c>
-      <c r="J18" s="19" t="s">
+        <v>4644.33962264151</v>
+      </c>
+      <c r="J18" s="20" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="12" t="n">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="B19" s="13" t="s">
+      <c r="B19" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="C19" s="12" t="s">
+      <c r="C19" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="D19" s="14" t="s">
+      <c r="D19" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="E19" s="15" t="n">
+      <c r="E19" s="16" t="n">
         <f aca="false">SUM('The Open'!F7:F12)</f>
         <v>600</v>
       </c>
-      <c r="F19" s="15" t="n">
+      <c r="F19" s="16" t="n">
         <f aca="false">SUMIF('The Open'!I7:I12,"Pending",'The Open'!F7:F12)</f>
         <v>600</v>
       </c>
-      <c r="G19" s="16" t="n">
+      <c r="G19" s="17" t="n">
         <f aca="false">SUM('The Open'!J7:J12)</f>
         <v>0</v>
       </c>
-      <c r="H19" s="17" t="n">
+      <c r="H19" s="18" t="n">
         <f aca="false">SUM('The Open'!K7:K12)</f>
         <v>0</v>
       </c>
-      <c r="I19" s="18" t="n">
+      <c r="I19" s="19" t="n">
         <f aca="false">I18+H19</f>
-        <v>5000</v>
-      </c>
-      <c r="J19" s="19" t="s">
+        <v>4644.33962264151</v>
+      </c>
+      <c r="J19" s="20" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="20" t="n">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="21" t="n">
         <v>7</v>
       </c>
-      <c r="B20" s="21" t="s">
+      <c r="B20" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="C20" s="20" t="s">
+      <c r="C20" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="D20" s="22" t="s">
+      <c r="D20" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="E20" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" s="26" t="n">
+      <c r="E20" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="27" t="n">
         <f aca="false">I19+H20</f>
-        <v>5000</v>
-      </c>
-      <c r="J20" s="27" t="s">
+        <v>4644.33962264151</v>
+      </c>
+      <c r="J20" s="28" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="28" t="n">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="29" t="n">
         <v>3</v>
       </c>
-      <c r="B21" s="29" t="s">
+      <c r="B21" s="30" t="s">
         <v>38</v>
       </c>
-      <c r="C21" s="28" t="s">
+      <c r="C21" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="D21" s="30" t="s">
+      <c r="D21" s="31" t="s">
         <v>39</v>
       </c>
-      <c r="E21" s="31" t="n">
+      <c r="E21" s="32" t="n">
         <f aca="false">SUM('MLB Jul 12'!F7:F14)</f>
         <v>1000</v>
       </c>
-      <c r="F21" s="31" t="n">
+      <c r="F21" s="32" t="n">
         <f aca="false">SUMIF('MLB Jul 12'!I7:I14,"Pending",'MLB Jul 12'!F7:F14)</f>
         <v>0</v>
       </c>
-      <c r="G21" s="32" t="n">
+      <c r="G21" s="33" t="n">
         <f aca="false">SUM('MLB Jul 12'!J7:J14)</f>
         <v>802.232258064516</v>
       </c>
-      <c r="H21" s="33" t="n">
+      <c r="H21" s="34" t="n">
         <f aca="false">SUM('MLB Jul 12'!K7:K14)</f>
         <v>-197.767741935484</v>
       </c>
-      <c r="I21" s="34" t="n">
+      <c r="I21" s="35" t="n">
         <f aca="false">I20+H21</f>
-        <v>4802.23225806452</v>
-      </c>
-      <c r="J21" s="35" t="s">
+        <v>4446.57188070603</v>
+      </c>
+      <c r="J21" s="36" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="28" t="n">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="B22" s="29" t="s">
+      <c r="B22" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="C22" s="28" t="s">
+      <c r="C22" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="D22" s="30" t="s">
+      <c r="D22" s="31" t="s">
         <v>39</v>
       </c>
-      <c r="E22" s="31" t="n">
+      <c r="E22" s="32" t="n">
         <f aca="false">SUM('UFC 329'!F7:F15)</f>
         <v>1050</v>
       </c>
-      <c r="F22" s="31" t="n">
+      <c r="F22" s="32" t="n">
         <f aca="false">SUMIF('UFC 329'!I7:I15,"Pending",'UFC 329'!F7:F15)</f>
         <v>0</v>
       </c>
-      <c r="G22" s="32" t="n">
+      <c r="G22" s="33" t="n">
         <f aca="false">SUM('UFC 329'!J7:J15)</f>
         <v>1215.1103728313</v>
       </c>
-      <c r="H22" s="33" t="n">
+      <c r="H22" s="34" t="n">
         <f aca="false">SUM('UFC 329'!K7:K15)</f>
         <v>165.110372831303</v>
       </c>
-      <c r="I22" s="34" t="n">
+      <c r="I22" s="35" t="n">
         <f aca="false">I21+H22</f>
-        <v>4967.34263089582</v>
-      </c>
-      <c r="J22" s="35" t="s">
+        <v>4611.68225353733</v>
+      </c>
+      <c r="J22" s="36" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="36"/>
-      <c r="B23" s="37" t="s">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="37"/>
+      <c r="B23" s="38" t="s">
         <v>44</v>
       </c>
-      <c r="C23" s="36"/>
-      <c r="D23" s="36"/>
-      <c r="E23" s="38" t="n">
+      <c r="C23" s="37"/>
+      <c r="D23" s="37"/>
+      <c r="E23" s="39" t="n">
         <f aca="false">SUM(E16:E22)</f>
         <v>5650</v>
       </c>
-      <c r="F23" s="38" t="n">
+      <c r="F23" s="39" t="n">
         <f aca="false">SUM(F16:F22)</f>
-        <v>3600</v>
-      </c>
-      <c r="G23" s="39" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G23" s="40" t="n">
         <f aca="false">SUM(G16:G22)</f>
-        <v>2017.34263089582</v>
-      </c>
-      <c r="H23" s="40" t="n">
+        <v>2261.68225353733</v>
+      </c>
+      <c r="H23" s="41" t="n">
         <f aca="false">SUM(H16:H22)</f>
-        <v>-32.6573691041808</v>
-      </c>
-      <c r="I23" s="36"/>
-      <c r="J23" s="36"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="3" t="s">
+        <v>-388.317746462671</v>
+      </c>
+      <c r="I23" s="37"/>
+      <c r="J23" s="37"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="4" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="11" t="s">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="B26" s="11" t="s">
+      <c r="B26" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="C26" s="11" t="s">
+      <c r="C26" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="D26" s="11" t="s">
+      <c r="D26" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="E26" s="11" t="s">
+      <c r="E26" s="12" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="4" t="s">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="B27" s="41" t="s">
+      <c r="B27" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="C27" s="42" t="s">
+      <c r="C27" s="43" t="s">
         <v>52</v>
       </c>
-      <c r="D27" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" s="9" t="s">
+      <c r="D27" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="10" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="4" t="s">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="B28" s="41" t="s">
+      <c r="B28" s="42" t="s">
         <v>55</v>
       </c>
-      <c r="C28" s="42" t="s">
+      <c r="C28" s="43" t="s">
         <v>56</v>
       </c>
-      <c r="D28" s="43" t="n">
+      <c r="D28" s="44" t="n">
         <v>50</v>
       </c>
-      <c r="E28" s="9" t="str">
+      <c r="E28" s="10" t="str">
         <f aca="false">IF('MLB Jul 12'!I14="Win","HIT",IF('MLB Jul 12'!I14="Loss","MISS","Pending"))</f>
         <v>MISS</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="4" t="s">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="B29" s="41" t="s">
+      <c r="B29" s="42" t="s">
         <v>58</v>
       </c>
-      <c r="C29" s="42" t="s">
+      <c r="C29" s="43" t="s">
         <v>59</v>
       </c>
-      <c r="D29" s="43" t="n">
+      <c r="D29" s="44" t="n">
         <v>40</v>
       </c>
-      <c r="E29" s="9" t="str">
+      <c r="E29" s="10" t="str">
         <f aca="false">IF('NASCAR Jul 12'!I13="Win","HIT",IF('NASCAR Jul 12'!I13="Loss","MISS","Pending"))</f>
         <v>Pending</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="4" t="s">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="B30" s="41" t="s">
+      <c r="B30" s="42" t="s">
         <v>61</v>
       </c>
-      <c r="C30" s="42" t="s">
+      <c r="C30" s="43" t="s">
         <v>62</v>
       </c>
-      <c r="D30" s="43" t="n">
+      <c r="D30" s="44" t="n">
         <v>100</v>
       </c>
-      <c r="E30" s="9" t="str">
+      <c r="E30" s="10" t="str">
         <f aca="false">IF('WNBA Jul 12'!I13="Win","HIT",IF('WNBA Jul 12'!I13="Loss","MISS","Pending"))</f>
-        <v>Pending</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="4" t="s">
+        <v>MISS</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="B31" s="41" t="s">
+      <c r="B31" s="42" t="s">
         <v>64</v>
       </c>
-      <c r="C31" s="42" t="s">
+      <c r="C31" s="43" t="s">
         <v>65</v>
       </c>
-      <c r="D31" s="43" t="n">
+      <c r="D31" s="44" t="n">
         <v>50</v>
       </c>
-      <c r="E31" s="9" t="str">
+      <c r="E31" s="10" t="str">
         <f aca="false">IF('The Open'!I12="Win","HIT",IF('The Open'!I12="Loss","MISS","Pending"))</f>
         <v>Pending</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="4" t="s">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="B32" s="41" t="s">
+      <c r="B32" s="42" t="s">
         <v>67</v>
       </c>
-      <c r="C32" s="42" t="s">
+      <c r="C32" s="43" t="s">
         <v>68</v>
       </c>
-      <c r="D32" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" s="9" t="s">
+      <c r="D32" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="10" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="37" t="s">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="38" t="s">
         <v>70</v>
       </c>
-      <c r="B33" s="36"/>
-      <c r="C33" s="36"/>
-      <c r="D33" s="36"/>
-      <c r="E33" s="44" t="str">
+      <c r="B33" s="37"/>
+      <c r="C33" s="37"/>
+      <c r="D33" s="37"/>
+      <c r="E33" s="45" t="str">
         <f aca="false">IF(COUNTIF(E27:E32,"HIT")+COUNTIF(E27:E32,"MISS")=0,"—",COUNTIF(E27:E32,"HIT")&amp;"-for-"&amp;(COUNTIF(E27:E32,"HIT")+COUNTIF(E27:E32,"MISS"))&amp;" ("&amp;TEXT(COUNTIF(E27:E32,"HIT")/(COUNTIF(E27:E32,"HIT")+COUNTIF(E27:E32,"MISS")),"0%")&amp;")")</f>
-        <v>0-for-2 (0%)</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="45" t="s">
+        <v>0-for-3 (0%)</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="46" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="45" t="s">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="46" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="45" t="s">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="46" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="45" t="s">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="46" t="s">
         <v>74</v>
       </c>
     </row>
@@ -2917,16 +2830,16 @@
   <dimension ref="A1:L41"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="46" width="5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="46" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="46" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="46" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="46" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="46" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="46" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="46" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="9" style="46" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="46" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="9" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="40"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2938,736 +2851,736 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="49" t="s">
+      <c r="A2" s="3" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="49" t="s">
+      <c r="A3" s="3" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="50" t="s">
+      <c r="A5" s="4" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D6" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="E6" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="F6" s="11" t="s">
+      <c r="F6" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="G6" s="11" t="s">
+      <c r="G6" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="H6" s="11" t="s">
+      <c r="H6" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="I6" s="11" t="s">
+      <c r="I6" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="J6" s="11" t="s">
+      <c r="J6" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="K6" s="11" t="s">
+      <c r="K6" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="L6" s="11" t="s">
+      <c r="L6" s="12" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="51" t="n">
+      <c r="A7" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="52" t="s">
+      <c r="B7" s="50" t="s">
         <v>90</v>
       </c>
-      <c r="C7" s="53" t="s">
+      <c r="C7" s="51" t="s">
         <v>91</v>
       </c>
-      <c r="D7" s="51" t="s">
+      <c r="D7" s="49" t="s">
         <v>92</v>
       </c>
-      <c r="E7" s="54" t="n">
+      <c r="E7" s="52" t="n">
         <v>-265</v>
       </c>
-      <c r="F7" s="55" t="n">
+      <c r="F7" s="44" t="n">
         <v>265</v>
       </c>
-      <c r="G7" s="56" t="n">
+      <c r="G7" s="53" t="n">
         <f aca="false">IF(E7&gt;0,F7*E7/100,F7*100/ABS(E7))</f>
         <v>100</v>
       </c>
-      <c r="H7" s="56" t="n">
+      <c r="H7" s="53" t="n">
         <f aca="false">F7+G7</f>
         <v>365</v>
       </c>
-      <c r="I7" s="57" t="s">
+      <c r="I7" s="54" t="s">
         <v>93</v>
       </c>
-      <c r="J7" s="56" t="n">
+      <c r="J7" s="53" t="n">
         <f aca="false">IF(I7="Win",F7+G7,IF(I7="Push",F7,IF(I7="Loss",0,0)))</f>
         <v>365</v>
       </c>
-      <c r="K7" s="58" t="n">
+      <c r="K7" s="55" t="n">
         <f aca="false">IF(I7="Pending",0,J7-F7)</f>
         <v>100</v>
       </c>
-      <c r="L7" s="59" t="s">
+      <c r="L7" s="56" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="51" t="n">
+      <c r="A8" s="49" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="52" t="s">
+      <c r="B8" s="50" t="s">
         <v>95</v>
       </c>
-      <c r="C8" s="53" t="s">
+      <c r="C8" s="51" t="s">
         <v>96</v>
       </c>
-      <c r="D8" s="51" t="s">
+      <c r="D8" s="49" t="s">
         <v>97</v>
       </c>
-      <c r="E8" s="54" t="n">
+      <c r="E8" s="52" t="n">
         <v>-140</v>
       </c>
-      <c r="F8" s="55" t="n">
+      <c r="F8" s="44" t="n">
         <v>200</v>
       </c>
-      <c r="G8" s="56" t="n">
+      <c r="G8" s="53" t="n">
         <f aca="false">IF(E8&gt;0,F8*E8/100,F8*100/ABS(E8))</f>
         <v>142.857142857143</v>
       </c>
-      <c r="H8" s="56" t="n">
+      <c r="H8" s="53" t="n">
         <f aca="false">F8+G8</f>
         <v>342.857142857143</v>
       </c>
-      <c r="I8" s="57" t="s">
+      <c r="I8" s="54" t="s">
         <v>93</v>
       </c>
-      <c r="J8" s="56" t="n">
+      <c r="J8" s="53" t="n">
         <f aca="false">IF(I8="Win",F8+G8,IF(I8="Push",F8,IF(I8="Loss",0,0)))</f>
         <v>342.857142857143</v>
       </c>
-      <c r="K8" s="58" t="n">
+      <c r="K8" s="55" t="n">
         <f aca="false">IF(I8="Pending",0,J8-F8)</f>
         <v>142.857142857143</v>
       </c>
-      <c r="L8" s="59" t="s">
+      <c r="L8" s="56" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="51" t="n">
+      <c r="A9" s="49" t="n">
         <v>3</v>
       </c>
-      <c r="B9" s="52" t="s">
+      <c r="B9" s="50" t="s">
         <v>99</v>
       </c>
-      <c r="C9" s="53" t="s">
+      <c r="C9" s="51" t="s">
         <v>100</v>
       </c>
-      <c r="D9" s="51" t="s">
+      <c r="D9" s="49" t="s">
         <v>92</v>
       </c>
-      <c r="E9" s="54" t="n">
+      <c r="E9" s="52" t="n">
         <v>-148</v>
       </c>
-      <c r="F9" s="55" t="n">
+      <c r="F9" s="44" t="n">
         <v>148</v>
       </c>
-      <c r="G9" s="56" t="n">
+      <c r="G9" s="53" t="n">
         <f aca="false">IF(E9&gt;0,F9*E9/100,F9*100/ABS(E9))</f>
         <v>100</v>
       </c>
-      <c r="H9" s="56" t="n">
+      <c r="H9" s="53" t="n">
         <f aca="false">F9+G9</f>
         <v>248</v>
       </c>
-      <c r="I9" s="60" t="s">
+      <c r="I9" s="57" t="s">
         <v>101</v>
       </c>
-      <c r="J9" s="56" t="n">
+      <c r="J9" s="53" t="n">
         <f aca="false">IF(I9="Win",F9+G9,IF(I9="Push",F9,IF(I9="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K9" s="58" t="n">
+      <c r="K9" s="55" t="n">
         <f aca="false">IF(I9="Pending",0,J9-F9)</f>
         <v>-148</v>
       </c>
-      <c r="L9" s="59" t="s">
+      <c r="L9" s="56" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="51" t="n">
+      <c r="A10" s="49" t="n">
         <v>4</v>
       </c>
-      <c r="B10" s="52" t="s">
+      <c r="B10" s="50" t="s">
         <v>103</v>
       </c>
-      <c r="C10" s="53" t="s">
+      <c r="C10" s="51" t="s">
         <v>104</v>
       </c>
-      <c r="D10" s="51" t="s">
+      <c r="D10" s="49" t="s">
         <v>92</v>
       </c>
-      <c r="E10" s="54" t="n">
+      <c r="E10" s="52" t="n">
         <v>114</v>
       </c>
-      <c r="F10" s="55" t="n">
+      <c r="F10" s="44" t="n">
         <v>100</v>
       </c>
-      <c r="G10" s="56" t="n">
+      <c r="G10" s="53" t="n">
         <f aca="false">IF(E10&gt;0,F10*E10/100,F10*100/ABS(E10))</f>
         <v>114</v>
       </c>
-      <c r="H10" s="56" t="n">
+      <c r="H10" s="53" t="n">
         <f aca="false">F10+G10</f>
         <v>214</v>
       </c>
-      <c r="I10" s="57" t="s">
+      <c r="I10" s="54" t="s">
         <v>93</v>
       </c>
-      <c r="J10" s="56" t="n">
+      <c r="J10" s="53" t="n">
         <f aca="false">IF(I10="Win",F10+G10,IF(I10="Push",F10,IF(I10="Loss",0,0)))</f>
         <v>214</v>
       </c>
-      <c r="K10" s="58" t="n">
+      <c r="K10" s="55" t="n">
         <f aca="false">IF(I10="Pending",0,J10-F10)</f>
         <v>114</v>
       </c>
-      <c r="L10" s="59" t="s">
+      <c r="L10" s="56" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="51" t="n">
+      <c r="A11" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="52" t="s">
+      <c r="B11" s="50" t="s">
         <v>106</v>
       </c>
-      <c r="C11" s="53" t="s">
+      <c r="C11" s="51" t="s">
         <v>107</v>
       </c>
-      <c r="D11" s="51" t="s">
+      <c r="D11" s="49" t="s">
         <v>92</v>
       </c>
-      <c r="E11" s="54" t="n">
+      <c r="E11" s="52" t="n">
         <v>-218</v>
       </c>
-      <c r="F11" s="55" t="n">
+      <c r="F11" s="44" t="n">
         <v>100</v>
       </c>
-      <c r="G11" s="56" t="n">
+      <c r="G11" s="53" t="n">
         <f aca="false">IF(E11&gt;0,F11*E11/100,F11*100/ABS(E11))</f>
         <v>45.8715596330275</v>
       </c>
-      <c r="H11" s="56" t="n">
+      <c r="H11" s="53" t="n">
         <f aca="false">F11+G11</f>
         <v>145.871559633028</v>
       </c>
-      <c r="I11" s="60" t="s">
+      <c r="I11" s="57" t="s">
         <v>101</v>
       </c>
-      <c r="J11" s="56" t="n">
+      <c r="J11" s="53" t="n">
         <f aca="false">IF(I11="Win",F11+G11,IF(I11="Push",F11,IF(I11="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K11" s="58" t="n">
+      <c r="K11" s="55" t="n">
         <f aca="false">IF(I11="Pending",0,J11-F11)</f>
         <v>-100</v>
       </c>
-      <c r="L11" s="59" t="s">
+      <c r="L11" s="56" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="51" t="n">
+      <c r="A12" s="49" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="52" t="s">
+      <c r="B12" s="50" t="s">
         <v>109</v>
       </c>
-      <c r="C12" s="53" t="s">
+      <c r="C12" s="51" t="s">
         <v>110</v>
       </c>
-      <c r="D12" s="51" t="s">
+      <c r="D12" s="49" t="s">
         <v>92</v>
       </c>
-      <c r="E12" s="54" t="n">
+      <c r="E12" s="52" t="n">
         <v>-125</v>
       </c>
-      <c r="F12" s="55" t="n">
+      <c r="F12" s="44" t="n">
         <v>75</v>
       </c>
-      <c r="G12" s="56" t="n">
+      <c r="G12" s="53" t="n">
         <f aca="false">IF(E12&gt;0,F12*E12/100,F12*100/ABS(E12))</f>
         <v>60</v>
       </c>
-      <c r="H12" s="56" t="n">
+      <c r="H12" s="53" t="n">
         <f aca="false">F12+G12</f>
         <v>135</v>
       </c>
-      <c r="I12" s="57" t="s">
+      <c r="I12" s="54" t="s">
         <v>93</v>
       </c>
-      <c r="J12" s="56" t="n">
+      <c r="J12" s="53" t="n">
         <f aca="false">IF(I12="Win",F12+G12,IF(I12="Push",F12,IF(I12="Loss",0,0)))</f>
         <v>135</v>
       </c>
-      <c r="K12" s="58" t="n">
+      <c r="K12" s="55" t="n">
         <f aca="false">IF(I12="Pending",0,J12-F12)</f>
         <v>60</v>
       </c>
-      <c r="L12" s="59" t="s">
+      <c r="L12" s="56" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="51" t="n">
+      <c r="A13" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="52" t="s">
+      <c r="B13" s="50" t="s">
         <v>112</v>
       </c>
-      <c r="C13" s="53" t="s">
+      <c r="C13" s="51" t="s">
         <v>113</v>
       </c>
-      <c r="D13" s="51" t="s">
+      <c r="D13" s="49" t="s">
         <v>92</v>
       </c>
-      <c r="E13" s="54" t="n">
+      <c r="E13" s="52" t="n">
         <v>-225</v>
       </c>
-      <c r="F13" s="55" t="n">
+      <c r="F13" s="44" t="n">
         <v>50</v>
       </c>
-      <c r="G13" s="56" t="n">
+      <c r="G13" s="53" t="n">
         <f aca="false">IF(E13&gt;0,F13*E13/100,F13*100/ABS(E13))</f>
         <v>22.2222222222222</v>
       </c>
-      <c r="H13" s="56" t="n">
+      <c r="H13" s="53" t="n">
         <f aca="false">F13+G13</f>
         <v>72.2222222222222</v>
       </c>
-      <c r="I13" s="57" t="s">
+      <c r="I13" s="54" t="s">
         <v>93</v>
       </c>
-      <c r="J13" s="56" t="n">
+      <c r="J13" s="53" t="n">
         <f aca="false">IF(I13="Win",F13+G13,IF(I13="Push",F13,IF(I13="Loss",0,0)))</f>
         <v>72.2222222222222</v>
       </c>
-      <c r="K13" s="58" t="n">
+      <c r="K13" s="55" t="n">
         <f aca="false">IF(I13="Pending",0,J13-F13)</f>
         <v>22.2222222222222</v>
       </c>
-      <c r="L13" s="59" t="s">
+      <c r="L13" s="56" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="51" t="n">
+      <c r="A14" s="49" t="n">
         <v>8</v>
       </c>
-      <c r="B14" s="52" t="s">
+      <c r="B14" s="50" t="s">
         <v>115</v>
       </c>
-      <c r="C14" s="53" t="s">
+      <c r="C14" s="51" t="s">
         <v>116</v>
       </c>
-      <c r="D14" s="51" t="s">
+      <c r="D14" s="49" t="s">
         <v>92</v>
       </c>
-      <c r="E14" s="54" t="n">
+      <c r="E14" s="52" t="n">
         <v>-258</v>
       </c>
-      <c r="F14" s="55" t="n">
+      <c r="F14" s="44" t="n">
         <v>62</v>
       </c>
-      <c r="G14" s="56" t="n">
+      <c r="G14" s="53" t="n">
         <f aca="false">IF(E14&gt;0,F14*E14/100,F14*100/ABS(E14))</f>
         <v>24.031007751938</v>
       </c>
-      <c r="H14" s="56" t="n">
+      <c r="H14" s="53" t="n">
         <f aca="false">F14+G14</f>
         <v>86.031007751938</v>
       </c>
-      <c r="I14" s="57" t="s">
+      <c r="I14" s="54" t="s">
         <v>93</v>
       </c>
-      <c r="J14" s="56" t="n">
+      <c r="J14" s="53" t="n">
         <f aca="false">IF(I14="Win",F14+G14,IF(I14="Push",F14,IF(I14="Loss",0,0)))</f>
         <v>86.031007751938</v>
       </c>
-      <c r="K14" s="58" t="n">
+      <c r="K14" s="55" t="n">
         <f aca="false">IF(I14="Pending",0,J14-F14)</f>
         <v>24.031007751938</v>
       </c>
-      <c r="L14" s="59" t="s">
+      <c r="L14" s="56" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="51" t="n">
+      <c r="A15" s="49" t="n">
         <v>9</v>
       </c>
-      <c r="B15" s="52" t="s">
+      <c r="B15" s="50" t="s">
         <v>118</v>
       </c>
-      <c r="C15" s="53" t="s">
+      <c r="C15" s="51" t="s">
         <v>119</v>
       </c>
-      <c r="D15" s="51" t="s">
+      <c r="D15" s="49" t="s">
         <v>120</v>
       </c>
-      <c r="E15" s="54" t="n">
+      <c r="E15" s="52" t="n">
         <v>443</v>
       </c>
-      <c r="F15" s="55" t="n">
+      <c r="F15" s="44" t="n">
         <v>50</v>
       </c>
-      <c r="G15" s="56" t="n">
+      <c r="G15" s="53" t="n">
         <f aca="false">IF(E15&gt;0,F15*E15/100,F15*100/ABS(E15))</f>
         <v>221.5</v>
       </c>
-      <c r="H15" s="56" t="n">
+      <c r="H15" s="53" t="n">
         <f aca="false">F15+G15</f>
         <v>271.5</v>
       </c>
-      <c r="I15" s="60" t="s">
+      <c r="I15" s="57" t="s">
         <v>101</v>
       </c>
-      <c r="J15" s="56" t="n">
+      <c r="J15" s="53" t="n">
         <f aca="false">IF(I15="Win",F15+G15,IF(I15="Push",F15,IF(I15="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K15" s="58" t="n">
+      <c r="K15" s="55" t="n">
         <f aca="false">IF(I15="Pending",0,J15-F15)</f>
         <v>-50</v>
       </c>
-      <c r="L15" s="59" t="s">
+      <c r="L15" s="56" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="61"/>
-      <c r="B16" s="62" t="s">
+      <c r="A16" s="58"/>
+      <c r="B16" s="59" t="s">
         <v>44</v>
       </c>
-      <c r="C16" s="61"/>
-      <c r="D16" s="61"/>
-      <c r="E16" s="61"/>
-      <c r="F16" s="63" t="n">
+      <c r="C16" s="58"/>
+      <c r="D16" s="58"/>
+      <c r="E16" s="58"/>
+      <c r="F16" s="39" t="n">
         <f aca="false">SUM(F7:F15)</f>
         <v>1050</v>
       </c>
-      <c r="G16" s="64" t="n">
+      <c r="G16" s="40" t="n">
         <f aca="false">SUM(G7:G15)</f>
         <v>830.481932464331</v>
       </c>
-      <c r="H16" s="64" t="n">
+      <c r="H16" s="40" t="n">
         <f aca="false">SUM(H7:H15)</f>
         <v>1880.48193246433</v>
       </c>
-      <c r="I16" s="61"/>
-      <c r="J16" s="64" t="n">
+      <c r="I16" s="58"/>
+      <c r="J16" s="40" t="n">
         <f aca="false">SUM(J7:J15)</f>
         <v>1215.1103728313</v>
       </c>
-      <c r="K16" s="65" t="n">
+      <c r="K16" s="41" t="n">
         <f aca="false">SUM(K7:K15)</f>
         <v>165.110372831303</v>
       </c>
-      <c r="L16" s="61"/>
+      <c r="L16" s="58"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="50" t="s">
+      <c r="B18" s="4" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="52" t="s">
+      <c r="B19" s="50" t="s">
         <v>123</v>
       </c>
-      <c r="C19" s="66" t="n">
+      <c r="C19" s="60" t="n">
         <f aca="false">COUNTIF(I7:I15,"Win")</f>
         <v>6</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="52" t="s">
+      <c r="B20" s="50" t="s">
         <v>124</v>
       </c>
-      <c r="C20" s="66" t="n">
+      <c r="C20" s="60" t="n">
         <f aca="false">COUNTIF(I7:I15,"Loss")</f>
         <v>3</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="52" t="s">
+      <c r="B21" s="50" t="s">
         <v>125</v>
       </c>
-      <c r="C21" s="66" t="n">
+      <c r="C21" s="60" t="n">
         <f aca="false">COUNTIF(I7:I15,"Push")</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="52" t="s">
+      <c r="B22" s="50" t="s">
         <v>126</v>
       </c>
-      <c r="C22" s="66" t="n">
+      <c r="C22" s="60" t="n">
         <f aca="false">COUNTIF(I7:I15,"Pending")</f>
         <v>0</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="52" t="s">
+      <c r="B23" s="50" t="s">
         <v>127</v>
       </c>
-      <c r="C23" s="67" t="n">
+      <c r="C23" s="61" t="n">
         <f aca="false">IF(COUNTIF(I7:I15,"Win")+COUNTIF(I7:I15,"Loss")=0,"—",COUNTIF(I7:I15,"Win")/(COUNTIF(I7:I15,"Win")+COUNTIF(I7:I15,"Loss")))</f>
         <v>0.666666666666667</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="52" t="s">
+      <c r="B24" s="50" t="s">
         <v>128</v>
       </c>
-      <c r="C24" s="68" t="n">
+      <c r="C24" s="62" t="n">
         <f aca="false">SUM(F7:F15)</f>
         <v>1050</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="52" t="s">
+      <c r="B25" s="50" t="s">
         <v>129</v>
       </c>
-      <c r="C25" s="56" t="n">
+      <c r="C25" s="53" t="n">
         <f aca="false">SUM(J7:J15)</f>
         <v>1215.1103728313</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="52" t="s">
+      <c r="B26" s="50" t="s">
         <v>130</v>
       </c>
-      <c r="C26" s="58" t="n">
+      <c r="C26" s="55" t="n">
         <f aca="false">SUM(K7:K15)</f>
         <v>165.110372831303</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="52" t="s">
+      <c r="B27" s="50" t="s">
         <v>131</v>
       </c>
-      <c r="C27" s="67" t="n">
+      <c r="C27" s="61" t="n">
         <f aca="false">IF(SUM(F7:F15)=0,"—",SUM(K7:K15)/SUM(F7:F15))</f>
         <v>0.157247974125051</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="52" t="s">
+      <c r="B28" s="50" t="s">
         <v>132</v>
       </c>
-      <c r="C28" s="56" t="n">
+      <c r="C28" s="53" t="n">
         <f aca="false">SUM(H7:H15)</f>
         <v>1880.48193246433</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="50" t="s">
+      <c r="A30" s="4" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="11" t="s">
+      <c r="A31" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B31" s="11" t="s">
+      <c r="B31" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="C31" s="11" t="s">
+      <c r="C31" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="D31" s="11" t="s">
+      <c r="D31" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="E31" s="11" t="s">
+      <c r="E31" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="F31" s="11" t="s">
+      <c r="F31" s="12" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="51" t="n">
+      <c r="A32" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="B32" s="52" t="s">
+      <c r="B32" s="50" t="s">
         <v>139</v>
       </c>
-      <c r="C32" s="59" t="s">
+      <c r="C32" s="56" t="s">
         <v>140</v>
       </c>
-      <c r="D32" s="42" t="s">
+      <c r="D32" s="43" t="s">
         <v>141</v>
       </c>
-      <c r="E32" s="69" t="s">
+      <c r="E32" s="63" t="s">
         <v>142</v>
       </c>
-      <c r="F32" s="69" t="s">
+      <c r="F32" s="63" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="51" t="n">
+      <c r="A33" s="49" t="n">
         <v>2</v>
       </c>
-      <c r="B33" s="52" t="s">
+      <c r="B33" s="50" t="s">
         <v>144</v>
       </c>
-      <c r="C33" s="59" t="s">
+      <c r="C33" s="56" t="s">
         <v>145</v>
       </c>
-      <c r="D33" s="42" t="s">
+      <c r="D33" s="43" t="s">
         <v>146</v>
       </c>
-      <c r="E33" s="69" t="s">
+      <c r="E33" s="63" t="s">
         <v>147</v>
       </c>
-      <c r="F33" s="69" t="s">
+      <c r="F33" s="63" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="51" t="n">
+      <c r="A34" s="49" t="n">
         <v>3</v>
       </c>
-      <c r="B34" s="52" t="s">
+      <c r="B34" s="50" t="s">
         <v>149</v>
       </c>
-      <c r="C34" s="59" t="s">
+      <c r="C34" s="56" t="s">
         <v>150</v>
       </c>
-      <c r="D34" s="42" t="s">
+      <c r="D34" s="43" t="s">
         <v>151</v>
       </c>
-      <c r="E34" s="69" t="s">
+      <c r="E34" s="63" t="s">
         <v>152</v>
       </c>
-      <c r="F34" s="69" t="s">
+      <c r="F34" s="63" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="51" t="n">
+      <c r="A35" s="49" t="n">
         <v>4</v>
       </c>
-      <c r="B35" s="52" t="s">
+      <c r="B35" s="50" t="s">
         <v>154</v>
       </c>
-      <c r="C35" s="59" t="s">
+      <c r="C35" s="56" t="s">
         <v>155</v>
       </c>
-      <c r="D35" s="42" t="s">
+      <c r="D35" s="43" t="s">
         <v>156</v>
       </c>
-      <c r="E35" s="69" t="s">
+      <c r="E35" s="63" t="s">
         <v>157</v>
       </c>
-      <c r="F35" s="69" t="s">
+      <c r="F35" s="63" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="51" t="n">
+      <c r="A36" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="B36" s="52" t="s">
+      <c r="B36" s="50" t="s">
         <v>159</v>
       </c>
-      <c r="C36" s="59" t="s">
+      <c r="C36" s="56" t="s">
         <v>160</v>
       </c>
-      <c r="D36" s="42" t="s">
+      <c r="D36" s="43" t="s">
         <v>161</v>
       </c>
-      <c r="E36" s="69" t="s">
+      <c r="E36" s="63" t="s">
         <v>162</v>
       </c>
-      <c r="F36" s="69" t="s">
+      <c r="F36" s="63" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="51" t="n">
+      <c r="A37" s="49" t="n">
         <v>6</v>
       </c>
-      <c r="B37" s="52" t="s">
+      <c r="B37" s="50" t="s">
         <v>164</v>
       </c>
-      <c r="C37" s="59" t="s">
+      <c r="C37" s="56" t="s">
         <v>165</v>
       </c>
-      <c r="D37" s="42" t="s">
+      <c r="D37" s="43" t="s">
         <v>52</v>
       </c>
-      <c r="E37" s="69" t="s">
+      <c r="E37" s="63" t="s">
         <v>166</v>
       </c>
-      <c r="F37" s="69" t="s">
+      <c r="F37" s="63" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="70" t="s">
+      <c r="A39" s="46" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="70" t="s">
+      <c r="A40" s="46" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="70" t="s">
+      <c r="A41" s="46" t="s">
         <v>170</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="K7:K16">
-    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>AND(ISNUMBER(K7),K7&gt;0)</formula>
     </cfRule>
-    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>AND(ISNUMBER(K7),K7&lt;0)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C26:C27">
-    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>AND(ISNUMBER(C26),C26&gt;0)</formula>
     </cfRule>
-    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>AND(ISNUMBER(C26),C26&lt;0)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3696,606 +3609,606 @@
   <dimension ref="A1:L35"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="46" width="5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="46" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="46" width="42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="46" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="46" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="46" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="46" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="9" style="46" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="46" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="9" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="44"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="47" t="s">
         <v>171</v>
       </c>
-      <c r="H1" s="71" t="s">
+      <c r="H1" s="64" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="49" t="s">
+      <c r="A2" s="3" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="49" t="s">
+      <c r="A3" s="3" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="50" t="s">
+      <c r="A5" s="4" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="12" t="s">
         <v>175</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D6" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="E6" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="F6" s="11" t="s">
+      <c r="F6" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="G6" s="11" t="s">
+      <c r="G6" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="H6" s="11" t="s">
+      <c r="H6" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="I6" s="11" t="s">
+      <c r="I6" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="J6" s="11" t="s">
+      <c r="J6" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="K6" s="11" t="s">
+      <c r="K6" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="L6" s="11" t="s">
+      <c r="L6" s="12" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="51" t="n">
+      <c r="A7" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="52" t="s">
+      <c r="B7" s="50" t="s">
         <v>176</v>
       </c>
-      <c r="C7" s="53" t="s">
+      <c r="C7" s="51" t="s">
         <v>177</v>
       </c>
-      <c r="D7" s="51" t="s">
+      <c r="D7" s="49" t="s">
         <v>178</v>
       </c>
-      <c r="E7" s="54" t="n">
+      <c r="E7" s="52" t="n">
         <v>-144</v>
       </c>
-      <c r="F7" s="55" t="n">
+      <c r="F7" s="44" t="n">
         <v>300</v>
       </c>
-      <c r="G7" s="56" t="n">
+      <c r="G7" s="53" t="n">
         <f aca="false">IF(E7&gt;0,F7*E7/100,F7*100/ABS(E7))</f>
         <v>208.333333333333</v>
       </c>
-      <c r="H7" s="56" t="n">
+      <c r="H7" s="53" t="n">
         <f aca="false">F7+G7</f>
         <v>508.333333333333</v>
       </c>
-      <c r="I7" s="72" t="s">
+      <c r="I7" s="65" t="s">
         <v>126</v>
       </c>
-      <c r="J7" s="56" t="n">
+      <c r="J7" s="53" t="n">
         <f aca="false">IF(I7="Win",F7+G7,IF(I7="Push",F7,IF(I7="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K7" s="58" t="n">
+      <c r="K7" s="55" t="n">
         <f aca="false">IF(I7="Pending",0,J7-F7)</f>
         <v>0</v>
       </c>
-      <c r="L7" s="59" t="s">
+      <c r="L7" s="56" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="51" t="n">
+      <c r="A8" s="49" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="52" t="s">
+      <c r="B8" s="50" t="s">
         <v>180</v>
       </c>
-      <c r="C8" s="53" t="s">
+      <c r="C8" s="51" t="s">
         <v>181</v>
       </c>
-      <c r="D8" s="51" t="s">
+      <c r="D8" s="49" t="s">
         <v>182</v>
       </c>
-      <c r="E8" s="54" t="n">
+      <c r="E8" s="52" t="n">
         <v>-122</v>
       </c>
-      <c r="F8" s="55" t="n">
+      <c r="F8" s="44" t="n">
         <v>120</v>
       </c>
-      <c r="G8" s="56" t="n">
+      <c r="G8" s="53" t="n">
         <f aca="false">IF(E8&gt;0,F8*E8/100,F8*100/ABS(E8))</f>
         <v>98.3606557377049</v>
       </c>
-      <c r="H8" s="56" t="n">
+      <c r="H8" s="53" t="n">
         <f aca="false">F8+G8</f>
         <v>218.360655737705</v>
       </c>
-      <c r="I8" s="72" t="s">
+      <c r="I8" s="65" t="s">
         <v>126</v>
       </c>
-      <c r="J8" s="56" t="n">
+      <c r="J8" s="53" t="n">
         <f aca="false">IF(I8="Win",F8+G8,IF(I8="Push",F8,IF(I8="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K8" s="58" t="n">
+      <c r="K8" s="55" t="n">
         <f aca="false">IF(I8="Pending",0,J8-F8)</f>
         <v>0</v>
       </c>
-      <c r="L8" s="59" t="s">
+      <c r="L8" s="56" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="51" t="n">
+      <c r="A9" s="49" t="n">
         <v>3</v>
       </c>
-      <c r="B9" s="52" t="s">
+      <c r="B9" s="50" t="s">
         <v>184</v>
       </c>
-      <c r="C9" s="53" t="s">
+      <c r="C9" s="51" t="s">
         <v>185</v>
       </c>
-      <c r="D9" s="51" t="s">
+      <c r="D9" s="49" t="s">
         <v>186</v>
       </c>
-      <c r="E9" s="54" t="n">
+      <c r="E9" s="52" t="n">
         <v>175</v>
       </c>
-      <c r="F9" s="55" t="n">
+      <c r="F9" s="44" t="n">
         <v>150</v>
       </c>
-      <c r="G9" s="56" t="n">
+      <c r="G9" s="53" t="n">
         <f aca="false">IF(E9&gt;0,F9*E9/100,F9*100/ABS(E9))</f>
         <v>262.5</v>
       </c>
-      <c r="H9" s="56" t="n">
+      <c r="H9" s="53" t="n">
         <f aca="false">F9+G9</f>
         <v>412.5</v>
       </c>
-      <c r="I9" s="72" t="s">
+      <c r="I9" s="65" t="s">
         <v>126</v>
       </c>
-      <c r="J9" s="56" t="n">
+      <c r="J9" s="53" t="n">
         <f aca="false">IF(I9="Win",F9+G9,IF(I9="Push",F9,IF(I9="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K9" s="58" t="n">
+      <c r="K9" s="55" t="n">
         <f aca="false">IF(I9="Pending",0,J9-F9)</f>
         <v>0</v>
       </c>
-      <c r="L9" s="59" t="s">
+      <c r="L9" s="56" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="51" t="n">
+      <c r="A10" s="49" t="n">
         <v>4</v>
       </c>
-      <c r="B10" s="52" t="s">
+      <c r="B10" s="50" t="s">
         <v>188</v>
       </c>
-      <c r="C10" s="53" t="s">
+      <c r="C10" s="51" t="s">
         <v>189</v>
       </c>
-      <c r="D10" s="51" t="s">
+      <c r="D10" s="49" t="s">
         <v>186</v>
       </c>
-      <c r="E10" s="54" t="n">
+      <c r="E10" s="52" t="n">
         <v>205</v>
       </c>
-      <c r="F10" s="55" t="n">
+      <c r="F10" s="44" t="n">
         <v>80</v>
       </c>
-      <c r="G10" s="56" t="n">
+      <c r="G10" s="53" t="n">
         <f aca="false">IF(E10&gt;0,F10*E10/100,F10*100/ABS(E10))</f>
         <v>164</v>
       </c>
-      <c r="H10" s="56" t="n">
+      <c r="H10" s="53" t="n">
         <f aca="false">F10+G10</f>
         <v>244</v>
       </c>
-      <c r="I10" s="72" t="s">
+      <c r="I10" s="65" t="s">
         <v>126</v>
       </c>
-      <c r="J10" s="56" t="n">
+      <c r="J10" s="53" t="n">
         <f aca="false">IF(I10="Win",F10+G10,IF(I10="Push",F10,IF(I10="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K10" s="58" t="n">
+      <c r="K10" s="55" t="n">
         <f aca="false">IF(I10="Pending",0,J10-F10)</f>
         <v>0</v>
       </c>
-      <c r="L10" s="59" t="s">
+      <c r="L10" s="56" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="51" t="n">
+      <c r="A11" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="52" t="s">
+      <c r="B11" s="50" t="s">
         <v>191</v>
       </c>
-      <c r="C11" s="53" t="s">
+      <c r="C11" s="51" t="s">
         <v>192</v>
       </c>
-      <c r="D11" s="51" t="s">
+      <c r="D11" s="49" t="s">
         <v>193</v>
       </c>
-      <c r="E11" s="54" t="n">
+      <c r="E11" s="52" t="n">
         <v>160</v>
       </c>
-      <c r="F11" s="55" t="n">
+      <c r="F11" s="44" t="n">
         <v>250</v>
       </c>
-      <c r="G11" s="56" t="n">
+      <c r="G11" s="53" t="n">
         <f aca="false">IF(E11&gt;0,F11*E11/100,F11*100/ABS(E11))</f>
         <v>400</v>
       </c>
-      <c r="H11" s="56" t="n">
+      <c r="H11" s="53" t="n">
         <f aca="false">F11+G11</f>
         <v>650</v>
       </c>
-      <c r="I11" s="72" t="s">
+      <c r="I11" s="65" t="s">
         <v>126</v>
       </c>
-      <c r="J11" s="56" t="n">
+      <c r="J11" s="53" t="n">
         <f aca="false">IF(I11="Win",F11+G11,IF(I11="Push",F11,IF(I11="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K11" s="58" t="n">
+      <c r="K11" s="55" t="n">
         <f aca="false">IF(I11="Pending",0,J11-F11)</f>
         <v>0</v>
       </c>
-      <c r="L11" s="59" t="s">
+      <c r="L11" s="56" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="51" t="n">
+      <c r="A12" s="49" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="52" t="s">
+      <c r="B12" s="50" t="s">
         <v>195</v>
       </c>
-      <c r="C12" s="53" t="s">
+      <c r="C12" s="51" t="s">
         <v>196</v>
       </c>
-      <c r="D12" s="51" t="s">
+      <c r="D12" s="49" t="s">
         <v>193</v>
       </c>
-      <c r="E12" s="54" t="n">
+      <c r="E12" s="52" t="n">
         <v>500</v>
       </c>
-      <c r="F12" s="55" t="n">
+      <c r="F12" s="44" t="n">
         <v>50</v>
       </c>
-      <c r="G12" s="56" t="n">
+      <c r="G12" s="53" t="n">
         <f aca="false">IF(E12&gt;0,F12*E12/100,F12*100/ABS(E12))</f>
         <v>250</v>
       </c>
-      <c r="H12" s="56" t="n">
+      <c r="H12" s="53" t="n">
         <f aca="false">F12+G12</f>
         <v>300</v>
       </c>
-      <c r="I12" s="72" t="s">
+      <c r="I12" s="65" t="s">
         <v>126</v>
       </c>
-      <c r="J12" s="56" t="n">
+      <c r="J12" s="53" t="n">
         <f aca="false">IF(I12="Win",F12+G12,IF(I12="Push",F12,IF(I12="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K12" s="58" t="n">
+      <c r="K12" s="55" t="n">
         <f aca="false">IF(I12="Pending",0,J12-F12)</f>
         <v>0</v>
       </c>
-      <c r="L12" s="59" t="s">
+      <c r="L12" s="56" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="51" t="n">
+      <c r="A13" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="52" t="s">
+      <c r="B13" s="50" t="s">
         <v>198</v>
       </c>
-      <c r="C13" s="53" t="s">
+      <c r="C13" s="51" t="s">
         <v>199</v>
       </c>
-      <c r="D13" s="51" t="s">
+      <c r="D13" s="49" t="s">
         <v>120</v>
       </c>
-      <c r="E13" s="54" t="n">
+      <c r="E13" s="52" t="n">
         <v>179</v>
       </c>
-      <c r="F13" s="55" t="n">
+      <c r="F13" s="44" t="n">
         <v>50</v>
       </c>
-      <c r="G13" s="56" t="n">
+      <c r="G13" s="53" t="n">
         <f aca="false">IF(E13&gt;0,F13*E13/100,F13*100/ABS(E13))</f>
         <v>89.5</v>
       </c>
-      <c r="H13" s="56" t="n">
+      <c r="H13" s="53" t="n">
         <f aca="false">F13+G13</f>
         <v>139.5</v>
       </c>
-      <c r="I13" s="72" t="s">
+      <c r="I13" s="65" t="s">
         <v>126</v>
       </c>
-      <c r="J13" s="56" t="n">
+      <c r="J13" s="53" t="n">
         <f aca="false">IF(I13="Win",F13+G13,IF(I13="Push",F13,IF(I13="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K13" s="58" t="n">
+      <c r="K13" s="55" t="n">
         <f aca="false">IF(I13="Pending",0,J13-F13)</f>
         <v>0</v>
       </c>
-      <c r="L13" s="59" t="s">
+      <c r="L13" s="56" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="61"/>
-      <c r="B14" s="62" t="s">
+      <c r="A14" s="58"/>
+      <c r="B14" s="59" t="s">
         <v>44</v>
       </c>
-      <c r="C14" s="61"/>
-      <c r="D14" s="61"/>
-      <c r="E14" s="61"/>
-      <c r="F14" s="63" t="n">
+      <c r="C14" s="58"/>
+      <c r="D14" s="58"/>
+      <c r="E14" s="58"/>
+      <c r="F14" s="39" t="n">
         <f aca="false">SUM(F7:F13)</f>
         <v>1000</v>
       </c>
-      <c r="G14" s="64" t="n">
+      <c r="G14" s="40" t="n">
         <f aca="false">SUM(G7:G13)</f>
         <v>1472.69398907104</v>
       </c>
-      <c r="H14" s="64" t="n">
+      <c r="H14" s="40" t="n">
         <f aca="false">SUM(H7:H13)</f>
         <v>2472.69398907104</v>
       </c>
-      <c r="I14" s="61"/>
-      <c r="J14" s="64" t="n">
+      <c r="I14" s="58"/>
+      <c r="J14" s="40" t="n">
         <f aca="false">SUM(J7:J13)</f>
         <v>0</v>
       </c>
-      <c r="K14" s="65" t="n">
+      <c r="K14" s="41" t="n">
         <f aca="false">SUM(K7:K13)</f>
         <v>0</v>
       </c>
-      <c r="L14" s="61"/>
+      <c r="L14" s="58"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="50" t="s">
+      <c r="B16" s="4" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="52" t="s">
+      <c r="B17" s="50" t="s">
         <v>123</v>
       </c>
-      <c r="C17" s="66" t="n">
+      <c r="C17" s="60" t="n">
         <f aca="false">COUNTIF(I7:I13,"Win")</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="52" t="s">
+      <c r="B18" s="50" t="s">
         <v>124</v>
       </c>
-      <c r="C18" s="66" t="n">
+      <c r="C18" s="60" t="n">
         <f aca="false">COUNTIF(I7:I13,"Loss")</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="52" t="s">
+      <c r="B19" s="50" t="s">
         <v>125</v>
       </c>
-      <c r="C19" s="66" t="n">
+      <c r="C19" s="60" t="n">
         <f aca="false">COUNTIF(I7:I13,"Push")</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="52" t="s">
+      <c r="B20" s="50" t="s">
         <v>126</v>
       </c>
-      <c r="C20" s="66" t="n">
+      <c r="C20" s="60" t="n">
         <f aca="false">COUNTIF(I7:I13,"Pending")</f>
         <v>7</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="52" t="s">
+      <c r="B21" s="50" t="s">
         <v>127</v>
       </c>
-      <c r="C21" s="67" t="str">
+      <c r="C21" s="61" t="str">
         <f aca="false">IF(COUNTIF(I7:I13,"Win")+COUNTIF(I7:I13,"Loss")=0,"—",COUNTIF(I7:I13,"Win")/(COUNTIF(I7:I13,"Win")+COUNTIF(I7:I13,"Loss")))</f>
         <v>—</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="52" t="s">
+      <c r="B22" s="50" t="s">
         <v>128</v>
       </c>
-      <c r="C22" s="68" t="n">
+      <c r="C22" s="62" t="n">
         <f aca="false">SUM(F7:F13)</f>
         <v>1000</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="52" t="s">
+      <c r="B23" s="50" t="s">
         <v>129</v>
       </c>
-      <c r="C23" s="56" t="n">
+      <c r="C23" s="53" t="n">
         <f aca="false">SUM(J7:J13)</f>
         <v>0</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="52" t="s">
+      <c r="B24" s="50" t="s">
         <v>130</v>
       </c>
-      <c r="C24" s="58" t="n">
+      <c r="C24" s="55" t="n">
         <f aca="false">SUM(K7:K13)</f>
         <v>0</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="52" t="s">
+      <c r="B25" s="50" t="s">
         <v>131</v>
       </c>
-      <c r="C25" s="67" t="n">
+      <c r="C25" s="61" t="n">
         <f aca="false">IF(SUM(F7:F13)=0,"—",SUM(K7:K13)/SUM(F7:F13))</f>
         <v>0</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="52" t="s">
+      <c r="B26" s="50" t="s">
         <v>201</v>
       </c>
-      <c r="C26" s="68" t="n">
+      <c r="C26" s="62" t="n">
         <f aca="false">929</f>
         <v>929</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="50" t="s">
+      <c r="A28" s="4" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="11" t="s">
+      <c r="A29" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B29" s="11" t="s">
+      <c r="B29" s="12" t="s">
         <v>203</v>
       </c>
-      <c r="C29" s="11" t="s">
+      <c r="C29" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="D29" s="11" t="s">
+      <c r="D29" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="E29" s="11" t="s">
+      <c r="E29" s="12" t="s">
         <v>204</v>
       </c>
-      <c r="F29" s="11" t="s">
+      <c r="F29" s="12" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="51" t="n">
+      <c r="A30" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="B30" s="52" t="s">
+      <c r="B30" s="50" t="s">
         <v>205</v>
       </c>
-      <c r="C30" s="59" t="s">
+      <c r="C30" s="56" t="s">
         <v>206</v>
       </c>
-      <c r="D30" s="42" t="s">
+      <c r="D30" s="43" t="s">
         <v>207</v>
       </c>
-      <c r="E30" s="72"/>
-      <c r="F30" s="72"/>
+      <c r="E30" s="65"/>
+      <c r="F30" s="65"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="51" t="n">
+      <c r="A31" s="49" t="n">
         <v>2</v>
       </c>
-      <c r="B31" s="52" t="s">
+      <c r="B31" s="50" t="s">
         <v>208</v>
       </c>
-      <c r="C31" s="59" t="s">
+      <c r="C31" s="56" t="s">
         <v>209</v>
       </c>
-      <c r="D31" s="42" t="s">
+      <c r="D31" s="43" t="s">
         <v>210</v>
       </c>
-      <c r="E31" s="72"/>
-      <c r="F31" s="72"/>
+      <c r="E31" s="65"/>
+      <c r="F31" s="65"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="51" t="n">
+      <c r="A32" s="49" t="n">
         <v>3</v>
       </c>
-      <c r="B32" s="52" t="s">
+      <c r="B32" s="50" t="s">
         <v>211</v>
       </c>
-      <c r="C32" s="59" t="s">
+      <c r="C32" s="56" t="s">
         <v>212</v>
       </c>
-      <c r="D32" s="42" t="s">
+      <c r="D32" s="43" t="s">
         <v>213</v>
       </c>
-      <c r="E32" s="72"/>
-      <c r="F32" s="72"/>
+      <c r="E32" s="65"/>
+      <c r="F32" s="65"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="51" t="n">
+      <c r="A33" s="49" t="n">
         <v>4</v>
       </c>
-      <c r="B33" s="52" t="s">
+      <c r="B33" s="50" t="s">
         <v>214</v>
       </c>
-      <c r="C33" s="59" t="s">
+      <c r="C33" s="56" t="s">
         <v>215</v>
       </c>
-      <c r="D33" s="42" t="s">
+      <c r="D33" s="43" t="s">
         <v>216</v>
       </c>
-      <c r="E33" s="72"/>
-      <c r="F33" s="72"/>
+      <c r="E33" s="65"/>
+      <c r="F33" s="65"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="70" t="s">
+      <c r="A35" s="46" t="s">
         <v>217</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="K7:K14">
-    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>AND(ISNUMBER(K7),K7&gt;0)</formula>
     </cfRule>
-    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>AND(ISNUMBER(K7),K7&lt;0)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C24:C25">
-    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>AND(ISNUMBER(C24),C24&gt;0)</formula>
     </cfRule>
-    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>AND(ISNUMBER(C24),C24&lt;0)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4324,16 +4237,16 @@
   <dimension ref="A1:M42"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="46" width="5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="46" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="46" width="46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="46" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="46" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="46" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="46" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="9" style="46" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="46" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="46" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="9" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="46"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4345,749 +4258,749 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="49" t="s">
+      <c r="A2" s="3" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="49" t="s">
+      <c r="A3" s="3" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="50" t="s">
+      <c r="A5" s="4" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="12" t="s">
         <v>222</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D6" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="E6" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="F6" s="11" t="s">
+      <c r="F6" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="G6" s="11" t="s">
+      <c r="G6" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="H6" s="11" t="s">
+      <c r="H6" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="I6" s="11" t="s">
+      <c r="I6" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="J6" s="11" t="s">
+      <c r="J6" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="K6" s="11" t="s">
+      <c r="K6" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="L6" s="11" t="s">
+      <c r="L6" s="12" t="s">
         <v>223</v>
       </c>
-      <c r="M6" s="11" t="s">
+      <c r="M6" s="12" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="51" t="n">
+      <c r="A7" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="52" t="s">
+      <c r="B7" s="50" t="s">
         <v>224</v>
       </c>
-      <c r="C7" s="53" t="s">
+      <c r="C7" s="51" t="s">
         <v>225</v>
       </c>
-      <c r="D7" s="51" t="s">
+      <c r="D7" s="49" t="s">
         <v>92</v>
       </c>
-      <c r="E7" s="54" t="n">
+      <c r="E7" s="52" t="n">
         <v>-155</v>
       </c>
-      <c r="F7" s="55" t="n">
+      <c r="F7" s="44" t="n">
         <v>200</v>
       </c>
-      <c r="G7" s="56" t="n">
+      <c r="G7" s="53" t="n">
         <f aca="false">IF(E7&gt;0,F7*E7/100,F7*100/ABS(E7))</f>
         <v>129.032258064516</v>
       </c>
-      <c r="H7" s="56" t="n">
+      <c r="H7" s="53" t="n">
         <f aca="false">F7+G7</f>
         <v>329.032258064516</v>
       </c>
-      <c r="I7" s="57" t="s">
+      <c r="I7" s="54" t="s">
         <v>93</v>
       </c>
-      <c r="J7" s="56" t="n">
+      <c r="J7" s="53" t="n">
         <f aca="false">IF(I7="Win",F7+G7,IF(I7="Push",F7,IF(I7="Loss",0,0)))</f>
         <v>329.032258064516</v>
       </c>
-      <c r="K7" s="58" t="n">
+      <c r="K7" s="55" t="n">
         <f aca="false">IF(I7="Pending",0,J7-F7)</f>
         <v>129.032258064516</v>
       </c>
-      <c r="L7" s="73" t="n">
+      <c r="L7" s="66" t="n">
         <v>0.62</v>
       </c>
-      <c r="M7" s="59" t="s">
+      <c r="M7" s="56" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="51" t="n">
+      <c r="A8" s="49" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="52" t="s">
+      <c r="B8" s="50" t="s">
         <v>227</v>
       </c>
-      <c r="C8" s="53" t="s">
+      <c r="C8" s="51" t="s">
         <v>228</v>
       </c>
-      <c r="D8" s="51" t="s">
+      <c r="D8" s="49" t="s">
         <v>92</v>
       </c>
-      <c r="E8" s="54" t="n">
+      <c r="E8" s="52" t="n">
         <v>-104</v>
       </c>
-      <c r="F8" s="55" t="n">
+      <c r="F8" s="44" t="n">
         <v>150</v>
       </c>
-      <c r="G8" s="56" t="n">
+      <c r="G8" s="53" t="n">
         <f aca="false">IF(E8&gt;0,F8*E8/100,F8*100/ABS(E8))</f>
         <v>144.230769230769</v>
       </c>
-      <c r="H8" s="56" t="n">
+      <c r="H8" s="53" t="n">
         <f aca="false">F8+G8</f>
         <v>294.230769230769</v>
       </c>
-      <c r="I8" s="60" t="s">
+      <c r="I8" s="57" t="s">
         <v>101</v>
       </c>
-      <c r="J8" s="56" t="n">
+      <c r="J8" s="53" t="n">
         <f aca="false">IF(I8="Win",F8+G8,IF(I8="Push",F8,IF(I8="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K8" s="58" t="n">
+      <c r="K8" s="55" t="n">
         <f aca="false">IF(I8="Pending",0,J8-F8)</f>
         <v>-150</v>
       </c>
-      <c r="L8" s="73" t="n">
+      <c r="L8" s="66" t="n">
         <v>0.54</v>
       </c>
-      <c r="M8" s="59" t="s">
+      <c r="M8" s="56" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="51" t="n">
+      <c r="A9" s="49" t="n">
         <v>3</v>
       </c>
-      <c r="B9" s="52" t="s">
+      <c r="B9" s="50" t="s">
         <v>230</v>
       </c>
-      <c r="C9" s="53" t="s">
+      <c r="C9" s="51" t="s">
         <v>231</v>
       </c>
-      <c r="D9" s="51" t="s">
+      <c r="D9" s="49" t="s">
         <v>92</v>
       </c>
-      <c r="E9" s="54" t="n">
+      <c r="E9" s="52" t="n">
         <v>-115</v>
       </c>
-      <c r="F9" s="55" t="n">
+      <c r="F9" s="44" t="n">
         <v>150</v>
       </c>
-      <c r="G9" s="56" t="n">
+      <c r="G9" s="53" t="n">
         <f aca="false">IF(E9&gt;0,F9*E9/100,F9*100/ABS(E9))</f>
         <v>130.434782608696</v>
       </c>
-      <c r="H9" s="56" t="n">
+      <c r="H9" s="53" t="n">
         <f aca="false">F9+G9</f>
         <v>280.434782608696</v>
       </c>
-      <c r="I9" s="60" t="s">
+      <c r="I9" s="57" t="s">
         <v>101</v>
       </c>
-      <c r="J9" s="56" t="n">
+      <c r="J9" s="53" t="n">
         <f aca="false">IF(I9="Win",F9+G9,IF(I9="Push",F9,IF(I9="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K9" s="58" t="n">
+      <c r="K9" s="55" t="n">
         <f aca="false">IF(I9="Pending",0,J9-F9)</f>
         <v>-150</v>
       </c>
-      <c r="L9" s="73" t="n">
+      <c r="L9" s="66" t="n">
         <v>0.55</v>
       </c>
-      <c r="M9" s="59" t="s">
+      <c r="M9" s="56" t="s">
         <v>232</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="51" t="n">
+      <c r="A10" s="49" t="n">
         <v>4</v>
       </c>
-      <c r="B10" s="52" t="s">
+      <c r="B10" s="50" t="s">
         <v>233</v>
       </c>
-      <c r="C10" s="53" t="s">
+      <c r="C10" s="51" t="s">
         <v>234</v>
       </c>
-      <c r="D10" s="51" t="s">
+      <c r="D10" s="49" t="s">
         <v>182</v>
       </c>
-      <c r="E10" s="54" t="n">
+      <c r="E10" s="52" t="n">
         <v>-114</v>
       </c>
-      <c r="F10" s="55" t="n">
+      <c r="F10" s="44" t="n">
         <v>120</v>
       </c>
-      <c r="G10" s="56" t="n">
+      <c r="G10" s="53" t="n">
         <f aca="false">IF(E10&gt;0,F10*E10/100,F10*100/ABS(E10))</f>
         <v>105.263157894737</v>
       </c>
-      <c r="H10" s="56" t="n">
+      <c r="H10" s="53" t="n">
         <f aca="false">F10+G10</f>
         <v>225.263157894737</v>
       </c>
-      <c r="I10" s="60" t="s">
+      <c r="I10" s="57" t="s">
         <v>101</v>
       </c>
-      <c r="J10" s="56" t="n">
+      <c r="J10" s="53" t="n">
         <f aca="false">IF(I10="Win",F10+G10,IF(I10="Push",F10,IF(I10="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K10" s="58" t="n">
+      <c r="K10" s="55" t="n">
         <f aca="false">IF(I10="Pending",0,J10-F10)</f>
         <v>-120</v>
       </c>
-      <c r="L10" s="73" t="n">
+      <c r="L10" s="66" t="n">
         <v>0.55</v>
       </c>
-      <c r="M10" s="59" t="s">
+      <c r="M10" s="56" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="51" t="n">
+      <c r="A11" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="52" t="s">
+      <c r="B11" s="50" t="s">
         <v>236</v>
       </c>
-      <c r="C11" s="53" t="s">
+      <c r="C11" s="51" t="s">
         <v>237</v>
       </c>
-      <c r="D11" s="51" t="s">
+      <c r="D11" s="49" t="s">
         <v>92</v>
       </c>
-      <c r="E11" s="54" t="n">
+      <c r="E11" s="52" t="n">
         <v>104</v>
       </c>
-      <c r="F11" s="55" t="n">
+      <c r="F11" s="44" t="n">
         <v>130</v>
       </c>
-      <c r="G11" s="56" t="n">
+      <c r="G11" s="53" t="n">
         <f aca="false">IF(E11&gt;0,F11*E11/100,F11*100/ABS(E11))</f>
         <v>135.2</v>
       </c>
-      <c r="H11" s="56" t="n">
+      <c r="H11" s="53" t="n">
         <f aca="false">F11+G11</f>
         <v>265.2</v>
       </c>
-      <c r="I11" s="57" t="s">
+      <c r="I11" s="54" t="s">
         <v>93</v>
       </c>
-      <c r="J11" s="56" t="n">
+      <c r="J11" s="53" t="n">
         <f aca="false">IF(I11="Win",F11+G11,IF(I11="Push",F11,IF(I11="Loss",0,0)))</f>
         <v>265.2</v>
       </c>
-      <c r="K11" s="58" t="n">
+      <c r="K11" s="55" t="n">
         <f aca="false">IF(I11="Pending",0,J11-F11)</f>
         <v>135.2</v>
       </c>
-      <c r="L11" s="73" t="n">
+      <c r="L11" s="66" t="n">
         <v>0.52</v>
       </c>
-      <c r="M11" s="59" t="s">
+      <c r="M11" s="56" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="51" t="n">
+      <c r="A12" s="49" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="52" t="s">
+      <c r="B12" s="50" t="s">
         <v>239</v>
       </c>
-      <c r="C12" s="53" t="s">
+      <c r="C12" s="51" t="s">
         <v>240</v>
       </c>
-      <c r="D12" s="51" t="s">
+      <c r="D12" s="49" t="s">
         <v>92</v>
       </c>
-      <c r="E12" s="54" t="n">
+      <c r="E12" s="52" t="n">
         <v>108</v>
       </c>
-      <c r="F12" s="55" t="n">
+      <c r="F12" s="44" t="n">
         <v>100</v>
       </c>
-      <c r="G12" s="56" t="n">
+      <c r="G12" s="53" t="n">
         <f aca="false">IF(E12&gt;0,F12*E12/100,F12*100/ABS(E12))</f>
         <v>108</v>
       </c>
-      <c r="H12" s="56" t="n">
+      <c r="H12" s="53" t="n">
         <f aca="false">F12+G12</f>
         <v>208</v>
       </c>
-      <c r="I12" s="60" t="s">
+      <c r="I12" s="57" t="s">
         <v>101</v>
       </c>
-      <c r="J12" s="56" t="n">
+      <c r="J12" s="53" t="n">
         <f aca="false">IF(I12="Win",F12+G12,IF(I12="Push",F12,IF(I12="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K12" s="58" t="n">
+      <c r="K12" s="55" t="n">
         <f aca="false">IF(I12="Pending",0,J12-F12)</f>
         <v>-100</v>
       </c>
-      <c r="L12" s="73" t="n">
+      <c r="L12" s="66" t="n">
         <v>0.5</v>
       </c>
-      <c r="M12" s="59" t="s">
+      <c r="M12" s="56" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="51" t="n">
+      <c r="A13" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="52" t="s">
+      <c r="B13" s="50" t="s">
         <v>242</v>
       </c>
-      <c r="C13" s="53" t="s">
+      <c r="C13" s="51" t="s">
         <v>243</v>
       </c>
-      <c r="D13" s="51" t="s">
+      <c r="D13" s="49" t="s">
         <v>92</v>
       </c>
-      <c r="E13" s="54" t="n">
+      <c r="E13" s="52" t="n">
         <v>108</v>
       </c>
-      <c r="F13" s="55" t="n">
+      <c r="F13" s="44" t="n">
         <v>100</v>
       </c>
-      <c r="G13" s="56" t="n">
+      <c r="G13" s="53" t="n">
         <f aca="false">IF(E13&gt;0,F13*E13/100,F13*100/ABS(E13))</f>
         <v>108</v>
       </c>
-      <c r="H13" s="56" t="n">
+      <c r="H13" s="53" t="n">
         <f aca="false">F13+G13</f>
         <v>208</v>
       </c>
-      <c r="I13" s="57" t="s">
+      <c r="I13" s="54" t="s">
         <v>93</v>
       </c>
-      <c r="J13" s="56" t="n">
+      <c r="J13" s="53" t="n">
         <f aca="false">IF(I13="Win",F13+G13,IF(I13="Push",F13,IF(I13="Loss",0,0)))</f>
         <v>208</v>
       </c>
-      <c r="K13" s="58" t="n">
+      <c r="K13" s="55" t="n">
         <f aca="false">IF(I13="Pending",0,J13-F13)</f>
         <v>108</v>
       </c>
-      <c r="L13" s="73" t="n">
+      <c r="L13" s="66" t="n">
         <v>0.5</v>
       </c>
-      <c r="M13" s="59" t="s">
+      <c r="M13" s="56" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="51" t="n">
+      <c r="A14" s="49" t="n">
         <v>8</v>
       </c>
-      <c r="B14" s="52" t="s">
+      <c r="B14" s="50" t="s">
         <v>245</v>
       </c>
-      <c r="C14" s="53" t="s">
+      <c r="C14" s="51" t="s">
         <v>246</v>
       </c>
-      <c r="D14" s="51" t="s">
+      <c r="D14" s="49" t="s">
         <v>120</v>
       </c>
-      <c r="E14" s="54" t="n">
+      <c r="E14" s="52" t="n">
         <v>732</v>
       </c>
-      <c r="F14" s="55" t="n">
+      <c r="F14" s="44" t="n">
         <v>50</v>
       </c>
-      <c r="G14" s="56" t="n">
+      <c r="G14" s="53" t="n">
         <f aca="false">IF(E14&gt;0,F14*E14/100,F14*100/ABS(E14))</f>
         <v>366</v>
       </c>
-      <c r="H14" s="56" t="n">
+      <c r="H14" s="53" t="n">
         <f aca="false">F14+G14</f>
         <v>416</v>
       </c>
-      <c r="I14" s="60" t="s">
+      <c r="I14" s="57" t="s">
         <v>101</v>
       </c>
-      <c r="J14" s="56" t="n">
+      <c r="J14" s="53" t="n">
         <f aca="false">IF(I14="Win",F14+G14,IF(I14="Push",F14,IF(I14="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K14" s="58" t="n">
+      <c r="K14" s="55" t="n">
         <f aca="false">IF(I14="Pending",0,J14-F14)</f>
         <v>-50</v>
       </c>
-      <c r="L14" s="73" t="n">
+      <c r="L14" s="66" t="n">
         <v>0.14</v>
       </c>
-      <c r="M14" s="59" t="s">
+      <c r="M14" s="56" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="61"/>
-      <c r="B15" s="62" t="s">
+      <c r="A15" s="58"/>
+      <c r="B15" s="59" t="s">
         <v>44</v>
       </c>
-      <c r="C15" s="61"/>
-      <c r="D15" s="61"/>
-      <c r="E15" s="61"/>
-      <c r="F15" s="63" t="n">
+      <c r="C15" s="58"/>
+      <c r="D15" s="58"/>
+      <c r="E15" s="58"/>
+      <c r="F15" s="39" t="n">
         <f aca="false">SUM(F7:F14)</f>
         <v>1000</v>
       </c>
-      <c r="G15" s="64" t="n">
+      <c r="G15" s="40" t="n">
         <f aca="false">SUM(G7:G14)</f>
         <v>1226.16096779872</v>
       </c>
-      <c r="H15" s="64" t="n">
+      <c r="H15" s="40" t="n">
         <f aca="false">SUM(H7:H14)</f>
         <v>2226.16096779872</v>
       </c>
-      <c r="I15" s="61"/>
-      <c r="J15" s="64" t="n">
+      <c r="I15" s="58"/>
+      <c r="J15" s="40" t="n">
         <f aca="false">SUM(J7:J14)</f>
         <v>802.232258064516</v>
       </c>
-      <c r="K15" s="65" t="n">
+      <c r="K15" s="41" t="n">
         <f aca="false">SUM(K7:K14)</f>
         <v>-197.767741935484</v>
       </c>
-      <c r="L15" s="74" t="n">
+      <c r="L15" s="67" t="n">
         <f aca="false">SUM(L7:L14)</f>
         <v>3.92</v>
       </c>
-      <c r="M15" s="61"/>
+      <c r="M15" s="58"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="50" t="s">
+      <c r="B17" s="4" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="52" t="s">
+      <c r="B18" s="50" t="s">
         <v>123</v>
       </c>
-      <c r="C18" s="66" t="n">
+      <c r="C18" s="60" t="n">
         <f aca="false">COUNTIF(I7:I14,"Win")</f>
         <v>3</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="52" t="s">
+      <c r="B19" s="50" t="s">
         <v>124</v>
       </c>
-      <c r="C19" s="66" t="n">
+      <c r="C19" s="60" t="n">
         <f aca="false">COUNTIF(I7:I14,"Loss")</f>
         <v>5</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="52" t="s">
+      <c r="B20" s="50" t="s">
         <v>125</v>
       </c>
-      <c r="C20" s="66" t="n">
+      <c r="C20" s="60" t="n">
         <f aca="false">COUNTIF(I7:I14,"Push")</f>
         <v>0</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="52" t="s">
+      <c r="B21" s="50" t="s">
         <v>126</v>
       </c>
-      <c r="C21" s="66" t="n">
+      <c r="C21" s="60" t="n">
         <f aca="false">COUNTIF(I7:I14,"Pending")</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="52" t="s">
+      <c r="B22" s="50" t="s">
         <v>127</v>
       </c>
-      <c r="C22" s="67" t="n">
+      <c r="C22" s="61" t="n">
         <f aca="false">IF(COUNTIF(I7:I14,"Win")+COUNTIF(I7:I14,"Loss")=0,"—",COUNTIF(I7:I14,"Win")/(COUNTIF(I7:I14,"Win")+COUNTIF(I7:I14,"Loss")))</f>
         <v>0.375</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="52" t="s">
+      <c r="B23" s="50" t="s">
         <v>128</v>
       </c>
-      <c r="C23" s="68" t="n">
+      <c r="C23" s="62" t="n">
         <f aca="false">SUM(F7:F14)</f>
         <v>1000</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="52" t="s">
+      <c r="B24" s="50" t="s">
         <v>129</v>
       </c>
-      <c r="C24" s="56" t="n">
+      <c r="C24" s="53" t="n">
         <f aca="false">SUM(J7:J14)</f>
         <v>802.232258064516</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="52" t="s">
+      <c r="B25" s="50" t="s">
         <v>130</v>
       </c>
-      <c r="C25" s="58" t="n">
+      <c r="C25" s="55" t="n">
         <f aca="false">SUM(K7:K14)</f>
         <v>-197.767741935484</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="52" t="s">
+      <c r="B26" s="50" t="s">
         <v>131</v>
       </c>
-      <c r="C26" s="67" t="n">
+      <c r="C26" s="61" t="n">
         <f aca="false">IF(SUM(F7:F14)=0,"—",SUM(K7:K14)/SUM(F7:F14))</f>
         <v>-0.197767741935484</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="52" t="s">
+      <c r="B27" s="50" t="s">
         <v>132</v>
       </c>
-      <c r="C27" s="56" t="n">
+      <c r="C27" s="53" t="n">
         <f aca="false">SUM(H7:H14)</f>
         <v>2226.16096779872</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="52" t="s">
+      <c r="B28" s="50" t="s">
         <v>248</v>
       </c>
-      <c r="C28" s="75" t="n">
+      <c r="C28" s="68" t="n">
         <f aca="false">SUM(L7:L14)</f>
         <v>3.92</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="52" t="s">
+      <c r="B29" s="50" t="s">
         <v>249</v>
       </c>
-      <c r="C29" s="58" t="n">
+      <c r="C29" s="55" t="n">
         <f aca="false">SUMPRODUCT(L7:L14,G7:G14)-SUMPRODUCT(1-L7:L14,F7:F14)</f>
         <v>45.1624826615033</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="50" t="s">
+      <c r="A31" s="4" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="11" t="s">
+      <c r="A32" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B32" s="11" t="s">
+      <c r="B32" s="12" t="s">
         <v>251</v>
       </c>
-      <c r="C32" s="11" t="s">
+      <c r="C32" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="D32" s="11" t="s">
+      <c r="D32" s="12" t="s">
         <v>252</v>
       </c>
-      <c r="E32" s="11" t="s">
+      <c r="E32" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="F32" s="11" t="s">
+      <c r="F32" s="12" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="51" t="n">
+      <c r="A33" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="B33" s="52" t="s">
+      <c r="B33" s="50" t="s">
         <v>253</v>
       </c>
-      <c r="C33" s="59" t="s">
+      <c r="C33" s="56" t="s">
         <v>254</v>
       </c>
-      <c r="D33" s="42" t="s">
+      <c r="D33" s="43" t="s">
         <v>255</v>
       </c>
-      <c r="E33" s="72"/>
-      <c r="F33" s="72"/>
+      <c r="E33" s="65"/>
+      <c r="F33" s="65"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="51" t="n">
+      <c r="A34" s="49" t="n">
         <v>2</v>
       </c>
-      <c r="B34" s="52" t="s">
+      <c r="B34" s="50" t="s">
         <v>256</v>
       </c>
-      <c r="C34" s="59" t="s">
+      <c r="C34" s="56" t="s">
         <v>257</v>
       </c>
-      <c r="D34" s="42" t="s">
+      <c r="D34" s="43" t="s">
         <v>258</v>
       </c>
-      <c r="E34" s="72"/>
-      <c r="F34" s="72"/>
+      <c r="E34" s="65"/>
+      <c r="F34" s="65"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="51" t="n">
+      <c r="A35" s="49" t="n">
         <v>3</v>
       </c>
-      <c r="B35" s="52" t="s">
+      <c r="B35" s="50" t="s">
         <v>259</v>
       </c>
-      <c r="C35" s="59" t="s">
+      <c r="C35" s="56" t="s">
         <v>260</v>
       </c>
-      <c r="D35" s="42" t="s">
+      <c r="D35" s="43" t="s">
         <v>261</v>
       </c>
-      <c r="E35" s="72"/>
-      <c r="F35" s="72"/>
+      <c r="E35" s="65"/>
+      <c r="F35" s="65"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="51" t="n">
+      <c r="A36" s="49" t="n">
         <v>4</v>
       </c>
-      <c r="B36" s="52" t="s">
+      <c r="B36" s="50" t="s">
         <v>262</v>
       </c>
-      <c r="C36" s="59" t="s">
+      <c r="C36" s="56" t="s">
         <v>263</v>
       </c>
-      <c r="D36" s="42" t="s">
+      <c r="D36" s="43" t="s">
         <v>264</v>
       </c>
-      <c r="E36" s="72"/>
-      <c r="F36" s="72"/>
+      <c r="E36" s="65"/>
+      <c r="F36" s="65"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="51" t="n">
+      <c r="A37" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="B37" s="52" t="s">
+      <c r="B37" s="50" t="s">
         <v>265</v>
       </c>
-      <c r="C37" s="59" t="s">
+      <c r="C37" s="56" t="s">
         <v>266</v>
       </c>
-      <c r="D37" s="42" t="s">
+      <c r="D37" s="43" t="s">
         <v>267</v>
       </c>
-      <c r="E37" s="72"/>
-      <c r="F37" s="72"/>
+      <c r="E37" s="65"/>
+      <c r="F37" s="65"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="51" t="n">
+      <c r="A38" s="49" t="n">
         <v>6</v>
       </c>
-      <c r="B38" s="52" t="s">
+      <c r="B38" s="50" t="s">
         <v>268</v>
       </c>
-      <c r="C38" s="59" t="s">
+      <c r="C38" s="56" t="s">
         <v>269</v>
       </c>
-      <c r="D38" s="42" t="s">
+      <c r="D38" s="43" t="s">
         <v>270</v>
       </c>
-      <c r="E38" s="72"/>
-      <c r="F38" s="72"/>
+      <c r="E38" s="65"/>
+      <c r="F38" s="65"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="51" t="n">
+      <c r="A39" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="B39" s="52" t="s">
+      <c r="B39" s="50" t="s">
         <v>271</v>
       </c>
-      <c r="C39" s="59" t="s">
+      <c r="C39" s="56" t="s">
         <v>272</v>
       </c>
-      <c r="D39" s="42" t="s">
+      <c r="D39" s="43" t="s">
         <v>273</v>
       </c>
-      <c r="E39" s="72"/>
-      <c r="F39" s="72"/>
+      <c r="E39" s="65"/>
+      <c r="F39" s="65"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="51" t="n">
+      <c r="A40" s="49" t="n">
         <v>8</v>
       </c>
-      <c r="B40" s="52" t="s">
+      <c r="B40" s="50" t="s">
         <v>274</v>
       </c>
-      <c r="C40" s="59" t="s">
+      <c r="C40" s="56" t="s">
         <v>275</v>
       </c>
-      <c r="D40" s="42" t="s">
+      <c r="D40" s="43" t="s">
         <v>276</v>
       </c>
-      <c r="E40" s="72"/>
-      <c r="F40" s="72"/>
+      <c r="E40" s="65"/>
+      <c r="F40" s="65"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="70" t="s">
+      <c r="A42" s="46" t="s">
         <v>277</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="K7:K15">
-    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>AND(ISNUMBER(K7),K7&gt;0)</formula>
     </cfRule>
-    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>AND(ISNUMBER(K7),K7&lt;0)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C25:C26">
-    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>AND(ISNUMBER(C25),C25&gt;0)</formula>
     </cfRule>
-    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>AND(ISNUMBER(C25),C25&lt;0)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C29">
-    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>AND(ISNUMBER(C29),C29&gt;0)</formula>
     </cfRule>
-    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>AND(ISNUMBER(C29),C29&lt;0)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5116,555 +5029,555 @@
   <dimension ref="A1:M29"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="46" width="5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="46" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="46" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="46" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="46" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="46" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="46" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="9" style="46" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="46" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="46" width="50"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="9" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="50"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="47" t="s">
         <v>278</v>
       </c>
-      <c r="H1" s="71" t="s">
+      <c r="H1" s="64" t="s">
         <v>279</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="49" t="s">
+      <c r="A2" s="3" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="76" t="s">
+      <c r="A3" s="69" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="50" t="s">
+      <c r="A5" s="4" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="12" t="s">
         <v>203</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D6" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="E6" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="F6" s="11" t="s">
+      <c r="F6" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="G6" s="11" t="s">
+      <c r="G6" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="H6" s="11" t="s">
+      <c r="H6" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="I6" s="11" t="s">
+      <c r="I6" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="J6" s="11" t="s">
+      <c r="J6" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="K6" s="11" t="s">
+      <c r="K6" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="L6" s="11" t="s">
+      <c r="L6" s="12" t="s">
         <v>223</v>
       </c>
-      <c r="M6" s="11" t="s">
+      <c r="M6" s="12" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="51" t="n">
+      <c r="A7" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="5" t="s">
         <v>282</v>
       </c>
-      <c r="C7" s="41" t="s">
+      <c r="C7" s="42" t="s">
         <v>283</v>
       </c>
-      <c r="D7" s="51" t="s">
+      <c r="D7" s="49" t="s">
         <v>284</v>
       </c>
-      <c r="E7" s="54" t="n">
+      <c r="E7" s="52" t="n">
         <v>-113</v>
       </c>
-      <c r="F7" s="55" t="n">
+      <c r="F7" s="44" t="n">
         <v>300</v>
       </c>
-      <c r="G7" s="56" t="n">
+      <c r="G7" s="53" t="n">
         <f aca="false">IF(E7&gt;0,F7*E7/100,F7*100/ABS(E7))</f>
         <v>265.486725663717</v>
       </c>
-      <c r="H7" s="56" t="n">
+      <c r="H7" s="53" t="n">
         <f aca="false">F7+G7</f>
         <v>565.486725663717</v>
       </c>
-      <c r="I7" s="72" t="s">
+      <c r="I7" s="65" t="s">
         <v>126</v>
       </c>
-      <c r="J7" s="56" t="n">
+      <c r="J7" s="53" t="n">
         <f aca="false">IF(I7="Win",F7+G7,IF(I7="Push",F7,IF(I7="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K7" s="58" t="n">
+      <c r="K7" s="55" t="n">
         <f aca="false">IF(I7="Pending",0,J7-F7)</f>
         <v>0</v>
       </c>
-      <c r="L7" s="73" t="n">
+      <c r="L7" s="66" t="n">
         <v>0.58</v>
       </c>
-      <c r="M7" s="77" t="s">
+      <c r="M7" s="70" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="51" t="n">
+      <c r="A8" s="49" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="5" t="s">
         <v>286</v>
       </c>
-      <c r="C8" s="41" t="s">
+      <c r="C8" s="42" t="s">
         <v>287</v>
       </c>
-      <c r="D8" s="51" t="s">
+      <c r="D8" s="49" t="s">
         <v>97</v>
       </c>
-      <c r="E8" s="54" t="n">
+      <c r="E8" s="52" t="n">
         <v>456</v>
       </c>
-      <c r="F8" s="55" t="n">
+      <c r="F8" s="44" t="n">
         <v>200</v>
       </c>
-      <c r="G8" s="56" t="n">
+      <c r="G8" s="53" t="n">
         <f aca="false">IF(E8&gt;0,F8*E8/100,F8*100/ABS(E8))</f>
         <v>912</v>
       </c>
-      <c r="H8" s="56" t="n">
+      <c r="H8" s="53" t="n">
         <f aca="false">F8+G8</f>
         <v>1112</v>
       </c>
-      <c r="I8" s="72" t="s">
+      <c r="I8" s="65" t="s">
         <v>126</v>
       </c>
-      <c r="J8" s="56" t="n">
+      <c r="J8" s="53" t="n">
         <f aca="false">IF(I8="Win",F8+G8,IF(I8="Push",F8,IF(I8="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K8" s="58" t="n">
+      <c r="K8" s="55" t="n">
         <f aca="false">IF(I8="Pending",0,J8-F8)</f>
         <v>0</v>
       </c>
-      <c r="L8" s="73" t="n">
+      <c r="L8" s="66" t="n">
         <v>0.24</v>
       </c>
-      <c r="M8" s="77" t="s">
+      <c r="M8" s="70" t="s">
         <v>288</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="51" t="n">
+      <c r="A9" s="49" t="n">
         <v>3</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="5" t="s">
         <v>289</v>
       </c>
-      <c r="C9" s="41" t="s">
+      <c r="C9" s="42" t="s">
         <v>290</v>
       </c>
-      <c r="D9" s="51" t="s">
+      <c r="D9" s="49" t="s">
         <v>193</v>
       </c>
-      <c r="E9" s="54" t="n">
+      <c r="E9" s="52" t="n">
         <v>1150</v>
       </c>
-      <c r="F9" s="55" t="n">
+      <c r="F9" s="44" t="n">
         <v>150</v>
       </c>
-      <c r="G9" s="56" t="n">
+      <c r="G9" s="53" t="n">
         <f aca="false">IF(E9&gt;0,F9*E9/100,F9*100/ABS(E9))</f>
         <v>1725</v>
       </c>
-      <c r="H9" s="56" t="n">
+      <c r="H9" s="53" t="n">
         <f aca="false">F9+G9</f>
         <v>1875</v>
       </c>
-      <c r="I9" s="72" t="s">
+      <c r="I9" s="65" t="s">
         <v>126</v>
       </c>
-      <c r="J9" s="56" t="n">
+      <c r="J9" s="53" t="n">
         <f aca="false">IF(I9="Win",F9+G9,IF(I9="Push",F9,IF(I9="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K9" s="58" t="n">
+      <c r="K9" s="55" t="n">
         <f aca="false">IF(I9="Pending",0,J9-F9)</f>
         <v>0</v>
       </c>
-      <c r="L9" s="73" t="n">
+      <c r="L9" s="66" t="n">
         <v>0.1</v>
       </c>
-      <c r="M9" s="77" t="s">
+      <c r="M9" s="70" t="s">
         <v>291</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="51" t="n">
+      <c r="A10" s="49" t="n">
         <v>4</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="5" t="s">
         <v>292</v>
       </c>
-      <c r="C10" s="41" t="s">
+      <c r="C10" s="42" t="s">
         <v>290</v>
       </c>
-      <c r="D10" s="51" t="s">
+      <c r="D10" s="49" t="s">
         <v>193</v>
       </c>
-      <c r="E10" s="54" t="n">
+      <c r="E10" s="52" t="n">
         <v>1567</v>
       </c>
-      <c r="F10" s="55" t="n">
+      <c r="F10" s="44" t="n">
         <v>120</v>
       </c>
-      <c r="G10" s="56" t="n">
+      <c r="G10" s="53" t="n">
         <f aca="false">IF(E10&gt;0,F10*E10/100,F10*100/ABS(E10))</f>
         <v>1880.4</v>
       </c>
-      <c r="H10" s="56" t="n">
+      <c r="H10" s="53" t="n">
         <f aca="false">F10+G10</f>
         <v>2000.4</v>
       </c>
-      <c r="I10" s="72" t="s">
+      <c r="I10" s="65" t="s">
         <v>126</v>
       </c>
-      <c r="J10" s="56" t="n">
+      <c r="J10" s="53" t="n">
         <f aca="false">IF(I10="Win",F10+G10,IF(I10="Push",F10,IF(I10="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K10" s="58" t="n">
+      <c r="K10" s="55" t="n">
         <f aca="false">IF(I10="Pending",0,J10-F10)</f>
         <v>0</v>
       </c>
-      <c r="L10" s="73" t="n">
+      <c r="L10" s="66" t="n">
         <v>0.08</v>
       </c>
-      <c r="M10" s="77" t="s">
+      <c r="M10" s="70" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="51" t="n">
+      <c r="A11" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="5" t="s">
         <v>294</v>
       </c>
-      <c r="C11" s="41" t="s">
+      <c r="C11" s="42" t="s">
         <v>290</v>
       </c>
-      <c r="D11" s="51" t="s">
+      <c r="D11" s="49" t="s">
         <v>193</v>
       </c>
-      <c r="E11" s="54" t="n">
+      <c r="E11" s="52" t="n">
         <v>1800</v>
       </c>
-      <c r="F11" s="55" t="n">
+      <c r="F11" s="44" t="n">
         <v>100</v>
       </c>
-      <c r="G11" s="56" t="n">
+      <c r="G11" s="53" t="n">
         <f aca="false">IF(E11&gt;0,F11*E11/100,F11*100/ABS(E11))</f>
         <v>1800</v>
       </c>
-      <c r="H11" s="56" t="n">
+      <c r="H11" s="53" t="n">
         <f aca="false">F11+G11</f>
         <v>1900</v>
       </c>
-      <c r="I11" s="72" t="s">
+      <c r="I11" s="65" t="s">
         <v>126</v>
       </c>
-      <c r="J11" s="56" t="n">
+      <c r="J11" s="53" t="n">
         <f aca="false">IF(I11="Win",F11+G11,IF(I11="Push",F11,IF(I11="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K11" s="58" t="n">
+      <c r="K11" s="55" t="n">
         <f aca="false">IF(I11="Pending",0,J11-F11)</f>
         <v>0</v>
       </c>
-      <c r="L11" s="73" t="n">
+      <c r="L11" s="66" t="n">
         <v>0.07</v>
       </c>
-      <c r="M11" s="77" t="s">
+      <c r="M11" s="70" t="s">
         <v>295</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="51" t="n">
+      <c r="A12" s="49" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="C12" s="41" t="s">
+      <c r="C12" s="42" t="s">
         <v>290</v>
       </c>
-      <c r="D12" s="51" t="s">
+      <c r="D12" s="49" t="s">
         <v>193</v>
       </c>
-      <c r="E12" s="54" t="n">
+      <c r="E12" s="52" t="n">
         <v>1150</v>
       </c>
-      <c r="F12" s="55" t="n">
+      <c r="F12" s="44" t="n">
         <v>90</v>
       </c>
-      <c r="G12" s="56" t="n">
+      <c r="G12" s="53" t="n">
         <f aca="false">IF(E12&gt;0,F12*E12/100,F12*100/ABS(E12))</f>
         <v>1035</v>
       </c>
-      <c r="H12" s="56" t="n">
+      <c r="H12" s="53" t="n">
         <f aca="false">F12+G12</f>
         <v>1125</v>
       </c>
-      <c r="I12" s="72" t="s">
+      <c r="I12" s="65" t="s">
         <v>126</v>
       </c>
-      <c r="J12" s="56" t="n">
+      <c r="J12" s="53" t="n">
         <f aca="false">IF(I12="Win",F12+G12,IF(I12="Push",F12,IF(I12="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K12" s="58" t="n">
+      <c r="K12" s="55" t="n">
         <f aca="false">IF(I12="Pending",0,J12-F12)</f>
         <v>0</v>
       </c>
-      <c r="L12" s="73" t="n">
+      <c r="L12" s="66" t="n">
         <v>0.08</v>
       </c>
-      <c r="M12" s="77" t="s">
+      <c r="M12" s="70" t="s">
         <v>297</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="51" t="n">
+      <c r="A13" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="5" t="s">
         <v>298</v>
       </c>
-      <c r="C13" s="41" t="s">
+      <c r="C13" s="42" t="s">
         <v>290</v>
       </c>
-      <c r="D13" s="51" t="s">
+      <c r="D13" s="49" t="s">
         <v>193</v>
       </c>
-      <c r="E13" s="54" t="n">
+      <c r="E13" s="52" t="n">
         <v>1900</v>
       </c>
-      <c r="F13" s="55" t="n">
+      <c r="F13" s="44" t="n">
         <v>40</v>
       </c>
-      <c r="G13" s="56" t="n">
+      <c r="G13" s="53" t="n">
         <f aca="false">IF(E13&gt;0,F13*E13/100,F13*100/ABS(E13))</f>
         <v>760</v>
       </c>
-      <c r="H13" s="56" t="n">
+      <c r="H13" s="53" t="n">
         <f aca="false">F13+G13</f>
         <v>800</v>
       </c>
-      <c r="I13" s="72" t="s">
+      <c r="I13" s="65" t="s">
         <v>126</v>
       </c>
-      <c r="J13" s="56" t="n">
+      <c r="J13" s="53" t="n">
         <f aca="false">IF(I13="Win",F13+G13,IF(I13="Push",F13,IF(I13="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K13" s="58" t="n">
+      <c r="K13" s="55" t="n">
         <f aca="false">IF(I13="Pending",0,J13-F13)</f>
         <v>0</v>
       </c>
-      <c r="L13" s="73" t="n">
+      <c r="L13" s="66" t="n">
         <v>0.05</v>
       </c>
-      <c r="M13" s="77" t="s">
+      <c r="M13" s="70" t="s">
         <v>299</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="36"/>
-      <c r="B14" s="37" t="s">
+      <c r="A14" s="37"/>
+      <c r="B14" s="38" t="s">
         <v>44</v>
       </c>
-      <c r="C14" s="36"/>
-      <c r="D14" s="36"/>
-      <c r="E14" s="36"/>
-      <c r="F14" s="63" t="n">
+      <c r="C14" s="37"/>
+      <c r="D14" s="37"/>
+      <c r="E14" s="37"/>
+      <c r="F14" s="39" t="n">
         <f aca="false">SUM(F7:F13)</f>
         <v>1000</v>
       </c>
-      <c r="G14" s="64" t="n">
+      <c r="G14" s="40" t="n">
         <f aca="false">SUM(G7:G13)</f>
         <v>8377.88672566372</v>
       </c>
-      <c r="H14" s="64" t="n">
+      <c r="H14" s="40" t="n">
         <f aca="false">SUM(H7:H13)</f>
         <v>9377.88672566372</v>
       </c>
-      <c r="I14" s="36"/>
-      <c r="J14" s="64" t="n">
+      <c r="I14" s="37"/>
+      <c r="J14" s="40" t="n">
         <f aca="false">SUM(J7:J13)</f>
         <v>0</v>
       </c>
-      <c r="K14" s="65" t="n">
+      <c r="K14" s="41" t="n">
         <f aca="false">SUM(K7:K13)</f>
         <v>0</v>
       </c>
-      <c r="L14" s="74" t="n">
+      <c r="L14" s="67" t="n">
         <f aca="false">SUM(L7:L13)</f>
         <v>1.2</v>
       </c>
-      <c r="M14" s="36"/>
+      <c r="M14" s="37"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="50" t="s">
+      <c r="B16" s="4" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="C17" s="66" t="n">
+      <c r="C17" s="60" t="n">
         <f aca="false">COUNTIF(I7:I13,"Win")</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="C18" s="66" t="n">
+      <c r="C18" s="60" t="n">
         <f aca="false">COUNTIF(I7:I13,"Loss")</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="C19" s="66" t="n">
+      <c r="C19" s="60" t="n">
         <f aca="false">COUNTIF(I7:I13,"Push")</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="C20" s="66" t="n">
+      <c r="C20" s="60" t="n">
         <f aca="false">COUNTIF(I7:I13,"Pending")</f>
         <v>7</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="C21" s="67" t="str">
+      <c r="C21" s="61" t="str">
         <f aca="false">IF(COUNTIF(I7:I13,"Win")+COUNTIF(I7:I13,"Loss")=0,"—",COUNTIF(I7:I13,"Win")/(COUNTIF(I7:I13,"Win")+COUNTIF(I7:I13,"Loss")))</f>
         <v>—</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="C22" s="68" t="n">
+      <c r="C22" s="62" t="n">
         <f aca="false">SUM(F7:F13)</f>
         <v>1000</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="C23" s="56" t="n">
+      <c r="C23" s="53" t="n">
         <f aca="false">SUM(J7:J13)</f>
         <v>0</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="C24" s="58" t="n">
+      <c r="C24" s="55" t="n">
         <f aca="false">SUM(K7:K13)</f>
         <v>0</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="C25" s="67" t="n">
+      <c r="C25" s="61" t="n">
         <f aca="false">IF(SUM(F7:F13)=0,"—",SUM(K7:K13)/SUM(F7:F13))</f>
         <v>0</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="4" t="s">
+      <c r="B26" s="5" t="s">
         <v>248</v>
       </c>
-      <c r="C26" s="75" t="n">
+      <c r="C26" s="68" t="n">
         <f aca="false">SUM(L7:L13)</f>
         <v>1.2</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="4" t="s">
+      <c r="B27" s="5" t="s">
         <v>300</v>
       </c>
-      <c r="C27" s="68" t="n">
+      <c r="C27" s="62" t="n">
         <f aca="false">2678</f>
         <v>2678</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="70" t="s">
+      <c r="A29" s="46" t="s">
         <v>301</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="K7:K14">
-    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>AND(ISNUMBER(K7),K7&gt;0)</formula>
     </cfRule>
-    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>AND(ISNUMBER(K7),K7&lt;0)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C24:C25">
-    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>AND(ISNUMBER(C24),C24&gt;0)</formula>
     </cfRule>
-    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>AND(ISNUMBER(C24),C24&lt;0)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5692,11 +5605,11 @@
   <dimension ref="A1:G28"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="46" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="46" width="38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="46" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="46" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="46" width="48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="48"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5705,366 +5618,366 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="49" t="s">
+      <c r="A2" s="3" t="s">
         <v>303</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="12" t="s">
         <v>304</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="12" t="s">
         <v>305</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="12" t="s">
         <v>306</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="12" t="s">
         <v>307</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="12" t="s">
         <v>308</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="F4" s="12" t="s">
         <v>309</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="G4" s="12" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="5" t="s">
         <v>310</v>
       </c>
-      <c r="B5" s="78" t="s">
+      <c r="B5" s="71" t="s">
         <v>311</v>
       </c>
-      <c r="C5" s="79"/>
-      <c r="D5" s="79" t="s">
+      <c r="C5" s="72"/>
+      <c r="D5" s="72" t="s">
         <v>312</v>
       </c>
-      <c r="E5" s="79" t="s">
+      <c r="E5" s="72" t="s">
         <v>312</v>
       </c>
-      <c r="F5" s="79"/>
-      <c r="G5" s="80" t="s">
+      <c r="F5" s="72"/>
+      <c r="G5" s="73" t="s">
         <v>313</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="5" t="s">
         <v>314</v>
       </c>
-      <c r="B6" s="78" t="s">
+      <c r="B6" s="71" t="s">
         <v>315</v>
       </c>
-      <c r="C6" s="79" t="s">
+      <c r="C6" s="72" t="s">
         <v>312</v>
       </c>
-      <c r="D6" s="79"/>
-      <c r="E6" s="79"/>
-      <c r="F6" s="79"/>
-      <c r="G6" s="80" t="s">
+      <c r="D6" s="72"/>
+      <c r="E6" s="72"/>
+      <c r="F6" s="72"/>
+      <c r="G6" s="73" t="s">
         <v>316</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="5" t="s">
         <v>317</v>
       </c>
-      <c r="B7" s="78" t="s">
+      <c r="B7" s="71" t="s">
         <v>318</v>
       </c>
-      <c r="C7" s="79" t="s">
+      <c r="C7" s="72" t="s">
         <v>312</v>
       </c>
-      <c r="D7" s="79"/>
-      <c r="E7" s="79"/>
-      <c r="F7" s="79"/>
-      <c r="G7" s="80" t="s">
+      <c r="D7" s="72"/>
+      <c r="E7" s="72"/>
+      <c r="F7" s="72"/>
+      <c r="G7" s="73" t="s">
         <v>319</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="5" t="s">
         <v>320</v>
       </c>
-      <c r="B8" s="78" t="s">
+      <c r="B8" s="71" t="s">
         <v>321</v>
       </c>
-      <c r="C8" s="79"/>
-      <c r="D8" s="79" t="s">
+      <c r="C8" s="72"/>
+      <c r="D8" s="72" t="s">
         <v>312</v>
       </c>
-      <c r="E8" s="79"/>
-      <c r="F8" s="79"/>
-      <c r="G8" s="80" t="s">
+      <c r="E8" s="72"/>
+      <c r="F8" s="72"/>
+      <c r="G8" s="73" t="s">
         <v>322</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="5" t="s">
         <v>323</v>
       </c>
-      <c r="B9" s="78" t="s">
+      <c r="B9" s="71" t="s">
         <v>324</v>
       </c>
-      <c r="C9" s="79"/>
-      <c r="D9" s="79" t="s">
+      <c r="C9" s="72"/>
+      <c r="D9" s="72" t="s">
         <v>312</v>
       </c>
-      <c r="E9" s="79"/>
-      <c r="F9" s="79" t="s">
+      <c r="E9" s="72"/>
+      <c r="F9" s="72" t="s">
         <v>312</v>
       </c>
-      <c r="G9" s="80" t="s">
+      <c r="G9" s="73" t="s">
         <v>325</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="5" t="s">
         <v>326</v>
       </c>
-      <c r="B10" s="78" t="s">
+      <c r="B10" s="71" t="s">
         <v>327</v>
       </c>
-      <c r="C10" s="79"/>
-      <c r="D10" s="79" t="s">
+      <c r="C10" s="72"/>
+      <c r="D10" s="72" t="s">
         <v>312</v>
       </c>
-      <c r="E10" s="79" t="s">
+      <c r="E10" s="72" t="s">
         <v>312</v>
       </c>
-      <c r="F10" s="79"/>
-      <c r="G10" s="80" t="s">
+      <c r="F10" s="72"/>
+      <c r="G10" s="73" t="s">
         <v>328</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="5" t="s">
         <v>329</v>
       </c>
-      <c r="B11" s="78" t="s">
+      <c r="B11" s="71" t="s">
         <v>330</v>
       </c>
-      <c r="C11" s="79"/>
-      <c r="D11" s="79" t="s">
+      <c r="C11" s="72"/>
+      <c r="D11" s="72" t="s">
         <v>312</v>
       </c>
-      <c r="E11" s="79"/>
-      <c r="F11" s="79" t="s">
+      <c r="E11" s="72"/>
+      <c r="F11" s="72" t="s">
         <v>312</v>
       </c>
-      <c r="G11" s="80" t="s">
+      <c r="G11" s="73" t="s">
         <v>331</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="5" t="s">
         <v>332</v>
       </c>
-      <c r="B12" s="78" t="s">
+      <c r="B12" s="71" t="s">
         <v>333</v>
       </c>
-      <c r="C12" s="79"/>
-      <c r="D12" s="79" t="s">
+      <c r="C12" s="72"/>
+      <c r="D12" s="72" t="s">
         <v>312</v>
       </c>
-      <c r="E12" s="79"/>
-      <c r="F12" s="79"/>
-      <c r="G12" s="80" t="s">
+      <c r="E12" s="72"/>
+      <c r="F12" s="72"/>
+      <c r="G12" s="73" t="s">
         <v>334</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="5" t="s">
         <v>335</v>
       </c>
-      <c r="B13" s="78" t="s">
+      <c r="B13" s="71" t="s">
         <v>336</v>
       </c>
-      <c r="C13" s="79"/>
-      <c r="D13" s="79" t="s">
+      <c r="C13" s="72"/>
+      <c r="D13" s="72" t="s">
         <v>312</v>
       </c>
-      <c r="E13" s="79"/>
-      <c r="F13" s="79"/>
-      <c r="G13" s="80" t="s">
+      <c r="E13" s="72"/>
+      <c r="F13" s="72"/>
+      <c r="G13" s="73" t="s">
         <v>337</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="5" t="s">
         <v>338</v>
       </c>
-      <c r="B14" s="78" t="s">
+      <c r="B14" s="71" t="s">
         <v>339</v>
       </c>
-      <c r="C14" s="79"/>
-      <c r="D14" s="79" t="s">
+      <c r="C14" s="72"/>
+      <c r="D14" s="72" t="s">
         <v>312</v>
       </c>
-      <c r="E14" s="79"/>
-      <c r="F14" s="79"/>
-      <c r="G14" s="80" t="s">
+      <c r="E14" s="72"/>
+      <c r="F14" s="72"/>
+      <c r="G14" s="73" t="s">
         <v>340</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="5" t="s">
         <v>341</v>
       </c>
-      <c r="B15" s="78" t="s">
+      <c r="B15" s="71" t="s">
         <v>342</v>
       </c>
-      <c r="C15" s="79"/>
-      <c r="D15" s="79" t="s">
+      <c r="C15" s="72"/>
+      <c r="D15" s="72" t="s">
         <v>312</v>
       </c>
-      <c r="E15" s="79"/>
-      <c r="F15" s="79"/>
-      <c r="G15" s="80" t="s">
+      <c r="E15" s="72"/>
+      <c r="F15" s="72"/>
+      <c r="G15" s="73" t="s">
         <v>343</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="5" t="s">
         <v>344</v>
       </c>
-      <c r="B16" s="78" t="s">
+      <c r="B16" s="71" t="s">
         <v>345</v>
       </c>
-      <c r="C16" s="79"/>
-      <c r="D16" s="79"/>
-      <c r="E16" s="79" t="s">
+      <c r="C16" s="72"/>
+      <c r="D16" s="72"/>
+      <c r="E16" s="72" t="s">
         <v>312</v>
       </c>
-      <c r="F16" s="79" t="s">
+      <c r="F16" s="72" t="s">
         <v>312</v>
       </c>
-      <c r="G16" s="80" t="s">
+      <c r="G16" s="73" t="s">
         <v>346</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="5" t="s">
         <v>347</v>
       </c>
-      <c r="B17" s="78" t="s">
+      <c r="B17" s="71" t="s">
         <v>348</v>
       </c>
-      <c r="C17" s="79"/>
-      <c r="D17" s="79"/>
-      <c r="E17" s="79" t="s">
+      <c r="C17" s="72"/>
+      <c r="D17" s="72"/>
+      <c r="E17" s="72" t="s">
         <v>312</v>
       </c>
-      <c r="F17" s="79"/>
-      <c r="G17" s="80" t="s">
+      <c r="F17" s="72"/>
+      <c r="G17" s="73" t="s">
         <v>349</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="5" t="s">
         <v>350</v>
       </c>
-      <c r="B18" s="78" t="s">
+      <c r="B18" s="71" t="s">
         <v>351</v>
       </c>
-      <c r="C18" s="79"/>
-      <c r="D18" s="79"/>
-      <c r="E18" s="79" t="s">
+      <c r="C18" s="72"/>
+      <c r="D18" s="72"/>
+      <c r="E18" s="72" t="s">
         <v>312</v>
       </c>
-      <c r="F18" s="79"/>
-      <c r="G18" s="80" t="s">
+      <c r="F18" s="72"/>
+      <c r="G18" s="73" t="s">
         <v>352</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="B19" s="78" t="s">
+      <c r="B19" s="71" t="s">
         <v>354</v>
       </c>
-      <c r="C19" s="79"/>
-      <c r="D19" s="79"/>
-      <c r="E19" s="79"/>
-      <c r="F19" s="79" t="s">
+      <c r="C19" s="72"/>
+      <c r="D19" s="72"/>
+      <c r="E19" s="72"/>
+      <c r="F19" s="72" t="s">
         <v>312</v>
       </c>
-      <c r="G19" s="80" t="s">
+      <c r="G19" s="73" t="s">
         <v>355</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="81" t="s">
+      <c r="A20" s="74" t="s">
         <v>356</v>
       </c>
-      <c r="B20" s="82" t="s">
+      <c r="B20" s="75" t="s">
         <v>357</v>
       </c>
-      <c r="D20" s="83" t="s">
+      <c r="D20" s="76" t="s">
         <v>312</v>
       </c>
-      <c r="F20" s="83" t="s">
+      <c r="F20" s="76" t="s">
         <v>312</v>
       </c>
-      <c r="G20" s="70" t="s">
+      <c r="G20" s="46" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="84" t="s">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="74" t="s">
         <v>359</v>
       </c>
-      <c r="B21" s="85" t="s">
+      <c r="B21" s="75" t="s">
         <v>360</v>
       </c>
-      <c r="G21" s="45" t="s">
+      <c r="G21" s="46" t="s">
         <v>361</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="84" t="s">
+      <c r="A22" s="74" t="s">
         <v>362</v>
       </c>
-      <c r="B22" s="85" t="s">
+      <c r="B22" s="75" t="s">
         <v>363</v>
       </c>
-      <c r="G22" s="45" t="s">
+      <c r="G22" s="46" t="s">
         <v>364</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="84" t="s">
+      <c r="A23" s="74" t="s">
         <v>365</v>
       </c>
-      <c r="B23" s="85" t="s">
+      <c r="B23" s="75" t="s">
         <v>366</v>
       </c>
-      <c r="G23" s="45" t="s">
+      <c r="G23" s="46" t="s">
         <v>367</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="86" t="s">
+      <c r="A25" s="77" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="49" t="s">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="3" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="49" t="s">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="3" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="49" t="s">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="3" t="s">
         <v>371</v>
       </c>
     </row>
@@ -6088,564 +6001,564 @@
   <dimension ref="A1:M30"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="46" width="5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="46" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="46" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="46" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="46" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="46" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="46" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="9" style="46" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="46" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="46" width="50"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="9" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="50"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="47" t="s">
         <v>372</v>
       </c>
-      <c r="H1" s="71" t="s">
+      <c r="H1" s="64" t="s">
         <v>373</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="49" t="s">
+      <c r="A2" s="3" t="s">
         <v>374</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="49" t="s">
+      <c r="A3" s="3" t="s">
         <v>375</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="50" t="s">
+      <c r="A5" s="4" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="12" t="s">
         <v>222</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D6" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="E6" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="F6" s="11" t="s">
+      <c r="F6" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="G6" s="11" t="s">
+      <c r="G6" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="H6" s="11" t="s">
+      <c r="H6" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="I6" s="11" t="s">
+      <c r="I6" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="J6" s="11" t="s">
+      <c r="J6" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="K6" s="11" t="s">
+      <c r="K6" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="L6" s="11" t="s">
+      <c r="L6" s="12" t="s">
         <v>223</v>
       </c>
-      <c r="M6" s="11" t="s">
+      <c r="M6" s="12" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="51" t="n">
+      <c r="A7" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="5" t="s">
         <v>376</v>
       </c>
-      <c r="C7" s="41" t="s">
+      <c r="C7" s="42" t="s">
         <v>377</v>
       </c>
-      <c r="D7" s="51" t="s">
+      <c r="D7" s="49" t="s">
         <v>378</v>
       </c>
-      <c r="E7" s="54" t="n">
+      <c r="E7" s="52" t="n">
         <v>-115</v>
       </c>
-      <c r="F7" s="55" t="n">
+      <c r="F7" s="44" t="n">
         <v>200</v>
       </c>
-      <c r="G7" s="56" t="n">
+      <c r="G7" s="53" t="n">
         <f aca="false">IF(E7&gt;0,F7*E7/100,F7*100/ABS(E7))</f>
         <v>173.913043478261</v>
       </c>
-      <c r="H7" s="56" t="n">
+      <c r="H7" s="53" t="n">
         <f aca="false">F7+G7</f>
         <v>373.913043478261</v>
       </c>
-      <c r="I7" s="72" t="s">
-        <v>126</v>
-      </c>
-      <c r="J7" s="56" t="n">
+      <c r="I7" s="57" t="s">
+        <v>101</v>
+      </c>
+      <c r="J7" s="53" t="n">
         <f aca="false">IF(I7="Win",F7+G7,IF(I7="Push",F7,IF(I7="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K7" s="58" t="n">
+      <c r="K7" s="55" t="n">
         <f aca="false">IF(I7="Pending",0,J7-F7)</f>
-        <v>0</v>
-      </c>
-      <c r="L7" s="73" t="n">
+        <v>-200</v>
+      </c>
+      <c r="L7" s="66" t="n">
         <v>0.56</v>
       </c>
-      <c r="M7" s="77" t="s">
+      <c r="M7" s="70" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="51" t="n">
+      <c r="A8" s="49" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="5" t="s">
         <v>380</v>
       </c>
-      <c r="C8" s="41" t="s">
+      <c r="C8" s="42" t="s">
         <v>381</v>
       </c>
-      <c r="D8" s="51" t="s">
+      <c r="D8" s="49" t="s">
         <v>182</v>
       </c>
-      <c r="E8" s="54" t="n">
+      <c r="E8" s="52" t="n">
         <v>-112</v>
       </c>
-      <c r="F8" s="55" t="n">
+      <c r="F8" s="44" t="n">
         <v>150</v>
       </c>
-      <c r="G8" s="56" t="n">
+      <c r="G8" s="53" t="n">
         <f aca="false">IF(E8&gt;0,F8*E8/100,F8*100/ABS(E8))</f>
         <v>133.928571428571</v>
       </c>
-      <c r="H8" s="56" t="n">
+      <c r="H8" s="53" t="n">
         <f aca="false">F8+G8</f>
         <v>283.928571428571</v>
       </c>
-      <c r="I8" s="72" t="s">
-        <v>126</v>
-      </c>
-      <c r="J8" s="56" t="n">
+      <c r="I8" s="57" t="s">
+        <v>101</v>
+      </c>
+      <c r="J8" s="53" t="n">
         <f aca="false">IF(I8="Win",F8+G8,IF(I8="Push",F8,IF(I8="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K8" s="58" t="n">
+      <c r="K8" s="55" t="n">
         <f aca="false">IF(I8="Pending",0,J8-F8)</f>
-        <v>0</v>
-      </c>
-      <c r="L8" s="73" t="n">
+        <v>-150</v>
+      </c>
+      <c r="L8" s="66" t="n">
         <v>0.56</v>
       </c>
-      <c r="M8" s="77" t="s">
+      <c r="M8" s="70" t="s">
         <v>382</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="51" t="n">
+      <c r="A9" s="49" t="n">
         <v>3</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="5" t="s">
         <v>383</v>
       </c>
-      <c r="C9" s="41" t="s">
+      <c r="C9" s="42" t="s">
         <v>384</v>
       </c>
-      <c r="D9" s="51" t="s">
+      <c r="D9" s="49" t="s">
         <v>97</v>
       </c>
-      <c r="E9" s="54" t="n">
+      <c r="E9" s="52" t="n">
         <v>-159</v>
       </c>
-      <c r="F9" s="55" t="n">
+      <c r="F9" s="44" t="n">
         <v>150</v>
       </c>
-      <c r="G9" s="56" t="n">
+      <c r="G9" s="53" t="n">
         <f aca="false">IF(E9&gt;0,F9*E9/100,F9*100/ABS(E9))</f>
         <v>94.3396226415094</v>
       </c>
-      <c r="H9" s="56" t="n">
+      <c r="H9" s="53" t="n">
         <f aca="false">F9+G9</f>
         <v>244.339622641509</v>
       </c>
-      <c r="I9" s="72" t="s">
-        <v>126</v>
-      </c>
-      <c r="J9" s="56" t="n">
+      <c r="I9" s="54" t="s">
+        <v>93</v>
+      </c>
+      <c r="J9" s="53" t="n">
         <f aca="false">IF(I9="Win",F9+G9,IF(I9="Push",F9,IF(I9="Loss",0,0)))</f>
-        <v>0</v>
-      </c>
-      <c r="K9" s="58" t="n">
+        <v>244.339622641509</v>
+      </c>
+      <c r="K9" s="55" t="n">
         <f aca="false">IF(I9="Pending",0,J9-F9)</f>
-        <v>0</v>
-      </c>
-      <c r="L9" s="73" t="n">
+        <v>94.3396226415094</v>
+      </c>
+      <c r="L9" s="66" t="n">
         <v>0.65</v>
       </c>
-      <c r="M9" s="77" t="s">
+      <c r="M9" s="70" t="s">
         <v>385</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="51" t="n">
+      <c r="A10" s="49" t="n">
         <v>4</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="5" t="s">
         <v>386</v>
       </c>
-      <c r="C10" s="41" t="s">
+      <c r="C10" s="42" t="s">
         <v>387</v>
       </c>
-      <c r="D10" s="51" t="s">
+      <c r="D10" s="49" t="s">
         <v>378</v>
       </c>
-      <c r="E10" s="54" t="n">
+      <c r="E10" s="52" t="n">
         <v>-108</v>
       </c>
-      <c r="F10" s="55" t="n">
+      <c r="F10" s="44" t="n">
         <v>150</v>
       </c>
-      <c r="G10" s="56" t="n">
+      <c r="G10" s="53" t="n">
         <f aca="false">IF(E10&gt;0,F10*E10/100,F10*100/ABS(E10))</f>
         <v>138.888888888889</v>
       </c>
-      <c r="H10" s="56" t="n">
+      <c r="H10" s="53" t="n">
         <f aca="false">F10+G10</f>
         <v>288.888888888889</v>
       </c>
-      <c r="I10" s="72" t="s">
+      <c r="I10" s="65" t="s">
         <v>126</v>
       </c>
-      <c r="J10" s="56" t="n">
+      <c r="J10" s="53" t="n">
         <f aca="false">IF(I10="Win",F10+G10,IF(I10="Push",F10,IF(I10="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K10" s="58" t="n">
+      <c r="K10" s="55" t="n">
         <f aca="false">IF(I10="Pending",0,J10-F10)</f>
         <v>0</v>
       </c>
-      <c r="L10" s="73" t="n">
+      <c r="L10" s="66" t="n">
         <v>0.55</v>
       </c>
-      <c r="M10" s="77" t="s">
+      <c r="M10" s="70" t="s">
         <v>388</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="51" t="n">
+      <c r="A11" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="5" t="s">
         <v>389</v>
       </c>
-      <c r="C11" s="41" t="s">
+      <c r="C11" s="42" t="s">
         <v>390</v>
       </c>
-      <c r="D11" s="51" t="s">
+      <c r="D11" s="49" t="s">
         <v>97</v>
       </c>
-      <c r="E11" s="54" t="n">
+      <c r="E11" s="52" t="n">
         <v>-120</v>
       </c>
-      <c r="F11" s="55" t="n">
+      <c r="F11" s="44" t="n">
         <v>130</v>
       </c>
-      <c r="G11" s="56" t="n">
+      <c r="G11" s="53" t="n">
         <f aca="false">IF(E11&gt;0,F11*E11/100,F11*100/ABS(E11))</f>
         <v>108.333333333333</v>
       </c>
-      <c r="H11" s="56" t="n">
+      <c r="H11" s="53" t="n">
         <f aca="false">F11+G11</f>
         <v>238.333333333333</v>
       </c>
-      <c r="I11" s="72" t="s">
+      <c r="I11" s="65" t="s">
         <v>126</v>
       </c>
-      <c r="J11" s="56" t="n">
+      <c r="J11" s="53" t="n">
         <f aca="false">IF(I11="Win",F11+G11,IF(I11="Push",F11,IF(I11="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K11" s="58" t="n">
+      <c r="K11" s="55" t="n">
         <f aca="false">IF(I11="Pending",0,J11-F11)</f>
         <v>0</v>
       </c>
-      <c r="L11" s="73" t="n">
+      <c r="L11" s="66" t="n">
         <v>0.6</v>
       </c>
-      <c r="M11" s="77" t="s">
+      <c r="M11" s="70" t="s">
         <v>391</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="51" t="n">
+      <c r="A12" s="49" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="5" t="s">
         <v>392</v>
       </c>
-      <c r="C12" s="41" t="s">
+      <c r="C12" s="42" t="s">
         <v>393</v>
       </c>
-      <c r="D12" s="51" t="s">
+      <c r="D12" s="49" t="s">
         <v>97</v>
       </c>
-      <c r="E12" s="54" t="n">
+      <c r="E12" s="52" t="n">
         <v>-121</v>
       </c>
-      <c r="F12" s="55" t="n">
+      <c r="F12" s="44" t="n">
         <v>120</v>
       </c>
-      <c r="G12" s="56" t="n">
+      <c r="G12" s="53" t="n">
         <f aca="false">IF(E12&gt;0,F12*E12/100,F12*100/ABS(E12))</f>
         <v>99.1735537190083</v>
       </c>
-      <c r="H12" s="56" t="n">
+      <c r="H12" s="53" t="n">
         <f aca="false">F12+G12</f>
         <v>219.173553719008</v>
       </c>
-      <c r="I12" s="72" t="s">
+      <c r="I12" s="65" t="s">
         <v>126</v>
       </c>
-      <c r="J12" s="56" t="n">
+      <c r="J12" s="53" t="n">
         <f aca="false">IF(I12="Win",F12+G12,IF(I12="Push",F12,IF(I12="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K12" s="58" t="n">
+      <c r="K12" s="55" t="n">
         <f aca="false">IF(I12="Pending",0,J12-F12)</f>
         <v>0</v>
       </c>
-      <c r="L12" s="73" t="n">
+      <c r="L12" s="66" t="n">
         <v>0.58</v>
       </c>
-      <c r="M12" s="77" t="s">
+      <c r="M12" s="70" t="s">
         <v>394</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="51" t="n">
+      <c r="A13" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="5" t="s">
         <v>395</v>
       </c>
-      <c r="C13" s="41" t="s">
+      <c r="C13" s="42" t="s">
         <v>396</v>
       </c>
-      <c r="D13" s="51" t="s">
+      <c r="D13" s="49" t="s">
         <v>120</v>
       </c>
-      <c r="E13" s="54" t="n">
+      <c r="E13" s="52" t="n">
         <v>971</v>
       </c>
-      <c r="F13" s="55" t="n">
+      <c r="F13" s="44" t="n">
         <v>100</v>
       </c>
-      <c r="G13" s="56" t="n">
+      <c r="G13" s="53" t="n">
         <f aca="false">IF(E13&gt;0,F13*E13/100,F13*100/ABS(E13))</f>
         <v>971</v>
       </c>
-      <c r="H13" s="56" t="n">
+      <c r="H13" s="53" t="n">
         <f aca="false">F13+G13</f>
         <v>1071</v>
       </c>
-      <c r="I13" s="72" t="s">
-        <v>126</v>
-      </c>
-      <c r="J13" s="56" t="n">
+      <c r="I13" s="57" t="s">
+        <v>101</v>
+      </c>
+      <c r="J13" s="53" t="n">
         <f aca="false">IF(I13="Win",F13+G13,IF(I13="Push",F13,IF(I13="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K13" s="58" t="n">
+      <c r="K13" s="55" t="n">
         <f aca="false">IF(I13="Pending",0,J13-F13)</f>
-        <v>0</v>
-      </c>
-      <c r="L13" s="73" t="n">
+        <v>-100</v>
+      </c>
+      <c r="L13" s="66" t="n">
         <v>0.12</v>
       </c>
-      <c r="M13" s="77" t="s">
+      <c r="M13" s="70" t="s">
         <v>397</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="36"/>
-      <c r="B14" s="37" t="s">
+      <c r="A14" s="37"/>
+      <c r="B14" s="38" t="s">
         <v>44</v>
       </c>
-      <c r="C14" s="36"/>
-      <c r="D14" s="36"/>
-      <c r="E14" s="36"/>
-      <c r="F14" s="63" t="n">
+      <c r="C14" s="37"/>
+      <c r="D14" s="37"/>
+      <c r="E14" s="37"/>
+      <c r="F14" s="39" t="n">
         <f aca="false">SUM(F7:F13)</f>
         <v>1000</v>
       </c>
-      <c r="G14" s="64" t="n">
+      <c r="G14" s="40" t="n">
         <f aca="false">SUM(G7:G13)</f>
         <v>1719.57701348957</v>
       </c>
-      <c r="H14" s="64" t="n">
+      <c r="H14" s="40" t="n">
         <f aca="false">SUM(H7:H13)</f>
         <v>2719.57701348957</v>
       </c>
-      <c r="I14" s="36"/>
-      <c r="J14" s="64" t="n">
+      <c r="I14" s="37"/>
+      <c r="J14" s="40" t="n">
         <f aca="false">SUM(J7:J13)</f>
-        <v>0</v>
-      </c>
-      <c r="K14" s="65" t="n">
+        <v>244.339622641509</v>
+      </c>
+      <c r="K14" s="41" t="n">
         <f aca="false">SUM(K7:K13)</f>
-        <v>0</v>
-      </c>
-      <c r="L14" s="74" t="n">
+        <v>-355.660377358491</v>
+      </c>
+      <c r="L14" s="67" t="n">
         <f aca="false">SUM(L7:L13)</f>
         <v>3.62</v>
       </c>
-      <c r="M14" s="36"/>
+      <c r="M14" s="37"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="50" t="s">
+      <c r="B16" s="4" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="C17" s="66" t="n">
+      <c r="C17" s="60" t="n">
         <f aca="false">COUNTIF(I7:I13,"Win")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="C18" s="66" t="n">
+      <c r="C18" s="60" t="n">
         <f aca="false">COUNTIF(I7:I13,"Loss")</f>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="C19" s="66" t="n">
+      <c r="C19" s="60" t="n">
         <f aca="false">COUNTIF(I7:I13,"Push")</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="C20" s="66" t="n">
+      <c r="C20" s="60" t="n">
         <f aca="false">COUNTIF(I7:I13,"Pending")</f>
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="C21" s="67" t="str">
+      <c r="C21" s="61" t="n">
         <f aca="false">IF(COUNTIF(I7:I13,"Win")+COUNTIF(I7:I13,"Loss")=0,"—",COUNTIF(I7:I13,"Win")/(COUNTIF(I7:I13,"Win")+COUNTIF(I7:I13,"Loss")))</f>
-        <v>—</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="C22" s="68" t="n">
+      <c r="C22" s="62" t="n">
         <f aca="false">SUM(F7:F13)</f>
         <v>1000</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="C23" s="56" t="n">
+      <c r="C23" s="53" t="n">
         <f aca="false">SUM(J7:J13)</f>
-        <v>0</v>
+        <v>244.339622641509</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="C24" s="58" t="n">
+      <c r="C24" s="55" t="n">
         <f aca="false">SUM(K7:K13)</f>
-        <v>0</v>
+        <v>-355.660377358491</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="C25" s="67" t="n">
+      <c r="C25" s="61" t="n">
         <f aca="false">IF(SUM(F7:F13)=0,"—",SUM(K7:K13)/SUM(F7:F13))</f>
-        <v>0</v>
+        <v>-0.355660377358491</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="4" t="s">
+      <c r="B26" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="C26" s="56" t="n">
+      <c r="C26" s="53" t="n">
         <f aca="false">SUM(H7:H13)</f>
         <v>2719.57701348957</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="4" t="s">
+      <c r="B27" s="5" t="s">
         <v>248</v>
       </c>
-      <c r="C27" s="75" t="n">
+      <c r="C27" s="68" t="n">
         <f aca="false">SUM(L7:L13)</f>
         <v>3.62</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="4" t="s">
+      <c r="B28" s="5" t="s">
         <v>249</v>
       </c>
-      <c r="C28" s="58" t="n">
+      <c r="C28" s="55" t="n">
         <f aca="false">SUMPRODUCT(L7:L13,G7:G13)-SUMPRODUCT(1-L7:L13,F7:F13)</f>
         <v>84.7416091107209</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="70" t="s">
+      <c r="A30" s="46" t="s">
         <v>398</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="K7:K14">
-    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>AND(ISNUMBER(K7),K7&gt;0)</formula>
     </cfRule>
-    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>AND(ISNUMBER(K7),K7&lt;0)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C24:C25">
-    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>AND(ISNUMBER(C24),C24&gt;0)</formula>
     </cfRule>
-    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>AND(ISNUMBER(C24),C24&lt;0)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6674,485 +6587,485 @@
   <dimension ref="A1:M24"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="9" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="50"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="9" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="50"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="87" t="s">
+    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="47" t="s">
         <v>399</v>
       </c>
-      <c r="H1" s="88" t="s">
+      <c r="H1" s="64" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="4" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="12" t="s">
         <v>203</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D6" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="E6" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="F6" s="11" t="s">
+      <c r="F6" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="G6" s="11" t="s">
+      <c r="G6" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="H6" s="11" t="s">
+      <c r="H6" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="I6" s="11" t="s">
+      <c r="I6" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="J6" s="11" t="s">
+      <c r="J6" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="K6" s="11" t="s">
+      <c r="K6" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="L6" s="11" t="s">
+      <c r="L6" s="12" t="s">
         <v>223</v>
       </c>
-      <c r="M6" s="11" t="s">
+      <c r="M6" s="12" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="51" t="n">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="5" t="s">
         <v>403</v>
       </c>
-      <c r="C7" s="41" t="s">
+      <c r="C7" s="42" t="s">
         <v>290</v>
       </c>
-      <c r="D7" s="51" t="s">
+      <c r="D7" s="49" t="s">
         <v>193</v>
       </c>
-      <c r="E7" s="54" t="n">
+      <c r="E7" s="52" t="n">
         <v>450</v>
       </c>
-      <c r="F7" s="43" t="n">
+      <c r="F7" s="44" t="n">
         <v>200</v>
       </c>
-      <c r="G7" s="89" t="n">
+      <c r="G7" s="53" t="n">
         <f aca="false">IF(E7&gt;0,F7*E7/100,F7*100/ABS(E7))</f>
         <v>900</v>
       </c>
-      <c r="H7" s="89" t="n">
+      <c r="H7" s="53" t="n">
         <f aca="false">F7+G7</f>
         <v>1100</v>
       </c>
-      <c r="I7" s="72" t="s">
+      <c r="I7" s="65" t="s">
         <v>126</v>
       </c>
-      <c r="J7" s="89" t="n">
+      <c r="J7" s="53" t="n">
         <f aca="false">IF(I7="Win",F7+G7,IF(I7="Push",F7,IF(I7="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K7" s="90" t="n">
+      <c r="K7" s="55" t="n">
         <f aca="false">IF(I7="Pending",0,J7-F7)</f>
         <v>0</v>
       </c>
-      <c r="L7" s="91" t="n">
+      <c r="L7" s="78" t="n">
         <v>0.18</v>
       </c>
-      <c r="M7" s="77" t="s">
+      <c r="M7" s="70" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="51" t="n">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="49" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="5" t="s">
         <v>405</v>
       </c>
-      <c r="C8" s="41" t="s">
+      <c r="C8" s="42" t="s">
         <v>290</v>
       </c>
-      <c r="D8" s="51" t="s">
+      <c r="D8" s="49" t="s">
         <v>193</v>
       </c>
-      <c r="E8" s="54" t="n">
+      <c r="E8" s="52" t="n">
         <v>1600</v>
       </c>
-      <c r="F8" s="43" t="n">
+      <c r="F8" s="44" t="n">
         <v>100</v>
       </c>
-      <c r="G8" s="89" t="n">
+      <c r="G8" s="53" t="n">
         <f aca="false">IF(E8&gt;0,F8*E8/100,F8*100/ABS(E8))</f>
         <v>1600</v>
       </c>
-      <c r="H8" s="89" t="n">
+      <c r="H8" s="53" t="n">
         <f aca="false">F8+G8</f>
         <v>1700</v>
       </c>
-      <c r="I8" s="72" t="s">
+      <c r="I8" s="65" t="s">
         <v>126</v>
       </c>
-      <c r="J8" s="89" t="n">
+      <c r="J8" s="53" t="n">
         <f aca="false">IF(I8="Win",F8+G8,IF(I8="Push",F8,IF(I8="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K8" s="90" t="n">
+      <c r="K8" s="55" t="n">
         <f aca="false">IF(I8="Pending",0,J8-F8)</f>
         <v>0</v>
       </c>
-      <c r="L8" s="91" t="n">
+      <c r="L8" s="78" t="n">
         <v>0.07</v>
       </c>
-      <c r="M8" s="77" t="s">
+      <c r="M8" s="70" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="51" t="n">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="49" t="n">
         <v>3</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="5" t="s">
         <v>407</v>
       </c>
-      <c r="C9" s="41" t="s">
+      <c r="C9" s="42" t="s">
         <v>290</v>
       </c>
-      <c r="D9" s="51" t="s">
+      <c r="D9" s="49" t="s">
         <v>193</v>
       </c>
-      <c r="E9" s="54" t="n">
+      <c r="E9" s="52" t="n">
         <v>1600</v>
       </c>
-      <c r="F9" s="43" t="n">
+      <c r="F9" s="44" t="n">
         <v>100</v>
       </c>
-      <c r="G9" s="89" t="n">
+      <c r="G9" s="53" t="n">
         <f aca="false">IF(E9&gt;0,F9*E9/100,F9*100/ABS(E9))</f>
         <v>1600</v>
       </c>
-      <c r="H9" s="89" t="n">
+      <c r="H9" s="53" t="n">
         <f aca="false">F9+G9</f>
         <v>1700</v>
       </c>
-      <c r="I9" s="72" t="s">
+      <c r="I9" s="65" t="s">
         <v>126</v>
       </c>
-      <c r="J9" s="89" t="n">
+      <c r="J9" s="53" t="n">
         <f aca="false">IF(I9="Win",F9+G9,IF(I9="Push",F9,IF(I9="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K9" s="90" t="n">
+      <c r="K9" s="55" t="n">
         <f aca="false">IF(I9="Pending",0,J9-F9)</f>
         <v>0</v>
       </c>
-      <c r="L9" s="91" t="n">
+      <c r="L9" s="78" t="n">
         <v>0.07</v>
       </c>
-      <c r="M9" s="77" t="s">
+      <c r="M9" s="70" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="51" t="n">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="49" t="n">
         <v>4</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="5" t="s">
         <v>409</v>
       </c>
-      <c r="C10" s="41" t="s">
+      <c r="C10" s="42" t="s">
         <v>290</v>
       </c>
-      <c r="D10" s="51" t="s">
+      <c r="D10" s="49" t="s">
         <v>193</v>
       </c>
-      <c r="E10" s="54" t="n">
+      <c r="E10" s="52" t="n">
         <v>2000</v>
       </c>
-      <c r="F10" s="43" t="n">
+      <c r="F10" s="44" t="n">
         <v>80</v>
       </c>
-      <c r="G10" s="89" t="n">
+      <c r="G10" s="53" t="n">
         <f aca="false">IF(E10&gt;0,F10*E10/100,F10*100/ABS(E10))</f>
         <v>1600</v>
       </c>
-      <c r="H10" s="89" t="n">
+      <c r="H10" s="53" t="n">
         <f aca="false">F10+G10</f>
         <v>1680</v>
       </c>
-      <c r="I10" s="72" t="s">
+      <c r="I10" s="65" t="s">
         <v>126</v>
       </c>
-      <c r="J10" s="89" t="n">
+      <c r="J10" s="53" t="n">
         <f aca="false">IF(I10="Win",F10+G10,IF(I10="Push",F10,IF(I10="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K10" s="90" t="n">
+      <c r="K10" s="55" t="n">
         <f aca="false">IF(I10="Pending",0,J10-F10)</f>
         <v>0</v>
       </c>
-      <c r="L10" s="91" t="n">
+      <c r="L10" s="78" t="n">
         <v>0.055</v>
       </c>
-      <c r="M10" s="77" t="s">
+      <c r="M10" s="70" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="51" t="n">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="5" t="s">
         <v>411</v>
       </c>
-      <c r="C11" s="41" t="s">
+      <c r="C11" s="42" t="s">
         <v>290</v>
       </c>
-      <c r="D11" s="51" t="s">
+      <c r="D11" s="49" t="s">
         <v>193</v>
       </c>
-      <c r="E11" s="54" t="n">
+      <c r="E11" s="52" t="n">
         <v>2800</v>
       </c>
-      <c r="F11" s="43" t="n">
+      <c r="F11" s="44" t="n">
         <v>70</v>
       </c>
-      <c r="G11" s="89" t="n">
+      <c r="G11" s="53" t="n">
         <f aca="false">IF(E11&gt;0,F11*E11/100,F11*100/ABS(E11))</f>
         <v>1960</v>
       </c>
-      <c r="H11" s="89" t="n">
+      <c r="H11" s="53" t="n">
         <f aca="false">F11+G11</f>
         <v>2030</v>
       </c>
-      <c r="I11" s="72" t="s">
+      <c r="I11" s="65" t="s">
         <v>126</v>
       </c>
-      <c r="J11" s="89" t="n">
+      <c r="J11" s="53" t="n">
         <f aca="false">IF(I11="Win",F11+G11,IF(I11="Push",F11,IF(I11="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K11" s="90" t="n">
+      <c r="K11" s="55" t="n">
         <f aca="false">IF(I11="Pending",0,J11-F11)</f>
         <v>0</v>
       </c>
-      <c r="L11" s="91" t="n">
+      <c r="L11" s="78" t="n">
         <v>0.045</v>
       </c>
-      <c r="M11" s="77" t="s">
+      <c r="M11" s="70" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="51" t="n">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="49" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="5" t="s">
         <v>413</v>
       </c>
-      <c r="C12" s="41" t="s">
+      <c r="C12" s="42" t="s">
         <v>290</v>
       </c>
-      <c r="D12" s="51" t="s">
+      <c r="D12" s="49" t="s">
         <v>193</v>
       </c>
-      <c r="E12" s="54" t="n">
+      <c r="E12" s="52" t="n">
         <v>5000</v>
       </c>
-      <c r="F12" s="43" t="n">
+      <c r="F12" s="44" t="n">
         <v>50</v>
       </c>
-      <c r="G12" s="89" t="n">
+      <c r="G12" s="53" t="n">
         <f aca="false">IF(E12&gt;0,F12*E12/100,F12*100/ABS(E12))</f>
         <v>2500</v>
       </c>
-      <c r="H12" s="89" t="n">
+      <c r="H12" s="53" t="n">
         <f aca="false">F12+G12</f>
         <v>2550</v>
       </c>
-      <c r="I12" s="72" t="s">
+      <c r="I12" s="65" t="s">
         <v>126</v>
       </c>
-      <c r="J12" s="89" t="n">
+      <c r="J12" s="53" t="n">
         <f aca="false">IF(I12="Win",F12+G12,IF(I12="Push",F12,IF(I12="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K12" s="90" t="n">
+      <c r="K12" s="55" t="n">
         <f aca="false">IF(I12="Pending",0,J12-F12)</f>
         <v>0</v>
       </c>
-      <c r="L12" s="91" t="n">
+      <c r="L12" s="78" t="n">
         <v>0.025</v>
       </c>
-      <c r="M12" s="77" t="s">
+      <c r="M12" s="70" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="27" t="n">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="28" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="21" t="s">
+      <c r="B13" s="22" t="s">
         <v>415</v>
       </c>
-      <c r="C13" s="27" t="s">
+      <c r="C13" s="28" t="s">
         <v>416</v>
       </c>
-      <c r="D13" s="27" t="s">
+      <c r="D13" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="E13" s="27"/>
-      <c r="F13" s="27"/>
-      <c r="G13" s="27"/>
-      <c r="H13" s="27"/>
-      <c r="I13" s="27"/>
-      <c r="J13" s="27"/>
-      <c r="K13" s="27"/>
-      <c r="L13" s="27"/>
-      <c r="M13" s="27" t="s">
+      <c r="E13" s="28"/>
+      <c r="F13" s="28"/>
+      <c r="G13" s="28"/>
+      <c r="H13" s="28"/>
+      <c r="I13" s="28"/>
+      <c r="J13" s="28"/>
+      <c r="K13" s="28"/>
+      <c r="L13" s="28"/>
+      <c r="M13" s="28" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="36"/>
-      <c r="B14" s="37" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="37"/>
+      <c r="B14" s="38" t="s">
         <v>418</v>
       </c>
-      <c r="C14" s="36"/>
-      <c r="D14" s="36"/>
-      <c r="E14" s="36"/>
-      <c r="F14" s="38" t="n">
+      <c r="C14" s="37"/>
+      <c r="D14" s="37"/>
+      <c r="E14" s="37"/>
+      <c r="F14" s="39" t="n">
         <f aca="false">SUM(F7:F13)</f>
         <v>600</v>
       </c>
-      <c r="G14" s="39" t="n">
+      <c r="G14" s="40" t="n">
         <f aca="false">SUM(G7:G12)</f>
         <v>10160</v>
       </c>
-      <c r="H14" s="39" t="n">
+      <c r="H14" s="40" t="n">
         <f aca="false">SUM(H7:H12)</f>
         <v>10760</v>
       </c>
-      <c r="I14" s="36"/>
-      <c r="J14" s="39" t="n">
+      <c r="I14" s="37"/>
+      <c r="J14" s="40" t="n">
         <f aca="false">SUM(J7:J12)</f>
         <v>0</v>
       </c>
-      <c r="K14" s="40" t="n">
+      <c r="K14" s="41" t="n">
         <f aca="false">SUM(K7:K12)</f>
         <v>0</v>
       </c>
-      <c r="L14" s="92" t="n">
+      <c r="L14" s="79" t="n">
         <f aca="false">SUM(L7:L12)</f>
         <v>0.445</v>
       </c>
-      <c r="M14" s="36"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="3" t="s">
+      <c r="M14" s="37"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B16" s="4" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="4" t="s">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B17" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="C17" s="66" t="n">
+      <c r="C17" s="60" t="n">
         <f aca="false">COUNTIF(I7:I12,"Win")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="4" t="s">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B18" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="C18" s="66" t="n">
+      <c r="C18" s="60" t="n">
         <f aca="false">COUNTIF(I7:I12,"Loss")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="4" t="s">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B19" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="C19" s="66" t="n">
+      <c r="C19" s="60" t="n">
         <f aca="false">COUNTIF(I7:I12,"Pending")</f>
         <v>6</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="4" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B20" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="C20" s="67" t="str">
+      <c r="C20" s="61" t="str">
         <f aca="false">IF(COUNTIF(I7:I12,"Win")+COUNTIF(I7:I12,"Loss")=0,"—",COUNTIF(I7:I12,"Win")/(COUNTIF(I7:I12,"Win")+COUNTIF(I7:I12,"Loss")))</f>
         <v>—</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="4" t="s">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B21" s="5" t="s">
         <v>419</v>
       </c>
-      <c r="C21" s="93" t="n">
+      <c r="C21" s="62" t="n">
         <f aca="false">SUM(F7:F12)</f>
         <v>600</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="4" t="s">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B22" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="C22" s="89" t="n">
+      <c r="C22" s="53" t="n">
         <f aca="false">SUM(J7:J12)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="4" t="s">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B23" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="C23" s="90" t="n">
+      <c r="C23" s="55" t="n">
         <f aca="false">SUM(K7:K12)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="4" t="s">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B24" s="5" t="s">
         <v>420</v>
       </c>
-      <c r="C24" s="67" t="n">
+      <c r="C24" s="61" t="n">
         <f aca="false">SUM(L7:L12)</f>
         <v>0.445</v>
       </c>

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -104,7 +104,7 @@
     <t xml:space="preserve">ACTIVE</t>
   </si>
   <si>
-    <t xml:space="preserve">Tab: WNBA Jul 12 · Game 1: 1-3 incl. parlay (-$355.66) · Aces game live</t>
+    <t xml:space="preserve">Tab: WNBA Jul 12 · 2-3, Wilson DD &amp; Mitchell 3s pending box score</t>
   </si>
   <si>
     <t xml:space="preserve">NASCAR Quaker State 400</t>
@@ -1193,7 +1193,7 @@
     <t xml:space="preserve">vs Fever · 9 PM ET</t>
   </si>
   <si>
-    <t xml:space="preserve">+41 differential last 7 home w/ Wilson; rested off 48-pt blowout Sat</t>
+    <t xml:space="preserve">+41 differential last 7 home w/ Wilson; rested off 48-pt blowout Sat · RESULT: Aces won by 6-8 (CBS final 115/117-109) after huge 4th-qtr rally — covered</t>
   </si>
   <si>
     <t xml:space="preserve">A'ja Wilson Double-Double (Yes)</t>
@@ -2253,7 +2253,7 @@
       </c>
       <c r="B6" s="7" t="n">
         <f aca="false">H23</f>
-        <v>-388.317746462671</v>
+        <v>-249.428857573782</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="B7" s="8" t="n">
         <f aca="false">B5+B6</f>
-        <v>4611.68225353733</v>
+        <v>4750.57114242622</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="B8" s="9" t="n">
         <f aca="false">F23</f>
-        <v>3000</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2280,7 +2280,7 @@
       </c>
       <c r="B9" s="8" t="n">
         <f aca="false">B7-B8</f>
-        <v>1611.68225353733</v>
+        <v>1900.57114242622</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2356,19 +2356,19 @@
       </c>
       <c r="F16" s="16" t="n">
         <f aca="false">SUMIF('WNBA Jul 12'!I7:I13,"Pending",'WNBA Jul 12'!F7:F13)</f>
-        <v>400</v>
+        <v>250</v>
       </c>
       <c r="G16" s="17" t="n">
         <f aca="false">SUM('WNBA Jul 12'!J7:J13)</f>
-        <v>244.339622641509</v>
+        <v>533.228511530398</v>
       </c>
       <c r="H16" s="18" t="n">
         <f aca="false">SUM('WNBA Jul 12'!K7:K13)</f>
-        <v>-355.660377358491</v>
+        <v>-216.771488469602</v>
       </c>
       <c r="I16" s="19" t="n">
         <f aca="false">B5+H16</f>
-        <v>4644.33962264151</v>
+        <v>4783.2285115304</v>
       </c>
       <c r="J16" s="20" t="s">
         <v>25</v>
@@ -2405,7 +2405,7 @@
       </c>
       <c r="I17" s="19" t="n">
         <f aca="false">I16+H17</f>
-        <v>4644.33962264151</v>
+        <v>4783.2285115304</v>
       </c>
       <c r="J17" s="20" t="s">
         <v>27</v>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="I18" s="19" t="n">
         <f aca="false">I17+H18</f>
-        <v>4644.33962264151</v>
+        <v>4783.2285115304</v>
       </c>
       <c r="J18" s="20" t="s">
         <v>30</v>
@@ -2479,7 +2479,7 @@
       </c>
       <c r="I19" s="19" t="n">
         <f aca="false">I18+H19</f>
-        <v>4644.33962264151</v>
+        <v>4783.2285115304</v>
       </c>
       <c r="J19" s="20" t="s">
         <v>33</v>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="I20" s="27" t="n">
         <f aca="false">I19+H20</f>
-        <v>4644.33962264151</v>
+        <v>4783.2285115304</v>
       </c>
       <c r="J20" s="28" t="s">
         <v>37</v>
@@ -2549,7 +2549,7 @@
       </c>
       <c r="I21" s="35" t="n">
         <f aca="false">I20+H21</f>
-        <v>4446.57188070603</v>
+        <v>4585.46076959491</v>
       </c>
       <c r="J21" s="36" t="s">
         <v>40</v>
@@ -2586,7 +2586,7 @@
       </c>
       <c r="I22" s="35" t="n">
         <f aca="false">I21+H22</f>
-        <v>4611.68225353733</v>
+        <v>4750.57114242622</v>
       </c>
       <c r="J22" s="36" t="s">
         <v>43</v>
@@ -2605,15 +2605,15 @@
       </c>
       <c r="F23" s="39" t="n">
         <f aca="false">SUM(F16:F22)</f>
-        <v>3000</v>
+        <v>2850</v>
       </c>
       <c r="G23" s="40" t="n">
         <f aca="false">SUM(G16:G22)</f>
-        <v>2261.68225353733</v>
+        <v>2550.57114242622</v>
       </c>
       <c r="H23" s="41" t="n">
         <f aca="false">SUM(H16:H22)</f>
-        <v>-388.317746462671</v>
+        <v>-249.428857573782</v>
       </c>
       <c r="I23" s="37"/>
       <c r="J23" s="37"/>
@@ -6239,16 +6239,16 @@
         <f aca="false">F10+G10</f>
         <v>288.888888888889</v>
       </c>
-      <c r="I10" s="65" t="s">
-        <v>126</v>
+      <c r="I10" s="54" t="s">
+        <v>93</v>
       </c>
       <c r="J10" s="53" t="n">
         <f aca="false">IF(I10="Win",F10+G10,IF(I10="Push",F10,IF(I10="Loss",0,0)))</f>
-        <v>0</v>
+        <v>288.888888888889</v>
       </c>
       <c r="K10" s="55" t="n">
         <f aca="false">IF(I10="Pending",0,J10-F10)</f>
-        <v>0</v>
+        <v>138.888888888889</v>
       </c>
       <c r="L10" s="66" t="n">
         <v>0.55</v>
@@ -6415,11 +6415,11 @@
       <c r="I14" s="37"/>
       <c r="J14" s="40" t="n">
         <f aca="false">SUM(J7:J13)</f>
-        <v>244.339622641509</v>
+        <v>533.228511530398</v>
       </c>
       <c r="K14" s="41" t="n">
         <f aca="false">SUM(K7:K13)</f>
-        <v>-355.660377358491</v>
+        <v>-216.771488469602</v>
       </c>
       <c r="L14" s="67" t="n">
         <f aca="false">SUM(L7:L13)</f>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C17" s="60" t="n">
         <f aca="false">COUNTIF(I7:I13,"Win")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6465,7 +6465,7 @@
       </c>
       <c r="C20" s="60" t="n">
         <f aca="false">COUNTIF(I7:I13,"Pending")</f>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6474,7 +6474,7 @@
       </c>
       <c r="C21" s="61" t="n">
         <f aca="false">IF(COUNTIF(I7:I13,"Win")+COUNTIF(I7:I13,"Loss")=0,"—",COUNTIF(I7:I13,"Win")/(COUNTIF(I7:I13,"Win")+COUNTIF(I7:I13,"Loss")))</f>
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6492,7 +6492,7 @@
       </c>
       <c r="C23" s="53" t="n">
         <f aca="false">SUM(J7:J13)</f>
-        <v>244.339622641509</v>
+        <v>533.228511530398</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6501,7 +6501,7 @@
       </c>
       <c r="C24" s="55" t="n">
         <f aca="false">SUM(K7:K13)</f>
-        <v>-355.660377358491</v>
+        <v>-216.771488469602</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6510,7 +6510,7 @@
       </c>
       <c r="C25" s="61" t="n">
         <f aca="false">IF(SUM(F7:F13)=0,"—",SUM(K7:K13)/SUM(F7:F13))</f>
-        <v>-0.355660377358491</v>
+        <v>-0.216771488469602</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
   <workbookProtection/>
   <bookViews>
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
@@ -95,60 +95,60 @@
     <t xml:space="preserve">Detail Tab / Notes</t>
   </si>
   <si>
+    <t xml:space="preserve">NASCAR Quaker State 400</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACTIVE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tab: NASCAR Jul 12 · red-flag lightning delay at lap 109 · finish ~1 AM CT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">World Cup 2026 — Final Four</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jul 14-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tab: World Cup 2026 · semis Tue/Wed, final Sun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Open Championship (golf)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jul 16-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tab: The Open · $600 outrights + $400 props Wed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rugby Nations Cup — Final Rd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QUEUED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Draft card built · odds post ~Fri · $0 at risk</t>
+  </si>
+  <si>
     <t xml:space="preserve">WNBA Sunday Doubleheader</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACTIVE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tab: WNBA Jul 12 · 2-3, Wilson DD &amp; Mitchell 3s pending box score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NASCAR Quaker State 400</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tab: NASCAR Jul 12 · race ~7 PM ET tonight</t>
-  </si>
-  <si>
-    <t xml:space="preserve">World Cup 2026 — Final Four</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jul 14-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tab: World Cup 2026 · semis Tue/Wed, final Sun</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Open Championship (golf)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jul 16-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tab: The Open · $600 outrights + $400 props Wed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rugby Nations Cup — Final Rd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QUEUED</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Draft card built · odds post ~Fri · $0 at risk</t>
+    <t xml:space="preserve">SETTLED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tab: WNBA Jul 12 · SETTLED 3-4 (42.9%), -$298.15 · Fever routed Aces 109-75</t>
   </si>
   <si>
     <t xml:space="preserve">MLB Sunday Slate (15 games)</t>
   </si>
   <si>
-    <t xml:space="preserve">SETTLED</t>
-  </si>
-  <si>
     <t xml:space="preserve">Tab: MLB Jul 12 · SETTLED 3-5 (37.5%), -$197.77</t>
   </si>
   <si>
@@ -866,7 +866,7 @@
     <t xml:space="preserve">TEST 4 — NASCAR QUAKER STATE 400 · ECHOPARK SPEEDWAY (ATLANTA) · JULY 12, 2026</t>
   </si>
   <si>
-    <t xml:space="preserve">STATUS: ACTIVE — race ~7 PM ET tonight</t>
+    <t xml:space="preserve">STATUS: ACTIVE — red-flagged (lightning) at lap 109/260; finish expected ~1 AM CT</t>
   </si>
   <si>
     <t xml:space="preserve">Race ~7:00 PM ET on TNT · Source: nascar-jul12-betting-card.html · Odds: Covers/VSiN/CBS (FanDuel) consensus, Sunday PM</t>
@@ -1148,7 +1148,7 @@
     <t xml:space="preserve">TEST 5 — WNBA SUNDAY NIGHT DOUBLEHEADER · JULY 12, 2026</t>
   </si>
   <si>
-    <t xml:space="preserve">STATUS: ACTIVE — Game 1 graded 1-2; Fever@Aces in progress</t>
+    <t xml:space="preserve">STATUS: SETTLED — 3-4 (42.9%), -$298.15 · Fever routed Aces 109-75</t>
   </si>
   <si>
     <t xml:space="preserve">Sky @ Wings 7 PM ET (ESPN) · Fever @ Aces 9 PM ET (NBC) · Source: wnba-jul12-betting-card.html · Lines: FanDuel via SI Betting / Covers, ~5 PM CT</t>
@@ -1193,7 +1193,7 @@
     <t xml:space="preserve">vs Fever · 9 PM ET</t>
   </si>
   <si>
-    <t xml:space="preserve">+41 differential last 7 home w/ Wilson; rested off 48-pt blowout Sat · RESULT: Aces won by 6-8 (CBS final 115/117-109) after huge 4th-qtr rally — covered</t>
+    <t xml:space="preserve">+41 differential last 7 home w/ Wilson; rested off 48-pt blowout Sat · RESULT: Fever 109-75 — Aces lost by 34, spread dead</t>
   </si>
   <si>
     <t xml:space="preserve">A'ja Wilson Double-Double (Yes)</t>
@@ -1202,7 +1202,7 @@
     <t xml:space="preserve">Aces F · player prop</t>
   </si>
   <si>
-    <t xml:space="preserve">DD in 5 straight career games vs Clark; 10.8 reb/game at home; 11 DDs (3rd in W)</t>
+    <t xml:space="preserve">DD in 5 straight career games vs Clark; 10.8 reb/game at home; 11 DDs (3rd in W) · RESULT: Wilson 20 pts / 12 reb — double-double cashed</t>
   </si>
   <si>
     <t xml:space="preserve">Kelsey Mitchell Over 2.5 Threes</t>
@@ -1211,7 +1211,7 @@
     <t xml:space="preserve">Fever G · player prop</t>
   </si>
   <si>
-    <t xml:space="preserve">3+ threes in 6 straight, 8 of 10; 41.1% from deep; LV 12th vs opp threes</t>
+    <t xml:space="preserve">3+ threes in 6 straight, 8 of 10; 41.1% from deep; LV 12th vs opp threes · RESULT: Mitchell 3-of-8 from deep (27 pts) — cleared 2.5</t>
   </si>
   <si>
     <t xml:space="preserve">LONGSHOT: 4-Leg Parlay</t>
@@ -2253,7 +2253,7 @@
       </c>
       <c r="B6" s="7" t="n">
         <f aca="false">H23</f>
-        <v>-249.428857573782</v>
+        <v>-330.81085941033</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="B7" s="8" t="n">
         <f aca="false">B5+B6</f>
-        <v>4750.57114242622</v>
+        <v>4669.18914058967</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="B8" s="9" t="n">
         <f aca="false">F23</f>
-        <v>2850</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2280,7 +2280,7 @@
       </c>
       <c r="B9" s="8" t="n">
         <f aca="false">B7-B8</f>
-        <v>1900.57114242622</v>
+        <v>2069.18914058967</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="B10" s="10" t="str">
         <f aca="false">COUNTIF(D16:D22,"ACTIVE")&amp;" of 4 max"</f>
-        <v>4 of 4 max</v>
+        <v>3 of 4 max</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2339,7 +2339,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B16" s="14" t="s">
         <v>22</v>
@@ -2351,171 +2351,171 @@
         <v>24</v>
       </c>
       <c r="E16" s="16" t="n">
+        <f aca="false">SUM('NASCAR Jul 12'!F7:F13)</f>
+        <v>1000</v>
+      </c>
+      <c r="F16" s="16" t="n">
+        <f aca="false">SUMIF('NASCAR Jul 12'!I7:I13,"Pending",'NASCAR Jul 12'!F7:F13)</f>
+        <v>1000</v>
+      </c>
+      <c r="G16" s="17" t="n">
+        <f aca="false">SUM('NASCAR Jul 12'!J7:J13)</f>
+        <v>0</v>
+      </c>
+      <c r="H16" s="18" t="n">
+        <f aca="false">SUM('NASCAR Jul 12'!K7:K13)</f>
+        <v>0</v>
+      </c>
+      <c r="I16" s="19" t="n">
+        <f aca="false">B5+H16</f>
+        <v>5000</v>
+      </c>
+      <c r="J16" s="20" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B17" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="C17" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="D17" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="E17" s="16" t="n">
+        <f aca="false">SUM('World Cup 2026'!F7:F13)</f>
+        <v>1000</v>
+      </c>
+      <c r="F17" s="16" t="n">
+        <f aca="false">SUMIF('World Cup 2026'!I7:I13,"Pending",'World Cup 2026'!F7:F13)</f>
+        <v>1000</v>
+      </c>
+      <c r="G17" s="17" t="n">
+        <f aca="false">SUM('World Cup 2026'!J7:J13)</f>
+        <v>0</v>
+      </c>
+      <c r="H17" s="18" t="n">
+        <f aca="false">SUM('World Cup 2026'!K7:K13)</f>
+        <v>0</v>
+      </c>
+      <c r="I17" s="19" t="n">
+        <f aca="false">I16+H17</f>
+        <v>5000</v>
+      </c>
+      <c r="J17" s="20" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D18" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="E18" s="16" t="n">
+        <f aca="false">SUM('The Open'!F7:F12)</f>
+        <v>600</v>
+      </c>
+      <c r="F18" s="16" t="n">
+        <f aca="false">SUMIF('The Open'!I7:I12,"Pending",'The Open'!F7:F12)</f>
+        <v>600</v>
+      </c>
+      <c r="G18" s="17" t="n">
+        <f aca="false">SUM('The Open'!J7:J12)</f>
+        <v>0</v>
+      </c>
+      <c r="H18" s="18" t="n">
+        <f aca="false">SUM('The Open'!K7:K12)</f>
+        <v>0</v>
+      </c>
+      <c r="I18" s="19" t="n">
+        <f aca="false">I17+H18</f>
+        <v>5000</v>
+      </c>
+      <c r="J18" s="20" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="B19" s="22" t="s">
+        <v>32</v>
+      </c>
+      <c r="C19" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="D19" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="E19" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="27" t="n">
+        <f aca="false">I18+H19</f>
+        <v>5000</v>
+      </c>
+      <c r="J19" s="28" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="B20" s="30" t="s">
+        <v>36</v>
+      </c>
+      <c r="C20" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="D20" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="E20" s="32" t="n">
         <f aca="false">SUM('WNBA Jul 12'!F7:F13)</f>
         <v>1000</v>
       </c>
-      <c r="F16" s="16" t="n">
+      <c r="F20" s="32" t="n">
         <f aca="false">SUMIF('WNBA Jul 12'!I7:I13,"Pending",'WNBA Jul 12'!F7:F13)</f>
-        <v>250</v>
-      </c>
-      <c r="G16" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="33" t="n">
         <f aca="false">SUM('WNBA Jul 12'!J7:J13)</f>
-        <v>533.228511530398</v>
-      </c>
-      <c r="H16" s="18" t="n">
+        <v>701.846509693851</v>
+      </c>
+      <c r="H20" s="34" t="n">
         <f aca="false">SUM('WNBA Jul 12'!K7:K13)</f>
-        <v>-216.771488469602</v>
-      </c>
-      <c r="I16" s="19" t="n">
-        <f aca="false">B5+H16</f>
-        <v>4783.2285115304</v>
-      </c>
-      <c r="J16" s="20" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="13" t="n">
-        <v>4</v>
-      </c>
-      <c r="B17" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="C17" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="D17" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="E17" s="16" t="n">
-        <f aca="false">SUM('NASCAR Jul 12'!F7:F13)</f>
-        <v>1000</v>
-      </c>
-      <c r="F17" s="16" t="n">
-        <f aca="false">SUMIF('NASCAR Jul 12'!I7:I13,"Pending",'NASCAR Jul 12'!F7:F13)</f>
-        <v>1000</v>
-      </c>
-      <c r="G17" s="17" t="n">
-        <f aca="false">SUM('NASCAR Jul 12'!J7:J13)</f>
-        <v>0</v>
-      </c>
-      <c r="H17" s="18" t="n">
-        <f aca="false">SUM('NASCAR Jul 12'!K7:K13)</f>
-        <v>0</v>
-      </c>
-      <c r="I17" s="19" t="n">
-        <f aca="false">I16+H17</f>
-        <v>4783.2285115304</v>
-      </c>
-      <c r="J17" s="20" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="B18" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="C18" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="D18" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="E18" s="16" t="n">
-        <f aca="false">SUM('World Cup 2026'!F7:F13)</f>
-        <v>1000</v>
-      </c>
-      <c r="F18" s="16" t="n">
-        <f aca="false">SUMIF('World Cup 2026'!I7:I13,"Pending",'World Cup 2026'!F7:F13)</f>
-        <v>1000</v>
-      </c>
-      <c r="G18" s="17" t="n">
-        <f aca="false">SUM('World Cup 2026'!J7:J13)</f>
-        <v>0</v>
-      </c>
-      <c r="H18" s="18" t="n">
-        <f aca="false">SUM('World Cup 2026'!K7:K13)</f>
-        <v>0</v>
-      </c>
-      <c r="I18" s="19" t="n">
-        <f aca="false">I17+H18</f>
-        <v>4783.2285115304</v>
-      </c>
-      <c r="J18" s="20" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="13" t="n">
-        <v>6</v>
-      </c>
-      <c r="B19" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="C19" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="D19" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="E19" s="16" t="n">
-        <f aca="false">SUM('The Open'!F7:F12)</f>
-        <v>600</v>
-      </c>
-      <c r="F19" s="16" t="n">
-        <f aca="false">SUMIF('The Open'!I7:I12,"Pending",'The Open'!F7:F12)</f>
-        <v>600</v>
-      </c>
-      <c r="G19" s="17" t="n">
-        <f aca="false">SUM('The Open'!J7:J12)</f>
-        <v>0</v>
-      </c>
-      <c r="H19" s="18" t="n">
-        <f aca="false">SUM('The Open'!K7:K12)</f>
-        <v>0</v>
-      </c>
-      <c r="I19" s="19" t="n">
-        <f aca="false">I18+H19</f>
-        <v>4783.2285115304</v>
-      </c>
-      <c r="J19" s="20" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="21" t="n">
-        <v>7</v>
-      </c>
-      <c r="B20" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="C20" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="D20" s="23" t="s">
-        <v>36</v>
-      </c>
-      <c r="E20" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" s="27" t="n">
+        <v>-298.153490306149</v>
+      </c>
+      <c r="I20" s="35" t="n">
         <f aca="false">I19+H20</f>
-        <v>4783.2285115304</v>
-      </c>
-      <c r="J20" s="28" t="s">
-        <v>37</v>
+        <v>4701.84650969385</v>
+      </c>
+      <c r="J20" s="36" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2523,13 +2523,13 @@
         <v>3</v>
       </c>
       <c r="B21" s="30" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C21" s="29" t="s">
         <v>23</v>
       </c>
       <c r="D21" s="31" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E21" s="32" t="n">
         <f aca="false">SUM('MLB Jul 12'!F7:F14)</f>
@@ -2549,7 +2549,7 @@
       </c>
       <c r="I21" s="35" t="n">
         <f aca="false">I20+H21</f>
-        <v>4585.46076959491</v>
+        <v>4504.07876775837</v>
       </c>
       <c r="J21" s="36" t="s">
         <v>40</v>
@@ -2566,7 +2566,7 @@
         <v>42</v>
       </c>
       <c r="D22" s="31" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E22" s="32" t="n">
         <f aca="false">SUM('UFC 329'!F7:F15)</f>
@@ -2586,7 +2586,7 @@
       </c>
       <c r="I22" s="35" t="n">
         <f aca="false">I21+H22</f>
-        <v>4750.57114242622</v>
+        <v>4669.18914058967</v>
       </c>
       <c r="J22" s="36" t="s">
         <v>43</v>
@@ -2605,15 +2605,15 @@
       </c>
       <c r="F23" s="39" t="n">
         <f aca="false">SUM(F16:F22)</f>
-        <v>2850</v>
+        <v>2600</v>
       </c>
       <c r="G23" s="40" t="n">
         <f aca="false">SUM(G16:G22)</f>
-        <v>2550.57114242622</v>
+        <v>2719.18914058967</v>
       </c>
       <c r="H23" s="41" t="n">
         <f aca="false">SUM(H16:H22)</f>
-        <v>-249.428857573782</v>
+        <v>-330.81085941033</v>
       </c>
       <c r="I23" s="37"/>
       <c r="J23" s="37"/>
@@ -5995,7 +5995,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <tabColor rgb="FF1B7A3D"/>
+    <tabColor rgb="FF808080"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:M30"/>
@@ -6239,16 +6239,16 @@
         <f aca="false">F10+G10</f>
         <v>288.888888888889</v>
       </c>
-      <c r="I10" s="54" t="s">
-        <v>93</v>
+      <c r="I10" s="65" t="s">
+        <v>101</v>
       </c>
       <c r="J10" s="53" t="n">
         <f aca="false">IF(I10="Win",F10+G10,IF(I10="Push",F10,IF(I10="Loss",0,0)))</f>
-        <v>288.888888888889</v>
+        <v>0</v>
       </c>
       <c r="K10" s="55" t="n">
         <f aca="false">IF(I10="Pending",0,J10-F10)</f>
-        <v>138.888888888889</v>
+        <v>-150</v>
       </c>
       <c r="L10" s="66" t="n">
         <v>0.55</v>
@@ -6285,15 +6285,15 @@
         <v>238.333333333333</v>
       </c>
       <c r="I11" s="65" t="s">
-        <v>126</v>
+        <v>93</v>
       </c>
       <c r="J11" s="53" t="n">
         <f aca="false">IF(I11="Win",F11+G11,IF(I11="Push",F11,IF(I11="Loss",0,0)))</f>
-        <v>0</v>
+        <v>238.333333333333</v>
       </c>
       <c r="K11" s="55" t="n">
         <f aca="false">IF(I11="Pending",0,J11-F11)</f>
-        <v>0</v>
+        <v>108.333333333333</v>
       </c>
       <c r="L11" s="66" t="n">
         <v>0.6</v>
@@ -6330,15 +6330,15 @@
         <v>219.173553719008</v>
       </c>
       <c r="I12" s="65" t="s">
-        <v>126</v>
+        <v>93</v>
       </c>
       <c r="J12" s="53" t="n">
         <f aca="false">IF(I12="Win",F12+G12,IF(I12="Push",F12,IF(I12="Loss",0,0)))</f>
-        <v>0</v>
+        <v>219.173553719008</v>
       </c>
       <c r="K12" s="55" t="n">
         <f aca="false">IF(I12="Pending",0,J12-F12)</f>
-        <v>0</v>
+        <v>99.1735537190083</v>
       </c>
       <c r="L12" s="66" t="n">
         <v>0.58</v>
@@ -6415,11 +6415,11 @@
       <c r="I14" s="37"/>
       <c r="J14" s="40" t="n">
         <f aca="false">SUM(J7:J13)</f>
-        <v>533.228511530398</v>
+        <v>701.846509693851</v>
       </c>
       <c r="K14" s="41" t="n">
         <f aca="false">SUM(K7:K13)</f>
-        <v>-216.771488469602</v>
+        <v>-298.153490306149</v>
       </c>
       <c r="L14" s="67" t="n">
         <f aca="false">SUM(L7:L13)</f>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C17" s="60" t="n">
         <f aca="false">COUNTIF(I7:I13,"Win")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6447,7 +6447,7 @@
       </c>
       <c r="C18" s="60" t="n">
         <f aca="false">COUNTIF(I7:I13,"Loss")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6465,7 +6465,7 @@
       </c>
       <c r="C20" s="60" t="n">
         <f aca="false">COUNTIF(I7:I13,"Pending")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6474,7 +6474,7 @@
       </c>
       <c r="C21" s="61" t="n">
         <f aca="false">IF(COUNTIF(I7:I13,"Win")+COUNTIF(I7:I13,"Loss")=0,"—",COUNTIF(I7:I13,"Win")/(COUNTIF(I7:I13,"Win")+COUNTIF(I7:I13,"Loss")))</f>
-        <v>0.4</v>
+        <v>0.428571428571429</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6492,7 +6492,7 @@
       </c>
       <c r="C23" s="53" t="n">
         <f aca="false">SUM(J7:J13)</f>
-        <v>533.228511530398</v>
+        <v>701.846509693851</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6501,7 +6501,7 @@
       </c>
       <c r="C24" s="55" t="n">
         <f aca="false">SUM(K7:K13)</f>
-        <v>-216.771488469602</v>
+        <v>-298.153490306149</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6510,7 +6510,7 @@
       </c>
       <c r="C25" s="61" t="n">
         <f aca="false">IF(SUM(F7:F13)=0,"—",SUM(K7:K13)/SUM(F7:F13))</f>
-        <v>-0.216771488469602</v>
+        <v>-0.298153490306149</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -101,18 +101,21 @@
     <t xml:space="preserve">2026-07-12</t>
   </si>
   <si>
+    <t xml:space="preserve">SETTLED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tab: NASCAR Jul 12 · SETTLED 1-6 (14.3%), -$434.51 · Blaney won in OT after 3h lightning red flag; Wallace P2 stripped (yellow-line)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">World Cup 2026 — Final Four</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jul 14-19</t>
+  </si>
+  <si>
     <t xml:space="preserve">ACTIVE</t>
   </si>
   <si>
-    <t xml:space="preserve">Tab: NASCAR Jul 12 · red-flag lightning delay at lap 109 · finish ~1 AM CT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">World Cup 2026 — Final Four</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jul 14-19</t>
-  </si>
-  <si>
     <t xml:space="preserve">Tab: World Cup 2026 · semis Tue/Wed, final Sun</t>
   </si>
   <si>
@@ -140,9 +143,6 @@
     <t xml:space="preserve">WNBA Sunday Doubleheader</t>
   </si>
   <si>
-    <t xml:space="preserve">SETTLED</t>
-  </si>
-  <si>
     <t xml:space="preserve">Tab: WNBA Jul 12 · SETTLED 3-4 (42.9%), -$298.15 · Fever routed Aces 109-75</t>
   </si>
   <si>
@@ -866,7 +866,7 @@
     <t xml:space="preserve">TEST 4 — NASCAR QUAKER STATE 400 · ECHOPARK SPEEDWAY (ATLANTA) · JULY 12, 2026</t>
   </si>
   <si>
-    <t xml:space="preserve">STATUS: ACTIVE — red-flagged (lightning) at lap 109/260; finish expected ~1 AM CT</t>
+    <t xml:space="preserve">STATUS: SETTLED — Blaney won in OT ~12:55 AM CT Mon after 3h lightning red flag · card 1-6, net -$434.51</t>
   </si>
   <si>
     <t xml:space="preserve">Race ~7:00 PM ET on TNT · Source: nascar-jul12-betting-card.html · Odds: Covers/VSiN/CBS (FanDuel) consensus, Sunday PM</t>
@@ -884,7 +884,7 @@
     <t xml:space="preserve">Matchup</t>
   </si>
   <si>
-    <t xml:space="preserve">7 top-10s in last 8 here; 1 wreck in 16 starts vs Byron's 4 in 14</t>
+    <t xml:space="preserve">7 top-10s in last 8 here; 1 wreck in 16 starts vs Byron's 4 in 14 · WIN — Blaney won the race outright (OT, ~12:55 AM CT Mon); H2H over Byron clinched</t>
   </si>
   <si>
     <t xml:space="preserve">Daniel Suarez Top-5</t>
@@ -893,7 +893,7 @@
     <t xml:space="preserve">Finishing position prop</t>
   </si>
   <si>
-    <t xml:space="preserve">Top-5 in 4 of last 6 Atlanta races; biggest % edge on card</t>
+    <t xml:space="preserve">Top-5 in 4 of last 6 Atlanta races; biggest % edge on card · LOSS — official top 5: Blaney, Bell, Hocevar, Gibbs, E. Jones; Suárez outside top 5</t>
   </si>
   <si>
     <t xml:space="preserve">Chase Elliott to Win</t>
@@ -902,31 +902,31 @@
     <t xml:space="preserve">Outright winner</t>
   </si>
   <si>
-    <t xml:space="preserve">Defending race winner, Georgia native, Chevy won 4 of last 5 here</t>
+    <t xml:space="preserve">Defending race winner, Georgia native, Chevy won 4 of last 5 here · LOSS — Elliott did not win (Blaney P1)</t>
   </si>
   <si>
     <t xml:space="preserve">Carson Hocevar to Win</t>
   </si>
   <si>
-    <t xml:space="preserve">3 straight Atlanta top-10s; elite drafter</t>
+    <t xml:space="preserve">3 straight Atlanta top-10s; elite drafter · LOSS — Hocevar P3; closest of the winner basket</t>
   </si>
   <si>
     <t xml:space="preserve">Brad Keselowski to Win</t>
   </si>
   <si>
-    <t xml:space="preserve">2 Atlanta wins, 6 top-3s; CBS model top pick; RFK form</t>
+    <t xml:space="preserve">2 Atlanta wins, 6 top-3s; CBS model top pick; RFK form · LOSS — Keselowski did not win</t>
   </si>
   <si>
     <t xml:space="preserve">Tyler Reddick to Win</t>
   </si>
   <si>
-    <t xml:space="preserve">Drafting ace; Toyota gambled on race trim over qualifying</t>
+    <t xml:space="preserve">Drafting ace; Toyota gambled on race trim over qualifying · LOSS — Reddick did not win (P8 per post-race reports)</t>
   </si>
   <si>
     <t xml:space="preserve">Kyle Larson to Win (LONGSHOT)</t>
   </si>
   <si>
-    <t xml:space="preserve">Mandatory longshot — best driver at his longest price; P3 start</t>
+    <t xml:space="preserve">Mandatory longshot — best driver at his longest price; P3 start · LOSS — Larson did not win; longshot record now 0-for-4</t>
   </si>
   <si>
     <t xml:space="preserve">Best-Case P/L (basket excl.)</t>
@@ -2253,7 +2253,7 @@
       </c>
       <c r="B6" s="7" t="n">
         <f aca="false">H23</f>
-        <v>-330.81085941033</v>
+        <v>-765.324133746613</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="B7" s="8" t="n">
         <f aca="false">B5+B6</f>
-        <v>4669.18914058967</v>
+        <v>4234.67586625339</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="B8" s="9" t="n">
         <f aca="false">F23</f>
-        <v>2600</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2280,7 +2280,7 @@
       </c>
       <c r="B9" s="8" t="n">
         <f aca="false">B7-B8</f>
-        <v>2069.18914058967</v>
+        <v>2634.67586625339</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="B10" s="10" t="str">
         <f aca="false">COUNTIF(D16:D22,"ACTIVE")&amp;" of 4 max"</f>
-        <v>3 of 4 max</v>
+        <v>2 of 4 max</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2356,19 +2356,19 @@
       </c>
       <c r="F16" s="16" t="n">
         <f aca="false">SUMIF('NASCAR Jul 12'!I7:I13,"Pending",'NASCAR Jul 12'!F7:F13)</f>
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="G16" s="17" t="n">
         <f aca="false">SUM('NASCAR Jul 12'!J7:J13)</f>
-        <v>0</v>
+        <v>565.486725663717</v>
       </c>
       <c r="H16" s="18" t="n">
         <f aca="false">SUM('NASCAR Jul 12'!K7:K13)</f>
-        <v>0</v>
+        <v>-434.513274336283</v>
       </c>
       <c r="I16" s="19" t="n">
         <f aca="false">B5+H16</f>
-        <v>5000</v>
+        <v>4565.48672566372</v>
       </c>
       <c r="J16" s="20" t="s">
         <v>25</v>
@@ -2385,7 +2385,7 @@
         <v>27</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E17" s="16" t="n">
         <f aca="false">SUM('World Cup 2026'!F7:F13)</f>
@@ -2405,10 +2405,10 @@
       </c>
       <c r="I17" s="19" t="n">
         <f aca="false">I16+H17</f>
-        <v>5000</v>
+        <v>4565.48672566372</v>
       </c>
       <c r="J17" s="20" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2416,13 +2416,13 @@
         <v>6</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E18" s="16" t="n">
         <f aca="false">SUM('The Open'!F7:F12)</f>
@@ -2442,10 +2442,10 @@
       </c>
       <c r="I18" s="19" t="n">
         <f aca="false">I17+H18</f>
-        <v>5000</v>
+        <v>4565.48672566372</v>
       </c>
       <c r="J18" s="20" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2453,13 +2453,13 @@
         <v>7</v>
       </c>
       <c r="B19" s="22" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C19" s="21" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D19" s="23" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E19" s="24" t="n">
         <v>0</v>
@@ -2475,10 +2475,10 @@
       </c>
       <c r="I19" s="27" t="n">
         <f aca="false">I18+H19</f>
-        <v>5000</v>
+        <v>4565.48672566372</v>
       </c>
       <c r="J19" s="28" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2486,13 +2486,13 @@
         <v>5</v>
       </c>
       <c r="B20" s="30" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C20" s="29" t="s">
         <v>23</v>
       </c>
       <c r="D20" s="31" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="E20" s="32" t="n">
         <f aca="false">SUM('WNBA Jul 12'!F7:F13)</f>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="I20" s="35" t="n">
         <f aca="false">I19+H20</f>
-        <v>4701.84650969385</v>
+        <v>4267.33323535757</v>
       </c>
       <c r="J20" s="36" t="s">
         <v>38</v>
@@ -2529,7 +2529,7 @@
         <v>23</v>
       </c>
       <c r="D21" s="31" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="E21" s="32" t="n">
         <f aca="false">SUM('MLB Jul 12'!F7:F14)</f>
@@ -2549,7 +2549,7 @@
       </c>
       <c r="I21" s="35" t="n">
         <f aca="false">I20+H21</f>
-        <v>4504.07876775837</v>
+        <v>4069.56549342208</v>
       </c>
       <c r="J21" s="36" t="s">
         <v>40</v>
@@ -2566,7 +2566,7 @@
         <v>42</v>
       </c>
       <c r="D22" s="31" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="E22" s="32" t="n">
         <f aca="false">SUM('UFC 329'!F7:F15)</f>
@@ -2586,7 +2586,7 @@
       </c>
       <c r="I22" s="35" t="n">
         <f aca="false">I21+H22</f>
-        <v>4669.18914058967</v>
+        <v>4234.67586625339</v>
       </c>
       <c r="J22" s="36" t="s">
         <v>43</v>
@@ -2605,15 +2605,15 @@
       </c>
       <c r="F23" s="39" t="n">
         <f aca="false">SUM(F16:F22)</f>
-        <v>2600</v>
+        <v>1600</v>
       </c>
       <c r="G23" s="40" t="n">
         <f aca="false">SUM(G16:G22)</f>
-        <v>2719.18914058967</v>
+        <v>3284.67586625339</v>
       </c>
       <c r="H23" s="41" t="n">
         <f aca="false">SUM(H16:H22)</f>
-        <v>-330.81085941033</v>
+        <v>-765.324133746613</v>
       </c>
       <c r="I23" s="37"/>
       <c r="J23" s="37"/>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="E29" s="10" t="str">
         <f aca="false">IF('NASCAR Jul 12'!I13="Win","HIT",IF('NASCAR Jul 12'!I13="Loss","MISS","Pending"))</f>
-        <v>Pending</v>
+        <v>MISS</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2755,7 +2755,7 @@
       <c r="D33" s="37"/>
       <c r="E33" s="45" t="str">
         <f aca="false">IF(COUNTIF(E27:E32,"HIT")+COUNTIF(E27:E32,"MISS")=0,"—",COUNTIF(E27:E32,"HIT")&amp;"-for-"&amp;(COUNTIF(E27:E32,"HIT")+COUNTIF(E27:E32,"MISS"))&amp;" ("&amp;TEXT(COUNTIF(E27:E32,"HIT")/(COUNTIF(E27:E32,"HIT")+COUNTIF(E27:E32,"MISS")),"0%")&amp;")")</f>
-        <v>0-for-3 (0%)</v>
+        <v>0-for-4 (0%)</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5023,7 +5023,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <tabColor rgb="FF1B7A3D"/>
+    <tabColor rgb="FF808080"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:M29"/>
@@ -5133,15 +5133,15 @@
         <v>565.486725663717</v>
       </c>
       <c r="I7" s="65" t="s">
-        <v>126</v>
+        <v>93</v>
       </c>
       <c r="J7" s="53" t="n">
         <f aca="false">IF(I7="Win",F7+G7,IF(I7="Push",F7,IF(I7="Loss",0,0)))</f>
-        <v>0</v>
+        <v>565.486725663717</v>
       </c>
       <c r="K7" s="55" t="n">
         <f aca="false">IF(I7="Pending",0,J7-F7)</f>
-        <v>0</v>
+        <v>265.486725663717</v>
       </c>
       <c r="L7" s="66" t="n">
         <v>0.58</v>
@@ -5178,7 +5178,7 @@
         <v>1112</v>
       </c>
       <c r="I8" s="65" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="J8" s="53" t="n">
         <f aca="false">IF(I8="Win",F8+G8,IF(I8="Push",F8,IF(I8="Loss",0,0)))</f>
@@ -5186,7 +5186,7 @@
       </c>
       <c r="K8" s="55" t="n">
         <f aca="false">IF(I8="Pending",0,J8-F8)</f>
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="L8" s="66" t="n">
         <v>0.24</v>
@@ -5223,7 +5223,7 @@
         <v>1875</v>
       </c>
       <c r="I9" s="65" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="J9" s="53" t="n">
         <f aca="false">IF(I9="Win",F9+G9,IF(I9="Push",F9,IF(I9="Loss",0,0)))</f>
@@ -5231,7 +5231,7 @@
       </c>
       <c r="K9" s="55" t="n">
         <f aca="false">IF(I9="Pending",0,J9-F9)</f>
-        <v>0</v>
+        <v>-150</v>
       </c>
       <c r="L9" s="66" t="n">
         <v>0.1</v>
@@ -5268,7 +5268,7 @@
         <v>2000.4</v>
       </c>
       <c r="I10" s="65" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="J10" s="53" t="n">
         <f aca="false">IF(I10="Win",F10+G10,IF(I10="Push",F10,IF(I10="Loss",0,0)))</f>
@@ -5276,7 +5276,7 @@
       </c>
       <c r="K10" s="55" t="n">
         <f aca="false">IF(I10="Pending",0,J10-F10)</f>
-        <v>0</v>
+        <v>-120</v>
       </c>
       <c r="L10" s="66" t="n">
         <v>0.08</v>
@@ -5313,7 +5313,7 @@
         <v>1900</v>
       </c>
       <c r="I11" s="65" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="J11" s="53" t="n">
         <f aca="false">IF(I11="Win",F11+G11,IF(I11="Push",F11,IF(I11="Loss",0,0)))</f>
@@ -5321,7 +5321,7 @@
       </c>
       <c r="K11" s="55" t="n">
         <f aca="false">IF(I11="Pending",0,J11-F11)</f>
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="L11" s="66" t="n">
         <v>0.07</v>
@@ -5358,7 +5358,7 @@
         <v>1125</v>
       </c>
       <c r="I12" s="65" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="J12" s="53" t="n">
         <f aca="false">IF(I12="Win",F12+G12,IF(I12="Push",F12,IF(I12="Loss",0,0)))</f>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="K12" s="55" t="n">
         <f aca="false">IF(I12="Pending",0,J12-F12)</f>
-        <v>0</v>
+        <v>-90</v>
       </c>
       <c r="L12" s="66" t="n">
         <v>0.08</v>
@@ -5403,7 +5403,7 @@
         <v>800</v>
       </c>
       <c r="I13" s="65" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="J13" s="53" t="n">
         <f aca="false">IF(I13="Win",F13+G13,IF(I13="Push",F13,IF(I13="Loss",0,0)))</f>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="K13" s="55" t="n">
         <f aca="false">IF(I13="Pending",0,J13-F13)</f>
-        <v>0</v>
+        <v>-40</v>
       </c>
       <c r="L13" s="66" t="n">
         <v>0.05</v>
@@ -5443,11 +5443,11 @@
       <c r="I14" s="37"/>
       <c r="J14" s="40" t="n">
         <f aca="false">SUM(J7:J13)</f>
-        <v>0</v>
+        <v>565.486725663717</v>
       </c>
       <c r="K14" s="41" t="n">
         <f aca="false">SUM(K7:K13)</f>
-        <v>0</v>
+        <v>-434.513274336283</v>
       </c>
       <c r="L14" s="67" t="n">
         <f aca="false">SUM(L7:L13)</f>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="C17" s="60" t="n">
         <f aca="false">COUNTIF(I7:I13,"Win")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5475,7 +5475,7 @@
       </c>
       <c r="C18" s="60" t="n">
         <f aca="false">COUNTIF(I7:I13,"Loss")</f>
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5493,16 +5493,16 @@
       </c>
       <c r="C20" s="60" t="n">
         <f aca="false">COUNTIF(I7:I13,"Pending")</f>
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="C21" s="61" t="str">
+      <c r="C21" s="61" t="n">
         <f aca="false">IF(COUNTIF(I7:I13,"Win")+COUNTIF(I7:I13,"Loss")=0,"—",COUNTIF(I7:I13,"Win")/(COUNTIF(I7:I13,"Win")+COUNTIF(I7:I13,"Loss")))</f>
-        <v>—</v>
+        <v>0.142857142857143</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5520,7 +5520,7 @@
       </c>
       <c r="C23" s="53" t="n">
         <f aca="false">SUM(J7:J13)</f>
-        <v>0</v>
+        <v>565.486725663717</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5529,7 +5529,7 @@
       </c>
       <c r="C24" s="55" t="n">
         <f aca="false">SUM(K7:K13)</f>
-        <v>0</v>
+        <v>-434.513274336283</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5538,7 +5538,7 @@
       </c>
       <c r="C25" s="61" t="n">
         <f aca="false">IF(SUM(F7:F13)=0,"—",SUM(K7:K13)/SUM(F7:F13))</f>
-        <v>0</v>
+        <v>-0.434513274336283</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -16,6 +16,7 @@
     <sheet name="References" sheetId="6" state="visible" r:id="rId8"/>
     <sheet name="WNBA Jul 12" sheetId="7" state="visible" r:id="rId9"/>
     <sheet name="The Open" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="HR Derby" sheetId="9" state="visible" r:id="rId11"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="673" uniqueCount="421">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="723" uniqueCount="437">
   <si>
     <t xml:space="preserve">BETTING TEST ACCOUNT — ROLL-UP DASHBOARD</t>
   </si>
@@ -89,10 +90,34 @@
     <t xml:space="preserve">Net P/L to Date</t>
   </si>
   <si>
-    <t xml:space="preserve">Running Balance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Detail Tab / Notes</t>
+    <t xml:space="preserve">MLB Home Run Derby</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACTIVE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">World Cup 2026 — Final Four</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jul 14-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Open Championship (golf)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jul 16-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rugby Nations Cup — Final Rd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QUEUED</t>
   </si>
   <si>
     <t xml:space="preserve">NASCAR Quaker State 400</t>
@@ -104,63 +129,18 @@
     <t xml:space="preserve">SETTLED</t>
   </si>
   <si>
-    <t xml:space="preserve">Tab: NASCAR Jul 12 · SETTLED 1-6 (14.3%), -$434.51 · Blaney won in OT after 3h lightning red flag; Wallace P2 stripped (yellow-line)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">World Cup 2026 — Final Four</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jul 14-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACTIVE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tab: World Cup 2026 · semis Tue/Wed, final Sun</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Open Championship (golf)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jul 16-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tab: The Open · $600 outrights + $400 props Wed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rugby Nations Cup — Final Rd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QUEUED</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Draft card built · odds post ~Fri · $0 at risk</t>
-  </si>
-  <si>
     <t xml:space="preserve">WNBA Sunday Doubleheader</t>
   </si>
   <si>
-    <t xml:space="preserve">Tab: WNBA Jul 12 · SETTLED 3-4 (42.9%), -$298.15 · Fever routed Aces 109-75</t>
-  </si>
-  <si>
     <t xml:space="preserve">MLB Sunday Slate (15 games)</t>
   </si>
   <si>
-    <t xml:space="preserve">Tab: MLB Jul 12 · SETTLED 3-5 (37.5%), -$197.77</t>
-  </si>
-  <si>
     <t xml:space="preserve">UFC 329: McGregor vs Holloway 2</t>
   </si>
   <si>
     <t xml:space="preserve">2026-07-11</t>
   </si>
   <si>
-    <t xml:space="preserve">Tab: UFC 329 · 6-3, +$165.11 · archives Jul 18</t>
-  </si>
-  <si>
     <t xml:space="preserve">TOTALS</t>
   </si>
   <si>
@@ -239,21 +219,21 @@
     <t xml:space="preserve">Queued</t>
   </si>
   <si>
+    <t xml:space="preserve">Test 8 · HR Derby</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Willson Contreras outright</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+1400</t>
+  </si>
+  <si>
     <t xml:space="preserve">LONGSHOT HIT RATE</t>
   </si>
   <si>
     <t xml:space="preserve">Note: WC card carries an England hedge, not a longshot — excluded. UFC longshot was $0-stake and missed.</t>
   </si>
   <si>
-    <t xml:space="preserve">Legend: GREEN rows = ACTIVE · YELLOW = QUEUED (no money) · GREY = SETTLED/ARCHIVE. Tab colors match.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">'Net P/L to Date' includes partially-graded cards; Running Balance applies P/L top-to-bottom in display order (bottom row = current balance).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blue = manual input · Black = formula.</t>
-  </si>
-  <si>
     <t xml:space="preserve">TEST 1 — UFC 329: McGREGOR vs HOLLOWAY 2</t>
   </si>
   <si>
@@ -1145,6 +1125,12 @@
     <t xml:space="preserve">Sites queried but returning no usable facts (blocked/empty) are not listed.</t>
   </si>
   <si>
+    <t xml:space="preserve">Test 8 · HR Derby Jul 13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dknetwork.draftkings.com (outright odds); actionnetwork.com (format, props); vsin.com (props, picks); sports.yahoo.com (event info); mlb.com (schedule)</t>
+  </si>
+  <si>
     <t xml:space="preserve">TEST 5 — WNBA SUNDAY NIGHT DOUBLEHEADER · JULY 12, 2026</t>
   </si>
   <si>
@@ -1290,26 +1276,92 @@
   </si>
   <si>
     <t xml:space="preserve">Basket Coverage (one wins)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEST 8 — MLB HOME RUN DERBY · CITIZENS BANK PARK, PHILADELPHIA · JULY 13, 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STATUS: ACTIVE — settles tonight ~9:30 PM CT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 PM ET / 7 CT on Netflix · Source: cards/hrderby-jul13-betting-card.html · Outrights: DraftKings ~9 AM CT Jul 13 · Props: Action Network / VSiN lines, -110 std price</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bets 1, 2, 7 mutually exclusive (one winner). New format: 20 swings R1, top 4 to bracket (1v4/2v3), 15-swing semis+final, bonus swings while homering.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kyle Schwarber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anchor — MLB HR leader (32), home park, format suits him</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Caminero</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44 HR in last year's derby, same BP pitcher</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Schwarber R1 Over 10.5 HRs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Round 1 total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20 swings + bonus rule; 11 clears</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total Derby HRs Over 119.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Event total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bonus-swing rule + Philly July carry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ben Rice R1 Over 9.5 HRs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lefty pull power, 330-ft RF corner — VSiN lean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Longest HR Over 484.5 ft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Distance prop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caminero/Caglianone raw power, hot night</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LONGSHOT: Willson Contreras</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Longest price on board · counts in longshot record</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="11">
+  <numFmts count="14">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="\$#,##0"/>
     <numFmt numFmtId="166" formatCode="\$#,##0.00;&quot;($&quot;#,##0.00\);\-"/>
     <numFmt numFmtId="167" formatCode="\$#,##0.00"/>
-    <numFmt numFmtId="168" formatCode="\+0;\-0"/>
-    <numFmt numFmtId="169" formatCode="0"/>
-    <numFmt numFmtId="170" formatCode="0.0%"/>
-    <numFmt numFmtId="171" formatCode="0%"/>
-    <numFmt numFmtId="172" formatCode="0.0&quot; exp. wins&quot;"/>
-    <numFmt numFmtId="173" formatCode="0.0"/>
-    <numFmt numFmtId="174" formatCode="0.00&quot; exp. wins&quot;"/>
+    <numFmt numFmtId="168" formatCode="\$#,##0.00"/>
+    <numFmt numFmtId="169" formatCode="\$#,##0"/>
+    <numFmt numFmtId="170" formatCode="\+0;\-0"/>
+    <numFmt numFmtId="171" formatCode="0"/>
+    <numFmt numFmtId="172" formatCode="0.0%"/>
+    <numFmt numFmtId="173" formatCode="0%"/>
+    <numFmt numFmtId="174" formatCode="0.0&quot; exp. wins&quot;"/>
+    <numFmt numFmtId="175" formatCode="0.0"/>
+    <numFmt numFmtId="176" formatCode="0.00&quot; exp. wins&quot;"/>
+    <numFmt numFmtId="177" formatCode="\$#,##0.00;&quot;($&quot;#,##0.00\);\-"/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1386,39 +1438,8 @@
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
-      <sz val="10"/>
-      <color rgb="FF1B7A3D"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
       <sz val="9"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="10"/>
-      <color rgb="FF9C6500"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="10"/>
-      <color rgb="FF808080"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF0000FF"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -1433,6 +1454,13 @@
     <font>
       <b val="true"/>
       <sz val="13"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -1471,6 +1499,14 @@
     <font>
       <b val="true"/>
       <sz val="10"/>
+      <color rgb="FF1B7A3D"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -1489,8 +1525,14 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1523,12 +1565,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor rgb="FFE7E6E6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF808080"/>
         <bgColor rgb="FF969696"/>
       </patternFill>
@@ -1547,6 +1583,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor rgb="FFE7E6E6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor rgb="FFFFFF00"/>
       </patternFill>
@@ -1555,6 +1597,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF1B7A3D"/>
         <bgColor rgb="FF008080"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE81828"/>
+        <bgColor rgb="FFC00000"/>
       </patternFill>
     </fill>
   </fills>
@@ -1607,7 +1655,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="89">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1656,10 +1704,22 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1668,27 +1728,19 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1700,28 +1752,12 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -1732,82 +1768,62 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="169" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1816,7 +1832,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1824,7 +1844,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1832,27 +1852,39 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="7" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="7" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1860,71 +1892,123 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="174" fontId="7" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="175" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="176" fontId="7" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="24" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="174" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="177" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1937,7 +2021,35 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="4">
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <family val="0"/>
+        <b val="1"/>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <family val="0"/>
+        <b val="1"/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <name val="Arial"/>
@@ -1971,7 +2083,7 @@
     <indexedColors>
       <rgbColor rgb="FF000000"/>
       <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFC00000"/>
+      <rgbColor rgb="FFE81828"/>
       <rgbColor rgb="FF00FF00"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -1998,7 +2110,7 @@
       <rgbColor rgb="FFFFFF00"/>
       <rgbColor rgb="FF00FFFF"/>
       <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FFC00000"/>
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
@@ -2211,7 +2323,7 @@
     <tabColor rgb="FF1F2A44"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J38"/>
+  <dimension ref="A1:M40"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30"/>
@@ -2252,7 +2364,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="7" t="n">
-        <f aca="false">H23</f>
+        <f aca="false">H24</f>
         <v>-765.324133746613</v>
       </c>
     </row>
@@ -2270,8 +2382,8 @@
         <v>6</v>
       </c>
       <c r="B8" s="9" t="n">
-        <f aca="false">F23</f>
-        <v>1600</v>
+        <f aca="false">F24</f>
+        <v>2600</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2280,7 +2392,7 @@
       </c>
       <c r="B9" s="8" t="n">
         <f aca="false">B7-B8</f>
-        <v>2634.67586625339</v>
+        <v>1634.67586625339</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2288,8 +2400,8 @@
         <v>8</v>
       </c>
       <c r="B10" s="10" t="str">
-        <f aca="false">COUNTIF(D16:D22,"ACTIVE")&amp;" of 4 max"</f>
-        <v>2 of 4 max</v>
+        <f aca="false">COUNTIF(D16:D23,"ACTIVE")&amp;" of 4 max"</f>
+        <v>3 of 4 max</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2301,482 +2413,691 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="12" t="s">
         <v>11</v>
       </c>
+      <c r="B14" s="13"/>
+      <c r="C14" s="13"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="13"/>
+      <c r="F14" s="13"/>
+      <c r="G14" s="13"/>
+      <c r="H14" s="13"/>
+      <c r="I14" s="13"/>
+      <c r="J14" s="13"/>
+      <c r="K14" s="13"/>
+      <c r="L14" s="13"/>
+      <c r="M14" s="13"/>
     </row>
     <row r="15" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="12" t="s">
+      <c r="A15" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="B15" s="12" t="s">
+      <c r="B15" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="12" t="s">
+      <c r="C15" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="D15" s="12" t="s">
+      <c r="D15" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="E15" s="12" t="s">
+      <c r="E15" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="F15" s="12" t="s">
+      <c r="F15" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="G15" s="12" t="s">
+      <c r="G15" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="H15" s="12" t="s">
+      <c r="H15" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="I15" s="12" t="s">
+      <c r="I15" s="15"/>
+      <c r="J15" s="15"/>
+      <c r="K15" s="13"/>
+      <c r="L15" s="13"/>
+      <c r="M15" s="13"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="B16" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="J15" s="12" t="s">
+      <c r="C16" s="16" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="13" t="n">
+      <c r="D16" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="E16" s="19" t="n">
+        <f aca="false">SUM('HR Derby'!F7:F13)</f>
+        <v>1000</v>
+      </c>
+      <c r="F16" s="19" t="n">
+        <f aca="false">SUMIF('HR Derby'!I7:I13,"Pending",'HR Derby'!F7:F13)</f>
+        <v>1000</v>
+      </c>
+      <c r="G16" s="19" t="n">
+        <f aca="false">SUM('HR Derby'!J7:J13)</f>
+        <v>0</v>
+      </c>
+      <c r="H16" s="19" t="n">
+        <f aca="false">SUM('HR Derby'!K7:K13)</f>
+        <v>0</v>
+      </c>
+      <c r="I16" s="20"/>
+      <c r="J16" s="21"/>
+      <c r="K16" s="13"/>
+      <c r="L16" s="13"/>
+      <c r="M16" s="13"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="B17" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="C17" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="D17" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="E17" s="19" t="n">
+        <f aca="false">SUM('World Cup 2026'!F7:F13)</f>
+        <v>1000</v>
+      </c>
+      <c r="F17" s="19" t="n">
+        <f aca="false">SUMIF('World Cup 2026'!I7:I13,"Pending",'World Cup 2026'!F7:F13)</f>
+        <v>1000</v>
+      </c>
+      <c r="G17" s="19" t="n">
+        <f aca="false">SUM('World Cup 2026'!J7:J13)</f>
+        <v>0</v>
+      </c>
+      <c r="H17" s="19" t="n">
+        <f aca="false">SUM('World Cup 2026'!K7:K13)</f>
+        <v>0</v>
+      </c>
+      <c r="I17" s="20"/>
+      <c r="J17" s="21"/>
+      <c r="K17" s="13"/>
+      <c r="L17" s="13"/>
+      <c r="M17" s="13"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="B18" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="D18" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="E18" s="19" t="n">
+        <f aca="false">SUM('The Open'!F7:F12)</f>
+        <v>600</v>
+      </c>
+      <c r="F18" s="19" t="n">
+        <f aca="false">SUMIF('The Open'!I7:I12,"Pending",'The Open'!F7:F12)</f>
+        <v>600</v>
+      </c>
+      <c r="G18" s="19" t="n">
+        <f aca="false">SUM('The Open'!J7:J12)</f>
+        <v>0</v>
+      </c>
+      <c r="H18" s="19" t="n">
+        <f aca="false">SUM('The Open'!K7:K12)</f>
+        <v>0</v>
+      </c>
+      <c r="I18" s="20"/>
+      <c r="J18" s="21"/>
+      <c r="K18" s="13"/>
+      <c r="L18" s="13"/>
+      <c r="M18" s="13"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="22" t="n">
+        <v>7</v>
+      </c>
+      <c r="B19" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="D19" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="E19" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="20"/>
+      <c r="J19" s="21"/>
+      <c r="K19" s="13"/>
+      <c r="L19" s="13"/>
+      <c r="M19" s="13"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="B16" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="C16" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="D16" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="E16" s="16" t="n">
+      <c r="B20" s="27" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="D20" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="E20" s="29" t="n">
         <f aca="false">SUM('NASCAR Jul 12'!F7:F13)</f>
         <v>1000</v>
       </c>
-      <c r="F16" s="16" t="n">
+      <c r="F20" s="29" t="n">
         <f aca="false">SUMIF('NASCAR Jul 12'!I7:I13,"Pending",'NASCAR Jul 12'!F7:F13)</f>
         <v>0</v>
       </c>
-      <c r="G16" s="17" t="n">
+      <c r="G20" s="29" t="n">
         <f aca="false">SUM('NASCAR Jul 12'!J7:J13)</f>
         <v>565.486725663717</v>
       </c>
-      <c r="H16" s="18" t="n">
+      <c r="H20" s="29" t="n">
         <f aca="false">SUM('NASCAR Jul 12'!K7:K13)</f>
         <v>-434.513274336283</v>
       </c>
-      <c r="I16" s="19" t="n">
-        <f aca="false">B5+H16</f>
-        <v>4565.48672566372</v>
-      </c>
-      <c r="J16" s="20" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="B17" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="C17" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="D17" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="E17" s="16" t="n">
-        <f aca="false">SUM('World Cup 2026'!F7:F13)</f>
-        <v>1000</v>
-      </c>
-      <c r="F17" s="16" t="n">
-        <f aca="false">SUMIF('World Cup 2026'!I7:I13,"Pending",'World Cup 2026'!F7:F13)</f>
-        <v>1000</v>
-      </c>
-      <c r="G17" s="17" t="n">
-        <f aca="false">SUM('World Cup 2026'!J7:J13)</f>
-        <v>0</v>
-      </c>
-      <c r="H17" s="18" t="n">
-        <f aca="false">SUM('World Cup 2026'!K7:K13)</f>
-        <v>0</v>
-      </c>
-      <c r="I17" s="19" t="n">
-        <f aca="false">I16+H17</f>
-        <v>4565.48672566372</v>
-      </c>
-      <c r="J17" s="20" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="13" t="n">
-        <v>6</v>
-      </c>
-      <c r="B18" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="C18" s="13" t="s">
+      <c r="I20" s="20"/>
+      <c r="J20" s="21"/>
+      <c r="K20" s="13"/>
+      <c r="L20" s="13"/>
+      <c r="M20" s="13"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="B21" s="27" t="s">
+        <v>33</v>
+      </c>
+      <c r="C21" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="D18" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="E18" s="16" t="n">
-        <f aca="false">SUM('The Open'!F7:F12)</f>
-        <v>600</v>
-      </c>
-      <c r="F18" s="16" t="n">
-        <f aca="false">SUMIF('The Open'!I7:I12,"Pending",'The Open'!F7:F12)</f>
-        <v>600</v>
-      </c>
-      <c r="G18" s="17" t="n">
-        <f aca="false">SUM('The Open'!J7:J12)</f>
-        <v>0</v>
-      </c>
-      <c r="H18" s="18" t="n">
-        <f aca="false">SUM('The Open'!K7:K12)</f>
-        <v>0</v>
-      </c>
-      <c r="I18" s="19" t="n">
-        <f aca="false">I17+H18</f>
-        <v>4565.48672566372</v>
-      </c>
-      <c r="J18" s="20" t="s">
+      <c r="D21" s="28" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="21" t="n">
-        <v>7</v>
-      </c>
-      <c r="B19" s="22" t="s">
-        <v>33</v>
-      </c>
-      <c r="C19" s="21" t="s">
-        <v>34</v>
-      </c>
-      <c r="D19" s="23" t="s">
-        <v>35</v>
-      </c>
-      <c r="E19" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="27" t="n">
-        <f aca="false">I18+H19</f>
-        <v>4565.48672566372</v>
-      </c>
-      <c r="J19" s="28" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="29" t="n">
-        <v>5</v>
-      </c>
-      <c r="B20" s="30" t="s">
-        <v>37</v>
-      </c>
-      <c r="C20" s="29" t="s">
-        <v>23</v>
-      </c>
-      <c r="D20" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="E20" s="32" t="n">
+      <c r="E21" s="29" t="n">
         <f aca="false">SUM('WNBA Jul 12'!F7:F13)</f>
         <v>1000</v>
       </c>
-      <c r="F20" s="32" t="n">
+      <c r="F21" s="29" t="n">
         <f aca="false">SUMIF('WNBA Jul 12'!I7:I13,"Pending",'WNBA Jul 12'!F7:F13)</f>
         <v>0</v>
       </c>
-      <c r="G20" s="33" t="n">
+      <c r="G21" s="29" t="n">
         <f aca="false">SUM('WNBA Jul 12'!J7:J13)</f>
         <v>701.846509693851</v>
       </c>
-      <c r="H20" s="34" t="n">
+      <c r="H21" s="29" t="n">
         <f aca="false">SUM('WNBA Jul 12'!K7:K13)</f>
         <v>-298.153490306149</v>
       </c>
-      <c r="I20" s="35" t="n">
-        <f aca="false">I19+H20</f>
-        <v>4267.33323535757</v>
-      </c>
-      <c r="J20" s="36" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="29" t="n">
+      <c r="I21" s="20"/>
+      <c r="J21" s="21"/>
+      <c r="K21" s="13"/>
+      <c r="L21" s="13"/>
+      <c r="M21" s="13"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="B21" s="30" t="s">
-        <v>39</v>
-      </c>
-      <c r="C21" s="29" t="s">
-        <v>23</v>
-      </c>
-      <c r="D21" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="E21" s="32" t="n">
+      <c r="B22" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="C22" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="D22" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="E22" s="29" t="n">
         <f aca="false">SUM('MLB Jul 12'!F7:F14)</f>
         <v>1000</v>
       </c>
-      <c r="F21" s="32" t="n">
+      <c r="F22" s="29" t="n">
         <f aca="false">SUMIF('MLB Jul 12'!I7:I14,"Pending",'MLB Jul 12'!F7:F14)</f>
         <v>0</v>
       </c>
-      <c r="G21" s="33" t="n">
+      <c r="G22" s="29" t="n">
         <f aca="false">SUM('MLB Jul 12'!J7:J14)</f>
         <v>802.232258064516</v>
       </c>
-      <c r="H21" s="34" t="n">
+      <c r="H22" s="29" t="n">
         <f aca="false">SUM('MLB Jul 12'!K7:K14)</f>
         <v>-197.767741935484</v>
       </c>
-      <c r="I21" s="35" t="n">
-        <f aca="false">I20+H21</f>
-        <v>4069.56549342208</v>
-      </c>
-      <c r="J21" s="36" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="29" t="n">
+      <c r="I22" s="20"/>
+      <c r="J22" s="21"/>
+      <c r="K22" s="13"/>
+      <c r="L22" s="13"/>
+      <c r="M22" s="13"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="B22" s="30" t="s">
-        <v>41</v>
-      </c>
-      <c r="C22" s="29" t="s">
-        <v>42</v>
-      </c>
-      <c r="D22" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="E22" s="32" t="n">
+      <c r="B23" s="27" t="s">
+        <v>35</v>
+      </c>
+      <c r="C23" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="D23" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="E23" s="29" t="n">
         <f aca="false">SUM('UFC 329'!F7:F15)</f>
         <v>1050</v>
       </c>
-      <c r="F22" s="32" t="n">
+      <c r="F23" s="29" t="n">
         <f aca="false">SUMIF('UFC 329'!I7:I15,"Pending",'UFC 329'!F7:F15)</f>
         <v>0</v>
       </c>
-      <c r="G22" s="33" t="n">
+      <c r="G23" s="29" t="n">
         <f aca="false">SUM('UFC 329'!J7:J15)</f>
         <v>1215.1103728313</v>
       </c>
-      <c r="H22" s="34" t="n">
+      <c r="H23" s="29" t="n">
         <f aca="false">SUM('UFC 329'!K7:K15)</f>
         <v>165.110372831303</v>
       </c>
-      <c r="I22" s="35" t="n">
-        <f aca="false">I21+H22</f>
-        <v>4234.67586625339</v>
-      </c>
-      <c r="J22" s="36" t="s">
+      <c r="I23" s="30"/>
+      <c r="J23" s="30"/>
+      <c r="K23" s="13"/>
+      <c r="L23" s="13"/>
+      <c r="M23" s="13"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="13"/>
+      <c r="B24" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="C24" s="13"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="32" t="n">
+        <f aca="false">SUM(E16:E23)</f>
+        <v>6650</v>
+      </c>
+      <c r="F24" s="32" t="n">
+        <f aca="false">SUM(F16:F23)</f>
+        <v>2600</v>
+      </c>
+      <c r="G24" s="32" t="n">
+        <f aca="false">SUM(G16:G23)</f>
+        <v>3284.67586625339</v>
+      </c>
+      <c r="H24" s="32" t="n">
+        <f aca="false">SUM(H16:H23)</f>
+        <v>-765.324133746613</v>
+      </c>
+      <c r="I24" s="13"/>
+      <c r="J24" s="13"/>
+      <c r="K24" s="13"/>
+      <c r="L24" s="13"/>
+      <c r="M24" s="13"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="12"/>
+      <c r="B25" s="13"/>
+      <c r="C25" s="13"/>
+      <c r="D25" s="13"/>
+      <c r="E25" s="13"/>
+      <c r="F25" s="13"/>
+      <c r="G25" s="13"/>
+      <c r="H25" s="13"/>
+      <c r="I25" s="13"/>
+      <c r="J25" s="13"/>
+      <c r="K25" s="13"/>
+      <c r="L25" s="13"/>
+      <c r="M25" s="13"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="33" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="15"/>
+      <c r="C26" s="15"/>
+      <c r="D26" s="15"/>
+      <c r="E26" s="15"/>
+      <c r="F26" s="13"/>
+      <c r="G26" s="13"/>
+      <c r="H26" s="13"/>
+      <c r="I26" s="13"/>
+      <c r="J26" s="13"/>
+      <c r="K26" s="13"/>
+      <c r="L26" s="13"/>
+      <c r="M26" s="13"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="C27" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="D27" s="34" t="s">
+        <v>42</v>
+      </c>
+      <c r="E27" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="F27" s="13"/>
+      <c r="G27" s="13"/>
+      <c r="H27" s="13"/>
+      <c r="I27" s="13"/>
+      <c r="J27" s="13"/>
+      <c r="K27" s="13"/>
+      <c r="L27" s="13"/>
+      <c r="M27" s="13"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="35" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="37"/>
-      <c r="B23" s="38" t="s">
+      <c r="B28" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="C23" s="37"/>
-      <c r="D23" s="37"/>
-      <c r="E23" s="39" t="n">
-        <f aca="false">SUM(E16:E22)</f>
-        <v>5650</v>
-      </c>
-      <c r="F23" s="39" t="n">
-        <f aca="false">SUM(F16:F22)</f>
-        <v>1600</v>
-      </c>
-      <c r="G23" s="40" t="n">
-        <f aca="false">SUM(G16:G22)</f>
-        <v>3284.67586625339</v>
-      </c>
-      <c r="H23" s="41" t="n">
-        <f aca="false">SUM(H16:H22)</f>
-        <v>-765.324133746613</v>
-      </c>
-      <c r="I23" s="37"/>
-      <c r="J23" s="37"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="4" t="s">
+      <c r="C28" s="36" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="12" t="s">
+      <c r="D28" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="B26" s="12" t="s">
+      <c r="F28" s="13"/>
+      <c r="G28" s="13"/>
+      <c r="H28" s="13"/>
+      <c r="I28" s="13"/>
+      <c r="J28" s="13"/>
+      <c r="K28" s="13"/>
+      <c r="L28" s="13"/>
+      <c r="M28" s="13"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="35" t="s">
         <v>47</v>
       </c>
-      <c r="C26" s="12" t="s">
+      <c r="B29" s="35" t="s">
         <v>48</v>
       </c>
-      <c r="D26" s="12" t="s">
+      <c r="C29" s="36" t="s">
         <v>49</v>
       </c>
-      <c r="E26" s="12" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="5" t="s">
+      <c r="D29" s="37" t="n">
         <v>50</v>
       </c>
-      <c r="B27" s="42" t="s">
-        <v>51</v>
-      </c>
-      <c r="C27" s="43" t="s">
-        <v>52</v>
-      </c>
-      <c r="D27" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" s="10" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="B28" s="42" t="s">
-        <v>55</v>
-      </c>
-      <c r="C28" s="43" t="s">
-        <v>56</v>
-      </c>
-      <c r="D28" s="44" t="n">
-        <v>50</v>
-      </c>
-      <c r="E28" s="10" t="str">
+      <c r="E29" s="10" t="str">
         <f aca="false">IF('MLB Jul 12'!I14="Win","HIT",IF('MLB Jul 12'!I14="Loss","MISS","Pending"))</f>
         <v>MISS</v>
       </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="B29" s="42" t="s">
-        <v>58</v>
-      </c>
-      <c r="C29" s="43" t="s">
-        <v>59</v>
-      </c>
-      <c r="D29" s="44" t="n">
+      <c r="F29" s="13"/>
+      <c r="G29" s="13"/>
+      <c r="H29" s="13"/>
+      <c r="I29" s="13"/>
+      <c r="J29" s="13"/>
+      <c r="K29" s="13"/>
+      <c r="L29" s="13"/>
+      <c r="M29" s="13"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="35" t="s">
+        <v>50</v>
+      </c>
+      <c r="B30" s="35" t="s">
+        <v>51</v>
+      </c>
+      <c r="C30" s="36" t="s">
+        <v>52</v>
+      </c>
+      <c r="D30" s="37" t="n">
         <v>40</v>
       </c>
-      <c r="E29" s="10" t="str">
+      <c r="E30" s="10" t="str">
         <f aca="false">IF('NASCAR Jul 12'!I13="Win","HIT",IF('NASCAR Jul 12'!I13="Loss","MISS","Pending"))</f>
         <v>MISS</v>
       </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="B30" s="42" t="s">
-        <v>61</v>
-      </c>
-      <c r="C30" s="43" t="s">
-        <v>62</v>
-      </c>
-      <c r="D30" s="44" t="n">
+      <c r="F30" s="13"/>
+      <c r="G30" s="13"/>
+      <c r="H30" s="13"/>
+      <c r="I30" s="13"/>
+      <c r="J30" s="13"/>
+      <c r="K30" s="13"/>
+      <c r="L30" s="13"/>
+      <c r="M30" s="13"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="35" t="s">
+        <v>53</v>
+      </c>
+      <c r="B31" s="35" t="s">
+        <v>54</v>
+      </c>
+      <c r="C31" s="36" t="s">
+        <v>55</v>
+      </c>
+      <c r="D31" s="37" t="n">
         <v>100</v>
       </c>
-      <c r="E30" s="10" t="str">
+      <c r="E31" s="10" t="str">
         <f aca="false">IF('WNBA Jul 12'!I13="Win","HIT",IF('WNBA Jul 12'!I13="Loss","MISS","Pending"))</f>
         <v>MISS</v>
       </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="B31" s="42" t="s">
-        <v>64</v>
-      </c>
-      <c r="C31" s="43" t="s">
-        <v>65</v>
-      </c>
-      <c r="D31" s="44" t="n">
+      <c r="F31" s="13"/>
+      <c r="G31" s="13"/>
+      <c r="H31" s="13"/>
+      <c r="I31" s="13"/>
+      <c r="J31" s="13"/>
+      <c r="K31" s="13"/>
+      <c r="L31" s="13"/>
+      <c r="M31" s="13"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="B32" s="35" t="s">
+        <v>57</v>
+      </c>
+      <c r="C32" s="36" t="s">
+        <v>58</v>
+      </c>
+      <c r="D32" s="37" t="n">
         <v>50</v>
       </c>
-      <c r="E31" s="10" t="str">
+      <c r="E32" s="10" t="str">
         <f aca="false">IF('The Open'!I12="Win","HIT",IF('The Open'!I12="Loss","MISS","Pending"))</f>
         <v>Pending</v>
       </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="5" t="s">
+      <c r="F32" s="13"/>
+      <c r="G32" s="13"/>
+      <c r="H32" s="13"/>
+      <c r="I32" s="13"/>
+      <c r="J32" s="13"/>
+      <c r="K32" s="13"/>
+      <c r="L32" s="13"/>
+      <c r="M32" s="13"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="35" t="s">
+        <v>59</v>
+      </c>
+      <c r="B33" s="35" t="s">
+        <v>60</v>
+      </c>
+      <c r="C33" s="36" t="s">
+        <v>61</v>
+      </c>
+      <c r="D33" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="F33" s="13"/>
+      <c r="G33" s="13"/>
+      <c r="H33" s="13"/>
+      <c r="I33" s="13"/>
+      <c r="J33" s="13"/>
+      <c r="K33" s="13"/>
+      <c r="L33" s="13"/>
+      <c r="M33" s="13"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="35" t="s">
+        <v>63</v>
+      </c>
+      <c r="B34" s="35" t="s">
+        <v>64</v>
+      </c>
+      <c r="C34" s="36" t="s">
+        <v>65</v>
+      </c>
+      <c r="D34" s="37" t="n">
+        <v>75</v>
+      </c>
+      <c r="E34" s="10" t="str">
+        <f aca="false">IF('HR Derby'!I13="Win","HIT",IF('HR Derby'!I13="Loss","MISS","Pending"))</f>
+        <v>Pending</v>
+      </c>
+      <c r="F34" s="13"/>
+      <c r="G34" s="13"/>
+      <c r="H34" s="13"/>
+      <c r="I34" s="13"/>
+      <c r="J34" s="13"/>
+      <c r="K34" s="13"/>
+      <c r="L34" s="13"/>
+      <c r="M34" s="13"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="31" t="s">
         <v>66</v>
       </c>
-      <c r="B32" s="42" t="s">
+      <c r="B35" s="13"/>
+      <c r="C35" s="13"/>
+      <c r="D35" s="13"/>
+      <c r="E35" s="10" t="str">
+        <f aca="false">IF(COUNTIF(E28:E34,"HIT")+COUNTIF(E28:E34,"MISS")=0,"—",COUNTIF(E28:E34,"HIT")&amp;"-for-"&amp;(COUNTIF(E28:E34,"HIT")+COUNTIF(E28:E34,"MISS"))&amp;" ("&amp;TEXT(COUNTIF(E28:E34,"HIT")/(COUNTIF(E28:E34,"HIT")+COUNTIF(E28:E34,"MISS")),"0%")&amp;")")</f>
+        <v>0-for-4 (0%)</v>
+      </c>
+      <c r="F35" s="13"/>
+      <c r="G35" s="13"/>
+      <c r="H35" s="13"/>
+      <c r="I35" s="13"/>
+      <c r="J35" s="13"/>
+      <c r="K35" s="13"/>
+      <c r="L35" s="13"/>
+      <c r="M35" s="13"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="38" t="s">
         <v>67</v>
       </c>
-      <c r="C32" s="43" t="s">
-        <v>68</v>
-      </c>
-      <c r="D32" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" s="10" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="38" t="s">
-        <v>70</v>
-      </c>
-      <c r="B33" s="37"/>
-      <c r="C33" s="37"/>
-      <c r="D33" s="37"/>
-      <c r="E33" s="45" t="str">
-        <f aca="false">IF(COUNTIF(E27:E32,"HIT")+COUNTIF(E27:E32,"MISS")=0,"—",COUNTIF(E27:E32,"HIT")&amp;"-for-"&amp;(COUNTIF(E27:E32,"HIT")+COUNTIF(E27:E32,"MISS"))&amp;" ("&amp;TEXT(COUNTIF(E27:E32,"HIT")/(COUNTIF(E27:E32,"HIT")+COUNTIF(E27:E32,"MISS")),"0%")&amp;")")</f>
-        <v>0-for-4 (0%)</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="46" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="46" t="s">
-        <v>72</v>
-      </c>
+      <c r="B36" s="13"/>
+      <c r="C36" s="13"/>
+      <c r="D36" s="13"/>
+      <c r="E36" s="13"/>
+      <c r="F36" s="13"/>
+      <c r="G36" s="13"/>
+      <c r="H36" s="13"/>
+      <c r="I36" s="13"/>
+      <c r="J36" s="13"/>
+      <c r="K36" s="13"/>
+      <c r="L36" s="13"/>
+      <c r="M36" s="13"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="46" t="s">
-        <v>73</v>
-      </c>
+      <c r="A37" s="39"/>
+      <c r="B37" s="13"/>
+      <c r="C37" s="13"/>
+      <c r="D37" s="13"/>
+      <c r="E37" s="13"/>
+      <c r="F37" s="13"/>
+      <c r="G37" s="13"/>
+      <c r="H37" s="13"/>
+      <c r="I37" s="13"/>
+      <c r="J37" s="13"/>
+      <c r="K37" s="13"/>
+      <c r="L37" s="13"/>
+      <c r="M37" s="13"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="46" t="s">
-        <v>74</v>
-      </c>
+      <c r="A38" s="39"/>
+      <c r="B38" s="13"/>
+      <c r="C38" s="13"/>
+      <c r="D38" s="13"/>
+      <c r="E38" s="13"/>
+      <c r="F38" s="13"/>
+      <c r="G38" s="13"/>
+      <c r="H38" s="13"/>
+      <c r="I38" s="13"/>
+      <c r="J38" s="13"/>
+      <c r="K38" s="13"/>
+      <c r="L38" s="13"/>
+      <c r="M38" s="13"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="13"/>
+      <c r="B39" s="13"/>
+      <c r="C39" s="13"/>
+      <c r="D39" s="13"/>
+      <c r="E39" s="13"/>
+      <c r="F39" s="13"/>
+      <c r="G39" s="13"/>
+      <c r="H39" s="13"/>
+      <c r="I39" s="13"/>
+      <c r="J39" s="13"/>
+      <c r="K39" s="13"/>
+      <c r="L39" s="13"/>
+      <c r="M39" s="13"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="13"/>
+      <c r="B40" s="13"/>
+      <c r="C40" s="13"/>
+      <c r="D40" s="13"/>
+      <c r="E40" s="13"/>
+      <c r="F40" s="13"/>
+      <c r="G40" s="13"/>
+      <c r="H40" s="13"/>
+      <c r="I40" s="13"/>
+      <c r="J40" s="13"/>
+      <c r="K40" s="13"/>
+      <c r="L40" s="13"/>
+      <c r="M40" s="13"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="H16:H23">
@@ -2809,6 +3130,14 @@
     </cfRule>
     <cfRule type="expression" priority="9" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>AND(ISNUMBER(B7),B7&lt;5000)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H16:H24">
+    <cfRule type="expression" priority="10" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+      <formula>AND(ISNUMBER(H16),H16&gt;0)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="11" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+      <formula>AND(ISNUMBER(H16),H16&lt;0)</formula>
     </cfRule>
   </conditionalFormatting>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -2843,728 +3172,728 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="47" t="s">
-        <v>75</v>
-      </c>
-      <c r="H1" s="48" t="s">
-        <v>76</v>
+      <c r="A1" s="40" t="s">
+        <v>68</v>
+      </c>
+      <c r="H1" s="41" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="F6" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="G6" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H6" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="I6" s="14" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="12" t="s">
+      <c r="J6" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="K6" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="L6" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="E6" s="12" t="s">
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="42" t="s">
         <v>83</v>
       </c>
-      <c r="F6" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="G6" s="12" t="s">
+      <c r="C7" s="43" t="s">
         <v>84</v>
       </c>
-      <c r="H6" s="12" t="s">
+      <c r="D7" s="36" t="s">
         <v>85</v>
       </c>
-      <c r="I6" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="J6" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="K6" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="L6" s="12" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="49" t="n">
-        <v>1</v>
-      </c>
-      <c r="B7" s="50" t="s">
-        <v>90</v>
-      </c>
-      <c r="C7" s="51" t="s">
-        <v>91</v>
-      </c>
-      <c r="D7" s="49" t="s">
-        <v>92</v>
-      </c>
-      <c r="E7" s="52" t="n">
+      <c r="E7" s="44" t="n">
         <v>-265</v>
       </c>
-      <c r="F7" s="44" t="n">
+      <c r="F7" s="45" t="n">
         <v>265</v>
       </c>
-      <c r="G7" s="53" t="n">
+      <c r="G7" s="46" t="n">
         <f aca="false">IF(E7&gt;0,F7*E7/100,F7*100/ABS(E7))</f>
         <v>100</v>
       </c>
-      <c r="H7" s="53" t="n">
+      <c r="H7" s="46" t="n">
         <f aca="false">F7+G7</f>
         <v>365</v>
       </c>
-      <c r="I7" s="54" t="s">
-        <v>93</v>
-      </c>
-      <c r="J7" s="53" t="n">
+      <c r="I7" s="47" t="s">
+        <v>86</v>
+      </c>
+      <c r="J7" s="46" t="n">
         <f aca="false">IF(I7="Win",F7+G7,IF(I7="Push",F7,IF(I7="Loss",0,0)))</f>
         <v>365</v>
       </c>
-      <c r="K7" s="55" t="n">
+      <c r="K7" s="48" t="n">
         <f aca="false">IF(I7="Pending",0,J7-F7)</f>
         <v>100</v>
       </c>
-      <c r="L7" s="56" t="s">
-        <v>94</v>
+      <c r="L7" s="49" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="49" t="n">
+      <c r="A8" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="50" t="s">
-        <v>95</v>
-      </c>
-      <c r="C8" s="51" t="s">
-        <v>96</v>
-      </c>
-      <c r="D8" s="49" t="s">
-        <v>97</v>
-      </c>
-      <c r="E8" s="52" t="n">
+      <c r="B8" s="42" t="s">
+        <v>88</v>
+      </c>
+      <c r="C8" s="43" t="s">
+        <v>89</v>
+      </c>
+      <c r="D8" s="36" t="s">
+        <v>90</v>
+      </c>
+      <c r="E8" s="44" t="n">
         <v>-140</v>
       </c>
-      <c r="F8" s="44" t="n">
+      <c r="F8" s="45" t="n">
         <v>200</v>
       </c>
-      <c r="G8" s="53" t="n">
+      <c r="G8" s="46" t="n">
         <f aca="false">IF(E8&gt;0,F8*E8/100,F8*100/ABS(E8))</f>
         <v>142.857142857143</v>
       </c>
-      <c r="H8" s="53" t="n">
+      <c r="H8" s="46" t="n">
         <f aca="false">F8+G8</f>
         <v>342.857142857143</v>
       </c>
-      <c r="I8" s="54" t="s">
-        <v>93</v>
-      </c>
-      <c r="J8" s="53" t="n">
+      <c r="I8" s="47" t="s">
+        <v>86</v>
+      </c>
+      <c r="J8" s="46" t="n">
         <f aca="false">IF(I8="Win",F8+G8,IF(I8="Push",F8,IF(I8="Loss",0,0)))</f>
         <v>342.857142857143</v>
       </c>
-      <c r="K8" s="55" t="n">
+      <c r="K8" s="48" t="n">
         <f aca="false">IF(I8="Pending",0,J8-F8)</f>
         <v>142.857142857143</v>
       </c>
-      <c r="L8" s="56" t="s">
-        <v>98</v>
+      <c r="L8" s="49" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="49" t="n">
+      <c r="A9" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="B9" s="50" t="s">
-        <v>99</v>
-      </c>
-      <c r="C9" s="51" t="s">
-        <v>100</v>
-      </c>
-      <c r="D9" s="49" t="s">
+      <c r="B9" s="42" t="s">
         <v>92</v>
       </c>
-      <c r="E9" s="52" t="n">
+      <c r="C9" s="43" t="s">
+        <v>93</v>
+      </c>
+      <c r="D9" s="36" t="s">
+        <v>85</v>
+      </c>
+      <c r="E9" s="44" t="n">
         <v>-148</v>
       </c>
-      <c r="F9" s="44" t="n">
+      <c r="F9" s="45" t="n">
         <v>148</v>
       </c>
-      <c r="G9" s="53" t="n">
+      <c r="G9" s="46" t="n">
         <f aca="false">IF(E9&gt;0,F9*E9/100,F9*100/ABS(E9))</f>
         <v>100</v>
       </c>
-      <c r="H9" s="53" t="n">
+      <c r="H9" s="46" t="n">
         <f aca="false">F9+G9</f>
         <v>248</v>
       </c>
-      <c r="I9" s="57" t="s">
-        <v>101</v>
-      </c>
-      <c r="J9" s="53" t="n">
+      <c r="I9" s="50" t="s">
+        <v>94</v>
+      </c>
+      <c r="J9" s="46" t="n">
         <f aca="false">IF(I9="Win",F9+G9,IF(I9="Push",F9,IF(I9="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K9" s="55" t="n">
+      <c r="K9" s="48" t="n">
         <f aca="false">IF(I9="Pending",0,J9-F9)</f>
         <v>-148</v>
       </c>
-      <c r="L9" s="56" t="s">
-        <v>102</v>
+      <c r="L9" s="49" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="49" t="n">
+      <c r="A10" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="B10" s="50" t="s">
-        <v>103</v>
-      </c>
-      <c r="C10" s="51" t="s">
-        <v>104</v>
-      </c>
-      <c r="D10" s="49" t="s">
-        <v>92</v>
-      </c>
-      <c r="E10" s="52" t="n">
+      <c r="B10" s="42" t="s">
+        <v>96</v>
+      </c>
+      <c r="C10" s="43" t="s">
+        <v>97</v>
+      </c>
+      <c r="D10" s="36" t="s">
+        <v>85</v>
+      </c>
+      <c r="E10" s="44" t="n">
         <v>114</v>
       </c>
-      <c r="F10" s="44" t="n">
+      <c r="F10" s="45" t="n">
         <v>100</v>
       </c>
-      <c r="G10" s="53" t="n">
+      <c r="G10" s="46" t="n">
         <f aca="false">IF(E10&gt;0,F10*E10/100,F10*100/ABS(E10))</f>
         <v>114</v>
       </c>
-      <c r="H10" s="53" t="n">
+      <c r="H10" s="46" t="n">
         <f aca="false">F10+G10</f>
         <v>214</v>
       </c>
-      <c r="I10" s="54" t="s">
-        <v>93</v>
-      </c>
-      <c r="J10" s="53" t="n">
+      <c r="I10" s="47" t="s">
+        <v>86</v>
+      </c>
+      <c r="J10" s="46" t="n">
         <f aca="false">IF(I10="Win",F10+G10,IF(I10="Push",F10,IF(I10="Loss",0,0)))</f>
         <v>214</v>
       </c>
-      <c r="K10" s="55" t="n">
+      <c r="K10" s="48" t="n">
         <f aca="false">IF(I10="Pending",0,J10-F10)</f>
         <v>114</v>
       </c>
-      <c r="L10" s="56" t="s">
-        <v>105</v>
+      <c r="L10" s="49" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="49" t="n">
+      <c r="A11" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="50" t="s">
-        <v>106</v>
-      </c>
-      <c r="C11" s="51" t="s">
-        <v>107</v>
-      </c>
-      <c r="D11" s="49" t="s">
-        <v>92</v>
-      </c>
-      <c r="E11" s="52" t="n">
+      <c r="B11" s="42" t="s">
+        <v>99</v>
+      </c>
+      <c r="C11" s="43" t="s">
+        <v>100</v>
+      </c>
+      <c r="D11" s="36" t="s">
+        <v>85</v>
+      </c>
+      <c r="E11" s="44" t="n">
         <v>-218</v>
       </c>
-      <c r="F11" s="44" t="n">
+      <c r="F11" s="45" t="n">
         <v>100</v>
       </c>
-      <c r="G11" s="53" t="n">
+      <c r="G11" s="46" t="n">
         <f aca="false">IF(E11&gt;0,F11*E11/100,F11*100/ABS(E11))</f>
         <v>45.8715596330275</v>
       </c>
-      <c r="H11" s="53" t="n">
+      <c r="H11" s="46" t="n">
         <f aca="false">F11+G11</f>
         <v>145.871559633028</v>
       </c>
-      <c r="I11" s="57" t="s">
-        <v>101</v>
-      </c>
-      <c r="J11" s="53" t="n">
+      <c r="I11" s="50" t="s">
+        <v>94</v>
+      </c>
+      <c r="J11" s="46" t="n">
         <f aca="false">IF(I11="Win",F11+G11,IF(I11="Push",F11,IF(I11="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K11" s="55" t="n">
+      <c r="K11" s="48" t="n">
         <f aca="false">IF(I11="Pending",0,J11-F11)</f>
         <v>-100</v>
       </c>
-      <c r="L11" s="56" t="s">
-        <v>108</v>
+      <c r="L11" s="49" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="49" t="n">
+      <c r="A12" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="50" t="s">
-        <v>109</v>
-      </c>
-      <c r="C12" s="51" t="s">
-        <v>110</v>
-      </c>
-      <c r="D12" s="49" t="s">
-        <v>92</v>
-      </c>
-      <c r="E12" s="52" t="n">
+      <c r="B12" s="42" t="s">
+        <v>102</v>
+      </c>
+      <c r="C12" s="43" t="s">
+        <v>103</v>
+      </c>
+      <c r="D12" s="36" t="s">
+        <v>85</v>
+      </c>
+      <c r="E12" s="44" t="n">
         <v>-125</v>
       </c>
-      <c r="F12" s="44" t="n">
+      <c r="F12" s="45" t="n">
         <v>75</v>
       </c>
-      <c r="G12" s="53" t="n">
+      <c r="G12" s="46" t="n">
         <f aca="false">IF(E12&gt;0,F12*E12/100,F12*100/ABS(E12))</f>
         <v>60</v>
       </c>
-      <c r="H12" s="53" t="n">
+      <c r="H12" s="46" t="n">
         <f aca="false">F12+G12</f>
         <v>135</v>
       </c>
-      <c r="I12" s="54" t="s">
-        <v>93</v>
-      </c>
-      <c r="J12" s="53" t="n">
+      <c r="I12" s="47" t="s">
+        <v>86</v>
+      </c>
+      <c r="J12" s="46" t="n">
         <f aca="false">IF(I12="Win",F12+G12,IF(I12="Push",F12,IF(I12="Loss",0,0)))</f>
         <v>135</v>
       </c>
-      <c r="K12" s="55" t="n">
+      <c r="K12" s="48" t="n">
         <f aca="false">IF(I12="Pending",0,J12-F12)</f>
         <v>60</v>
       </c>
-      <c r="L12" s="56" t="s">
-        <v>111</v>
+      <c r="L12" s="49" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="49" t="n">
+      <c r="A13" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="50" t="s">
-        <v>112</v>
-      </c>
-      <c r="C13" s="51" t="s">
-        <v>113</v>
-      </c>
-      <c r="D13" s="49" t="s">
-        <v>92</v>
-      </c>
-      <c r="E13" s="52" t="n">
+      <c r="B13" s="42" t="s">
+        <v>105</v>
+      </c>
+      <c r="C13" s="43" t="s">
+        <v>106</v>
+      </c>
+      <c r="D13" s="36" t="s">
+        <v>85</v>
+      </c>
+      <c r="E13" s="44" t="n">
         <v>-225</v>
       </c>
-      <c r="F13" s="44" t="n">
+      <c r="F13" s="45" t="n">
         <v>50</v>
       </c>
-      <c r="G13" s="53" t="n">
+      <c r="G13" s="46" t="n">
         <f aca="false">IF(E13&gt;0,F13*E13/100,F13*100/ABS(E13))</f>
         <v>22.2222222222222</v>
       </c>
-      <c r="H13" s="53" t="n">
+      <c r="H13" s="46" t="n">
         <f aca="false">F13+G13</f>
         <v>72.2222222222222</v>
       </c>
-      <c r="I13" s="54" t="s">
-        <v>93</v>
-      </c>
-      <c r="J13" s="53" t="n">
+      <c r="I13" s="47" t="s">
+        <v>86</v>
+      </c>
+      <c r="J13" s="46" t="n">
         <f aca="false">IF(I13="Win",F13+G13,IF(I13="Push",F13,IF(I13="Loss",0,0)))</f>
         <v>72.2222222222222</v>
       </c>
-      <c r="K13" s="55" t="n">
+      <c r="K13" s="48" t="n">
         <f aca="false">IF(I13="Pending",0,J13-F13)</f>
         <v>22.2222222222222</v>
       </c>
-      <c r="L13" s="56" t="s">
-        <v>114</v>
+      <c r="L13" s="49" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="49" t="n">
+      <c r="A14" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="B14" s="50" t="s">
-        <v>115</v>
-      </c>
-      <c r="C14" s="51" t="s">
-        <v>116</v>
-      </c>
-      <c r="D14" s="49" t="s">
-        <v>92</v>
-      </c>
-      <c r="E14" s="52" t="n">
+      <c r="B14" s="42" t="s">
+        <v>108</v>
+      </c>
+      <c r="C14" s="43" t="s">
+        <v>109</v>
+      </c>
+      <c r="D14" s="36" t="s">
+        <v>85</v>
+      </c>
+      <c r="E14" s="44" t="n">
         <v>-258</v>
       </c>
-      <c r="F14" s="44" t="n">
+      <c r="F14" s="45" t="n">
         <v>62</v>
       </c>
-      <c r="G14" s="53" t="n">
+      <c r="G14" s="46" t="n">
         <f aca="false">IF(E14&gt;0,F14*E14/100,F14*100/ABS(E14))</f>
         <v>24.031007751938</v>
       </c>
-      <c r="H14" s="53" t="n">
+      <c r="H14" s="46" t="n">
         <f aca="false">F14+G14</f>
         <v>86.031007751938</v>
       </c>
-      <c r="I14" s="54" t="s">
-        <v>93</v>
-      </c>
-      <c r="J14" s="53" t="n">
+      <c r="I14" s="47" t="s">
+        <v>86</v>
+      </c>
+      <c r="J14" s="46" t="n">
         <f aca="false">IF(I14="Win",F14+G14,IF(I14="Push",F14,IF(I14="Loss",0,0)))</f>
         <v>86.031007751938</v>
       </c>
-      <c r="K14" s="55" t="n">
+      <c r="K14" s="48" t="n">
         <f aca="false">IF(I14="Pending",0,J14-F14)</f>
         <v>24.031007751938</v>
       </c>
-      <c r="L14" s="56" t="s">
-        <v>117</v>
+      <c r="L14" s="49" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="49" t="n">
+      <c r="A15" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="B15" s="50" t="s">
-        <v>118</v>
-      </c>
-      <c r="C15" s="51" t="s">
-        <v>119</v>
-      </c>
-      <c r="D15" s="49" t="s">
-        <v>120</v>
-      </c>
-      <c r="E15" s="52" t="n">
+      <c r="B15" s="42" t="s">
+        <v>111</v>
+      </c>
+      <c r="C15" s="43" t="s">
+        <v>112</v>
+      </c>
+      <c r="D15" s="36" t="s">
+        <v>113</v>
+      </c>
+      <c r="E15" s="44" t="n">
         <v>443</v>
       </c>
-      <c r="F15" s="44" t="n">
+      <c r="F15" s="45" t="n">
         <v>50</v>
       </c>
-      <c r="G15" s="53" t="n">
+      <c r="G15" s="46" t="n">
         <f aca="false">IF(E15&gt;0,F15*E15/100,F15*100/ABS(E15))</f>
         <v>221.5</v>
       </c>
-      <c r="H15" s="53" t="n">
+      <c r="H15" s="46" t="n">
         <f aca="false">F15+G15</f>
         <v>271.5</v>
       </c>
-      <c r="I15" s="57" t="s">
-        <v>101</v>
-      </c>
-      <c r="J15" s="53" t="n">
+      <c r="I15" s="50" t="s">
+        <v>94</v>
+      </c>
+      <c r="J15" s="46" t="n">
         <f aca="false">IF(I15="Win",F15+G15,IF(I15="Push",F15,IF(I15="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K15" s="55" t="n">
+      <c r="K15" s="48" t="n">
         <f aca="false">IF(I15="Pending",0,J15-F15)</f>
         <v>-50</v>
       </c>
-      <c r="L15" s="56" t="s">
-        <v>121</v>
+      <c r="L15" s="49" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="58"/>
-      <c r="B16" s="59" t="s">
-        <v>44</v>
-      </c>
-      <c r="C16" s="58"/>
-      <c r="D16" s="58"/>
-      <c r="E16" s="58"/>
-      <c r="F16" s="39" t="n">
+      <c r="A16" s="51"/>
+      <c r="B16" s="52" t="s">
+        <v>37</v>
+      </c>
+      <c r="C16" s="51"/>
+      <c r="D16" s="51"/>
+      <c r="E16" s="51"/>
+      <c r="F16" s="53" t="n">
         <f aca="false">SUM(F7:F15)</f>
         <v>1050</v>
       </c>
-      <c r="G16" s="40" t="n">
+      <c r="G16" s="54" t="n">
         <f aca="false">SUM(G7:G15)</f>
         <v>830.481932464331</v>
       </c>
-      <c r="H16" s="40" t="n">
+      <c r="H16" s="54" t="n">
         <f aca="false">SUM(H7:H15)</f>
         <v>1880.48193246433</v>
       </c>
-      <c r="I16" s="58"/>
-      <c r="J16" s="40" t="n">
+      <c r="I16" s="51"/>
+      <c r="J16" s="54" t="n">
         <f aca="false">SUM(J7:J15)</f>
         <v>1215.1103728313</v>
       </c>
-      <c r="K16" s="41" t="n">
+      <c r="K16" s="55" t="n">
         <f aca="false">SUM(K7:K15)</f>
         <v>165.110372831303</v>
       </c>
-      <c r="L16" s="58"/>
+      <c r="L16" s="51"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="4" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="50" t="s">
-        <v>123</v>
-      </c>
-      <c r="C19" s="60" t="n">
+      <c r="B19" s="42" t="s">
+        <v>116</v>
+      </c>
+      <c r="C19" s="56" t="n">
         <f aca="false">COUNTIF(I7:I15,"Win")</f>
         <v>6</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="50" t="s">
-        <v>124</v>
-      </c>
-      <c r="C20" s="60" t="n">
+      <c r="B20" s="42" t="s">
+        <v>117</v>
+      </c>
+      <c r="C20" s="56" t="n">
         <f aca="false">COUNTIF(I7:I15,"Loss")</f>
         <v>3</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="50" t="s">
-        <v>125</v>
-      </c>
-      <c r="C21" s="60" t="n">
+      <c r="B21" s="42" t="s">
+        <v>118</v>
+      </c>
+      <c r="C21" s="56" t="n">
         <f aca="false">COUNTIF(I7:I15,"Push")</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="50" t="s">
-        <v>126</v>
-      </c>
-      <c r="C22" s="60" t="n">
+      <c r="B22" s="42" t="s">
+        <v>119</v>
+      </c>
+      <c r="C22" s="56" t="n">
         <f aca="false">COUNTIF(I7:I15,"Pending")</f>
         <v>0</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="50" t="s">
-        <v>127</v>
-      </c>
-      <c r="C23" s="61" t="n">
+      <c r="B23" s="42" t="s">
+        <v>120</v>
+      </c>
+      <c r="C23" s="57" t="n">
         <f aca="false">IF(COUNTIF(I7:I15,"Win")+COUNTIF(I7:I15,"Loss")=0,"—",COUNTIF(I7:I15,"Win")/(COUNTIF(I7:I15,"Win")+COUNTIF(I7:I15,"Loss")))</f>
         <v>0.666666666666667</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="50" t="s">
-        <v>128</v>
-      </c>
-      <c r="C24" s="62" t="n">
+      <c r="B24" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="C24" s="58" t="n">
         <f aca="false">SUM(F7:F15)</f>
         <v>1050</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="50" t="s">
-        <v>129</v>
-      </c>
-      <c r="C25" s="53" t="n">
+      <c r="B25" s="42" t="s">
+        <v>122</v>
+      </c>
+      <c r="C25" s="46" t="n">
         <f aca="false">SUM(J7:J15)</f>
         <v>1215.1103728313</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="50" t="s">
-        <v>130</v>
-      </c>
-      <c r="C26" s="55" t="n">
+      <c r="B26" s="42" t="s">
+        <v>123</v>
+      </c>
+      <c r="C26" s="48" t="n">
         <f aca="false">SUM(K7:K15)</f>
         <v>165.110372831303</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="50" t="s">
-        <v>131</v>
-      </c>
-      <c r="C27" s="61" t="n">
+      <c r="B27" s="42" t="s">
+        <v>124</v>
+      </c>
+      <c r="C27" s="57" t="n">
         <f aca="false">IF(SUM(F7:F15)=0,"—",SUM(K7:K15)/SUM(F7:F15))</f>
         <v>0.157247974125051</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="50" t="s">
-        <v>132</v>
-      </c>
-      <c r="C28" s="53" t="n">
+      <c r="B28" s="42" t="s">
+        <v>125</v>
+      </c>
+      <c r="C28" s="46" t="n">
         <f aca="false">SUM(H7:H15)</f>
         <v>1880.48193246433</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B31" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="C31" s="14" t="s">
+        <v>128</v>
+      </c>
+      <c r="D31" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="E31" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="F31" s="14" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="B32" s="42" t="s">
+        <v>132</v>
+      </c>
+      <c r="C32" s="49" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="31" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="B31" s="12" t="s">
+      <c r="D32" s="59" t="s">
         <v>134</v>
       </c>
-      <c r="C31" s="12" t="s">
+      <c r="E32" s="60" t="s">
         <v>135</v>
       </c>
-      <c r="D31" s="12" t="s">
+      <c r="F32" s="60" t="s">
         <v>136</v>
       </c>
-      <c r="E31" s="12" t="s">
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="36" t="n">
+        <v>2</v>
+      </c>
+      <c r="B33" s="42" t="s">
         <v>137</v>
       </c>
-      <c r="F31" s="12" t="s">
+      <c r="C33" s="49" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="49" t="n">
-        <v>1</v>
-      </c>
-      <c r="B32" s="50" t="s">
+      <c r="D33" s="59" t="s">
         <v>139</v>
       </c>
-      <c r="C32" s="56" t="s">
+      <c r="E33" s="60" t="s">
         <v>140</v>
       </c>
-      <c r="D32" s="43" t="s">
+      <c r="F33" s="60" t="s">
         <v>141</v>
       </c>
-      <c r="E32" s="63" t="s">
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="36" t="n">
+        <v>3</v>
+      </c>
+      <c r="B34" s="42" t="s">
         <v>142</v>
       </c>
-      <c r="F32" s="63" t="s">
+      <c r="C34" s="49" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="49" t="n">
-        <v>2</v>
-      </c>
-      <c r="B33" s="50" t="s">
+      <c r="D34" s="59" t="s">
         <v>144</v>
       </c>
-      <c r="C33" s="56" t="s">
+      <c r="E34" s="60" t="s">
         <v>145</v>
       </c>
-      <c r="D33" s="43" t="s">
+      <c r="F34" s="60" t="s">
         <v>146</v>
       </c>
-      <c r="E33" s="63" t="s">
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="36" t="n">
+        <v>4</v>
+      </c>
+      <c r="B35" s="42" t="s">
         <v>147</v>
       </c>
-      <c r="F33" s="63" t="s">
+      <c r="C35" s="49" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="49" t="n">
-        <v>3</v>
-      </c>
-      <c r="B34" s="50" t="s">
+      <c r="D35" s="59" t="s">
         <v>149</v>
       </c>
-      <c r="C34" s="56" t="s">
+      <c r="E35" s="60" t="s">
         <v>150</v>
       </c>
-      <c r="D34" s="43" t="s">
+      <c r="F35" s="60" t="s">
         <v>151</v>
       </c>
-      <c r="E34" s="63" t="s">
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="36" t="n">
+        <v>5</v>
+      </c>
+      <c r="B36" s="42" t="s">
         <v>152</v>
       </c>
-      <c r="F34" s="63" t="s">
+      <c r="C36" s="49" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="49" t="n">
-        <v>4</v>
-      </c>
-      <c r="B35" s="50" t="s">
+      <c r="D36" s="59" t="s">
         <v>154</v>
       </c>
-      <c r="C35" s="56" t="s">
+      <c r="E36" s="60" t="s">
         <v>155</v>
       </c>
-      <c r="D35" s="43" t="s">
+      <c r="F36" s="60" t="s">
         <v>156</v>
       </c>
-      <c r="E35" s="63" t="s">
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="36" t="n">
+        <v>6</v>
+      </c>
+      <c r="B37" s="42" t="s">
         <v>157</v>
       </c>
-      <c r="F35" s="63" t="s">
+      <c r="C37" s="49" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="49" t="n">
-        <v>5</v>
-      </c>
-      <c r="B36" s="50" t="s">
+      <c r="D37" s="59" t="s">
+        <v>45</v>
+      </c>
+      <c r="E37" s="60" t="s">
         <v>159</v>
       </c>
-      <c r="C36" s="56" t="s">
+      <c r="F37" s="60" t="s">
         <v>160</v>
       </c>
-      <c r="D36" s="43" t="s">
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="61" t="s">
         <v>161</v>
       </c>
-      <c r="E36" s="63" t="s">
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="61" t="s">
         <v>162</v>
       </c>
-      <c r="F36" s="63" t="s">
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="61" t="s">
         <v>163</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="49" t="n">
-        <v>6</v>
-      </c>
-      <c r="B37" s="50" t="s">
-        <v>164</v>
-      </c>
-      <c r="C37" s="56" t="s">
-        <v>165</v>
-      </c>
-      <c r="D37" s="43" t="s">
-        <v>52</v>
-      </c>
-      <c r="E37" s="63" t="s">
-        <v>166</v>
-      </c>
-      <c r="F37" s="63" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="46" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="46" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="46" t="s">
-        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -3621,578 +3950,578 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="47" t="s">
-        <v>171</v>
-      </c>
-      <c r="H1" s="64" t="s">
-        <v>172</v>
+      <c r="A1" s="40" t="s">
+        <v>164</v>
+      </c>
+      <c r="H1" s="62" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>168</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="F6" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="G6" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H6" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="I6" s="14" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="12" t="s">
+      <c r="J6" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="C6" s="12" t="s">
-        <v>175</v>
-      </c>
-      <c r="D6" s="12" t="s">
+      <c r="K6" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="L6" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="E6" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="F6" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="G6" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="H6" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="I6" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="J6" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="K6" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="L6" s="12" t="s">
-        <v>89</v>
-      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="49" t="n">
+      <c r="A7" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="50" t="s">
-        <v>176</v>
-      </c>
-      <c r="C7" s="51" t="s">
-        <v>177</v>
-      </c>
-      <c r="D7" s="49" t="s">
-        <v>178</v>
-      </c>
-      <c r="E7" s="52" t="n">
+      <c r="B7" s="42" t="s">
+        <v>169</v>
+      </c>
+      <c r="C7" s="43" t="s">
+        <v>170</v>
+      </c>
+      <c r="D7" s="36" t="s">
+        <v>171</v>
+      </c>
+      <c r="E7" s="44" t="n">
         <v>-144</v>
       </c>
-      <c r="F7" s="44" t="n">
+      <c r="F7" s="45" t="n">
         <v>300</v>
       </c>
-      <c r="G7" s="53" t="n">
+      <c r="G7" s="46" t="n">
         <f aca="false">IF(E7&gt;0,F7*E7/100,F7*100/ABS(E7))</f>
         <v>208.333333333333</v>
       </c>
-      <c r="H7" s="53" t="n">
+      <c r="H7" s="46" t="n">
         <f aca="false">F7+G7</f>
         <v>508.333333333333</v>
       </c>
-      <c r="I7" s="65" t="s">
-        <v>126</v>
-      </c>
-      <c r="J7" s="53" t="n">
+      <c r="I7" s="63" t="s">
+        <v>119</v>
+      </c>
+      <c r="J7" s="46" t="n">
         <f aca="false">IF(I7="Win",F7+G7,IF(I7="Push",F7,IF(I7="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K7" s="55" t="n">
+      <c r="K7" s="48" t="n">
         <f aca="false">IF(I7="Pending",0,J7-F7)</f>
         <v>0</v>
       </c>
-      <c r="L7" s="56" t="s">
-        <v>179</v>
+      <c r="L7" s="49" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="49" t="n">
+      <c r="A8" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="50" t="s">
-        <v>180</v>
-      </c>
-      <c r="C8" s="51" t="s">
-        <v>181</v>
-      </c>
-      <c r="D8" s="49" t="s">
-        <v>182</v>
-      </c>
-      <c r="E8" s="52" t="n">
+      <c r="B8" s="42" t="s">
+        <v>173</v>
+      </c>
+      <c r="C8" s="43" t="s">
+        <v>174</v>
+      </c>
+      <c r="D8" s="36" t="s">
+        <v>175</v>
+      </c>
+      <c r="E8" s="44" t="n">
         <v>-122</v>
       </c>
-      <c r="F8" s="44" t="n">
+      <c r="F8" s="45" t="n">
         <v>120</v>
       </c>
-      <c r="G8" s="53" t="n">
+      <c r="G8" s="46" t="n">
         <f aca="false">IF(E8&gt;0,F8*E8/100,F8*100/ABS(E8))</f>
         <v>98.3606557377049</v>
       </c>
-      <c r="H8" s="53" t="n">
+      <c r="H8" s="46" t="n">
         <f aca="false">F8+G8</f>
         <v>218.360655737705</v>
       </c>
-      <c r="I8" s="65" t="s">
-        <v>126</v>
-      </c>
-      <c r="J8" s="53" t="n">
+      <c r="I8" s="63" t="s">
+        <v>119</v>
+      </c>
+      <c r="J8" s="46" t="n">
         <f aca="false">IF(I8="Win",F8+G8,IF(I8="Push",F8,IF(I8="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K8" s="55" t="n">
+      <c r="K8" s="48" t="n">
         <f aca="false">IF(I8="Pending",0,J8-F8)</f>
         <v>0</v>
       </c>
-      <c r="L8" s="56" t="s">
-        <v>183</v>
+      <c r="L8" s="49" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="49" t="n">
+      <c r="A9" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="B9" s="50" t="s">
-        <v>184</v>
-      </c>
-      <c r="C9" s="51" t="s">
-        <v>185</v>
-      </c>
-      <c r="D9" s="49" t="s">
-        <v>186</v>
-      </c>
-      <c r="E9" s="52" t="n">
+      <c r="B9" s="42" t="s">
+        <v>177</v>
+      </c>
+      <c r="C9" s="43" t="s">
+        <v>178</v>
+      </c>
+      <c r="D9" s="36" t="s">
+        <v>179</v>
+      </c>
+      <c r="E9" s="44" t="n">
         <v>175</v>
       </c>
-      <c r="F9" s="44" t="n">
+      <c r="F9" s="45" t="n">
         <v>150</v>
       </c>
-      <c r="G9" s="53" t="n">
+      <c r="G9" s="46" t="n">
         <f aca="false">IF(E9&gt;0,F9*E9/100,F9*100/ABS(E9))</f>
         <v>262.5</v>
       </c>
-      <c r="H9" s="53" t="n">
+      <c r="H9" s="46" t="n">
         <f aca="false">F9+G9</f>
         <v>412.5</v>
       </c>
-      <c r="I9" s="65" t="s">
-        <v>126</v>
-      </c>
-      <c r="J9" s="53" t="n">
+      <c r="I9" s="63" t="s">
+        <v>119</v>
+      </c>
+      <c r="J9" s="46" t="n">
         <f aca="false">IF(I9="Win",F9+G9,IF(I9="Push",F9,IF(I9="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K9" s="55" t="n">
+      <c r="K9" s="48" t="n">
         <f aca="false">IF(I9="Pending",0,J9-F9)</f>
         <v>0</v>
       </c>
-      <c r="L9" s="56" t="s">
-        <v>187</v>
+      <c r="L9" s="49" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="49" t="n">
+      <c r="A10" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="B10" s="50" t="s">
-        <v>188</v>
-      </c>
-      <c r="C10" s="51" t="s">
-        <v>189</v>
-      </c>
-      <c r="D10" s="49" t="s">
-        <v>186</v>
-      </c>
-      <c r="E10" s="52" t="n">
+      <c r="B10" s="42" t="s">
+        <v>181</v>
+      </c>
+      <c r="C10" s="43" t="s">
+        <v>182</v>
+      </c>
+      <c r="D10" s="36" t="s">
+        <v>179</v>
+      </c>
+      <c r="E10" s="44" t="n">
         <v>205</v>
       </c>
-      <c r="F10" s="44" t="n">
+      <c r="F10" s="45" t="n">
         <v>80</v>
       </c>
-      <c r="G10" s="53" t="n">
+      <c r="G10" s="46" t="n">
         <f aca="false">IF(E10&gt;0,F10*E10/100,F10*100/ABS(E10))</f>
         <v>164</v>
       </c>
-      <c r="H10" s="53" t="n">
+      <c r="H10" s="46" t="n">
         <f aca="false">F10+G10</f>
         <v>244</v>
       </c>
-      <c r="I10" s="65" t="s">
-        <v>126</v>
-      </c>
-      <c r="J10" s="53" t="n">
+      <c r="I10" s="63" t="s">
+        <v>119</v>
+      </c>
+      <c r="J10" s="46" t="n">
         <f aca="false">IF(I10="Win",F10+G10,IF(I10="Push",F10,IF(I10="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K10" s="55" t="n">
+      <c r="K10" s="48" t="n">
         <f aca="false">IF(I10="Pending",0,J10-F10)</f>
         <v>0</v>
       </c>
-      <c r="L10" s="56" t="s">
-        <v>190</v>
+      <c r="L10" s="49" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="49" t="n">
+      <c r="A11" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="50" t="s">
-        <v>191</v>
-      </c>
-      <c r="C11" s="51" t="s">
-        <v>192</v>
-      </c>
-      <c r="D11" s="49" t="s">
-        <v>193</v>
-      </c>
-      <c r="E11" s="52" t="n">
+      <c r="B11" s="42" t="s">
+        <v>184</v>
+      </c>
+      <c r="C11" s="43" t="s">
+        <v>185</v>
+      </c>
+      <c r="D11" s="36" t="s">
+        <v>186</v>
+      </c>
+      <c r="E11" s="44" t="n">
         <v>160</v>
       </c>
-      <c r="F11" s="44" t="n">
+      <c r="F11" s="45" t="n">
         <v>250</v>
       </c>
-      <c r="G11" s="53" t="n">
+      <c r="G11" s="46" t="n">
         <f aca="false">IF(E11&gt;0,F11*E11/100,F11*100/ABS(E11))</f>
         <v>400</v>
       </c>
-      <c r="H11" s="53" t="n">
+      <c r="H11" s="46" t="n">
         <f aca="false">F11+G11</f>
         <v>650</v>
       </c>
-      <c r="I11" s="65" t="s">
-        <v>126</v>
-      </c>
-      <c r="J11" s="53" t="n">
+      <c r="I11" s="63" t="s">
+        <v>119</v>
+      </c>
+      <c r="J11" s="46" t="n">
         <f aca="false">IF(I11="Win",F11+G11,IF(I11="Push",F11,IF(I11="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K11" s="55" t="n">
+      <c r="K11" s="48" t="n">
         <f aca="false">IF(I11="Pending",0,J11-F11)</f>
         <v>0</v>
       </c>
-      <c r="L11" s="56" t="s">
-        <v>194</v>
+      <c r="L11" s="49" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="49" t="n">
+      <c r="A12" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="50" t="s">
-        <v>195</v>
-      </c>
-      <c r="C12" s="51" t="s">
-        <v>196</v>
-      </c>
-      <c r="D12" s="49" t="s">
-        <v>193</v>
-      </c>
-      <c r="E12" s="52" t="n">
+      <c r="B12" s="42" t="s">
+        <v>188</v>
+      </c>
+      <c r="C12" s="43" t="s">
+        <v>189</v>
+      </c>
+      <c r="D12" s="36" t="s">
+        <v>186</v>
+      </c>
+      <c r="E12" s="44" t="n">
         <v>500</v>
       </c>
-      <c r="F12" s="44" t="n">
+      <c r="F12" s="45" t="n">
         <v>50</v>
       </c>
-      <c r="G12" s="53" t="n">
+      <c r="G12" s="46" t="n">
         <f aca="false">IF(E12&gt;0,F12*E12/100,F12*100/ABS(E12))</f>
         <v>250</v>
       </c>
-      <c r="H12" s="53" t="n">
+      <c r="H12" s="46" t="n">
         <f aca="false">F12+G12</f>
         <v>300</v>
       </c>
-      <c r="I12" s="65" t="s">
-        <v>126</v>
-      </c>
-      <c r="J12" s="53" t="n">
+      <c r="I12" s="63" t="s">
+        <v>119</v>
+      </c>
+      <c r="J12" s="46" t="n">
         <f aca="false">IF(I12="Win",F12+G12,IF(I12="Push",F12,IF(I12="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K12" s="55" t="n">
+      <c r="K12" s="48" t="n">
         <f aca="false">IF(I12="Pending",0,J12-F12)</f>
         <v>0</v>
       </c>
-      <c r="L12" s="56" t="s">
-        <v>197</v>
+      <c r="L12" s="49" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="49" t="n">
+      <c r="A13" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="50" t="s">
-        <v>198</v>
-      </c>
-      <c r="C13" s="51" t="s">
-        <v>199</v>
-      </c>
-      <c r="D13" s="49" t="s">
-        <v>120</v>
-      </c>
-      <c r="E13" s="52" t="n">
+      <c r="B13" s="42" t="s">
+        <v>191</v>
+      </c>
+      <c r="C13" s="43" t="s">
+        <v>192</v>
+      </c>
+      <c r="D13" s="36" t="s">
+        <v>113</v>
+      </c>
+      <c r="E13" s="44" t="n">
         <v>179</v>
       </c>
-      <c r="F13" s="44" t="n">
+      <c r="F13" s="45" t="n">
         <v>50</v>
       </c>
-      <c r="G13" s="53" t="n">
+      <c r="G13" s="46" t="n">
         <f aca="false">IF(E13&gt;0,F13*E13/100,F13*100/ABS(E13))</f>
         <v>89.5</v>
       </c>
-      <c r="H13" s="53" t="n">
+      <c r="H13" s="46" t="n">
         <f aca="false">F13+G13</f>
         <v>139.5</v>
       </c>
-      <c r="I13" s="65" t="s">
-        <v>126</v>
-      </c>
-      <c r="J13" s="53" t="n">
+      <c r="I13" s="63" t="s">
+        <v>119</v>
+      </c>
+      <c r="J13" s="46" t="n">
         <f aca="false">IF(I13="Win",F13+G13,IF(I13="Push",F13,IF(I13="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K13" s="55" t="n">
+      <c r="K13" s="48" t="n">
         <f aca="false">IF(I13="Pending",0,J13-F13)</f>
         <v>0</v>
       </c>
-      <c r="L13" s="56" t="s">
-        <v>200</v>
+      <c r="L13" s="49" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="58"/>
-      <c r="B14" s="59" t="s">
-        <v>44</v>
-      </c>
-      <c r="C14" s="58"/>
-      <c r="D14" s="58"/>
-      <c r="E14" s="58"/>
-      <c r="F14" s="39" t="n">
+      <c r="A14" s="51"/>
+      <c r="B14" s="52" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" s="51"/>
+      <c r="D14" s="51"/>
+      <c r="E14" s="51"/>
+      <c r="F14" s="53" t="n">
         <f aca="false">SUM(F7:F13)</f>
         <v>1000</v>
       </c>
-      <c r="G14" s="40" t="n">
+      <c r="G14" s="54" t="n">
         <f aca="false">SUM(G7:G13)</f>
         <v>1472.69398907104</v>
       </c>
-      <c r="H14" s="40" t="n">
+      <c r="H14" s="54" t="n">
         <f aca="false">SUM(H7:H13)</f>
         <v>2472.69398907104</v>
       </c>
-      <c r="I14" s="58"/>
-      <c r="J14" s="40" t="n">
+      <c r="I14" s="51"/>
+      <c r="J14" s="54" t="n">
         <f aca="false">SUM(J7:J13)</f>
         <v>0</v>
       </c>
-      <c r="K14" s="41" t="n">
+      <c r="K14" s="55" t="n">
         <f aca="false">SUM(K7:K13)</f>
         <v>0</v>
       </c>
-      <c r="L14" s="58"/>
+      <c r="L14" s="51"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="4" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="50" t="s">
-        <v>123</v>
-      </c>
-      <c r="C17" s="60" t="n">
+      <c r="B17" s="42" t="s">
+        <v>116</v>
+      </c>
+      <c r="C17" s="56" t="n">
         <f aca="false">COUNTIF(I7:I13,"Win")</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="50" t="s">
-        <v>124</v>
-      </c>
-      <c r="C18" s="60" t="n">
+      <c r="B18" s="42" t="s">
+        <v>117</v>
+      </c>
+      <c r="C18" s="56" t="n">
         <f aca="false">COUNTIF(I7:I13,"Loss")</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="50" t="s">
-        <v>125</v>
-      </c>
-      <c r="C19" s="60" t="n">
+      <c r="B19" s="42" t="s">
+        <v>118</v>
+      </c>
+      <c r="C19" s="56" t="n">
         <f aca="false">COUNTIF(I7:I13,"Push")</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="50" t="s">
-        <v>126</v>
-      </c>
-      <c r="C20" s="60" t="n">
+      <c r="B20" s="42" t="s">
+        <v>119</v>
+      </c>
+      <c r="C20" s="56" t="n">
         <f aca="false">COUNTIF(I7:I13,"Pending")</f>
         <v>7</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="50" t="s">
-        <v>127</v>
-      </c>
-      <c r="C21" s="61" t="str">
+      <c r="B21" s="42" t="s">
+        <v>120</v>
+      </c>
+      <c r="C21" s="57" t="str">
         <f aca="false">IF(COUNTIF(I7:I13,"Win")+COUNTIF(I7:I13,"Loss")=0,"—",COUNTIF(I7:I13,"Win")/(COUNTIF(I7:I13,"Win")+COUNTIF(I7:I13,"Loss")))</f>
         <v>—</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="50" t="s">
-        <v>128</v>
-      </c>
-      <c r="C22" s="62" t="n">
+      <c r="B22" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="C22" s="58" t="n">
         <f aca="false">SUM(F7:F13)</f>
         <v>1000</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="50" t="s">
-        <v>129</v>
-      </c>
-      <c r="C23" s="53" t="n">
+      <c r="B23" s="42" t="s">
+        <v>122</v>
+      </c>
+      <c r="C23" s="46" t="n">
         <f aca="false">SUM(J7:J13)</f>
         <v>0</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="50" t="s">
-        <v>130</v>
-      </c>
-      <c r="C24" s="55" t="n">
+      <c r="B24" s="42" t="s">
+        <v>123</v>
+      </c>
+      <c r="C24" s="48" t="n">
         <f aca="false">SUM(K7:K13)</f>
         <v>0</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="50" t="s">
-        <v>131</v>
-      </c>
-      <c r="C25" s="61" t="n">
+      <c r="B25" s="42" t="s">
+        <v>124</v>
+      </c>
+      <c r="C25" s="57" t="n">
         <f aca="false">IF(SUM(F7:F13)=0,"—",SUM(K7:K13)/SUM(F7:F13))</f>
         <v>0</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="50" t="s">
-        <v>201</v>
-      </c>
-      <c r="C26" s="62" t="n">
+      <c r="B26" s="42" t="s">
+        <v>194</v>
+      </c>
+      <c r="C26" s="58" t="n">
         <f aca="false">929</f>
         <v>929</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B29" s="14" t="s">
+        <v>196</v>
+      </c>
+      <c r="C29" s="14" t="s">
+        <v>128</v>
+      </c>
+      <c r="D29" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="E29" s="14" t="s">
+        <v>197</v>
+      </c>
+      <c r="F29" s="14" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="B30" s="42" t="s">
+        <v>198</v>
+      </c>
+      <c r="C30" s="49" t="s">
+        <v>199</v>
+      </c>
+      <c r="D30" s="59" t="s">
+        <v>200</v>
+      </c>
+      <c r="E30" s="63"/>
+      <c r="F30" s="63"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="36" t="n">
+        <v>2</v>
+      </c>
+      <c r="B31" s="42" t="s">
+        <v>201</v>
+      </c>
+      <c r="C31" s="49" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="29" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="B29" s="12" t="s">
+      <c r="D31" s="59" t="s">
         <v>203</v>
       </c>
-      <c r="C29" s="12" t="s">
-        <v>135</v>
-      </c>
-      <c r="D29" s="12" t="s">
-        <v>136</v>
-      </c>
-      <c r="E29" s="12" t="s">
+      <c r="E31" s="63"/>
+      <c r="F31" s="63"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="36" t="n">
+        <v>3</v>
+      </c>
+      <c r="B32" s="42" t="s">
         <v>204</v>
       </c>
-      <c r="F29" s="12" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="49" t="n">
-        <v>1</v>
-      </c>
-      <c r="B30" s="50" t="s">
+      <c r="C32" s="49" t="s">
         <v>205</v>
       </c>
-      <c r="C30" s="56" t="s">
+      <c r="D32" s="59" t="s">
         <v>206</v>
       </c>
-      <c r="D30" s="43" t="s">
+      <c r="E32" s="63"/>
+      <c r="F32" s="63"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="36" t="n">
+        <v>4</v>
+      </c>
+      <c r="B33" s="42" t="s">
         <v>207</v>
       </c>
-      <c r="E30" s="65"/>
-      <c r="F30" s="65"/>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="49" t="n">
-        <v>2</v>
-      </c>
-      <c r="B31" s="50" t="s">
+      <c r="C33" s="49" t="s">
         <v>208</v>
       </c>
-      <c r="C31" s="56" t="s">
+      <c r="D33" s="59" t="s">
         <v>209</v>
       </c>
-      <c r="D31" s="43" t="s">
+      <c r="E33" s="63"/>
+      <c r="F33" s="63"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="61" t="s">
         <v>210</v>
-      </c>
-      <c r="E31" s="65"/>
-      <c r="F31" s="65"/>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="49" t="n">
-        <v>3</v>
-      </c>
-      <c r="B32" s="50" t="s">
-        <v>211</v>
-      </c>
-      <c r="C32" s="56" t="s">
-        <v>212</v>
-      </c>
-      <c r="D32" s="43" t="s">
-        <v>213</v>
-      </c>
-      <c r="E32" s="65"/>
-      <c r="F32" s="65"/>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="49" t="n">
-        <v>4</v>
-      </c>
-      <c r="B33" s="50" t="s">
-        <v>214</v>
-      </c>
-      <c r="C33" s="56" t="s">
-        <v>215</v>
-      </c>
-      <c r="D33" s="43" t="s">
-        <v>216</v>
-      </c>
-      <c r="E33" s="65"/>
-      <c r="F33" s="65"/>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="46" t="s">
-        <v>217</v>
       </c>
     </row>
   </sheetData>
@@ -4250,733 +4579,733 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="47" t="s">
-        <v>218</v>
-      </c>
-      <c r="H1" s="48" t="s">
-        <v>219</v>
+      <c r="A1" s="40" t="s">
+        <v>211</v>
+      </c>
+      <c r="H1" s="41" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>215</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="F6" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="G6" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H6" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="I6" s="14" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="12" t="s">
+      <c r="J6" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="C6" s="12" t="s">
-        <v>222</v>
-      </c>
-      <c r="D6" s="12" t="s">
+      <c r="K6" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="L6" s="14" t="s">
+        <v>216</v>
+      </c>
+      <c r="M6" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="E6" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="F6" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="G6" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="H6" s="12" t="s">
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="42" t="s">
+        <v>217</v>
+      </c>
+      <c r="C7" s="43" t="s">
+        <v>218</v>
+      </c>
+      <c r="D7" s="36" t="s">
         <v>85</v>
       </c>
-      <c r="I6" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="J6" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="K6" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="L6" s="12" t="s">
-        <v>223</v>
-      </c>
-      <c r="M6" s="12" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="49" t="n">
-        <v>1</v>
-      </c>
-      <c r="B7" s="50" t="s">
-        <v>224</v>
-      </c>
-      <c r="C7" s="51" t="s">
-        <v>225</v>
-      </c>
-      <c r="D7" s="49" t="s">
-        <v>92</v>
-      </c>
-      <c r="E7" s="52" t="n">
+      <c r="E7" s="44" t="n">
         <v>-155</v>
       </c>
-      <c r="F7" s="44" t="n">
+      <c r="F7" s="45" t="n">
         <v>200</v>
       </c>
-      <c r="G7" s="53" t="n">
+      <c r="G7" s="46" t="n">
         <f aca="false">IF(E7&gt;0,F7*E7/100,F7*100/ABS(E7))</f>
         <v>129.032258064516</v>
       </c>
-      <c r="H7" s="53" t="n">
+      <c r="H7" s="46" t="n">
         <f aca="false">F7+G7</f>
         <v>329.032258064516</v>
       </c>
-      <c r="I7" s="54" t="s">
-        <v>93</v>
-      </c>
-      <c r="J7" s="53" t="n">
+      <c r="I7" s="47" t="s">
+        <v>86</v>
+      </c>
+      <c r="J7" s="46" t="n">
         <f aca="false">IF(I7="Win",F7+G7,IF(I7="Push",F7,IF(I7="Loss",0,0)))</f>
         <v>329.032258064516</v>
       </c>
-      <c r="K7" s="55" t="n">
+      <c r="K7" s="48" t="n">
         <f aca="false">IF(I7="Pending",0,J7-F7)</f>
         <v>129.032258064516</v>
       </c>
-      <c r="L7" s="66" t="n">
+      <c r="L7" s="64" t="n">
         <v>0.62</v>
       </c>
-      <c r="M7" s="56" t="s">
-        <v>226</v>
+      <c r="M7" s="49" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="49" t="n">
+      <c r="A8" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="50" t="s">
-        <v>227</v>
-      </c>
-      <c r="C8" s="51" t="s">
-        <v>228</v>
-      </c>
-      <c r="D8" s="49" t="s">
-        <v>92</v>
-      </c>
-      <c r="E8" s="52" t="n">
+      <c r="B8" s="42" t="s">
+        <v>220</v>
+      </c>
+      <c r="C8" s="43" t="s">
+        <v>221</v>
+      </c>
+      <c r="D8" s="36" t="s">
+        <v>85</v>
+      </c>
+      <c r="E8" s="44" t="n">
         <v>-104</v>
       </c>
-      <c r="F8" s="44" t="n">
+      <c r="F8" s="45" t="n">
         <v>150</v>
       </c>
-      <c r="G8" s="53" t="n">
+      <c r="G8" s="46" t="n">
         <f aca="false">IF(E8&gt;0,F8*E8/100,F8*100/ABS(E8))</f>
         <v>144.230769230769</v>
       </c>
-      <c r="H8" s="53" t="n">
+      <c r="H8" s="46" t="n">
         <f aca="false">F8+G8</f>
         <v>294.230769230769</v>
       </c>
-      <c r="I8" s="57" t="s">
-        <v>101</v>
-      </c>
-      <c r="J8" s="53" t="n">
+      <c r="I8" s="50" t="s">
+        <v>94</v>
+      </c>
+      <c r="J8" s="46" t="n">
         <f aca="false">IF(I8="Win",F8+G8,IF(I8="Push",F8,IF(I8="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K8" s="55" t="n">
+      <c r="K8" s="48" t="n">
         <f aca="false">IF(I8="Pending",0,J8-F8)</f>
         <v>-150</v>
       </c>
-      <c r="L8" s="66" t="n">
+      <c r="L8" s="64" t="n">
         <v>0.54</v>
       </c>
-      <c r="M8" s="56" t="s">
-        <v>229</v>
+      <c r="M8" s="49" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="49" t="n">
+      <c r="A9" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="B9" s="50" t="s">
-        <v>230</v>
-      </c>
-      <c r="C9" s="51" t="s">
-        <v>231</v>
-      </c>
-      <c r="D9" s="49" t="s">
-        <v>92</v>
-      </c>
-      <c r="E9" s="52" t="n">
+      <c r="B9" s="42" t="s">
+        <v>223</v>
+      </c>
+      <c r="C9" s="43" t="s">
+        <v>224</v>
+      </c>
+      <c r="D9" s="36" t="s">
+        <v>85</v>
+      </c>
+      <c r="E9" s="44" t="n">
         <v>-115</v>
       </c>
-      <c r="F9" s="44" t="n">
+      <c r="F9" s="45" t="n">
         <v>150</v>
       </c>
-      <c r="G9" s="53" t="n">
+      <c r="G9" s="46" t="n">
         <f aca="false">IF(E9&gt;0,F9*E9/100,F9*100/ABS(E9))</f>
         <v>130.434782608696</v>
       </c>
-      <c r="H9" s="53" t="n">
+      <c r="H9" s="46" t="n">
         <f aca="false">F9+G9</f>
         <v>280.434782608696</v>
       </c>
-      <c r="I9" s="57" t="s">
-        <v>101</v>
-      </c>
-      <c r="J9" s="53" t="n">
+      <c r="I9" s="50" t="s">
+        <v>94</v>
+      </c>
+      <c r="J9" s="46" t="n">
         <f aca="false">IF(I9="Win",F9+G9,IF(I9="Push",F9,IF(I9="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K9" s="55" t="n">
+      <c r="K9" s="48" t="n">
         <f aca="false">IF(I9="Pending",0,J9-F9)</f>
         <v>-150</v>
       </c>
-      <c r="L9" s="66" t="n">
+      <c r="L9" s="64" t="n">
         <v>0.55</v>
       </c>
-      <c r="M9" s="56" t="s">
-        <v>232</v>
+      <c r="M9" s="49" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="49" t="n">
+      <c r="A10" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="B10" s="50" t="s">
-        <v>233</v>
-      </c>
-      <c r="C10" s="51" t="s">
-        <v>234</v>
-      </c>
-      <c r="D10" s="49" t="s">
-        <v>182</v>
-      </c>
-      <c r="E10" s="52" t="n">
+      <c r="B10" s="42" t="s">
+        <v>226</v>
+      </c>
+      <c r="C10" s="43" t="s">
+        <v>227</v>
+      </c>
+      <c r="D10" s="36" t="s">
+        <v>175</v>
+      </c>
+      <c r="E10" s="44" t="n">
         <v>-114</v>
       </c>
-      <c r="F10" s="44" t="n">
+      <c r="F10" s="45" t="n">
         <v>120</v>
       </c>
-      <c r="G10" s="53" t="n">
+      <c r="G10" s="46" t="n">
         <f aca="false">IF(E10&gt;0,F10*E10/100,F10*100/ABS(E10))</f>
         <v>105.263157894737</v>
       </c>
-      <c r="H10" s="53" t="n">
+      <c r="H10" s="46" t="n">
         <f aca="false">F10+G10</f>
         <v>225.263157894737</v>
       </c>
-      <c r="I10" s="57" t="s">
-        <v>101</v>
-      </c>
-      <c r="J10" s="53" t="n">
+      <c r="I10" s="50" t="s">
+        <v>94</v>
+      </c>
+      <c r="J10" s="46" t="n">
         <f aca="false">IF(I10="Win",F10+G10,IF(I10="Push",F10,IF(I10="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K10" s="55" t="n">
+      <c r="K10" s="48" t="n">
         <f aca="false">IF(I10="Pending",0,J10-F10)</f>
         <v>-120</v>
       </c>
-      <c r="L10" s="66" t="n">
+      <c r="L10" s="64" t="n">
         <v>0.55</v>
       </c>
-      <c r="M10" s="56" t="s">
-        <v>235</v>
+      <c r="M10" s="49" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="49" t="n">
+      <c r="A11" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="50" t="s">
-        <v>236</v>
-      </c>
-      <c r="C11" s="51" t="s">
-        <v>237</v>
-      </c>
-      <c r="D11" s="49" t="s">
-        <v>92</v>
-      </c>
-      <c r="E11" s="52" t="n">
+      <c r="B11" s="42" t="s">
+        <v>229</v>
+      </c>
+      <c r="C11" s="43" t="s">
+        <v>230</v>
+      </c>
+      <c r="D11" s="36" t="s">
+        <v>85</v>
+      </c>
+      <c r="E11" s="44" t="n">
         <v>104</v>
       </c>
-      <c r="F11" s="44" t="n">
+      <c r="F11" s="45" t="n">
         <v>130</v>
       </c>
-      <c r="G11" s="53" t="n">
+      <c r="G11" s="46" t="n">
         <f aca="false">IF(E11&gt;0,F11*E11/100,F11*100/ABS(E11))</f>
         <v>135.2</v>
       </c>
-      <c r="H11" s="53" t="n">
+      <c r="H11" s="46" t="n">
         <f aca="false">F11+G11</f>
         <v>265.2</v>
       </c>
-      <c r="I11" s="54" t="s">
-        <v>93</v>
-      </c>
-      <c r="J11" s="53" t="n">
+      <c r="I11" s="47" t="s">
+        <v>86</v>
+      </c>
+      <c r="J11" s="46" t="n">
         <f aca="false">IF(I11="Win",F11+G11,IF(I11="Push",F11,IF(I11="Loss",0,0)))</f>
         <v>265.2</v>
       </c>
-      <c r="K11" s="55" t="n">
+      <c r="K11" s="48" t="n">
         <f aca="false">IF(I11="Pending",0,J11-F11)</f>
         <v>135.2</v>
       </c>
-      <c r="L11" s="66" t="n">
+      <c r="L11" s="64" t="n">
         <v>0.52</v>
       </c>
-      <c r="M11" s="56" t="s">
-        <v>238</v>
+      <c r="M11" s="49" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="49" t="n">
+      <c r="A12" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="50" t="s">
-        <v>239</v>
-      </c>
-      <c r="C12" s="51" t="s">
-        <v>240</v>
-      </c>
-      <c r="D12" s="49" t="s">
-        <v>92</v>
-      </c>
-      <c r="E12" s="52" t="n">
+      <c r="B12" s="42" t="s">
+        <v>232</v>
+      </c>
+      <c r="C12" s="43" t="s">
+        <v>233</v>
+      </c>
+      <c r="D12" s="36" t="s">
+        <v>85</v>
+      </c>
+      <c r="E12" s="44" t="n">
         <v>108</v>
       </c>
-      <c r="F12" s="44" t="n">
+      <c r="F12" s="45" t="n">
         <v>100</v>
       </c>
-      <c r="G12" s="53" t="n">
+      <c r="G12" s="46" t="n">
         <f aca="false">IF(E12&gt;0,F12*E12/100,F12*100/ABS(E12))</f>
         <v>108</v>
       </c>
-      <c r="H12" s="53" t="n">
+      <c r="H12" s="46" t="n">
         <f aca="false">F12+G12</f>
         <v>208</v>
       </c>
-      <c r="I12" s="57" t="s">
-        <v>101</v>
-      </c>
-      <c r="J12" s="53" t="n">
+      <c r="I12" s="50" t="s">
+        <v>94</v>
+      </c>
+      <c r="J12" s="46" t="n">
         <f aca="false">IF(I12="Win",F12+G12,IF(I12="Push",F12,IF(I12="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K12" s="55" t="n">
+      <c r="K12" s="48" t="n">
         <f aca="false">IF(I12="Pending",0,J12-F12)</f>
         <v>-100</v>
       </c>
-      <c r="L12" s="66" t="n">
+      <c r="L12" s="64" t="n">
         <v>0.5</v>
       </c>
-      <c r="M12" s="56" t="s">
-        <v>241</v>
+      <c r="M12" s="49" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="49" t="n">
+      <c r="A13" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="50" t="s">
-        <v>242</v>
-      </c>
-      <c r="C13" s="51" t="s">
-        <v>243</v>
-      </c>
-      <c r="D13" s="49" t="s">
-        <v>92</v>
-      </c>
-      <c r="E13" s="52" t="n">
+      <c r="B13" s="42" t="s">
+        <v>235</v>
+      </c>
+      <c r="C13" s="43" t="s">
+        <v>236</v>
+      </c>
+      <c r="D13" s="36" t="s">
+        <v>85</v>
+      </c>
+      <c r="E13" s="44" t="n">
         <v>108</v>
       </c>
-      <c r="F13" s="44" t="n">
+      <c r="F13" s="45" t="n">
         <v>100</v>
       </c>
-      <c r="G13" s="53" t="n">
+      <c r="G13" s="46" t="n">
         <f aca="false">IF(E13&gt;0,F13*E13/100,F13*100/ABS(E13))</f>
         <v>108</v>
       </c>
-      <c r="H13" s="53" t="n">
+      <c r="H13" s="46" t="n">
         <f aca="false">F13+G13</f>
         <v>208</v>
       </c>
-      <c r="I13" s="54" t="s">
-        <v>93</v>
-      </c>
-      <c r="J13" s="53" t="n">
+      <c r="I13" s="47" t="s">
+        <v>86</v>
+      </c>
+      <c r="J13" s="46" t="n">
         <f aca="false">IF(I13="Win",F13+G13,IF(I13="Push",F13,IF(I13="Loss",0,0)))</f>
         <v>208</v>
       </c>
-      <c r="K13" s="55" t="n">
+      <c r="K13" s="48" t="n">
         <f aca="false">IF(I13="Pending",0,J13-F13)</f>
         <v>108</v>
       </c>
-      <c r="L13" s="66" t="n">
+      <c r="L13" s="64" t="n">
         <v>0.5</v>
       </c>
-      <c r="M13" s="56" t="s">
-        <v>244</v>
+      <c r="M13" s="49" t="s">
+        <v>237</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="49" t="n">
+      <c r="A14" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="B14" s="50" t="s">
-        <v>245</v>
-      </c>
-      <c r="C14" s="51" t="s">
-        <v>246</v>
-      </c>
-      <c r="D14" s="49" t="s">
-        <v>120</v>
-      </c>
-      <c r="E14" s="52" t="n">
+      <c r="B14" s="42" t="s">
+        <v>238</v>
+      </c>
+      <c r="C14" s="43" t="s">
+        <v>239</v>
+      </c>
+      <c r="D14" s="36" t="s">
+        <v>113</v>
+      </c>
+      <c r="E14" s="44" t="n">
         <v>732</v>
       </c>
-      <c r="F14" s="44" t="n">
+      <c r="F14" s="45" t="n">
         <v>50</v>
       </c>
-      <c r="G14" s="53" t="n">
+      <c r="G14" s="46" t="n">
         <f aca="false">IF(E14&gt;0,F14*E14/100,F14*100/ABS(E14))</f>
         <v>366</v>
       </c>
-      <c r="H14" s="53" t="n">
+      <c r="H14" s="46" t="n">
         <f aca="false">F14+G14</f>
         <v>416</v>
       </c>
-      <c r="I14" s="57" t="s">
-        <v>101</v>
-      </c>
-      <c r="J14" s="53" t="n">
+      <c r="I14" s="50" t="s">
+        <v>94</v>
+      </c>
+      <c r="J14" s="46" t="n">
         <f aca="false">IF(I14="Win",F14+G14,IF(I14="Push",F14,IF(I14="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K14" s="55" t="n">
+      <c r="K14" s="48" t="n">
         <f aca="false">IF(I14="Pending",0,J14-F14)</f>
         <v>-50</v>
       </c>
-      <c r="L14" s="66" t="n">
+      <c r="L14" s="64" t="n">
         <v>0.14</v>
       </c>
-      <c r="M14" s="56" t="s">
-        <v>247</v>
+      <c r="M14" s="49" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="58"/>
-      <c r="B15" s="59" t="s">
-        <v>44</v>
-      </c>
-      <c r="C15" s="58"/>
-      <c r="D15" s="58"/>
-      <c r="E15" s="58"/>
-      <c r="F15" s="39" t="n">
+      <c r="A15" s="51"/>
+      <c r="B15" s="52" t="s">
+        <v>37</v>
+      </c>
+      <c r="C15" s="51"/>
+      <c r="D15" s="51"/>
+      <c r="E15" s="51"/>
+      <c r="F15" s="53" t="n">
         <f aca="false">SUM(F7:F14)</f>
         <v>1000</v>
       </c>
-      <c r="G15" s="40" t="n">
+      <c r="G15" s="54" t="n">
         <f aca="false">SUM(G7:G14)</f>
         <v>1226.16096779872</v>
       </c>
-      <c r="H15" s="40" t="n">
+      <c r="H15" s="54" t="n">
         <f aca="false">SUM(H7:H14)</f>
         <v>2226.16096779872</v>
       </c>
-      <c r="I15" s="58"/>
-      <c r="J15" s="40" t="n">
+      <c r="I15" s="51"/>
+      <c r="J15" s="54" t="n">
         <f aca="false">SUM(J7:J14)</f>
         <v>802.232258064516</v>
       </c>
-      <c r="K15" s="41" t="n">
+      <c r="K15" s="55" t="n">
         <f aca="false">SUM(K7:K14)</f>
         <v>-197.767741935484</v>
       </c>
-      <c r="L15" s="67" t="n">
+      <c r="L15" s="65" t="n">
         <f aca="false">SUM(L7:L14)</f>
         <v>3.92</v>
       </c>
-      <c r="M15" s="58"/>
+      <c r="M15" s="51"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="4" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="50" t="s">
-        <v>123</v>
-      </c>
-      <c r="C18" s="60" t="n">
+      <c r="B18" s="42" t="s">
+        <v>116</v>
+      </c>
+      <c r="C18" s="56" t="n">
         <f aca="false">COUNTIF(I7:I14,"Win")</f>
         <v>3</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="50" t="s">
-        <v>124</v>
-      </c>
-      <c r="C19" s="60" t="n">
+      <c r="B19" s="42" t="s">
+        <v>117</v>
+      </c>
+      <c r="C19" s="56" t="n">
         <f aca="false">COUNTIF(I7:I14,"Loss")</f>
         <v>5</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="50" t="s">
-        <v>125</v>
-      </c>
-      <c r="C20" s="60" t="n">
+      <c r="B20" s="42" t="s">
+        <v>118</v>
+      </c>
+      <c r="C20" s="56" t="n">
         <f aca="false">COUNTIF(I7:I14,"Push")</f>
         <v>0</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="50" t="s">
-        <v>126</v>
-      </c>
-      <c r="C21" s="60" t="n">
+      <c r="B21" s="42" t="s">
+        <v>119</v>
+      </c>
+      <c r="C21" s="56" t="n">
         <f aca="false">COUNTIF(I7:I14,"Pending")</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="50" t="s">
-        <v>127</v>
-      </c>
-      <c r="C22" s="61" t="n">
+      <c r="B22" s="42" t="s">
+        <v>120</v>
+      </c>
+      <c r="C22" s="57" t="n">
         <f aca="false">IF(COUNTIF(I7:I14,"Win")+COUNTIF(I7:I14,"Loss")=0,"—",COUNTIF(I7:I14,"Win")/(COUNTIF(I7:I14,"Win")+COUNTIF(I7:I14,"Loss")))</f>
         <v>0.375</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="50" t="s">
-        <v>128</v>
-      </c>
-      <c r="C23" s="62" t="n">
+      <c r="B23" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="C23" s="58" t="n">
         <f aca="false">SUM(F7:F14)</f>
         <v>1000</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="50" t="s">
-        <v>129</v>
-      </c>
-      <c r="C24" s="53" t="n">
+      <c r="B24" s="42" t="s">
+        <v>122</v>
+      </c>
+      <c r="C24" s="46" t="n">
         <f aca="false">SUM(J7:J14)</f>
         <v>802.232258064516</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="50" t="s">
-        <v>130</v>
-      </c>
-      <c r="C25" s="55" t="n">
+      <c r="B25" s="42" t="s">
+        <v>123</v>
+      </c>
+      <c r="C25" s="48" t="n">
         <f aca="false">SUM(K7:K14)</f>
         <v>-197.767741935484</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="50" t="s">
-        <v>131</v>
-      </c>
-      <c r="C26" s="61" t="n">
+      <c r="B26" s="42" t="s">
+        <v>124</v>
+      </c>
+      <c r="C26" s="57" t="n">
         <f aca="false">IF(SUM(F7:F14)=0,"—",SUM(K7:K14)/SUM(F7:F14))</f>
         <v>-0.197767741935484</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="50" t="s">
-        <v>132</v>
-      </c>
-      <c r="C27" s="53" t="n">
+      <c r="B27" s="42" t="s">
+        <v>125</v>
+      </c>
+      <c r="C27" s="46" t="n">
         <f aca="false">SUM(H7:H14)</f>
         <v>2226.16096779872</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="50" t="s">
-        <v>248</v>
-      </c>
-      <c r="C28" s="68" t="n">
+      <c r="B28" s="42" t="s">
+        <v>241</v>
+      </c>
+      <c r="C28" s="66" t="n">
         <f aca="false">SUM(L7:L14)</f>
         <v>3.92</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="50" t="s">
-        <v>249</v>
-      </c>
-      <c r="C29" s="55" t="n">
+      <c r="B29" s="42" t="s">
+        <v>242</v>
+      </c>
+      <c r="C29" s="48" t="n">
         <f aca="false">SUMPRODUCT(L7:L14,G7:G14)-SUMPRODUCT(1-L7:L14,F7:F14)</f>
         <v>45.1624826615033</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B32" s="14" t="s">
+        <v>244</v>
+      </c>
+      <c r="C32" s="14" t="s">
+        <v>128</v>
+      </c>
+      <c r="D32" s="14" t="s">
+        <v>245</v>
+      </c>
+      <c r="E32" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="F32" s="14" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="B33" s="42" t="s">
+        <v>246</v>
+      </c>
+      <c r="C33" s="49" t="s">
+        <v>247</v>
+      </c>
+      <c r="D33" s="59" t="s">
+        <v>248</v>
+      </c>
+      <c r="E33" s="63"/>
+      <c r="F33" s="63"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="36" t="n">
+        <v>2</v>
+      </c>
+      <c r="B34" s="42" t="s">
+        <v>249</v>
+      </c>
+      <c r="C34" s="49" t="s">
         <v>250</v>
       </c>
-    </row>
-    <row r="32" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="B32" s="12" t="s">
+      <c r="D34" s="59" t="s">
         <v>251</v>
       </c>
-      <c r="C32" s="12" t="s">
-        <v>135</v>
-      </c>
-      <c r="D32" s="12" t="s">
+      <c r="E34" s="63"/>
+      <c r="F34" s="63"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="36" t="n">
+        <v>3</v>
+      </c>
+      <c r="B35" s="42" t="s">
         <v>252</v>
       </c>
-      <c r="E32" s="12" t="s">
-        <v>137</v>
-      </c>
-      <c r="F32" s="12" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="49" t="n">
-        <v>1</v>
-      </c>
-      <c r="B33" s="50" t="s">
+      <c r="C35" s="49" t="s">
         <v>253</v>
       </c>
-      <c r="C33" s="56" t="s">
+      <c r="D35" s="59" t="s">
         <v>254</v>
       </c>
-      <c r="D33" s="43" t="s">
+      <c r="E35" s="63"/>
+      <c r="F35" s="63"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="36" t="n">
+        <v>4</v>
+      </c>
+      <c r="B36" s="42" t="s">
         <v>255</v>
       </c>
-      <c r="E33" s="65"/>
-      <c r="F33" s="65"/>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="49" t="n">
-        <v>2</v>
-      </c>
-      <c r="B34" s="50" t="s">
+      <c r="C36" s="49" t="s">
         <v>256</v>
       </c>
-      <c r="C34" s="56" t="s">
+      <c r="D36" s="59" t="s">
         <v>257</v>
       </c>
-      <c r="D34" s="43" t="s">
+      <c r="E36" s="63"/>
+      <c r="F36" s="63"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="36" t="n">
+        <v>5</v>
+      </c>
+      <c r="B37" s="42" t="s">
         <v>258</v>
       </c>
-      <c r="E34" s="65"/>
-      <c r="F34" s="65"/>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="49" t="n">
-        <v>3</v>
-      </c>
-      <c r="B35" s="50" t="s">
+      <c r="C37" s="49" t="s">
         <v>259</v>
       </c>
-      <c r="C35" s="56" t="s">
+      <c r="D37" s="59" t="s">
         <v>260</v>
       </c>
-      <c r="D35" s="43" t="s">
+      <c r="E37" s="63"/>
+      <c r="F37" s="63"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="36" t="n">
+        <v>6</v>
+      </c>
+      <c r="B38" s="42" t="s">
         <v>261</v>
       </c>
-      <c r="E35" s="65"/>
-      <c r="F35" s="65"/>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="49" t="n">
-        <v>4</v>
-      </c>
-      <c r="B36" s="50" t="s">
+      <c r="C38" s="49" t="s">
         <v>262</v>
       </c>
-      <c r="C36" s="56" t="s">
+      <c r="D38" s="59" t="s">
         <v>263</v>
       </c>
-      <c r="D36" s="43" t="s">
+      <c r="E38" s="63"/>
+      <c r="F38" s="63"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="36" t="n">
+        <v>7</v>
+      </c>
+      <c r="B39" s="42" t="s">
         <v>264</v>
       </c>
-      <c r="E36" s="65"/>
-      <c r="F36" s="65"/>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="49" t="n">
-        <v>5</v>
-      </c>
-      <c r="B37" s="50" t="s">
+      <c r="C39" s="49" t="s">
         <v>265</v>
       </c>
-      <c r="C37" s="56" t="s">
+      <c r="D39" s="59" t="s">
         <v>266</v>
       </c>
-      <c r="D37" s="43" t="s">
+      <c r="E39" s="63"/>
+      <c r="F39" s="63"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="36" t="n">
+        <v>8</v>
+      </c>
+      <c r="B40" s="42" t="s">
         <v>267</v>
       </c>
-      <c r="E37" s="65"/>
-      <c r="F37" s="65"/>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="49" t="n">
-        <v>6</v>
-      </c>
-      <c r="B38" s="50" t="s">
+      <c r="C40" s="49" t="s">
         <v>268</v>
       </c>
-      <c r="C38" s="56" t="s">
+      <c r="D40" s="59" t="s">
         <v>269</v>
       </c>
-      <c r="D38" s="43" t="s">
+      <c r="E40" s="63"/>
+      <c r="F40" s="63"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="61" t="s">
         <v>270</v>
-      </c>
-      <c r="E38" s="65"/>
-      <c r="F38" s="65"/>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="49" t="n">
-        <v>7</v>
-      </c>
-      <c r="B39" s="50" t="s">
-        <v>271</v>
-      </c>
-      <c r="C39" s="56" t="s">
-        <v>272</v>
-      </c>
-      <c r="D39" s="43" t="s">
-        <v>273</v>
-      </c>
-      <c r="E39" s="65"/>
-      <c r="F39" s="65"/>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="49" t="n">
-        <v>8</v>
-      </c>
-      <c r="B40" s="50" t="s">
-        <v>274</v>
-      </c>
-      <c r="C40" s="56" t="s">
-        <v>275</v>
-      </c>
-      <c r="D40" s="43" t="s">
-        <v>276</v>
-      </c>
-      <c r="E40" s="65"/>
-      <c r="F40" s="65"/>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="46" t="s">
-        <v>277</v>
       </c>
     </row>
   </sheetData>
@@ -5042,526 +5371,526 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="47" t="s">
-        <v>278</v>
-      </c>
-      <c r="H1" s="64" t="s">
-        <v>279</v>
+      <c r="A1" s="40" t="s">
+        <v>271</v>
+      </c>
+      <c r="H1" s="62" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="69" t="s">
-        <v>281</v>
+      <c r="A3" s="67" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>196</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="F6" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="G6" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H6" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="I6" s="14" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="12" t="s">
+      <c r="J6" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="C6" s="12" t="s">
-        <v>203</v>
-      </c>
-      <c r="D6" s="12" t="s">
+      <c r="K6" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="L6" s="14" t="s">
+        <v>216</v>
+      </c>
+      <c r="M6" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="E6" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="F6" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="G6" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="H6" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="I6" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="J6" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="K6" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="L6" s="12" t="s">
-        <v>223</v>
-      </c>
-      <c r="M6" s="12" t="s">
-        <v>89</v>
-      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="49" t="n">
+      <c r="A7" s="36" t="n">
         <v>1</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>282</v>
-      </c>
-      <c r="C7" s="42" t="s">
-        <v>283</v>
-      </c>
-      <c r="D7" s="49" t="s">
-        <v>284</v>
-      </c>
-      <c r="E7" s="52" t="n">
+        <v>275</v>
+      </c>
+      <c r="C7" s="35" t="s">
+        <v>276</v>
+      </c>
+      <c r="D7" s="36" t="s">
+        <v>277</v>
+      </c>
+      <c r="E7" s="44" t="n">
         <v>-113</v>
       </c>
-      <c r="F7" s="44" t="n">
+      <c r="F7" s="45" t="n">
         <v>300</v>
       </c>
-      <c r="G7" s="53" t="n">
+      <c r="G7" s="46" t="n">
         <f aca="false">IF(E7&gt;0,F7*E7/100,F7*100/ABS(E7))</f>
         <v>265.486725663717</v>
       </c>
-      <c r="H7" s="53" t="n">
+      <c r="H7" s="46" t="n">
         <f aca="false">F7+G7</f>
         <v>565.486725663717</v>
       </c>
-      <c r="I7" s="65" t="s">
-        <v>93</v>
-      </c>
-      <c r="J7" s="53" t="n">
+      <c r="I7" s="63" t="s">
+        <v>86</v>
+      </c>
+      <c r="J7" s="46" t="n">
         <f aca="false">IF(I7="Win",F7+G7,IF(I7="Push",F7,IF(I7="Loss",0,0)))</f>
         <v>565.486725663717</v>
       </c>
-      <c r="K7" s="55" t="n">
+      <c r="K7" s="48" t="n">
         <f aca="false">IF(I7="Pending",0,J7-F7)</f>
         <v>265.486725663717</v>
       </c>
-      <c r="L7" s="66" t="n">
+      <c r="L7" s="64" t="n">
         <v>0.58</v>
       </c>
-      <c r="M7" s="70" t="s">
-        <v>285</v>
+      <c r="M7" s="68" t="s">
+        <v>278</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="49" t="n">
+      <c r="A8" s="36" t="n">
         <v>2</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>286</v>
-      </c>
-      <c r="C8" s="42" t="s">
-        <v>287</v>
-      </c>
-      <c r="D8" s="49" t="s">
-        <v>97</v>
-      </c>
-      <c r="E8" s="52" t="n">
+        <v>279</v>
+      </c>
+      <c r="C8" s="35" t="s">
+        <v>280</v>
+      </c>
+      <c r="D8" s="36" t="s">
+        <v>90</v>
+      </c>
+      <c r="E8" s="44" t="n">
         <v>456</v>
       </c>
-      <c r="F8" s="44" t="n">
+      <c r="F8" s="45" t="n">
         <v>200</v>
       </c>
-      <c r="G8" s="53" t="n">
+      <c r="G8" s="46" t="n">
         <f aca="false">IF(E8&gt;0,F8*E8/100,F8*100/ABS(E8))</f>
         <v>912</v>
       </c>
-      <c r="H8" s="53" t="n">
+      <c r="H8" s="46" t="n">
         <f aca="false">F8+G8</f>
         <v>1112</v>
       </c>
-      <c r="I8" s="65" t="s">
-        <v>101</v>
-      </c>
-      <c r="J8" s="53" t="n">
+      <c r="I8" s="63" t="s">
+        <v>94</v>
+      </c>
+      <c r="J8" s="46" t="n">
         <f aca="false">IF(I8="Win",F8+G8,IF(I8="Push",F8,IF(I8="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K8" s="55" t="n">
+      <c r="K8" s="48" t="n">
         <f aca="false">IF(I8="Pending",0,J8-F8)</f>
         <v>-200</v>
       </c>
-      <c r="L8" s="66" t="n">
+      <c r="L8" s="64" t="n">
         <v>0.24</v>
       </c>
-      <c r="M8" s="70" t="s">
-        <v>288</v>
+      <c r="M8" s="68" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="49" t="n">
+      <c r="A9" s="36" t="n">
         <v>3</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>289</v>
-      </c>
-      <c r="C9" s="42" t="s">
-        <v>290</v>
-      </c>
-      <c r="D9" s="49" t="s">
-        <v>193</v>
-      </c>
-      <c r="E9" s="52" t="n">
+        <v>282</v>
+      </c>
+      <c r="C9" s="35" t="s">
+        <v>283</v>
+      </c>
+      <c r="D9" s="36" t="s">
+        <v>186</v>
+      </c>
+      <c r="E9" s="44" t="n">
         <v>1150</v>
       </c>
-      <c r="F9" s="44" t="n">
+      <c r="F9" s="45" t="n">
         <v>150</v>
       </c>
-      <c r="G9" s="53" t="n">
+      <c r="G9" s="46" t="n">
         <f aca="false">IF(E9&gt;0,F9*E9/100,F9*100/ABS(E9))</f>
         <v>1725</v>
       </c>
-      <c r="H9" s="53" t="n">
+      <c r="H9" s="46" t="n">
         <f aca="false">F9+G9</f>
         <v>1875</v>
       </c>
-      <c r="I9" s="65" t="s">
-        <v>101</v>
-      </c>
-      <c r="J9" s="53" t="n">
+      <c r="I9" s="63" t="s">
+        <v>94</v>
+      </c>
+      <c r="J9" s="46" t="n">
         <f aca="false">IF(I9="Win",F9+G9,IF(I9="Push",F9,IF(I9="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K9" s="55" t="n">
+      <c r="K9" s="48" t="n">
         <f aca="false">IF(I9="Pending",0,J9-F9)</f>
         <v>-150</v>
       </c>
-      <c r="L9" s="66" t="n">
+      <c r="L9" s="64" t="n">
         <v>0.1</v>
       </c>
-      <c r="M9" s="70" t="s">
-        <v>291</v>
+      <c r="M9" s="68" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="49" t="n">
+      <c r="A10" s="36" t="n">
         <v>4</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>292</v>
-      </c>
-      <c r="C10" s="42" t="s">
-        <v>290</v>
-      </c>
-      <c r="D10" s="49" t="s">
-        <v>193</v>
-      </c>
-      <c r="E10" s="52" t="n">
+        <v>285</v>
+      </c>
+      <c r="C10" s="35" t="s">
+        <v>283</v>
+      </c>
+      <c r="D10" s="36" t="s">
+        <v>186</v>
+      </c>
+      <c r="E10" s="44" t="n">
         <v>1567</v>
       </c>
-      <c r="F10" s="44" t="n">
+      <c r="F10" s="45" t="n">
         <v>120</v>
       </c>
-      <c r="G10" s="53" t="n">
+      <c r="G10" s="46" t="n">
         <f aca="false">IF(E10&gt;0,F10*E10/100,F10*100/ABS(E10))</f>
         <v>1880.4</v>
       </c>
-      <c r="H10" s="53" t="n">
+      <c r="H10" s="46" t="n">
         <f aca="false">F10+G10</f>
         <v>2000.4</v>
       </c>
-      <c r="I10" s="65" t="s">
-        <v>101</v>
-      </c>
-      <c r="J10" s="53" t="n">
+      <c r="I10" s="63" t="s">
+        <v>94</v>
+      </c>
+      <c r="J10" s="46" t="n">
         <f aca="false">IF(I10="Win",F10+G10,IF(I10="Push",F10,IF(I10="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K10" s="55" t="n">
+      <c r="K10" s="48" t="n">
         <f aca="false">IF(I10="Pending",0,J10-F10)</f>
         <v>-120</v>
       </c>
-      <c r="L10" s="66" t="n">
+      <c r="L10" s="64" t="n">
         <v>0.08</v>
       </c>
-      <c r="M10" s="70" t="s">
-        <v>293</v>
+      <c r="M10" s="68" t="s">
+        <v>286</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="49" t="n">
+      <c r="A11" s="36" t="n">
         <v>5</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>294</v>
-      </c>
-      <c r="C11" s="42" t="s">
-        <v>290</v>
-      </c>
-      <c r="D11" s="49" t="s">
-        <v>193</v>
-      </c>
-      <c r="E11" s="52" t="n">
+        <v>287</v>
+      </c>
+      <c r="C11" s="35" t="s">
+        <v>283</v>
+      </c>
+      <c r="D11" s="36" t="s">
+        <v>186</v>
+      </c>
+      <c r="E11" s="44" t="n">
         <v>1800</v>
       </c>
-      <c r="F11" s="44" t="n">
+      <c r="F11" s="45" t="n">
         <v>100</v>
       </c>
-      <c r="G11" s="53" t="n">
+      <c r="G11" s="46" t="n">
         <f aca="false">IF(E11&gt;0,F11*E11/100,F11*100/ABS(E11))</f>
         <v>1800</v>
       </c>
-      <c r="H11" s="53" t="n">
+      <c r="H11" s="46" t="n">
         <f aca="false">F11+G11</f>
         <v>1900</v>
       </c>
-      <c r="I11" s="65" t="s">
-        <v>101</v>
-      </c>
-      <c r="J11" s="53" t="n">
+      <c r="I11" s="63" t="s">
+        <v>94</v>
+      </c>
+      <c r="J11" s="46" t="n">
         <f aca="false">IF(I11="Win",F11+G11,IF(I11="Push",F11,IF(I11="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K11" s="55" t="n">
+      <c r="K11" s="48" t="n">
         <f aca="false">IF(I11="Pending",0,J11-F11)</f>
         <v>-100</v>
       </c>
-      <c r="L11" s="66" t="n">
+      <c r="L11" s="64" t="n">
         <v>0.07</v>
       </c>
-      <c r="M11" s="70" t="s">
-        <v>295</v>
+      <c r="M11" s="68" t="s">
+        <v>288</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="49" t="n">
+      <c r="A12" s="36" t="n">
         <v>6</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>296</v>
-      </c>
-      <c r="C12" s="42" t="s">
-        <v>290</v>
-      </c>
-      <c r="D12" s="49" t="s">
-        <v>193</v>
-      </c>
-      <c r="E12" s="52" t="n">
+        <v>289</v>
+      </c>
+      <c r="C12" s="35" t="s">
+        <v>283</v>
+      </c>
+      <c r="D12" s="36" t="s">
+        <v>186</v>
+      </c>
+      <c r="E12" s="44" t="n">
         <v>1150</v>
       </c>
-      <c r="F12" s="44" t="n">
+      <c r="F12" s="45" t="n">
         <v>90</v>
       </c>
-      <c r="G12" s="53" t="n">
+      <c r="G12" s="46" t="n">
         <f aca="false">IF(E12&gt;0,F12*E12/100,F12*100/ABS(E12))</f>
         <v>1035</v>
       </c>
-      <c r="H12" s="53" t="n">
+      <c r="H12" s="46" t="n">
         <f aca="false">F12+G12</f>
         <v>1125</v>
       </c>
-      <c r="I12" s="65" t="s">
-        <v>101</v>
-      </c>
-      <c r="J12" s="53" t="n">
+      <c r="I12" s="63" t="s">
+        <v>94</v>
+      </c>
+      <c r="J12" s="46" t="n">
         <f aca="false">IF(I12="Win",F12+G12,IF(I12="Push",F12,IF(I12="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K12" s="55" t="n">
+      <c r="K12" s="48" t="n">
         <f aca="false">IF(I12="Pending",0,J12-F12)</f>
         <v>-90</v>
       </c>
-      <c r="L12" s="66" t="n">
+      <c r="L12" s="64" t="n">
         <v>0.08</v>
       </c>
-      <c r="M12" s="70" t="s">
-        <v>297</v>
+      <c r="M12" s="68" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="49" t="n">
+      <c r="A13" s="36" t="n">
         <v>7</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>298</v>
-      </c>
-      <c r="C13" s="42" t="s">
-        <v>290</v>
-      </c>
-      <c r="D13" s="49" t="s">
-        <v>193</v>
-      </c>
-      <c r="E13" s="52" t="n">
+        <v>291</v>
+      </c>
+      <c r="C13" s="35" t="s">
+        <v>283</v>
+      </c>
+      <c r="D13" s="36" t="s">
+        <v>186</v>
+      </c>
+      <c r="E13" s="44" t="n">
         <v>1900</v>
       </c>
-      <c r="F13" s="44" t="n">
+      <c r="F13" s="45" t="n">
         <v>40</v>
       </c>
-      <c r="G13" s="53" t="n">
+      <c r="G13" s="46" t="n">
         <f aca="false">IF(E13&gt;0,F13*E13/100,F13*100/ABS(E13))</f>
         <v>760</v>
       </c>
-      <c r="H13" s="53" t="n">
+      <c r="H13" s="46" t="n">
         <f aca="false">F13+G13</f>
         <v>800</v>
       </c>
-      <c r="I13" s="65" t="s">
-        <v>101</v>
-      </c>
-      <c r="J13" s="53" t="n">
+      <c r="I13" s="63" t="s">
+        <v>94</v>
+      </c>
+      <c r="J13" s="46" t="n">
         <f aca="false">IF(I13="Win",F13+G13,IF(I13="Push",F13,IF(I13="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K13" s="55" t="n">
+      <c r="K13" s="48" t="n">
         <f aca="false">IF(I13="Pending",0,J13-F13)</f>
         <v>-40</v>
       </c>
-      <c r="L13" s="66" t="n">
+      <c r="L13" s="64" t="n">
         <v>0.05</v>
       </c>
-      <c r="M13" s="70" t="s">
-        <v>299</v>
+      <c r="M13" s="68" t="s">
+        <v>292</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="37"/>
-      <c r="B14" s="38" t="s">
-        <v>44</v>
-      </c>
-      <c r="C14" s="37"/>
-      <c r="D14" s="37"/>
-      <c r="E14" s="37"/>
-      <c r="F14" s="39" t="n">
+      <c r="A14" s="69"/>
+      <c r="B14" s="70" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" s="69"/>
+      <c r="D14" s="69"/>
+      <c r="E14" s="69"/>
+      <c r="F14" s="53" t="n">
         <f aca="false">SUM(F7:F13)</f>
         <v>1000</v>
       </c>
-      <c r="G14" s="40" t="n">
+      <c r="G14" s="54" t="n">
         <f aca="false">SUM(G7:G13)</f>
         <v>8377.88672566372</v>
       </c>
-      <c r="H14" s="40" t="n">
+      <c r="H14" s="54" t="n">
         <f aca="false">SUM(H7:H13)</f>
         <v>9377.88672566372</v>
       </c>
-      <c r="I14" s="37"/>
-      <c r="J14" s="40" t="n">
+      <c r="I14" s="69"/>
+      <c r="J14" s="54" t="n">
         <f aca="false">SUM(J7:J13)</f>
         <v>565.486725663717</v>
       </c>
-      <c r="K14" s="41" t="n">
+      <c r="K14" s="55" t="n">
         <f aca="false">SUM(K7:K13)</f>
         <v>-434.513274336283</v>
       </c>
-      <c r="L14" s="67" t="n">
+      <c r="L14" s="65" t="n">
         <f aca="false">SUM(L7:L13)</f>
         <v>1.2</v>
       </c>
-      <c r="M14" s="37"/>
+      <c r="M14" s="69"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="4" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="C17" s="60" t="n">
+        <v>116</v>
+      </c>
+      <c r="C17" s="56" t="n">
         <f aca="false">COUNTIF(I7:I13,"Win")</f>
         <v>1</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="C18" s="60" t="n">
+        <v>117</v>
+      </c>
+      <c r="C18" s="56" t="n">
         <f aca="false">COUNTIF(I7:I13,"Loss")</f>
         <v>6</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="C19" s="60" t="n">
+        <v>118</v>
+      </c>
+      <c r="C19" s="56" t="n">
         <f aca="false">COUNTIF(I7:I13,"Push")</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="C20" s="60" t="n">
+        <v>119</v>
+      </c>
+      <c r="C20" s="56" t="n">
         <f aca="false">COUNTIF(I7:I13,"Pending")</f>
         <v>0</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="C21" s="61" t="n">
+        <v>120</v>
+      </c>
+      <c r="C21" s="57" t="n">
         <f aca="false">IF(COUNTIF(I7:I13,"Win")+COUNTIF(I7:I13,"Loss")=0,"—",COUNTIF(I7:I13,"Win")/(COUNTIF(I7:I13,"Win")+COUNTIF(I7:I13,"Loss")))</f>
         <v>0.142857142857143</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="C22" s="62" t="n">
+        <v>121</v>
+      </c>
+      <c r="C22" s="58" t="n">
         <f aca="false">SUM(F7:F13)</f>
         <v>1000</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="C23" s="53" t="n">
+        <v>122</v>
+      </c>
+      <c r="C23" s="46" t="n">
         <f aca="false">SUM(J7:J13)</f>
         <v>565.486725663717</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="C24" s="55" t="n">
+        <v>123</v>
+      </c>
+      <c r="C24" s="48" t="n">
         <f aca="false">SUM(K7:K13)</f>
         <v>-434.513274336283</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="C25" s="61" t="n">
+        <v>124</v>
+      </c>
+      <c r="C25" s="57" t="n">
         <f aca="false">IF(SUM(F7:F13)=0,"—",SUM(K7:K13)/SUM(F7:F13))</f>
         <v>-0.434513274336283</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="5" t="s">
-        <v>248</v>
-      </c>
-      <c r="C26" s="68" t="n">
+        <v>241</v>
+      </c>
+      <c r="C26" s="66" t="n">
         <f aca="false">SUM(L7:L13)</f>
         <v>1.2</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="5" t="s">
-        <v>300</v>
-      </c>
-      <c r="C27" s="62" t="n">
+        <v>293</v>
+      </c>
+      <c r="C27" s="58" t="n">
         <f aca="false">2678</f>
         <v>2678</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="46" t="s">
-        <v>301</v>
+      <c r="A29" s="61" t="s">
+        <v>294</v>
       </c>
     </row>
   </sheetData>
@@ -5602,7 +5931,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="26"/>
@@ -5613,372 +5942,380 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="47" t="s">
-        <v>302</v>
+      <c r="A1" s="40" t="s">
+        <v>295</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="12" t="s">
-        <v>304</v>
-      </c>
-      <c r="B4" s="12" t="s">
-        <v>305</v>
-      </c>
-      <c r="C4" s="12" t="s">
-        <v>306</v>
-      </c>
-      <c r="D4" s="12" t="s">
-        <v>307</v>
-      </c>
-      <c r="E4" s="12" t="s">
-        <v>308</v>
-      </c>
-      <c r="F4" s="12" t="s">
-        <v>309</v>
-      </c>
-      <c r="G4" s="12" t="s">
-        <v>89</v>
+      <c r="A4" s="14" t="s">
+        <v>297</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>298</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>300</v>
+      </c>
+      <c r="E4" s="14" t="s">
+        <v>301</v>
+      </c>
+      <c r="F4" s="14" t="s">
+        <v>302</v>
+      </c>
+      <c r="G4" s="14" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="B5" s="71" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="C5" s="72"/>
       <c r="D5" s="72" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="E5" s="72" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="F5" s="72"/>
       <c r="G5" s="73" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="B6" s="71" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="C6" s="72" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="D6" s="72"/>
       <c r="E6" s="72"/>
       <c r="F6" s="72"/>
       <c r="G6" s="73" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="B7" s="71" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="C7" s="72" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="D7" s="72"/>
       <c r="E7" s="72"/>
       <c r="F7" s="72"/>
       <c r="G7" s="73" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="B8" s="71" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="C8" s="72"/>
       <c r="D8" s="72" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="E8" s="72"/>
       <c r="F8" s="72"/>
       <c r="G8" s="73" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="B9" s="71" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="C9" s="72"/>
       <c r="D9" s="72" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="E9" s="72"/>
       <c r="F9" s="72" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="G9" s="73" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="B10" s="71" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="C10" s="72"/>
       <c r="D10" s="72" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="E10" s="72" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="F10" s="72"/>
       <c r="G10" s="73" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="B11" s="71" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="C11" s="72"/>
       <c r="D11" s="72" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="E11" s="72"/>
       <c r="F11" s="72" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="G11" s="73" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="B12" s="71" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="C12" s="72"/>
       <c r="D12" s="72" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="E12" s="72"/>
       <c r="F12" s="72"/>
       <c r="G12" s="73" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="B13" s="71" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="C13" s="72"/>
       <c r="D13" s="72" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="E13" s="72"/>
       <c r="F13" s="72"/>
       <c r="G13" s="73" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="B14" s="71" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="C14" s="72"/>
       <c r="D14" s="72" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="E14" s="72"/>
       <c r="F14" s="72"/>
       <c r="G14" s="73" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="B15" s="71" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="C15" s="72"/>
       <c r="D15" s="72" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="E15" s="72"/>
       <c r="F15" s="72"/>
       <c r="G15" s="73" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="B16" s="71" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="C16" s="72"/>
       <c r="D16" s="72"/>
       <c r="E16" s="72" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="F16" s="72" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="G16" s="73" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="B17" s="71" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="C17" s="72"/>
       <c r="D17" s="72"/>
       <c r="E17" s="72" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="F17" s="72"/>
       <c r="G17" s="73" t="s">
-        <v>349</v>
+        <v>342</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="B18" s="71" t="s">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="C18" s="72"/>
       <c r="D18" s="72"/>
       <c r="E18" s="72" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="F18" s="72"/>
       <c r="G18" s="73" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="B19" s="71" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="C19" s="72"/>
       <c r="D19" s="72"/>
       <c r="E19" s="72"/>
       <c r="F19" s="72" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="G19" s="73" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="74" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="B20" s="75" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="D20" s="76" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="F20" s="76" t="s">
-        <v>312</v>
-      </c>
-      <c r="G20" s="46" t="s">
-        <v>358</v>
+        <v>305</v>
+      </c>
+      <c r="G20" s="61" t="s">
+        <v>351</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="74" t="s">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="B21" s="75" t="s">
-        <v>360</v>
-      </c>
-      <c r="G21" s="46" t="s">
-        <v>361</v>
+        <v>353</v>
+      </c>
+      <c r="G21" s="61" t="s">
+        <v>354</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="74" t="s">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="B22" s="75" t="s">
-        <v>363</v>
-      </c>
-      <c r="G22" s="46" t="s">
-        <v>364</v>
+        <v>356</v>
+      </c>
+      <c r="G22" s="61" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="74" t="s">
-        <v>365</v>
+        <v>358</v>
       </c>
       <c r="B23" s="75" t="s">
-        <v>366</v>
-      </c>
-      <c r="G23" s="46" t="s">
-        <v>367</v>
+        <v>359</v>
+      </c>
+      <c r="G23" s="61" t="s">
+        <v>360</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="77" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="s">
-        <v>370</v>
+        <v>363</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="3" t="s">
-        <v>371</v>
+        <v>364</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="78" t="s">
+        <v>365</v>
+      </c>
+      <c r="B29" s="78" t="s">
+        <v>366</v>
       </c>
     </row>
   </sheetData>
@@ -6014,535 +6351,535 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="47" t="s">
-        <v>372</v>
-      </c>
-      <c r="H1" s="64" t="s">
-        <v>373</v>
+      <c r="A1" s="40" t="s">
+        <v>367</v>
+      </c>
+      <c r="H1" s="62" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>215</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="F6" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="G6" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H6" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="I6" s="14" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="12" t="s">
+      <c r="J6" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="C6" s="12" t="s">
-        <v>222</v>
-      </c>
-      <c r="D6" s="12" t="s">
+      <c r="K6" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="L6" s="14" t="s">
+        <v>216</v>
+      </c>
+      <c r="M6" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="E6" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="F6" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="G6" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="H6" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="I6" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="J6" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="K6" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="L6" s="12" t="s">
-        <v>223</v>
-      </c>
-      <c r="M6" s="12" t="s">
-        <v>89</v>
-      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="49" t="n">
+      <c r="A7" s="36" t="n">
         <v>1</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>376</v>
-      </c>
-      <c r="C7" s="42" t="s">
-        <v>377</v>
-      </c>
-      <c r="D7" s="49" t="s">
-        <v>378</v>
-      </c>
-      <c r="E7" s="52" t="n">
+        <v>371</v>
+      </c>
+      <c r="C7" s="35" t="s">
+        <v>372</v>
+      </c>
+      <c r="D7" s="36" t="s">
+        <v>373</v>
+      </c>
+      <c r="E7" s="44" t="n">
         <v>-115</v>
       </c>
-      <c r="F7" s="44" t="n">
+      <c r="F7" s="45" t="n">
         <v>200</v>
       </c>
-      <c r="G7" s="53" t="n">
+      <c r="G7" s="46" t="n">
         <f aca="false">IF(E7&gt;0,F7*E7/100,F7*100/ABS(E7))</f>
         <v>173.913043478261</v>
       </c>
-      <c r="H7" s="53" t="n">
+      <c r="H7" s="46" t="n">
         <f aca="false">F7+G7</f>
         <v>373.913043478261</v>
       </c>
-      <c r="I7" s="57" t="s">
-        <v>101</v>
-      </c>
-      <c r="J7" s="53" t="n">
+      <c r="I7" s="50" t="s">
+        <v>94</v>
+      </c>
+      <c r="J7" s="46" t="n">
         <f aca="false">IF(I7="Win",F7+G7,IF(I7="Push",F7,IF(I7="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K7" s="55" t="n">
+      <c r="K7" s="48" t="n">
         <f aca="false">IF(I7="Pending",0,J7-F7)</f>
         <v>-200</v>
       </c>
-      <c r="L7" s="66" t="n">
+      <c r="L7" s="64" t="n">
         <v>0.56</v>
       </c>
-      <c r="M7" s="70" t="s">
-        <v>379</v>
+      <c r="M7" s="68" t="s">
+        <v>374</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="49" t="n">
+      <c r="A8" s="36" t="n">
         <v>2</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>380</v>
-      </c>
-      <c r="C8" s="42" t="s">
-        <v>381</v>
-      </c>
-      <c r="D8" s="49" t="s">
-        <v>182</v>
-      </c>
-      <c r="E8" s="52" t="n">
+        <v>375</v>
+      </c>
+      <c r="C8" s="35" t="s">
+        <v>376</v>
+      </c>
+      <c r="D8" s="36" t="s">
+        <v>175</v>
+      </c>
+      <c r="E8" s="44" t="n">
         <v>-112</v>
       </c>
-      <c r="F8" s="44" t="n">
+      <c r="F8" s="45" t="n">
         <v>150</v>
       </c>
-      <c r="G8" s="53" t="n">
+      <c r="G8" s="46" t="n">
         <f aca="false">IF(E8&gt;0,F8*E8/100,F8*100/ABS(E8))</f>
         <v>133.928571428571</v>
       </c>
-      <c r="H8" s="53" t="n">
+      <c r="H8" s="46" t="n">
         <f aca="false">F8+G8</f>
         <v>283.928571428571</v>
       </c>
-      <c r="I8" s="57" t="s">
-        <v>101</v>
-      </c>
-      <c r="J8" s="53" t="n">
+      <c r="I8" s="50" t="s">
+        <v>94</v>
+      </c>
+      <c r="J8" s="46" t="n">
         <f aca="false">IF(I8="Win",F8+G8,IF(I8="Push",F8,IF(I8="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K8" s="55" t="n">
+      <c r="K8" s="48" t="n">
         <f aca="false">IF(I8="Pending",0,J8-F8)</f>
         <v>-150</v>
       </c>
-      <c r="L8" s="66" t="n">
+      <c r="L8" s="64" t="n">
         <v>0.56</v>
       </c>
-      <c r="M8" s="70" t="s">
-        <v>382</v>
+      <c r="M8" s="68" t="s">
+        <v>377</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="49" t="n">
+      <c r="A9" s="36" t="n">
         <v>3</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>383</v>
-      </c>
-      <c r="C9" s="42" t="s">
-        <v>384</v>
-      </c>
-      <c r="D9" s="49" t="s">
-        <v>97</v>
-      </c>
-      <c r="E9" s="52" t="n">
+        <v>378</v>
+      </c>
+      <c r="C9" s="35" t="s">
+        <v>379</v>
+      </c>
+      <c r="D9" s="36" t="s">
+        <v>90</v>
+      </c>
+      <c r="E9" s="44" t="n">
         <v>-159</v>
       </c>
-      <c r="F9" s="44" t="n">
+      <c r="F9" s="45" t="n">
         <v>150</v>
       </c>
-      <c r="G9" s="53" t="n">
+      <c r="G9" s="46" t="n">
         <f aca="false">IF(E9&gt;0,F9*E9/100,F9*100/ABS(E9))</f>
         <v>94.3396226415094</v>
       </c>
-      <c r="H9" s="53" t="n">
+      <c r="H9" s="46" t="n">
         <f aca="false">F9+G9</f>
         <v>244.339622641509</v>
       </c>
-      <c r="I9" s="54" t="s">
-        <v>93</v>
-      </c>
-      <c r="J9" s="53" t="n">
+      <c r="I9" s="47" t="s">
+        <v>86</v>
+      </c>
+      <c r="J9" s="46" t="n">
         <f aca="false">IF(I9="Win",F9+G9,IF(I9="Push",F9,IF(I9="Loss",0,0)))</f>
         <v>244.339622641509</v>
       </c>
-      <c r="K9" s="55" t="n">
+      <c r="K9" s="48" t="n">
         <f aca="false">IF(I9="Pending",0,J9-F9)</f>
         <v>94.3396226415094</v>
       </c>
-      <c r="L9" s="66" t="n">
+      <c r="L9" s="64" t="n">
         <v>0.65</v>
       </c>
-      <c r="M9" s="70" t="s">
-        <v>385</v>
+      <c r="M9" s="68" t="s">
+        <v>380</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="49" t="n">
+      <c r="A10" s="36" t="n">
         <v>4</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>386</v>
-      </c>
-      <c r="C10" s="42" t="s">
-        <v>387</v>
-      </c>
-      <c r="D10" s="49" t="s">
-        <v>378</v>
-      </c>
-      <c r="E10" s="52" t="n">
+        <v>381</v>
+      </c>
+      <c r="C10" s="35" t="s">
+        <v>382</v>
+      </c>
+      <c r="D10" s="36" t="s">
+        <v>373</v>
+      </c>
+      <c r="E10" s="44" t="n">
         <v>-108</v>
       </c>
-      <c r="F10" s="44" t="n">
+      <c r="F10" s="45" t="n">
         <v>150</v>
       </c>
-      <c r="G10" s="53" t="n">
+      <c r="G10" s="46" t="n">
         <f aca="false">IF(E10&gt;0,F10*E10/100,F10*100/ABS(E10))</f>
         <v>138.888888888889</v>
       </c>
-      <c r="H10" s="53" t="n">
+      <c r="H10" s="46" t="n">
         <f aca="false">F10+G10</f>
         <v>288.888888888889</v>
       </c>
-      <c r="I10" s="65" t="s">
-        <v>101</v>
-      </c>
-      <c r="J10" s="53" t="n">
+      <c r="I10" s="63" t="s">
+        <v>94</v>
+      </c>
+      <c r="J10" s="46" t="n">
         <f aca="false">IF(I10="Win",F10+G10,IF(I10="Push",F10,IF(I10="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K10" s="55" t="n">
+      <c r="K10" s="48" t="n">
         <f aca="false">IF(I10="Pending",0,J10-F10)</f>
         <v>-150</v>
       </c>
-      <c r="L10" s="66" t="n">
+      <c r="L10" s="64" t="n">
         <v>0.55</v>
       </c>
-      <c r="M10" s="70" t="s">
-        <v>388</v>
+      <c r="M10" s="68" t="s">
+        <v>383</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="49" t="n">
+      <c r="A11" s="36" t="n">
         <v>5</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>389</v>
-      </c>
-      <c r="C11" s="42" t="s">
-        <v>390</v>
-      </c>
-      <c r="D11" s="49" t="s">
-        <v>97</v>
-      </c>
-      <c r="E11" s="52" t="n">
+        <v>384</v>
+      </c>
+      <c r="C11" s="35" t="s">
+        <v>385</v>
+      </c>
+      <c r="D11" s="36" t="s">
+        <v>90</v>
+      </c>
+      <c r="E11" s="44" t="n">
         <v>-120</v>
       </c>
-      <c r="F11" s="44" t="n">
+      <c r="F11" s="45" t="n">
         <v>130</v>
       </c>
-      <c r="G11" s="53" t="n">
+      <c r="G11" s="46" t="n">
         <f aca="false">IF(E11&gt;0,F11*E11/100,F11*100/ABS(E11))</f>
         <v>108.333333333333</v>
       </c>
-      <c r="H11" s="53" t="n">
+      <c r="H11" s="46" t="n">
         <f aca="false">F11+G11</f>
         <v>238.333333333333</v>
       </c>
-      <c r="I11" s="65" t="s">
-        <v>93</v>
-      </c>
-      <c r="J11" s="53" t="n">
+      <c r="I11" s="63" t="s">
+        <v>86</v>
+      </c>
+      <c r="J11" s="46" t="n">
         <f aca="false">IF(I11="Win",F11+G11,IF(I11="Push",F11,IF(I11="Loss",0,0)))</f>
         <v>238.333333333333</v>
       </c>
-      <c r="K11" s="55" t="n">
+      <c r="K11" s="48" t="n">
         <f aca="false">IF(I11="Pending",0,J11-F11)</f>
         <v>108.333333333333</v>
       </c>
-      <c r="L11" s="66" t="n">
+      <c r="L11" s="64" t="n">
         <v>0.6</v>
       </c>
-      <c r="M11" s="70" t="s">
-        <v>391</v>
+      <c r="M11" s="68" t="s">
+        <v>386</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="49" t="n">
+      <c r="A12" s="36" t="n">
         <v>6</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>392</v>
-      </c>
-      <c r="C12" s="42" t="s">
-        <v>393</v>
-      </c>
-      <c r="D12" s="49" t="s">
-        <v>97</v>
-      </c>
-      <c r="E12" s="52" t="n">
+        <v>387</v>
+      </c>
+      <c r="C12" s="35" t="s">
+        <v>388</v>
+      </c>
+      <c r="D12" s="36" t="s">
+        <v>90</v>
+      </c>
+      <c r="E12" s="44" t="n">
         <v>-121</v>
       </c>
-      <c r="F12" s="44" t="n">
+      <c r="F12" s="45" t="n">
         <v>120</v>
       </c>
-      <c r="G12" s="53" t="n">
+      <c r="G12" s="46" t="n">
         <f aca="false">IF(E12&gt;0,F12*E12/100,F12*100/ABS(E12))</f>
         <v>99.1735537190083</v>
       </c>
-      <c r="H12" s="53" t="n">
+      <c r="H12" s="46" t="n">
         <f aca="false">F12+G12</f>
         <v>219.173553719008</v>
       </c>
-      <c r="I12" s="65" t="s">
-        <v>93</v>
-      </c>
-      <c r="J12" s="53" t="n">
+      <c r="I12" s="63" t="s">
+        <v>86</v>
+      </c>
+      <c r="J12" s="46" t="n">
         <f aca="false">IF(I12="Win",F12+G12,IF(I12="Push",F12,IF(I12="Loss",0,0)))</f>
         <v>219.173553719008</v>
       </c>
-      <c r="K12" s="55" t="n">
+      <c r="K12" s="48" t="n">
         <f aca="false">IF(I12="Pending",0,J12-F12)</f>
         <v>99.1735537190083</v>
       </c>
-      <c r="L12" s="66" t="n">
+      <c r="L12" s="64" t="n">
         <v>0.58</v>
       </c>
-      <c r="M12" s="70" t="s">
-        <v>394</v>
+      <c r="M12" s="68" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="49" t="n">
+      <c r="A13" s="36" t="n">
         <v>7</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>395</v>
-      </c>
-      <c r="C13" s="42" t="s">
-        <v>396</v>
-      </c>
-      <c r="D13" s="49" t="s">
-        <v>120</v>
-      </c>
-      <c r="E13" s="52" t="n">
+        <v>390</v>
+      </c>
+      <c r="C13" s="35" t="s">
+        <v>391</v>
+      </c>
+      <c r="D13" s="36" t="s">
+        <v>113</v>
+      </c>
+      <c r="E13" s="44" t="n">
         <v>971</v>
       </c>
-      <c r="F13" s="44" t="n">
+      <c r="F13" s="45" t="n">
         <v>100</v>
       </c>
-      <c r="G13" s="53" t="n">
+      <c r="G13" s="46" t="n">
         <f aca="false">IF(E13&gt;0,F13*E13/100,F13*100/ABS(E13))</f>
         <v>971</v>
       </c>
-      <c r="H13" s="53" t="n">
+      <c r="H13" s="46" t="n">
         <f aca="false">F13+G13</f>
         <v>1071</v>
       </c>
-      <c r="I13" s="57" t="s">
-        <v>101</v>
-      </c>
-      <c r="J13" s="53" t="n">
+      <c r="I13" s="50" t="s">
+        <v>94</v>
+      </c>
+      <c r="J13" s="46" t="n">
         <f aca="false">IF(I13="Win",F13+G13,IF(I13="Push",F13,IF(I13="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K13" s="55" t="n">
+      <c r="K13" s="48" t="n">
         <f aca="false">IF(I13="Pending",0,J13-F13)</f>
         <v>-100</v>
       </c>
-      <c r="L13" s="66" t="n">
+      <c r="L13" s="64" t="n">
         <v>0.12</v>
       </c>
-      <c r="M13" s="70" t="s">
-        <v>397</v>
+      <c r="M13" s="68" t="s">
+        <v>392</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="37"/>
-      <c r="B14" s="38" t="s">
-        <v>44</v>
-      </c>
-      <c r="C14" s="37"/>
-      <c r="D14" s="37"/>
-      <c r="E14" s="37"/>
-      <c r="F14" s="39" t="n">
+      <c r="A14" s="69"/>
+      <c r="B14" s="70" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" s="69"/>
+      <c r="D14" s="69"/>
+      <c r="E14" s="69"/>
+      <c r="F14" s="53" t="n">
         <f aca="false">SUM(F7:F13)</f>
         <v>1000</v>
       </c>
-      <c r="G14" s="40" t="n">
+      <c r="G14" s="54" t="n">
         <f aca="false">SUM(G7:G13)</f>
         <v>1719.57701348957</v>
       </c>
-      <c r="H14" s="40" t="n">
+      <c r="H14" s="54" t="n">
         <f aca="false">SUM(H7:H13)</f>
         <v>2719.57701348957</v>
       </c>
-      <c r="I14" s="37"/>
-      <c r="J14" s="40" t="n">
+      <c r="I14" s="69"/>
+      <c r="J14" s="54" t="n">
         <f aca="false">SUM(J7:J13)</f>
         <v>701.846509693851</v>
       </c>
-      <c r="K14" s="41" t="n">
+      <c r="K14" s="55" t="n">
         <f aca="false">SUM(K7:K13)</f>
         <v>-298.153490306149</v>
       </c>
-      <c r="L14" s="67" t="n">
+      <c r="L14" s="65" t="n">
         <f aca="false">SUM(L7:L13)</f>
         <v>3.62</v>
       </c>
-      <c r="M14" s="37"/>
+      <c r="M14" s="69"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="4" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="C17" s="60" t="n">
+        <v>116</v>
+      </c>
+      <c r="C17" s="56" t="n">
         <f aca="false">COUNTIF(I7:I13,"Win")</f>
         <v>3</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="C18" s="60" t="n">
+        <v>117</v>
+      </c>
+      <c r="C18" s="56" t="n">
         <f aca="false">COUNTIF(I7:I13,"Loss")</f>
         <v>4</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="C19" s="60" t="n">
+        <v>118</v>
+      </c>
+      <c r="C19" s="56" t="n">
         <f aca="false">COUNTIF(I7:I13,"Push")</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="C20" s="60" t="n">
+        <v>119</v>
+      </c>
+      <c r="C20" s="56" t="n">
         <f aca="false">COUNTIF(I7:I13,"Pending")</f>
         <v>0</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="C21" s="61" t="n">
+        <v>120</v>
+      </c>
+      <c r="C21" s="57" t="n">
         <f aca="false">IF(COUNTIF(I7:I13,"Win")+COUNTIF(I7:I13,"Loss")=0,"—",COUNTIF(I7:I13,"Win")/(COUNTIF(I7:I13,"Win")+COUNTIF(I7:I13,"Loss")))</f>
         <v>0.428571428571429</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="C22" s="62" t="n">
+        <v>121</v>
+      </c>
+      <c r="C22" s="58" t="n">
         <f aca="false">SUM(F7:F13)</f>
         <v>1000</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="C23" s="53" t="n">
+        <v>122</v>
+      </c>
+      <c r="C23" s="46" t="n">
         <f aca="false">SUM(J7:J13)</f>
         <v>701.846509693851</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="C24" s="55" t="n">
+        <v>123</v>
+      </c>
+      <c r="C24" s="48" t="n">
         <f aca="false">SUM(K7:K13)</f>
         <v>-298.153490306149</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="C25" s="61" t="n">
+        <v>124</v>
+      </c>
+      <c r="C25" s="57" t="n">
         <f aca="false">IF(SUM(F7:F13)=0,"—",SUM(K7:K13)/SUM(F7:F13))</f>
         <v>-0.298153490306149</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="C26" s="53" t="n">
+        <v>125</v>
+      </c>
+      <c r="C26" s="46" t="n">
         <f aca="false">SUM(H7:H13)</f>
         <v>2719.57701348957</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="5" t="s">
-        <v>248</v>
-      </c>
-      <c r="C27" s="68" t="n">
+        <v>241</v>
+      </c>
+      <c r="C27" s="66" t="n">
         <f aca="false">SUM(L7:L13)</f>
         <v>3.62</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="C28" s="55" t="n">
+        <v>242</v>
+      </c>
+      <c r="C28" s="48" t="n">
         <f aca="false">SUMPRODUCT(L7:L13,G7:G13)-SUMPRODUCT(1-L7:L13,F7:F13)</f>
         <v>84.7416091107209</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="46" t="s">
-        <v>398</v>
+      <c r="A30" s="61" t="s">
+        <v>393</v>
       </c>
     </row>
   </sheetData>
@@ -6600,472 +6937,472 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="47" t="s">
-        <v>399</v>
-      </c>
-      <c r="H1" s="64" t="s">
-        <v>400</v>
+      <c r="A1" s="40" t="s">
+        <v>394</v>
+      </c>
+      <c r="H1" s="62" t="s">
+        <v>395</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>196</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="F6" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="G6" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H6" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="I6" s="14" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="12" t="s">
+      <c r="J6" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="C6" s="12" t="s">
-        <v>203</v>
-      </c>
-      <c r="D6" s="12" t="s">
+      <c r="K6" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="L6" s="14" t="s">
+        <v>216</v>
+      </c>
+      <c r="M6" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="E6" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="F6" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="G6" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="H6" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="I6" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="J6" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="K6" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="L6" s="12" t="s">
-        <v>223</v>
-      </c>
-      <c r="M6" s="12" t="s">
-        <v>89</v>
-      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="49" t="n">
+      <c r="A7" s="36" t="n">
         <v>1</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>403</v>
-      </c>
-      <c r="C7" s="42" t="s">
-        <v>290</v>
-      </c>
-      <c r="D7" s="49" t="s">
-        <v>193</v>
-      </c>
-      <c r="E7" s="52" t="n">
+        <v>398</v>
+      </c>
+      <c r="C7" s="35" t="s">
+        <v>283</v>
+      </c>
+      <c r="D7" s="36" t="s">
+        <v>186</v>
+      </c>
+      <c r="E7" s="44" t="n">
         <v>450</v>
       </c>
-      <c r="F7" s="44" t="n">
+      <c r="F7" s="45" t="n">
         <v>200</v>
       </c>
-      <c r="G7" s="53" t="n">
+      <c r="G7" s="46" t="n">
         <f aca="false">IF(E7&gt;0,F7*E7/100,F7*100/ABS(E7))</f>
         <v>900</v>
       </c>
-      <c r="H7" s="53" t="n">
+      <c r="H7" s="46" t="n">
         <f aca="false">F7+G7</f>
         <v>1100</v>
       </c>
-      <c r="I7" s="65" t="s">
-        <v>126</v>
-      </c>
-      <c r="J7" s="53" t="n">
+      <c r="I7" s="63" t="s">
+        <v>119</v>
+      </c>
+      <c r="J7" s="46" t="n">
         <f aca="false">IF(I7="Win",F7+G7,IF(I7="Push",F7,IF(I7="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K7" s="55" t="n">
+      <c r="K7" s="48" t="n">
         <f aca="false">IF(I7="Pending",0,J7-F7)</f>
         <v>0</v>
       </c>
-      <c r="L7" s="78" t="n">
+      <c r="L7" s="79" t="n">
         <v>0.18</v>
       </c>
-      <c r="M7" s="70" t="s">
-        <v>404</v>
+      <c r="M7" s="68" t="s">
+        <v>399</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="49" t="n">
+      <c r="A8" s="36" t="n">
         <v>2</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>405</v>
-      </c>
-      <c r="C8" s="42" t="s">
-        <v>290</v>
-      </c>
-      <c r="D8" s="49" t="s">
-        <v>193</v>
-      </c>
-      <c r="E8" s="52" t="n">
+        <v>400</v>
+      </c>
+      <c r="C8" s="35" t="s">
+        <v>283</v>
+      </c>
+      <c r="D8" s="36" t="s">
+        <v>186</v>
+      </c>
+      <c r="E8" s="44" t="n">
         <v>1600</v>
       </c>
-      <c r="F8" s="44" t="n">
+      <c r="F8" s="45" t="n">
         <v>100</v>
       </c>
-      <c r="G8" s="53" t="n">
+      <c r="G8" s="46" t="n">
         <f aca="false">IF(E8&gt;0,F8*E8/100,F8*100/ABS(E8))</f>
         <v>1600</v>
       </c>
-      <c r="H8" s="53" t="n">
+      <c r="H8" s="46" t="n">
         <f aca="false">F8+G8</f>
         <v>1700</v>
       </c>
-      <c r="I8" s="65" t="s">
-        <v>126</v>
-      </c>
-      <c r="J8" s="53" t="n">
+      <c r="I8" s="63" t="s">
+        <v>119</v>
+      </c>
+      <c r="J8" s="46" t="n">
         <f aca="false">IF(I8="Win",F8+G8,IF(I8="Push",F8,IF(I8="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K8" s="55" t="n">
+      <c r="K8" s="48" t="n">
         <f aca="false">IF(I8="Pending",0,J8-F8)</f>
         <v>0</v>
       </c>
-      <c r="L8" s="78" t="n">
+      <c r="L8" s="79" t="n">
         <v>0.07</v>
       </c>
-      <c r="M8" s="70" t="s">
-        <v>406</v>
+      <c r="M8" s="68" t="s">
+        <v>401</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="49" t="n">
+      <c r="A9" s="36" t="n">
         <v>3</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>407</v>
-      </c>
-      <c r="C9" s="42" t="s">
-        <v>290</v>
-      </c>
-      <c r="D9" s="49" t="s">
-        <v>193</v>
-      </c>
-      <c r="E9" s="52" t="n">
+        <v>402</v>
+      </c>
+      <c r="C9" s="35" t="s">
+        <v>283</v>
+      </c>
+      <c r="D9" s="36" t="s">
+        <v>186</v>
+      </c>
+      <c r="E9" s="44" t="n">
         <v>1600</v>
       </c>
-      <c r="F9" s="44" t="n">
+      <c r="F9" s="45" t="n">
         <v>100</v>
       </c>
-      <c r="G9" s="53" t="n">
+      <c r="G9" s="46" t="n">
         <f aca="false">IF(E9&gt;0,F9*E9/100,F9*100/ABS(E9))</f>
         <v>1600</v>
       </c>
-      <c r="H9" s="53" t="n">
+      <c r="H9" s="46" t="n">
         <f aca="false">F9+G9</f>
         <v>1700</v>
       </c>
-      <c r="I9" s="65" t="s">
-        <v>126</v>
-      </c>
-      <c r="J9" s="53" t="n">
+      <c r="I9" s="63" t="s">
+        <v>119</v>
+      </c>
+      <c r="J9" s="46" t="n">
         <f aca="false">IF(I9="Win",F9+G9,IF(I9="Push",F9,IF(I9="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K9" s="55" t="n">
+      <c r="K9" s="48" t="n">
         <f aca="false">IF(I9="Pending",0,J9-F9)</f>
         <v>0</v>
       </c>
-      <c r="L9" s="78" t="n">
+      <c r="L9" s="79" t="n">
         <v>0.07</v>
       </c>
-      <c r="M9" s="70" t="s">
-        <v>408</v>
+      <c r="M9" s="68" t="s">
+        <v>403</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="49" t="n">
+      <c r="A10" s="36" t="n">
         <v>4</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="C10" s="42" t="s">
-        <v>290</v>
-      </c>
-      <c r="D10" s="49" t="s">
-        <v>193</v>
-      </c>
-      <c r="E10" s="52" t="n">
+        <v>404</v>
+      </c>
+      <c r="C10" s="35" t="s">
+        <v>283</v>
+      </c>
+      <c r="D10" s="36" t="s">
+        <v>186</v>
+      </c>
+      <c r="E10" s="44" t="n">
         <v>2000</v>
       </c>
-      <c r="F10" s="44" t="n">
+      <c r="F10" s="45" t="n">
         <v>80</v>
       </c>
-      <c r="G10" s="53" t="n">
+      <c r="G10" s="46" t="n">
         <f aca="false">IF(E10&gt;0,F10*E10/100,F10*100/ABS(E10))</f>
         <v>1600</v>
       </c>
-      <c r="H10" s="53" t="n">
+      <c r="H10" s="46" t="n">
         <f aca="false">F10+G10</f>
         <v>1680</v>
       </c>
-      <c r="I10" s="65" t="s">
-        <v>126</v>
-      </c>
-      <c r="J10" s="53" t="n">
+      <c r="I10" s="63" t="s">
+        <v>119</v>
+      </c>
+      <c r="J10" s="46" t="n">
         <f aca="false">IF(I10="Win",F10+G10,IF(I10="Push",F10,IF(I10="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K10" s="55" t="n">
+      <c r="K10" s="48" t="n">
         <f aca="false">IF(I10="Pending",0,J10-F10)</f>
         <v>0</v>
       </c>
-      <c r="L10" s="78" t="n">
+      <c r="L10" s="79" t="n">
         <v>0.055</v>
       </c>
-      <c r="M10" s="70" t="s">
-        <v>410</v>
+      <c r="M10" s="68" t="s">
+        <v>405</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="49" t="n">
+      <c r="A11" s="36" t="n">
         <v>5</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>411</v>
-      </c>
-      <c r="C11" s="42" t="s">
-        <v>290</v>
-      </c>
-      <c r="D11" s="49" t="s">
-        <v>193</v>
-      </c>
-      <c r="E11" s="52" t="n">
+        <v>406</v>
+      </c>
+      <c r="C11" s="35" t="s">
+        <v>283</v>
+      </c>
+      <c r="D11" s="36" t="s">
+        <v>186</v>
+      </c>
+      <c r="E11" s="44" t="n">
         <v>2800</v>
       </c>
-      <c r="F11" s="44" t="n">
+      <c r="F11" s="45" t="n">
         <v>70</v>
       </c>
-      <c r="G11" s="53" t="n">
+      <c r="G11" s="46" t="n">
         <f aca="false">IF(E11&gt;0,F11*E11/100,F11*100/ABS(E11))</f>
         <v>1960</v>
       </c>
-      <c r="H11" s="53" t="n">
+      <c r="H11" s="46" t="n">
         <f aca="false">F11+G11</f>
         <v>2030</v>
       </c>
-      <c r="I11" s="65" t="s">
-        <v>126</v>
-      </c>
-      <c r="J11" s="53" t="n">
+      <c r="I11" s="63" t="s">
+        <v>119</v>
+      </c>
+      <c r="J11" s="46" t="n">
         <f aca="false">IF(I11="Win",F11+G11,IF(I11="Push",F11,IF(I11="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K11" s="55" t="n">
+      <c r="K11" s="48" t="n">
         <f aca="false">IF(I11="Pending",0,J11-F11)</f>
         <v>0</v>
       </c>
-      <c r="L11" s="78" t="n">
+      <c r="L11" s="79" t="n">
         <v>0.045</v>
       </c>
-      <c r="M11" s="70" t="s">
-        <v>412</v>
+      <c r="M11" s="68" t="s">
+        <v>407</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="49" t="n">
+      <c r="A12" s="36" t="n">
         <v>6</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>413</v>
-      </c>
-      <c r="C12" s="42" t="s">
-        <v>290</v>
-      </c>
-      <c r="D12" s="49" t="s">
-        <v>193</v>
-      </c>
-      <c r="E12" s="52" t="n">
+        <v>408</v>
+      </c>
+      <c r="C12" s="35" t="s">
+        <v>283</v>
+      </c>
+      <c r="D12" s="36" t="s">
+        <v>186</v>
+      </c>
+      <c r="E12" s="44" t="n">
         <v>5000</v>
       </c>
-      <c r="F12" s="44" t="n">
+      <c r="F12" s="45" t="n">
         <v>50</v>
       </c>
-      <c r="G12" s="53" t="n">
+      <c r="G12" s="46" t="n">
         <f aca="false">IF(E12&gt;0,F12*E12/100,F12*100/ABS(E12))</f>
         <v>2500</v>
       </c>
-      <c r="H12" s="53" t="n">
+      <c r="H12" s="46" t="n">
         <f aca="false">F12+G12</f>
         <v>2550</v>
       </c>
-      <c r="I12" s="65" t="s">
-        <v>126</v>
-      </c>
-      <c r="J12" s="53" t="n">
+      <c r="I12" s="63" t="s">
+        <v>119</v>
+      </c>
+      <c r="J12" s="46" t="n">
         <f aca="false">IF(I12="Win",F12+G12,IF(I12="Push",F12,IF(I12="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K12" s="55" t="n">
+      <c r="K12" s="48" t="n">
         <f aca="false">IF(I12="Pending",0,J12-F12)</f>
         <v>0</v>
       </c>
-      <c r="L12" s="78" t="n">
+      <c r="L12" s="79" t="n">
         <v>0.025</v>
       </c>
-      <c r="M12" s="70" t="s">
-        <v>414</v>
+      <c r="M12" s="68" t="s">
+        <v>409</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="28" t="n">
+      <c r="A13" s="80" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="22" t="s">
-        <v>415</v>
-      </c>
-      <c r="C13" s="28" t="s">
-        <v>416</v>
-      </c>
-      <c r="D13" s="28" t="s">
-        <v>68</v>
-      </c>
-      <c r="E13" s="28"/>
-      <c r="F13" s="28"/>
-      <c r="G13" s="28"/>
-      <c r="H13" s="28"/>
-      <c r="I13" s="28"/>
-      <c r="J13" s="28"/>
-      <c r="K13" s="28"/>
-      <c r="L13" s="28"/>
-      <c r="M13" s="28" t="s">
-        <v>417</v>
+      <c r="B13" s="23" t="s">
+        <v>410</v>
+      </c>
+      <c r="C13" s="80" t="s">
+        <v>411</v>
+      </c>
+      <c r="D13" s="80" t="s">
+        <v>61</v>
+      </c>
+      <c r="E13" s="80"/>
+      <c r="F13" s="80"/>
+      <c r="G13" s="80"/>
+      <c r="H13" s="80"/>
+      <c r="I13" s="80"/>
+      <c r="J13" s="80"/>
+      <c r="K13" s="80"/>
+      <c r="L13" s="80"/>
+      <c r="M13" s="80" t="s">
+        <v>412</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="37"/>
-      <c r="B14" s="38" t="s">
-        <v>418</v>
-      </c>
-      <c r="C14" s="37"/>
-      <c r="D14" s="37"/>
-      <c r="E14" s="37"/>
-      <c r="F14" s="39" t="n">
+      <c r="A14" s="69"/>
+      <c r="B14" s="70" t="s">
+        <v>413</v>
+      </c>
+      <c r="C14" s="69"/>
+      <c r="D14" s="69"/>
+      <c r="E14" s="69"/>
+      <c r="F14" s="53" t="n">
         <f aca="false">SUM(F7:F13)</f>
         <v>600</v>
       </c>
-      <c r="G14" s="40" t="n">
+      <c r="G14" s="54" t="n">
         <f aca="false">SUM(G7:G12)</f>
         <v>10160</v>
       </c>
-      <c r="H14" s="40" t="n">
+      <c r="H14" s="54" t="n">
         <f aca="false">SUM(H7:H12)</f>
         <v>10760</v>
       </c>
-      <c r="I14" s="37"/>
-      <c r="J14" s="40" t="n">
+      <c r="I14" s="69"/>
+      <c r="J14" s="54" t="n">
         <f aca="false">SUM(J7:J12)</f>
         <v>0</v>
       </c>
-      <c r="K14" s="41" t="n">
+      <c r="K14" s="55" t="n">
         <f aca="false">SUM(K7:K12)</f>
         <v>0</v>
       </c>
-      <c r="L14" s="79" t="n">
+      <c r="L14" s="81" t="n">
         <f aca="false">SUM(L7:L12)</f>
         <v>0.445</v>
       </c>
-      <c r="M14" s="37"/>
+      <c r="M14" s="69"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="4" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="C17" s="60" t="n">
+        <v>116</v>
+      </c>
+      <c r="C17" s="56" t="n">
         <f aca="false">COUNTIF(I7:I12,"Win")</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="C18" s="60" t="n">
+        <v>117</v>
+      </c>
+      <c r="C18" s="56" t="n">
         <f aca="false">COUNTIF(I7:I12,"Loss")</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="C19" s="60" t="n">
+        <v>119</v>
+      </c>
+      <c r="C19" s="56" t="n">
         <f aca="false">COUNTIF(I7:I12,"Pending")</f>
         <v>6</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="C20" s="61" t="str">
+        <v>120</v>
+      </c>
+      <c r="C20" s="57" t="str">
         <f aca="false">IF(COUNTIF(I7:I12,"Win")+COUNTIF(I7:I12,"Loss")=0,"—",COUNTIF(I7:I12,"Win")/(COUNTIF(I7:I12,"Win")+COUNTIF(I7:I12,"Loss")))</f>
         <v>—</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="5" t="s">
-        <v>419</v>
-      </c>
-      <c r="C21" s="62" t="n">
+        <v>414</v>
+      </c>
+      <c r="C21" s="58" t="n">
         <f aca="false">SUM(F7:F12)</f>
         <v>600</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="C22" s="53" t="n">
+        <v>122</v>
+      </c>
+      <c r="C22" s="46" t="n">
         <f aca="false">SUM(J7:J12)</f>
         <v>0</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="C23" s="55" t="n">
+        <v>123</v>
+      </c>
+      <c r="C23" s="48" t="n">
         <f aca="false">SUM(K7:K12)</f>
         <v>0</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="5" t="s">
-        <v>420</v>
-      </c>
-      <c r="C24" s="61" t="n">
+        <v>415</v>
+      </c>
+      <c r="C24" s="57" t="n">
         <f aca="false">SUM(L7:L12)</f>
         <v>0.445</v>
       </c>
@@ -7101,4 +7438,456 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FFE81828"/>
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:M14"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="46"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="82" t="s">
+        <v>416</v>
+      </c>
+      <c r="H1" s="83" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="84" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="84" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="85" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>196</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="F6" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="G6" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H6" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="I6" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="J6" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="K6" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="L6" s="14" t="s">
+        <v>216</v>
+      </c>
+      <c r="M6" s="14" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>420</v>
+      </c>
+      <c r="C7" s="35" t="s">
+        <v>283</v>
+      </c>
+      <c r="D7" s="36" t="s">
+        <v>186</v>
+      </c>
+      <c r="E7" s="44" t="n">
+        <v>310</v>
+      </c>
+      <c r="F7" s="86" t="n">
+        <v>220</v>
+      </c>
+      <c r="G7" s="87" t="n">
+        <f aca="false">IF(E7&gt;0,F7*E7/100,F7*100/ABS(E7))</f>
+        <v>682</v>
+      </c>
+      <c r="H7" s="87" t="n">
+        <f aca="false">F7+G7</f>
+        <v>902</v>
+      </c>
+      <c r="I7" s="63" t="s">
+        <v>119</v>
+      </c>
+      <c r="J7" s="87" t="n">
+        <f aca="false">IF(I7="Win",F7+G7,IF(I7="Push",F7,IF(I7="Loss",0,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="K7" s="88" t="n">
+        <f aca="false">IF(I7="Pending",0,J7-F7)</f>
+        <v>0</v>
+      </c>
+      <c r="L7" s="79" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="M7" s="68" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="36" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>422</v>
+      </c>
+      <c r="C8" s="35" t="s">
+        <v>283</v>
+      </c>
+      <c r="D8" s="36" t="s">
+        <v>186</v>
+      </c>
+      <c r="E8" s="44" t="n">
+        <v>425</v>
+      </c>
+      <c r="F8" s="86" t="n">
+        <v>130</v>
+      </c>
+      <c r="G8" s="87" t="n">
+        <f aca="false">IF(E8&gt;0,F8*E8/100,F8*100/ABS(E8))</f>
+        <v>552.5</v>
+      </c>
+      <c r="H8" s="87" t="n">
+        <f aca="false">F8+G8</f>
+        <v>682.5</v>
+      </c>
+      <c r="I8" s="63" t="s">
+        <v>119</v>
+      </c>
+      <c r="J8" s="87" t="n">
+        <f aca="false">IF(I8="Win",F8+G8,IF(I8="Push",F8,IF(I8="Loss",0,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="K8" s="88" t="n">
+        <f aca="false">IF(I8="Pending",0,J8-F8)</f>
+        <v>0</v>
+      </c>
+      <c r="L8" s="79" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="M8" s="68" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="36" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>424</v>
+      </c>
+      <c r="C9" s="35" t="s">
+        <v>425</v>
+      </c>
+      <c r="D9" s="36" t="s">
+        <v>90</v>
+      </c>
+      <c r="E9" s="44" t="n">
+        <v>-110</v>
+      </c>
+      <c r="F9" s="86" t="n">
+        <v>180</v>
+      </c>
+      <c r="G9" s="87" t="n">
+        <f aca="false">IF(E9&gt;0,F9*E9/100,F9*100/ABS(E9))</f>
+        <v>163.636363636364</v>
+      </c>
+      <c r="H9" s="87" t="n">
+        <f aca="false">F9+G9</f>
+        <v>343.636363636364</v>
+      </c>
+      <c r="I9" s="63" t="s">
+        <v>119</v>
+      </c>
+      <c r="J9" s="87" t="n">
+        <f aca="false">IF(I9="Win",F9+G9,IF(I9="Push",F9,IF(I9="Loss",0,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="K9" s="88" t="n">
+        <f aca="false">IF(I9="Pending",0,J9-F9)</f>
+        <v>0</v>
+      </c>
+      <c r="L9" s="79" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M9" s="68" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="36" t="n">
+        <v>4</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>427</v>
+      </c>
+      <c r="C10" s="35" t="s">
+        <v>428</v>
+      </c>
+      <c r="D10" s="36" t="s">
+        <v>90</v>
+      </c>
+      <c r="E10" s="44" t="n">
+        <v>-110</v>
+      </c>
+      <c r="F10" s="86" t="n">
+        <v>150</v>
+      </c>
+      <c r="G10" s="87" t="n">
+        <f aca="false">IF(E10&gt;0,F10*E10/100,F10*100/ABS(E10))</f>
+        <v>136.363636363636</v>
+      </c>
+      <c r="H10" s="87" t="n">
+        <f aca="false">F10+G10</f>
+        <v>286.363636363636</v>
+      </c>
+      <c r="I10" s="63" t="s">
+        <v>119</v>
+      </c>
+      <c r="J10" s="87" t="n">
+        <f aca="false">IF(I10="Win",F10+G10,IF(I10="Push",F10,IF(I10="Loss",0,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="K10" s="88" t="n">
+        <f aca="false">IF(I10="Pending",0,J10-F10)</f>
+        <v>0</v>
+      </c>
+      <c r="L10" s="79" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="M10" s="68" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="36" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="C11" s="35" t="s">
+        <v>425</v>
+      </c>
+      <c r="D11" s="36" t="s">
+        <v>90</v>
+      </c>
+      <c r="E11" s="44" t="n">
+        <v>-110</v>
+      </c>
+      <c r="F11" s="86" t="n">
+        <v>120</v>
+      </c>
+      <c r="G11" s="87" t="n">
+        <f aca="false">IF(E11&gt;0,F11*E11/100,F11*100/ABS(E11))</f>
+        <v>109.090909090909</v>
+      </c>
+      <c r="H11" s="87" t="n">
+        <f aca="false">F11+G11</f>
+        <v>229.090909090909</v>
+      </c>
+      <c r="I11" s="63" t="s">
+        <v>119</v>
+      </c>
+      <c r="J11" s="87" t="n">
+        <f aca="false">IF(I11="Win",F11+G11,IF(I11="Push",F11,IF(I11="Loss",0,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="K11" s="88" t="n">
+        <f aca="false">IF(I11="Pending",0,J11-F11)</f>
+        <v>0</v>
+      </c>
+      <c r="L11" s="79" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="M11" s="68" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="36" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>432</v>
+      </c>
+      <c r="C12" s="35" t="s">
+        <v>433</v>
+      </c>
+      <c r="D12" s="36" t="s">
+        <v>90</v>
+      </c>
+      <c r="E12" s="44" t="n">
+        <v>-110</v>
+      </c>
+      <c r="F12" s="86" t="n">
+        <v>125</v>
+      </c>
+      <c r="G12" s="87" t="n">
+        <f aca="false">IF(E12&gt;0,F12*E12/100,F12*100/ABS(E12))</f>
+        <v>113.636363636364</v>
+      </c>
+      <c r="H12" s="87" t="n">
+        <f aca="false">F12+G12</f>
+        <v>238.636363636364</v>
+      </c>
+      <c r="I12" s="63" t="s">
+        <v>119</v>
+      </c>
+      <c r="J12" s="87" t="n">
+        <f aca="false">IF(I12="Win",F12+G12,IF(I12="Push",F12,IF(I12="Loss",0,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="K12" s="88" t="n">
+        <f aca="false">IF(I12="Pending",0,J12-F12)</f>
+        <v>0</v>
+      </c>
+      <c r="L12" s="79" t="n">
+        <v>0.56</v>
+      </c>
+      <c r="M12" s="68" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="36" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>435</v>
+      </c>
+      <c r="C13" s="35" t="s">
+        <v>283</v>
+      </c>
+      <c r="D13" s="36" t="s">
+        <v>186</v>
+      </c>
+      <c r="E13" s="44" t="n">
+        <v>1400</v>
+      </c>
+      <c r="F13" s="86" t="n">
+        <v>75</v>
+      </c>
+      <c r="G13" s="87" t="n">
+        <f aca="false">IF(E13&gt;0,F13*E13/100,F13*100/ABS(E13))</f>
+        <v>1050</v>
+      </c>
+      <c r="H13" s="87" t="n">
+        <f aca="false">F13+G13</f>
+        <v>1125</v>
+      </c>
+      <c r="I13" s="63" t="s">
+        <v>119</v>
+      </c>
+      <c r="J13" s="87" t="n">
+        <f aca="false">IF(I13="Win",F13+G13,IF(I13="Push",F13,IF(I13="Loss",0,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="K13" s="88" t="n">
+        <f aca="false">IF(I13="Pending",0,J13-F13)</f>
+        <v>0</v>
+      </c>
+      <c r="L13" s="79" t="n">
+        <v>0.07</v>
+      </c>
+      <c r="M13" s="68" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="85" t="s">
+        <v>37</v>
+      </c>
+      <c r="F14" s="32" t="n">
+        <f aca="false">SUM(F7:F13)</f>
+        <v>1000</v>
+      </c>
+      <c r="G14" s="32" t="n">
+        <f aca="false">SUM(G7:G13)</f>
+        <v>2807.22727272727</v>
+      </c>
+      <c r="H14" s="32" t="n">
+        <f aca="false">SUM(H7:H13)</f>
+        <v>3807.22727272727</v>
+      </c>
+      <c r="J14" s="32" t="n">
+        <f aca="false">SUM(J7:J13)</f>
+        <v>0</v>
+      </c>
+      <c r="K14" s="32" t="n">
+        <f aca="false">SUM(K7:K13)</f>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="K7:K14">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+      <formula>AND(ISNUMBER(K7),K7&gt;0)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+      <formula>AND(ISNUMBER(K7),K7&lt;0)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="I7:I13" type="list">
+      <formula1>"Pending,Win,Loss,Push"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
 </file>
--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -1281,7 +1281,7 @@
     <t xml:space="preserve">TEST 8 — MLB HOME RUN DERBY · CITIZENS BANK PARK, PHILADELPHIA · JULY 13, 2026</t>
   </si>
   <si>
-    <t xml:space="preserve">STATUS: ACTIVE — settles tonight ~9:30 PM CT</t>
+    <t xml:space="preserve">STATUS: ACTIVE — LIVE, R1 in progress; longest-HR prop cashed</t>
   </si>
   <si>
     <t xml:space="preserve">8 PM ET / 7 CT on Netflix · Source: cards/hrderby-jul13-betting-card.html · Outrights: DraftKings ~9 AM CT Jul 13 · Props: Action Network / VSiN lines, -110 std price</t>
@@ -1332,7 +1332,7 @@
     <t xml:space="preserve">Distance prop</t>
   </si>
   <si>
-    <t xml:space="preserve">Caminero/Caglianone raw power, hot night</t>
+    <t xml:space="preserve">Contreras 490-ft R1 blast clears 484.5 — graded live mid-event (NESN/Sportsnet/Yahoo agree)</t>
   </si>
   <si>
     <t xml:space="preserve">LONGSHOT: Willson Contreras</t>
@@ -1345,21 +1345,18 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="14">
+  <numFmts count="11">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="\$#,##0"/>
     <numFmt numFmtId="166" formatCode="\$#,##0.00;&quot;($&quot;#,##0.00\);\-"/>
     <numFmt numFmtId="167" formatCode="\$#,##0.00"/>
-    <numFmt numFmtId="168" formatCode="\$#,##0.00"/>
-    <numFmt numFmtId="169" formatCode="\$#,##0"/>
-    <numFmt numFmtId="170" formatCode="\+0;\-0"/>
-    <numFmt numFmtId="171" formatCode="0"/>
-    <numFmt numFmtId="172" formatCode="0.0%"/>
-    <numFmt numFmtId="173" formatCode="0%"/>
-    <numFmt numFmtId="174" formatCode="0.0&quot; exp. wins&quot;"/>
-    <numFmt numFmtId="175" formatCode="0.0"/>
-    <numFmt numFmtId="176" formatCode="0.00&quot; exp. wins&quot;"/>
-    <numFmt numFmtId="177" formatCode="\$#,##0.00;&quot;($&quot;#,##0.00\);\-"/>
+    <numFmt numFmtId="168" formatCode="\+0;\-0"/>
+    <numFmt numFmtId="169" formatCode="0"/>
+    <numFmt numFmtId="170" formatCode="0.0%"/>
+    <numFmt numFmtId="171" formatCode="0%"/>
+    <numFmt numFmtId="172" formatCode="0.0&quot; exp. wins&quot;"/>
+    <numFmt numFmtId="173" formatCode="0.0"/>
+    <numFmt numFmtId="174" formatCode="0.00&quot; exp. wins&quot;"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -1655,7 +1652,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="76">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1704,19 +1701,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1732,15 +1721,15 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1756,7 +1745,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1772,23 +1761,15 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1804,15 +1785,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1832,7 +1809,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1880,15 +1857,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1900,10 +1873,6 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="9" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1912,15 +1881,15 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="171" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="174" fontId="7" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="172" fontId="7" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="175" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1968,11 +1937,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1980,36 +1949,12 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="176" fontId="7" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="174" fontId="7" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="177" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -2021,35 +1966,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="4">
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <charset val="1"/>
-        <family val="0"/>
-        <b val="1"/>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <charset val="1"/>
-        <family val="0"/>
-        <b val="1"/>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="2">
     <dxf>
       <font>
         <name val="Arial"/>
@@ -2365,7 +2282,7 @@
       </c>
       <c r="B6" s="7" t="n">
         <f aca="false">H24</f>
-        <v>-765.324133746613</v>
+        <v>-651.687770110249</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2374,7 +2291,7 @@
       </c>
       <c r="B7" s="8" t="n">
         <f aca="false">B5+B6</f>
-        <v>4234.67586625339</v>
+        <v>4348.31222988975</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2383,7 +2300,7 @@
       </c>
       <c r="B8" s="9" t="n">
         <f aca="false">F24</f>
-        <v>2600</v>
+        <v>2475</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2392,7 +2309,7 @@
       </c>
       <c r="B9" s="8" t="n">
         <f aca="false">B7-B8</f>
-        <v>1634.67586625339</v>
+        <v>1873.31222988975</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2413,691 +2330,568 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="12" t="s">
+      <c r="A14" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B14" s="13"/>
-      <c r="C14" s="13"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="13"/>
-      <c r="F14" s="13"/>
-      <c r="G14" s="13"/>
-      <c r="H14" s="13"/>
-      <c r="I14" s="13"/>
-      <c r="J14" s="13"/>
-      <c r="K14" s="13"/>
-      <c r="L14" s="13"/>
-      <c r="M14" s="13"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="1"/>
+      <c r="M14" s="1"/>
     </row>
     <row r="15" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="14" t="s">
+      <c r="A15" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B15" s="14" t="s">
+      <c r="B15" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="14" t="s">
+      <c r="C15" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="D15" s="14" t="s">
+      <c r="D15" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="E15" s="14" t="s">
+      <c r="E15" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="F15" s="14" t="s">
+      <c r="F15" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G15" s="14" t="s">
+      <c r="G15" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="H15" s="14" t="s">
+      <c r="H15" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="I15" s="15"/>
-      <c r="J15" s="15"/>
-      <c r="K15" s="13"/>
-      <c r="L15" s="13"/>
-      <c r="M15" s="13"/>
+      <c r="I15" s="13"/>
+      <c r="J15" s="13"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="16" t="n">
+      <c r="A16" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="B16" s="17" t="s">
+      <c r="B16" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="C16" s="16" t="s">
+      <c r="C16" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="D16" s="18" t="s">
+      <c r="D16" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="E16" s="19" t="n">
+      <c r="E16" s="17" t="n">
         <f aca="false">SUM('HR Derby'!F7:F13)</f>
         <v>1000</v>
       </c>
-      <c r="F16" s="19" t="n">
+      <c r="F16" s="17" t="n">
         <f aca="false">SUMIF('HR Derby'!I7:I13,"Pending",'HR Derby'!F7:F13)</f>
-        <v>1000</v>
-      </c>
-      <c r="G16" s="19" t="n">
+        <v>875</v>
+      </c>
+      <c r="G16" s="17" t="n">
         <f aca="false">SUM('HR Derby'!J7:J13)</f>
-        <v>0</v>
-      </c>
-      <c r="H16" s="19" t="n">
+        <v>238.636363636364</v>
+      </c>
+      <c r="H16" s="17" t="n">
         <f aca="false">SUM('HR Derby'!K7:K13)</f>
-        <v>0</v>
-      </c>
-      <c r="I16" s="20"/>
-      <c r="J16" s="21"/>
-      <c r="K16" s="13"/>
-      <c r="L16" s="13"/>
-      <c r="M16" s="13"/>
+        <v>113.636363636364</v>
+      </c>
+      <c r="I16" s="18"/>
+      <c r="J16" s="19"/>
+      <c r="K16" s="1"/>
+      <c r="L16" s="1"/>
+      <c r="M16" s="1"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="16" t="n">
+      <c r="A17" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="B17" s="17" t="s">
+      <c r="B17" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="C17" s="16" t="s">
+      <c r="C17" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="D17" s="18" t="s">
+      <c r="D17" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="E17" s="19" t="n">
+      <c r="E17" s="17" t="n">
         <f aca="false">SUM('World Cup 2026'!F7:F13)</f>
         <v>1000</v>
       </c>
-      <c r="F17" s="19" t="n">
+      <c r="F17" s="17" t="n">
         <f aca="false">SUMIF('World Cup 2026'!I7:I13,"Pending",'World Cup 2026'!F7:F13)</f>
         <v>1000</v>
       </c>
-      <c r="G17" s="19" t="n">
+      <c r="G17" s="17" t="n">
         <f aca="false">SUM('World Cup 2026'!J7:J13)</f>
         <v>0</v>
       </c>
-      <c r="H17" s="19" t="n">
+      <c r="H17" s="17" t="n">
         <f aca="false">SUM('World Cup 2026'!K7:K13)</f>
         <v>0</v>
       </c>
-      <c r="I17" s="20"/>
-      <c r="J17" s="21"/>
-      <c r="K17" s="13"/>
-      <c r="L17" s="13"/>
-      <c r="M17" s="13"/>
+      <c r="I17" s="18"/>
+      <c r="J17" s="19"/>
+      <c r="K17" s="1"/>
+      <c r="L17" s="1"/>
+      <c r="M17" s="1"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="16" t="n">
+      <c r="A18" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="B18" s="17" t="s">
+      <c r="B18" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="16" t="s">
+      <c r="C18" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="18" t="s">
+      <c r="D18" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="E18" s="19" t="n">
+      <c r="E18" s="17" t="n">
         <f aca="false">SUM('The Open'!F7:F12)</f>
         <v>600</v>
       </c>
-      <c r="F18" s="19" t="n">
+      <c r="F18" s="17" t="n">
         <f aca="false">SUMIF('The Open'!I7:I12,"Pending",'The Open'!F7:F12)</f>
         <v>600</v>
       </c>
-      <c r="G18" s="19" t="n">
+      <c r="G18" s="17" t="n">
         <f aca="false">SUM('The Open'!J7:J12)</f>
         <v>0</v>
       </c>
-      <c r="H18" s="19" t="n">
+      <c r="H18" s="17" t="n">
         <f aca="false">SUM('The Open'!K7:K12)</f>
         <v>0</v>
       </c>
-      <c r="I18" s="20"/>
-      <c r="J18" s="21"/>
-      <c r="K18" s="13"/>
-      <c r="L18" s="13"/>
-      <c r="M18" s="13"/>
+      <c r="I18" s="18"/>
+      <c r="J18" s="19"/>
+      <c r="K18" s="1"/>
+      <c r="L18" s="1"/>
+      <c r="M18" s="1"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="22" t="n">
+      <c r="A19" s="20" t="n">
         <v>7</v>
       </c>
-      <c r="B19" s="23" t="s">
+      <c r="B19" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="C19" s="22" t="s">
+      <c r="C19" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="D19" s="24" t="s">
+      <c r="D19" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="E19" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="20"/>
-      <c r="J19" s="21"/>
-      <c r="K19" s="13"/>
-      <c r="L19" s="13"/>
-      <c r="M19" s="13"/>
+      <c r="E19" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="18"/>
+      <c r="J19" s="19"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1"/>
+      <c r="M19" s="1"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="26" t="n">
+      <c r="A20" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="B20" s="27" t="s">
+      <c r="B20" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="C20" s="26" t="s">
+      <c r="C20" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="D20" s="28" t="s">
+      <c r="D20" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="E20" s="29" t="n">
+      <c r="E20" s="27" t="n">
         <f aca="false">SUM('NASCAR Jul 12'!F7:F13)</f>
         <v>1000</v>
       </c>
-      <c r="F20" s="29" t="n">
+      <c r="F20" s="27" t="n">
         <f aca="false">SUMIF('NASCAR Jul 12'!I7:I13,"Pending",'NASCAR Jul 12'!F7:F13)</f>
         <v>0</v>
       </c>
-      <c r="G20" s="29" t="n">
+      <c r="G20" s="27" t="n">
         <f aca="false">SUM('NASCAR Jul 12'!J7:J13)</f>
         <v>565.486725663717</v>
       </c>
-      <c r="H20" s="29" t="n">
+      <c r="H20" s="27" t="n">
         <f aca="false">SUM('NASCAR Jul 12'!K7:K13)</f>
         <v>-434.513274336283</v>
       </c>
-      <c r="I20" s="20"/>
-      <c r="J20" s="21"/>
-      <c r="K20" s="13"/>
-      <c r="L20" s="13"/>
-      <c r="M20" s="13"/>
+      <c r="I20" s="18"/>
+      <c r="J20" s="19"/>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1"/>
+      <c r="M20" s="1"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="26" t="n">
+      <c r="A21" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="B21" s="27" t="s">
+      <c r="B21" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="C21" s="26" t="s">
+      <c r="C21" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="D21" s="28" t="s">
+      <c r="D21" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="E21" s="29" t="n">
+      <c r="E21" s="27" t="n">
         <f aca="false">SUM('WNBA Jul 12'!F7:F13)</f>
         <v>1000</v>
       </c>
-      <c r="F21" s="29" t="n">
+      <c r="F21" s="27" t="n">
         <f aca="false">SUMIF('WNBA Jul 12'!I7:I13,"Pending",'WNBA Jul 12'!F7:F13)</f>
         <v>0</v>
       </c>
-      <c r="G21" s="29" t="n">
+      <c r="G21" s="27" t="n">
         <f aca="false">SUM('WNBA Jul 12'!J7:J13)</f>
         <v>701.846509693851</v>
       </c>
-      <c r="H21" s="29" t="n">
+      <c r="H21" s="27" t="n">
         <f aca="false">SUM('WNBA Jul 12'!K7:K13)</f>
         <v>-298.153490306149</v>
       </c>
-      <c r="I21" s="20"/>
-      <c r="J21" s="21"/>
-      <c r="K21" s="13"/>
-      <c r="L21" s="13"/>
-      <c r="M21" s="13"/>
+      <c r="I21" s="18"/>
+      <c r="J21" s="19"/>
+      <c r="K21" s="1"/>
+      <c r="L21" s="1"/>
+      <c r="M21" s="1"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="26" t="n">
+      <c r="A22" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="B22" s="27" t="s">
+      <c r="B22" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="C22" s="26" t="s">
+      <c r="C22" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="D22" s="28" t="s">
+      <c r="D22" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="E22" s="29" t="n">
+      <c r="E22" s="27" t="n">
         <f aca="false">SUM('MLB Jul 12'!F7:F14)</f>
         <v>1000</v>
       </c>
-      <c r="F22" s="29" t="n">
+      <c r="F22" s="27" t="n">
         <f aca="false">SUMIF('MLB Jul 12'!I7:I14,"Pending",'MLB Jul 12'!F7:F14)</f>
         <v>0</v>
       </c>
-      <c r="G22" s="29" t="n">
+      <c r="G22" s="27" t="n">
         <f aca="false">SUM('MLB Jul 12'!J7:J14)</f>
         <v>802.232258064516</v>
       </c>
-      <c r="H22" s="29" t="n">
+      <c r="H22" s="27" t="n">
         <f aca="false">SUM('MLB Jul 12'!K7:K14)</f>
         <v>-197.767741935484</v>
       </c>
-      <c r="I22" s="20"/>
-      <c r="J22" s="21"/>
-      <c r="K22" s="13"/>
-      <c r="L22" s="13"/>
-      <c r="M22" s="13"/>
+      <c r="I22" s="18"/>
+      <c r="J22" s="19"/>
+      <c r="K22" s="1"/>
+      <c r="L22" s="1"/>
+      <c r="M22" s="1"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="26" t="n">
+      <c r="A23" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="B23" s="27" t="s">
+      <c r="B23" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="C23" s="26" t="s">
+      <c r="C23" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="D23" s="28" t="s">
+      <c r="D23" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="E23" s="29" t="n">
+      <c r="E23" s="27" t="n">
         <f aca="false">SUM('UFC 329'!F7:F15)</f>
         <v>1050</v>
       </c>
-      <c r="F23" s="29" t="n">
+      <c r="F23" s="27" t="n">
         <f aca="false">SUMIF('UFC 329'!I7:I15,"Pending",'UFC 329'!F7:F15)</f>
         <v>0</v>
       </c>
-      <c r="G23" s="29" t="n">
+      <c r="G23" s="27" t="n">
         <f aca="false">SUM('UFC 329'!J7:J15)</f>
         <v>1215.1103728313</v>
       </c>
-      <c r="H23" s="29" t="n">
+      <c r="H23" s="27" t="n">
         <f aca="false">SUM('UFC 329'!K7:K15)</f>
         <v>165.110372831303</v>
       </c>
-      <c r="I23" s="30"/>
-      <c r="J23" s="30"/>
-      <c r="K23" s="13"/>
-      <c r="L23" s="13"/>
-      <c r="M23" s="13"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="13"/>
-      <c r="B24" s="31" t="s">
+      <c r="I23" s="28"/>
+      <c r="J23" s="28"/>
+      <c r="K23" s="1"/>
+      <c r="L23" s="1"/>
+      <c r="M23" s="1"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B24" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="C24" s="13"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="32" t="n">
+      <c r="E24" s="8" t="n">
         <f aca="false">SUM(E16:E23)</f>
         <v>6650</v>
       </c>
-      <c r="F24" s="32" t="n">
+      <c r="F24" s="8" t="n">
         <f aca="false">SUM(F16:F23)</f>
-        <v>2600</v>
-      </c>
-      <c r="G24" s="32" t="n">
+        <v>2475</v>
+      </c>
+      <c r="G24" s="8" t="n">
         <f aca="false">SUM(G16:G23)</f>
-        <v>3284.67586625339</v>
-      </c>
-      <c r="H24" s="32" t="n">
+        <v>3523.31222988975</v>
+      </c>
+      <c r="H24" s="8" t="n">
         <f aca="false">SUM(H16:H23)</f>
-        <v>-765.324133746613</v>
-      </c>
-      <c r="I24" s="13"/>
-      <c r="J24" s="13"/>
-      <c r="K24" s="13"/>
-      <c r="L24" s="13"/>
-      <c r="M24" s="13"/>
+        <v>-651.687770110249</v>
+      </c>
+      <c r="K24" s="1"/>
+      <c r="L24" s="1"/>
+      <c r="M24" s="1"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="12"/>
-      <c r="B25" s="13"/>
-      <c r="C25" s="13"/>
-      <c r="D25" s="13"/>
-      <c r="E25" s="13"/>
-      <c r="F25" s="13"/>
-      <c r="G25" s="13"/>
-      <c r="H25" s="13"/>
-      <c r="I25" s="13"/>
-      <c r="J25" s="13"/>
-      <c r="K25" s="13"/>
-      <c r="L25" s="13"/>
-      <c r="M25" s="13"/>
+      <c r="A25" s="4"/>
+      <c r="K25" s="1"/>
+      <c r="L25" s="1"/>
+      <c r="M25" s="1"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="33" t="s">
+      <c r="A26" s="29" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="15"/>
-      <c r="C26" s="15"/>
-      <c r="D26" s="15"/>
-      <c r="E26" s="15"/>
-      <c r="F26" s="13"/>
-      <c r="G26" s="13"/>
-      <c r="H26" s="13"/>
-      <c r="I26" s="13"/>
-      <c r="J26" s="13"/>
-      <c r="K26" s="13"/>
-      <c r="L26" s="13"/>
-      <c r="M26" s="13"/>
+      <c r="B26" s="13"/>
+      <c r="C26" s="13"/>
+      <c r="D26" s="13"/>
+      <c r="E26" s="13"/>
+      <c r="K26" s="1"/>
+      <c r="L26" s="1"/>
+      <c r="M26" s="1"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="14" t="s">
+      <c r="A27" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="14" t="s">
+      <c r="B27" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="C27" s="14" t="s">
+      <c r="C27" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="D27" s="34" t="s">
+      <c r="D27" s="30" t="s">
         <v>42</v>
       </c>
-      <c r="E27" s="14" t="s">
+      <c r="E27" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="F27" s="13"/>
-      <c r="G27" s="13"/>
-      <c r="H27" s="13"/>
-      <c r="I27" s="13"/>
-      <c r="J27" s="13"/>
-      <c r="K27" s="13"/>
-      <c r="L27" s="13"/>
-      <c r="M27" s="13"/>
+      <c r="K27" s="1"/>
+      <c r="L27" s="1"/>
+      <c r="M27" s="1"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="35" t="s">
+      <c r="A28" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="B28" s="35" t="s">
+      <c r="B28" s="31" t="s">
         <v>44</v>
       </c>
-      <c r="C28" s="36" t="s">
+      <c r="C28" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="D28" s="37" t="n">
+      <c r="D28" s="33" t="n">
         <v>0</v>
       </c>
       <c r="E28" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="F28" s="13"/>
-      <c r="G28" s="13"/>
-      <c r="H28" s="13"/>
-      <c r="I28" s="13"/>
-      <c r="J28" s="13"/>
-      <c r="K28" s="13"/>
-      <c r="L28" s="13"/>
-      <c r="M28" s="13"/>
+      <c r="K28" s="1"/>
+      <c r="L28" s="1"/>
+      <c r="M28" s="1"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="35" t="s">
+      <c r="A29" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="B29" s="35" t="s">
+      <c r="B29" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="C29" s="36" t="s">
+      <c r="C29" s="32" t="s">
         <v>49</v>
       </c>
-      <c r="D29" s="37" t="n">
+      <c r="D29" s="33" t="n">
         <v>50</v>
       </c>
       <c r="E29" s="10" t="str">
         <f aca="false">IF('MLB Jul 12'!I14="Win","HIT",IF('MLB Jul 12'!I14="Loss","MISS","Pending"))</f>
         <v>MISS</v>
       </c>
-      <c r="F29" s="13"/>
-      <c r="G29" s="13"/>
-      <c r="H29" s="13"/>
-      <c r="I29" s="13"/>
-      <c r="J29" s="13"/>
-      <c r="K29" s="13"/>
-      <c r="L29" s="13"/>
-      <c r="M29" s="13"/>
+      <c r="K29" s="1"/>
+      <c r="L29" s="1"/>
+      <c r="M29" s="1"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="35" t="s">
+      <c r="A30" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="B30" s="35" t="s">
+      <c r="B30" s="31" t="s">
         <v>51</v>
       </c>
-      <c r="C30" s="36" t="s">
+      <c r="C30" s="32" t="s">
         <v>52</v>
       </c>
-      <c r="D30" s="37" t="n">
+      <c r="D30" s="33" t="n">
         <v>40</v>
       </c>
       <c r="E30" s="10" t="str">
         <f aca="false">IF('NASCAR Jul 12'!I13="Win","HIT",IF('NASCAR Jul 12'!I13="Loss","MISS","Pending"))</f>
         <v>MISS</v>
       </c>
-      <c r="F30" s="13"/>
-      <c r="G30" s="13"/>
-      <c r="H30" s="13"/>
-      <c r="I30" s="13"/>
-      <c r="J30" s="13"/>
-      <c r="K30" s="13"/>
-      <c r="L30" s="13"/>
-      <c r="M30" s="13"/>
+      <c r="K30" s="1"/>
+      <c r="L30" s="1"/>
+      <c r="M30" s="1"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="35" t="s">
+      <c r="A31" s="31" t="s">
         <v>53</v>
       </c>
-      <c r="B31" s="35" t="s">
+      <c r="B31" s="31" t="s">
         <v>54</v>
       </c>
-      <c r="C31" s="36" t="s">
+      <c r="C31" s="32" t="s">
         <v>55</v>
       </c>
-      <c r="D31" s="37" t="n">
+      <c r="D31" s="33" t="n">
         <v>100</v>
       </c>
       <c r="E31" s="10" t="str">
         <f aca="false">IF('WNBA Jul 12'!I13="Win","HIT",IF('WNBA Jul 12'!I13="Loss","MISS","Pending"))</f>
         <v>MISS</v>
       </c>
-      <c r="F31" s="13"/>
-      <c r="G31" s="13"/>
-      <c r="H31" s="13"/>
-      <c r="I31" s="13"/>
-      <c r="J31" s="13"/>
-      <c r="K31" s="13"/>
-      <c r="L31" s="13"/>
-      <c r="M31" s="13"/>
+      <c r="K31" s="1"/>
+      <c r="L31" s="1"/>
+      <c r="M31" s="1"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="35" t="s">
+      <c r="A32" s="31" t="s">
         <v>56</v>
       </c>
-      <c r="B32" s="35" t="s">
+      <c r="B32" s="31" t="s">
         <v>57</v>
       </c>
-      <c r="C32" s="36" t="s">
+      <c r="C32" s="32" t="s">
         <v>58</v>
       </c>
-      <c r="D32" s="37" t="n">
+      <c r="D32" s="33" t="n">
         <v>50</v>
       </c>
       <c r="E32" s="10" t="str">
         <f aca="false">IF('The Open'!I12="Win","HIT",IF('The Open'!I12="Loss","MISS","Pending"))</f>
         <v>Pending</v>
       </c>
-      <c r="F32" s="13"/>
-      <c r="G32" s="13"/>
-      <c r="H32" s="13"/>
-      <c r="I32" s="13"/>
-      <c r="J32" s="13"/>
-      <c r="K32" s="13"/>
-      <c r="L32" s="13"/>
-      <c r="M32" s="13"/>
+      <c r="K32" s="1"/>
+      <c r="L32" s="1"/>
+      <c r="M32" s="1"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="35" t="s">
+      <c r="A33" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="B33" s="35" t="s">
+      <c r="B33" s="31" t="s">
         <v>60</v>
       </c>
-      <c r="C33" s="36" t="s">
+      <c r="C33" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="D33" s="37" t="n">
+      <c r="D33" s="33" t="n">
         <v>0</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="F33" s="13"/>
-      <c r="G33" s="13"/>
-      <c r="H33" s="13"/>
-      <c r="I33" s="13"/>
-      <c r="J33" s="13"/>
-      <c r="K33" s="13"/>
-      <c r="L33" s="13"/>
-      <c r="M33" s="13"/>
+      <c r="K33" s="1"/>
+      <c r="L33" s="1"/>
+      <c r="M33" s="1"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="35" t="s">
+      <c r="A34" s="31" t="s">
         <v>63</v>
       </c>
-      <c r="B34" s="35" t="s">
+      <c r="B34" s="31" t="s">
         <v>64</v>
       </c>
-      <c r="C34" s="36" t="s">
+      <c r="C34" s="32" t="s">
         <v>65</v>
       </c>
-      <c r="D34" s="37" t="n">
+      <c r="D34" s="33" t="n">
         <v>75</v>
       </c>
       <c r="E34" s="10" t="str">
         <f aca="false">IF('HR Derby'!I13="Win","HIT",IF('HR Derby'!I13="Loss","MISS","Pending"))</f>
         <v>Pending</v>
       </c>
-      <c r="F34" s="13"/>
-      <c r="G34" s="13"/>
-      <c r="H34" s="13"/>
-      <c r="I34" s="13"/>
-      <c r="J34" s="13"/>
-      <c r="K34" s="13"/>
-      <c r="L34" s="13"/>
-      <c r="M34" s="13"/>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="31" t="s">
+      <c r="K34" s="1"/>
+      <c r="L34" s="1"/>
+      <c r="M34" s="1"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="B35" s="13"/>
-      <c r="C35" s="13"/>
-      <c r="D35" s="13"/>
       <c r="E35" s="10" t="str">
         <f aca="false">IF(COUNTIF(E28:E34,"HIT")+COUNTIF(E28:E34,"MISS")=0,"—",COUNTIF(E28:E34,"HIT")&amp;"-for-"&amp;(COUNTIF(E28:E34,"HIT")+COUNTIF(E28:E34,"MISS"))&amp;" ("&amp;TEXT(COUNTIF(E28:E34,"HIT")/(COUNTIF(E28:E34,"HIT")+COUNTIF(E28:E34,"MISS")),"0%")&amp;")")</f>
         <v>0-for-4 (0%)</v>
       </c>
-      <c r="F35" s="13"/>
-      <c r="G35" s="13"/>
-      <c r="H35" s="13"/>
-      <c r="I35" s="13"/>
-      <c r="J35" s="13"/>
-      <c r="K35" s="13"/>
-      <c r="L35" s="13"/>
-      <c r="M35" s="13"/>
+      <c r="K35" s="1"/>
+      <c r="L35" s="1"/>
+      <c r="M35" s="1"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="38" t="s">
+      <c r="A36" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B36" s="13"/>
-      <c r="C36" s="13"/>
-      <c r="D36" s="13"/>
-      <c r="E36" s="13"/>
-      <c r="F36" s="13"/>
-      <c r="G36" s="13"/>
-      <c r="H36" s="13"/>
-      <c r="I36" s="13"/>
-      <c r="J36" s="13"/>
-      <c r="K36" s="13"/>
-      <c r="L36" s="13"/>
-      <c r="M36" s="13"/>
+      <c r="K36" s="1"/>
+      <c r="L36" s="1"/>
+      <c r="M36" s="1"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="39"/>
-      <c r="B37" s="13"/>
-      <c r="C37" s="13"/>
-      <c r="D37" s="13"/>
-      <c r="E37" s="13"/>
-      <c r="F37" s="13"/>
-      <c r="G37" s="13"/>
-      <c r="H37" s="13"/>
-      <c r="I37" s="13"/>
-      <c r="J37" s="13"/>
-      <c r="K37" s="13"/>
-      <c r="L37" s="13"/>
-      <c r="M37" s="13"/>
+      <c r="A37" s="34"/>
+      <c r="K37" s="1"/>
+      <c r="L37" s="1"/>
+      <c r="M37" s="1"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="39"/>
-      <c r="B38" s="13"/>
-      <c r="C38" s="13"/>
-      <c r="D38" s="13"/>
-      <c r="E38" s="13"/>
-      <c r="F38" s="13"/>
-      <c r="G38" s="13"/>
-      <c r="H38" s="13"/>
-      <c r="I38" s="13"/>
-      <c r="J38" s="13"/>
-      <c r="K38" s="13"/>
-      <c r="L38" s="13"/>
-      <c r="M38" s="13"/>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="13"/>
-      <c r="B39" s="13"/>
-      <c r="C39" s="13"/>
-      <c r="D39" s="13"/>
-      <c r="E39" s="13"/>
-      <c r="F39" s="13"/>
-      <c r="G39" s="13"/>
-      <c r="H39" s="13"/>
-      <c r="I39" s="13"/>
-      <c r="J39" s="13"/>
-      <c r="K39" s="13"/>
-      <c r="L39" s="13"/>
-      <c r="M39" s="13"/>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="13"/>
-      <c r="B40" s="13"/>
-      <c r="C40" s="13"/>
-      <c r="D40" s="13"/>
-      <c r="E40" s="13"/>
-      <c r="F40" s="13"/>
-      <c r="G40" s="13"/>
-      <c r="H40" s="13"/>
-      <c r="I40" s="13"/>
-      <c r="J40" s="13"/>
-      <c r="K40" s="13"/>
-      <c r="L40" s="13"/>
-      <c r="M40" s="13"/>
+      <c r="A38" s="34"/>
+      <c r="K38" s="1"/>
+      <c r="L38" s="1"/>
+      <c r="M38" s="1"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="K39" s="1"/>
+      <c r="L39" s="1"/>
+      <c r="M39" s="1"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="K40" s="1"/>
+      <c r="L40" s="1"/>
+      <c r="M40" s="1"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="H16:H23">
@@ -3133,10 +2927,10 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H16:H24">
-    <cfRule type="expression" priority="10" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+    <cfRule type="expression" priority="10" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>AND(ISNUMBER(H16),H16&gt;0)</formula>
     </cfRule>
-    <cfRule type="expression" priority="11" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+    <cfRule type="expression" priority="11" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>AND(ISNUMBER(H16),H16&lt;0)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3172,10 +2966,10 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="35" t="s">
         <v>68</v>
       </c>
-      <c r="H1" s="41" t="s">
+      <c r="H1" s="36" t="s">
         <v>69</v>
       </c>
     </row>
@@ -3195,451 +2989,451 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="14" t="s">
+      <c r="A6" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="D6" s="14" t="s">
+      <c r="D6" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="E6" s="14" t="s">
+      <c r="E6" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="F6" s="14" t="s">
+      <c r="F6" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="G6" s="14" t="s">
+      <c r="G6" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="H6" s="14" t="s">
+      <c r="H6" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="I6" s="14" t="s">
+      <c r="I6" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="J6" s="14" t="s">
+      <c r="J6" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="K6" s="14" t="s">
+      <c r="K6" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="L6" s="14" t="s">
+      <c r="L6" s="12" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="36" t="n">
+      <c r="A7" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="42" t="s">
+      <c r="B7" s="37" t="s">
         <v>83</v>
       </c>
-      <c r="C7" s="43" t="s">
+      <c r="C7" s="38" t="s">
         <v>84</v>
       </c>
-      <c r="D7" s="36" t="s">
+      <c r="D7" s="32" t="s">
         <v>85</v>
       </c>
-      <c r="E7" s="44" t="n">
+      <c r="E7" s="39" t="n">
         <v>-265</v>
       </c>
-      <c r="F7" s="45" t="n">
+      <c r="F7" s="40" t="n">
         <v>265</v>
       </c>
-      <c r="G7" s="46" t="n">
+      <c r="G7" s="41" t="n">
         <f aca="false">IF(E7&gt;0,F7*E7/100,F7*100/ABS(E7))</f>
         <v>100</v>
       </c>
-      <c r="H7" s="46" t="n">
+      <c r="H7" s="41" t="n">
         <f aca="false">F7+G7</f>
         <v>365</v>
       </c>
-      <c r="I7" s="47" t="s">
+      <c r="I7" s="42" t="s">
         <v>86</v>
       </c>
-      <c r="J7" s="46" t="n">
+      <c r="J7" s="41" t="n">
         <f aca="false">IF(I7="Win",F7+G7,IF(I7="Push",F7,IF(I7="Loss",0,0)))</f>
         <v>365</v>
       </c>
-      <c r="K7" s="48" t="n">
+      <c r="K7" s="43" t="n">
         <f aca="false">IF(I7="Pending",0,J7-F7)</f>
         <v>100</v>
       </c>
-      <c r="L7" s="49" t="s">
+      <c r="L7" s="44" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="36" t="n">
+      <c r="A8" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="42" t="s">
+      <c r="B8" s="37" t="s">
         <v>88</v>
       </c>
-      <c r="C8" s="43" t="s">
+      <c r="C8" s="38" t="s">
         <v>89</v>
       </c>
-      <c r="D8" s="36" t="s">
+      <c r="D8" s="32" t="s">
         <v>90</v>
       </c>
-      <c r="E8" s="44" t="n">
+      <c r="E8" s="39" t="n">
         <v>-140</v>
       </c>
-      <c r="F8" s="45" t="n">
+      <c r="F8" s="40" t="n">
         <v>200</v>
       </c>
-      <c r="G8" s="46" t="n">
+      <c r="G8" s="41" t="n">
         <f aca="false">IF(E8&gt;0,F8*E8/100,F8*100/ABS(E8))</f>
         <v>142.857142857143</v>
       </c>
-      <c r="H8" s="46" t="n">
+      <c r="H8" s="41" t="n">
         <f aca="false">F8+G8</f>
         <v>342.857142857143</v>
       </c>
-      <c r="I8" s="47" t="s">
+      <c r="I8" s="42" t="s">
         <v>86</v>
       </c>
-      <c r="J8" s="46" t="n">
+      <c r="J8" s="41" t="n">
         <f aca="false">IF(I8="Win",F8+G8,IF(I8="Push",F8,IF(I8="Loss",0,0)))</f>
         <v>342.857142857143</v>
       </c>
-      <c r="K8" s="48" t="n">
+      <c r="K8" s="43" t="n">
         <f aca="false">IF(I8="Pending",0,J8-F8)</f>
         <v>142.857142857143</v>
       </c>
-      <c r="L8" s="49" t="s">
+      <c r="L8" s="44" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="36" t="n">
+      <c r="A9" s="32" t="n">
         <v>3</v>
       </c>
-      <c r="B9" s="42" t="s">
+      <c r="B9" s="37" t="s">
         <v>92</v>
       </c>
-      <c r="C9" s="43" t="s">
+      <c r="C9" s="38" t="s">
         <v>93</v>
       </c>
-      <c r="D9" s="36" t="s">
+      <c r="D9" s="32" t="s">
         <v>85</v>
       </c>
-      <c r="E9" s="44" t="n">
+      <c r="E9" s="39" t="n">
         <v>-148</v>
       </c>
-      <c r="F9" s="45" t="n">
+      <c r="F9" s="40" t="n">
         <v>148</v>
       </c>
-      <c r="G9" s="46" t="n">
+      <c r="G9" s="41" t="n">
         <f aca="false">IF(E9&gt;0,F9*E9/100,F9*100/ABS(E9))</f>
         <v>100</v>
       </c>
-      <c r="H9" s="46" t="n">
+      <c r="H9" s="41" t="n">
         <f aca="false">F9+G9</f>
         <v>248</v>
       </c>
-      <c r="I9" s="50" t="s">
+      <c r="I9" s="45" t="s">
         <v>94</v>
       </c>
-      <c r="J9" s="46" t="n">
+      <c r="J9" s="41" t="n">
         <f aca="false">IF(I9="Win",F9+G9,IF(I9="Push",F9,IF(I9="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K9" s="48" t="n">
+      <c r="K9" s="43" t="n">
         <f aca="false">IF(I9="Pending",0,J9-F9)</f>
         <v>-148</v>
       </c>
-      <c r="L9" s="49" t="s">
+      <c r="L9" s="44" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="36" t="n">
+      <c r="A10" s="32" t="n">
         <v>4</v>
       </c>
-      <c r="B10" s="42" t="s">
+      <c r="B10" s="37" t="s">
         <v>96</v>
       </c>
-      <c r="C10" s="43" t="s">
+      <c r="C10" s="38" t="s">
         <v>97</v>
       </c>
-      <c r="D10" s="36" t="s">
+      <c r="D10" s="32" t="s">
         <v>85</v>
       </c>
-      <c r="E10" s="44" t="n">
+      <c r="E10" s="39" t="n">
         <v>114</v>
       </c>
-      <c r="F10" s="45" t="n">
+      <c r="F10" s="40" t="n">
         <v>100</v>
       </c>
-      <c r="G10" s="46" t="n">
+      <c r="G10" s="41" t="n">
         <f aca="false">IF(E10&gt;0,F10*E10/100,F10*100/ABS(E10))</f>
         <v>114</v>
       </c>
-      <c r="H10" s="46" t="n">
+      <c r="H10" s="41" t="n">
         <f aca="false">F10+G10</f>
         <v>214</v>
       </c>
-      <c r="I10" s="47" t="s">
+      <c r="I10" s="42" t="s">
         <v>86</v>
       </c>
-      <c r="J10" s="46" t="n">
+      <c r="J10" s="41" t="n">
         <f aca="false">IF(I10="Win",F10+G10,IF(I10="Push",F10,IF(I10="Loss",0,0)))</f>
         <v>214</v>
       </c>
-      <c r="K10" s="48" t="n">
+      <c r="K10" s="43" t="n">
         <f aca="false">IF(I10="Pending",0,J10-F10)</f>
         <v>114</v>
       </c>
-      <c r="L10" s="49" t="s">
+      <c r="L10" s="44" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="36" t="n">
+      <c r="A11" s="32" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="42" t="s">
+      <c r="B11" s="37" t="s">
         <v>99</v>
       </c>
-      <c r="C11" s="43" t="s">
+      <c r="C11" s="38" t="s">
         <v>100</v>
       </c>
-      <c r="D11" s="36" t="s">
+      <c r="D11" s="32" t="s">
         <v>85</v>
       </c>
-      <c r="E11" s="44" t="n">
+      <c r="E11" s="39" t="n">
         <v>-218</v>
       </c>
-      <c r="F11" s="45" t="n">
+      <c r="F11" s="40" t="n">
         <v>100</v>
       </c>
-      <c r="G11" s="46" t="n">
+      <c r="G11" s="41" t="n">
         <f aca="false">IF(E11&gt;0,F11*E11/100,F11*100/ABS(E11))</f>
         <v>45.8715596330275</v>
       </c>
-      <c r="H11" s="46" t="n">
+      <c r="H11" s="41" t="n">
         <f aca="false">F11+G11</f>
         <v>145.871559633028</v>
       </c>
-      <c r="I11" s="50" t="s">
+      <c r="I11" s="45" t="s">
         <v>94</v>
       </c>
-      <c r="J11" s="46" t="n">
+      <c r="J11" s="41" t="n">
         <f aca="false">IF(I11="Win",F11+G11,IF(I11="Push",F11,IF(I11="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K11" s="48" t="n">
+      <c r="K11" s="43" t="n">
         <f aca="false">IF(I11="Pending",0,J11-F11)</f>
         <v>-100</v>
       </c>
-      <c r="L11" s="49" t="s">
+      <c r="L11" s="44" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="36" t="n">
+      <c r="A12" s="32" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="42" t="s">
+      <c r="B12" s="37" t="s">
         <v>102</v>
       </c>
-      <c r="C12" s="43" t="s">
+      <c r="C12" s="38" t="s">
         <v>103</v>
       </c>
-      <c r="D12" s="36" t="s">
+      <c r="D12" s="32" t="s">
         <v>85</v>
       </c>
-      <c r="E12" s="44" t="n">
+      <c r="E12" s="39" t="n">
         <v>-125</v>
       </c>
-      <c r="F12" s="45" t="n">
+      <c r="F12" s="40" t="n">
         <v>75</v>
       </c>
-      <c r="G12" s="46" t="n">
+      <c r="G12" s="41" t="n">
         <f aca="false">IF(E12&gt;0,F12*E12/100,F12*100/ABS(E12))</f>
         <v>60</v>
       </c>
-      <c r="H12" s="46" t="n">
+      <c r="H12" s="41" t="n">
         <f aca="false">F12+G12</f>
         <v>135</v>
       </c>
-      <c r="I12" s="47" t="s">
+      <c r="I12" s="42" t="s">
         <v>86</v>
       </c>
-      <c r="J12" s="46" t="n">
+      <c r="J12" s="41" t="n">
         <f aca="false">IF(I12="Win",F12+G12,IF(I12="Push",F12,IF(I12="Loss",0,0)))</f>
         <v>135</v>
       </c>
-      <c r="K12" s="48" t="n">
+      <c r="K12" s="43" t="n">
         <f aca="false">IF(I12="Pending",0,J12-F12)</f>
         <v>60</v>
       </c>
-      <c r="L12" s="49" t="s">
+      <c r="L12" s="44" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="36" t="n">
+      <c r="A13" s="32" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="42" t="s">
+      <c r="B13" s="37" t="s">
         <v>105</v>
       </c>
-      <c r="C13" s="43" t="s">
+      <c r="C13" s="38" t="s">
         <v>106</v>
       </c>
-      <c r="D13" s="36" t="s">
+      <c r="D13" s="32" t="s">
         <v>85</v>
       </c>
-      <c r="E13" s="44" t="n">
+      <c r="E13" s="39" t="n">
         <v>-225</v>
       </c>
-      <c r="F13" s="45" t="n">
+      <c r="F13" s="40" t="n">
         <v>50</v>
       </c>
-      <c r="G13" s="46" t="n">
+      <c r="G13" s="41" t="n">
         <f aca="false">IF(E13&gt;0,F13*E13/100,F13*100/ABS(E13))</f>
         <v>22.2222222222222</v>
       </c>
-      <c r="H13" s="46" t="n">
+      <c r="H13" s="41" t="n">
         <f aca="false">F13+G13</f>
         <v>72.2222222222222</v>
       </c>
-      <c r="I13" s="47" t="s">
+      <c r="I13" s="42" t="s">
         <v>86</v>
       </c>
-      <c r="J13" s="46" t="n">
+      <c r="J13" s="41" t="n">
         <f aca="false">IF(I13="Win",F13+G13,IF(I13="Push",F13,IF(I13="Loss",0,0)))</f>
         <v>72.2222222222222</v>
       </c>
-      <c r="K13" s="48" t="n">
+      <c r="K13" s="43" t="n">
         <f aca="false">IF(I13="Pending",0,J13-F13)</f>
         <v>22.2222222222222</v>
       </c>
-      <c r="L13" s="49" t="s">
+      <c r="L13" s="44" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="36" t="n">
+      <c r="A14" s="32" t="n">
         <v>8</v>
       </c>
-      <c r="B14" s="42" t="s">
+      <c r="B14" s="37" t="s">
         <v>108</v>
       </c>
-      <c r="C14" s="43" t="s">
+      <c r="C14" s="38" t="s">
         <v>109</v>
       </c>
-      <c r="D14" s="36" t="s">
+      <c r="D14" s="32" t="s">
         <v>85</v>
       </c>
-      <c r="E14" s="44" t="n">
+      <c r="E14" s="39" t="n">
         <v>-258</v>
       </c>
-      <c r="F14" s="45" t="n">
+      <c r="F14" s="40" t="n">
         <v>62</v>
       </c>
-      <c r="G14" s="46" t="n">
+      <c r="G14" s="41" t="n">
         <f aca="false">IF(E14&gt;0,F14*E14/100,F14*100/ABS(E14))</f>
         <v>24.031007751938</v>
       </c>
-      <c r="H14" s="46" t="n">
+      <c r="H14" s="41" t="n">
         <f aca="false">F14+G14</f>
         <v>86.031007751938</v>
       </c>
-      <c r="I14" s="47" t="s">
+      <c r="I14" s="42" t="s">
         <v>86</v>
       </c>
-      <c r="J14" s="46" t="n">
+      <c r="J14" s="41" t="n">
         <f aca="false">IF(I14="Win",F14+G14,IF(I14="Push",F14,IF(I14="Loss",0,0)))</f>
         <v>86.031007751938</v>
       </c>
-      <c r="K14" s="48" t="n">
+      <c r="K14" s="43" t="n">
         <f aca="false">IF(I14="Pending",0,J14-F14)</f>
         <v>24.031007751938</v>
       </c>
-      <c r="L14" s="49" t="s">
+      <c r="L14" s="44" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="36" t="n">
+      <c r="A15" s="32" t="n">
         <v>9</v>
       </c>
-      <c r="B15" s="42" t="s">
+      <c r="B15" s="37" t="s">
         <v>111</v>
       </c>
-      <c r="C15" s="43" t="s">
+      <c r="C15" s="38" t="s">
         <v>112</v>
       </c>
-      <c r="D15" s="36" t="s">
+      <c r="D15" s="32" t="s">
         <v>113</v>
       </c>
-      <c r="E15" s="44" t="n">
+      <c r="E15" s="39" t="n">
         <v>443</v>
       </c>
-      <c r="F15" s="45" t="n">
+      <c r="F15" s="40" t="n">
         <v>50</v>
       </c>
-      <c r="G15" s="46" t="n">
+      <c r="G15" s="41" t="n">
         <f aca="false">IF(E15&gt;0,F15*E15/100,F15*100/ABS(E15))</f>
         <v>221.5</v>
       </c>
-      <c r="H15" s="46" t="n">
+      <c r="H15" s="41" t="n">
         <f aca="false">F15+G15</f>
         <v>271.5</v>
       </c>
-      <c r="I15" s="50" t="s">
+      <c r="I15" s="45" t="s">
         <v>94</v>
       </c>
-      <c r="J15" s="46" t="n">
+      <c r="J15" s="41" t="n">
         <f aca="false">IF(I15="Win",F15+G15,IF(I15="Push",F15,IF(I15="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K15" s="48" t="n">
+      <c r="K15" s="43" t="n">
         <f aca="false">IF(I15="Pending",0,J15-F15)</f>
         <v>-50</v>
       </c>
-      <c r="L15" s="49" t="s">
+      <c r="L15" s="44" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="51"/>
-      <c r="B16" s="52" t="s">
+      <c r="A16" s="46"/>
+      <c r="B16" s="47" t="s">
         <v>37</v>
       </c>
-      <c r="C16" s="51"/>
-      <c r="D16" s="51"/>
-      <c r="E16" s="51"/>
-      <c r="F16" s="53" t="n">
+      <c r="C16" s="46"/>
+      <c r="D16" s="46"/>
+      <c r="E16" s="46"/>
+      <c r="F16" s="48" t="n">
         <f aca="false">SUM(F7:F15)</f>
         <v>1050</v>
       </c>
-      <c r="G16" s="54" t="n">
+      <c r="G16" s="49" t="n">
         <f aca="false">SUM(G7:G15)</f>
         <v>830.481932464331</v>
       </c>
-      <c r="H16" s="54" t="n">
+      <c r="H16" s="49" t="n">
         <f aca="false">SUM(H7:H15)</f>
         <v>1880.48193246433</v>
       </c>
-      <c r="I16" s="51"/>
-      <c r="J16" s="54" t="n">
+      <c r="I16" s="46"/>
+      <c r="J16" s="49" t="n">
         <f aca="false">SUM(J7:J15)</f>
         <v>1215.1103728313</v>
       </c>
-      <c r="K16" s="55" t="n">
+      <c r="K16" s="50" t="n">
         <f aca="false">SUM(K7:K15)</f>
         <v>165.110372831303</v>
       </c>
-      <c r="L16" s="51"/>
+      <c r="L16" s="46"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="4" t="s">
@@ -3647,91 +3441,91 @@
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="42" t="s">
+      <c r="B19" s="37" t="s">
         <v>116</v>
       </c>
-      <c r="C19" s="56" t="n">
+      <c r="C19" s="51" t="n">
         <f aca="false">COUNTIF(I7:I15,"Win")</f>
         <v>6</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="42" t="s">
+      <c r="B20" s="37" t="s">
         <v>117</v>
       </c>
-      <c r="C20" s="56" t="n">
+      <c r="C20" s="51" t="n">
         <f aca="false">COUNTIF(I7:I15,"Loss")</f>
         <v>3</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="42" t="s">
+      <c r="B21" s="37" t="s">
         <v>118</v>
       </c>
-      <c r="C21" s="56" t="n">
+      <c r="C21" s="51" t="n">
         <f aca="false">COUNTIF(I7:I15,"Push")</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="42" t="s">
+      <c r="B22" s="37" t="s">
         <v>119</v>
       </c>
-      <c r="C22" s="56" t="n">
+      <c r="C22" s="51" t="n">
         <f aca="false">COUNTIF(I7:I15,"Pending")</f>
         <v>0</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="42" t="s">
+      <c r="B23" s="37" t="s">
         <v>120</v>
       </c>
-      <c r="C23" s="57" t="n">
+      <c r="C23" s="52" t="n">
         <f aca="false">IF(COUNTIF(I7:I15,"Win")+COUNTIF(I7:I15,"Loss")=0,"—",COUNTIF(I7:I15,"Win")/(COUNTIF(I7:I15,"Win")+COUNTIF(I7:I15,"Loss")))</f>
         <v>0.666666666666667</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="42" t="s">
+      <c r="B24" s="37" t="s">
         <v>121</v>
       </c>
-      <c r="C24" s="58" t="n">
+      <c r="C24" s="33" t="n">
         <f aca="false">SUM(F7:F15)</f>
         <v>1050</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="42" t="s">
+      <c r="B25" s="37" t="s">
         <v>122</v>
       </c>
-      <c r="C25" s="46" t="n">
+      <c r="C25" s="41" t="n">
         <f aca="false">SUM(J7:J15)</f>
         <v>1215.1103728313</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="42" t="s">
+      <c r="B26" s="37" t="s">
         <v>123</v>
       </c>
-      <c r="C26" s="48" t="n">
+      <c r="C26" s="43" t="n">
         <f aca="false">SUM(K7:K15)</f>
         <v>165.110372831303</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="42" t="s">
+      <c r="B27" s="37" t="s">
         <v>124</v>
       </c>
-      <c r="C27" s="57" t="n">
+      <c r="C27" s="52" t="n">
         <f aca="false">IF(SUM(F7:F15)=0,"—",SUM(K7:K15)/SUM(F7:F15))</f>
         <v>0.157247974125051</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="42" t="s">
+      <c r="B28" s="37" t="s">
         <v>125</v>
       </c>
-      <c r="C28" s="46" t="n">
+      <c r="C28" s="41" t="n">
         <f aca="false">SUM(H7:H15)</f>
         <v>1880.48193246433</v>
       </c>
@@ -3742,157 +3536,157 @@
       </c>
     </row>
     <row r="31" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="14" t="s">
+      <c r="A31" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B31" s="14" t="s">
+      <c r="B31" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="C31" s="14" t="s">
+      <c r="C31" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="D31" s="14" t="s">
+      <c r="D31" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="E31" s="14" t="s">
+      <c r="E31" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="F31" s="14" t="s">
+      <c r="F31" s="12" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="36" t="n">
+      <c r="A32" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="B32" s="42" t="s">
+      <c r="B32" s="37" t="s">
         <v>132</v>
       </c>
-      <c r="C32" s="49" t="s">
+      <c r="C32" s="44" t="s">
         <v>133</v>
       </c>
-      <c r="D32" s="59" t="s">
+      <c r="D32" s="53" t="s">
         <v>134</v>
       </c>
-      <c r="E32" s="60" t="s">
+      <c r="E32" s="54" t="s">
         <v>135</v>
       </c>
-      <c r="F32" s="60" t="s">
+      <c r="F32" s="54" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="36" t="n">
+      <c r="A33" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="B33" s="42" t="s">
+      <c r="B33" s="37" t="s">
         <v>137</v>
       </c>
-      <c r="C33" s="49" t="s">
+      <c r="C33" s="44" t="s">
         <v>138</v>
       </c>
-      <c r="D33" s="59" t="s">
+      <c r="D33" s="53" t="s">
         <v>139</v>
       </c>
-      <c r="E33" s="60" t="s">
+      <c r="E33" s="54" t="s">
         <v>140</v>
       </c>
-      <c r="F33" s="60" t="s">
+      <c r="F33" s="54" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="36" t="n">
+      <c r="A34" s="32" t="n">
         <v>3</v>
       </c>
-      <c r="B34" s="42" t="s">
+      <c r="B34" s="37" t="s">
         <v>142</v>
       </c>
-      <c r="C34" s="49" t="s">
+      <c r="C34" s="44" t="s">
         <v>143</v>
       </c>
-      <c r="D34" s="59" t="s">
+      <c r="D34" s="53" t="s">
         <v>144</v>
       </c>
-      <c r="E34" s="60" t="s">
+      <c r="E34" s="54" t="s">
         <v>145</v>
       </c>
-      <c r="F34" s="60" t="s">
+      <c r="F34" s="54" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="36" t="n">
+      <c r="A35" s="32" t="n">
         <v>4</v>
       </c>
-      <c r="B35" s="42" t="s">
+      <c r="B35" s="37" t="s">
         <v>147</v>
       </c>
-      <c r="C35" s="49" t="s">
+      <c r="C35" s="44" t="s">
         <v>148</v>
       </c>
-      <c r="D35" s="59" t="s">
+      <c r="D35" s="53" t="s">
         <v>149</v>
       </c>
-      <c r="E35" s="60" t="s">
+      <c r="E35" s="54" t="s">
         <v>150</v>
       </c>
-      <c r="F35" s="60" t="s">
+      <c r="F35" s="54" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="36" t="n">
+      <c r="A36" s="32" t="n">
         <v>5</v>
       </c>
-      <c r="B36" s="42" t="s">
+      <c r="B36" s="37" t="s">
         <v>152</v>
       </c>
-      <c r="C36" s="49" t="s">
+      <c r="C36" s="44" t="s">
         <v>153</v>
       </c>
-      <c r="D36" s="59" t="s">
+      <c r="D36" s="53" t="s">
         <v>154</v>
       </c>
-      <c r="E36" s="60" t="s">
+      <c r="E36" s="54" t="s">
         <v>155</v>
       </c>
-      <c r="F36" s="60" t="s">
+      <c r="F36" s="54" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="36" t="n">
+      <c r="A37" s="32" t="n">
         <v>6</v>
       </c>
-      <c r="B37" s="42" t="s">
+      <c r="B37" s="37" t="s">
         <v>157</v>
       </c>
-      <c r="C37" s="49" t="s">
+      <c r="C37" s="44" t="s">
         <v>158</v>
       </c>
-      <c r="D37" s="59" t="s">
+      <c r="D37" s="53" t="s">
         <v>45</v>
       </c>
-      <c r="E37" s="60" t="s">
+      <c r="E37" s="54" t="s">
         <v>159</v>
       </c>
-      <c r="F37" s="60" t="s">
+      <c r="F37" s="54" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="61" t="s">
+      <c r="A39" s="34" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="61" t="s">
+      <c r="A40" s="34" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="61" t="s">
+      <c r="A41" s="34" t="s">
         <v>163</v>
       </c>
     </row>
@@ -3950,10 +3744,10 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="35" t="s">
         <v>164</v>
       </c>
-      <c r="H1" s="62" t="s">
+      <c r="H1" s="55" t="s">
         <v>165</v>
       </c>
     </row>
@@ -3973,367 +3767,367 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="14" t="s">
+      <c r="A6" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="12" t="s">
         <v>168</v>
       </c>
-      <c r="D6" s="14" t="s">
+      <c r="D6" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="E6" s="14" t="s">
+      <c r="E6" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="F6" s="14" t="s">
+      <c r="F6" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="G6" s="14" t="s">
+      <c r="G6" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="H6" s="14" t="s">
+      <c r="H6" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="I6" s="14" t="s">
+      <c r="I6" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="J6" s="14" t="s">
+      <c r="J6" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="K6" s="14" t="s">
+      <c r="K6" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="L6" s="14" t="s">
+      <c r="L6" s="12" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="36" t="n">
+      <c r="A7" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="42" t="s">
+      <c r="B7" s="37" t="s">
         <v>169</v>
       </c>
-      <c r="C7" s="43" t="s">
+      <c r="C7" s="38" t="s">
         <v>170</v>
       </c>
-      <c r="D7" s="36" t="s">
+      <c r="D7" s="32" t="s">
         <v>171</v>
       </c>
-      <c r="E7" s="44" t="n">
+      <c r="E7" s="39" t="n">
         <v>-144</v>
       </c>
-      <c r="F7" s="45" t="n">
+      <c r="F7" s="40" t="n">
         <v>300</v>
       </c>
-      <c r="G7" s="46" t="n">
+      <c r="G7" s="41" t="n">
         <f aca="false">IF(E7&gt;0,F7*E7/100,F7*100/ABS(E7))</f>
         <v>208.333333333333</v>
       </c>
-      <c r="H7" s="46" t="n">
+      <c r="H7" s="41" t="n">
         <f aca="false">F7+G7</f>
         <v>508.333333333333</v>
       </c>
-      <c r="I7" s="63" t="s">
+      <c r="I7" s="56" t="s">
         <v>119</v>
       </c>
-      <c r="J7" s="46" t="n">
+      <c r="J7" s="41" t="n">
         <f aca="false">IF(I7="Win",F7+G7,IF(I7="Push",F7,IF(I7="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K7" s="48" t="n">
+      <c r="K7" s="43" t="n">
         <f aca="false">IF(I7="Pending",0,J7-F7)</f>
         <v>0</v>
       </c>
-      <c r="L7" s="49" t="s">
+      <c r="L7" s="44" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="36" t="n">
+      <c r="A8" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="42" t="s">
+      <c r="B8" s="37" t="s">
         <v>173</v>
       </c>
-      <c r="C8" s="43" t="s">
+      <c r="C8" s="38" t="s">
         <v>174</v>
       </c>
-      <c r="D8" s="36" t="s">
+      <c r="D8" s="32" t="s">
         <v>175</v>
       </c>
-      <c r="E8" s="44" t="n">
+      <c r="E8" s="39" t="n">
         <v>-122</v>
       </c>
-      <c r="F8" s="45" t="n">
+      <c r="F8" s="40" t="n">
         <v>120</v>
       </c>
-      <c r="G8" s="46" t="n">
+      <c r="G8" s="41" t="n">
         <f aca="false">IF(E8&gt;0,F8*E8/100,F8*100/ABS(E8))</f>
         <v>98.3606557377049</v>
       </c>
-      <c r="H8" s="46" t="n">
+      <c r="H8" s="41" t="n">
         <f aca="false">F8+G8</f>
         <v>218.360655737705</v>
       </c>
-      <c r="I8" s="63" t="s">
+      <c r="I8" s="56" t="s">
         <v>119</v>
       </c>
-      <c r="J8" s="46" t="n">
+      <c r="J8" s="41" t="n">
         <f aca="false">IF(I8="Win",F8+G8,IF(I8="Push",F8,IF(I8="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K8" s="48" t="n">
+      <c r="K8" s="43" t="n">
         <f aca="false">IF(I8="Pending",0,J8-F8)</f>
         <v>0</v>
       </c>
-      <c r="L8" s="49" t="s">
+      <c r="L8" s="44" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="36" t="n">
+      <c r="A9" s="32" t="n">
         <v>3</v>
       </c>
-      <c r="B9" s="42" t="s">
+      <c r="B9" s="37" t="s">
         <v>177</v>
       </c>
-      <c r="C9" s="43" t="s">
+      <c r="C9" s="38" t="s">
         <v>178</v>
       </c>
-      <c r="D9" s="36" t="s">
+      <c r="D9" s="32" t="s">
         <v>179</v>
       </c>
-      <c r="E9" s="44" t="n">
+      <c r="E9" s="39" t="n">
         <v>175</v>
       </c>
-      <c r="F9" s="45" t="n">
+      <c r="F9" s="40" t="n">
         <v>150</v>
       </c>
-      <c r="G9" s="46" t="n">
+      <c r="G9" s="41" t="n">
         <f aca="false">IF(E9&gt;0,F9*E9/100,F9*100/ABS(E9))</f>
         <v>262.5</v>
       </c>
-      <c r="H9" s="46" t="n">
+      <c r="H9" s="41" t="n">
         <f aca="false">F9+G9</f>
         <v>412.5</v>
       </c>
-      <c r="I9" s="63" t="s">
+      <c r="I9" s="56" t="s">
         <v>119</v>
       </c>
-      <c r="J9" s="46" t="n">
+      <c r="J9" s="41" t="n">
         <f aca="false">IF(I9="Win",F9+G9,IF(I9="Push",F9,IF(I9="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K9" s="48" t="n">
+      <c r="K9" s="43" t="n">
         <f aca="false">IF(I9="Pending",0,J9-F9)</f>
         <v>0</v>
       </c>
-      <c r="L9" s="49" t="s">
+      <c r="L9" s="44" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="36" t="n">
+      <c r="A10" s="32" t="n">
         <v>4</v>
       </c>
-      <c r="B10" s="42" t="s">
+      <c r="B10" s="37" t="s">
         <v>181</v>
       </c>
-      <c r="C10" s="43" t="s">
+      <c r="C10" s="38" t="s">
         <v>182</v>
       </c>
-      <c r="D10" s="36" t="s">
+      <c r="D10" s="32" t="s">
         <v>179</v>
       </c>
-      <c r="E10" s="44" t="n">
+      <c r="E10" s="39" t="n">
         <v>205</v>
       </c>
-      <c r="F10" s="45" t="n">
+      <c r="F10" s="40" t="n">
         <v>80</v>
       </c>
-      <c r="G10" s="46" t="n">
+      <c r="G10" s="41" t="n">
         <f aca="false">IF(E10&gt;0,F10*E10/100,F10*100/ABS(E10))</f>
         <v>164</v>
       </c>
-      <c r="H10" s="46" t="n">
+      <c r="H10" s="41" t="n">
         <f aca="false">F10+G10</f>
         <v>244</v>
       </c>
-      <c r="I10" s="63" t="s">
+      <c r="I10" s="56" t="s">
         <v>119</v>
       </c>
-      <c r="J10" s="46" t="n">
+      <c r="J10" s="41" t="n">
         <f aca="false">IF(I10="Win",F10+G10,IF(I10="Push",F10,IF(I10="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K10" s="48" t="n">
+      <c r="K10" s="43" t="n">
         <f aca="false">IF(I10="Pending",0,J10-F10)</f>
         <v>0</v>
       </c>
-      <c r="L10" s="49" t="s">
+      <c r="L10" s="44" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="36" t="n">
+      <c r="A11" s="32" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="42" t="s">
+      <c r="B11" s="37" t="s">
         <v>184</v>
       </c>
-      <c r="C11" s="43" t="s">
+      <c r="C11" s="38" t="s">
         <v>185</v>
       </c>
-      <c r="D11" s="36" t="s">
+      <c r="D11" s="32" t="s">
         <v>186</v>
       </c>
-      <c r="E11" s="44" t="n">
+      <c r="E11" s="39" t="n">
         <v>160</v>
       </c>
-      <c r="F11" s="45" t="n">
+      <c r="F11" s="40" t="n">
         <v>250</v>
       </c>
-      <c r="G11" s="46" t="n">
+      <c r="G11" s="41" t="n">
         <f aca="false">IF(E11&gt;0,F11*E11/100,F11*100/ABS(E11))</f>
         <v>400</v>
       </c>
-      <c r="H11" s="46" t="n">
+      <c r="H11" s="41" t="n">
         <f aca="false">F11+G11</f>
         <v>650</v>
       </c>
-      <c r="I11" s="63" t="s">
+      <c r="I11" s="56" t="s">
         <v>119</v>
       </c>
-      <c r="J11" s="46" t="n">
+      <c r="J11" s="41" t="n">
         <f aca="false">IF(I11="Win",F11+G11,IF(I11="Push",F11,IF(I11="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K11" s="48" t="n">
+      <c r="K11" s="43" t="n">
         <f aca="false">IF(I11="Pending",0,J11-F11)</f>
         <v>0</v>
       </c>
-      <c r="L11" s="49" t="s">
+      <c r="L11" s="44" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="36" t="n">
+      <c r="A12" s="32" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="42" t="s">
+      <c r="B12" s="37" t="s">
         <v>188</v>
       </c>
-      <c r="C12" s="43" t="s">
+      <c r="C12" s="38" t="s">
         <v>189</v>
       </c>
-      <c r="D12" s="36" t="s">
+      <c r="D12" s="32" t="s">
         <v>186</v>
       </c>
-      <c r="E12" s="44" t="n">
+      <c r="E12" s="39" t="n">
         <v>500</v>
       </c>
-      <c r="F12" s="45" t="n">
+      <c r="F12" s="40" t="n">
         <v>50</v>
       </c>
-      <c r="G12" s="46" t="n">
+      <c r="G12" s="41" t="n">
         <f aca="false">IF(E12&gt;0,F12*E12/100,F12*100/ABS(E12))</f>
         <v>250</v>
       </c>
-      <c r="H12" s="46" t="n">
+      <c r="H12" s="41" t="n">
         <f aca="false">F12+G12</f>
         <v>300</v>
       </c>
-      <c r="I12" s="63" t="s">
+      <c r="I12" s="56" t="s">
         <v>119</v>
       </c>
-      <c r="J12" s="46" t="n">
+      <c r="J12" s="41" t="n">
         <f aca="false">IF(I12="Win",F12+G12,IF(I12="Push",F12,IF(I12="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K12" s="48" t="n">
+      <c r="K12" s="43" t="n">
         <f aca="false">IF(I12="Pending",0,J12-F12)</f>
         <v>0</v>
       </c>
-      <c r="L12" s="49" t="s">
+      <c r="L12" s="44" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="36" t="n">
+      <c r="A13" s="32" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="42" t="s">
+      <c r="B13" s="37" t="s">
         <v>191</v>
       </c>
-      <c r="C13" s="43" t="s">
+      <c r="C13" s="38" t="s">
         <v>192</v>
       </c>
-      <c r="D13" s="36" t="s">
+      <c r="D13" s="32" t="s">
         <v>113</v>
       </c>
-      <c r="E13" s="44" t="n">
+      <c r="E13" s="39" t="n">
         <v>179</v>
       </c>
-      <c r="F13" s="45" t="n">
+      <c r="F13" s="40" t="n">
         <v>50</v>
       </c>
-      <c r="G13" s="46" t="n">
+      <c r="G13" s="41" t="n">
         <f aca="false">IF(E13&gt;0,F13*E13/100,F13*100/ABS(E13))</f>
         <v>89.5</v>
       </c>
-      <c r="H13" s="46" t="n">
+      <c r="H13" s="41" t="n">
         <f aca="false">F13+G13</f>
         <v>139.5</v>
       </c>
-      <c r="I13" s="63" t="s">
+      <c r="I13" s="56" t="s">
         <v>119</v>
       </c>
-      <c r="J13" s="46" t="n">
+      <c r="J13" s="41" t="n">
         <f aca="false">IF(I13="Win",F13+G13,IF(I13="Push",F13,IF(I13="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K13" s="48" t="n">
+      <c r="K13" s="43" t="n">
         <f aca="false">IF(I13="Pending",0,J13-F13)</f>
         <v>0</v>
       </c>
-      <c r="L13" s="49" t="s">
+      <c r="L13" s="44" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="51"/>
-      <c r="B14" s="52" t="s">
+      <c r="A14" s="46"/>
+      <c r="B14" s="47" t="s">
         <v>37</v>
       </c>
-      <c r="C14" s="51"/>
-      <c r="D14" s="51"/>
-      <c r="E14" s="51"/>
-      <c r="F14" s="53" t="n">
+      <c r="C14" s="46"/>
+      <c r="D14" s="46"/>
+      <c r="E14" s="46"/>
+      <c r="F14" s="48" t="n">
         <f aca="false">SUM(F7:F13)</f>
         <v>1000</v>
       </c>
-      <c r="G14" s="54" t="n">
+      <c r="G14" s="49" t="n">
         <f aca="false">SUM(G7:G13)</f>
         <v>1472.69398907104</v>
       </c>
-      <c r="H14" s="54" t="n">
+      <c r="H14" s="49" t="n">
         <f aca="false">SUM(H7:H13)</f>
         <v>2472.69398907104</v>
       </c>
-      <c r="I14" s="51"/>
-      <c r="J14" s="54" t="n">
+      <c r="I14" s="46"/>
+      <c r="J14" s="49" t="n">
         <f aca="false">SUM(J7:J13)</f>
         <v>0</v>
       </c>
-      <c r="K14" s="55" t="n">
+      <c r="K14" s="50" t="n">
         <f aca="false">SUM(K7:K13)</f>
         <v>0</v>
       </c>
-      <c r="L14" s="51"/>
+      <c r="L14" s="46"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="4" t="s">
@@ -4341,91 +4135,91 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="42" t="s">
+      <c r="B17" s="37" t="s">
         <v>116</v>
       </c>
-      <c r="C17" s="56" t="n">
+      <c r="C17" s="51" t="n">
         <f aca="false">COUNTIF(I7:I13,"Win")</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="42" t="s">
+      <c r="B18" s="37" t="s">
         <v>117</v>
       </c>
-      <c r="C18" s="56" t="n">
+      <c r="C18" s="51" t="n">
         <f aca="false">COUNTIF(I7:I13,"Loss")</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="42" t="s">
+      <c r="B19" s="37" t="s">
         <v>118</v>
       </c>
-      <c r="C19" s="56" t="n">
+      <c r="C19" s="51" t="n">
         <f aca="false">COUNTIF(I7:I13,"Push")</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="42" t="s">
+      <c r="B20" s="37" t="s">
         <v>119</v>
       </c>
-      <c r="C20" s="56" t="n">
+      <c r="C20" s="51" t="n">
         <f aca="false">COUNTIF(I7:I13,"Pending")</f>
         <v>7</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="42" t="s">
+      <c r="B21" s="37" t="s">
         <v>120</v>
       </c>
-      <c r="C21" s="57" t="str">
+      <c r="C21" s="52" t="str">
         <f aca="false">IF(COUNTIF(I7:I13,"Win")+COUNTIF(I7:I13,"Loss")=0,"—",COUNTIF(I7:I13,"Win")/(COUNTIF(I7:I13,"Win")+COUNTIF(I7:I13,"Loss")))</f>
         <v>—</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="42" t="s">
+      <c r="B22" s="37" t="s">
         <v>121</v>
       </c>
-      <c r="C22" s="58" t="n">
+      <c r="C22" s="33" t="n">
         <f aca="false">SUM(F7:F13)</f>
         <v>1000</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="42" t="s">
+      <c r="B23" s="37" t="s">
         <v>122</v>
       </c>
-      <c r="C23" s="46" t="n">
+      <c r="C23" s="41" t="n">
         <f aca="false">SUM(J7:J13)</f>
         <v>0</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="42" t="s">
+      <c r="B24" s="37" t="s">
         <v>123</v>
       </c>
-      <c r="C24" s="48" t="n">
+      <c r="C24" s="43" t="n">
         <f aca="false">SUM(K7:K13)</f>
         <v>0</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="42" t="s">
+      <c r="B25" s="37" t="s">
         <v>124</v>
       </c>
-      <c r="C25" s="57" t="n">
+      <c r="C25" s="52" t="n">
         <f aca="false">IF(SUM(F7:F13)=0,"—",SUM(K7:K13)/SUM(F7:F13))</f>
         <v>0</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="42" t="s">
+      <c r="B26" s="37" t="s">
         <v>194</v>
       </c>
-      <c r="C26" s="58" t="n">
+      <c r="C26" s="33" t="n">
         <f aca="false">929</f>
         <v>929</v>
       </c>
@@ -4436,91 +4230,91 @@
       </c>
     </row>
     <row r="29" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="14" t="s">
+      <c r="A29" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B29" s="14" t="s">
+      <c r="B29" s="12" t="s">
         <v>196</v>
       </c>
-      <c r="C29" s="14" t="s">
+      <c r="C29" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="D29" s="14" t="s">
+      <c r="D29" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="E29" s="14" t="s">
+      <c r="E29" s="12" t="s">
         <v>197</v>
       </c>
-      <c r="F29" s="14" t="s">
+      <c r="F29" s="12" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="36" t="n">
+      <c r="A30" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="B30" s="42" t="s">
+      <c r="B30" s="37" t="s">
         <v>198</v>
       </c>
-      <c r="C30" s="49" t="s">
+      <c r="C30" s="44" t="s">
         <v>199</v>
       </c>
-      <c r="D30" s="59" t="s">
+      <c r="D30" s="53" t="s">
         <v>200</v>
       </c>
-      <c r="E30" s="63"/>
-      <c r="F30" s="63"/>
+      <c r="E30" s="56"/>
+      <c r="F30" s="56"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="36" t="n">
+      <c r="A31" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="B31" s="42" t="s">
+      <c r="B31" s="37" t="s">
         <v>201</v>
       </c>
-      <c r="C31" s="49" t="s">
+      <c r="C31" s="44" t="s">
         <v>202</v>
       </c>
-      <c r="D31" s="59" t="s">
+      <c r="D31" s="53" t="s">
         <v>203</v>
       </c>
-      <c r="E31" s="63"/>
-      <c r="F31" s="63"/>
+      <c r="E31" s="56"/>
+      <c r="F31" s="56"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="36" t="n">
+      <c r="A32" s="32" t="n">
         <v>3</v>
       </c>
-      <c r="B32" s="42" t="s">
+      <c r="B32" s="37" t="s">
         <v>204</v>
       </c>
-      <c r="C32" s="49" t="s">
+      <c r="C32" s="44" t="s">
         <v>205</v>
       </c>
-      <c r="D32" s="59" t="s">
+      <c r="D32" s="53" t="s">
         <v>206</v>
       </c>
-      <c r="E32" s="63"/>
-      <c r="F32" s="63"/>
+      <c r="E32" s="56"/>
+      <c r="F32" s="56"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="36" t="n">
+      <c r="A33" s="32" t="n">
         <v>4</v>
       </c>
-      <c r="B33" s="42" t="s">
+      <c r="B33" s="37" t="s">
         <v>207</v>
       </c>
-      <c r="C33" s="49" t="s">
+      <c r="C33" s="44" t="s">
         <v>208</v>
       </c>
-      <c r="D33" s="59" t="s">
+      <c r="D33" s="53" t="s">
         <v>209</v>
       </c>
-      <c r="E33" s="63"/>
-      <c r="F33" s="63"/>
+      <c r="E33" s="56"/>
+      <c r="F33" s="56"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="61" t="s">
+      <c r="A35" s="34" t="s">
         <v>210</v>
       </c>
     </row>
@@ -4579,10 +4373,10 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="35" t="s">
         <v>211</v>
       </c>
-      <c r="H1" s="41" t="s">
+      <c r="H1" s="36" t="s">
         <v>212</v>
       </c>
     </row>
@@ -4602,440 +4396,440 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="14" t="s">
+      <c r="A6" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="12" t="s">
         <v>215</v>
       </c>
-      <c r="D6" s="14" t="s">
+      <c r="D6" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="E6" s="14" t="s">
+      <c r="E6" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="F6" s="14" t="s">
+      <c r="F6" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="G6" s="14" t="s">
+      <c r="G6" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="H6" s="14" t="s">
+      <c r="H6" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="I6" s="14" t="s">
+      <c r="I6" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="J6" s="14" t="s">
+      <c r="J6" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="K6" s="14" t="s">
+      <c r="K6" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="L6" s="14" t="s">
+      <c r="L6" s="12" t="s">
         <v>216</v>
       </c>
-      <c r="M6" s="14" t="s">
+      <c r="M6" s="12" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="36" t="n">
+      <c r="A7" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="42" t="s">
+      <c r="B7" s="37" t="s">
         <v>217</v>
       </c>
-      <c r="C7" s="43" t="s">
+      <c r="C7" s="38" t="s">
         <v>218</v>
       </c>
-      <c r="D7" s="36" t="s">
+      <c r="D7" s="32" t="s">
         <v>85</v>
       </c>
-      <c r="E7" s="44" t="n">
+      <c r="E7" s="39" t="n">
         <v>-155</v>
       </c>
-      <c r="F7" s="45" t="n">
+      <c r="F7" s="40" t="n">
         <v>200</v>
       </c>
-      <c r="G7" s="46" t="n">
+      <c r="G7" s="41" t="n">
         <f aca="false">IF(E7&gt;0,F7*E7/100,F7*100/ABS(E7))</f>
         <v>129.032258064516</v>
       </c>
-      <c r="H7" s="46" t="n">
+      <c r="H7" s="41" t="n">
         <f aca="false">F7+G7</f>
         <v>329.032258064516</v>
       </c>
-      <c r="I7" s="47" t="s">
+      <c r="I7" s="42" t="s">
         <v>86</v>
       </c>
-      <c r="J7" s="46" t="n">
+      <c r="J7" s="41" t="n">
         <f aca="false">IF(I7="Win",F7+G7,IF(I7="Push",F7,IF(I7="Loss",0,0)))</f>
         <v>329.032258064516</v>
       </c>
-      <c r="K7" s="48" t="n">
+      <c r="K7" s="43" t="n">
         <f aca="false">IF(I7="Pending",0,J7-F7)</f>
         <v>129.032258064516</v>
       </c>
-      <c r="L7" s="64" t="n">
+      <c r="L7" s="57" t="n">
         <v>0.62</v>
       </c>
-      <c r="M7" s="49" t="s">
+      <c r="M7" s="44" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="36" t="n">
+      <c r="A8" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="42" t="s">
+      <c r="B8" s="37" t="s">
         <v>220</v>
       </c>
-      <c r="C8" s="43" t="s">
+      <c r="C8" s="38" t="s">
         <v>221</v>
       </c>
-      <c r="D8" s="36" t="s">
+      <c r="D8" s="32" t="s">
         <v>85</v>
       </c>
-      <c r="E8" s="44" t="n">
+      <c r="E8" s="39" t="n">
         <v>-104</v>
       </c>
-      <c r="F8" s="45" t="n">
+      <c r="F8" s="40" t="n">
         <v>150</v>
       </c>
-      <c r="G8" s="46" t="n">
+      <c r="G8" s="41" t="n">
         <f aca="false">IF(E8&gt;0,F8*E8/100,F8*100/ABS(E8))</f>
         <v>144.230769230769</v>
       </c>
-      <c r="H8" s="46" t="n">
+      <c r="H8" s="41" t="n">
         <f aca="false">F8+G8</f>
         <v>294.230769230769</v>
       </c>
-      <c r="I8" s="50" t="s">
+      <c r="I8" s="45" t="s">
         <v>94</v>
       </c>
-      <c r="J8" s="46" t="n">
+      <c r="J8" s="41" t="n">
         <f aca="false">IF(I8="Win",F8+G8,IF(I8="Push",F8,IF(I8="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K8" s="48" t="n">
+      <c r="K8" s="43" t="n">
         <f aca="false">IF(I8="Pending",0,J8-F8)</f>
         <v>-150</v>
       </c>
-      <c r="L8" s="64" t="n">
+      <c r="L8" s="57" t="n">
         <v>0.54</v>
       </c>
-      <c r="M8" s="49" t="s">
+      <c r="M8" s="44" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="36" t="n">
+      <c r="A9" s="32" t="n">
         <v>3</v>
       </c>
-      <c r="B9" s="42" t="s">
+      <c r="B9" s="37" t="s">
         <v>223</v>
       </c>
-      <c r="C9" s="43" t="s">
+      <c r="C9" s="38" t="s">
         <v>224</v>
       </c>
-      <c r="D9" s="36" t="s">
+      <c r="D9" s="32" t="s">
         <v>85</v>
       </c>
-      <c r="E9" s="44" t="n">
+      <c r="E9" s="39" t="n">
         <v>-115</v>
       </c>
-      <c r="F9" s="45" t="n">
+      <c r="F9" s="40" t="n">
         <v>150</v>
       </c>
-      <c r="G9" s="46" t="n">
+      <c r="G9" s="41" t="n">
         <f aca="false">IF(E9&gt;0,F9*E9/100,F9*100/ABS(E9))</f>
         <v>130.434782608696</v>
       </c>
-      <c r="H9" s="46" t="n">
+      <c r="H9" s="41" t="n">
         <f aca="false">F9+G9</f>
         <v>280.434782608696</v>
       </c>
-      <c r="I9" s="50" t="s">
+      <c r="I9" s="45" t="s">
         <v>94</v>
       </c>
-      <c r="J9" s="46" t="n">
+      <c r="J9" s="41" t="n">
         <f aca="false">IF(I9="Win",F9+G9,IF(I9="Push",F9,IF(I9="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K9" s="48" t="n">
+      <c r="K9" s="43" t="n">
         <f aca="false">IF(I9="Pending",0,J9-F9)</f>
         <v>-150</v>
       </c>
-      <c r="L9" s="64" t="n">
+      <c r="L9" s="57" t="n">
         <v>0.55</v>
       </c>
-      <c r="M9" s="49" t="s">
+      <c r="M9" s="44" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="36" t="n">
+      <c r="A10" s="32" t="n">
         <v>4</v>
       </c>
-      <c r="B10" s="42" t="s">
+      <c r="B10" s="37" t="s">
         <v>226</v>
       </c>
-      <c r="C10" s="43" t="s">
+      <c r="C10" s="38" t="s">
         <v>227</v>
       </c>
-      <c r="D10" s="36" t="s">
+      <c r="D10" s="32" t="s">
         <v>175</v>
       </c>
-      <c r="E10" s="44" t="n">
+      <c r="E10" s="39" t="n">
         <v>-114</v>
       </c>
-      <c r="F10" s="45" t="n">
+      <c r="F10" s="40" t="n">
         <v>120</v>
       </c>
-      <c r="G10" s="46" t="n">
+      <c r="G10" s="41" t="n">
         <f aca="false">IF(E10&gt;0,F10*E10/100,F10*100/ABS(E10))</f>
         <v>105.263157894737</v>
       </c>
-      <c r="H10" s="46" t="n">
+      <c r="H10" s="41" t="n">
         <f aca="false">F10+G10</f>
         <v>225.263157894737</v>
       </c>
-      <c r="I10" s="50" t="s">
+      <c r="I10" s="45" t="s">
         <v>94</v>
       </c>
-      <c r="J10" s="46" t="n">
+      <c r="J10" s="41" t="n">
         <f aca="false">IF(I10="Win",F10+G10,IF(I10="Push",F10,IF(I10="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K10" s="48" t="n">
+      <c r="K10" s="43" t="n">
         <f aca="false">IF(I10="Pending",0,J10-F10)</f>
         <v>-120</v>
       </c>
-      <c r="L10" s="64" t="n">
+      <c r="L10" s="57" t="n">
         <v>0.55</v>
       </c>
-      <c r="M10" s="49" t="s">
+      <c r="M10" s="44" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="36" t="n">
+      <c r="A11" s="32" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="42" t="s">
+      <c r="B11" s="37" t="s">
         <v>229</v>
       </c>
-      <c r="C11" s="43" t="s">
+      <c r="C11" s="38" t="s">
         <v>230</v>
       </c>
-      <c r="D11" s="36" t="s">
+      <c r="D11" s="32" t="s">
         <v>85</v>
       </c>
-      <c r="E11" s="44" t="n">
+      <c r="E11" s="39" t="n">
         <v>104</v>
       </c>
-      <c r="F11" s="45" t="n">
+      <c r="F11" s="40" t="n">
         <v>130</v>
       </c>
-      <c r="G11" s="46" t="n">
+      <c r="G11" s="41" t="n">
         <f aca="false">IF(E11&gt;0,F11*E11/100,F11*100/ABS(E11))</f>
         <v>135.2</v>
       </c>
-      <c r="H11" s="46" t="n">
+      <c r="H11" s="41" t="n">
         <f aca="false">F11+G11</f>
         <v>265.2</v>
       </c>
-      <c r="I11" s="47" t="s">
+      <c r="I11" s="42" t="s">
         <v>86</v>
       </c>
-      <c r="J11" s="46" t="n">
+      <c r="J11" s="41" t="n">
         <f aca="false">IF(I11="Win",F11+G11,IF(I11="Push",F11,IF(I11="Loss",0,0)))</f>
         <v>265.2</v>
       </c>
-      <c r="K11" s="48" t="n">
+      <c r="K11" s="43" t="n">
         <f aca="false">IF(I11="Pending",0,J11-F11)</f>
         <v>135.2</v>
       </c>
-      <c r="L11" s="64" t="n">
+      <c r="L11" s="57" t="n">
         <v>0.52</v>
       </c>
-      <c r="M11" s="49" t="s">
+      <c r="M11" s="44" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="36" t="n">
+      <c r="A12" s="32" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="42" t="s">
+      <c r="B12" s="37" t="s">
         <v>232</v>
       </c>
-      <c r="C12" s="43" t="s">
+      <c r="C12" s="38" t="s">
         <v>233</v>
       </c>
-      <c r="D12" s="36" t="s">
+      <c r="D12" s="32" t="s">
         <v>85</v>
       </c>
-      <c r="E12" s="44" t="n">
+      <c r="E12" s="39" t="n">
         <v>108</v>
       </c>
-      <c r="F12" s="45" t="n">
+      <c r="F12" s="40" t="n">
         <v>100</v>
       </c>
-      <c r="G12" s="46" t="n">
+      <c r="G12" s="41" t="n">
         <f aca="false">IF(E12&gt;0,F12*E12/100,F12*100/ABS(E12))</f>
         <v>108</v>
       </c>
-      <c r="H12" s="46" t="n">
+      <c r="H12" s="41" t="n">
         <f aca="false">F12+G12</f>
         <v>208</v>
       </c>
-      <c r="I12" s="50" t="s">
+      <c r="I12" s="45" t="s">
         <v>94</v>
       </c>
-      <c r="J12" s="46" t="n">
+      <c r="J12" s="41" t="n">
         <f aca="false">IF(I12="Win",F12+G12,IF(I12="Push",F12,IF(I12="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K12" s="48" t="n">
+      <c r="K12" s="43" t="n">
         <f aca="false">IF(I12="Pending",0,J12-F12)</f>
         <v>-100</v>
       </c>
-      <c r="L12" s="64" t="n">
+      <c r="L12" s="57" t="n">
         <v>0.5</v>
       </c>
-      <c r="M12" s="49" t="s">
+      <c r="M12" s="44" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="36" t="n">
+      <c r="A13" s="32" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="42" t="s">
+      <c r="B13" s="37" t="s">
         <v>235</v>
       </c>
-      <c r="C13" s="43" t="s">
+      <c r="C13" s="38" t="s">
         <v>236</v>
       </c>
-      <c r="D13" s="36" t="s">
+      <c r="D13" s="32" t="s">
         <v>85</v>
       </c>
-      <c r="E13" s="44" t="n">
+      <c r="E13" s="39" t="n">
         <v>108</v>
       </c>
-      <c r="F13" s="45" t="n">
+      <c r="F13" s="40" t="n">
         <v>100</v>
       </c>
-      <c r="G13" s="46" t="n">
+      <c r="G13" s="41" t="n">
         <f aca="false">IF(E13&gt;0,F13*E13/100,F13*100/ABS(E13))</f>
         <v>108</v>
       </c>
-      <c r="H13" s="46" t="n">
+      <c r="H13" s="41" t="n">
         <f aca="false">F13+G13</f>
         <v>208</v>
       </c>
-      <c r="I13" s="47" t="s">
+      <c r="I13" s="42" t="s">
         <v>86</v>
       </c>
-      <c r="J13" s="46" t="n">
+      <c r="J13" s="41" t="n">
         <f aca="false">IF(I13="Win",F13+G13,IF(I13="Push",F13,IF(I13="Loss",0,0)))</f>
         <v>208</v>
       </c>
-      <c r="K13" s="48" t="n">
+      <c r="K13" s="43" t="n">
         <f aca="false">IF(I13="Pending",0,J13-F13)</f>
         <v>108</v>
       </c>
-      <c r="L13" s="64" t="n">
+      <c r="L13" s="57" t="n">
         <v>0.5</v>
       </c>
-      <c r="M13" s="49" t="s">
+      <c r="M13" s="44" t="s">
         <v>237</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="36" t="n">
+      <c r="A14" s="32" t="n">
         <v>8</v>
       </c>
-      <c r="B14" s="42" t="s">
+      <c r="B14" s="37" t="s">
         <v>238</v>
       </c>
-      <c r="C14" s="43" t="s">
+      <c r="C14" s="38" t="s">
         <v>239</v>
       </c>
-      <c r="D14" s="36" t="s">
+      <c r="D14" s="32" t="s">
         <v>113</v>
       </c>
-      <c r="E14" s="44" t="n">
+      <c r="E14" s="39" t="n">
         <v>732</v>
       </c>
-      <c r="F14" s="45" t="n">
+      <c r="F14" s="40" t="n">
         <v>50</v>
       </c>
-      <c r="G14" s="46" t="n">
+      <c r="G14" s="41" t="n">
         <f aca="false">IF(E14&gt;0,F14*E14/100,F14*100/ABS(E14))</f>
         <v>366</v>
       </c>
-      <c r="H14" s="46" t="n">
+      <c r="H14" s="41" t="n">
         <f aca="false">F14+G14</f>
         <v>416</v>
       </c>
-      <c r="I14" s="50" t="s">
+      <c r="I14" s="45" t="s">
         <v>94</v>
       </c>
-      <c r="J14" s="46" t="n">
+      <c r="J14" s="41" t="n">
         <f aca="false">IF(I14="Win",F14+G14,IF(I14="Push",F14,IF(I14="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K14" s="48" t="n">
+      <c r="K14" s="43" t="n">
         <f aca="false">IF(I14="Pending",0,J14-F14)</f>
         <v>-50</v>
       </c>
-      <c r="L14" s="64" t="n">
+      <c r="L14" s="57" t="n">
         <v>0.14</v>
       </c>
-      <c r="M14" s="49" t="s">
+      <c r="M14" s="44" t="s">
         <v>240</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="51"/>
-      <c r="B15" s="52" t="s">
+      <c r="A15" s="46"/>
+      <c r="B15" s="47" t="s">
         <v>37</v>
       </c>
-      <c r="C15" s="51"/>
-      <c r="D15" s="51"/>
-      <c r="E15" s="51"/>
-      <c r="F15" s="53" t="n">
+      <c r="C15" s="46"/>
+      <c r="D15" s="46"/>
+      <c r="E15" s="46"/>
+      <c r="F15" s="48" t="n">
         <f aca="false">SUM(F7:F14)</f>
         <v>1000</v>
       </c>
-      <c r="G15" s="54" t="n">
+      <c r="G15" s="49" t="n">
         <f aca="false">SUM(G7:G14)</f>
         <v>1226.16096779872</v>
       </c>
-      <c r="H15" s="54" t="n">
+      <c r="H15" s="49" t="n">
         <f aca="false">SUM(H7:H14)</f>
         <v>2226.16096779872</v>
       </c>
-      <c r="I15" s="51"/>
-      <c r="J15" s="54" t="n">
+      <c r="I15" s="46"/>
+      <c r="J15" s="49" t="n">
         <f aca="false">SUM(J7:J14)</f>
         <v>802.232258064516</v>
       </c>
-      <c r="K15" s="55" t="n">
+      <c r="K15" s="50" t="n">
         <f aca="false">SUM(K7:K14)</f>
         <v>-197.767741935484</v>
       </c>
-      <c r="L15" s="65" t="n">
+      <c r="L15" s="58" t="n">
         <f aca="false">SUM(L7:L14)</f>
         <v>3.92</v>
       </c>
-      <c r="M15" s="51"/>
+      <c r="M15" s="46"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="4" t="s">
@@ -5043,109 +4837,109 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="42" t="s">
+      <c r="B18" s="37" t="s">
         <v>116</v>
       </c>
-      <c r="C18" s="56" t="n">
+      <c r="C18" s="51" t="n">
         <f aca="false">COUNTIF(I7:I14,"Win")</f>
         <v>3</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="42" t="s">
+      <c r="B19" s="37" t="s">
         <v>117</v>
       </c>
-      <c r="C19" s="56" t="n">
+      <c r="C19" s="51" t="n">
         <f aca="false">COUNTIF(I7:I14,"Loss")</f>
         <v>5</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="42" t="s">
+      <c r="B20" s="37" t="s">
         <v>118</v>
       </c>
-      <c r="C20" s="56" t="n">
+      <c r="C20" s="51" t="n">
         <f aca="false">COUNTIF(I7:I14,"Push")</f>
         <v>0</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="42" t="s">
+      <c r="B21" s="37" t="s">
         <v>119</v>
       </c>
-      <c r="C21" s="56" t="n">
+      <c r="C21" s="51" t="n">
         <f aca="false">COUNTIF(I7:I14,"Pending")</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="42" t="s">
+      <c r="B22" s="37" t="s">
         <v>120</v>
       </c>
-      <c r="C22" s="57" t="n">
+      <c r="C22" s="52" t="n">
         <f aca="false">IF(COUNTIF(I7:I14,"Win")+COUNTIF(I7:I14,"Loss")=0,"—",COUNTIF(I7:I14,"Win")/(COUNTIF(I7:I14,"Win")+COUNTIF(I7:I14,"Loss")))</f>
         <v>0.375</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="42" t="s">
+      <c r="B23" s="37" t="s">
         <v>121</v>
       </c>
-      <c r="C23" s="58" t="n">
+      <c r="C23" s="33" t="n">
         <f aca="false">SUM(F7:F14)</f>
         <v>1000</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="42" t="s">
+      <c r="B24" s="37" t="s">
         <v>122</v>
       </c>
-      <c r="C24" s="46" t="n">
+      <c r="C24" s="41" t="n">
         <f aca="false">SUM(J7:J14)</f>
         <v>802.232258064516</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="42" t="s">
+      <c r="B25" s="37" t="s">
         <v>123</v>
       </c>
-      <c r="C25" s="48" t="n">
+      <c r="C25" s="43" t="n">
         <f aca="false">SUM(K7:K14)</f>
         <v>-197.767741935484</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="42" t="s">
+      <c r="B26" s="37" t="s">
         <v>124</v>
       </c>
-      <c r="C26" s="57" t="n">
+      <c r="C26" s="52" t="n">
         <f aca="false">IF(SUM(F7:F14)=0,"—",SUM(K7:K14)/SUM(F7:F14))</f>
         <v>-0.197767741935484</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="42" t="s">
+      <c r="B27" s="37" t="s">
         <v>125</v>
       </c>
-      <c r="C27" s="46" t="n">
+      <c r="C27" s="41" t="n">
         <f aca="false">SUM(H7:H14)</f>
         <v>2226.16096779872</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="42" t="s">
+      <c r="B28" s="37" t="s">
         <v>241</v>
       </c>
-      <c r="C28" s="66" t="n">
+      <c r="C28" s="59" t="n">
         <f aca="false">SUM(L7:L14)</f>
         <v>3.92</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="42" t="s">
+      <c r="B29" s="37" t="s">
         <v>242</v>
       </c>
-      <c r="C29" s="48" t="n">
+      <c r="C29" s="43" t="n">
         <f aca="false">SUMPRODUCT(L7:L14,G7:G14)-SUMPRODUCT(1-L7:L14,F7:F14)</f>
         <v>45.1624826615033</v>
       </c>
@@ -5156,155 +4950,155 @@
       </c>
     </row>
     <row r="32" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="14" t="s">
+      <c r="A32" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B32" s="14" t="s">
+      <c r="B32" s="12" t="s">
         <v>244</v>
       </c>
-      <c r="C32" s="14" t="s">
+      <c r="C32" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="D32" s="14" t="s">
+      <c r="D32" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="E32" s="14" t="s">
+      <c r="E32" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="F32" s="14" t="s">
+      <c r="F32" s="12" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="36" t="n">
+      <c r="A33" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="B33" s="42" t="s">
+      <c r="B33" s="37" t="s">
         <v>246</v>
       </c>
-      <c r="C33" s="49" t="s">
+      <c r="C33" s="44" t="s">
         <v>247</v>
       </c>
-      <c r="D33" s="59" t="s">
+      <c r="D33" s="53" t="s">
         <v>248</v>
       </c>
-      <c r="E33" s="63"/>
-      <c r="F33" s="63"/>
+      <c r="E33" s="56"/>
+      <c r="F33" s="56"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="36" t="n">
+      <c r="A34" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="B34" s="42" t="s">
+      <c r="B34" s="37" t="s">
         <v>249</v>
       </c>
-      <c r="C34" s="49" t="s">
+      <c r="C34" s="44" t="s">
         <v>250</v>
       </c>
-      <c r="D34" s="59" t="s">
+      <c r="D34" s="53" t="s">
         <v>251</v>
       </c>
-      <c r="E34" s="63"/>
-      <c r="F34" s="63"/>
+      <c r="E34" s="56"/>
+      <c r="F34" s="56"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="36" t="n">
+      <c r="A35" s="32" t="n">
         <v>3</v>
       </c>
-      <c r="B35" s="42" t="s">
+      <c r="B35" s="37" t="s">
         <v>252</v>
       </c>
-      <c r="C35" s="49" t="s">
+      <c r="C35" s="44" t="s">
         <v>253</v>
       </c>
-      <c r="D35" s="59" t="s">
+      <c r="D35" s="53" t="s">
         <v>254</v>
       </c>
-      <c r="E35" s="63"/>
-      <c r="F35" s="63"/>
+      <c r="E35" s="56"/>
+      <c r="F35" s="56"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="36" t="n">
+      <c r="A36" s="32" t="n">
         <v>4</v>
       </c>
-      <c r="B36" s="42" t="s">
+      <c r="B36" s="37" t="s">
         <v>255</v>
       </c>
-      <c r="C36" s="49" t="s">
+      <c r="C36" s="44" t="s">
         <v>256</v>
       </c>
-      <c r="D36" s="59" t="s">
+      <c r="D36" s="53" t="s">
         <v>257</v>
       </c>
-      <c r="E36" s="63"/>
-      <c r="F36" s="63"/>
+      <c r="E36" s="56"/>
+      <c r="F36" s="56"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="36" t="n">
+      <c r="A37" s="32" t="n">
         <v>5</v>
       </c>
-      <c r="B37" s="42" t="s">
+      <c r="B37" s="37" t="s">
         <v>258</v>
       </c>
-      <c r="C37" s="49" t="s">
+      <c r="C37" s="44" t="s">
         <v>259</v>
       </c>
-      <c r="D37" s="59" t="s">
+      <c r="D37" s="53" t="s">
         <v>260</v>
       </c>
-      <c r="E37" s="63"/>
-      <c r="F37" s="63"/>
+      <c r="E37" s="56"/>
+      <c r="F37" s="56"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="36" t="n">
+      <c r="A38" s="32" t="n">
         <v>6</v>
       </c>
-      <c r="B38" s="42" t="s">
+      <c r="B38" s="37" t="s">
         <v>261</v>
       </c>
-      <c r="C38" s="49" t="s">
+      <c r="C38" s="44" t="s">
         <v>262</v>
       </c>
-      <c r="D38" s="59" t="s">
+      <c r="D38" s="53" t="s">
         <v>263</v>
       </c>
-      <c r="E38" s="63"/>
-      <c r="F38" s="63"/>
+      <c r="E38" s="56"/>
+      <c r="F38" s="56"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="36" t="n">
+      <c r="A39" s="32" t="n">
         <v>7</v>
       </c>
-      <c r="B39" s="42" t="s">
+      <c r="B39" s="37" t="s">
         <v>264</v>
       </c>
-      <c r="C39" s="49" t="s">
+      <c r="C39" s="44" t="s">
         <v>265</v>
       </c>
-      <c r="D39" s="59" t="s">
+      <c r="D39" s="53" t="s">
         <v>266</v>
       </c>
-      <c r="E39" s="63"/>
-      <c r="F39" s="63"/>
+      <c r="E39" s="56"/>
+      <c r="F39" s="56"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="36" t="n">
+      <c r="A40" s="32" t="n">
         <v>8</v>
       </c>
-      <c r="B40" s="42" t="s">
+      <c r="B40" s="37" t="s">
         <v>267</v>
       </c>
-      <c r="C40" s="49" t="s">
+      <c r="C40" s="44" t="s">
         <v>268</v>
       </c>
-      <c r="D40" s="59" t="s">
+      <c r="D40" s="53" t="s">
         <v>269</v>
       </c>
-      <c r="E40" s="63"/>
-      <c r="F40" s="63"/>
+      <c r="E40" s="56"/>
+      <c r="F40" s="56"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="61" t="s">
+      <c r="A42" s="34" t="s">
         <v>270</v>
       </c>
     </row>
@@ -5371,10 +5165,10 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="35" t="s">
         <v>271</v>
       </c>
-      <c r="H1" s="62" t="s">
+      <c r="H1" s="55" t="s">
         <v>272</v>
       </c>
     </row>
@@ -5384,7 +5178,7 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="67" t="s">
+      <c r="A3" s="60" t="s">
         <v>274</v>
       </c>
     </row>
@@ -5394,395 +5188,395 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="14" t="s">
+      <c r="A6" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="12" t="s">
         <v>196</v>
       </c>
-      <c r="D6" s="14" t="s">
+      <c r="D6" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="E6" s="14" t="s">
+      <c r="E6" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="F6" s="14" t="s">
+      <c r="F6" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="G6" s="14" t="s">
+      <c r="G6" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="H6" s="14" t="s">
+      <c r="H6" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="I6" s="14" t="s">
+      <c r="I6" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="J6" s="14" t="s">
+      <c r="J6" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="K6" s="14" t="s">
+      <c r="K6" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="L6" s="14" t="s">
+      <c r="L6" s="12" t="s">
         <v>216</v>
       </c>
-      <c r="M6" s="14" t="s">
+      <c r="M6" s="12" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="36" t="n">
+      <c r="A7" s="32" t="n">
         <v>1</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>275</v>
       </c>
-      <c r="C7" s="35" t="s">
+      <c r="C7" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="D7" s="36" t="s">
+      <c r="D7" s="32" t="s">
         <v>277</v>
       </c>
-      <c r="E7" s="44" t="n">
+      <c r="E7" s="39" t="n">
         <v>-113</v>
       </c>
-      <c r="F7" s="45" t="n">
+      <c r="F7" s="40" t="n">
         <v>300</v>
       </c>
-      <c r="G7" s="46" t="n">
+      <c r="G7" s="41" t="n">
         <f aca="false">IF(E7&gt;0,F7*E7/100,F7*100/ABS(E7))</f>
         <v>265.486725663717</v>
       </c>
-      <c r="H7" s="46" t="n">
+      <c r="H7" s="41" t="n">
         <f aca="false">F7+G7</f>
         <v>565.486725663717</v>
       </c>
-      <c r="I7" s="63" t="s">
+      <c r="I7" s="56" t="s">
         <v>86</v>
       </c>
-      <c r="J7" s="46" t="n">
+      <c r="J7" s="41" t="n">
         <f aca="false">IF(I7="Win",F7+G7,IF(I7="Push",F7,IF(I7="Loss",0,0)))</f>
         <v>565.486725663717</v>
       </c>
-      <c r="K7" s="48" t="n">
+      <c r="K7" s="43" t="n">
         <f aca="false">IF(I7="Pending",0,J7-F7)</f>
         <v>265.486725663717</v>
       </c>
-      <c r="L7" s="64" t="n">
+      <c r="L7" s="57" t="n">
         <v>0.58</v>
       </c>
-      <c r="M7" s="68" t="s">
+      <c r="M7" s="61" t="s">
         <v>278</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="36" t="n">
+      <c r="A8" s="32" t="n">
         <v>2</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>279</v>
       </c>
-      <c r="C8" s="35" t="s">
+      <c r="C8" s="31" t="s">
         <v>280</v>
       </c>
-      <c r="D8" s="36" t="s">
+      <c r="D8" s="32" t="s">
         <v>90</v>
       </c>
-      <c r="E8" s="44" t="n">
+      <c r="E8" s="39" t="n">
         <v>456</v>
       </c>
-      <c r="F8" s="45" t="n">
+      <c r="F8" s="40" t="n">
         <v>200</v>
       </c>
-      <c r="G8" s="46" t="n">
+      <c r="G8" s="41" t="n">
         <f aca="false">IF(E8&gt;0,F8*E8/100,F8*100/ABS(E8))</f>
         <v>912</v>
       </c>
-      <c r="H8" s="46" t="n">
+      <c r="H8" s="41" t="n">
         <f aca="false">F8+G8</f>
         <v>1112</v>
       </c>
-      <c r="I8" s="63" t="s">
+      <c r="I8" s="56" t="s">
         <v>94</v>
       </c>
-      <c r="J8" s="46" t="n">
+      <c r="J8" s="41" t="n">
         <f aca="false">IF(I8="Win",F8+G8,IF(I8="Push",F8,IF(I8="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K8" s="48" t="n">
+      <c r="K8" s="43" t="n">
         <f aca="false">IF(I8="Pending",0,J8-F8)</f>
         <v>-200</v>
       </c>
-      <c r="L8" s="64" t="n">
+      <c r="L8" s="57" t="n">
         <v>0.24</v>
       </c>
-      <c r="M8" s="68" t="s">
+      <c r="M8" s="61" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="36" t="n">
+      <c r="A9" s="32" t="n">
         <v>3</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>282</v>
       </c>
-      <c r="C9" s="35" t="s">
+      <c r="C9" s="31" t="s">
         <v>283</v>
       </c>
-      <c r="D9" s="36" t="s">
+      <c r="D9" s="32" t="s">
         <v>186</v>
       </c>
-      <c r="E9" s="44" t="n">
+      <c r="E9" s="39" t="n">
         <v>1150</v>
       </c>
-      <c r="F9" s="45" t="n">
+      <c r="F9" s="40" t="n">
         <v>150</v>
       </c>
-      <c r="G9" s="46" t="n">
+      <c r="G9" s="41" t="n">
         <f aca="false">IF(E9&gt;0,F9*E9/100,F9*100/ABS(E9))</f>
         <v>1725</v>
       </c>
-      <c r="H9" s="46" t="n">
+      <c r="H9" s="41" t="n">
         <f aca="false">F9+G9</f>
         <v>1875</v>
       </c>
-      <c r="I9" s="63" t="s">
+      <c r="I9" s="56" t="s">
         <v>94</v>
       </c>
-      <c r="J9" s="46" t="n">
+      <c r="J9" s="41" t="n">
         <f aca="false">IF(I9="Win",F9+G9,IF(I9="Push",F9,IF(I9="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K9" s="48" t="n">
+      <c r="K9" s="43" t="n">
         <f aca="false">IF(I9="Pending",0,J9-F9)</f>
         <v>-150</v>
       </c>
-      <c r="L9" s="64" t="n">
+      <c r="L9" s="57" t="n">
         <v>0.1</v>
       </c>
-      <c r="M9" s="68" t="s">
+      <c r="M9" s="61" t="s">
         <v>284</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="36" t="n">
+      <c r="A10" s="32" t="n">
         <v>4</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>285</v>
       </c>
-      <c r="C10" s="35" t="s">
+      <c r="C10" s="31" t="s">
         <v>283</v>
       </c>
-      <c r="D10" s="36" t="s">
+      <c r="D10" s="32" t="s">
         <v>186</v>
       </c>
-      <c r="E10" s="44" t="n">
+      <c r="E10" s="39" t="n">
         <v>1567</v>
       </c>
-      <c r="F10" s="45" t="n">
+      <c r="F10" s="40" t="n">
         <v>120</v>
       </c>
-      <c r="G10" s="46" t="n">
+      <c r="G10" s="41" t="n">
         <f aca="false">IF(E10&gt;0,F10*E10/100,F10*100/ABS(E10))</f>
         <v>1880.4</v>
       </c>
-      <c r="H10" s="46" t="n">
+      <c r="H10" s="41" t="n">
         <f aca="false">F10+G10</f>
         <v>2000.4</v>
       </c>
-      <c r="I10" s="63" t="s">
+      <c r="I10" s="56" t="s">
         <v>94</v>
       </c>
-      <c r="J10" s="46" t="n">
+      <c r="J10" s="41" t="n">
         <f aca="false">IF(I10="Win",F10+G10,IF(I10="Push",F10,IF(I10="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K10" s="48" t="n">
+      <c r="K10" s="43" t="n">
         <f aca="false">IF(I10="Pending",0,J10-F10)</f>
         <v>-120</v>
       </c>
-      <c r="L10" s="64" t="n">
+      <c r="L10" s="57" t="n">
         <v>0.08</v>
       </c>
-      <c r="M10" s="68" t="s">
+      <c r="M10" s="61" t="s">
         <v>286</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="36" t="n">
+      <c r="A11" s="32" t="n">
         <v>5</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>287</v>
       </c>
-      <c r="C11" s="35" t="s">
+      <c r="C11" s="31" t="s">
         <v>283</v>
       </c>
-      <c r="D11" s="36" t="s">
+      <c r="D11" s="32" t="s">
         <v>186</v>
       </c>
-      <c r="E11" s="44" t="n">
+      <c r="E11" s="39" t="n">
         <v>1800</v>
       </c>
-      <c r="F11" s="45" t="n">
+      <c r="F11" s="40" t="n">
         <v>100</v>
       </c>
-      <c r="G11" s="46" t="n">
+      <c r="G11" s="41" t="n">
         <f aca="false">IF(E11&gt;0,F11*E11/100,F11*100/ABS(E11))</f>
         <v>1800</v>
       </c>
-      <c r="H11" s="46" t="n">
+      <c r="H11" s="41" t="n">
         <f aca="false">F11+G11</f>
         <v>1900</v>
       </c>
-      <c r="I11" s="63" t="s">
+      <c r="I11" s="56" t="s">
         <v>94</v>
       </c>
-      <c r="J11" s="46" t="n">
+      <c r="J11" s="41" t="n">
         <f aca="false">IF(I11="Win",F11+G11,IF(I11="Push",F11,IF(I11="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K11" s="48" t="n">
+      <c r="K11" s="43" t="n">
         <f aca="false">IF(I11="Pending",0,J11-F11)</f>
         <v>-100</v>
       </c>
-      <c r="L11" s="64" t="n">
+      <c r="L11" s="57" t="n">
         <v>0.07</v>
       </c>
-      <c r="M11" s="68" t="s">
+      <c r="M11" s="61" t="s">
         <v>288</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="36" t="n">
+      <c r="A12" s="32" t="n">
         <v>6</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>289</v>
       </c>
-      <c r="C12" s="35" t="s">
+      <c r="C12" s="31" t="s">
         <v>283</v>
       </c>
-      <c r="D12" s="36" t="s">
+      <c r="D12" s="32" t="s">
         <v>186</v>
       </c>
-      <c r="E12" s="44" t="n">
+      <c r="E12" s="39" t="n">
         <v>1150</v>
       </c>
-      <c r="F12" s="45" t="n">
+      <c r="F12" s="40" t="n">
         <v>90</v>
       </c>
-      <c r="G12" s="46" t="n">
+      <c r="G12" s="41" t="n">
         <f aca="false">IF(E12&gt;0,F12*E12/100,F12*100/ABS(E12))</f>
         <v>1035</v>
       </c>
-      <c r="H12" s="46" t="n">
+      <c r="H12" s="41" t="n">
         <f aca="false">F12+G12</f>
         <v>1125</v>
       </c>
-      <c r="I12" s="63" t="s">
+      <c r="I12" s="56" t="s">
         <v>94</v>
       </c>
-      <c r="J12" s="46" t="n">
+      <c r="J12" s="41" t="n">
         <f aca="false">IF(I12="Win",F12+G12,IF(I12="Push",F12,IF(I12="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K12" s="48" t="n">
+      <c r="K12" s="43" t="n">
         <f aca="false">IF(I12="Pending",0,J12-F12)</f>
         <v>-90</v>
       </c>
-      <c r="L12" s="64" t="n">
+      <c r="L12" s="57" t="n">
         <v>0.08</v>
       </c>
-      <c r="M12" s="68" t="s">
+      <c r="M12" s="61" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="36" t="n">
+      <c r="A13" s="32" t="n">
         <v>7</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>291</v>
       </c>
-      <c r="C13" s="35" t="s">
+      <c r="C13" s="31" t="s">
         <v>283</v>
       </c>
-      <c r="D13" s="36" t="s">
+      <c r="D13" s="32" t="s">
         <v>186</v>
       </c>
-      <c r="E13" s="44" t="n">
+      <c r="E13" s="39" t="n">
         <v>1900</v>
       </c>
-      <c r="F13" s="45" t="n">
+      <c r="F13" s="40" t="n">
         <v>40</v>
       </c>
-      <c r="G13" s="46" t="n">
+      <c r="G13" s="41" t="n">
         <f aca="false">IF(E13&gt;0,F13*E13/100,F13*100/ABS(E13))</f>
         <v>760</v>
       </c>
-      <c r="H13" s="46" t="n">
+      <c r="H13" s="41" t="n">
         <f aca="false">F13+G13</f>
         <v>800</v>
       </c>
-      <c r="I13" s="63" t="s">
+      <c r="I13" s="56" t="s">
         <v>94</v>
       </c>
-      <c r="J13" s="46" t="n">
+      <c r="J13" s="41" t="n">
         <f aca="false">IF(I13="Win",F13+G13,IF(I13="Push",F13,IF(I13="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K13" s="48" t="n">
+      <c r="K13" s="43" t="n">
         <f aca="false">IF(I13="Pending",0,J13-F13)</f>
         <v>-40</v>
       </c>
-      <c r="L13" s="64" t="n">
+      <c r="L13" s="57" t="n">
         <v>0.05</v>
       </c>
-      <c r="M13" s="68" t="s">
+      <c r="M13" s="61" t="s">
         <v>292</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="69"/>
-      <c r="B14" s="70" t="s">
+      <c r="A14" s="62"/>
+      <c r="B14" s="63" t="s">
         <v>37</v>
       </c>
-      <c r="C14" s="69"/>
-      <c r="D14" s="69"/>
-      <c r="E14" s="69"/>
-      <c r="F14" s="53" t="n">
+      <c r="C14" s="62"/>
+      <c r="D14" s="62"/>
+      <c r="E14" s="62"/>
+      <c r="F14" s="48" t="n">
         <f aca="false">SUM(F7:F13)</f>
         <v>1000</v>
       </c>
-      <c r="G14" s="54" t="n">
+      <c r="G14" s="49" t="n">
         <f aca="false">SUM(G7:G13)</f>
         <v>8377.88672566372</v>
       </c>
-      <c r="H14" s="54" t="n">
+      <c r="H14" s="49" t="n">
         <f aca="false">SUM(H7:H13)</f>
         <v>9377.88672566372</v>
       </c>
-      <c r="I14" s="69"/>
-      <c r="J14" s="54" t="n">
+      <c r="I14" s="62"/>
+      <c r="J14" s="49" t="n">
         <f aca="false">SUM(J7:J13)</f>
         <v>565.486725663717</v>
       </c>
-      <c r="K14" s="55" t="n">
+      <c r="K14" s="50" t="n">
         <f aca="false">SUM(K7:K13)</f>
         <v>-434.513274336283</v>
       </c>
-      <c r="L14" s="65" t="n">
+      <c r="L14" s="58" t="n">
         <f aca="false">SUM(L7:L13)</f>
         <v>1.2</v>
       </c>
-      <c r="M14" s="69"/>
+      <c r="M14" s="62"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="4" t="s">
@@ -5793,7 +5587,7 @@
       <c r="B17" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="C17" s="56" t="n">
+      <c r="C17" s="51" t="n">
         <f aca="false">COUNTIF(I7:I13,"Win")</f>
         <v>1</v>
       </c>
@@ -5802,7 +5596,7 @@
       <c r="B18" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="C18" s="56" t="n">
+      <c r="C18" s="51" t="n">
         <f aca="false">COUNTIF(I7:I13,"Loss")</f>
         <v>6</v>
       </c>
@@ -5811,7 +5605,7 @@
       <c r="B19" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="C19" s="56" t="n">
+      <c r="C19" s="51" t="n">
         <f aca="false">COUNTIF(I7:I13,"Push")</f>
         <v>0</v>
       </c>
@@ -5820,7 +5614,7 @@
       <c r="B20" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="C20" s="56" t="n">
+      <c r="C20" s="51" t="n">
         <f aca="false">COUNTIF(I7:I13,"Pending")</f>
         <v>0</v>
       </c>
@@ -5829,7 +5623,7 @@
       <c r="B21" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="C21" s="57" t="n">
+      <c r="C21" s="52" t="n">
         <f aca="false">IF(COUNTIF(I7:I13,"Win")+COUNTIF(I7:I13,"Loss")=0,"—",COUNTIF(I7:I13,"Win")/(COUNTIF(I7:I13,"Win")+COUNTIF(I7:I13,"Loss")))</f>
         <v>0.142857142857143</v>
       </c>
@@ -5838,7 +5632,7 @@
       <c r="B22" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="C22" s="58" t="n">
+      <c r="C22" s="33" t="n">
         <f aca="false">SUM(F7:F13)</f>
         <v>1000</v>
       </c>
@@ -5847,7 +5641,7 @@
       <c r="B23" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="C23" s="46" t="n">
+      <c r="C23" s="41" t="n">
         <f aca="false">SUM(J7:J13)</f>
         <v>565.486725663717</v>
       </c>
@@ -5856,7 +5650,7 @@
       <c r="B24" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="C24" s="48" t="n">
+      <c r="C24" s="43" t="n">
         <f aca="false">SUM(K7:K13)</f>
         <v>-434.513274336283</v>
       </c>
@@ -5865,7 +5659,7 @@
       <c r="B25" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="C25" s="57" t="n">
+      <c r="C25" s="52" t="n">
         <f aca="false">IF(SUM(F7:F13)=0,"—",SUM(K7:K13)/SUM(F7:F13))</f>
         <v>-0.434513274336283</v>
       </c>
@@ -5874,7 +5668,7 @@
       <c r="B26" s="5" t="s">
         <v>241</v>
       </c>
-      <c r="C26" s="66" t="n">
+      <c r="C26" s="59" t="n">
         <f aca="false">SUM(L7:L13)</f>
         <v>1.2</v>
       </c>
@@ -5883,13 +5677,13 @@
       <c r="B27" s="5" t="s">
         <v>293</v>
       </c>
-      <c r="C27" s="58" t="n">
+      <c r="C27" s="33" t="n">
         <f aca="false">2678</f>
         <v>2678</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="61" t="s">
+      <c r="A29" s="34" t="s">
         <v>294</v>
       </c>
     </row>
@@ -5942,7 +5736,7 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="35" t="s">
         <v>295</v>
       </c>
     </row>
@@ -5952,25 +5746,25 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="14" t="s">
+      <c r="A4" s="12" t="s">
         <v>297</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="12" t="s">
         <v>298</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="12" t="s">
         <v>299</v>
       </c>
-      <c r="D4" s="14" t="s">
+      <c r="D4" s="12" t="s">
         <v>300</v>
       </c>
-      <c r="E4" s="14" t="s">
+      <c r="E4" s="12" t="s">
         <v>301</v>
       </c>
-      <c r="F4" s="14" t="s">
+      <c r="F4" s="12" t="s">
         <v>302</v>
       </c>
-      <c r="G4" s="14" t="s">
+      <c r="G4" s="12" t="s">
         <v>82</v>
       </c>
     </row>
@@ -5978,18 +5772,18 @@
       <c r="A5" s="5" t="s">
         <v>303</v>
       </c>
-      <c r="B5" s="71" t="s">
+      <c r="B5" s="64" t="s">
         <v>304</v>
       </c>
-      <c r="C5" s="72"/>
-      <c r="D5" s="72" t="s">
+      <c r="C5" s="65"/>
+      <c r="D5" s="65" t="s">
         <v>305</v>
       </c>
-      <c r="E5" s="72" t="s">
+      <c r="E5" s="65" t="s">
         <v>305</v>
       </c>
-      <c r="F5" s="72"/>
-      <c r="G5" s="73" t="s">
+      <c r="F5" s="65"/>
+      <c r="G5" s="66" t="s">
         <v>306</v>
       </c>
     </row>
@@ -5997,16 +5791,16 @@
       <c r="A6" s="5" t="s">
         <v>307</v>
       </c>
-      <c r="B6" s="71" t="s">
+      <c r="B6" s="64" t="s">
         <v>308</v>
       </c>
-      <c r="C6" s="72" t="s">
+      <c r="C6" s="65" t="s">
         <v>305</v>
       </c>
-      <c r="D6" s="72"/>
-      <c r="E6" s="72"/>
-      <c r="F6" s="72"/>
-      <c r="G6" s="73" t="s">
+      <c r="D6" s="65"/>
+      <c r="E6" s="65"/>
+      <c r="F6" s="65"/>
+      <c r="G6" s="66" t="s">
         <v>309</v>
       </c>
     </row>
@@ -6014,16 +5808,16 @@
       <c r="A7" s="5" t="s">
         <v>310</v>
       </c>
-      <c r="B7" s="71" t="s">
+      <c r="B7" s="64" t="s">
         <v>311</v>
       </c>
-      <c r="C7" s="72" t="s">
+      <c r="C7" s="65" t="s">
         <v>305</v>
       </c>
-      <c r="D7" s="72"/>
-      <c r="E7" s="72"/>
-      <c r="F7" s="72"/>
-      <c r="G7" s="73" t="s">
+      <c r="D7" s="65"/>
+      <c r="E7" s="65"/>
+      <c r="F7" s="65"/>
+      <c r="G7" s="66" t="s">
         <v>312</v>
       </c>
     </row>
@@ -6031,16 +5825,16 @@
       <c r="A8" s="5" t="s">
         <v>313</v>
       </c>
-      <c r="B8" s="71" t="s">
+      <c r="B8" s="64" t="s">
         <v>314</v>
       </c>
-      <c r="C8" s="72"/>
-      <c r="D8" s="72" t="s">
+      <c r="C8" s="65"/>
+      <c r="D8" s="65" t="s">
         <v>305</v>
       </c>
-      <c r="E8" s="72"/>
-      <c r="F8" s="72"/>
-      <c r="G8" s="73" t="s">
+      <c r="E8" s="65"/>
+      <c r="F8" s="65"/>
+      <c r="G8" s="66" t="s">
         <v>315</v>
       </c>
     </row>
@@ -6048,18 +5842,18 @@
       <c r="A9" s="5" t="s">
         <v>316</v>
       </c>
-      <c r="B9" s="71" t="s">
+      <c r="B9" s="64" t="s">
         <v>317</v>
       </c>
-      <c r="C9" s="72"/>
-      <c r="D9" s="72" t="s">
+      <c r="C9" s="65"/>
+      <c r="D9" s="65" t="s">
         <v>305</v>
       </c>
-      <c r="E9" s="72"/>
-      <c r="F9" s="72" t="s">
+      <c r="E9" s="65"/>
+      <c r="F9" s="65" t="s">
         <v>305</v>
       </c>
-      <c r="G9" s="73" t="s">
+      <c r="G9" s="66" t="s">
         <v>318</v>
       </c>
     </row>
@@ -6067,18 +5861,18 @@
       <c r="A10" s="5" t="s">
         <v>319</v>
       </c>
-      <c r="B10" s="71" t="s">
+      <c r="B10" s="64" t="s">
         <v>320</v>
       </c>
-      <c r="C10" s="72"/>
-      <c r="D10" s="72" t="s">
+      <c r="C10" s="65"/>
+      <c r="D10" s="65" t="s">
         <v>305</v>
       </c>
-      <c r="E10" s="72" t="s">
+      <c r="E10" s="65" t="s">
         <v>305</v>
       </c>
-      <c r="F10" s="72"/>
-      <c r="G10" s="73" t="s">
+      <c r="F10" s="65"/>
+      <c r="G10" s="66" t="s">
         <v>321</v>
       </c>
     </row>
@@ -6086,18 +5880,18 @@
       <c r="A11" s="5" t="s">
         <v>322</v>
       </c>
-      <c r="B11" s="71" t="s">
+      <c r="B11" s="64" t="s">
         <v>323</v>
       </c>
-      <c r="C11" s="72"/>
-      <c r="D11" s="72" t="s">
+      <c r="C11" s="65"/>
+      <c r="D11" s="65" t="s">
         <v>305</v>
       </c>
-      <c r="E11" s="72"/>
-      <c r="F11" s="72" t="s">
+      <c r="E11" s="65"/>
+      <c r="F11" s="65" t="s">
         <v>305</v>
       </c>
-      <c r="G11" s="73" t="s">
+      <c r="G11" s="66" t="s">
         <v>324</v>
       </c>
     </row>
@@ -6105,16 +5899,16 @@
       <c r="A12" s="5" t="s">
         <v>325</v>
       </c>
-      <c r="B12" s="71" t="s">
+      <c r="B12" s="64" t="s">
         <v>326</v>
       </c>
-      <c r="C12" s="72"/>
-      <c r="D12" s="72" t="s">
+      <c r="C12" s="65"/>
+      <c r="D12" s="65" t="s">
         <v>305</v>
       </c>
-      <c r="E12" s="72"/>
-      <c r="F12" s="72"/>
-      <c r="G12" s="73" t="s">
+      <c r="E12" s="65"/>
+      <c r="F12" s="65"/>
+      <c r="G12" s="66" t="s">
         <v>327</v>
       </c>
     </row>
@@ -6122,16 +5916,16 @@
       <c r="A13" s="5" t="s">
         <v>328</v>
       </c>
-      <c r="B13" s="71" t="s">
+      <c r="B13" s="64" t="s">
         <v>329</v>
       </c>
-      <c r="C13" s="72"/>
-      <c r="D13" s="72" t="s">
+      <c r="C13" s="65"/>
+      <c r="D13" s="65" t="s">
         <v>305</v>
       </c>
-      <c r="E13" s="72"/>
-      <c r="F13" s="72"/>
-      <c r="G13" s="73" t="s">
+      <c r="E13" s="65"/>
+      <c r="F13" s="65"/>
+      <c r="G13" s="66" t="s">
         <v>330</v>
       </c>
     </row>
@@ -6139,16 +5933,16 @@
       <c r="A14" s="5" t="s">
         <v>331</v>
       </c>
-      <c r="B14" s="71" t="s">
+      <c r="B14" s="64" t="s">
         <v>332</v>
       </c>
-      <c r="C14" s="72"/>
-      <c r="D14" s="72" t="s">
+      <c r="C14" s="65"/>
+      <c r="D14" s="65" t="s">
         <v>305</v>
       </c>
-      <c r="E14" s="72"/>
-      <c r="F14" s="72"/>
-      <c r="G14" s="73" t="s">
+      <c r="E14" s="65"/>
+      <c r="F14" s="65"/>
+      <c r="G14" s="66" t="s">
         <v>333</v>
       </c>
     </row>
@@ -6156,16 +5950,16 @@
       <c r="A15" s="5" t="s">
         <v>334</v>
       </c>
-      <c r="B15" s="71" t="s">
+      <c r="B15" s="64" t="s">
         <v>335</v>
       </c>
-      <c r="C15" s="72"/>
-      <c r="D15" s="72" t="s">
+      <c r="C15" s="65"/>
+      <c r="D15" s="65" t="s">
         <v>305</v>
       </c>
-      <c r="E15" s="72"/>
-      <c r="F15" s="72"/>
-      <c r="G15" s="73" t="s">
+      <c r="E15" s="65"/>
+      <c r="F15" s="65"/>
+      <c r="G15" s="66" t="s">
         <v>336</v>
       </c>
     </row>
@@ -6173,18 +5967,18 @@
       <c r="A16" s="5" t="s">
         <v>337</v>
       </c>
-      <c r="B16" s="71" t="s">
+      <c r="B16" s="64" t="s">
         <v>338</v>
       </c>
-      <c r="C16" s="72"/>
-      <c r="D16" s="72"/>
-      <c r="E16" s="72" t="s">
+      <c r="C16" s="65"/>
+      <c r="D16" s="65"/>
+      <c r="E16" s="65" t="s">
         <v>305</v>
       </c>
-      <c r="F16" s="72" t="s">
+      <c r="F16" s="65" t="s">
         <v>305</v>
       </c>
-      <c r="G16" s="73" t="s">
+      <c r="G16" s="66" t="s">
         <v>339</v>
       </c>
     </row>
@@ -6192,16 +5986,16 @@
       <c r="A17" s="5" t="s">
         <v>340</v>
       </c>
-      <c r="B17" s="71" t="s">
+      <c r="B17" s="64" t="s">
         <v>341</v>
       </c>
-      <c r="C17" s="72"/>
-      <c r="D17" s="72"/>
-      <c r="E17" s="72" t="s">
+      <c r="C17" s="65"/>
+      <c r="D17" s="65"/>
+      <c r="E17" s="65" t="s">
         <v>305</v>
       </c>
-      <c r="F17" s="72"/>
-      <c r="G17" s="73" t="s">
+      <c r="F17" s="65"/>
+      <c r="G17" s="66" t="s">
         <v>342</v>
       </c>
     </row>
@@ -6209,16 +6003,16 @@
       <c r="A18" s="5" t="s">
         <v>343</v>
       </c>
-      <c r="B18" s="71" t="s">
+      <c r="B18" s="64" t="s">
         <v>344</v>
       </c>
-      <c r="C18" s="72"/>
-      <c r="D18" s="72"/>
-      <c r="E18" s="72" t="s">
+      <c r="C18" s="65"/>
+      <c r="D18" s="65"/>
+      <c r="E18" s="65" t="s">
         <v>305</v>
       </c>
-      <c r="F18" s="72"/>
-      <c r="G18" s="73" t="s">
+      <c r="F18" s="65"/>
+      <c r="G18" s="66" t="s">
         <v>345</v>
       </c>
     </row>
@@ -6226,72 +6020,72 @@
       <c r="A19" s="5" t="s">
         <v>346</v>
       </c>
-      <c r="B19" s="71" t="s">
+      <c r="B19" s="64" t="s">
         <v>347</v>
       </c>
-      <c r="C19" s="72"/>
-      <c r="D19" s="72"/>
-      <c r="E19" s="72"/>
-      <c r="F19" s="72" t="s">
+      <c r="C19" s="65"/>
+      <c r="D19" s="65"/>
+      <c r="E19" s="65"/>
+      <c r="F19" s="65" t="s">
         <v>305</v>
       </c>
-      <c r="G19" s="73" t="s">
+      <c r="G19" s="66" t="s">
         <v>348</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="74" t="s">
+      <c r="A20" s="67" t="s">
         <v>349</v>
       </c>
-      <c r="B20" s="75" t="s">
+      <c r="B20" s="68" t="s">
         <v>350</v>
       </c>
-      <c r="D20" s="76" t="s">
+      <c r="D20" s="69" t="s">
         <v>305</v>
       </c>
-      <c r="F20" s="76" t="s">
+      <c r="F20" s="69" t="s">
         <v>305</v>
       </c>
-      <c r="G20" s="61" t="s">
+      <c r="G20" s="34" t="s">
         <v>351</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="74" t="s">
+      <c r="A21" s="67" t="s">
         <v>352</v>
       </c>
-      <c r="B21" s="75" t="s">
+      <c r="B21" s="68" t="s">
         <v>353</v>
       </c>
-      <c r="G21" s="61" t="s">
+      <c r="G21" s="34" t="s">
         <v>354</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="74" t="s">
+      <c r="A22" s="67" t="s">
         <v>355</v>
       </c>
-      <c r="B22" s="75" t="s">
+      <c r="B22" s="68" t="s">
         <v>356</v>
       </c>
-      <c r="G22" s="61" t="s">
+      <c r="G22" s="34" t="s">
         <v>357</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="74" t="s">
+      <c r="A23" s="67" t="s">
         <v>358</v>
       </c>
-      <c r="B23" s="75" t="s">
+      <c r="B23" s="68" t="s">
         <v>359</v>
       </c>
-      <c r="G23" s="61" t="s">
+      <c r="G23" s="34" t="s">
         <v>360</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="77" t="s">
+      <c r="A25" s="70" t="s">
         <v>361</v>
       </c>
     </row>
@@ -6310,11 +6104,11 @@
         <v>364</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="78" t="s">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="71" t="s">
         <v>365</v>
       </c>
-      <c r="B29" s="78" t="s">
+      <c r="B29" s="71" t="s">
         <v>366</v>
       </c>
     </row>
@@ -6351,10 +6145,10 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="35" t="s">
         <v>367</v>
       </c>
-      <c r="H1" s="62" t="s">
+      <c r="H1" s="55" t="s">
         <v>368</v>
       </c>
     </row>
@@ -6374,395 +6168,395 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="14" t="s">
+      <c r="A6" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="12" t="s">
         <v>215</v>
       </c>
-      <c r="D6" s="14" t="s">
+      <c r="D6" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="E6" s="14" t="s">
+      <c r="E6" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="F6" s="14" t="s">
+      <c r="F6" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="G6" s="14" t="s">
+      <c r="G6" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="H6" s="14" t="s">
+      <c r="H6" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="I6" s="14" t="s">
+      <c r="I6" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="J6" s="14" t="s">
+      <c r="J6" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="K6" s="14" t="s">
+      <c r="K6" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="L6" s="14" t="s">
+      <c r="L6" s="12" t="s">
         <v>216</v>
       </c>
-      <c r="M6" s="14" t="s">
+      <c r="M6" s="12" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="36" t="n">
+      <c r="A7" s="32" t="n">
         <v>1</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>371</v>
       </c>
-      <c r="C7" s="35" t="s">
+      <c r="C7" s="31" t="s">
         <v>372</v>
       </c>
-      <c r="D7" s="36" t="s">
+      <c r="D7" s="32" t="s">
         <v>373</v>
       </c>
-      <c r="E7" s="44" t="n">
+      <c r="E7" s="39" t="n">
         <v>-115</v>
       </c>
-      <c r="F7" s="45" t="n">
+      <c r="F7" s="40" t="n">
         <v>200</v>
       </c>
-      <c r="G7" s="46" t="n">
+      <c r="G7" s="41" t="n">
         <f aca="false">IF(E7&gt;0,F7*E7/100,F7*100/ABS(E7))</f>
         <v>173.913043478261</v>
       </c>
-      <c r="H7" s="46" t="n">
+      <c r="H7" s="41" t="n">
         <f aca="false">F7+G7</f>
         <v>373.913043478261</v>
       </c>
-      <c r="I7" s="50" t="s">
+      <c r="I7" s="45" t="s">
         <v>94</v>
       </c>
-      <c r="J7" s="46" t="n">
+      <c r="J7" s="41" t="n">
         <f aca="false">IF(I7="Win",F7+G7,IF(I7="Push",F7,IF(I7="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K7" s="48" t="n">
+      <c r="K7" s="43" t="n">
         <f aca="false">IF(I7="Pending",0,J7-F7)</f>
         <v>-200</v>
       </c>
-      <c r="L7" s="64" t="n">
+      <c r="L7" s="57" t="n">
         <v>0.56</v>
       </c>
-      <c r="M7" s="68" t="s">
+      <c r="M7" s="61" t="s">
         <v>374</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="36" t="n">
+      <c r="A8" s="32" t="n">
         <v>2</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>375</v>
       </c>
-      <c r="C8" s="35" t="s">
+      <c r="C8" s="31" t="s">
         <v>376</v>
       </c>
-      <c r="D8" s="36" t="s">
+      <c r="D8" s="32" t="s">
         <v>175</v>
       </c>
-      <c r="E8" s="44" t="n">
+      <c r="E8" s="39" t="n">
         <v>-112</v>
       </c>
-      <c r="F8" s="45" t="n">
+      <c r="F8" s="40" t="n">
         <v>150</v>
       </c>
-      <c r="G8" s="46" t="n">
+      <c r="G8" s="41" t="n">
         <f aca="false">IF(E8&gt;0,F8*E8/100,F8*100/ABS(E8))</f>
         <v>133.928571428571</v>
       </c>
-      <c r="H8" s="46" t="n">
+      <c r="H8" s="41" t="n">
         <f aca="false">F8+G8</f>
         <v>283.928571428571</v>
       </c>
-      <c r="I8" s="50" t="s">
+      <c r="I8" s="45" t="s">
         <v>94</v>
       </c>
-      <c r="J8" s="46" t="n">
+      <c r="J8" s="41" t="n">
         <f aca="false">IF(I8="Win",F8+G8,IF(I8="Push",F8,IF(I8="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K8" s="48" t="n">
+      <c r="K8" s="43" t="n">
         <f aca="false">IF(I8="Pending",0,J8-F8)</f>
         <v>-150</v>
       </c>
-      <c r="L8" s="64" t="n">
+      <c r="L8" s="57" t="n">
         <v>0.56</v>
       </c>
-      <c r="M8" s="68" t="s">
+      <c r="M8" s="61" t="s">
         <v>377</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="36" t="n">
+      <c r="A9" s="32" t="n">
         <v>3</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>378</v>
       </c>
-      <c r="C9" s="35" t="s">
+      <c r="C9" s="31" t="s">
         <v>379</v>
       </c>
-      <c r="D9" s="36" t="s">
+      <c r="D9" s="32" t="s">
         <v>90</v>
       </c>
-      <c r="E9" s="44" t="n">
+      <c r="E9" s="39" t="n">
         <v>-159</v>
       </c>
-      <c r="F9" s="45" t="n">
+      <c r="F9" s="40" t="n">
         <v>150</v>
       </c>
-      <c r="G9" s="46" t="n">
+      <c r="G9" s="41" t="n">
         <f aca="false">IF(E9&gt;0,F9*E9/100,F9*100/ABS(E9))</f>
         <v>94.3396226415094</v>
       </c>
-      <c r="H9" s="46" t="n">
+      <c r="H9" s="41" t="n">
         <f aca="false">F9+G9</f>
         <v>244.339622641509</v>
       </c>
-      <c r="I9" s="47" t="s">
+      <c r="I9" s="42" t="s">
         <v>86</v>
       </c>
-      <c r="J9" s="46" t="n">
+      <c r="J9" s="41" t="n">
         <f aca="false">IF(I9="Win",F9+G9,IF(I9="Push",F9,IF(I9="Loss",0,0)))</f>
         <v>244.339622641509</v>
       </c>
-      <c r="K9" s="48" t="n">
+      <c r="K9" s="43" t="n">
         <f aca="false">IF(I9="Pending",0,J9-F9)</f>
         <v>94.3396226415094</v>
       </c>
-      <c r="L9" s="64" t="n">
+      <c r="L9" s="57" t="n">
         <v>0.65</v>
       </c>
-      <c r="M9" s="68" t="s">
+      <c r="M9" s="61" t="s">
         <v>380</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="36" t="n">
+      <c r="A10" s="32" t="n">
         <v>4</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>381</v>
       </c>
-      <c r="C10" s="35" t="s">
+      <c r="C10" s="31" t="s">
         <v>382</v>
       </c>
-      <c r="D10" s="36" t="s">
+      <c r="D10" s="32" t="s">
         <v>373</v>
       </c>
-      <c r="E10" s="44" t="n">
+      <c r="E10" s="39" t="n">
         <v>-108</v>
       </c>
-      <c r="F10" s="45" t="n">
+      <c r="F10" s="40" t="n">
         <v>150</v>
       </c>
-      <c r="G10" s="46" t="n">
+      <c r="G10" s="41" t="n">
         <f aca="false">IF(E10&gt;0,F10*E10/100,F10*100/ABS(E10))</f>
         <v>138.888888888889</v>
       </c>
-      <c r="H10" s="46" t="n">
+      <c r="H10" s="41" t="n">
         <f aca="false">F10+G10</f>
         <v>288.888888888889</v>
       </c>
-      <c r="I10" s="63" t="s">
+      <c r="I10" s="56" t="s">
         <v>94</v>
       </c>
-      <c r="J10" s="46" t="n">
+      <c r="J10" s="41" t="n">
         <f aca="false">IF(I10="Win",F10+G10,IF(I10="Push",F10,IF(I10="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K10" s="48" t="n">
+      <c r="K10" s="43" t="n">
         <f aca="false">IF(I10="Pending",0,J10-F10)</f>
         <v>-150</v>
       </c>
-      <c r="L10" s="64" t="n">
+      <c r="L10" s="57" t="n">
         <v>0.55</v>
       </c>
-      <c r="M10" s="68" t="s">
+      <c r="M10" s="61" t="s">
         <v>383</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="36" t="n">
+      <c r="A11" s="32" t="n">
         <v>5</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>384</v>
       </c>
-      <c r="C11" s="35" t="s">
+      <c r="C11" s="31" t="s">
         <v>385</v>
       </c>
-      <c r="D11" s="36" t="s">
+      <c r="D11" s="32" t="s">
         <v>90</v>
       </c>
-      <c r="E11" s="44" t="n">
+      <c r="E11" s="39" t="n">
         <v>-120</v>
       </c>
-      <c r="F11" s="45" t="n">
+      <c r="F11" s="40" t="n">
         <v>130</v>
       </c>
-      <c r="G11" s="46" t="n">
+      <c r="G11" s="41" t="n">
         <f aca="false">IF(E11&gt;0,F11*E11/100,F11*100/ABS(E11))</f>
         <v>108.333333333333</v>
       </c>
-      <c r="H11" s="46" t="n">
+      <c r="H11" s="41" t="n">
         <f aca="false">F11+G11</f>
         <v>238.333333333333</v>
       </c>
-      <c r="I11" s="63" t="s">
+      <c r="I11" s="56" t="s">
         <v>86</v>
       </c>
-      <c r="J11" s="46" t="n">
+      <c r="J11" s="41" t="n">
         <f aca="false">IF(I11="Win",F11+G11,IF(I11="Push",F11,IF(I11="Loss",0,0)))</f>
         <v>238.333333333333</v>
       </c>
-      <c r="K11" s="48" t="n">
+      <c r="K11" s="43" t="n">
         <f aca="false">IF(I11="Pending",0,J11-F11)</f>
         <v>108.333333333333</v>
       </c>
-      <c r="L11" s="64" t="n">
+      <c r="L11" s="57" t="n">
         <v>0.6</v>
       </c>
-      <c r="M11" s="68" t="s">
+      <c r="M11" s="61" t="s">
         <v>386</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="36" t="n">
+      <c r="A12" s="32" t="n">
         <v>6</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>387</v>
       </c>
-      <c r="C12" s="35" t="s">
+      <c r="C12" s="31" t="s">
         <v>388</v>
       </c>
-      <c r="D12" s="36" t="s">
+      <c r="D12" s="32" t="s">
         <v>90</v>
       </c>
-      <c r="E12" s="44" t="n">
+      <c r="E12" s="39" t="n">
         <v>-121</v>
       </c>
-      <c r="F12" s="45" t="n">
+      <c r="F12" s="40" t="n">
         <v>120</v>
       </c>
-      <c r="G12" s="46" t="n">
+      <c r="G12" s="41" t="n">
         <f aca="false">IF(E12&gt;0,F12*E12/100,F12*100/ABS(E12))</f>
         <v>99.1735537190083</v>
       </c>
-      <c r="H12" s="46" t="n">
+      <c r="H12" s="41" t="n">
         <f aca="false">F12+G12</f>
         <v>219.173553719008</v>
       </c>
-      <c r="I12" s="63" t="s">
+      <c r="I12" s="56" t="s">
         <v>86</v>
       </c>
-      <c r="J12" s="46" t="n">
+      <c r="J12" s="41" t="n">
         <f aca="false">IF(I12="Win",F12+G12,IF(I12="Push",F12,IF(I12="Loss",0,0)))</f>
         <v>219.173553719008</v>
       </c>
-      <c r="K12" s="48" t="n">
+      <c r="K12" s="43" t="n">
         <f aca="false">IF(I12="Pending",0,J12-F12)</f>
         <v>99.1735537190083</v>
       </c>
-      <c r="L12" s="64" t="n">
+      <c r="L12" s="57" t="n">
         <v>0.58</v>
       </c>
-      <c r="M12" s="68" t="s">
+      <c r="M12" s="61" t="s">
         <v>389</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="36" t="n">
+      <c r="A13" s="32" t="n">
         <v>7</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>390</v>
       </c>
-      <c r="C13" s="35" t="s">
+      <c r="C13" s="31" t="s">
         <v>391</v>
       </c>
-      <c r="D13" s="36" t="s">
+      <c r="D13" s="32" t="s">
         <v>113</v>
       </c>
-      <c r="E13" s="44" t="n">
+      <c r="E13" s="39" t="n">
         <v>971</v>
       </c>
-      <c r="F13" s="45" t="n">
+      <c r="F13" s="40" t="n">
         <v>100</v>
       </c>
-      <c r="G13" s="46" t="n">
+      <c r="G13" s="41" t="n">
         <f aca="false">IF(E13&gt;0,F13*E13/100,F13*100/ABS(E13))</f>
         <v>971</v>
       </c>
-      <c r="H13" s="46" t="n">
+      <c r="H13" s="41" t="n">
         <f aca="false">F13+G13</f>
         <v>1071</v>
       </c>
-      <c r="I13" s="50" t="s">
+      <c r="I13" s="45" t="s">
         <v>94</v>
       </c>
-      <c r="J13" s="46" t="n">
+      <c r="J13" s="41" t="n">
         <f aca="false">IF(I13="Win",F13+G13,IF(I13="Push",F13,IF(I13="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K13" s="48" t="n">
+      <c r="K13" s="43" t="n">
         <f aca="false">IF(I13="Pending",0,J13-F13)</f>
         <v>-100</v>
       </c>
-      <c r="L13" s="64" t="n">
+      <c r="L13" s="57" t="n">
         <v>0.12</v>
       </c>
-      <c r="M13" s="68" t="s">
+      <c r="M13" s="61" t="s">
         <v>392</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="69"/>
-      <c r="B14" s="70" t="s">
+      <c r="A14" s="62"/>
+      <c r="B14" s="63" t="s">
         <v>37</v>
       </c>
-      <c r="C14" s="69"/>
-      <c r="D14" s="69"/>
-      <c r="E14" s="69"/>
-      <c r="F14" s="53" t="n">
+      <c r="C14" s="62"/>
+      <c r="D14" s="62"/>
+      <c r="E14" s="62"/>
+      <c r="F14" s="48" t="n">
         <f aca="false">SUM(F7:F13)</f>
         <v>1000</v>
       </c>
-      <c r="G14" s="54" t="n">
+      <c r="G14" s="49" t="n">
         <f aca="false">SUM(G7:G13)</f>
         <v>1719.57701348957</v>
       </c>
-      <c r="H14" s="54" t="n">
+      <c r="H14" s="49" t="n">
         <f aca="false">SUM(H7:H13)</f>
         <v>2719.57701348957</v>
       </c>
-      <c r="I14" s="69"/>
-      <c r="J14" s="54" t="n">
+      <c r="I14" s="62"/>
+      <c r="J14" s="49" t="n">
         <f aca="false">SUM(J7:J13)</f>
         <v>701.846509693851</v>
       </c>
-      <c r="K14" s="55" t="n">
+      <c r="K14" s="50" t="n">
         <f aca="false">SUM(K7:K13)</f>
         <v>-298.153490306149</v>
       </c>
-      <c r="L14" s="65" t="n">
+      <c r="L14" s="58" t="n">
         <f aca="false">SUM(L7:L13)</f>
         <v>3.62</v>
       </c>
-      <c r="M14" s="69"/>
+      <c r="M14" s="62"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="4" t="s">
@@ -6773,7 +6567,7 @@
       <c r="B17" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="C17" s="56" t="n">
+      <c r="C17" s="51" t="n">
         <f aca="false">COUNTIF(I7:I13,"Win")</f>
         <v>3</v>
       </c>
@@ -6782,7 +6576,7 @@
       <c r="B18" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="C18" s="56" t="n">
+      <c r="C18" s="51" t="n">
         <f aca="false">COUNTIF(I7:I13,"Loss")</f>
         <v>4</v>
       </c>
@@ -6791,7 +6585,7 @@
       <c r="B19" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="C19" s="56" t="n">
+      <c r="C19" s="51" t="n">
         <f aca="false">COUNTIF(I7:I13,"Push")</f>
         <v>0</v>
       </c>
@@ -6800,7 +6594,7 @@
       <c r="B20" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="C20" s="56" t="n">
+      <c r="C20" s="51" t="n">
         <f aca="false">COUNTIF(I7:I13,"Pending")</f>
         <v>0</v>
       </c>
@@ -6809,7 +6603,7 @@
       <c r="B21" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="C21" s="57" t="n">
+      <c r="C21" s="52" t="n">
         <f aca="false">IF(COUNTIF(I7:I13,"Win")+COUNTIF(I7:I13,"Loss")=0,"—",COUNTIF(I7:I13,"Win")/(COUNTIF(I7:I13,"Win")+COUNTIF(I7:I13,"Loss")))</f>
         <v>0.428571428571429</v>
       </c>
@@ -6818,7 +6612,7 @@
       <c r="B22" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="C22" s="58" t="n">
+      <c r="C22" s="33" t="n">
         <f aca="false">SUM(F7:F13)</f>
         <v>1000</v>
       </c>
@@ -6827,7 +6621,7 @@
       <c r="B23" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="C23" s="46" t="n">
+      <c r="C23" s="41" t="n">
         <f aca="false">SUM(J7:J13)</f>
         <v>701.846509693851</v>
       </c>
@@ -6836,7 +6630,7 @@
       <c r="B24" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="C24" s="48" t="n">
+      <c r="C24" s="43" t="n">
         <f aca="false">SUM(K7:K13)</f>
         <v>-298.153490306149</v>
       </c>
@@ -6845,7 +6639,7 @@
       <c r="B25" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="C25" s="57" t="n">
+      <c r="C25" s="52" t="n">
         <f aca="false">IF(SUM(F7:F13)=0,"—",SUM(K7:K13)/SUM(F7:F13))</f>
         <v>-0.298153490306149</v>
       </c>
@@ -6854,7 +6648,7 @@
       <c r="B26" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="C26" s="46" t="n">
+      <c r="C26" s="41" t="n">
         <f aca="false">SUM(H7:H13)</f>
         <v>2719.57701348957</v>
       </c>
@@ -6863,7 +6657,7 @@
       <c r="B27" s="5" t="s">
         <v>241</v>
       </c>
-      <c r="C27" s="66" t="n">
+      <c r="C27" s="59" t="n">
         <f aca="false">SUM(L7:L13)</f>
         <v>3.62</v>
       </c>
@@ -6872,13 +6666,13 @@
       <c r="B28" s="5" t="s">
         <v>242</v>
       </c>
-      <c r="C28" s="48" t="n">
+      <c r="C28" s="43" t="n">
         <f aca="false">SUMPRODUCT(L7:L13,G7:G13)-SUMPRODUCT(1-L7:L13,F7:F13)</f>
         <v>84.7416091107209</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="61" t="s">
+      <c r="A30" s="34" t="s">
         <v>393</v>
       </c>
     </row>
@@ -6937,10 +6731,10 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="35" t="s">
         <v>394</v>
       </c>
-      <c r="H1" s="62" t="s">
+      <c r="H1" s="55" t="s">
         <v>395</v>
       </c>
     </row>
@@ -6960,375 +6754,375 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="14" t="s">
+      <c r="A6" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="12" t="s">
         <v>196</v>
       </c>
-      <c r="D6" s="14" t="s">
+      <c r="D6" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="E6" s="14" t="s">
+      <c r="E6" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="F6" s="14" t="s">
+      <c r="F6" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="G6" s="14" t="s">
+      <c r="G6" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="H6" s="14" t="s">
+      <c r="H6" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="I6" s="14" t="s">
+      <c r="I6" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="J6" s="14" t="s">
+      <c r="J6" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="K6" s="14" t="s">
+      <c r="K6" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="L6" s="14" t="s">
+      <c r="L6" s="12" t="s">
         <v>216</v>
       </c>
-      <c r="M6" s="14" t="s">
+      <c r="M6" s="12" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="36" t="n">
+      <c r="A7" s="32" t="n">
         <v>1</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>398</v>
       </c>
-      <c r="C7" s="35" t="s">
+      <c r="C7" s="31" t="s">
         <v>283</v>
       </c>
-      <c r="D7" s="36" t="s">
+      <c r="D7" s="32" t="s">
         <v>186</v>
       </c>
-      <c r="E7" s="44" t="n">
+      <c r="E7" s="39" t="n">
         <v>450</v>
       </c>
-      <c r="F7" s="45" t="n">
+      <c r="F7" s="40" t="n">
         <v>200</v>
       </c>
-      <c r="G7" s="46" t="n">
+      <c r="G7" s="41" t="n">
         <f aca="false">IF(E7&gt;0,F7*E7/100,F7*100/ABS(E7))</f>
         <v>900</v>
       </c>
-      <c r="H7" s="46" t="n">
+      <c r="H7" s="41" t="n">
         <f aca="false">F7+G7</f>
         <v>1100</v>
       </c>
-      <c r="I7" s="63" t="s">
+      <c r="I7" s="56" t="s">
         <v>119</v>
       </c>
-      <c r="J7" s="46" t="n">
+      <c r="J7" s="41" t="n">
         <f aca="false">IF(I7="Win",F7+G7,IF(I7="Push",F7,IF(I7="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K7" s="48" t="n">
+      <c r="K7" s="43" t="n">
         <f aca="false">IF(I7="Pending",0,J7-F7)</f>
         <v>0</v>
       </c>
-      <c r="L7" s="79" t="n">
+      <c r="L7" s="72" t="n">
         <v>0.18</v>
       </c>
-      <c r="M7" s="68" t="s">
+      <c r="M7" s="61" t="s">
         <v>399</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="36" t="n">
+      <c r="A8" s="32" t="n">
         <v>2</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>400</v>
       </c>
-      <c r="C8" s="35" t="s">
+      <c r="C8" s="31" t="s">
         <v>283</v>
       </c>
-      <c r="D8" s="36" t="s">
+      <c r="D8" s="32" t="s">
         <v>186</v>
       </c>
-      <c r="E8" s="44" t="n">
+      <c r="E8" s="39" t="n">
         <v>1600</v>
       </c>
-      <c r="F8" s="45" t="n">
+      <c r="F8" s="40" t="n">
         <v>100</v>
       </c>
-      <c r="G8" s="46" t="n">
+      <c r="G8" s="41" t="n">
         <f aca="false">IF(E8&gt;0,F8*E8/100,F8*100/ABS(E8))</f>
         <v>1600</v>
       </c>
-      <c r="H8" s="46" t="n">
+      <c r="H8" s="41" t="n">
         <f aca="false">F8+G8</f>
         <v>1700</v>
       </c>
-      <c r="I8" s="63" t="s">
+      <c r="I8" s="56" t="s">
         <v>119</v>
       </c>
-      <c r="J8" s="46" t="n">
+      <c r="J8" s="41" t="n">
         <f aca="false">IF(I8="Win",F8+G8,IF(I8="Push",F8,IF(I8="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K8" s="48" t="n">
+      <c r="K8" s="43" t="n">
         <f aca="false">IF(I8="Pending",0,J8-F8)</f>
         <v>0</v>
       </c>
-      <c r="L8" s="79" t="n">
+      <c r="L8" s="72" t="n">
         <v>0.07</v>
       </c>
-      <c r="M8" s="68" t="s">
+      <c r="M8" s="61" t="s">
         <v>401</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="36" t="n">
+      <c r="A9" s="32" t="n">
         <v>3</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>402</v>
       </c>
-      <c r="C9" s="35" t="s">
+      <c r="C9" s="31" t="s">
         <v>283</v>
       </c>
-      <c r="D9" s="36" t="s">
+      <c r="D9" s="32" t="s">
         <v>186</v>
       </c>
-      <c r="E9" s="44" t="n">
+      <c r="E9" s="39" t="n">
         <v>1600</v>
       </c>
-      <c r="F9" s="45" t="n">
+      <c r="F9" s="40" t="n">
         <v>100</v>
       </c>
-      <c r="G9" s="46" t="n">
+      <c r="G9" s="41" t="n">
         <f aca="false">IF(E9&gt;0,F9*E9/100,F9*100/ABS(E9))</f>
         <v>1600</v>
       </c>
-      <c r="H9" s="46" t="n">
+      <c r="H9" s="41" t="n">
         <f aca="false">F9+G9</f>
         <v>1700</v>
       </c>
-      <c r="I9" s="63" t="s">
+      <c r="I9" s="56" t="s">
         <v>119</v>
       </c>
-      <c r="J9" s="46" t="n">
+      <c r="J9" s="41" t="n">
         <f aca="false">IF(I9="Win",F9+G9,IF(I9="Push",F9,IF(I9="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K9" s="48" t="n">
+      <c r="K9" s="43" t="n">
         <f aca="false">IF(I9="Pending",0,J9-F9)</f>
         <v>0</v>
       </c>
-      <c r="L9" s="79" t="n">
+      <c r="L9" s="72" t="n">
         <v>0.07</v>
       </c>
-      <c r="M9" s="68" t="s">
+      <c r="M9" s="61" t="s">
         <v>403</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="36" t="n">
+      <c r="A10" s="32" t="n">
         <v>4</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>404</v>
       </c>
-      <c r="C10" s="35" t="s">
+      <c r="C10" s="31" t="s">
         <v>283</v>
       </c>
-      <c r="D10" s="36" t="s">
+      <c r="D10" s="32" t="s">
         <v>186</v>
       </c>
-      <c r="E10" s="44" t="n">
+      <c r="E10" s="39" t="n">
         <v>2000</v>
       </c>
-      <c r="F10" s="45" t="n">
+      <c r="F10" s="40" t="n">
         <v>80</v>
       </c>
-      <c r="G10" s="46" t="n">
+      <c r="G10" s="41" t="n">
         <f aca="false">IF(E10&gt;0,F10*E10/100,F10*100/ABS(E10))</f>
         <v>1600</v>
       </c>
-      <c r="H10" s="46" t="n">
+      <c r="H10" s="41" t="n">
         <f aca="false">F10+G10</f>
         <v>1680</v>
       </c>
-      <c r="I10" s="63" t="s">
+      <c r="I10" s="56" t="s">
         <v>119</v>
       </c>
-      <c r="J10" s="46" t="n">
+      <c r="J10" s="41" t="n">
         <f aca="false">IF(I10="Win",F10+G10,IF(I10="Push",F10,IF(I10="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K10" s="48" t="n">
+      <c r="K10" s="43" t="n">
         <f aca="false">IF(I10="Pending",0,J10-F10)</f>
         <v>0</v>
       </c>
-      <c r="L10" s="79" t="n">
+      <c r="L10" s="72" t="n">
         <v>0.055</v>
       </c>
-      <c r="M10" s="68" t="s">
+      <c r="M10" s="61" t="s">
         <v>405</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="36" t="n">
+      <c r="A11" s="32" t="n">
         <v>5</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>406</v>
       </c>
-      <c r="C11" s="35" t="s">
+      <c r="C11" s="31" t="s">
         <v>283</v>
       </c>
-      <c r="D11" s="36" t="s">
+      <c r="D11" s="32" t="s">
         <v>186</v>
       </c>
-      <c r="E11" s="44" t="n">
+      <c r="E11" s="39" t="n">
         <v>2800</v>
       </c>
-      <c r="F11" s="45" t="n">
+      <c r="F11" s="40" t="n">
         <v>70</v>
       </c>
-      <c r="G11" s="46" t="n">
+      <c r="G11" s="41" t="n">
         <f aca="false">IF(E11&gt;0,F11*E11/100,F11*100/ABS(E11))</f>
         <v>1960</v>
       </c>
-      <c r="H11" s="46" t="n">
+      <c r="H11" s="41" t="n">
         <f aca="false">F11+G11</f>
         <v>2030</v>
       </c>
-      <c r="I11" s="63" t="s">
+      <c r="I11" s="56" t="s">
         <v>119</v>
       </c>
-      <c r="J11" s="46" t="n">
+      <c r="J11" s="41" t="n">
         <f aca="false">IF(I11="Win",F11+G11,IF(I11="Push",F11,IF(I11="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K11" s="48" t="n">
+      <c r="K11" s="43" t="n">
         <f aca="false">IF(I11="Pending",0,J11-F11)</f>
         <v>0</v>
       </c>
-      <c r="L11" s="79" t="n">
+      <c r="L11" s="72" t="n">
         <v>0.045</v>
       </c>
-      <c r="M11" s="68" t="s">
+      <c r="M11" s="61" t="s">
         <v>407</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="36" t="n">
+      <c r="A12" s="32" t="n">
         <v>6</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>408</v>
       </c>
-      <c r="C12" s="35" t="s">
+      <c r="C12" s="31" t="s">
         <v>283</v>
       </c>
-      <c r="D12" s="36" t="s">
+      <c r="D12" s="32" t="s">
         <v>186</v>
       </c>
-      <c r="E12" s="44" t="n">
+      <c r="E12" s="39" t="n">
         <v>5000</v>
       </c>
-      <c r="F12" s="45" t="n">
+      <c r="F12" s="40" t="n">
         <v>50</v>
       </c>
-      <c r="G12" s="46" t="n">
+      <c r="G12" s="41" t="n">
         <f aca="false">IF(E12&gt;0,F12*E12/100,F12*100/ABS(E12))</f>
         <v>2500</v>
       </c>
-      <c r="H12" s="46" t="n">
+      <c r="H12" s="41" t="n">
         <f aca="false">F12+G12</f>
         <v>2550</v>
       </c>
-      <c r="I12" s="63" t="s">
+      <c r="I12" s="56" t="s">
         <v>119</v>
       </c>
-      <c r="J12" s="46" t="n">
+      <c r="J12" s="41" t="n">
         <f aca="false">IF(I12="Win",F12+G12,IF(I12="Push",F12,IF(I12="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K12" s="48" t="n">
+      <c r="K12" s="43" t="n">
         <f aca="false">IF(I12="Pending",0,J12-F12)</f>
         <v>0</v>
       </c>
-      <c r="L12" s="79" t="n">
+      <c r="L12" s="72" t="n">
         <v>0.025</v>
       </c>
-      <c r="M12" s="68" t="s">
+      <c r="M12" s="61" t="s">
         <v>409</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="80" t="n">
+      <c r="A13" s="73" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="23" t="s">
+      <c r="B13" s="21" t="s">
         <v>410</v>
       </c>
-      <c r="C13" s="80" t="s">
+      <c r="C13" s="73" t="s">
         <v>411</v>
       </c>
-      <c r="D13" s="80" t="s">
+      <c r="D13" s="73" t="s">
         <v>61</v>
       </c>
-      <c r="E13" s="80"/>
-      <c r="F13" s="80"/>
-      <c r="G13" s="80"/>
-      <c r="H13" s="80"/>
-      <c r="I13" s="80"/>
-      <c r="J13" s="80"/>
-      <c r="K13" s="80"/>
-      <c r="L13" s="80"/>
-      <c r="M13" s="80" t="s">
+      <c r="E13" s="73"/>
+      <c r="F13" s="73"/>
+      <c r="G13" s="73"/>
+      <c r="H13" s="73"/>
+      <c r="I13" s="73"/>
+      <c r="J13" s="73"/>
+      <c r="K13" s="73"/>
+      <c r="L13" s="73"/>
+      <c r="M13" s="73" t="s">
         <v>412</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="69"/>
-      <c r="B14" s="70" t="s">
+      <c r="A14" s="62"/>
+      <c r="B14" s="63" t="s">
         <v>413</v>
       </c>
-      <c r="C14" s="69"/>
-      <c r="D14" s="69"/>
-      <c r="E14" s="69"/>
-      <c r="F14" s="53" t="n">
+      <c r="C14" s="62"/>
+      <c r="D14" s="62"/>
+      <c r="E14" s="62"/>
+      <c r="F14" s="48" t="n">
         <f aca="false">SUM(F7:F13)</f>
         <v>600</v>
       </c>
-      <c r="G14" s="54" t="n">
+      <c r="G14" s="49" t="n">
         <f aca="false">SUM(G7:G12)</f>
         <v>10160</v>
       </c>
-      <c r="H14" s="54" t="n">
+      <c r="H14" s="49" t="n">
         <f aca="false">SUM(H7:H12)</f>
         <v>10760</v>
       </c>
-      <c r="I14" s="69"/>
-      <c r="J14" s="54" t="n">
+      <c r="I14" s="62"/>
+      <c r="J14" s="49" t="n">
         <f aca="false">SUM(J7:J12)</f>
         <v>0</v>
       </c>
-      <c r="K14" s="55" t="n">
+      <c r="K14" s="50" t="n">
         <f aca="false">SUM(K7:K12)</f>
         <v>0</v>
       </c>
-      <c r="L14" s="81" t="n">
+      <c r="L14" s="74" t="n">
         <f aca="false">SUM(L7:L12)</f>
         <v>0.445</v>
       </c>
-      <c r="M14" s="69"/>
+      <c r="M14" s="62"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="4" t="s">
@@ -7339,7 +7133,7 @@
       <c r="B17" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="C17" s="56" t="n">
+      <c r="C17" s="51" t="n">
         <f aca="false">COUNTIF(I7:I12,"Win")</f>
         <v>0</v>
       </c>
@@ -7348,7 +7142,7 @@
       <c r="B18" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="C18" s="56" t="n">
+      <c r="C18" s="51" t="n">
         <f aca="false">COUNTIF(I7:I12,"Loss")</f>
         <v>0</v>
       </c>
@@ -7357,7 +7151,7 @@
       <c r="B19" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="C19" s="56" t="n">
+      <c r="C19" s="51" t="n">
         <f aca="false">COUNTIF(I7:I12,"Pending")</f>
         <v>6</v>
       </c>
@@ -7366,7 +7160,7 @@
       <c r="B20" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="C20" s="57" t="str">
+      <c r="C20" s="52" t="str">
         <f aca="false">IF(COUNTIF(I7:I12,"Win")+COUNTIF(I7:I12,"Loss")=0,"—",COUNTIF(I7:I12,"Win")/(COUNTIF(I7:I12,"Win")+COUNTIF(I7:I12,"Loss")))</f>
         <v>—</v>
       </c>
@@ -7375,7 +7169,7 @@
       <c r="B21" s="5" t="s">
         <v>414</v>
       </c>
-      <c r="C21" s="58" t="n">
+      <c r="C21" s="33" t="n">
         <f aca="false">SUM(F7:F12)</f>
         <v>600</v>
       </c>
@@ -7384,7 +7178,7 @@
       <c r="B22" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="C22" s="46" t="n">
+      <c r="C22" s="41" t="n">
         <f aca="false">SUM(J7:J12)</f>
         <v>0</v>
       </c>
@@ -7393,7 +7187,7 @@
       <c r="B23" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="C23" s="48" t="n">
+      <c r="C23" s="43" t="n">
         <f aca="false">SUM(K7:K12)</f>
         <v>0</v>
       </c>
@@ -7402,7 +7196,7 @@
       <c r="B24" s="5" t="s">
         <v>415</v>
       </c>
-      <c r="C24" s="57" t="n">
+      <c r="C24" s="52" t="n">
         <f aca="false">SUM(L7:L12)</f>
         <v>0.445</v>
       </c>
@@ -7449,430 +7243,430 @@
   <dimension ref="A1:M14"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="46"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="82" t="s">
+    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="35" t="s">
         <v>416</v>
       </c>
-      <c r="H1" s="83" t="s">
+      <c r="H1" s="75" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="84" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>418</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="84" t="s">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="85" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="4" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="14" t="s">
+    <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="12" t="s">
         <v>196</v>
       </c>
-      <c r="D6" s="14" t="s">
+      <c r="D6" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="E6" s="14" t="s">
+      <c r="E6" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="F6" s="14" t="s">
+      <c r="F6" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="G6" s="14" t="s">
+      <c r="G6" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="H6" s="14" t="s">
+      <c r="H6" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="I6" s="14" t="s">
+      <c r="I6" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="J6" s="14" t="s">
+      <c r="J6" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="K6" s="14" t="s">
+      <c r="K6" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="L6" s="14" t="s">
+      <c r="L6" s="12" t="s">
         <v>216</v>
       </c>
-      <c r="M6" s="14" t="s">
+      <c r="M6" s="12" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="36" t="n">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="32" t="n">
         <v>1</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>420</v>
       </c>
-      <c r="C7" s="35" t="s">
+      <c r="C7" s="31" t="s">
         <v>283</v>
       </c>
-      <c r="D7" s="36" t="s">
+      <c r="D7" s="32" t="s">
         <v>186</v>
       </c>
-      <c r="E7" s="44" t="n">
+      <c r="E7" s="39" t="n">
         <v>310</v>
       </c>
-      <c r="F7" s="86" t="n">
+      <c r="F7" s="40" t="n">
         <v>220</v>
       </c>
-      <c r="G7" s="87" t="n">
+      <c r="G7" s="41" t="n">
         <f aca="false">IF(E7&gt;0,F7*E7/100,F7*100/ABS(E7))</f>
         <v>682</v>
       </c>
-      <c r="H7" s="87" t="n">
+      <c r="H7" s="41" t="n">
         <f aca="false">F7+G7</f>
         <v>902</v>
       </c>
-      <c r="I7" s="63" t="s">
+      <c r="I7" s="56" t="s">
         <v>119</v>
       </c>
-      <c r="J7" s="87" t="n">
+      <c r="J7" s="41" t="n">
         <f aca="false">IF(I7="Win",F7+G7,IF(I7="Push",F7,IF(I7="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K7" s="88" t="n">
+      <c r="K7" s="43" t="n">
         <f aca="false">IF(I7="Pending",0,J7-F7)</f>
         <v>0</v>
       </c>
-      <c r="L7" s="79" t="n">
+      <c r="L7" s="72" t="n">
         <v>0.27</v>
       </c>
-      <c r="M7" s="68" t="s">
+      <c r="M7" s="61" t="s">
         <v>421</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="36" t="n">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="32" t="n">
         <v>2</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>422</v>
       </c>
-      <c r="C8" s="35" t="s">
+      <c r="C8" s="31" t="s">
         <v>283</v>
       </c>
-      <c r="D8" s="36" t="s">
+      <c r="D8" s="32" t="s">
         <v>186</v>
       </c>
-      <c r="E8" s="44" t="n">
+      <c r="E8" s="39" t="n">
         <v>425</v>
       </c>
-      <c r="F8" s="86" t="n">
+      <c r="F8" s="40" t="n">
         <v>130</v>
       </c>
-      <c r="G8" s="87" t="n">
+      <c r="G8" s="41" t="n">
         <f aca="false">IF(E8&gt;0,F8*E8/100,F8*100/ABS(E8))</f>
         <v>552.5</v>
       </c>
-      <c r="H8" s="87" t="n">
+      <c r="H8" s="41" t="n">
         <f aca="false">F8+G8</f>
         <v>682.5</v>
       </c>
-      <c r="I8" s="63" t="s">
+      <c r="I8" s="56" t="s">
         <v>119</v>
       </c>
-      <c r="J8" s="87" t="n">
+      <c r="J8" s="41" t="n">
         <f aca="false">IF(I8="Win",F8+G8,IF(I8="Push",F8,IF(I8="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K8" s="88" t="n">
+      <c r="K8" s="43" t="n">
         <f aca="false">IF(I8="Pending",0,J8-F8)</f>
         <v>0</v>
       </c>
-      <c r="L8" s="79" t="n">
+      <c r="L8" s="72" t="n">
         <v>0.18</v>
       </c>
-      <c r="M8" s="68" t="s">
+      <c r="M8" s="61" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="36" t="n">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="32" t="n">
         <v>3</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>424</v>
       </c>
-      <c r="C9" s="35" t="s">
+      <c r="C9" s="31" t="s">
         <v>425</v>
       </c>
-      <c r="D9" s="36" t="s">
+      <c r="D9" s="32" t="s">
         <v>90</v>
       </c>
-      <c r="E9" s="44" t="n">
+      <c r="E9" s="39" t="n">
         <v>-110</v>
       </c>
-      <c r="F9" s="86" t="n">
+      <c r="F9" s="40" t="n">
         <v>180</v>
       </c>
-      <c r="G9" s="87" t="n">
+      <c r="G9" s="41" t="n">
         <f aca="false">IF(E9&gt;0,F9*E9/100,F9*100/ABS(E9))</f>
         <v>163.636363636364</v>
       </c>
-      <c r="H9" s="87" t="n">
+      <c r="H9" s="41" t="n">
         <f aca="false">F9+G9</f>
         <v>343.636363636364</v>
       </c>
-      <c r="I9" s="63" t="s">
+      <c r="I9" s="56" t="s">
         <v>119</v>
       </c>
-      <c r="J9" s="87" t="n">
+      <c r="J9" s="41" t="n">
         <f aca="false">IF(I9="Win",F9+G9,IF(I9="Push",F9,IF(I9="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K9" s="88" t="n">
+      <c r="K9" s="43" t="n">
         <f aca="false">IF(I9="Pending",0,J9-F9)</f>
         <v>0</v>
       </c>
-      <c r="L9" s="79" t="n">
+      <c r="L9" s="72" t="n">
         <v>0.6</v>
       </c>
-      <c r="M9" s="68" t="s">
+      <c r="M9" s="61" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="36" t="n">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="32" t="n">
         <v>4</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>427</v>
       </c>
-      <c r="C10" s="35" t="s">
+      <c r="C10" s="31" t="s">
         <v>428</v>
       </c>
-      <c r="D10" s="36" t="s">
+      <c r="D10" s="32" t="s">
         <v>90</v>
       </c>
-      <c r="E10" s="44" t="n">
+      <c r="E10" s="39" t="n">
         <v>-110</v>
       </c>
-      <c r="F10" s="86" t="n">
+      <c r="F10" s="40" t="n">
         <v>150</v>
       </c>
-      <c r="G10" s="87" t="n">
+      <c r="G10" s="41" t="n">
         <f aca="false">IF(E10&gt;0,F10*E10/100,F10*100/ABS(E10))</f>
         <v>136.363636363636</v>
       </c>
-      <c r="H10" s="87" t="n">
+      <c r="H10" s="41" t="n">
         <f aca="false">F10+G10</f>
         <v>286.363636363636</v>
       </c>
-      <c r="I10" s="63" t="s">
+      <c r="I10" s="56" t="s">
         <v>119</v>
       </c>
-      <c r="J10" s="87" t="n">
+      <c r="J10" s="41" t="n">
         <f aca="false">IF(I10="Win",F10+G10,IF(I10="Push",F10,IF(I10="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K10" s="88" t="n">
+      <c r="K10" s="43" t="n">
         <f aca="false">IF(I10="Pending",0,J10-F10)</f>
         <v>0</v>
       </c>
-      <c r="L10" s="79" t="n">
+      <c r="L10" s="72" t="n">
         <v>0.58</v>
       </c>
-      <c r="M10" s="68" t="s">
+      <c r="M10" s="61" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="36" t="n">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="32" t="n">
         <v>5</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>430</v>
       </c>
-      <c r="C11" s="35" t="s">
+      <c r="C11" s="31" t="s">
         <v>425</v>
       </c>
-      <c r="D11" s="36" t="s">
+      <c r="D11" s="32" t="s">
         <v>90</v>
       </c>
-      <c r="E11" s="44" t="n">
+      <c r="E11" s="39" t="n">
         <v>-110</v>
       </c>
-      <c r="F11" s="86" t="n">
+      <c r="F11" s="40" t="n">
         <v>120</v>
       </c>
-      <c r="G11" s="87" t="n">
+      <c r="G11" s="41" t="n">
         <f aca="false">IF(E11&gt;0,F11*E11/100,F11*100/ABS(E11))</f>
         <v>109.090909090909</v>
       </c>
-      <c r="H11" s="87" t="n">
+      <c r="H11" s="41" t="n">
         <f aca="false">F11+G11</f>
         <v>229.090909090909</v>
       </c>
-      <c r="I11" s="63" t="s">
+      <c r="I11" s="56" t="s">
         <v>119</v>
       </c>
-      <c r="J11" s="87" t="n">
+      <c r="J11" s="41" t="n">
         <f aca="false">IF(I11="Win",F11+G11,IF(I11="Push",F11,IF(I11="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K11" s="88" t="n">
+      <c r="K11" s="43" t="n">
         <f aca="false">IF(I11="Pending",0,J11-F11)</f>
         <v>0</v>
       </c>
-      <c r="L11" s="79" t="n">
+      <c r="L11" s="72" t="n">
         <v>0.57</v>
       </c>
-      <c r="M11" s="68" t="s">
+      <c r="M11" s="61" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="36" t="n">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="32" t="n">
         <v>6</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>432</v>
       </c>
-      <c r="C12" s="35" t="s">
+      <c r="C12" s="31" t="s">
         <v>433</v>
       </c>
-      <c r="D12" s="36" t="s">
+      <c r="D12" s="32" t="s">
         <v>90</v>
       </c>
-      <c r="E12" s="44" t="n">
+      <c r="E12" s="39" t="n">
         <v>-110</v>
       </c>
-      <c r="F12" s="86" t="n">
+      <c r="F12" s="40" t="n">
         <v>125</v>
       </c>
-      <c r="G12" s="87" t="n">
+      <c r="G12" s="41" t="n">
         <f aca="false">IF(E12&gt;0,F12*E12/100,F12*100/ABS(E12))</f>
         <v>113.636363636364</v>
       </c>
-      <c r="H12" s="87" t="n">
+      <c r="H12" s="41" t="n">
         <f aca="false">F12+G12</f>
         <v>238.636363636364</v>
       </c>
-      <c r="I12" s="63" t="s">
-        <v>119</v>
-      </c>
-      <c r="J12" s="87" t="n">
+      <c r="I12" s="56" t="s">
+        <v>86</v>
+      </c>
+      <c r="J12" s="41" t="n">
         <f aca="false">IF(I12="Win",F12+G12,IF(I12="Push",F12,IF(I12="Loss",0,0)))</f>
-        <v>0</v>
-      </c>
-      <c r="K12" s="88" t="n">
+        <v>238.636363636364</v>
+      </c>
+      <c r="K12" s="43" t="n">
         <f aca="false">IF(I12="Pending",0,J12-F12)</f>
-        <v>0</v>
-      </c>
-      <c r="L12" s="79" t="n">
+        <v>113.636363636364</v>
+      </c>
+      <c r="L12" s="72" t="n">
         <v>0.56</v>
       </c>
-      <c r="M12" s="68" t="s">
+      <c r="M12" s="61" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="36" t="n">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="32" t="n">
         <v>7</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>435</v>
       </c>
-      <c r="C13" s="35" t="s">
+      <c r="C13" s="31" t="s">
         <v>283</v>
       </c>
-      <c r="D13" s="36" t="s">
+      <c r="D13" s="32" t="s">
         <v>186</v>
       </c>
-      <c r="E13" s="44" t="n">
+      <c r="E13" s="39" t="n">
         <v>1400</v>
       </c>
-      <c r="F13" s="86" t="n">
+      <c r="F13" s="40" t="n">
         <v>75</v>
       </c>
-      <c r="G13" s="87" t="n">
+      <c r="G13" s="41" t="n">
         <f aca="false">IF(E13&gt;0,F13*E13/100,F13*100/ABS(E13))</f>
         <v>1050</v>
       </c>
-      <c r="H13" s="87" t="n">
+      <c r="H13" s="41" t="n">
         <f aca="false">F13+G13</f>
         <v>1125</v>
       </c>
-      <c r="I13" s="63" t="s">
+      <c r="I13" s="56" t="s">
         <v>119</v>
       </c>
-      <c r="J13" s="87" t="n">
+      <c r="J13" s="41" t="n">
         <f aca="false">IF(I13="Win",F13+G13,IF(I13="Push",F13,IF(I13="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K13" s="88" t="n">
+      <c r="K13" s="43" t="n">
         <f aca="false">IF(I13="Pending",0,J13-F13)</f>
         <v>0</v>
       </c>
-      <c r="L13" s="79" t="n">
+      <c r="L13" s="72" t="n">
         <v>0.07</v>
       </c>
-      <c r="M13" s="68" t="s">
+      <c r="M13" s="61" t="s">
         <v>436</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="85" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B14" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="F14" s="32" t="n">
+      <c r="F14" s="8" t="n">
         <f aca="false">SUM(F7:F13)</f>
         <v>1000</v>
       </c>
-      <c r="G14" s="32" t="n">
+      <c r="G14" s="8" t="n">
         <f aca="false">SUM(G7:G13)</f>
         <v>2807.22727272727</v>
       </c>
-      <c r="H14" s="32" t="n">
+      <c r="H14" s="8" t="n">
         <f aca="false">SUM(H7:H13)</f>
         <v>3807.22727272727</v>
       </c>
-      <c r="J14" s="32" t="n">
+      <c r="J14" s="8" t="n">
         <f aca="false">SUM(J7:J13)</f>
-        <v>0</v>
-      </c>
-      <c r="K14" s="32" t="n">
+        <v>238.636363636364</v>
+      </c>
+      <c r="K14" s="8" t="n">
         <f aca="false">SUM(K7:K13)</f>
-        <v>0</v>
+        <v>113.636363636364</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="K7:K14">
-    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>AND(ISNUMBER(K7),K7&gt;0)</formula>
     </cfRule>
-    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>AND(ISNUMBER(K7),K7&lt;0)</formula>
     </cfRule>
   </conditionalFormatting>

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -1281,7 +1281,7 @@
     <t xml:space="preserve">TEST 8 — MLB HOME RUN DERBY · CITIZENS BANK PARK, PHILADELPHIA · JULY 13, 2026</t>
   </si>
   <si>
-    <t xml:space="preserve">STATUS: ACTIVE — LIVE, R1 in progress; longest-HR prop cashed</t>
+    <t xml:space="preserve">STATUS: ACTIVE — 1-1 (−$6.36) · semis: Contreras(1) v Schwarber(4), Walker(2) v Caminero(3)</t>
   </si>
   <si>
     <t xml:space="preserve">8 PM ET / 7 CT on Netflix · Source: cards/hrderby-jul13-betting-card.html · Outrights: DraftKings ~9 AM CT Jul 13 · Props: Action Network / VSiN lines, -110 std price</t>
@@ -1323,7 +1323,7 @@
     <t xml:space="preserve">Ben Rice R1 Over 9.5 HRs</t>
   </si>
   <si>
-    <t xml:space="preserve">Lefty pull power, 330-ft RF corner — VSiN lean</t>
+    <t xml:space="preserve">Lefty pull power, 330-ft RF corner — VSiN lean · RESULT: Rice 7 in R1 — under 9.5 (2 sources)</t>
   </si>
   <si>
     <t xml:space="preserve">Longest HR Over 484.5 ft</t>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="B6" s="7" t="n">
         <f aca="false">H24</f>
-        <v>-651.687770110249</v>
+        <v>-771.687770110249</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="B7" s="8" t="n">
         <f aca="false">B5+B6</f>
-        <v>4348.31222988975</v>
+        <v>4228.31222988975</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2300,7 +2300,7 @@
       </c>
       <c r="B8" s="9" t="n">
         <f aca="false">F24</f>
-        <v>2475</v>
+        <v>2355</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2387,7 +2387,7 @@
       </c>
       <c r="F16" s="17" t="n">
         <f aca="false">SUMIF('HR Derby'!I7:I13,"Pending",'HR Derby'!F7:F13)</f>
-        <v>875</v>
+        <v>755</v>
       </c>
       <c r="G16" s="17" t="n">
         <f aca="false">SUM('HR Derby'!J7:J13)</f>
@@ -2395,7 +2395,7 @@
       </c>
       <c r="H16" s="17" t="n">
         <f aca="false">SUM('HR Derby'!K7:K13)</f>
-        <v>113.636363636364</v>
+        <v>-6.36363636363637</v>
       </c>
       <c r="I16" s="18"/>
       <c r="J16" s="19"/>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="F24" s="8" t="n">
         <f aca="false">SUM(F16:F23)</f>
-        <v>2475</v>
+        <v>2355</v>
       </c>
       <c r="G24" s="8" t="n">
         <f aca="false">SUM(G16:G23)</f>
@@ -2662,7 +2662,7 @@
       </c>
       <c r="H24" s="8" t="n">
         <f aca="false">SUM(H16:H23)</f>
-        <v>-651.687770110249</v>
+        <v>-771.687770110249</v>
       </c>
       <c r="K24" s="1"/>
       <c r="L24" s="1"/>
@@ -7529,7 +7529,7 @@
         <v>229.090909090909</v>
       </c>
       <c r="I11" s="56" t="s">
-        <v>119</v>
+        <v>94</v>
       </c>
       <c r="J11" s="41" t="n">
         <f aca="false">IF(I11="Win",F11+G11,IF(I11="Push",F11,IF(I11="Loss",0,0)))</f>
@@ -7537,7 +7537,7 @@
       </c>
       <c r="K11" s="43" t="n">
         <f aca="false">IF(I11="Pending",0,J11-F11)</f>
-        <v>0</v>
+        <v>-120</v>
       </c>
       <c r="L11" s="72" t="n">
         <v>0.57</v>
@@ -7658,7 +7658,7 @@
       </c>
       <c r="K14" s="8" t="n">
         <f aca="false">SUM(K7:K13)</f>
-        <v>113.636363636364</v>
+        <v>-6.36363636363637</v>
       </c>
     </row>
   </sheetData>

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -1360,13 +1360,13 @@
     <t xml:space="preserve">TEST 9 — WNBA WEDNESDAY SLATE · JULY 15, 2026</t>
   </si>
   <si>
-    <t xml:space="preserve">STATUS: ACTIVE — draft; settles Wed night Jul 15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Source: cards/wnba-jul15-betting-card.html · Lines: DraftKings/Caesars/consensus, drafted ~9 PM CT Jul 14 · final lock ~9 AM CT Jul 15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 games: Sparks@Lynx (~12 PM CT), Storm@Sky (aft), Fever vs Valkyries 7 PM CT. Clark points line (row 10) confirmed at lock.</t>
+    <t xml:space="preserve">STATUS: ACTIVE — pre-game; settles Wed night Jul 15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source: cards/wnba-jul15-betting-card.html · Lines: DraftKings/Caesars/consensus, locked ~9 PM CT Jul 14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 games: Sparks@Lynx (~12 PM CT), Storm@Sky (aft), Fever vs Valkyries 7 PM CT. Clark prop = Over 22.5 points.</t>
   </si>
   <si>
     <t xml:space="preserve">Fever -3.5</t>
@@ -1396,10 +1396,10 @@
     <t xml:space="preserve">Lynx offense + Sparks poor D &amp; fast pace</t>
   </si>
   <si>
-    <t xml:space="preserve">Caitlin Clark Over points *</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Home usage; * points line confirmed at lock (~22.5)</t>
+    <t xml:space="preserve">Caitlin Clark Over 22.5 points</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Home usage vs beatable Valkyries D; Clark healthy, no minutes cap</t>
   </si>
   <si>
     <t xml:space="preserve">Chicago Sky ML</t>
@@ -1430,21 +1430,18 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="14">
+  <numFmts count="11">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="\$#,##0"/>
     <numFmt numFmtId="166" formatCode="\$#,##0.00;&quot;($&quot;#,##0.00\);\-"/>
     <numFmt numFmtId="167" formatCode="\$#,##0.00"/>
-    <numFmt numFmtId="168" formatCode="\$#,##0.00"/>
-    <numFmt numFmtId="169" formatCode="\$#,##0"/>
-    <numFmt numFmtId="170" formatCode="\+0;\-0"/>
-    <numFmt numFmtId="171" formatCode="0"/>
-    <numFmt numFmtId="172" formatCode="0.0%"/>
-    <numFmt numFmtId="173" formatCode="0%"/>
-    <numFmt numFmtId="174" formatCode="0.0&quot; exp. wins&quot;"/>
-    <numFmt numFmtId="175" formatCode="0.0"/>
-    <numFmt numFmtId="176" formatCode="0.00&quot; exp. wins&quot;"/>
-    <numFmt numFmtId="177" formatCode="\$#,##0.00;&quot;($&quot;#,##0.00\);\-"/>
+    <numFmt numFmtId="168" formatCode="\+0;\-0"/>
+    <numFmt numFmtId="169" formatCode="0"/>
+    <numFmt numFmtId="170" formatCode="0.0%"/>
+    <numFmt numFmtId="171" formatCode="0%"/>
+    <numFmt numFmtId="172" formatCode="0.0&quot; exp. wins&quot;"/>
+    <numFmt numFmtId="173" formatCode="0.0"/>
+    <numFmt numFmtId="174" formatCode="0.00&quot; exp. wins&quot;"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -1746,7 +1743,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="92">
+  <cellXfs count="78">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1795,23 +1792,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1827,15 +1812,15 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1851,7 +1836,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1867,27 +1852,19 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1903,12 +1880,8 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
@@ -1927,7 +1900,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1975,15 +1948,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2007,15 +1976,15 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="171" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="174" fontId="7" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="172" fontId="7" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="175" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2067,11 +2036,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="172" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2079,7 +2044,7 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="176" fontId="7" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="174" fontId="7" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2087,32 +2052,8 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="177" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -2124,35 +2065,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="4">
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <charset val="1"/>
-        <family val="0"/>
-        <b val="1"/>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <charset val="1"/>
-        <family val="0"/>
-        <b val="1"/>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="2">
     <dxf>
       <font>
         <name val="Arial"/>
@@ -2516,737 +2429,620 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="12" t="s">
+      <c r="A14" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B14" s="13"/>
-      <c r="C14" s="13"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="13"/>
-      <c r="F14" s="13"/>
-      <c r="G14" s="13"/>
-      <c r="H14" s="13"/>
-      <c r="I14" s="13"/>
-      <c r="J14" s="13"/>
-      <c r="K14" s="14"/>
-      <c r="L14" s="14"/>
-      <c r="M14" s="14"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="1"/>
+      <c r="M14" s="1"/>
     </row>
     <row r="15" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="15" t="s">
+      <c r="A15" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B15" s="15" t="s">
+      <c r="B15" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="15" t="s">
+      <c r="C15" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="D15" s="15" t="s">
+      <c r="D15" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="E15" s="15" t="s">
+      <c r="E15" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="F15" s="15" t="s">
+      <c r="F15" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G15" s="15" t="s">
+      <c r="G15" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="H15" s="15" t="s">
+      <c r="H15" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="I15" s="16"/>
-      <c r="J15" s="16"/>
-      <c r="K15" s="14"/>
-      <c r="L15" s="14"/>
-      <c r="M15" s="14"/>
+      <c r="I15" s="13"/>
+      <c r="J15" s="13"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="17" t="n">
+      <c r="A16" s="14" t="n">
         <v>9</v>
       </c>
-      <c r="B16" s="18" t="s">
+      <c r="B16" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="C16" s="17" t="s">
+      <c r="C16" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="D16" s="19" t="s">
+      <c r="D16" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="E16" s="20" t="n">
+      <c r="E16" s="17" t="n">
         <f aca="false">SUM('WNBA Jul 15'!F7:F13)</f>
         <v>1000</v>
       </c>
-      <c r="F16" s="20" t="n">
+      <c r="F16" s="17" t="n">
         <f aca="false">SUMIF('WNBA Jul 15'!I7:I13,"Pending",'WNBA Jul 15'!F7:F13)</f>
         <v>1000</v>
       </c>
-      <c r="G16" s="20" t="n">
+      <c r="G16" s="17" t="n">
         <f aca="false">SUM('WNBA Jul 15'!J7:J13)</f>
         <v>0</v>
       </c>
-      <c r="H16" s="20" t="n">
+      <c r="H16" s="17" t="n">
         <f aca="false">SUM('WNBA Jul 15'!K7:K13)</f>
         <v>0</v>
       </c>
-      <c r="I16" s="21"/>
-      <c r="J16" s="22"/>
-      <c r="K16" s="14"/>
-      <c r="L16" s="14"/>
-      <c r="M16" s="14"/>
+      <c r="I16" s="18"/>
+      <c r="J16" s="19"/>
+      <c r="K16" s="1"/>
+      <c r="L16" s="1"/>
+      <c r="M16" s="1"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="17" t="n">
+      <c r="A17" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="B17" s="18" t="s">
+      <c r="B17" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="C17" s="17" t="s">
+      <c r="C17" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="D17" s="19" t="s">
+      <c r="D17" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="E17" s="20" t="n">
+      <c r="E17" s="17" t="n">
         <f aca="false">SUM('World Cup 2026'!F7:F13)</f>
         <v>1000</v>
       </c>
-      <c r="F17" s="20" t="n">
+      <c r="F17" s="17" t="n">
         <f aca="false">SUMIF('World Cup 2026'!I7:I13,"Pending",'World Cup 2026'!F7:F13)</f>
         <v>1000</v>
       </c>
-      <c r="G17" s="20" t="n">
+      <c r="G17" s="17" t="n">
         <f aca="false">SUM('World Cup 2026'!J7:J13)</f>
         <v>0</v>
       </c>
-      <c r="H17" s="20" t="n">
+      <c r="H17" s="17" t="n">
         <f aca="false">SUM('World Cup 2026'!K7:K13)</f>
         <v>0</v>
       </c>
-      <c r="I17" s="21"/>
-      <c r="J17" s="22"/>
-      <c r="K17" s="14"/>
-      <c r="L17" s="14"/>
-      <c r="M17" s="14"/>
+      <c r="I17" s="18"/>
+      <c r="J17" s="19"/>
+      <c r="K17" s="1"/>
+      <c r="L17" s="1"/>
+      <c r="M17" s="1"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="17" t="n">
+      <c r="A18" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="B18" s="18" t="s">
+      <c r="B18" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="17" t="s">
+      <c r="C18" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="19" t="s">
+      <c r="D18" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="E18" s="20" t="n">
+      <c r="E18" s="17" t="n">
         <f aca="false">SUM('The Open'!F7:F12)</f>
         <v>600</v>
       </c>
-      <c r="F18" s="20" t="n">
+      <c r="F18" s="17" t="n">
         <f aca="false">SUMIF('The Open'!I7:I12,"Pending",'The Open'!F7:F12)</f>
         <v>600</v>
       </c>
-      <c r="G18" s="20" t="n">
+      <c r="G18" s="17" t="n">
         <f aca="false">SUM('The Open'!J7:J12)</f>
         <v>0</v>
       </c>
-      <c r="H18" s="20" t="n">
+      <c r="H18" s="17" t="n">
         <f aca="false">SUM('The Open'!K7:K12)</f>
         <v>0</v>
       </c>
-      <c r="I18" s="21"/>
-      <c r="J18" s="22"/>
-      <c r="K18" s="14"/>
-      <c r="L18" s="14"/>
-      <c r="M18" s="14"/>
+      <c r="I18" s="18"/>
+      <c r="J18" s="19"/>
+      <c r="K18" s="1"/>
+      <c r="L18" s="1"/>
+      <c r="M18" s="1"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="23" t="n">
+      <c r="A19" s="20" t="n">
         <v>7</v>
       </c>
-      <c r="B19" s="24" t="s">
+      <c r="B19" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="C19" s="23" t="s">
+      <c r="C19" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="D19" s="25" t="s">
+      <c r="D19" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="E19" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="21"/>
-      <c r="J19" s="22"/>
-      <c r="K19" s="14"/>
-      <c r="L19" s="14"/>
-      <c r="M19" s="14"/>
+      <c r="E19" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="18"/>
+      <c r="J19" s="19"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1"/>
+      <c r="M19" s="1"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="27" t="n">
+      <c r="A20" s="24" t="n">
         <v>8</v>
       </c>
-      <c r="B20" s="28" t="s">
+      <c r="B20" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="C20" s="27" t="s">
+      <c r="C20" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="D20" s="29" t="s">
+      <c r="D20" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="E20" s="30" t="n">
+      <c r="E20" s="27" t="n">
         <f aca="false">SUM('HR Derby'!F7:F13)</f>
         <v>1000</v>
       </c>
-      <c r="F20" s="30" t="n">
+      <c r="F20" s="27" t="n">
         <f aca="false">SUMIF('HR Derby'!I7:I13,"Pending",'HR Derby'!F7:F13)</f>
         <v>0</v>
       </c>
-      <c r="G20" s="30" t="n">
+      <c r="G20" s="27" t="n">
         <f aca="false">SUM('HR Derby'!J7:J13)</f>
         <v>525</v>
       </c>
-      <c r="H20" s="30" t="n">
+      <c r="H20" s="27" t="n">
         <f aca="false">SUM('HR Derby'!K7:K13)</f>
         <v>-475</v>
       </c>
-      <c r="I20" s="21"/>
-      <c r="J20" s="22"/>
-      <c r="K20" s="14"/>
-      <c r="L20" s="14"/>
-      <c r="M20" s="14"/>
+      <c r="I20" s="18"/>
+      <c r="J20" s="19"/>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1"/>
+      <c r="M20" s="1"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="27" t="n">
+      <c r="A21" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="B21" s="28" t="s">
+      <c r="B21" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="C21" s="27" t="s">
+      <c r="C21" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="D21" s="29" t="s">
+      <c r="D21" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="E21" s="30" t="n">
+      <c r="E21" s="27" t="n">
         <f aca="false">SUM('NASCAR Jul 12'!F7:F13)</f>
         <v>1000</v>
       </c>
-      <c r="F21" s="30" t="n">
+      <c r="F21" s="27" t="n">
         <f aca="false">SUMIF('NASCAR Jul 12'!I7:I13,"Pending",'NASCAR Jul 12'!F7:F13)</f>
         <v>0</v>
       </c>
-      <c r="G21" s="30" t="n">
+      <c r="G21" s="27" t="n">
         <f aca="false">SUM('NASCAR Jul 12'!J7:J13)</f>
         <v>565.486725663717</v>
       </c>
-      <c r="H21" s="30" t="n">
+      <c r="H21" s="27" t="n">
         <f aca="false">SUM('NASCAR Jul 12'!K7:K13)</f>
         <v>-434.513274336283</v>
       </c>
-      <c r="I21" s="21"/>
-      <c r="J21" s="22"/>
-      <c r="K21" s="14"/>
-      <c r="L21" s="14"/>
-      <c r="M21" s="14"/>
+      <c r="I21" s="18"/>
+      <c r="J21" s="19"/>
+      <c r="K21" s="1"/>
+      <c r="L21" s="1"/>
+      <c r="M21" s="1"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="27" t="n">
+      <c r="A22" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="B22" s="28" t="s">
+      <c r="B22" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="C22" s="27" t="s">
+      <c r="C22" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="D22" s="29" t="s">
+      <c r="D22" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="E22" s="30" t="n">
+      <c r="E22" s="27" t="n">
         <f aca="false">SUM('WNBA Jul 12'!F7:F13)</f>
         <v>1000</v>
       </c>
-      <c r="F22" s="30" t="n">
+      <c r="F22" s="27" t="n">
         <f aca="false">SUMIF('WNBA Jul 12'!I7:I13,"Pending",'WNBA Jul 12'!F7:F13)</f>
         <v>0</v>
       </c>
-      <c r="G22" s="30" t="n">
+      <c r="G22" s="27" t="n">
         <f aca="false">SUM('WNBA Jul 12'!J7:J13)</f>
         <v>701.846509693851</v>
       </c>
-      <c r="H22" s="30" t="n">
+      <c r="H22" s="27" t="n">
         <f aca="false">SUM('WNBA Jul 12'!K7:K13)</f>
         <v>-298.153490306149</v>
       </c>
-      <c r="I22" s="21"/>
-      <c r="J22" s="22"/>
-      <c r="K22" s="14"/>
-      <c r="L22" s="14"/>
-      <c r="M22" s="14"/>
+      <c r="I22" s="18"/>
+      <c r="J22" s="19"/>
+      <c r="K22" s="1"/>
+      <c r="L22" s="1"/>
+      <c r="M22" s="1"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="27" t="n">
+      <c r="A23" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="B23" s="28" t="s">
+      <c r="B23" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="C23" s="27" t="s">
+      <c r="C23" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="D23" s="29" t="s">
+      <c r="D23" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="E23" s="30" t="n">
+      <c r="E23" s="27" t="n">
         <f aca="false">SUM('MLB Jul 12'!F7:F14)</f>
         <v>1000</v>
       </c>
-      <c r="F23" s="30" t="n">
+      <c r="F23" s="27" t="n">
         <f aca="false">SUMIF('MLB Jul 12'!I7:I14,"Pending",'MLB Jul 12'!F7:F14)</f>
         <v>0</v>
       </c>
-      <c r="G23" s="30" t="n">
+      <c r="G23" s="27" t="n">
         <f aca="false">SUM('MLB Jul 12'!J7:J14)</f>
         <v>802.232258064516</v>
       </c>
-      <c r="H23" s="30" t="n">
+      <c r="H23" s="27" t="n">
         <f aca="false">SUM('MLB Jul 12'!K7:K14)</f>
         <v>-197.767741935484</v>
       </c>
-      <c r="I23" s="31"/>
-      <c r="J23" s="31"/>
-      <c r="K23" s="14"/>
-      <c r="L23" s="14"/>
-      <c r="M23" s="14"/>
+      <c r="I23" s="28"/>
+      <c r="J23" s="28"/>
+      <c r="K23" s="1"/>
+      <c r="L23" s="1"/>
+      <c r="M23" s="1"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="27" t="n">
+      <c r="A24" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="B24" s="28" t="s">
+      <c r="B24" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="C24" s="27" t="s">
+      <c r="C24" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="D24" s="29" t="s">
+      <c r="D24" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="E24" s="30" t="n">
+      <c r="E24" s="27" t="n">
         <f aca="false">SUM('UFC 329'!F7:F15)</f>
         <v>1050</v>
       </c>
-      <c r="F24" s="30" t="n">
+      <c r="F24" s="27" t="n">
         <f aca="false">SUMIF('UFC 329'!I7:I15,"Pending",'UFC 329'!F7:F15)</f>
         <v>0</v>
       </c>
-      <c r="G24" s="30" t="n">
+      <c r="G24" s="27" t="n">
         <f aca="false">SUM('UFC 329'!J7:J15)</f>
         <v>1215.1103728313</v>
       </c>
-      <c r="H24" s="30" t="n">
+      <c r="H24" s="27" t="n">
         <f aca="false">SUM('UFC 329'!K7:K15)</f>
         <v>165.110372831303</v>
       </c>
-      <c r="I24" s="13"/>
-      <c r="J24" s="13"/>
-      <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
+      <c r="K24" s="1"/>
+      <c r="L24" s="1"/>
+      <c r="M24" s="1"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="12"/>
-      <c r="B25" s="32" t="s">
+      <c r="A25" s="4"/>
+      <c r="B25" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C25" s="13"/>
-      <c r="D25" s="13"/>
-      <c r="E25" s="33" t="n">
+      <c r="E25" s="8" t="n">
         <f aca="false">SUM(E16:E24)</f>
         <v>7650</v>
       </c>
-      <c r="F25" s="33" t="n">
+      <c r="F25" s="8" t="n">
         <f aca="false">SUM(F16:F24)</f>
         <v>2600</v>
       </c>
-      <c r="G25" s="33" t="n">
+      <c r="G25" s="8" t="n">
         <f aca="false">SUM(G16:G24)</f>
         <v>3809.67586625339</v>
       </c>
-      <c r="H25" s="33" t="n">
+      <c r="H25" s="8" t="n">
         <f aca="false">SUM(H16:H24)</f>
         <v>-1240.32413374661</v>
       </c>
-      <c r="I25" s="13"/>
-      <c r="J25" s="13"/>
-      <c r="K25" s="14"/>
-      <c r="L25" s="14"/>
-      <c r="M25" s="14"/>
+      <c r="K25" s="1"/>
+      <c r="L25" s="1"/>
+      <c r="M25" s="1"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="34"/>
-      <c r="B26" s="16"/>
-      <c r="C26" s="16"/>
-      <c r="D26" s="16"/>
-      <c r="E26" s="16"/>
-      <c r="F26" s="13"/>
-      <c r="G26" s="13"/>
-      <c r="H26" s="13"/>
-      <c r="I26" s="13"/>
-      <c r="J26" s="13"/>
-      <c r="K26" s="14"/>
-      <c r="L26" s="14"/>
-      <c r="M26" s="14"/>
+      <c r="A26" s="29"/>
+      <c r="B26" s="13"/>
+      <c r="C26" s="13"/>
+      <c r="D26" s="13"/>
+      <c r="E26" s="13"/>
+      <c r="K26" s="1"/>
+      <c r="L26" s="1"/>
+      <c r="M26" s="1"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="34" t="s">
+      <c r="A27" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="B27" s="16"/>
-      <c r="C27" s="16"/>
-      <c r="D27" s="35"/>
-      <c r="E27" s="16"/>
-      <c r="F27" s="13"/>
-      <c r="G27" s="13"/>
-      <c r="H27" s="13"/>
-      <c r="I27" s="13"/>
-      <c r="J27" s="13"/>
-      <c r="K27" s="14"/>
-      <c r="L27" s="14"/>
-      <c r="M27" s="14"/>
+      <c r="B27" s="13"/>
+      <c r="C27" s="13"/>
+      <c r="D27" s="30"/>
+      <c r="E27" s="13"/>
+      <c r="K27" s="1"/>
+      <c r="L27" s="1"/>
+      <c r="M27" s="1"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="15" t="s">
+      <c r="A28" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="B28" s="15" t="s">
+      <c r="B28" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="C28" s="15" t="s">
+      <c r="C28" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="D28" s="36" t="s">
+      <c r="D28" s="31" t="s">
         <v>44</v>
       </c>
-      <c r="E28" s="15" t="s">
+      <c r="E28" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="F28" s="13"/>
-      <c r="G28" s="13"/>
-      <c r="H28" s="13"/>
-      <c r="I28" s="13"/>
-      <c r="J28" s="13"/>
-      <c r="K28" s="14"/>
-      <c r="L28" s="14"/>
-      <c r="M28" s="14"/>
+      <c r="K28" s="1"/>
+      <c r="L28" s="1"/>
+      <c r="M28" s="1"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="37" t="s">
+      <c r="A29" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="B29" s="37" t="s">
+      <c r="B29" s="32" t="s">
         <v>46</v>
       </c>
-      <c r="C29" s="38" t="s">
+      <c r="C29" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="D29" s="39" t="n">
+      <c r="D29" s="34" t="n">
         <v>0</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="F29" s="13"/>
-      <c r="G29" s="13"/>
-      <c r="H29" s="13"/>
-      <c r="I29" s="13"/>
-      <c r="J29" s="13"/>
-      <c r="K29" s="14"/>
-      <c r="L29" s="14"/>
-      <c r="M29" s="14"/>
+      <c r="K29" s="1"/>
+      <c r="L29" s="1"/>
+      <c r="M29" s="1"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="37" t="s">
+      <c r="A30" s="32" t="s">
         <v>49</v>
       </c>
-      <c r="B30" s="37" t="s">
+      <c r="B30" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="C30" s="38" t="s">
+      <c r="C30" s="33" t="s">
         <v>51</v>
       </c>
-      <c r="D30" s="39" t="n">
+      <c r="D30" s="34" t="n">
         <v>50</v>
       </c>
       <c r="E30" s="10" t="str">
         <f aca="false">IF('MLB Jul 12'!I14="Win","HIT",IF('MLB Jul 12'!I14="Loss","MISS","Pending"))</f>
         <v>MISS</v>
       </c>
-      <c r="F30" s="13"/>
-      <c r="G30" s="13"/>
-      <c r="H30" s="13"/>
-      <c r="I30" s="13"/>
-      <c r="J30" s="13"/>
-      <c r="K30" s="14"/>
-      <c r="L30" s="14"/>
-      <c r="M30" s="14"/>
+      <c r="K30" s="1"/>
+      <c r="L30" s="1"/>
+      <c r="M30" s="1"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="37" t="s">
+      <c r="A31" s="32" t="s">
         <v>52</v>
       </c>
-      <c r="B31" s="37" t="s">
+      <c r="B31" s="32" t="s">
         <v>53</v>
       </c>
-      <c r="C31" s="38" t="s">
+      <c r="C31" s="33" t="s">
         <v>54</v>
       </c>
-      <c r="D31" s="39" t="n">
+      <c r="D31" s="34" t="n">
         <v>40</v>
       </c>
       <c r="E31" s="10" t="str">
         <f aca="false">IF('NASCAR Jul 12'!I13="Win","HIT",IF('NASCAR Jul 12'!I13="Loss","MISS","Pending"))</f>
         <v>MISS</v>
       </c>
-      <c r="F31" s="13"/>
-      <c r="G31" s="13"/>
-      <c r="H31" s="13"/>
-      <c r="I31" s="13"/>
-      <c r="J31" s="13"/>
-      <c r="K31" s="14"/>
-      <c r="L31" s="14"/>
-      <c r="M31" s="14"/>
+      <c r="K31" s="1"/>
+      <c r="L31" s="1"/>
+      <c r="M31" s="1"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="37" t="s">
+      <c r="A32" s="32" t="s">
         <v>55</v>
       </c>
-      <c r="B32" s="37" t="s">
+      <c r="B32" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="C32" s="38" t="s">
+      <c r="C32" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="D32" s="39" t="n">
+      <c r="D32" s="34" t="n">
         <v>100</v>
       </c>
       <c r="E32" s="10" t="str">
         <f aca="false">IF('WNBA Jul 12'!I13="Win","HIT",IF('WNBA Jul 12'!I13="Loss","MISS","Pending"))</f>
         <v>MISS</v>
       </c>
-      <c r="F32" s="13"/>
-      <c r="G32" s="13"/>
-      <c r="H32" s="13"/>
-      <c r="I32" s="13"/>
-      <c r="J32" s="13"/>
-      <c r="K32" s="14"/>
-      <c r="L32" s="14"/>
-      <c r="M32" s="14"/>
+      <c r="K32" s="1"/>
+      <c r="L32" s="1"/>
+      <c r="M32" s="1"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="37" t="s">
+      <c r="A33" s="32" t="s">
         <v>58</v>
       </c>
-      <c r="B33" s="37" t="s">
+      <c r="B33" s="32" t="s">
         <v>59</v>
       </c>
-      <c r="C33" s="38" t="s">
+      <c r="C33" s="33" t="s">
         <v>60</v>
       </c>
-      <c r="D33" s="39" t="n">
+      <c r="D33" s="34" t="n">
         <v>50</v>
       </c>
       <c r="E33" s="10" t="str">
         <f aca="false">IF('The Open'!I12="Win","HIT",IF('The Open'!I12="Loss","MISS","Pending"))</f>
         <v>Pending</v>
       </c>
-      <c r="F33" s="13"/>
-      <c r="G33" s="13"/>
-      <c r="H33" s="13"/>
-      <c r="I33" s="13"/>
-      <c r="J33" s="13"/>
-      <c r="K33" s="14"/>
-      <c r="L33" s="14"/>
-      <c r="M33" s="14"/>
+      <c r="K33" s="1"/>
+      <c r="L33" s="1"/>
+      <c r="M33" s="1"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="37" t="s">
+      <c r="A34" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="B34" s="37" t="s">
+      <c r="B34" s="32" t="s">
         <v>62</v>
       </c>
-      <c r="C34" s="38" t="s">
+      <c r="C34" s="33" t="s">
         <v>63</v>
       </c>
-      <c r="D34" s="39" t="n">
+      <c r="D34" s="34" t="n">
         <v>0</v>
       </c>
       <c r="E34" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="F34" s="13"/>
-      <c r="G34" s="13"/>
-      <c r="H34" s="13"/>
-      <c r="I34" s="13"/>
-      <c r="J34" s="13"/>
-      <c r="K34" s="14"/>
-      <c r="L34" s="14"/>
-      <c r="M34" s="14"/>
+      <c r="K34" s="1"/>
+      <c r="L34" s="1"/>
+      <c r="M34" s="1"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="37" t="s">
+      <c r="A35" s="32" t="s">
         <v>65</v>
       </c>
-      <c r="B35" s="37" t="s">
+      <c r="B35" s="32" t="s">
         <v>66</v>
       </c>
-      <c r="C35" s="38" t="s">
+      <c r="C35" s="33" t="s">
         <v>67</v>
       </c>
-      <c r="D35" s="39" t="n">
+      <c r="D35" s="34" t="n">
         <v>75</v>
       </c>
       <c r="E35" s="10" t="str">
         <f aca="false">IF('HR Derby'!I13="Win","HIT",IF('HR Derby'!I13="Loss","MISS","Pending"))</f>
         <v>MISS</v>
       </c>
-      <c r="F35" s="13"/>
-      <c r="G35" s="13"/>
-      <c r="H35" s="13"/>
-      <c r="I35" s="13"/>
-      <c r="J35" s="13"/>
-      <c r="K35" s="14"/>
-      <c r="L35" s="14"/>
-      <c r="M35" s="14"/>
+      <c r="K35" s="1"/>
+      <c r="L35" s="1"/>
+      <c r="M35" s="1"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="37" t="s">
+      <c r="A36" s="32" t="s">
         <v>68</v>
       </c>
-      <c r="B36" s="37" t="s">
+      <c r="B36" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="C36" s="38" t="s">
+      <c r="C36" s="33" t="s">
         <v>69</v>
       </c>
-      <c r="D36" s="39" t="n">
+      <c r="D36" s="34" t="n">
         <v>75</v>
       </c>
       <c r="E36" s="10" t="str">
         <f aca="false">IF('WNBA Jul 15'!I13="Win","HIT",IF('WNBA Jul 15'!I13="Loss","MISS","Pending"))</f>
         <v>Pending</v>
       </c>
-      <c r="F36" s="13"/>
-      <c r="G36" s="13"/>
-      <c r="H36" s="13"/>
-      <c r="I36" s="13"/>
-      <c r="J36" s="13"/>
-      <c r="K36" s="14"/>
-      <c r="L36" s="14"/>
-      <c r="M36" s="14"/>
+      <c r="K36" s="1"/>
+      <c r="L36" s="1"/>
+      <c r="M36" s="1"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="12" t="s">
+      <c r="A37" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="B37" s="13"/>
-      <c r="C37" s="13"/>
-      <c r="D37" s="13"/>
       <c r="E37" s="10" t="str">
         <f aca="false">IF(COUNTIF(E29:E36,"HIT")+COUNTIF(E29:E36,"MISS")=0,"—",COUNTIF(E29:E36,"HIT")&amp;"-for-"&amp;(COUNTIF(E29:E36,"HIT")+COUNTIF(E29:E36,"MISS"))&amp;" ("&amp;TEXT(COUNTIF(E29:E36,"HIT")/(COUNTIF(E29:E36,"HIT")+COUNTIF(E29:E36,"MISS")),"0%")&amp;")")</f>
         <v>0-for-5 (0%)</v>
       </c>
-      <c r="F37" s="13"/>
-      <c r="G37" s="13"/>
-      <c r="H37" s="13"/>
-      <c r="I37" s="13"/>
-      <c r="J37" s="13"/>
-      <c r="K37" s="14"/>
-      <c r="L37" s="14"/>
-      <c r="M37" s="14"/>
+      <c r="K37" s="1"/>
+      <c r="L37" s="1"/>
+      <c r="M37" s="1"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="40" t="s">
+      <c r="A38" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="B38" s="13"/>
-      <c r="C38" s="13"/>
-      <c r="D38" s="13"/>
-      <c r="E38" s="13"/>
-      <c r="F38" s="13"/>
-      <c r="G38" s="13"/>
-      <c r="H38" s="13"/>
-      <c r="I38" s="13"/>
-      <c r="J38" s="13"/>
-      <c r="K38" s="14"/>
-      <c r="L38" s="14"/>
-      <c r="M38" s="14"/>
+      <c r="K38" s="1"/>
+      <c r="L38" s="1"/>
+      <c r="M38" s="1"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="13"/>
-      <c r="B39" s="13"/>
-      <c r="C39" s="13"/>
-      <c r="D39" s="13"/>
-      <c r="E39" s="13"/>
-      <c r="F39" s="13"/>
-      <c r="G39" s="13"/>
-      <c r="H39" s="13"/>
-      <c r="I39" s="13"/>
-      <c r="J39" s="13"/>
-      <c r="K39" s="14"/>
-      <c r="L39" s="14"/>
-      <c r="M39" s="14"/>
+      <c r="K39" s="1"/>
+      <c r="L39" s="1"/>
+      <c r="M39" s="1"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="13"/>
-      <c r="B40" s="13"/>
-      <c r="C40" s="13"/>
-      <c r="D40" s="13"/>
-      <c r="E40" s="13"/>
-      <c r="F40" s="13"/>
-      <c r="G40" s="13"/>
-      <c r="H40" s="13"/>
-      <c r="I40" s="13"/>
-      <c r="J40" s="13"/>
-      <c r="K40" s="14"/>
-      <c r="L40" s="14"/>
-      <c r="M40" s="14"/>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="13"/>
-      <c r="B41" s="13"/>
-      <c r="C41" s="13"/>
-      <c r="D41" s="13"/>
-      <c r="E41" s="13"/>
-      <c r="F41" s="13"/>
-      <c r="G41" s="13"/>
-      <c r="H41" s="13"/>
-      <c r="I41" s="13"/>
-      <c r="J41" s="13"/>
-      <c r="K41" s="13"/>
-      <c r="L41" s="13"/>
-      <c r="M41" s="13"/>
+      <c r="K40" s="1"/>
+      <c r="L40" s="1"/>
+      <c r="M40" s="1"/>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="K41" s="1"/>
+      <c r="L41" s="1"/>
+      <c r="M41" s="1"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="H16:H23">
@@ -3290,10 +3086,10 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H16:H25">
-    <cfRule type="expression" priority="12" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+    <cfRule type="expression" priority="12" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>AND(ISNUMBER(H16),H16&gt;0)</formula>
     </cfRule>
-    <cfRule type="expression" priority="13" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+    <cfRule type="expression" priority="13" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>AND(ISNUMBER(H16),H16&lt;0)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3316,430 +3112,430 @@
   <dimension ref="A1:M14"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="46"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="85" t="s">
+    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="35" t="s">
         <v>442</v>
       </c>
-      <c r="H1" s="86" t="s">
+      <c r="H1" s="77" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="87" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="87" t="s">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="88" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="4" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="15" t="s">
+    <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="C6" s="12" t="s">
         <v>200</v>
       </c>
-      <c r="D6" s="15" t="s">
+      <c r="D6" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="E6" s="15" t="s">
+      <c r="E6" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="F6" s="15" t="s">
+      <c r="F6" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="G6" s="15" t="s">
+      <c r="G6" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="H6" s="15" t="s">
+      <c r="H6" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="I6" s="15" t="s">
+      <c r="I6" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="J6" s="15" t="s">
+      <c r="J6" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="K6" s="15" t="s">
+      <c r="K6" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="L6" s="15" t="s">
+      <c r="L6" s="12" t="s">
         <v>220</v>
       </c>
-      <c r="M6" s="15" t="s">
+      <c r="M6" s="12" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="38" t="n">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="33" t="n">
         <v>1</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>446</v>
       </c>
-      <c r="C7" s="37" t="s">
+      <c r="C7" s="32" t="s">
         <v>447</v>
       </c>
-      <c r="D7" s="38" t="s">
+      <c r="D7" s="33" t="s">
         <v>378</v>
       </c>
-      <c r="E7" s="45" t="n">
+      <c r="E7" s="39" t="n">
         <v>-105</v>
       </c>
-      <c r="F7" s="89" t="n">
+      <c r="F7" s="40" t="n">
         <v>185</v>
       </c>
-      <c r="G7" s="90" t="n">
+      <c r="G7" s="41" t="n">
         <f aca="false">IF(E7&gt;0,F7*E7/100,F7*100/ABS(E7))</f>
         <v>176.190476190476</v>
       </c>
-      <c r="H7" s="90" t="n">
+      <c r="H7" s="41" t="n">
         <f aca="false">F7+G7</f>
         <v>361.190476190476</v>
       </c>
-      <c r="I7" s="64" t="s">
+      <c r="I7" s="57" t="s">
         <v>123</v>
       </c>
-      <c r="J7" s="90" t="n">
+      <c r="J7" s="41" t="n">
         <f aca="false">IF(I7="Win",F7+G7,IF(I7="Push",F7,IF(I7="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K7" s="91" t="n">
+      <c r="K7" s="43" t="n">
         <f aca="false">IF(I7="Pending",0,J7-F7)</f>
         <v>0</v>
       </c>
-      <c r="L7" s="81" t="n">
+      <c r="L7" s="73" t="n">
         <v>0.57</v>
       </c>
-      <c r="M7" s="69" t="s">
+      <c r="M7" s="62" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="38" t="n">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="33" t="n">
         <v>2</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>449</v>
       </c>
-      <c r="C8" s="37" t="s">
+      <c r="C8" s="32" t="s">
         <v>450</v>
       </c>
-      <c r="D8" s="38" t="s">
+      <c r="D8" s="33" t="s">
         <v>179</v>
       </c>
-      <c r="E8" s="45" t="n">
+      <c r="E8" s="39" t="n">
         <v>-115</v>
       </c>
-      <c r="F8" s="89" t="n">
+      <c r="F8" s="40" t="n">
         <v>175</v>
       </c>
-      <c r="G8" s="90" t="n">
+      <c r="G8" s="41" t="n">
         <f aca="false">IF(E8&gt;0,F8*E8/100,F8*100/ABS(E8))</f>
         <v>152.173913043478</v>
       </c>
-      <c r="H8" s="90" t="n">
+      <c r="H8" s="41" t="n">
         <f aca="false">F8+G8</f>
         <v>327.173913043478</v>
       </c>
-      <c r="I8" s="64" t="s">
+      <c r="I8" s="57" t="s">
         <v>123</v>
       </c>
-      <c r="J8" s="90" t="n">
+      <c r="J8" s="41" t="n">
         <f aca="false">IF(I8="Win",F8+G8,IF(I8="Push",F8,IF(I8="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K8" s="91" t="n">
+      <c r="K8" s="43" t="n">
         <f aca="false">IF(I8="Pending",0,J8-F8)</f>
         <v>0</v>
       </c>
-      <c r="L8" s="81" t="n">
+      <c r="L8" s="73" t="n">
         <v>0.54</v>
       </c>
-      <c r="M8" s="69" t="s">
+      <c r="M8" s="62" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="38" t="n">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="33" t="n">
         <v>3</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>452</v>
       </c>
-      <c r="C9" s="37" t="s">
+      <c r="C9" s="32" t="s">
         <v>453</v>
       </c>
-      <c r="D9" s="38" t="s">
+      <c r="D9" s="33" t="s">
         <v>179</v>
       </c>
-      <c r="E9" s="45" t="n">
+      <c r="E9" s="39" t="n">
         <v>-110</v>
       </c>
-      <c r="F9" s="89" t="n">
+      <c r="F9" s="40" t="n">
         <v>160</v>
       </c>
-      <c r="G9" s="90" t="n">
+      <c r="G9" s="41" t="n">
         <f aca="false">IF(E9&gt;0,F9*E9/100,F9*100/ABS(E9))</f>
         <v>145.454545454545</v>
       </c>
-      <c r="H9" s="90" t="n">
+      <c r="H9" s="41" t="n">
         <f aca="false">F9+G9</f>
         <v>305.454545454546</v>
       </c>
-      <c r="I9" s="64" t="s">
+      <c r="I9" s="57" t="s">
         <v>123</v>
       </c>
-      <c r="J9" s="90" t="n">
+      <c r="J9" s="41" t="n">
         <f aca="false">IF(I9="Win",F9+G9,IF(I9="Push",F9,IF(I9="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K9" s="91" t="n">
+      <c r="K9" s="43" t="n">
         <f aca="false">IF(I9="Pending",0,J9-F9)</f>
         <v>0</v>
       </c>
-      <c r="L9" s="81" t="n">
+      <c r="L9" s="73" t="n">
         <v>0.55</v>
       </c>
-      <c r="M9" s="69" t="s">
+      <c r="M9" s="62" t="s">
         <v>454</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="38" t="n">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="33" t="n">
         <v>4</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>455</v>
       </c>
-      <c r="C10" s="37" t="s">
+      <c r="C10" s="32" t="s">
         <v>393</v>
       </c>
-      <c r="D10" s="38" t="s">
+      <c r="D10" s="33" t="s">
         <v>94</v>
       </c>
-      <c r="E10" s="45" t="n">
+      <c r="E10" s="39" t="n">
         <v>-110</v>
       </c>
-      <c r="F10" s="89" t="n">
+      <c r="F10" s="40" t="n">
         <v>150</v>
       </c>
-      <c r="G10" s="90" t="n">
+      <c r="G10" s="41" t="n">
         <f aca="false">IF(E10&gt;0,F10*E10/100,F10*100/ABS(E10))</f>
         <v>136.363636363636</v>
       </c>
-      <c r="H10" s="90" t="n">
+      <c r="H10" s="41" t="n">
         <f aca="false">F10+G10</f>
         <v>286.363636363636</v>
       </c>
-      <c r="I10" s="64" t="s">
+      <c r="I10" s="57" t="s">
         <v>123</v>
       </c>
-      <c r="J10" s="90" t="n">
+      <c r="J10" s="41" t="n">
         <f aca="false">IF(I10="Win",F10+G10,IF(I10="Push",F10,IF(I10="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K10" s="91" t="n">
+      <c r="K10" s="43" t="n">
         <f aca="false">IF(I10="Pending",0,J10-F10)</f>
         <v>0</v>
       </c>
-      <c r="L10" s="81" t="n">
+      <c r="L10" s="73" t="n">
         <v>0.54</v>
       </c>
-      <c r="M10" s="69" t="s">
+      <c r="M10" s="62" t="s">
         <v>456</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="38" t="n">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="33" t="n">
         <v>5</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>457</v>
       </c>
-      <c r="C11" s="37" t="s">
+      <c r="C11" s="32" t="s">
         <v>458</v>
       </c>
-      <c r="D11" s="38" t="s">
+      <c r="D11" s="33" t="s">
         <v>89</v>
       </c>
-      <c r="E11" s="45" t="n">
+      <c r="E11" s="39" t="n">
         <v>-130</v>
       </c>
-      <c r="F11" s="89" t="n">
+      <c r="F11" s="40" t="n">
         <v>140</v>
       </c>
-      <c r="G11" s="90" t="n">
+      <c r="G11" s="41" t="n">
         <f aca="false">IF(E11&gt;0,F11*E11/100,F11*100/ABS(E11))</f>
         <v>107.692307692308</v>
       </c>
-      <c r="H11" s="90" t="n">
+      <c r="H11" s="41" t="n">
         <f aca="false">F11+G11</f>
         <v>247.692307692308</v>
       </c>
-      <c r="I11" s="64" t="s">
+      <c r="I11" s="57" t="s">
         <v>123</v>
       </c>
-      <c r="J11" s="90" t="n">
+      <c r="J11" s="41" t="n">
         <f aca="false">IF(I11="Win",F11+G11,IF(I11="Push",F11,IF(I11="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K11" s="91" t="n">
+      <c r="K11" s="43" t="n">
         <f aca="false">IF(I11="Pending",0,J11-F11)</f>
         <v>0</v>
       </c>
-      <c r="L11" s="81" t="n">
+      <c r="L11" s="73" t="n">
         <v>0.58</v>
       </c>
-      <c r="M11" s="69" t="s">
+      <c r="M11" s="62" t="s">
         <v>459</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="38" t="n">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="33" t="n">
         <v>6</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>460</v>
       </c>
-      <c r="C12" s="37" t="s">
+      <c r="C12" s="32" t="s">
         <v>461</v>
       </c>
-      <c r="D12" s="38" t="s">
+      <c r="D12" s="33" t="s">
         <v>378</v>
       </c>
-      <c r="E12" s="45" t="n">
+      <c r="E12" s="39" t="n">
         <v>-110</v>
       </c>
-      <c r="F12" s="89" t="n">
+      <c r="F12" s="40" t="n">
         <v>115</v>
       </c>
-      <c r="G12" s="90" t="n">
+      <c r="G12" s="41" t="n">
         <f aca="false">IF(E12&gt;0,F12*E12/100,F12*100/ABS(E12))</f>
         <v>104.545454545455</v>
       </c>
-      <c r="H12" s="90" t="n">
+      <c r="H12" s="41" t="n">
         <f aca="false">F12+G12</f>
         <v>219.545454545455</v>
       </c>
-      <c r="I12" s="64" t="s">
+      <c r="I12" s="57" t="s">
         <v>123</v>
       </c>
-      <c r="J12" s="90" t="n">
+      <c r="J12" s="41" t="n">
         <f aca="false">IF(I12="Win",F12+G12,IF(I12="Push",F12,IF(I12="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K12" s="91" t="n">
+      <c r="K12" s="43" t="n">
         <f aca="false">IF(I12="Pending",0,J12-F12)</f>
         <v>0</v>
       </c>
-      <c r="L12" s="81" t="n">
+      <c r="L12" s="73" t="n">
         <v>0.52</v>
       </c>
-      <c r="M12" s="69" t="s">
+      <c r="M12" s="62" t="s">
         <v>462</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="38" t="n">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="33" t="n">
         <v>7</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>395</v>
       </c>
-      <c r="C13" s="37" t="s">
+      <c r="C13" s="32" t="s">
         <v>463</v>
       </c>
-      <c r="D13" s="38" t="s">
+      <c r="D13" s="33" t="s">
         <v>117</v>
       </c>
-      <c r="E13" s="45" t="n">
+      <c r="E13" s="39" t="n">
         <v>1133</v>
       </c>
-      <c r="F13" s="89" t="n">
+      <c r="F13" s="40" t="n">
         <v>75</v>
       </c>
-      <c r="G13" s="90" t="n">
+      <c r="G13" s="41" t="n">
         <f aca="false">IF(E13&gt;0,F13*E13/100,F13*100/ABS(E13))</f>
         <v>849.75</v>
       </c>
-      <c r="H13" s="90" t="n">
+      <c r="H13" s="41" t="n">
         <f aca="false">F13+G13</f>
         <v>924.75</v>
       </c>
-      <c r="I13" s="64" t="s">
+      <c r="I13" s="57" t="s">
         <v>123</v>
       </c>
-      <c r="J13" s="90" t="n">
+      <c r="J13" s="41" t="n">
         <f aca="false">IF(I13="Win",F13+G13,IF(I13="Push",F13,IF(I13="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K13" s="91" t="n">
+      <c r="K13" s="43" t="n">
         <f aca="false">IF(I13="Pending",0,J13-F13)</f>
         <v>0</v>
       </c>
-      <c r="L13" s="81" t="n">
+      <c r="L13" s="73" t="n">
         <v>0.1</v>
       </c>
-      <c r="M13" s="69" t="s">
+      <c r="M13" s="62" t="s">
         <v>464</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="88" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B14" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="F14" s="33" t="n">
+      <c r="F14" s="8" t="n">
         <f aca="false">SUM(F7:F13)</f>
         <v>1000</v>
       </c>
-      <c r="G14" s="33" t="n">
+      <c r="G14" s="8" t="n">
         <f aca="false">SUM(G7:G13)</f>
         <v>1672.1703332899</v>
       </c>
-      <c r="H14" s="33" t="n">
+      <c r="H14" s="8" t="n">
         <f aca="false">SUM(H7:H13)</f>
         <v>2672.1703332899</v>
       </c>
-      <c r="J14" s="33" t="n">
+      <c r="J14" s="8" t="n">
         <f aca="false">SUM(J7:J13)</f>
         <v>0</v>
       </c>
-      <c r="K14" s="33" t="n">
+      <c r="K14" s="8" t="n">
         <f aca="false">SUM(K7:K13)</f>
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="K7:K14">
-    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>AND(ISNUMBER(K7),K7&gt;0)</formula>
     </cfRule>
-    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>AND(ISNUMBER(K7),K7&lt;0)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3781,10 +3577,10 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="35" t="s">
         <v>72</v>
       </c>
-      <c r="H1" s="42" t="s">
+      <c r="H1" s="36" t="s">
         <v>73</v>
       </c>
     </row>
@@ -3804,451 +3600,451 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="C6" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="D6" s="15" t="s">
+      <c r="D6" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="E6" s="15" t="s">
+      <c r="E6" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="F6" s="15" t="s">
+      <c r="F6" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="G6" s="15" t="s">
+      <c r="G6" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="H6" s="15" t="s">
+      <c r="H6" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="I6" s="15" t="s">
+      <c r="I6" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="J6" s="15" t="s">
+      <c r="J6" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="K6" s="15" t="s">
+      <c r="K6" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="L6" s="15" t="s">
+      <c r="L6" s="12" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="38" t="n">
+      <c r="A7" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="43" t="s">
+      <c r="B7" s="37" t="s">
         <v>87</v>
       </c>
-      <c r="C7" s="44" t="s">
+      <c r="C7" s="38" t="s">
         <v>88</v>
       </c>
-      <c r="D7" s="38" t="s">
+      <c r="D7" s="33" t="s">
         <v>89</v>
       </c>
-      <c r="E7" s="45" t="n">
+      <c r="E7" s="39" t="n">
         <v>-265</v>
       </c>
-      <c r="F7" s="46" t="n">
+      <c r="F7" s="40" t="n">
         <v>265</v>
       </c>
-      <c r="G7" s="47" t="n">
+      <c r="G7" s="41" t="n">
         <f aca="false">IF(E7&gt;0,F7*E7/100,F7*100/ABS(E7))</f>
         <v>100</v>
       </c>
-      <c r="H7" s="47" t="n">
+      <c r="H7" s="41" t="n">
         <f aca="false">F7+G7</f>
         <v>365</v>
       </c>
-      <c r="I7" s="48" t="s">
+      <c r="I7" s="42" t="s">
         <v>90</v>
       </c>
-      <c r="J7" s="47" t="n">
+      <c r="J7" s="41" t="n">
         <f aca="false">IF(I7="Win",F7+G7,IF(I7="Push",F7,IF(I7="Loss",0,0)))</f>
         <v>365</v>
       </c>
-      <c r="K7" s="49" t="n">
+      <c r="K7" s="43" t="n">
         <f aca="false">IF(I7="Pending",0,J7-F7)</f>
         <v>100</v>
       </c>
-      <c r="L7" s="50" t="s">
+      <c r="L7" s="44" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="38" t="n">
+      <c r="A8" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="43" t="s">
+      <c r="B8" s="37" t="s">
         <v>92</v>
       </c>
-      <c r="C8" s="44" t="s">
+      <c r="C8" s="38" t="s">
         <v>93</v>
       </c>
-      <c r="D8" s="38" t="s">
+      <c r="D8" s="33" t="s">
         <v>94</v>
       </c>
-      <c r="E8" s="45" t="n">
+      <c r="E8" s="39" t="n">
         <v>-140</v>
       </c>
-      <c r="F8" s="46" t="n">
+      <c r="F8" s="40" t="n">
         <v>200</v>
       </c>
-      <c r="G8" s="47" t="n">
+      <c r="G8" s="41" t="n">
         <f aca="false">IF(E8&gt;0,F8*E8/100,F8*100/ABS(E8))</f>
         <v>142.857142857143</v>
       </c>
-      <c r="H8" s="47" t="n">
+      <c r="H8" s="41" t="n">
         <f aca="false">F8+G8</f>
         <v>342.857142857143</v>
       </c>
-      <c r="I8" s="48" t="s">
+      <c r="I8" s="42" t="s">
         <v>90</v>
       </c>
-      <c r="J8" s="47" t="n">
+      <c r="J8" s="41" t="n">
         <f aca="false">IF(I8="Win",F8+G8,IF(I8="Push",F8,IF(I8="Loss",0,0)))</f>
         <v>342.857142857143</v>
       </c>
-      <c r="K8" s="49" t="n">
+      <c r="K8" s="43" t="n">
         <f aca="false">IF(I8="Pending",0,J8-F8)</f>
         <v>142.857142857143</v>
       </c>
-      <c r="L8" s="50" t="s">
+      <c r="L8" s="44" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="38" t="n">
+      <c r="A9" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="B9" s="43" t="s">
+      <c r="B9" s="37" t="s">
         <v>96</v>
       </c>
-      <c r="C9" s="44" t="s">
+      <c r="C9" s="38" t="s">
         <v>97</v>
       </c>
-      <c r="D9" s="38" t="s">
+      <c r="D9" s="33" t="s">
         <v>89</v>
       </c>
-      <c r="E9" s="45" t="n">
+      <c r="E9" s="39" t="n">
         <v>-148</v>
       </c>
-      <c r="F9" s="46" t="n">
+      <c r="F9" s="40" t="n">
         <v>148</v>
       </c>
-      <c r="G9" s="47" t="n">
+      <c r="G9" s="41" t="n">
         <f aca="false">IF(E9&gt;0,F9*E9/100,F9*100/ABS(E9))</f>
         <v>100</v>
       </c>
-      <c r="H9" s="47" t="n">
+      <c r="H9" s="41" t="n">
         <f aca="false">F9+G9</f>
         <v>248</v>
       </c>
-      <c r="I9" s="51" t="s">
+      <c r="I9" s="45" t="s">
         <v>98</v>
       </c>
-      <c r="J9" s="47" t="n">
+      <c r="J9" s="41" t="n">
         <f aca="false">IF(I9="Win",F9+G9,IF(I9="Push",F9,IF(I9="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K9" s="49" t="n">
+      <c r="K9" s="43" t="n">
         <f aca="false">IF(I9="Pending",0,J9-F9)</f>
         <v>-148</v>
       </c>
-      <c r="L9" s="50" t="s">
+      <c r="L9" s="44" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="38" t="n">
+      <c r="A10" s="33" t="n">
         <v>4</v>
       </c>
-      <c r="B10" s="43" t="s">
+      <c r="B10" s="37" t="s">
         <v>100</v>
       </c>
-      <c r="C10" s="44" t="s">
+      <c r="C10" s="38" t="s">
         <v>101</v>
       </c>
-      <c r="D10" s="38" t="s">
+      <c r="D10" s="33" t="s">
         <v>89</v>
       </c>
-      <c r="E10" s="45" t="n">
+      <c r="E10" s="39" t="n">
         <v>114</v>
       </c>
-      <c r="F10" s="46" t="n">
+      <c r="F10" s="40" t="n">
         <v>100</v>
       </c>
-      <c r="G10" s="47" t="n">
+      <c r="G10" s="41" t="n">
         <f aca="false">IF(E10&gt;0,F10*E10/100,F10*100/ABS(E10))</f>
         <v>114</v>
       </c>
-      <c r="H10" s="47" t="n">
+      <c r="H10" s="41" t="n">
         <f aca="false">F10+G10</f>
         <v>214</v>
       </c>
-      <c r="I10" s="48" t="s">
+      <c r="I10" s="42" t="s">
         <v>90</v>
       </c>
-      <c r="J10" s="47" t="n">
+      <c r="J10" s="41" t="n">
         <f aca="false">IF(I10="Win",F10+G10,IF(I10="Push",F10,IF(I10="Loss",0,0)))</f>
         <v>214</v>
       </c>
-      <c r="K10" s="49" t="n">
+      <c r="K10" s="43" t="n">
         <f aca="false">IF(I10="Pending",0,J10-F10)</f>
         <v>114</v>
       </c>
-      <c r="L10" s="50" t="s">
+      <c r="L10" s="44" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="38" t="n">
+      <c r="A11" s="33" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="43" t="s">
+      <c r="B11" s="37" t="s">
         <v>103</v>
       </c>
-      <c r="C11" s="44" t="s">
+      <c r="C11" s="38" t="s">
         <v>104</v>
       </c>
-      <c r="D11" s="38" t="s">
+      <c r="D11" s="33" t="s">
         <v>89</v>
       </c>
-      <c r="E11" s="45" t="n">
+      <c r="E11" s="39" t="n">
         <v>-218</v>
       </c>
-      <c r="F11" s="46" t="n">
+      <c r="F11" s="40" t="n">
         <v>100</v>
       </c>
-      <c r="G11" s="47" t="n">
+      <c r="G11" s="41" t="n">
         <f aca="false">IF(E11&gt;0,F11*E11/100,F11*100/ABS(E11))</f>
         <v>45.8715596330275</v>
       </c>
-      <c r="H11" s="47" t="n">
+      <c r="H11" s="41" t="n">
         <f aca="false">F11+G11</f>
         <v>145.871559633028</v>
       </c>
-      <c r="I11" s="51" t="s">
+      <c r="I11" s="45" t="s">
         <v>98</v>
       </c>
-      <c r="J11" s="47" t="n">
+      <c r="J11" s="41" t="n">
         <f aca="false">IF(I11="Win",F11+G11,IF(I11="Push",F11,IF(I11="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K11" s="49" t="n">
+      <c r="K11" s="43" t="n">
         <f aca="false">IF(I11="Pending",0,J11-F11)</f>
         <v>-100</v>
       </c>
-      <c r="L11" s="50" t="s">
+      <c r="L11" s="44" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="38" t="n">
+      <c r="A12" s="33" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="43" t="s">
+      <c r="B12" s="37" t="s">
         <v>106</v>
       </c>
-      <c r="C12" s="44" t="s">
+      <c r="C12" s="38" t="s">
         <v>107</v>
       </c>
-      <c r="D12" s="38" t="s">
+      <c r="D12" s="33" t="s">
         <v>89</v>
       </c>
-      <c r="E12" s="45" t="n">
+      <c r="E12" s="39" t="n">
         <v>-125</v>
       </c>
-      <c r="F12" s="46" t="n">
+      <c r="F12" s="40" t="n">
         <v>75</v>
       </c>
-      <c r="G12" s="47" t="n">
+      <c r="G12" s="41" t="n">
         <f aca="false">IF(E12&gt;0,F12*E12/100,F12*100/ABS(E12))</f>
         <v>60</v>
       </c>
-      <c r="H12" s="47" t="n">
+      <c r="H12" s="41" t="n">
         <f aca="false">F12+G12</f>
         <v>135</v>
       </c>
-      <c r="I12" s="48" t="s">
+      <c r="I12" s="42" t="s">
         <v>90</v>
       </c>
-      <c r="J12" s="47" t="n">
+      <c r="J12" s="41" t="n">
         <f aca="false">IF(I12="Win",F12+G12,IF(I12="Push",F12,IF(I12="Loss",0,0)))</f>
         <v>135</v>
       </c>
-      <c r="K12" s="49" t="n">
+      <c r="K12" s="43" t="n">
         <f aca="false">IF(I12="Pending",0,J12-F12)</f>
         <v>60</v>
       </c>
-      <c r="L12" s="50" t="s">
+      <c r="L12" s="44" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="38" t="n">
+      <c r="A13" s="33" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="43" t="s">
+      <c r="B13" s="37" t="s">
         <v>109</v>
       </c>
-      <c r="C13" s="44" t="s">
+      <c r="C13" s="38" t="s">
         <v>110</v>
       </c>
-      <c r="D13" s="38" t="s">
+      <c r="D13" s="33" t="s">
         <v>89</v>
       </c>
-      <c r="E13" s="45" t="n">
+      <c r="E13" s="39" t="n">
         <v>-225</v>
       </c>
-      <c r="F13" s="46" t="n">
+      <c r="F13" s="40" t="n">
         <v>50</v>
       </c>
-      <c r="G13" s="47" t="n">
+      <c r="G13" s="41" t="n">
         <f aca="false">IF(E13&gt;0,F13*E13/100,F13*100/ABS(E13))</f>
         <v>22.2222222222222</v>
       </c>
-      <c r="H13" s="47" t="n">
+      <c r="H13" s="41" t="n">
         <f aca="false">F13+G13</f>
         <v>72.2222222222222</v>
       </c>
-      <c r="I13" s="48" t="s">
+      <c r="I13" s="42" t="s">
         <v>90</v>
       </c>
-      <c r="J13" s="47" t="n">
+      <c r="J13" s="41" t="n">
         <f aca="false">IF(I13="Win",F13+G13,IF(I13="Push",F13,IF(I13="Loss",0,0)))</f>
         <v>72.2222222222222</v>
       </c>
-      <c r="K13" s="49" t="n">
+      <c r="K13" s="43" t="n">
         <f aca="false">IF(I13="Pending",0,J13-F13)</f>
         <v>22.2222222222222</v>
       </c>
-      <c r="L13" s="50" t="s">
+      <c r="L13" s="44" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="38" t="n">
+      <c r="A14" s="33" t="n">
         <v>8</v>
       </c>
-      <c r="B14" s="43" t="s">
+      <c r="B14" s="37" t="s">
         <v>112</v>
       </c>
-      <c r="C14" s="44" t="s">
+      <c r="C14" s="38" t="s">
         <v>113</v>
       </c>
-      <c r="D14" s="38" t="s">
+      <c r="D14" s="33" t="s">
         <v>89</v>
       </c>
-      <c r="E14" s="45" t="n">
+      <c r="E14" s="39" t="n">
         <v>-258</v>
       </c>
-      <c r="F14" s="46" t="n">
+      <c r="F14" s="40" t="n">
         <v>62</v>
       </c>
-      <c r="G14" s="47" t="n">
+      <c r="G14" s="41" t="n">
         <f aca="false">IF(E14&gt;0,F14*E14/100,F14*100/ABS(E14))</f>
         <v>24.031007751938</v>
       </c>
-      <c r="H14" s="47" t="n">
+      <c r="H14" s="41" t="n">
         <f aca="false">F14+G14</f>
         <v>86.031007751938</v>
       </c>
-      <c r="I14" s="48" t="s">
+      <c r="I14" s="42" t="s">
         <v>90</v>
       </c>
-      <c r="J14" s="47" t="n">
+      <c r="J14" s="41" t="n">
         <f aca="false">IF(I14="Win",F14+G14,IF(I14="Push",F14,IF(I14="Loss",0,0)))</f>
         <v>86.031007751938</v>
       </c>
-      <c r="K14" s="49" t="n">
+      <c r="K14" s="43" t="n">
         <f aca="false">IF(I14="Pending",0,J14-F14)</f>
         <v>24.031007751938</v>
       </c>
-      <c r="L14" s="50" t="s">
+      <c r="L14" s="44" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="38" t="n">
+      <c r="A15" s="33" t="n">
         <v>9</v>
       </c>
-      <c r="B15" s="43" t="s">
+      <c r="B15" s="37" t="s">
         <v>115</v>
       </c>
-      <c r="C15" s="44" t="s">
+      <c r="C15" s="38" t="s">
         <v>116</v>
       </c>
-      <c r="D15" s="38" t="s">
+      <c r="D15" s="33" t="s">
         <v>117</v>
       </c>
-      <c r="E15" s="45" t="n">
+      <c r="E15" s="39" t="n">
         <v>443</v>
       </c>
-      <c r="F15" s="46" t="n">
+      <c r="F15" s="40" t="n">
         <v>50</v>
       </c>
-      <c r="G15" s="47" t="n">
+      <c r="G15" s="41" t="n">
         <f aca="false">IF(E15&gt;0,F15*E15/100,F15*100/ABS(E15))</f>
         <v>221.5</v>
       </c>
-      <c r="H15" s="47" t="n">
+      <c r="H15" s="41" t="n">
         <f aca="false">F15+G15</f>
         <v>271.5</v>
       </c>
-      <c r="I15" s="51" t="s">
+      <c r="I15" s="45" t="s">
         <v>98</v>
       </c>
-      <c r="J15" s="47" t="n">
+      <c r="J15" s="41" t="n">
         <f aca="false">IF(I15="Win",F15+G15,IF(I15="Push",F15,IF(I15="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K15" s="49" t="n">
+      <c r="K15" s="43" t="n">
         <f aca="false">IF(I15="Pending",0,J15-F15)</f>
         <v>-50</v>
       </c>
-      <c r="L15" s="50" t="s">
+      <c r="L15" s="44" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="52"/>
-      <c r="B16" s="53" t="s">
+      <c r="A16" s="46"/>
+      <c r="B16" s="47" t="s">
         <v>39</v>
       </c>
-      <c r="C16" s="52"/>
-      <c r="D16" s="52"/>
-      <c r="E16" s="52"/>
-      <c r="F16" s="54" t="n">
+      <c r="C16" s="46"/>
+      <c r="D16" s="46"/>
+      <c r="E16" s="46"/>
+      <c r="F16" s="48" t="n">
         <f aca="false">SUM(F7:F15)</f>
         <v>1050</v>
       </c>
-      <c r="G16" s="55" t="n">
+      <c r="G16" s="49" t="n">
         <f aca="false">SUM(G7:G15)</f>
         <v>830.481932464331</v>
       </c>
-      <c r="H16" s="55" t="n">
+      <c r="H16" s="49" t="n">
         <f aca="false">SUM(H7:H15)</f>
         <v>1880.48193246433</v>
       </c>
-      <c r="I16" s="52"/>
-      <c r="J16" s="55" t="n">
+      <c r="I16" s="46"/>
+      <c r="J16" s="49" t="n">
         <f aca="false">SUM(J7:J15)</f>
         <v>1215.1103728313</v>
       </c>
-      <c r="K16" s="56" t="n">
+      <c r="K16" s="50" t="n">
         <f aca="false">SUM(K7:K15)</f>
         <v>165.110372831303</v>
       </c>
-      <c r="L16" s="52"/>
+      <c r="L16" s="46"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="4" t="s">
@@ -4256,91 +4052,91 @@
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="43" t="s">
+      <c r="B19" s="37" t="s">
         <v>120</v>
       </c>
-      <c r="C19" s="57" t="n">
+      <c r="C19" s="51" t="n">
         <f aca="false">COUNTIF(I7:I15,"Win")</f>
         <v>6</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="43" t="s">
+      <c r="B20" s="37" t="s">
         <v>121</v>
       </c>
-      <c r="C20" s="57" t="n">
+      <c r="C20" s="51" t="n">
         <f aca="false">COUNTIF(I7:I15,"Loss")</f>
         <v>3</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="43" t="s">
+      <c r="B21" s="37" t="s">
         <v>122</v>
       </c>
-      <c r="C21" s="57" t="n">
+      <c r="C21" s="51" t="n">
         <f aca="false">COUNTIF(I7:I15,"Push")</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="43" t="s">
+      <c r="B22" s="37" t="s">
         <v>123</v>
       </c>
-      <c r="C22" s="57" t="n">
+      <c r="C22" s="51" t="n">
         <f aca="false">COUNTIF(I7:I15,"Pending")</f>
         <v>0</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="43" t="s">
+      <c r="B23" s="37" t="s">
         <v>124</v>
       </c>
-      <c r="C23" s="58" t="n">
+      <c r="C23" s="52" t="n">
         <f aca="false">IF(COUNTIF(I7:I15,"Win")+COUNTIF(I7:I15,"Loss")=0,"—",COUNTIF(I7:I15,"Win")/(COUNTIF(I7:I15,"Win")+COUNTIF(I7:I15,"Loss")))</f>
         <v>0.666666666666667</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="43" t="s">
+      <c r="B24" s="37" t="s">
         <v>125</v>
       </c>
-      <c r="C24" s="59" t="n">
+      <c r="C24" s="34" t="n">
         <f aca="false">SUM(F7:F15)</f>
         <v>1050</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="43" t="s">
+      <c r="B25" s="37" t="s">
         <v>126</v>
       </c>
-      <c r="C25" s="47" t="n">
+      <c r="C25" s="41" t="n">
         <f aca="false">SUM(J7:J15)</f>
         <v>1215.1103728313</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="43" t="s">
+      <c r="B26" s="37" t="s">
         <v>127</v>
       </c>
-      <c r="C26" s="49" t="n">
+      <c r="C26" s="43" t="n">
         <f aca="false">SUM(K7:K15)</f>
         <v>165.110372831303</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="43" t="s">
+      <c r="B27" s="37" t="s">
         <v>128</v>
       </c>
-      <c r="C27" s="58" t="n">
+      <c r="C27" s="52" t="n">
         <f aca="false">IF(SUM(F7:F15)=0,"—",SUM(K7:K15)/SUM(F7:F15))</f>
         <v>0.157247974125051</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="43" t="s">
+      <c r="B28" s="37" t="s">
         <v>129</v>
       </c>
-      <c r="C28" s="47" t="n">
+      <c r="C28" s="41" t="n">
         <f aca="false">SUM(H7:H15)</f>
         <v>1880.48193246433</v>
       </c>
@@ -4351,157 +4147,157 @@
       </c>
     </row>
     <row r="31" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="15" t="s">
+      <c r="A31" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B31" s="15" t="s">
+      <c r="B31" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="C31" s="15" t="s">
+      <c r="C31" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="D31" s="15" t="s">
+      <c r="D31" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="E31" s="15" t="s">
+      <c r="E31" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="F31" s="15" t="s">
+      <c r="F31" s="12" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="38" t="n">
+      <c r="A32" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="B32" s="43" t="s">
+      <c r="B32" s="37" t="s">
         <v>136</v>
       </c>
-      <c r="C32" s="50" t="s">
+      <c r="C32" s="44" t="s">
         <v>137</v>
       </c>
-      <c r="D32" s="60" t="s">
+      <c r="D32" s="53" t="s">
         <v>138</v>
       </c>
-      <c r="E32" s="61" t="s">
+      <c r="E32" s="54" t="s">
         <v>139</v>
       </c>
-      <c r="F32" s="61" t="s">
+      <c r="F32" s="54" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="38" t="n">
+      <c r="A33" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="B33" s="43" t="s">
+      <c r="B33" s="37" t="s">
         <v>141</v>
       </c>
-      <c r="C33" s="50" t="s">
+      <c r="C33" s="44" t="s">
         <v>142</v>
       </c>
-      <c r="D33" s="60" t="s">
+      <c r="D33" s="53" t="s">
         <v>143</v>
       </c>
-      <c r="E33" s="61" t="s">
+      <c r="E33" s="54" t="s">
         <v>144</v>
       </c>
-      <c r="F33" s="61" t="s">
+      <c r="F33" s="54" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="38" t="n">
+      <c r="A34" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="B34" s="43" t="s">
+      <c r="B34" s="37" t="s">
         <v>146</v>
       </c>
-      <c r="C34" s="50" t="s">
+      <c r="C34" s="44" t="s">
         <v>147</v>
       </c>
-      <c r="D34" s="60" t="s">
+      <c r="D34" s="53" t="s">
         <v>148</v>
       </c>
-      <c r="E34" s="61" t="s">
+      <c r="E34" s="54" t="s">
         <v>149</v>
       </c>
-      <c r="F34" s="61" t="s">
+      <c r="F34" s="54" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="38" t="n">
+      <c r="A35" s="33" t="n">
         <v>4</v>
       </c>
-      <c r="B35" s="43" t="s">
+      <c r="B35" s="37" t="s">
         <v>151</v>
       </c>
-      <c r="C35" s="50" t="s">
+      <c r="C35" s="44" t="s">
         <v>152</v>
       </c>
-      <c r="D35" s="60" t="s">
+      <c r="D35" s="53" t="s">
         <v>153</v>
       </c>
-      <c r="E35" s="61" t="s">
+      <c r="E35" s="54" t="s">
         <v>154</v>
       </c>
-      <c r="F35" s="61" t="s">
+      <c r="F35" s="54" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="38" t="n">
+      <c r="A36" s="33" t="n">
         <v>5</v>
       </c>
-      <c r="B36" s="43" t="s">
+      <c r="B36" s="37" t="s">
         <v>156</v>
       </c>
-      <c r="C36" s="50" t="s">
+      <c r="C36" s="44" t="s">
         <v>157</v>
       </c>
-      <c r="D36" s="60" t="s">
+      <c r="D36" s="53" t="s">
         <v>158</v>
       </c>
-      <c r="E36" s="61" t="s">
+      <c r="E36" s="54" t="s">
         <v>159</v>
       </c>
-      <c r="F36" s="61" t="s">
+      <c r="F36" s="54" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="38" t="n">
+      <c r="A37" s="33" t="n">
         <v>6</v>
       </c>
-      <c r="B37" s="43" t="s">
+      <c r="B37" s="37" t="s">
         <v>161</v>
       </c>
-      <c r="C37" s="50" t="s">
+      <c r="C37" s="44" t="s">
         <v>162</v>
       </c>
-      <c r="D37" s="60" t="s">
+      <c r="D37" s="53" t="s">
         <v>47</v>
       </c>
-      <c r="E37" s="61" t="s">
+      <c r="E37" s="54" t="s">
         <v>163</v>
       </c>
-      <c r="F37" s="61" t="s">
+      <c r="F37" s="54" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="62" t="s">
+      <c r="A39" s="55" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="62" t="s">
+      <c r="A40" s="55" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="62" t="s">
+      <c r="A41" s="55" t="s">
         <v>167</v>
       </c>
     </row>
@@ -4559,10 +4355,10 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="35" t="s">
         <v>168</v>
       </c>
-      <c r="H1" s="63" t="s">
+      <c r="H1" s="56" t="s">
         <v>169</v>
       </c>
     </row>
@@ -4582,367 +4378,367 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="C6" s="12" t="s">
         <v>172</v>
       </c>
-      <c r="D6" s="15" t="s">
+      <c r="D6" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="E6" s="15" t="s">
+      <c r="E6" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="F6" s="15" t="s">
+      <c r="F6" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="G6" s="15" t="s">
+      <c r="G6" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="H6" s="15" t="s">
+      <c r="H6" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="I6" s="15" t="s">
+      <c r="I6" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="J6" s="15" t="s">
+      <c r="J6" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="K6" s="15" t="s">
+      <c r="K6" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="L6" s="15" t="s">
+      <c r="L6" s="12" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="38" t="n">
+      <c r="A7" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="43" t="s">
+      <c r="B7" s="37" t="s">
         <v>173</v>
       </c>
-      <c r="C7" s="44" t="s">
+      <c r="C7" s="38" t="s">
         <v>174</v>
       </c>
-      <c r="D7" s="38" t="s">
+      <c r="D7" s="33" t="s">
         <v>175</v>
       </c>
-      <c r="E7" s="45" t="n">
+      <c r="E7" s="39" t="n">
         <v>-144</v>
       </c>
-      <c r="F7" s="46" t="n">
+      <c r="F7" s="40" t="n">
         <v>300</v>
       </c>
-      <c r="G7" s="47" t="n">
+      <c r="G7" s="41" t="n">
         <f aca="false">IF(E7&gt;0,F7*E7/100,F7*100/ABS(E7))</f>
         <v>208.333333333333</v>
       </c>
-      <c r="H7" s="47" t="n">
+      <c r="H7" s="41" t="n">
         <f aca="false">F7+G7</f>
         <v>508.333333333333</v>
       </c>
-      <c r="I7" s="64" t="s">
+      <c r="I7" s="57" t="s">
         <v>123</v>
       </c>
-      <c r="J7" s="47" t="n">
+      <c r="J7" s="41" t="n">
         <f aca="false">IF(I7="Win",F7+G7,IF(I7="Push",F7,IF(I7="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K7" s="49" t="n">
+      <c r="K7" s="43" t="n">
         <f aca="false">IF(I7="Pending",0,J7-F7)</f>
         <v>0</v>
       </c>
-      <c r="L7" s="50" t="s">
+      <c r="L7" s="44" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="38" t="n">
+      <c r="A8" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="43" t="s">
+      <c r="B8" s="37" t="s">
         <v>177</v>
       </c>
-      <c r="C8" s="44" t="s">
+      <c r="C8" s="38" t="s">
         <v>178</v>
       </c>
-      <c r="D8" s="38" t="s">
+      <c r="D8" s="33" t="s">
         <v>179</v>
       </c>
-      <c r="E8" s="45" t="n">
+      <c r="E8" s="39" t="n">
         <v>-122</v>
       </c>
-      <c r="F8" s="46" t="n">
+      <c r="F8" s="40" t="n">
         <v>120</v>
       </c>
-      <c r="G8" s="47" t="n">
+      <c r="G8" s="41" t="n">
         <f aca="false">IF(E8&gt;0,F8*E8/100,F8*100/ABS(E8))</f>
         <v>98.3606557377049</v>
       </c>
-      <c r="H8" s="47" t="n">
+      <c r="H8" s="41" t="n">
         <f aca="false">F8+G8</f>
         <v>218.360655737705</v>
       </c>
-      <c r="I8" s="64" t="s">
+      <c r="I8" s="57" t="s">
         <v>123</v>
       </c>
-      <c r="J8" s="47" t="n">
+      <c r="J8" s="41" t="n">
         <f aca="false">IF(I8="Win",F8+G8,IF(I8="Push",F8,IF(I8="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K8" s="49" t="n">
+      <c r="K8" s="43" t="n">
         <f aca="false">IF(I8="Pending",0,J8-F8)</f>
         <v>0</v>
       </c>
-      <c r="L8" s="50" t="s">
+      <c r="L8" s="44" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="38" t="n">
+      <c r="A9" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="B9" s="43" t="s">
+      <c r="B9" s="37" t="s">
         <v>181</v>
       </c>
-      <c r="C9" s="44" t="s">
+      <c r="C9" s="38" t="s">
         <v>182</v>
       </c>
-      <c r="D9" s="38" t="s">
+      <c r="D9" s="33" t="s">
         <v>183</v>
       </c>
-      <c r="E9" s="45" t="n">
+      <c r="E9" s="39" t="n">
         <v>175</v>
       </c>
-      <c r="F9" s="46" t="n">
+      <c r="F9" s="40" t="n">
         <v>150</v>
       </c>
-      <c r="G9" s="47" t="n">
+      <c r="G9" s="41" t="n">
         <f aca="false">IF(E9&gt;0,F9*E9/100,F9*100/ABS(E9))</f>
         <v>262.5</v>
       </c>
-      <c r="H9" s="47" t="n">
+      <c r="H9" s="41" t="n">
         <f aca="false">F9+G9</f>
         <v>412.5</v>
       </c>
-      <c r="I9" s="64" t="s">
+      <c r="I9" s="57" t="s">
         <v>123</v>
       </c>
-      <c r="J9" s="47" t="n">
+      <c r="J9" s="41" t="n">
         <f aca="false">IF(I9="Win",F9+G9,IF(I9="Push",F9,IF(I9="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K9" s="49" t="n">
+      <c r="K9" s="43" t="n">
         <f aca="false">IF(I9="Pending",0,J9-F9)</f>
         <v>0</v>
       </c>
-      <c r="L9" s="50" t="s">
+      <c r="L9" s="44" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="38" t="n">
+      <c r="A10" s="33" t="n">
         <v>4</v>
       </c>
-      <c r="B10" s="43" t="s">
+      <c r="B10" s="37" t="s">
         <v>185</v>
       </c>
-      <c r="C10" s="44" t="s">
+      <c r="C10" s="38" t="s">
         <v>186</v>
       </c>
-      <c r="D10" s="38" t="s">
+      <c r="D10" s="33" t="s">
         <v>183</v>
       </c>
-      <c r="E10" s="45" t="n">
+      <c r="E10" s="39" t="n">
         <v>205</v>
       </c>
-      <c r="F10" s="46" t="n">
+      <c r="F10" s="40" t="n">
         <v>80</v>
       </c>
-      <c r="G10" s="47" t="n">
+      <c r="G10" s="41" t="n">
         <f aca="false">IF(E10&gt;0,F10*E10/100,F10*100/ABS(E10))</f>
         <v>164</v>
       </c>
-      <c r="H10" s="47" t="n">
+      <c r="H10" s="41" t="n">
         <f aca="false">F10+G10</f>
         <v>244</v>
       </c>
-      <c r="I10" s="64" t="s">
+      <c r="I10" s="57" t="s">
         <v>123</v>
       </c>
-      <c r="J10" s="47" t="n">
+      <c r="J10" s="41" t="n">
         <f aca="false">IF(I10="Win",F10+G10,IF(I10="Push",F10,IF(I10="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K10" s="49" t="n">
+      <c r="K10" s="43" t="n">
         <f aca="false">IF(I10="Pending",0,J10-F10)</f>
         <v>0</v>
       </c>
-      <c r="L10" s="50" t="s">
+      <c r="L10" s="44" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="38" t="n">
+      <c r="A11" s="33" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="43" t="s">
+      <c r="B11" s="37" t="s">
         <v>188</v>
       </c>
-      <c r="C11" s="44" t="s">
+      <c r="C11" s="38" t="s">
         <v>189</v>
       </c>
-      <c r="D11" s="38" t="s">
+      <c r="D11" s="33" t="s">
         <v>190</v>
       </c>
-      <c r="E11" s="45" t="n">
+      <c r="E11" s="39" t="n">
         <v>160</v>
       </c>
-      <c r="F11" s="46" t="n">
+      <c r="F11" s="40" t="n">
         <v>250</v>
       </c>
-      <c r="G11" s="47" t="n">
+      <c r="G11" s="41" t="n">
         <f aca="false">IF(E11&gt;0,F11*E11/100,F11*100/ABS(E11))</f>
         <v>400</v>
       </c>
-      <c r="H11" s="47" t="n">
+      <c r="H11" s="41" t="n">
         <f aca="false">F11+G11</f>
         <v>650</v>
       </c>
-      <c r="I11" s="64" t="s">
+      <c r="I11" s="57" t="s">
         <v>123</v>
       </c>
-      <c r="J11" s="47" t="n">
+      <c r="J11" s="41" t="n">
         <f aca="false">IF(I11="Win",F11+G11,IF(I11="Push",F11,IF(I11="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K11" s="49" t="n">
+      <c r="K11" s="43" t="n">
         <f aca="false">IF(I11="Pending",0,J11-F11)</f>
         <v>0</v>
       </c>
-      <c r="L11" s="50" t="s">
+      <c r="L11" s="44" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="38" t="n">
+      <c r="A12" s="33" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="43" t="s">
+      <c r="B12" s="37" t="s">
         <v>192</v>
       </c>
-      <c r="C12" s="44" t="s">
+      <c r="C12" s="38" t="s">
         <v>193</v>
       </c>
-      <c r="D12" s="38" t="s">
+      <c r="D12" s="33" t="s">
         <v>190</v>
       </c>
-      <c r="E12" s="45" t="n">
+      <c r="E12" s="39" t="n">
         <v>500</v>
       </c>
-      <c r="F12" s="46" t="n">
+      <c r="F12" s="40" t="n">
         <v>50</v>
       </c>
-      <c r="G12" s="47" t="n">
+      <c r="G12" s="41" t="n">
         <f aca="false">IF(E12&gt;0,F12*E12/100,F12*100/ABS(E12))</f>
         <v>250</v>
       </c>
-      <c r="H12" s="47" t="n">
+      <c r="H12" s="41" t="n">
         <f aca="false">F12+G12</f>
         <v>300</v>
       </c>
-      <c r="I12" s="64" t="s">
+      <c r="I12" s="57" t="s">
         <v>123</v>
       </c>
-      <c r="J12" s="47" t="n">
+      <c r="J12" s="41" t="n">
         <f aca="false">IF(I12="Win",F12+G12,IF(I12="Push",F12,IF(I12="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K12" s="49" t="n">
+      <c r="K12" s="43" t="n">
         <f aca="false">IF(I12="Pending",0,J12-F12)</f>
         <v>0</v>
       </c>
-      <c r="L12" s="50" t="s">
+      <c r="L12" s="44" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="38" t="n">
+      <c r="A13" s="33" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="43" t="s">
+      <c r="B13" s="37" t="s">
         <v>195</v>
       </c>
-      <c r="C13" s="44" t="s">
+      <c r="C13" s="38" t="s">
         <v>196</v>
       </c>
-      <c r="D13" s="38" t="s">
+      <c r="D13" s="33" t="s">
         <v>117</v>
       </c>
-      <c r="E13" s="45" t="n">
+      <c r="E13" s="39" t="n">
         <v>179</v>
       </c>
-      <c r="F13" s="46" t="n">
+      <c r="F13" s="40" t="n">
         <v>50</v>
       </c>
-      <c r="G13" s="47" t="n">
+      <c r="G13" s="41" t="n">
         <f aca="false">IF(E13&gt;0,F13*E13/100,F13*100/ABS(E13))</f>
         <v>89.5</v>
       </c>
-      <c r="H13" s="47" t="n">
+      <c r="H13" s="41" t="n">
         <f aca="false">F13+G13</f>
         <v>139.5</v>
       </c>
-      <c r="I13" s="64" t="s">
+      <c r="I13" s="57" t="s">
         <v>123</v>
       </c>
-      <c r="J13" s="47" t="n">
+      <c r="J13" s="41" t="n">
         <f aca="false">IF(I13="Win",F13+G13,IF(I13="Push",F13,IF(I13="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K13" s="49" t="n">
+      <c r="K13" s="43" t="n">
         <f aca="false">IF(I13="Pending",0,J13-F13)</f>
         <v>0</v>
       </c>
-      <c r="L13" s="50" t="s">
+      <c r="L13" s="44" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="52"/>
-      <c r="B14" s="53" t="s">
+      <c r="A14" s="46"/>
+      <c r="B14" s="47" t="s">
         <v>39</v>
       </c>
-      <c r="C14" s="52"/>
-      <c r="D14" s="52"/>
-      <c r="E14" s="52"/>
-      <c r="F14" s="54" t="n">
+      <c r="C14" s="46"/>
+      <c r="D14" s="46"/>
+      <c r="E14" s="46"/>
+      <c r="F14" s="48" t="n">
         <f aca="false">SUM(F7:F13)</f>
         <v>1000</v>
       </c>
-      <c r="G14" s="55" t="n">
+      <c r="G14" s="49" t="n">
         <f aca="false">SUM(G7:G13)</f>
         <v>1472.69398907104</v>
       </c>
-      <c r="H14" s="55" t="n">
+      <c r="H14" s="49" t="n">
         <f aca="false">SUM(H7:H13)</f>
         <v>2472.69398907104</v>
       </c>
-      <c r="I14" s="52"/>
-      <c r="J14" s="55" t="n">
+      <c r="I14" s="46"/>
+      <c r="J14" s="49" t="n">
         <f aca="false">SUM(J7:J13)</f>
         <v>0</v>
       </c>
-      <c r="K14" s="56" t="n">
+      <c r="K14" s="50" t="n">
         <f aca="false">SUM(K7:K13)</f>
         <v>0</v>
       </c>
-      <c r="L14" s="52"/>
+      <c r="L14" s="46"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="4" t="s">
@@ -4950,91 +4746,91 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="43" t="s">
+      <c r="B17" s="37" t="s">
         <v>120</v>
       </c>
-      <c r="C17" s="57" t="n">
+      <c r="C17" s="51" t="n">
         <f aca="false">COUNTIF(I7:I13,"Win")</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="43" t="s">
+      <c r="B18" s="37" t="s">
         <v>121</v>
       </c>
-      <c r="C18" s="57" t="n">
+      <c r="C18" s="51" t="n">
         <f aca="false">COUNTIF(I7:I13,"Loss")</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="43" t="s">
+      <c r="B19" s="37" t="s">
         <v>122</v>
       </c>
-      <c r="C19" s="57" t="n">
+      <c r="C19" s="51" t="n">
         <f aca="false">COUNTIF(I7:I13,"Push")</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="43" t="s">
+      <c r="B20" s="37" t="s">
         <v>123</v>
       </c>
-      <c r="C20" s="57" t="n">
+      <c r="C20" s="51" t="n">
         <f aca="false">COUNTIF(I7:I13,"Pending")</f>
         <v>7</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="43" t="s">
+      <c r="B21" s="37" t="s">
         <v>124</v>
       </c>
-      <c r="C21" s="58" t="str">
+      <c r="C21" s="52" t="str">
         <f aca="false">IF(COUNTIF(I7:I13,"Win")+COUNTIF(I7:I13,"Loss")=0,"—",COUNTIF(I7:I13,"Win")/(COUNTIF(I7:I13,"Win")+COUNTIF(I7:I13,"Loss")))</f>
         <v>—</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="43" t="s">
+      <c r="B22" s="37" t="s">
         <v>125</v>
       </c>
-      <c r="C22" s="59" t="n">
+      <c r="C22" s="34" t="n">
         <f aca="false">SUM(F7:F13)</f>
         <v>1000</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="43" t="s">
+      <c r="B23" s="37" t="s">
         <v>126</v>
       </c>
-      <c r="C23" s="47" t="n">
+      <c r="C23" s="41" t="n">
         <f aca="false">SUM(J7:J13)</f>
         <v>0</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="43" t="s">
+      <c r="B24" s="37" t="s">
         <v>127</v>
       </c>
-      <c r="C24" s="49" t="n">
+      <c r="C24" s="43" t="n">
         <f aca="false">SUM(K7:K13)</f>
         <v>0</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="43" t="s">
+      <c r="B25" s="37" t="s">
         <v>128</v>
       </c>
-      <c r="C25" s="58" t="n">
+      <c r="C25" s="52" t="n">
         <f aca="false">IF(SUM(F7:F13)=0,"—",SUM(K7:K13)/SUM(F7:F13))</f>
         <v>0</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="43" t="s">
+      <c r="B26" s="37" t="s">
         <v>198</v>
       </c>
-      <c r="C26" s="59" t="n">
+      <c r="C26" s="34" t="n">
         <f aca="false">929</f>
         <v>929</v>
       </c>
@@ -5045,91 +4841,91 @@
       </c>
     </row>
     <row r="29" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="15" t="s">
+      <c r="A29" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B29" s="15" t="s">
+      <c r="B29" s="12" t="s">
         <v>200</v>
       </c>
-      <c r="C29" s="15" t="s">
+      <c r="C29" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="D29" s="15" t="s">
+      <c r="D29" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="E29" s="15" t="s">
+      <c r="E29" s="12" t="s">
         <v>201</v>
       </c>
-      <c r="F29" s="15" t="s">
+      <c r="F29" s="12" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="38" t="n">
+      <c r="A30" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="B30" s="43" t="s">
+      <c r="B30" s="37" t="s">
         <v>202</v>
       </c>
-      <c r="C30" s="50" t="s">
+      <c r="C30" s="44" t="s">
         <v>203</v>
       </c>
-      <c r="D30" s="60" t="s">
+      <c r="D30" s="53" t="s">
         <v>204</v>
       </c>
-      <c r="E30" s="64"/>
-      <c r="F30" s="64"/>
+      <c r="E30" s="57"/>
+      <c r="F30" s="57"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="38" t="n">
+      <c r="A31" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="B31" s="43" t="s">
+      <c r="B31" s="37" t="s">
         <v>205</v>
       </c>
-      <c r="C31" s="50" t="s">
+      <c r="C31" s="44" t="s">
         <v>206</v>
       </c>
-      <c r="D31" s="60" t="s">
+      <c r="D31" s="53" t="s">
         <v>207</v>
       </c>
-      <c r="E31" s="64"/>
-      <c r="F31" s="64"/>
+      <c r="E31" s="57"/>
+      <c r="F31" s="57"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="38" t="n">
+      <c r="A32" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="B32" s="43" t="s">
+      <c r="B32" s="37" t="s">
         <v>208</v>
       </c>
-      <c r="C32" s="50" t="s">
+      <c r="C32" s="44" t="s">
         <v>209</v>
       </c>
-      <c r="D32" s="60" t="s">
+      <c r="D32" s="53" t="s">
         <v>210</v>
       </c>
-      <c r="E32" s="64"/>
-      <c r="F32" s="64"/>
+      <c r="E32" s="57"/>
+      <c r="F32" s="57"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="38" t="n">
+      <c r="A33" s="33" t="n">
         <v>4</v>
       </c>
-      <c r="B33" s="43" t="s">
+      <c r="B33" s="37" t="s">
         <v>211</v>
       </c>
-      <c r="C33" s="50" t="s">
+      <c r="C33" s="44" t="s">
         <v>212</v>
       </c>
-      <c r="D33" s="60" t="s">
+      <c r="D33" s="53" t="s">
         <v>213</v>
       </c>
-      <c r="E33" s="64"/>
-      <c r="F33" s="64"/>
+      <c r="E33" s="57"/>
+      <c r="F33" s="57"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="62" t="s">
+      <c r="A35" s="55" t="s">
         <v>214</v>
       </c>
     </row>
@@ -5188,10 +4984,10 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="35" t="s">
         <v>215</v>
       </c>
-      <c r="H1" s="42" t="s">
+      <c r="H1" s="36" t="s">
         <v>216</v>
       </c>
     </row>
@@ -5211,440 +5007,440 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="C6" s="12" t="s">
         <v>219</v>
       </c>
-      <c r="D6" s="15" t="s">
+      <c r="D6" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="E6" s="15" t="s">
+      <c r="E6" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="F6" s="15" t="s">
+      <c r="F6" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="G6" s="15" t="s">
+      <c r="G6" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="H6" s="15" t="s">
+      <c r="H6" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="I6" s="15" t="s">
+      <c r="I6" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="J6" s="15" t="s">
+      <c r="J6" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="K6" s="15" t="s">
+      <c r="K6" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="L6" s="15" t="s">
+      <c r="L6" s="12" t="s">
         <v>220</v>
       </c>
-      <c r="M6" s="15" t="s">
+      <c r="M6" s="12" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="38" t="n">
+      <c r="A7" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="43" t="s">
+      <c r="B7" s="37" t="s">
         <v>221</v>
       </c>
-      <c r="C7" s="44" t="s">
+      <c r="C7" s="38" t="s">
         <v>222</v>
       </c>
-      <c r="D7" s="38" t="s">
+      <c r="D7" s="33" t="s">
         <v>89</v>
       </c>
-      <c r="E7" s="45" t="n">
+      <c r="E7" s="39" t="n">
         <v>-155</v>
       </c>
-      <c r="F7" s="46" t="n">
+      <c r="F7" s="40" t="n">
         <v>200</v>
       </c>
-      <c r="G7" s="47" t="n">
+      <c r="G7" s="41" t="n">
         <f aca="false">IF(E7&gt;0,F7*E7/100,F7*100/ABS(E7))</f>
         <v>129.032258064516</v>
       </c>
-      <c r="H7" s="47" t="n">
+      <c r="H7" s="41" t="n">
         <f aca="false">F7+G7</f>
         <v>329.032258064516</v>
       </c>
-      <c r="I7" s="48" t="s">
+      <c r="I7" s="42" t="s">
         <v>90</v>
       </c>
-      <c r="J7" s="47" t="n">
+      <c r="J7" s="41" t="n">
         <f aca="false">IF(I7="Win",F7+G7,IF(I7="Push",F7,IF(I7="Loss",0,0)))</f>
         <v>329.032258064516</v>
       </c>
-      <c r="K7" s="49" t="n">
+      <c r="K7" s="43" t="n">
         <f aca="false">IF(I7="Pending",0,J7-F7)</f>
         <v>129.032258064516</v>
       </c>
-      <c r="L7" s="65" t="n">
+      <c r="L7" s="58" t="n">
         <v>0.62</v>
       </c>
-      <c r="M7" s="50" t="s">
+      <c r="M7" s="44" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="38" t="n">
+      <c r="A8" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="43" t="s">
+      <c r="B8" s="37" t="s">
         <v>224</v>
       </c>
-      <c r="C8" s="44" t="s">
+      <c r="C8" s="38" t="s">
         <v>225</v>
       </c>
-      <c r="D8" s="38" t="s">
+      <c r="D8" s="33" t="s">
         <v>89</v>
       </c>
-      <c r="E8" s="45" t="n">
+      <c r="E8" s="39" t="n">
         <v>-104</v>
       </c>
-      <c r="F8" s="46" t="n">
+      <c r="F8" s="40" t="n">
         <v>150</v>
       </c>
-      <c r="G8" s="47" t="n">
+      <c r="G8" s="41" t="n">
         <f aca="false">IF(E8&gt;0,F8*E8/100,F8*100/ABS(E8))</f>
         <v>144.230769230769</v>
       </c>
-      <c r="H8" s="47" t="n">
+      <c r="H8" s="41" t="n">
         <f aca="false">F8+G8</f>
         <v>294.230769230769</v>
       </c>
-      <c r="I8" s="51" t="s">
+      <c r="I8" s="45" t="s">
         <v>98</v>
       </c>
-      <c r="J8" s="47" t="n">
+      <c r="J8" s="41" t="n">
         <f aca="false">IF(I8="Win",F8+G8,IF(I8="Push",F8,IF(I8="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K8" s="49" t="n">
+      <c r="K8" s="43" t="n">
         <f aca="false">IF(I8="Pending",0,J8-F8)</f>
         <v>-150</v>
       </c>
-      <c r="L8" s="65" t="n">
+      <c r="L8" s="58" t="n">
         <v>0.54</v>
       </c>
-      <c r="M8" s="50" t="s">
+      <c r="M8" s="44" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="38" t="n">
+      <c r="A9" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="B9" s="43" t="s">
+      <c r="B9" s="37" t="s">
         <v>227</v>
       </c>
-      <c r="C9" s="44" t="s">
+      <c r="C9" s="38" t="s">
         <v>228</v>
       </c>
-      <c r="D9" s="38" t="s">
+      <c r="D9" s="33" t="s">
         <v>89</v>
       </c>
-      <c r="E9" s="45" t="n">
+      <c r="E9" s="39" t="n">
         <v>-115</v>
       </c>
-      <c r="F9" s="46" t="n">
+      <c r="F9" s="40" t="n">
         <v>150</v>
       </c>
-      <c r="G9" s="47" t="n">
+      <c r="G9" s="41" t="n">
         <f aca="false">IF(E9&gt;0,F9*E9/100,F9*100/ABS(E9))</f>
         <v>130.434782608696</v>
       </c>
-      <c r="H9" s="47" t="n">
+      <c r="H9" s="41" t="n">
         <f aca="false">F9+G9</f>
         <v>280.434782608696</v>
       </c>
-      <c r="I9" s="51" t="s">
+      <c r="I9" s="45" t="s">
         <v>98</v>
       </c>
-      <c r="J9" s="47" t="n">
+      <c r="J9" s="41" t="n">
         <f aca="false">IF(I9="Win",F9+G9,IF(I9="Push",F9,IF(I9="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K9" s="49" t="n">
+      <c r="K9" s="43" t="n">
         <f aca="false">IF(I9="Pending",0,J9-F9)</f>
         <v>-150</v>
       </c>
-      <c r="L9" s="65" t="n">
+      <c r="L9" s="58" t="n">
         <v>0.55</v>
       </c>
-      <c r="M9" s="50" t="s">
+      <c r="M9" s="44" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="38" t="n">
+      <c r="A10" s="33" t="n">
         <v>4</v>
       </c>
-      <c r="B10" s="43" t="s">
+      <c r="B10" s="37" t="s">
         <v>230</v>
       </c>
-      <c r="C10" s="44" t="s">
+      <c r="C10" s="38" t="s">
         <v>231</v>
       </c>
-      <c r="D10" s="38" t="s">
+      <c r="D10" s="33" t="s">
         <v>179</v>
       </c>
-      <c r="E10" s="45" t="n">
+      <c r="E10" s="39" t="n">
         <v>-114</v>
       </c>
-      <c r="F10" s="46" t="n">
+      <c r="F10" s="40" t="n">
         <v>120</v>
       </c>
-      <c r="G10" s="47" t="n">
+      <c r="G10" s="41" t="n">
         <f aca="false">IF(E10&gt;0,F10*E10/100,F10*100/ABS(E10))</f>
         <v>105.263157894737</v>
       </c>
-      <c r="H10" s="47" t="n">
+      <c r="H10" s="41" t="n">
         <f aca="false">F10+G10</f>
         <v>225.263157894737</v>
       </c>
-      <c r="I10" s="51" t="s">
+      <c r="I10" s="45" t="s">
         <v>98</v>
       </c>
-      <c r="J10" s="47" t="n">
+      <c r="J10" s="41" t="n">
         <f aca="false">IF(I10="Win",F10+G10,IF(I10="Push",F10,IF(I10="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K10" s="49" t="n">
+      <c r="K10" s="43" t="n">
         <f aca="false">IF(I10="Pending",0,J10-F10)</f>
         <v>-120</v>
       </c>
-      <c r="L10" s="65" t="n">
+      <c r="L10" s="58" t="n">
         <v>0.55</v>
       </c>
-      <c r="M10" s="50" t="s">
+      <c r="M10" s="44" t="s">
         <v>232</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="38" t="n">
+      <c r="A11" s="33" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="43" t="s">
+      <c r="B11" s="37" t="s">
         <v>233</v>
       </c>
-      <c r="C11" s="44" t="s">
+      <c r="C11" s="38" t="s">
         <v>234</v>
       </c>
-      <c r="D11" s="38" t="s">
+      <c r="D11" s="33" t="s">
         <v>89</v>
       </c>
-      <c r="E11" s="45" t="n">
+      <c r="E11" s="39" t="n">
         <v>104</v>
       </c>
-      <c r="F11" s="46" t="n">
+      <c r="F11" s="40" t="n">
         <v>130</v>
       </c>
-      <c r="G11" s="47" t="n">
+      <c r="G11" s="41" t="n">
         <f aca="false">IF(E11&gt;0,F11*E11/100,F11*100/ABS(E11))</f>
         <v>135.2</v>
       </c>
-      <c r="H11" s="47" t="n">
+      <c r="H11" s="41" t="n">
         <f aca="false">F11+G11</f>
         <v>265.2</v>
       </c>
-      <c r="I11" s="48" t="s">
+      <c r="I11" s="42" t="s">
         <v>90</v>
       </c>
-      <c r="J11" s="47" t="n">
+      <c r="J11" s="41" t="n">
         <f aca="false">IF(I11="Win",F11+G11,IF(I11="Push",F11,IF(I11="Loss",0,0)))</f>
         <v>265.2</v>
       </c>
-      <c r="K11" s="49" t="n">
+      <c r="K11" s="43" t="n">
         <f aca="false">IF(I11="Pending",0,J11-F11)</f>
         <v>135.2</v>
       </c>
-      <c r="L11" s="65" t="n">
+      <c r="L11" s="58" t="n">
         <v>0.52</v>
       </c>
-      <c r="M11" s="50" t="s">
+      <c r="M11" s="44" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="38" t="n">
+      <c r="A12" s="33" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="43" t="s">
+      <c r="B12" s="37" t="s">
         <v>236</v>
       </c>
-      <c r="C12" s="44" t="s">
+      <c r="C12" s="38" t="s">
         <v>237</v>
       </c>
-      <c r="D12" s="38" t="s">
+      <c r="D12" s="33" t="s">
         <v>89</v>
       </c>
-      <c r="E12" s="45" t="n">
+      <c r="E12" s="39" t="n">
         <v>108</v>
       </c>
-      <c r="F12" s="46" t="n">
+      <c r="F12" s="40" t="n">
         <v>100</v>
       </c>
-      <c r="G12" s="47" t="n">
+      <c r="G12" s="41" t="n">
         <f aca="false">IF(E12&gt;0,F12*E12/100,F12*100/ABS(E12))</f>
         <v>108</v>
       </c>
-      <c r="H12" s="47" t="n">
+      <c r="H12" s="41" t="n">
         <f aca="false">F12+G12</f>
         <v>208</v>
       </c>
-      <c r="I12" s="51" t="s">
+      <c r="I12" s="45" t="s">
         <v>98</v>
       </c>
-      <c r="J12" s="47" t="n">
+      <c r="J12" s="41" t="n">
         <f aca="false">IF(I12="Win",F12+G12,IF(I12="Push",F12,IF(I12="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K12" s="49" t="n">
+      <c r="K12" s="43" t="n">
         <f aca="false">IF(I12="Pending",0,J12-F12)</f>
         <v>-100</v>
       </c>
-      <c r="L12" s="65" t="n">
+      <c r="L12" s="58" t="n">
         <v>0.5</v>
       </c>
-      <c r="M12" s="50" t="s">
+      <c r="M12" s="44" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="38" t="n">
+      <c r="A13" s="33" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="43" t="s">
+      <c r="B13" s="37" t="s">
         <v>239</v>
       </c>
-      <c r="C13" s="44" t="s">
+      <c r="C13" s="38" t="s">
         <v>240</v>
       </c>
-      <c r="D13" s="38" t="s">
+      <c r="D13" s="33" t="s">
         <v>89</v>
       </c>
-      <c r="E13" s="45" t="n">
+      <c r="E13" s="39" t="n">
         <v>108</v>
       </c>
-      <c r="F13" s="46" t="n">
+      <c r="F13" s="40" t="n">
         <v>100</v>
       </c>
-      <c r="G13" s="47" t="n">
+      <c r="G13" s="41" t="n">
         <f aca="false">IF(E13&gt;0,F13*E13/100,F13*100/ABS(E13))</f>
         <v>108</v>
       </c>
-      <c r="H13" s="47" t="n">
+      <c r="H13" s="41" t="n">
         <f aca="false">F13+G13</f>
         <v>208</v>
       </c>
-      <c r="I13" s="48" t="s">
+      <c r="I13" s="42" t="s">
         <v>90</v>
       </c>
-      <c r="J13" s="47" t="n">
+      <c r="J13" s="41" t="n">
         <f aca="false">IF(I13="Win",F13+G13,IF(I13="Push",F13,IF(I13="Loss",0,0)))</f>
         <v>208</v>
       </c>
-      <c r="K13" s="49" t="n">
+      <c r="K13" s="43" t="n">
         <f aca="false">IF(I13="Pending",0,J13-F13)</f>
         <v>108</v>
       </c>
-      <c r="L13" s="65" t="n">
+      <c r="L13" s="58" t="n">
         <v>0.5</v>
       </c>
-      <c r="M13" s="50" t="s">
+      <c r="M13" s="44" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="38" t="n">
+      <c r="A14" s="33" t="n">
         <v>8</v>
       </c>
-      <c r="B14" s="43" t="s">
+      <c r="B14" s="37" t="s">
         <v>242</v>
       </c>
-      <c r="C14" s="44" t="s">
+      <c r="C14" s="38" t="s">
         <v>243</v>
       </c>
-      <c r="D14" s="38" t="s">
+      <c r="D14" s="33" t="s">
         <v>117</v>
       </c>
-      <c r="E14" s="45" t="n">
+      <c r="E14" s="39" t="n">
         <v>732</v>
       </c>
-      <c r="F14" s="46" t="n">
+      <c r="F14" s="40" t="n">
         <v>50</v>
       </c>
-      <c r="G14" s="47" t="n">
+      <c r="G14" s="41" t="n">
         <f aca="false">IF(E14&gt;0,F14*E14/100,F14*100/ABS(E14))</f>
         <v>366</v>
       </c>
-      <c r="H14" s="47" t="n">
+      <c r="H14" s="41" t="n">
         <f aca="false">F14+G14</f>
         <v>416</v>
       </c>
-      <c r="I14" s="51" t="s">
+      <c r="I14" s="45" t="s">
         <v>98</v>
       </c>
-      <c r="J14" s="47" t="n">
+      <c r="J14" s="41" t="n">
         <f aca="false">IF(I14="Win",F14+G14,IF(I14="Push",F14,IF(I14="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K14" s="49" t="n">
+      <c r="K14" s="43" t="n">
         <f aca="false">IF(I14="Pending",0,J14-F14)</f>
         <v>-50</v>
       </c>
-      <c r="L14" s="65" t="n">
+      <c r="L14" s="58" t="n">
         <v>0.14</v>
       </c>
-      <c r="M14" s="50" t="s">
+      <c r="M14" s="44" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="52"/>
-      <c r="B15" s="53" t="s">
+      <c r="A15" s="46"/>
+      <c r="B15" s="47" t="s">
         <v>39</v>
       </c>
-      <c r="C15" s="52"/>
-      <c r="D15" s="52"/>
-      <c r="E15" s="52"/>
-      <c r="F15" s="54" t="n">
+      <c r="C15" s="46"/>
+      <c r="D15" s="46"/>
+      <c r="E15" s="46"/>
+      <c r="F15" s="48" t="n">
         <f aca="false">SUM(F7:F14)</f>
         <v>1000</v>
       </c>
-      <c r="G15" s="55" t="n">
+      <c r="G15" s="49" t="n">
         <f aca="false">SUM(G7:G14)</f>
         <v>1226.16096779872</v>
       </c>
-      <c r="H15" s="55" t="n">
+      <c r="H15" s="49" t="n">
         <f aca="false">SUM(H7:H14)</f>
         <v>2226.16096779872</v>
       </c>
-      <c r="I15" s="52"/>
-      <c r="J15" s="55" t="n">
+      <c r="I15" s="46"/>
+      <c r="J15" s="49" t="n">
         <f aca="false">SUM(J7:J14)</f>
         <v>802.232258064516</v>
       </c>
-      <c r="K15" s="56" t="n">
+      <c r="K15" s="50" t="n">
         <f aca="false">SUM(K7:K14)</f>
         <v>-197.767741935484</v>
       </c>
-      <c r="L15" s="66" t="n">
+      <c r="L15" s="59" t="n">
         <f aca="false">SUM(L7:L14)</f>
         <v>3.92</v>
       </c>
-      <c r="M15" s="52"/>
+      <c r="M15" s="46"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="4" t="s">
@@ -5652,109 +5448,109 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="43" t="s">
+      <c r="B18" s="37" t="s">
         <v>120</v>
       </c>
-      <c r="C18" s="57" t="n">
+      <c r="C18" s="51" t="n">
         <f aca="false">COUNTIF(I7:I14,"Win")</f>
         <v>3</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="43" t="s">
+      <c r="B19" s="37" t="s">
         <v>121</v>
       </c>
-      <c r="C19" s="57" t="n">
+      <c r="C19" s="51" t="n">
         <f aca="false">COUNTIF(I7:I14,"Loss")</f>
         <v>5</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="43" t="s">
+      <c r="B20" s="37" t="s">
         <v>122</v>
       </c>
-      <c r="C20" s="57" t="n">
+      <c r="C20" s="51" t="n">
         <f aca="false">COUNTIF(I7:I14,"Push")</f>
         <v>0</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="43" t="s">
+      <c r="B21" s="37" t="s">
         <v>123</v>
       </c>
-      <c r="C21" s="57" t="n">
+      <c r="C21" s="51" t="n">
         <f aca="false">COUNTIF(I7:I14,"Pending")</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="43" t="s">
+      <c r="B22" s="37" t="s">
         <v>124</v>
       </c>
-      <c r="C22" s="58" t="n">
+      <c r="C22" s="52" t="n">
         <f aca="false">IF(COUNTIF(I7:I14,"Win")+COUNTIF(I7:I14,"Loss")=0,"—",COUNTIF(I7:I14,"Win")/(COUNTIF(I7:I14,"Win")+COUNTIF(I7:I14,"Loss")))</f>
         <v>0.375</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="43" t="s">
+      <c r="B23" s="37" t="s">
         <v>125</v>
       </c>
-      <c r="C23" s="59" t="n">
+      <c r="C23" s="34" t="n">
         <f aca="false">SUM(F7:F14)</f>
         <v>1000</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="43" t="s">
+      <c r="B24" s="37" t="s">
         <v>126</v>
       </c>
-      <c r="C24" s="47" t="n">
+      <c r="C24" s="41" t="n">
         <f aca="false">SUM(J7:J14)</f>
         <v>802.232258064516</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="43" t="s">
+      <c r="B25" s="37" t="s">
         <v>127</v>
       </c>
-      <c r="C25" s="49" t="n">
+      <c r="C25" s="43" t="n">
         <f aca="false">SUM(K7:K14)</f>
         <v>-197.767741935484</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="43" t="s">
+      <c r="B26" s="37" t="s">
         <v>128</v>
       </c>
-      <c r="C26" s="58" t="n">
+      <c r="C26" s="52" t="n">
         <f aca="false">IF(SUM(F7:F14)=0,"—",SUM(K7:K14)/SUM(F7:F14))</f>
         <v>-0.197767741935484</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="43" t="s">
+      <c r="B27" s="37" t="s">
         <v>129</v>
       </c>
-      <c r="C27" s="47" t="n">
+      <c r="C27" s="41" t="n">
         <f aca="false">SUM(H7:H14)</f>
         <v>2226.16096779872</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="43" t="s">
+      <c r="B28" s="37" t="s">
         <v>245</v>
       </c>
-      <c r="C28" s="67" t="n">
+      <c r="C28" s="60" t="n">
         <f aca="false">SUM(L7:L14)</f>
         <v>3.92</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="43" t="s">
+      <c r="B29" s="37" t="s">
         <v>246</v>
       </c>
-      <c r="C29" s="49" t="n">
+      <c r="C29" s="43" t="n">
         <f aca="false">SUMPRODUCT(L7:L14,G7:G14)-SUMPRODUCT(1-L7:L14,F7:F14)</f>
         <v>45.1624826615033</v>
       </c>
@@ -5765,155 +5561,155 @@
       </c>
     </row>
     <row r="32" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="15" t="s">
+      <c r="A32" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B32" s="15" t="s">
+      <c r="B32" s="12" t="s">
         <v>248</v>
       </c>
-      <c r="C32" s="15" t="s">
+      <c r="C32" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="D32" s="15" t="s">
+      <c r="D32" s="12" t="s">
         <v>249</v>
       </c>
-      <c r="E32" s="15" t="s">
+      <c r="E32" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="F32" s="15" t="s">
+      <c r="F32" s="12" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="38" t="n">
+      <c r="A33" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="B33" s="43" t="s">
+      <c r="B33" s="37" t="s">
         <v>250</v>
       </c>
-      <c r="C33" s="50" t="s">
+      <c r="C33" s="44" t="s">
         <v>251</v>
       </c>
-      <c r="D33" s="60" t="s">
+      <c r="D33" s="53" t="s">
         <v>252</v>
       </c>
-      <c r="E33" s="64"/>
-      <c r="F33" s="64"/>
+      <c r="E33" s="57"/>
+      <c r="F33" s="57"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="38" t="n">
+      <c r="A34" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="B34" s="43" t="s">
+      <c r="B34" s="37" t="s">
         <v>253</v>
       </c>
-      <c r="C34" s="50" t="s">
+      <c r="C34" s="44" t="s">
         <v>254</v>
       </c>
-      <c r="D34" s="60" t="s">
+      <c r="D34" s="53" t="s">
         <v>255</v>
       </c>
-      <c r="E34" s="64"/>
-      <c r="F34" s="64"/>
+      <c r="E34" s="57"/>
+      <c r="F34" s="57"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="38" t="n">
+      <c r="A35" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="B35" s="43" t="s">
+      <c r="B35" s="37" t="s">
         <v>256</v>
       </c>
-      <c r="C35" s="50" t="s">
+      <c r="C35" s="44" t="s">
         <v>257</v>
       </c>
-      <c r="D35" s="60" t="s">
+      <c r="D35" s="53" t="s">
         <v>258</v>
       </c>
-      <c r="E35" s="64"/>
-      <c r="F35" s="64"/>
+      <c r="E35" s="57"/>
+      <c r="F35" s="57"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="38" t="n">
+      <c r="A36" s="33" t="n">
         <v>4</v>
       </c>
-      <c r="B36" s="43" t="s">
+      <c r="B36" s="37" t="s">
         <v>259</v>
       </c>
-      <c r="C36" s="50" t="s">
+      <c r="C36" s="44" t="s">
         <v>260</v>
       </c>
-      <c r="D36" s="60" t="s">
+      <c r="D36" s="53" t="s">
         <v>261</v>
       </c>
-      <c r="E36" s="64"/>
-      <c r="F36" s="64"/>
+      <c r="E36" s="57"/>
+      <c r="F36" s="57"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="38" t="n">
+      <c r="A37" s="33" t="n">
         <v>5</v>
       </c>
-      <c r="B37" s="43" t="s">
+      <c r="B37" s="37" t="s">
         <v>262</v>
       </c>
-      <c r="C37" s="50" t="s">
+      <c r="C37" s="44" t="s">
         <v>263</v>
       </c>
-      <c r="D37" s="60" t="s">
+      <c r="D37" s="53" t="s">
         <v>264</v>
       </c>
-      <c r="E37" s="64"/>
-      <c r="F37" s="64"/>
+      <c r="E37" s="57"/>
+      <c r="F37" s="57"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="38" t="n">
+      <c r="A38" s="33" t="n">
         <v>6</v>
       </c>
-      <c r="B38" s="43" t="s">
+      <c r="B38" s="37" t="s">
         <v>265</v>
       </c>
-      <c r="C38" s="50" t="s">
+      <c r="C38" s="44" t="s">
         <v>266</v>
       </c>
-      <c r="D38" s="60" t="s">
+      <c r="D38" s="53" t="s">
         <v>267</v>
       </c>
-      <c r="E38" s="64"/>
-      <c r="F38" s="64"/>
+      <c r="E38" s="57"/>
+      <c r="F38" s="57"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="38" t="n">
+      <c r="A39" s="33" t="n">
         <v>7</v>
       </c>
-      <c r="B39" s="43" t="s">
+      <c r="B39" s="37" t="s">
         <v>268</v>
       </c>
-      <c r="C39" s="50" t="s">
+      <c r="C39" s="44" t="s">
         <v>269</v>
       </c>
-      <c r="D39" s="60" t="s">
+      <c r="D39" s="53" t="s">
         <v>270</v>
       </c>
-      <c r="E39" s="64"/>
-      <c r="F39" s="64"/>
+      <c r="E39" s="57"/>
+      <c r="F39" s="57"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="38" t="n">
+      <c r="A40" s="33" t="n">
         <v>8</v>
       </c>
-      <c r="B40" s="43" t="s">
+      <c r="B40" s="37" t="s">
         <v>271</v>
       </c>
-      <c r="C40" s="50" t="s">
+      <c r="C40" s="44" t="s">
         <v>272</v>
       </c>
-      <c r="D40" s="60" t="s">
+      <c r="D40" s="53" t="s">
         <v>273</v>
       </c>
-      <c r="E40" s="64"/>
-      <c r="F40" s="64"/>
+      <c r="E40" s="57"/>
+      <c r="F40" s="57"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="62" t="s">
+      <c r="A42" s="55" t="s">
         <v>274</v>
       </c>
     </row>
@@ -5980,10 +5776,10 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="35" t="s">
         <v>275</v>
       </c>
-      <c r="H1" s="63" t="s">
+      <c r="H1" s="56" t="s">
         <v>276</v>
       </c>
     </row>
@@ -5993,7 +5789,7 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="68" t="s">
+      <c r="A3" s="61" t="s">
         <v>278</v>
       </c>
     </row>
@@ -6003,395 +5799,395 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="C6" s="12" t="s">
         <v>200</v>
       </c>
-      <c r="D6" s="15" t="s">
+      <c r="D6" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="E6" s="15" t="s">
+      <c r="E6" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="F6" s="15" t="s">
+      <c r="F6" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="G6" s="15" t="s">
+      <c r="G6" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="H6" s="15" t="s">
+      <c r="H6" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="I6" s="15" t="s">
+      <c r="I6" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="J6" s="15" t="s">
+      <c r="J6" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="K6" s="15" t="s">
+      <c r="K6" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="L6" s="15" t="s">
+      <c r="L6" s="12" t="s">
         <v>220</v>
       </c>
-      <c r="M6" s="15" t="s">
+      <c r="M6" s="12" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="38" t="n">
+      <c r="A7" s="33" t="n">
         <v>1</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>279</v>
       </c>
-      <c r="C7" s="37" t="s">
+      <c r="C7" s="32" t="s">
         <v>280</v>
       </c>
-      <c r="D7" s="38" t="s">
+      <c r="D7" s="33" t="s">
         <v>281</v>
       </c>
-      <c r="E7" s="45" t="n">
+      <c r="E7" s="39" t="n">
         <v>-113</v>
       </c>
-      <c r="F7" s="46" t="n">
+      <c r="F7" s="40" t="n">
         <v>300</v>
       </c>
-      <c r="G7" s="47" t="n">
+      <c r="G7" s="41" t="n">
         <f aca="false">IF(E7&gt;0,F7*E7/100,F7*100/ABS(E7))</f>
         <v>265.486725663717</v>
       </c>
-      <c r="H7" s="47" t="n">
+      <c r="H7" s="41" t="n">
         <f aca="false">F7+G7</f>
         <v>565.486725663717</v>
       </c>
-      <c r="I7" s="64" t="s">
+      <c r="I7" s="57" t="s">
         <v>90</v>
       </c>
-      <c r="J7" s="47" t="n">
+      <c r="J7" s="41" t="n">
         <f aca="false">IF(I7="Win",F7+G7,IF(I7="Push",F7,IF(I7="Loss",0,0)))</f>
         <v>565.486725663717</v>
       </c>
-      <c r="K7" s="49" t="n">
+      <c r="K7" s="43" t="n">
         <f aca="false">IF(I7="Pending",0,J7-F7)</f>
         <v>265.486725663717</v>
       </c>
-      <c r="L7" s="65" t="n">
+      <c r="L7" s="58" t="n">
         <v>0.58</v>
       </c>
-      <c r="M7" s="69" t="s">
+      <c r="M7" s="62" t="s">
         <v>282</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="38" t="n">
+      <c r="A8" s="33" t="n">
         <v>2</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>283</v>
       </c>
-      <c r="C8" s="37" t="s">
+      <c r="C8" s="32" t="s">
         <v>284</v>
       </c>
-      <c r="D8" s="38" t="s">
+      <c r="D8" s="33" t="s">
         <v>94</v>
       </c>
-      <c r="E8" s="45" t="n">
+      <c r="E8" s="39" t="n">
         <v>456</v>
       </c>
-      <c r="F8" s="46" t="n">
+      <c r="F8" s="40" t="n">
         <v>200</v>
       </c>
-      <c r="G8" s="47" t="n">
+      <c r="G8" s="41" t="n">
         <f aca="false">IF(E8&gt;0,F8*E8/100,F8*100/ABS(E8))</f>
         <v>912</v>
       </c>
-      <c r="H8" s="47" t="n">
+      <c r="H8" s="41" t="n">
         <f aca="false">F8+G8</f>
         <v>1112</v>
       </c>
-      <c r="I8" s="64" t="s">
+      <c r="I8" s="57" t="s">
         <v>98</v>
       </c>
-      <c r="J8" s="47" t="n">
+      <c r="J8" s="41" t="n">
         <f aca="false">IF(I8="Win",F8+G8,IF(I8="Push",F8,IF(I8="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K8" s="49" t="n">
+      <c r="K8" s="43" t="n">
         <f aca="false">IF(I8="Pending",0,J8-F8)</f>
         <v>-200</v>
       </c>
-      <c r="L8" s="65" t="n">
+      <c r="L8" s="58" t="n">
         <v>0.24</v>
       </c>
-      <c r="M8" s="69" t="s">
+      <c r="M8" s="62" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="38" t="n">
+      <c r="A9" s="33" t="n">
         <v>3</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>286</v>
       </c>
-      <c r="C9" s="37" t="s">
+      <c r="C9" s="32" t="s">
         <v>287</v>
       </c>
-      <c r="D9" s="38" t="s">
+      <c r="D9" s="33" t="s">
         <v>190</v>
       </c>
-      <c r="E9" s="45" t="n">
+      <c r="E9" s="39" t="n">
         <v>1150</v>
       </c>
-      <c r="F9" s="46" t="n">
+      <c r="F9" s="40" t="n">
         <v>150</v>
       </c>
-      <c r="G9" s="47" t="n">
+      <c r="G9" s="41" t="n">
         <f aca="false">IF(E9&gt;0,F9*E9/100,F9*100/ABS(E9))</f>
         <v>1725</v>
       </c>
-      <c r="H9" s="47" t="n">
+      <c r="H9" s="41" t="n">
         <f aca="false">F9+G9</f>
         <v>1875</v>
       </c>
-      <c r="I9" s="64" t="s">
+      <c r="I9" s="57" t="s">
         <v>98</v>
       </c>
-      <c r="J9" s="47" t="n">
+      <c r="J9" s="41" t="n">
         <f aca="false">IF(I9="Win",F9+G9,IF(I9="Push",F9,IF(I9="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K9" s="49" t="n">
+      <c r="K9" s="43" t="n">
         <f aca="false">IF(I9="Pending",0,J9-F9)</f>
         <v>-150</v>
       </c>
-      <c r="L9" s="65" t="n">
+      <c r="L9" s="58" t="n">
         <v>0.1</v>
       </c>
-      <c r="M9" s="69" t="s">
+      <c r="M9" s="62" t="s">
         <v>288</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="38" t="n">
+      <c r="A10" s="33" t="n">
         <v>4</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>289</v>
       </c>
-      <c r="C10" s="37" t="s">
+      <c r="C10" s="32" t="s">
         <v>287</v>
       </c>
-      <c r="D10" s="38" t="s">
+      <c r="D10" s="33" t="s">
         <v>190</v>
       </c>
-      <c r="E10" s="45" t="n">
+      <c r="E10" s="39" t="n">
         <v>1567</v>
       </c>
-      <c r="F10" s="46" t="n">
+      <c r="F10" s="40" t="n">
         <v>120</v>
       </c>
-      <c r="G10" s="47" t="n">
+      <c r="G10" s="41" t="n">
         <f aca="false">IF(E10&gt;0,F10*E10/100,F10*100/ABS(E10))</f>
         <v>1880.4</v>
       </c>
-      <c r="H10" s="47" t="n">
+      <c r="H10" s="41" t="n">
         <f aca="false">F10+G10</f>
         <v>2000.4</v>
       </c>
-      <c r="I10" s="64" t="s">
+      <c r="I10" s="57" t="s">
         <v>98</v>
       </c>
-      <c r="J10" s="47" t="n">
+      <c r="J10" s="41" t="n">
         <f aca="false">IF(I10="Win",F10+G10,IF(I10="Push",F10,IF(I10="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K10" s="49" t="n">
+      <c r="K10" s="43" t="n">
         <f aca="false">IF(I10="Pending",0,J10-F10)</f>
         <v>-120</v>
       </c>
-      <c r="L10" s="65" t="n">
+      <c r="L10" s="58" t="n">
         <v>0.08</v>
       </c>
-      <c r="M10" s="69" t="s">
+      <c r="M10" s="62" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="38" t="n">
+      <c r="A11" s="33" t="n">
         <v>5</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>291</v>
       </c>
-      <c r="C11" s="37" t="s">
+      <c r="C11" s="32" t="s">
         <v>287</v>
       </c>
-      <c r="D11" s="38" t="s">
+      <c r="D11" s="33" t="s">
         <v>190</v>
       </c>
-      <c r="E11" s="45" t="n">
+      <c r="E11" s="39" t="n">
         <v>1800</v>
       </c>
-      <c r="F11" s="46" t="n">
+      <c r="F11" s="40" t="n">
         <v>100</v>
       </c>
-      <c r="G11" s="47" t="n">
+      <c r="G11" s="41" t="n">
         <f aca="false">IF(E11&gt;0,F11*E11/100,F11*100/ABS(E11))</f>
         <v>1800</v>
       </c>
-      <c r="H11" s="47" t="n">
+      <c r="H11" s="41" t="n">
         <f aca="false">F11+G11</f>
         <v>1900</v>
       </c>
-      <c r="I11" s="64" t="s">
+      <c r="I11" s="57" t="s">
         <v>98</v>
       </c>
-      <c r="J11" s="47" t="n">
+      <c r="J11" s="41" t="n">
         <f aca="false">IF(I11="Win",F11+G11,IF(I11="Push",F11,IF(I11="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K11" s="49" t="n">
+      <c r="K11" s="43" t="n">
         <f aca="false">IF(I11="Pending",0,J11-F11)</f>
         <v>-100</v>
       </c>
-      <c r="L11" s="65" t="n">
+      <c r="L11" s="58" t="n">
         <v>0.07</v>
       </c>
-      <c r="M11" s="69" t="s">
+      <c r="M11" s="62" t="s">
         <v>292</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="38" t="n">
+      <c r="A12" s="33" t="n">
         <v>6</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>293</v>
       </c>
-      <c r="C12" s="37" t="s">
+      <c r="C12" s="32" t="s">
         <v>287</v>
       </c>
-      <c r="D12" s="38" t="s">
+      <c r="D12" s="33" t="s">
         <v>190</v>
       </c>
-      <c r="E12" s="45" t="n">
+      <c r="E12" s="39" t="n">
         <v>1150</v>
       </c>
-      <c r="F12" s="46" t="n">
+      <c r="F12" s="40" t="n">
         <v>90</v>
       </c>
-      <c r="G12" s="47" t="n">
+      <c r="G12" s="41" t="n">
         <f aca="false">IF(E12&gt;0,F12*E12/100,F12*100/ABS(E12))</f>
         <v>1035</v>
       </c>
-      <c r="H12" s="47" t="n">
+      <c r="H12" s="41" t="n">
         <f aca="false">F12+G12</f>
         <v>1125</v>
       </c>
-      <c r="I12" s="64" t="s">
+      <c r="I12" s="57" t="s">
         <v>98</v>
       </c>
-      <c r="J12" s="47" t="n">
+      <c r="J12" s="41" t="n">
         <f aca="false">IF(I12="Win",F12+G12,IF(I12="Push",F12,IF(I12="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K12" s="49" t="n">
+      <c r="K12" s="43" t="n">
         <f aca="false">IF(I12="Pending",0,J12-F12)</f>
         <v>-90</v>
       </c>
-      <c r="L12" s="65" t="n">
+      <c r="L12" s="58" t="n">
         <v>0.08</v>
       </c>
-      <c r="M12" s="69" t="s">
+      <c r="M12" s="62" t="s">
         <v>294</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="38" t="n">
+      <c r="A13" s="33" t="n">
         <v>7</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>295</v>
       </c>
-      <c r="C13" s="37" t="s">
+      <c r="C13" s="32" t="s">
         <v>287</v>
       </c>
-      <c r="D13" s="38" t="s">
+      <c r="D13" s="33" t="s">
         <v>190</v>
       </c>
-      <c r="E13" s="45" t="n">
+      <c r="E13" s="39" t="n">
         <v>1900</v>
       </c>
-      <c r="F13" s="46" t="n">
+      <c r="F13" s="40" t="n">
         <v>40</v>
       </c>
-      <c r="G13" s="47" t="n">
+      <c r="G13" s="41" t="n">
         <f aca="false">IF(E13&gt;0,F13*E13/100,F13*100/ABS(E13))</f>
         <v>760</v>
       </c>
-      <c r="H13" s="47" t="n">
+      <c r="H13" s="41" t="n">
         <f aca="false">F13+G13</f>
         <v>800</v>
       </c>
-      <c r="I13" s="64" t="s">
+      <c r="I13" s="57" t="s">
         <v>98</v>
       </c>
-      <c r="J13" s="47" t="n">
+      <c r="J13" s="41" t="n">
         <f aca="false">IF(I13="Win",F13+G13,IF(I13="Push",F13,IF(I13="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K13" s="49" t="n">
+      <c r="K13" s="43" t="n">
         <f aca="false">IF(I13="Pending",0,J13-F13)</f>
         <v>-40</v>
       </c>
-      <c r="L13" s="65" t="n">
+      <c r="L13" s="58" t="n">
         <v>0.05</v>
       </c>
-      <c r="M13" s="69" t="s">
+      <c r="M13" s="62" t="s">
         <v>296</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="70"/>
-      <c r="B14" s="71" t="s">
+      <c r="A14" s="63"/>
+      <c r="B14" s="64" t="s">
         <v>39</v>
       </c>
-      <c r="C14" s="70"/>
-      <c r="D14" s="70"/>
-      <c r="E14" s="70"/>
-      <c r="F14" s="54" t="n">
+      <c r="C14" s="63"/>
+      <c r="D14" s="63"/>
+      <c r="E14" s="63"/>
+      <c r="F14" s="48" t="n">
         <f aca="false">SUM(F7:F13)</f>
         <v>1000</v>
       </c>
-      <c r="G14" s="55" t="n">
+      <c r="G14" s="49" t="n">
         <f aca="false">SUM(G7:G13)</f>
         <v>8377.88672566372</v>
       </c>
-      <c r="H14" s="55" t="n">
+      <c r="H14" s="49" t="n">
         <f aca="false">SUM(H7:H13)</f>
         <v>9377.88672566372</v>
       </c>
-      <c r="I14" s="70"/>
-      <c r="J14" s="55" t="n">
+      <c r="I14" s="63"/>
+      <c r="J14" s="49" t="n">
         <f aca="false">SUM(J7:J13)</f>
         <v>565.486725663717</v>
       </c>
-      <c r="K14" s="56" t="n">
+      <c r="K14" s="50" t="n">
         <f aca="false">SUM(K7:K13)</f>
         <v>-434.513274336283</v>
       </c>
-      <c r="L14" s="66" t="n">
+      <c r="L14" s="59" t="n">
         <f aca="false">SUM(L7:L13)</f>
         <v>1.2</v>
       </c>
-      <c r="M14" s="70"/>
+      <c r="M14" s="63"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="4" t="s">
@@ -6402,7 +6198,7 @@
       <c r="B17" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="C17" s="57" t="n">
+      <c r="C17" s="51" t="n">
         <f aca="false">COUNTIF(I7:I13,"Win")</f>
         <v>1</v>
       </c>
@@ -6411,7 +6207,7 @@
       <c r="B18" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="C18" s="57" t="n">
+      <c r="C18" s="51" t="n">
         <f aca="false">COUNTIF(I7:I13,"Loss")</f>
         <v>6</v>
       </c>
@@ -6420,7 +6216,7 @@
       <c r="B19" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="C19" s="57" t="n">
+      <c r="C19" s="51" t="n">
         <f aca="false">COUNTIF(I7:I13,"Push")</f>
         <v>0</v>
       </c>
@@ -6429,7 +6225,7 @@
       <c r="B20" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="C20" s="57" t="n">
+      <c r="C20" s="51" t="n">
         <f aca="false">COUNTIF(I7:I13,"Pending")</f>
         <v>0</v>
       </c>
@@ -6438,7 +6234,7 @@
       <c r="B21" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="C21" s="58" t="n">
+      <c r="C21" s="52" t="n">
         <f aca="false">IF(COUNTIF(I7:I13,"Win")+COUNTIF(I7:I13,"Loss")=0,"—",COUNTIF(I7:I13,"Win")/(COUNTIF(I7:I13,"Win")+COUNTIF(I7:I13,"Loss")))</f>
         <v>0.142857142857143</v>
       </c>
@@ -6447,7 +6243,7 @@
       <c r="B22" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="C22" s="59" t="n">
+      <c r="C22" s="34" t="n">
         <f aca="false">SUM(F7:F13)</f>
         <v>1000</v>
       </c>
@@ -6456,7 +6252,7 @@
       <c r="B23" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="C23" s="47" t="n">
+      <c r="C23" s="41" t="n">
         <f aca="false">SUM(J7:J13)</f>
         <v>565.486725663717</v>
       </c>
@@ -6465,7 +6261,7 @@
       <c r="B24" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="C24" s="49" t="n">
+      <c r="C24" s="43" t="n">
         <f aca="false">SUM(K7:K13)</f>
         <v>-434.513274336283</v>
       </c>
@@ -6474,7 +6270,7 @@
       <c r="B25" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="C25" s="58" t="n">
+      <c r="C25" s="52" t="n">
         <f aca="false">IF(SUM(F7:F13)=0,"—",SUM(K7:K13)/SUM(F7:F13))</f>
         <v>-0.434513274336283</v>
       </c>
@@ -6483,7 +6279,7 @@
       <c r="B26" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="C26" s="67" t="n">
+      <c r="C26" s="60" t="n">
         <f aca="false">SUM(L7:L13)</f>
         <v>1.2</v>
       </c>
@@ -6492,13 +6288,13 @@
       <c r="B27" s="5" t="s">
         <v>297</v>
       </c>
-      <c r="C27" s="59" t="n">
+      <c r="C27" s="34" t="n">
         <f aca="false">2678</f>
         <v>2678</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="62" t="s">
+      <c r="A29" s="55" t="s">
         <v>298</v>
       </c>
     </row>
@@ -6551,7 +6347,7 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="35" t="s">
         <v>299</v>
       </c>
     </row>
@@ -6561,25 +6357,25 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="12" t="s">
         <v>301</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="12" t="s">
         <v>302</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="C4" s="12" t="s">
         <v>303</v>
       </c>
-      <c r="D4" s="15" t="s">
+      <c r="D4" s="12" t="s">
         <v>304</v>
       </c>
-      <c r="E4" s="15" t="s">
+      <c r="E4" s="12" t="s">
         <v>305</v>
       </c>
-      <c r="F4" s="15" t="s">
+      <c r="F4" s="12" t="s">
         <v>306</v>
       </c>
-      <c r="G4" s="15" t="s">
+      <c r="G4" s="12" t="s">
         <v>86</v>
       </c>
     </row>
@@ -6587,18 +6383,18 @@
       <c r="A5" s="5" t="s">
         <v>307</v>
       </c>
-      <c r="B5" s="72" t="s">
+      <c r="B5" s="65" t="s">
         <v>308</v>
       </c>
-      <c r="C5" s="73"/>
-      <c r="D5" s="73" t="s">
+      <c r="C5" s="66"/>
+      <c r="D5" s="66" t="s">
         <v>309</v>
       </c>
-      <c r="E5" s="73" t="s">
+      <c r="E5" s="66" t="s">
         <v>309</v>
       </c>
-      <c r="F5" s="73"/>
-      <c r="G5" s="74" t="s">
+      <c r="F5" s="66"/>
+      <c r="G5" s="67" t="s">
         <v>310</v>
       </c>
     </row>
@@ -6606,16 +6402,16 @@
       <c r="A6" s="5" t="s">
         <v>311</v>
       </c>
-      <c r="B6" s="72" t="s">
+      <c r="B6" s="65" t="s">
         <v>312</v>
       </c>
-      <c r="C6" s="73" t="s">
+      <c r="C6" s="66" t="s">
         <v>309</v>
       </c>
-      <c r="D6" s="73"/>
-      <c r="E6" s="73"/>
-      <c r="F6" s="73"/>
-      <c r="G6" s="74" t="s">
+      <c r="D6" s="66"/>
+      <c r="E6" s="66"/>
+      <c r="F6" s="66"/>
+      <c r="G6" s="67" t="s">
         <v>313</v>
       </c>
     </row>
@@ -6623,16 +6419,16 @@
       <c r="A7" s="5" t="s">
         <v>314</v>
       </c>
-      <c r="B7" s="72" t="s">
+      <c r="B7" s="65" t="s">
         <v>315</v>
       </c>
-      <c r="C7" s="73" t="s">
+      <c r="C7" s="66" t="s">
         <v>309</v>
       </c>
-      <c r="D7" s="73"/>
-      <c r="E7" s="73"/>
-      <c r="F7" s="73"/>
-      <c r="G7" s="74" t="s">
+      <c r="D7" s="66"/>
+      <c r="E7" s="66"/>
+      <c r="F7" s="66"/>
+      <c r="G7" s="67" t="s">
         <v>316</v>
       </c>
     </row>
@@ -6640,16 +6436,16 @@
       <c r="A8" s="5" t="s">
         <v>317</v>
       </c>
-      <c r="B8" s="72" t="s">
+      <c r="B8" s="65" t="s">
         <v>318</v>
       </c>
-      <c r="C8" s="73"/>
-      <c r="D8" s="73" t="s">
+      <c r="C8" s="66"/>
+      <c r="D8" s="66" t="s">
         <v>309</v>
       </c>
-      <c r="E8" s="73"/>
-      <c r="F8" s="73"/>
-      <c r="G8" s="74" t="s">
+      <c r="E8" s="66"/>
+      <c r="F8" s="66"/>
+      <c r="G8" s="67" t="s">
         <v>319</v>
       </c>
     </row>
@@ -6657,18 +6453,18 @@
       <c r="A9" s="5" t="s">
         <v>320</v>
       </c>
-      <c r="B9" s="72" t="s">
+      <c r="B9" s="65" t="s">
         <v>321</v>
       </c>
-      <c r="C9" s="73"/>
-      <c r="D9" s="73" t="s">
+      <c r="C9" s="66"/>
+      <c r="D9" s="66" t="s">
         <v>309</v>
       </c>
-      <c r="E9" s="73"/>
-      <c r="F9" s="73" t="s">
+      <c r="E9" s="66"/>
+      <c r="F9" s="66" t="s">
         <v>309</v>
       </c>
-      <c r="G9" s="74" t="s">
+      <c r="G9" s="67" t="s">
         <v>322</v>
       </c>
     </row>
@@ -6676,18 +6472,18 @@
       <c r="A10" s="5" t="s">
         <v>323</v>
       </c>
-      <c r="B10" s="72" t="s">
+      <c r="B10" s="65" t="s">
         <v>324</v>
       </c>
-      <c r="C10" s="73"/>
-      <c r="D10" s="73" t="s">
+      <c r="C10" s="66"/>
+      <c r="D10" s="66" t="s">
         <v>309</v>
       </c>
-      <c r="E10" s="73" t="s">
+      <c r="E10" s="66" t="s">
         <v>309</v>
       </c>
-      <c r="F10" s="73"/>
-      <c r="G10" s="74" t="s">
+      <c r="F10" s="66"/>
+      <c r="G10" s="67" t="s">
         <v>325</v>
       </c>
     </row>
@@ -6695,18 +6491,18 @@
       <c r="A11" s="5" t="s">
         <v>326</v>
       </c>
-      <c r="B11" s="72" t="s">
+      <c r="B11" s="65" t="s">
         <v>327</v>
       </c>
-      <c r="C11" s="73"/>
-      <c r="D11" s="73" t="s">
+      <c r="C11" s="66"/>
+      <c r="D11" s="66" t="s">
         <v>309</v>
       </c>
-      <c r="E11" s="73"/>
-      <c r="F11" s="73" t="s">
+      <c r="E11" s="66"/>
+      <c r="F11" s="66" t="s">
         <v>309</v>
       </c>
-      <c r="G11" s="74" t="s">
+      <c r="G11" s="67" t="s">
         <v>328</v>
       </c>
     </row>
@@ -6714,16 +6510,16 @@
       <c r="A12" s="5" t="s">
         <v>329</v>
       </c>
-      <c r="B12" s="72" t="s">
+      <c r="B12" s="65" t="s">
         <v>330</v>
       </c>
-      <c r="C12" s="73"/>
-      <c r="D12" s="73" t="s">
+      <c r="C12" s="66"/>
+      <c r="D12" s="66" t="s">
         <v>309</v>
       </c>
-      <c r="E12" s="73"/>
-      <c r="F12" s="73"/>
-      <c r="G12" s="74" t="s">
+      <c r="E12" s="66"/>
+      <c r="F12" s="66"/>
+      <c r="G12" s="67" t="s">
         <v>331</v>
       </c>
     </row>
@@ -6731,16 +6527,16 @@
       <c r="A13" s="5" t="s">
         <v>332</v>
       </c>
-      <c r="B13" s="72" t="s">
+      <c r="B13" s="65" t="s">
         <v>333</v>
       </c>
-      <c r="C13" s="73"/>
-      <c r="D13" s="73" t="s">
+      <c r="C13" s="66"/>
+      <c r="D13" s="66" t="s">
         <v>309</v>
       </c>
-      <c r="E13" s="73"/>
-      <c r="F13" s="73"/>
-      <c r="G13" s="74" t="s">
+      <c r="E13" s="66"/>
+      <c r="F13" s="66"/>
+      <c r="G13" s="67" t="s">
         <v>334</v>
       </c>
     </row>
@@ -6748,16 +6544,16 @@
       <c r="A14" s="5" t="s">
         <v>335</v>
       </c>
-      <c r="B14" s="72" t="s">
+      <c r="B14" s="65" t="s">
         <v>336</v>
       </c>
-      <c r="C14" s="73"/>
-      <c r="D14" s="73" t="s">
+      <c r="C14" s="66"/>
+      <c r="D14" s="66" t="s">
         <v>309</v>
       </c>
-      <c r="E14" s="73"/>
-      <c r="F14" s="73"/>
-      <c r="G14" s="74" t="s">
+      <c r="E14" s="66"/>
+      <c r="F14" s="66"/>
+      <c r="G14" s="67" t="s">
         <v>337</v>
       </c>
     </row>
@@ -6765,16 +6561,16 @@
       <c r="A15" s="5" t="s">
         <v>338</v>
       </c>
-      <c r="B15" s="72" t="s">
+      <c r="B15" s="65" t="s">
         <v>339</v>
       </c>
-      <c r="C15" s="73"/>
-      <c r="D15" s="73" t="s">
+      <c r="C15" s="66"/>
+      <c r="D15" s="66" t="s">
         <v>309</v>
       </c>
-      <c r="E15" s="73"/>
-      <c r="F15" s="73"/>
-      <c r="G15" s="74" t="s">
+      <c r="E15" s="66"/>
+      <c r="F15" s="66"/>
+      <c r="G15" s="67" t="s">
         <v>340</v>
       </c>
     </row>
@@ -6782,18 +6578,18 @@
       <c r="A16" s="5" t="s">
         <v>341</v>
       </c>
-      <c r="B16" s="72" t="s">
+      <c r="B16" s="65" t="s">
         <v>342</v>
       </c>
-      <c r="C16" s="73"/>
-      <c r="D16" s="73"/>
-      <c r="E16" s="73" t="s">
+      <c r="C16" s="66"/>
+      <c r="D16" s="66"/>
+      <c r="E16" s="66" t="s">
         <v>309</v>
       </c>
-      <c r="F16" s="73" t="s">
+      <c r="F16" s="66" t="s">
         <v>309</v>
       </c>
-      <c r="G16" s="74" t="s">
+      <c r="G16" s="67" t="s">
         <v>343</v>
       </c>
     </row>
@@ -6801,16 +6597,16 @@
       <c r="A17" s="5" t="s">
         <v>344</v>
       </c>
-      <c r="B17" s="72" t="s">
+      <c r="B17" s="65" t="s">
         <v>345</v>
       </c>
-      <c r="C17" s="73"/>
-      <c r="D17" s="73"/>
-      <c r="E17" s="73" t="s">
+      <c r="C17" s="66"/>
+      <c r="D17" s="66"/>
+      <c r="E17" s="66" t="s">
         <v>309</v>
       </c>
-      <c r="F17" s="73"/>
-      <c r="G17" s="74" t="s">
+      <c r="F17" s="66"/>
+      <c r="G17" s="67" t="s">
         <v>346</v>
       </c>
     </row>
@@ -6818,16 +6614,16 @@
       <c r="A18" s="5" t="s">
         <v>347</v>
       </c>
-      <c r="B18" s="72" t="s">
+      <c r="B18" s="65" t="s">
         <v>348</v>
       </c>
-      <c r="C18" s="73"/>
-      <c r="D18" s="73"/>
-      <c r="E18" s="73" t="s">
+      <c r="C18" s="66"/>
+      <c r="D18" s="66"/>
+      <c r="E18" s="66" t="s">
         <v>309</v>
       </c>
-      <c r="F18" s="73"/>
-      <c r="G18" s="74" t="s">
+      <c r="F18" s="66"/>
+      <c r="G18" s="67" t="s">
         <v>349</v>
       </c>
     </row>
@@ -6835,72 +6631,72 @@
       <c r="A19" s="5" t="s">
         <v>350</v>
       </c>
-      <c r="B19" s="72" t="s">
+      <c r="B19" s="65" t="s">
         <v>351</v>
       </c>
-      <c r="C19" s="73"/>
-      <c r="D19" s="73"/>
-      <c r="E19" s="73"/>
-      <c r="F19" s="73" t="s">
+      <c r="C19" s="66"/>
+      <c r="D19" s="66"/>
+      <c r="E19" s="66"/>
+      <c r="F19" s="66" t="s">
         <v>309</v>
       </c>
-      <c r="G19" s="74" t="s">
+      <c r="G19" s="67" t="s">
         <v>352</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="75" t="s">
+      <c r="A20" s="68" t="s">
         <v>353</v>
       </c>
-      <c r="B20" s="76" t="s">
+      <c r="B20" s="69" t="s">
         <v>354</v>
       </c>
-      <c r="D20" s="77" t="s">
+      <c r="D20" s="70" t="s">
         <v>309</v>
       </c>
-      <c r="F20" s="77" t="s">
+      <c r="F20" s="70" t="s">
         <v>309</v>
       </c>
-      <c r="G20" s="62" t="s">
+      <c r="G20" s="55" t="s">
         <v>355</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="75" t="s">
+      <c r="A21" s="68" t="s">
         <v>356</v>
       </c>
-      <c r="B21" s="76" t="s">
+      <c r="B21" s="69" t="s">
         <v>357</v>
       </c>
-      <c r="G21" s="62" t="s">
+      <c r="G21" s="55" t="s">
         <v>358</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="75" t="s">
+      <c r="A22" s="68" t="s">
         <v>359</v>
       </c>
-      <c r="B22" s="76" t="s">
+      <c r="B22" s="69" t="s">
         <v>360</v>
       </c>
-      <c r="G22" s="62" t="s">
+      <c r="G22" s="55" t="s">
         <v>361</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="75" t="s">
+      <c r="A23" s="68" t="s">
         <v>362</v>
       </c>
-      <c r="B23" s="76" t="s">
+      <c r="B23" s="69" t="s">
         <v>363</v>
       </c>
-      <c r="G23" s="62" t="s">
+      <c r="G23" s="55" t="s">
         <v>364</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="78" t="s">
+      <c r="A25" s="71" t="s">
         <v>365</v>
       </c>
     </row>
@@ -6920,18 +6716,18 @@
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="79" t="s">
+      <c r="A29" s="72" t="s">
         <v>369</v>
       </c>
-      <c r="B29" s="79" t="s">
+      <c r="B29" s="72" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="80" t="s">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="72" t="s">
         <v>68</v>
       </c>
-      <c r="B30" s="80" t="s">
+      <c r="B30" s="72" t="s">
         <v>371</v>
       </c>
     </row>
@@ -6968,10 +6764,10 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="35" t="s">
         <v>372</v>
       </c>
-      <c r="H1" s="63" t="s">
+      <c r="H1" s="56" t="s">
         <v>373</v>
       </c>
     </row>
@@ -6991,395 +6787,395 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="C6" s="12" t="s">
         <v>219</v>
       </c>
-      <c r="D6" s="15" t="s">
+      <c r="D6" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="E6" s="15" t="s">
+      <c r="E6" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="F6" s="15" t="s">
+      <c r="F6" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="G6" s="15" t="s">
+      <c r="G6" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="H6" s="15" t="s">
+      <c r="H6" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="I6" s="15" t="s">
+      <c r="I6" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="J6" s="15" t="s">
+      <c r="J6" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="K6" s="15" t="s">
+      <c r="K6" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="L6" s="15" t="s">
+      <c r="L6" s="12" t="s">
         <v>220</v>
       </c>
-      <c r="M6" s="15" t="s">
+      <c r="M6" s="12" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="38" t="n">
+      <c r="A7" s="33" t="n">
         <v>1</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>376</v>
       </c>
-      <c r="C7" s="37" t="s">
+      <c r="C7" s="32" t="s">
         <v>377</v>
       </c>
-      <c r="D7" s="38" t="s">
+      <c r="D7" s="33" t="s">
         <v>378</v>
       </c>
-      <c r="E7" s="45" t="n">
+      <c r="E7" s="39" t="n">
         <v>-115</v>
       </c>
-      <c r="F7" s="46" t="n">
+      <c r="F7" s="40" t="n">
         <v>200</v>
       </c>
-      <c r="G7" s="47" t="n">
+      <c r="G7" s="41" t="n">
         <f aca="false">IF(E7&gt;0,F7*E7/100,F7*100/ABS(E7))</f>
         <v>173.913043478261</v>
       </c>
-      <c r="H7" s="47" t="n">
+      <c r="H7" s="41" t="n">
         <f aca="false">F7+G7</f>
         <v>373.913043478261</v>
       </c>
-      <c r="I7" s="51" t="s">
+      <c r="I7" s="45" t="s">
         <v>98</v>
       </c>
-      <c r="J7" s="47" t="n">
+      <c r="J7" s="41" t="n">
         <f aca="false">IF(I7="Win",F7+G7,IF(I7="Push",F7,IF(I7="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K7" s="49" t="n">
+      <c r="K7" s="43" t="n">
         <f aca="false">IF(I7="Pending",0,J7-F7)</f>
         <v>-200</v>
       </c>
-      <c r="L7" s="65" t="n">
+      <c r="L7" s="58" t="n">
         <v>0.56</v>
       </c>
-      <c r="M7" s="69" t="s">
+      <c r="M7" s="62" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="38" t="n">
+      <c r="A8" s="33" t="n">
         <v>2</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>380</v>
       </c>
-      <c r="C8" s="37" t="s">
+      <c r="C8" s="32" t="s">
         <v>381</v>
       </c>
-      <c r="D8" s="38" t="s">
+      <c r="D8" s="33" t="s">
         <v>179</v>
       </c>
-      <c r="E8" s="45" t="n">
+      <c r="E8" s="39" t="n">
         <v>-112</v>
       </c>
-      <c r="F8" s="46" t="n">
+      <c r="F8" s="40" t="n">
         <v>150</v>
       </c>
-      <c r="G8" s="47" t="n">
+      <c r="G8" s="41" t="n">
         <f aca="false">IF(E8&gt;0,F8*E8/100,F8*100/ABS(E8))</f>
         <v>133.928571428571</v>
       </c>
-      <c r="H8" s="47" t="n">
+      <c r="H8" s="41" t="n">
         <f aca="false">F8+G8</f>
         <v>283.928571428571</v>
       </c>
-      <c r="I8" s="51" t="s">
+      <c r="I8" s="45" t="s">
         <v>98</v>
       </c>
-      <c r="J8" s="47" t="n">
+      <c r="J8" s="41" t="n">
         <f aca="false">IF(I8="Win",F8+G8,IF(I8="Push",F8,IF(I8="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K8" s="49" t="n">
+      <c r="K8" s="43" t="n">
         <f aca="false">IF(I8="Pending",0,J8-F8)</f>
         <v>-150</v>
       </c>
-      <c r="L8" s="65" t="n">
+      <c r="L8" s="58" t="n">
         <v>0.56</v>
       </c>
-      <c r="M8" s="69" t="s">
+      <c r="M8" s="62" t="s">
         <v>382</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="38" t="n">
+      <c r="A9" s="33" t="n">
         <v>3</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>383</v>
       </c>
-      <c r="C9" s="37" t="s">
+      <c r="C9" s="32" t="s">
         <v>384</v>
       </c>
-      <c r="D9" s="38" t="s">
+      <c r="D9" s="33" t="s">
         <v>94</v>
       </c>
-      <c r="E9" s="45" t="n">
+      <c r="E9" s="39" t="n">
         <v>-159</v>
       </c>
-      <c r="F9" s="46" t="n">
+      <c r="F9" s="40" t="n">
         <v>150</v>
       </c>
-      <c r="G9" s="47" t="n">
+      <c r="G9" s="41" t="n">
         <f aca="false">IF(E9&gt;0,F9*E9/100,F9*100/ABS(E9))</f>
         <v>94.3396226415094</v>
       </c>
-      <c r="H9" s="47" t="n">
+      <c r="H9" s="41" t="n">
         <f aca="false">F9+G9</f>
         <v>244.339622641509</v>
       </c>
-      <c r="I9" s="48" t="s">
+      <c r="I9" s="42" t="s">
         <v>90</v>
       </c>
-      <c r="J9" s="47" t="n">
+      <c r="J9" s="41" t="n">
         <f aca="false">IF(I9="Win",F9+G9,IF(I9="Push",F9,IF(I9="Loss",0,0)))</f>
         <v>244.339622641509</v>
       </c>
-      <c r="K9" s="49" t="n">
+      <c r="K9" s="43" t="n">
         <f aca="false">IF(I9="Pending",0,J9-F9)</f>
         <v>94.3396226415094</v>
       </c>
-      <c r="L9" s="65" t="n">
+      <c r="L9" s="58" t="n">
         <v>0.65</v>
       </c>
-      <c r="M9" s="69" t="s">
+      <c r="M9" s="62" t="s">
         <v>385</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="38" t="n">
+      <c r="A10" s="33" t="n">
         <v>4</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>386</v>
       </c>
-      <c r="C10" s="37" t="s">
+      <c r="C10" s="32" t="s">
         <v>387</v>
       </c>
-      <c r="D10" s="38" t="s">
+      <c r="D10" s="33" t="s">
         <v>378</v>
       </c>
-      <c r="E10" s="45" t="n">
+      <c r="E10" s="39" t="n">
         <v>-108</v>
       </c>
-      <c r="F10" s="46" t="n">
+      <c r="F10" s="40" t="n">
         <v>150</v>
       </c>
-      <c r="G10" s="47" t="n">
+      <c r="G10" s="41" t="n">
         <f aca="false">IF(E10&gt;0,F10*E10/100,F10*100/ABS(E10))</f>
         <v>138.888888888889</v>
       </c>
-      <c r="H10" s="47" t="n">
+      <c r="H10" s="41" t="n">
         <f aca="false">F10+G10</f>
         <v>288.888888888889</v>
       </c>
-      <c r="I10" s="64" t="s">
+      <c r="I10" s="57" t="s">
         <v>98</v>
       </c>
-      <c r="J10" s="47" t="n">
+      <c r="J10" s="41" t="n">
         <f aca="false">IF(I10="Win",F10+G10,IF(I10="Push",F10,IF(I10="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K10" s="49" t="n">
+      <c r="K10" s="43" t="n">
         <f aca="false">IF(I10="Pending",0,J10-F10)</f>
         <v>-150</v>
       </c>
-      <c r="L10" s="65" t="n">
+      <c r="L10" s="58" t="n">
         <v>0.55</v>
       </c>
-      <c r="M10" s="69" t="s">
+      <c r="M10" s="62" t="s">
         <v>388</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="38" t="n">
+      <c r="A11" s="33" t="n">
         <v>5</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>389</v>
       </c>
-      <c r="C11" s="37" t="s">
+      <c r="C11" s="32" t="s">
         <v>390</v>
       </c>
-      <c r="D11" s="38" t="s">
+      <c r="D11" s="33" t="s">
         <v>94</v>
       </c>
-      <c r="E11" s="45" t="n">
+      <c r="E11" s="39" t="n">
         <v>-120</v>
       </c>
-      <c r="F11" s="46" t="n">
+      <c r="F11" s="40" t="n">
         <v>130</v>
       </c>
-      <c r="G11" s="47" t="n">
+      <c r="G11" s="41" t="n">
         <f aca="false">IF(E11&gt;0,F11*E11/100,F11*100/ABS(E11))</f>
         <v>108.333333333333</v>
       </c>
-      <c r="H11" s="47" t="n">
+      <c r="H11" s="41" t="n">
         <f aca="false">F11+G11</f>
         <v>238.333333333333</v>
       </c>
-      <c r="I11" s="64" t="s">
+      <c r="I11" s="57" t="s">
         <v>90</v>
       </c>
-      <c r="J11" s="47" t="n">
+      <c r="J11" s="41" t="n">
         <f aca="false">IF(I11="Win",F11+G11,IF(I11="Push",F11,IF(I11="Loss",0,0)))</f>
         <v>238.333333333333</v>
       </c>
-      <c r="K11" s="49" t="n">
+      <c r="K11" s="43" t="n">
         <f aca="false">IF(I11="Pending",0,J11-F11)</f>
         <v>108.333333333333</v>
       </c>
-      <c r="L11" s="65" t="n">
+      <c r="L11" s="58" t="n">
         <v>0.6</v>
       </c>
-      <c r="M11" s="69" t="s">
+      <c r="M11" s="62" t="s">
         <v>391</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="38" t="n">
+      <c r="A12" s="33" t="n">
         <v>6</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>392</v>
       </c>
-      <c r="C12" s="37" t="s">
+      <c r="C12" s="32" t="s">
         <v>393</v>
       </c>
-      <c r="D12" s="38" t="s">
+      <c r="D12" s="33" t="s">
         <v>94</v>
       </c>
-      <c r="E12" s="45" t="n">
+      <c r="E12" s="39" t="n">
         <v>-121</v>
       </c>
-      <c r="F12" s="46" t="n">
+      <c r="F12" s="40" t="n">
         <v>120</v>
       </c>
-      <c r="G12" s="47" t="n">
+      <c r="G12" s="41" t="n">
         <f aca="false">IF(E12&gt;0,F12*E12/100,F12*100/ABS(E12))</f>
         <v>99.1735537190083</v>
       </c>
-      <c r="H12" s="47" t="n">
+      <c r="H12" s="41" t="n">
         <f aca="false">F12+G12</f>
         <v>219.173553719008</v>
       </c>
-      <c r="I12" s="64" t="s">
+      <c r="I12" s="57" t="s">
         <v>90</v>
       </c>
-      <c r="J12" s="47" t="n">
+      <c r="J12" s="41" t="n">
         <f aca="false">IF(I12="Win",F12+G12,IF(I12="Push",F12,IF(I12="Loss",0,0)))</f>
         <v>219.173553719008</v>
       </c>
-      <c r="K12" s="49" t="n">
+      <c r="K12" s="43" t="n">
         <f aca="false">IF(I12="Pending",0,J12-F12)</f>
         <v>99.1735537190083</v>
       </c>
-      <c r="L12" s="65" t="n">
+      <c r="L12" s="58" t="n">
         <v>0.58</v>
       </c>
-      <c r="M12" s="69" t="s">
+      <c r="M12" s="62" t="s">
         <v>394</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="38" t="n">
+      <c r="A13" s="33" t="n">
         <v>7</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>395</v>
       </c>
-      <c r="C13" s="37" t="s">
+      <c r="C13" s="32" t="s">
         <v>396</v>
       </c>
-      <c r="D13" s="38" t="s">
+      <c r="D13" s="33" t="s">
         <v>117</v>
       </c>
-      <c r="E13" s="45" t="n">
+      <c r="E13" s="39" t="n">
         <v>971</v>
       </c>
-      <c r="F13" s="46" t="n">
+      <c r="F13" s="40" t="n">
         <v>100</v>
       </c>
-      <c r="G13" s="47" t="n">
+      <c r="G13" s="41" t="n">
         <f aca="false">IF(E13&gt;0,F13*E13/100,F13*100/ABS(E13))</f>
         <v>971</v>
       </c>
-      <c r="H13" s="47" t="n">
+      <c r="H13" s="41" t="n">
         <f aca="false">F13+G13</f>
         <v>1071</v>
       </c>
-      <c r="I13" s="51" t="s">
+      <c r="I13" s="45" t="s">
         <v>98</v>
       </c>
-      <c r="J13" s="47" t="n">
+      <c r="J13" s="41" t="n">
         <f aca="false">IF(I13="Win",F13+G13,IF(I13="Push",F13,IF(I13="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K13" s="49" t="n">
+      <c r="K13" s="43" t="n">
         <f aca="false">IF(I13="Pending",0,J13-F13)</f>
         <v>-100</v>
       </c>
-      <c r="L13" s="65" t="n">
+      <c r="L13" s="58" t="n">
         <v>0.12</v>
       </c>
-      <c r="M13" s="69" t="s">
+      <c r="M13" s="62" t="s">
         <v>397</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="70"/>
-      <c r="B14" s="71" t="s">
+      <c r="A14" s="63"/>
+      <c r="B14" s="64" t="s">
         <v>39</v>
       </c>
-      <c r="C14" s="70"/>
-      <c r="D14" s="70"/>
-      <c r="E14" s="70"/>
-      <c r="F14" s="54" t="n">
+      <c r="C14" s="63"/>
+      <c r="D14" s="63"/>
+      <c r="E14" s="63"/>
+      <c r="F14" s="48" t="n">
         <f aca="false">SUM(F7:F13)</f>
         <v>1000</v>
       </c>
-      <c r="G14" s="55" t="n">
+      <c r="G14" s="49" t="n">
         <f aca="false">SUM(G7:G13)</f>
         <v>1719.57701348957</v>
       </c>
-      <c r="H14" s="55" t="n">
+      <c r="H14" s="49" t="n">
         <f aca="false">SUM(H7:H13)</f>
         <v>2719.57701348957</v>
       </c>
-      <c r="I14" s="70"/>
-      <c r="J14" s="55" t="n">
+      <c r="I14" s="63"/>
+      <c r="J14" s="49" t="n">
         <f aca="false">SUM(J7:J13)</f>
         <v>701.846509693851</v>
       </c>
-      <c r="K14" s="56" t="n">
+      <c r="K14" s="50" t="n">
         <f aca="false">SUM(K7:K13)</f>
         <v>-298.153490306149</v>
       </c>
-      <c r="L14" s="66" t="n">
+      <c r="L14" s="59" t="n">
         <f aca="false">SUM(L7:L13)</f>
         <v>3.62</v>
       </c>
-      <c r="M14" s="70"/>
+      <c r="M14" s="63"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="4" t="s">
@@ -7390,7 +7186,7 @@
       <c r="B17" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="C17" s="57" t="n">
+      <c r="C17" s="51" t="n">
         <f aca="false">COUNTIF(I7:I13,"Win")</f>
         <v>3</v>
       </c>
@@ -7399,7 +7195,7 @@
       <c r="B18" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="C18" s="57" t="n">
+      <c r="C18" s="51" t="n">
         <f aca="false">COUNTIF(I7:I13,"Loss")</f>
         <v>4</v>
       </c>
@@ -7408,7 +7204,7 @@
       <c r="B19" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="C19" s="57" t="n">
+      <c r="C19" s="51" t="n">
         <f aca="false">COUNTIF(I7:I13,"Push")</f>
         <v>0</v>
       </c>
@@ -7417,7 +7213,7 @@
       <c r="B20" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="C20" s="57" t="n">
+      <c r="C20" s="51" t="n">
         <f aca="false">COUNTIF(I7:I13,"Pending")</f>
         <v>0</v>
       </c>
@@ -7426,7 +7222,7 @@
       <c r="B21" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="C21" s="58" t="n">
+      <c r="C21" s="52" t="n">
         <f aca="false">IF(COUNTIF(I7:I13,"Win")+COUNTIF(I7:I13,"Loss")=0,"—",COUNTIF(I7:I13,"Win")/(COUNTIF(I7:I13,"Win")+COUNTIF(I7:I13,"Loss")))</f>
         <v>0.428571428571429</v>
       </c>
@@ -7435,7 +7231,7 @@
       <c r="B22" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="C22" s="59" t="n">
+      <c r="C22" s="34" t="n">
         <f aca="false">SUM(F7:F13)</f>
         <v>1000</v>
       </c>
@@ -7444,7 +7240,7 @@
       <c r="B23" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="C23" s="47" t="n">
+      <c r="C23" s="41" t="n">
         <f aca="false">SUM(J7:J13)</f>
         <v>701.846509693851</v>
       </c>
@@ -7453,7 +7249,7 @@
       <c r="B24" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="C24" s="49" t="n">
+      <c r="C24" s="43" t="n">
         <f aca="false">SUM(K7:K13)</f>
         <v>-298.153490306149</v>
       </c>
@@ -7462,7 +7258,7 @@
       <c r="B25" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="C25" s="58" t="n">
+      <c r="C25" s="52" t="n">
         <f aca="false">IF(SUM(F7:F13)=0,"—",SUM(K7:K13)/SUM(F7:F13))</f>
         <v>-0.298153490306149</v>
       </c>
@@ -7471,7 +7267,7 @@
       <c r="B26" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="C26" s="47" t="n">
+      <c r="C26" s="41" t="n">
         <f aca="false">SUM(H7:H13)</f>
         <v>2719.57701348957</v>
       </c>
@@ -7480,7 +7276,7 @@
       <c r="B27" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="C27" s="67" t="n">
+      <c r="C27" s="60" t="n">
         <f aca="false">SUM(L7:L13)</f>
         <v>3.62</v>
       </c>
@@ -7489,13 +7285,13 @@
       <c r="B28" s="5" t="s">
         <v>246</v>
       </c>
-      <c r="C28" s="49" t="n">
+      <c r="C28" s="43" t="n">
         <f aca="false">SUMPRODUCT(L7:L13,G7:G13)-SUMPRODUCT(1-L7:L13,F7:F13)</f>
         <v>84.7416091107209</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="62" t="s">
+      <c r="A30" s="55" t="s">
         <v>398</v>
       </c>
     </row>
@@ -7554,10 +7350,10 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="35" t="s">
         <v>399</v>
       </c>
-      <c r="H1" s="63" t="s">
+      <c r="H1" s="56" t="s">
         <v>400</v>
       </c>
     </row>
@@ -7577,375 +7373,375 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="C6" s="12" t="s">
         <v>200</v>
       </c>
-      <c r="D6" s="15" t="s">
+      <c r="D6" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="E6" s="15" t="s">
+      <c r="E6" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="F6" s="15" t="s">
+      <c r="F6" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="G6" s="15" t="s">
+      <c r="G6" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="H6" s="15" t="s">
+      <c r="H6" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="I6" s="15" t="s">
+      <c r="I6" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="J6" s="15" t="s">
+      <c r="J6" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="K6" s="15" t="s">
+      <c r="K6" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="L6" s="15" t="s">
+      <c r="L6" s="12" t="s">
         <v>220</v>
       </c>
-      <c r="M6" s="15" t="s">
+      <c r="M6" s="12" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="38" t="n">
+      <c r="A7" s="33" t="n">
         <v>1</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>403</v>
       </c>
-      <c r="C7" s="37" t="s">
+      <c r="C7" s="32" t="s">
         <v>287</v>
       </c>
-      <c r="D7" s="38" t="s">
+      <c r="D7" s="33" t="s">
         <v>190</v>
       </c>
-      <c r="E7" s="45" t="n">
+      <c r="E7" s="39" t="n">
         <v>450</v>
       </c>
-      <c r="F7" s="46" t="n">
+      <c r="F7" s="40" t="n">
         <v>200</v>
       </c>
-      <c r="G7" s="47" t="n">
+      <c r="G7" s="41" t="n">
         <f aca="false">IF(E7&gt;0,F7*E7/100,F7*100/ABS(E7))</f>
         <v>900</v>
       </c>
-      <c r="H7" s="47" t="n">
+      <c r="H7" s="41" t="n">
         <f aca="false">F7+G7</f>
         <v>1100</v>
       </c>
-      <c r="I7" s="64" t="s">
+      <c r="I7" s="57" t="s">
         <v>123</v>
       </c>
-      <c r="J7" s="47" t="n">
+      <c r="J7" s="41" t="n">
         <f aca="false">IF(I7="Win",F7+G7,IF(I7="Push",F7,IF(I7="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K7" s="49" t="n">
+      <c r="K7" s="43" t="n">
         <f aca="false">IF(I7="Pending",0,J7-F7)</f>
         <v>0</v>
       </c>
-      <c r="L7" s="81" t="n">
+      <c r="L7" s="73" t="n">
         <v>0.18</v>
       </c>
-      <c r="M7" s="69" t="s">
+      <c r="M7" s="62" t="s">
         <v>404</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="38" t="n">
+      <c r="A8" s="33" t="n">
         <v>2</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>405</v>
       </c>
-      <c r="C8" s="37" t="s">
+      <c r="C8" s="32" t="s">
         <v>287</v>
       </c>
-      <c r="D8" s="38" t="s">
+      <c r="D8" s="33" t="s">
         <v>190</v>
       </c>
-      <c r="E8" s="45" t="n">
+      <c r="E8" s="39" t="n">
         <v>1600</v>
       </c>
-      <c r="F8" s="46" t="n">
+      <c r="F8" s="40" t="n">
         <v>100</v>
       </c>
-      <c r="G8" s="47" t="n">
+      <c r="G8" s="41" t="n">
         <f aca="false">IF(E8&gt;0,F8*E8/100,F8*100/ABS(E8))</f>
         <v>1600</v>
       </c>
-      <c r="H8" s="47" t="n">
+      <c r="H8" s="41" t="n">
         <f aca="false">F8+G8</f>
         <v>1700</v>
       </c>
-      <c r="I8" s="64" t="s">
+      <c r="I8" s="57" t="s">
         <v>123</v>
       </c>
-      <c r="J8" s="47" t="n">
+      <c r="J8" s="41" t="n">
         <f aca="false">IF(I8="Win",F8+G8,IF(I8="Push",F8,IF(I8="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K8" s="49" t="n">
+      <c r="K8" s="43" t="n">
         <f aca="false">IF(I8="Pending",0,J8-F8)</f>
         <v>0</v>
       </c>
-      <c r="L8" s="81" t="n">
+      <c r="L8" s="73" t="n">
         <v>0.07</v>
       </c>
-      <c r="M8" s="69" t="s">
+      <c r="M8" s="62" t="s">
         <v>406</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="38" t="n">
+      <c r="A9" s="33" t="n">
         <v>3</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>407</v>
       </c>
-      <c r="C9" s="37" t="s">
+      <c r="C9" s="32" t="s">
         <v>287</v>
       </c>
-      <c r="D9" s="38" t="s">
+      <c r="D9" s="33" t="s">
         <v>190</v>
       </c>
-      <c r="E9" s="45" t="n">
+      <c r="E9" s="39" t="n">
         <v>1600</v>
       </c>
-      <c r="F9" s="46" t="n">
+      <c r="F9" s="40" t="n">
         <v>100</v>
       </c>
-      <c r="G9" s="47" t="n">
+      <c r="G9" s="41" t="n">
         <f aca="false">IF(E9&gt;0,F9*E9/100,F9*100/ABS(E9))</f>
         <v>1600</v>
       </c>
-      <c r="H9" s="47" t="n">
+      <c r="H9" s="41" t="n">
         <f aca="false">F9+G9</f>
         <v>1700</v>
       </c>
-      <c r="I9" s="64" t="s">
+      <c r="I9" s="57" t="s">
         <v>123</v>
       </c>
-      <c r="J9" s="47" t="n">
+      <c r="J9" s="41" t="n">
         <f aca="false">IF(I9="Win",F9+G9,IF(I9="Push",F9,IF(I9="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K9" s="49" t="n">
+      <c r="K9" s="43" t="n">
         <f aca="false">IF(I9="Pending",0,J9-F9)</f>
         <v>0</v>
       </c>
-      <c r="L9" s="81" t="n">
+      <c r="L9" s="73" t="n">
         <v>0.07</v>
       </c>
-      <c r="M9" s="69" t="s">
+      <c r="M9" s="62" t="s">
         <v>408</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="38" t="n">
+      <c r="A10" s="33" t="n">
         <v>4</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>409</v>
       </c>
-      <c r="C10" s="37" t="s">
+      <c r="C10" s="32" t="s">
         <v>287</v>
       </c>
-      <c r="D10" s="38" t="s">
+      <c r="D10" s="33" t="s">
         <v>190</v>
       </c>
-      <c r="E10" s="45" t="n">
+      <c r="E10" s="39" t="n">
         <v>2000</v>
       </c>
-      <c r="F10" s="46" t="n">
+      <c r="F10" s="40" t="n">
         <v>80</v>
       </c>
-      <c r="G10" s="47" t="n">
+      <c r="G10" s="41" t="n">
         <f aca="false">IF(E10&gt;0,F10*E10/100,F10*100/ABS(E10))</f>
         <v>1600</v>
       </c>
-      <c r="H10" s="47" t="n">
+      <c r="H10" s="41" t="n">
         <f aca="false">F10+G10</f>
         <v>1680</v>
       </c>
-      <c r="I10" s="64" t="s">
+      <c r="I10" s="57" t="s">
         <v>123</v>
       </c>
-      <c r="J10" s="47" t="n">
+      <c r="J10" s="41" t="n">
         <f aca="false">IF(I10="Win",F10+G10,IF(I10="Push",F10,IF(I10="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K10" s="49" t="n">
+      <c r="K10" s="43" t="n">
         <f aca="false">IF(I10="Pending",0,J10-F10)</f>
         <v>0</v>
       </c>
-      <c r="L10" s="81" t="n">
+      <c r="L10" s="73" t="n">
         <v>0.055</v>
       </c>
-      <c r="M10" s="69" t="s">
+      <c r="M10" s="62" t="s">
         <v>410</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="38" t="n">
+      <c r="A11" s="33" t="n">
         <v>5</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>411</v>
       </c>
-      <c r="C11" s="37" t="s">
+      <c r="C11" s="32" t="s">
         <v>287</v>
       </c>
-      <c r="D11" s="38" t="s">
+      <c r="D11" s="33" t="s">
         <v>190</v>
       </c>
-      <c r="E11" s="45" t="n">
+      <c r="E11" s="39" t="n">
         <v>2800</v>
       </c>
-      <c r="F11" s="46" t="n">
+      <c r="F11" s="40" t="n">
         <v>70</v>
       </c>
-      <c r="G11" s="47" t="n">
+      <c r="G11" s="41" t="n">
         <f aca="false">IF(E11&gt;0,F11*E11/100,F11*100/ABS(E11))</f>
         <v>1960</v>
       </c>
-      <c r="H11" s="47" t="n">
+      <c r="H11" s="41" t="n">
         <f aca="false">F11+G11</f>
         <v>2030</v>
       </c>
-      <c r="I11" s="64" t="s">
+      <c r="I11" s="57" t="s">
         <v>123</v>
       </c>
-      <c r="J11" s="47" t="n">
+      <c r="J11" s="41" t="n">
         <f aca="false">IF(I11="Win",F11+G11,IF(I11="Push",F11,IF(I11="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K11" s="49" t="n">
+      <c r="K11" s="43" t="n">
         <f aca="false">IF(I11="Pending",0,J11-F11)</f>
         <v>0</v>
       </c>
-      <c r="L11" s="81" t="n">
+      <c r="L11" s="73" t="n">
         <v>0.045</v>
       </c>
-      <c r="M11" s="69" t="s">
+      <c r="M11" s="62" t="s">
         <v>412</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="38" t="n">
+      <c r="A12" s="33" t="n">
         <v>6</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>413</v>
       </c>
-      <c r="C12" s="37" t="s">
+      <c r="C12" s="32" t="s">
         <v>287</v>
       </c>
-      <c r="D12" s="38" t="s">
+      <c r="D12" s="33" t="s">
         <v>190</v>
       </c>
-      <c r="E12" s="45" t="n">
+      <c r="E12" s="39" t="n">
         <v>5000</v>
       </c>
-      <c r="F12" s="46" t="n">
+      <c r="F12" s="40" t="n">
         <v>50</v>
       </c>
-      <c r="G12" s="47" t="n">
+      <c r="G12" s="41" t="n">
         <f aca="false">IF(E12&gt;0,F12*E12/100,F12*100/ABS(E12))</f>
         <v>2500</v>
       </c>
-      <c r="H12" s="47" t="n">
+      <c r="H12" s="41" t="n">
         <f aca="false">F12+G12</f>
         <v>2550</v>
       </c>
-      <c r="I12" s="64" t="s">
+      <c r="I12" s="57" t="s">
         <v>123</v>
       </c>
-      <c r="J12" s="47" t="n">
+      <c r="J12" s="41" t="n">
         <f aca="false">IF(I12="Win",F12+G12,IF(I12="Push",F12,IF(I12="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K12" s="49" t="n">
+      <c r="K12" s="43" t="n">
         <f aca="false">IF(I12="Pending",0,J12-F12)</f>
         <v>0</v>
       </c>
-      <c r="L12" s="81" t="n">
+      <c r="L12" s="73" t="n">
         <v>0.025</v>
       </c>
-      <c r="M12" s="69" t="s">
+      <c r="M12" s="62" t="s">
         <v>414</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="82" t="n">
+      <c r="A13" s="74" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="24" t="s">
+      <c r="B13" s="21" t="s">
         <v>415</v>
       </c>
-      <c r="C13" s="82" t="s">
+      <c r="C13" s="74" t="s">
         <v>416</v>
       </c>
-      <c r="D13" s="82" t="s">
+      <c r="D13" s="74" t="s">
         <v>63</v>
       </c>
-      <c r="E13" s="82"/>
-      <c r="F13" s="82"/>
-      <c r="G13" s="82"/>
-      <c r="H13" s="82"/>
-      <c r="I13" s="82"/>
-      <c r="J13" s="82"/>
-      <c r="K13" s="82"/>
-      <c r="L13" s="82"/>
-      <c r="M13" s="82" t="s">
+      <c r="E13" s="74"/>
+      <c r="F13" s="74"/>
+      <c r="G13" s="74"/>
+      <c r="H13" s="74"/>
+      <c r="I13" s="74"/>
+      <c r="J13" s="74"/>
+      <c r="K13" s="74"/>
+      <c r="L13" s="74"/>
+      <c r="M13" s="74" t="s">
         <v>417</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="70"/>
-      <c r="B14" s="71" t="s">
+      <c r="A14" s="63"/>
+      <c r="B14" s="64" t="s">
         <v>418</v>
       </c>
-      <c r="C14" s="70"/>
-      <c r="D14" s="70"/>
-      <c r="E14" s="70"/>
-      <c r="F14" s="54" t="n">
+      <c r="C14" s="63"/>
+      <c r="D14" s="63"/>
+      <c r="E14" s="63"/>
+      <c r="F14" s="48" t="n">
         <f aca="false">SUM(F7:F13)</f>
         <v>600</v>
       </c>
-      <c r="G14" s="55" t="n">
+      <c r="G14" s="49" t="n">
         <f aca="false">SUM(G7:G12)</f>
         <v>10160</v>
       </c>
-      <c r="H14" s="55" t="n">
+      <c r="H14" s="49" t="n">
         <f aca="false">SUM(H7:H12)</f>
         <v>10760</v>
       </c>
-      <c r="I14" s="70"/>
-      <c r="J14" s="55" t="n">
+      <c r="I14" s="63"/>
+      <c r="J14" s="49" t="n">
         <f aca="false">SUM(J7:J12)</f>
         <v>0</v>
       </c>
-      <c r="K14" s="56" t="n">
+      <c r="K14" s="50" t="n">
         <f aca="false">SUM(K7:K12)</f>
         <v>0</v>
       </c>
-      <c r="L14" s="83" t="n">
+      <c r="L14" s="75" t="n">
         <f aca="false">SUM(L7:L12)</f>
         <v>0.445</v>
       </c>
-      <c r="M14" s="70"/>
+      <c r="M14" s="63"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="4" t="s">
@@ -7956,7 +7752,7 @@
       <c r="B17" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="C17" s="57" t="n">
+      <c r="C17" s="51" t="n">
         <f aca="false">COUNTIF(I7:I12,"Win")</f>
         <v>0</v>
       </c>
@@ -7965,7 +7761,7 @@
       <c r="B18" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="C18" s="57" t="n">
+      <c r="C18" s="51" t="n">
         <f aca="false">COUNTIF(I7:I12,"Loss")</f>
         <v>0</v>
       </c>
@@ -7974,7 +7770,7 @@
       <c r="B19" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="C19" s="57" t="n">
+      <c r="C19" s="51" t="n">
         <f aca="false">COUNTIF(I7:I12,"Pending")</f>
         <v>6</v>
       </c>
@@ -7983,7 +7779,7 @@
       <c r="B20" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="C20" s="58" t="str">
+      <c r="C20" s="52" t="str">
         <f aca="false">IF(COUNTIF(I7:I12,"Win")+COUNTIF(I7:I12,"Loss")=0,"—",COUNTIF(I7:I12,"Win")/(COUNTIF(I7:I12,"Win")+COUNTIF(I7:I12,"Loss")))</f>
         <v>—</v>
       </c>
@@ -7992,7 +7788,7 @@
       <c r="B21" s="5" t="s">
         <v>419</v>
       </c>
-      <c r="C21" s="59" t="n">
+      <c r="C21" s="34" t="n">
         <f aca="false">SUM(F7:F12)</f>
         <v>600</v>
       </c>
@@ -8001,7 +7797,7 @@
       <c r="B22" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="C22" s="47" t="n">
+      <c r="C22" s="41" t="n">
         <f aca="false">SUM(J7:J12)</f>
         <v>0</v>
       </c>
@@ -8010,7 +7806,7 @@
       <c r="B23" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="C23" s="49" t="n">
+      <c r="C23" s="43" t="n">
         <f aca="false">SUM(K7:K12)</f>
         <v>0</v>
       </c>
@@ -8019,7 +7815,7 @@
       <c r="B24" s="5" t="s">
         <v>420</v>
       </c>
-      <c r="C24" s="58" t="n">
+      <c r="C24" s="52" t="n">
         <f aca="false">SUM(L7:L12)</f>
         <v>0.445</v>
       </c>
@@ -8081,10 +7877,10 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="35" t="s">
         <v>421</v>
       </c>
-      <c r="H1" s="84" t="s">
+      <c r="H1" s="76" t="s">
         <v>422</v>
       </c>
     </row>
@@ -8104,358 +7900,358 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="C6" s="12" t="s">
         <v>200</v>
       </c>
-      <c r="D6" s="15" t="s">
+      <c r="D6" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="E6" s="15" t="s">
+      <c r="E6" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="F6" s="15" t="s">
+      <c r="F6" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="G6" s="15" t="s">
+      <c r="G6" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="H6" s="15" t="s">
+      <c r="H6" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="I6" s="15" t="s">
+      <c r="I6" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="J6" s="15" t="s">
+      <c r="J6" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="K6" s="15" t="s">
+      <c r="K6" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="L6" s="15" t="s">
+      <c r="L6" s="12" t="s">
         <v>220</v>
       </c>
-      <c r="M6" s="15" t="s">
+      <c r="M6" s="12" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="38" t="n">
+      <c r="A7" s="33" t="n">
         <v>1</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>425</v>
       </c>
-      <c r="C7" s="37" t="s">
+      <c r="C7" s="32" t="s">
         <v>287</v>
       </c>
-      <c r="D7" s="38" t="s">
+      <c r="D7" s="33" t="s">
         <v>190</v>
       </c>
-      <c r="E7" s="45" t="n">
+      <c r="E7" s="39" t="n">
         <v>310</v>
       </c>
-      <c r="F7" s="46" t="n">
+      <c r="F7" s="40" t="n">
         <v>220</v>
       </c>
-      <c r="G7" s="47" t="n">
+      <c r="G7" s="41" t="n">
         <f aca="false">IF(E7&gt;0,F7*E7/100,F7*100/ABS(E7))</f>
         <v>682</v>
       </c>
-      <c r="H7" s="47" t="n">
+      <c r="H7" s="41" t="n">
         <f aca="false">F7+G7</f>
         <v>902</v>
       </c>
-      <c r="I7" s="64" t="s">
+      <c r="I7" s="57" t="s">
         <v>98</v>
       </c>
-      <c r="J7" s="47" t="n">
+      <c r="J7" s="41" t="n">
         <f aca="false">IF(I7="Win",F7+G7,IF(I7="Push",F7,IF(I7="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K7" s="49" t="n">
+      <c r="K7" s="43" t="n">
         <f aca="false">IF(I7="Pending",0,J7-F7)</f>
         <v>-220</v>
       </c>
-      <c r="L7" s="81" t="n">
+      <c r="L7" s="73" t="n">
         <v>0.27</v>
       </c>
-      <c r="M7" s="69" t="s">
+      <c r="M7" s="62" t="s">
         <v>426</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="38" t="n">
+      <c r="A8" s="33" t="n">
         <v>2</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>427</v>
       </c>
-      <c r="C8" s="37" t="s">
+      <c r="C8" s="32" t="s">
         <v>287</v>
       </c>
-      <c r="D8" s="38" t="s">
+      <c r="D8" s="33" t="s">
         <v>190</v>
       </c>
-      <c r="E8" s="45" t="n">
+      <c r="E8" s="39" t="n">
         <v>425</v>
       </c>
-      <c r="F8" s="46" t="n">
+      <c r="F8" s="40" t="n">
         <v>130</v>
       </c>
-      <c r="G8" s="47" t="n">
+      <c r="G8" s="41" t="n">
         <f aca="false">IF(E8&gt;0,F8*E8/100,F8*100/ABS(E8))</f>
         <v>552.5</v>
       </c>
-      <c r="H8" s="47" t="n">
+      <c r="H8" s="41" t="n">
         <f aca="false">F8+G8</f>
         <v>682.5</v>
       </c>
-      <c r="I8" s="64" t="s">
+      <c r="I8" s="57" t="s">
         <v>98</v>
       </c>
-      <c r="J8" s="47" t="n">
+      <c r="J8" s="41" t="n">
         <f aca="false">IF(I8="Win",F8+G8,IF(I8="Push",F8,IF(I8="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K8" s="49" t="n">
+      <c r="K8" s="43" t="n">
         <f aca="false">IF(I8="Pending",0,J8-F8)</f>
         <v>-130</v>
       </c>
-      <c r="L8" s="81" t="n">
+      <c r="L8" s="73" t="n">
         <v>0.18</v>
       </c>
-      <c r="M8" s="69" t="s">
+      <c r="M8" s="62" t="s">
         <v>428</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="38" t="n">
+      <c r="A9" s="33" t="n">
         <v>3</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>429</v>
       </c>
-      <c r="C9" s="37" t="s">
+      <c r="C9" s="32" t="s">
         <v>430</v>
       </c>
-      <c r="D9" s="38" t="s">
+      <c r="D9" s="33" t="s">
         <v>94</v>
       </c>
-      <c r="E9" s="45" t="n">
+      <c r="E9" s="39" t="n">
         <v>-110</v>
       </c>
-      <c r="F9" s="46" t="n">
+      <c r="F9" s="40" t="n">
         <v>180</v>
       </c>
-      <c r="G9" s="47" t="n">
+      <c r="G9" s="41" t="n">
         <f aca="false">IF(E9&gt;0,F9*E9/100,F9*100/ABS(E9))</f>
         <v>163.636363636364</v>
       </c>
-      <c r="H9" s="47" t="n">
+      <c r="H9" s="41" t="n">
         <f aca="false">F9+G9</f>
         <v>343.636363636364</v>
       </c>
-      <c r="I9" s="64" t="s">
+      <c r="I9" s="57" t="s">
         <v>98</v>
       </c>
-      <c r="J9" s="47" t="n">
+      <c r="J9" s="41" t="n">
         <f aca="false">IF(I9="Win",F9+G9,IF(I9="Push",F9,IF(I9="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K9" s="49" t="n">
+      <c r="K9" s="43" t="n">
         <f aca="false">IF(I9="Pending",0,J9-F9)</f>
         <v>-180</v>
       </c>
-      <c r="L9" s="81" t="n">
+      <c r="L9" s="73" t="n">
         <v>0.6</v>
       </c>
-      <c r="M9" s="69" t="s">
+      <c r="M9" s="62" t="s">
         <v>431</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="38" t="n">
+      <c r="A10" s="33" t="n">
         <v>4</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>432</v>
       </c>
-      <c r="C10" s="37" t="s">
+      <c r="C10" s="32" t="s">
         <v>433</v>
       </c>
-      <c r="D10" s="38" t="s">
+      <c r="D10" s="33" t="s">
         <v>94</v>
       </c>
-      <c r="E10" s="45" t="n">
+      <c r="E10" s="39" t="n">
         <v>-110</v>
       </c>
-      <c r="F10" s="46" t="n">
+      <c r="F10" s="40" t="n">
         <v>150</v>
       </c>
-      <c r="G10" s="47" t="n">
+      <c r="G10" s="41" t="n">
         <f aca="false">IF(E10&gt;0,F10*E10/100,F10*100/ABS(E10))</f>
         <v>136.363636363636</v>
       </c>
-      <c r="H10" s="47" t="n">
+      <c r="H10" s="41" t="n">
         <f aca="false">F10+G10</f>
         <v>286.363636363636</v>
       </c>
-      <c r="I10" s="64" t="s">
+      <c r="I10" s="57" t="s">
         <v>90</v>
       </c>
-      <c r="J10" s="47" t="n">
+      <c r="J10" s="41" t="n">
         <f aca="false">IF(I10="Win",F10+G10,IF(I10="Push",F10,IF(I10="Loss",0,0)))</f>
         <v>286.363636363636</v>
       </c>
-      <c r="K10" s="49" t="n">
+      <c r="K10" s="43" t="n">
         <f aca="false">IF(I10="Pending",0,J10-F10)</f>
         <v>136.363636363636</v>
       </c>
-      <c r="L10" s="81" t="n">
+      <c r="L10" s="73" t="n">
         <v>0.58</v>
       </c>
-      <c r="M10" s="69" t="s">
+      <c r="M10" s="62" t="s">
         <v>434</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="38" t="n">
+      <c r="A11" s="33" t="n">
         <v>5</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>435</v>
       </c>
-      <c r="C11" s="37" t="s">
+      <c r="C11" s="32" t="s">
         <v>430</v>
       </c>
-      <c r="D11" s="38" t="s">
+      <c r="D11" s="33" t="s">
         <v>94</v>
       </c>
-      <c r="E11" s="45" t="n">
+      <c r="E11" s="39" t="n">
         <v>-110</v>
       </c>
-      <c r="F11" s="46" t="n">
+      <c r="F11" s="40" t="n">
         <v>120</v>
       </c>
-      <c r="G11" s="47" t="n">
+      <c r="G11" s="41" t="n">
         <f aca="false">IF(E11&gt;0,F11*E11/100,F11*100/ABS(E11))</f>
         <v>109.090909090909</v>
       </c>
-      <c r="H11" s="47" t="n">
+      <c r="H11" s="41" t="n">
         <f aca="false">F11+G11</f>
         <v>229.090909090909</v>
       </c>
-      <c r="I11" s="64" t="s">
+      <c r="I11" s="57" t="s">
         <v>98</v>
       </c>
-      <c r="J11" s="47" t="n">
+      <c r="J11" s="41" t="n">
         <f aca="false">IF(I11="Win",F11+G11,IF(I11="Push",F11,IF(I11="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K11" s="49" t="n">
+      <c r="K11" s="43" t="n">
         <f aca="false">IF(I11="Pending",0,J11-F11)</f>
         <v>-120</v>
       </c>
-      <c r="L11" s="81" t="n">
+      <c r="L11" s="73" t="n">
         <v>0.57</v>
       </c>
-      <c r="M11" s="69" t="s">
+      <c r="M11" s="62" t="s">
         <v>436</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="38" t="n">
+      <c r="A12" s="33" t="n">
         <v>6</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>437</v>
       </c>
-      <c r="C12" s="37" t="s">
+      <c r="C12" s="32" t="s">
         <v>438</v>
       </c>
-      <c r="D12" s="38" t="s">
+      <c r="D12" s="33" t="s">
         <v>94</v>
       </c>
-      <c r="E12" s="45" t="n">
+      <c r="E12" s="39" t="n">
         <v>-110</v>
       </c>
-      <c r="F12" s="46" t="n">
+      <c r="F12" s="40" t="n">
         <v>125</v>
       </c>
-      <c r="G12" s="47" t="n">
+      <c r="G12" s="41" t="n">
         <f aca="false">IF(E12&gt;0,F12*E12/100,F12*100/ABS(E12))</f>
         <v>113.636363636364</v>
       </c>
-      <c r="H12" s="47" t="n">
+      <c r="H12" s="41" t="n">
         <f aca="false">F12+G12</f>
         <v>238.636363636364</v>
       </c>
-      <c r="I12" s="64" t="s">
+      <c r="I12" s="57" t="s">
         <v>90</v>
       </c>
-      <c r="J12" s="47" t="n">
+      <c r="J12" s="41" t="n">
         <f aca="false">IF(I12="Win",F12+G12,IF(I12="Push",F12,IF(I12="Loss",0,0)))</f>
         <v>238.636363636364</v>
       </c>
-      <c r="K12" s="49" t="n">
+      <c r="K12" s="43" t="n">
         <f aca="false">IF(I12="Pending",0,J12-F12)</f>
         <v>113.636363636364</v>
       </c>
-      <c r="L12" s="81" t="n">
+      <c r="L12" s="73" t="n">
         <v>0.56</v>
       </c>
-      <c r="M12" s="69" t="s">
+      <c r="M12" s="62" t="s">
         <v>439</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="38" t="n">
+      <c r="A13" s="33" t="n">
         <v>7</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>440</v>
       </c>
-      <c r="C13" s="37" t="s">
+      <c r="C13" s="32" t="s">
         <v>287</v>
       </c>
-      <c r="D13" s="38" t="s">
+      <c r="D13" s="33" t="s">
         <v>190</v>
       </c>
-      <c r="E13" s="45" t="n">
+      <c r="E13" s="39" t="n">
         <v>1400</v>
       </c>
-      <c r="F13" s="46" t="n">
+      <c r="F13" s="40" t="n">
         <v>75</v>
       </c>
-      <c r="G13" s="47" t="n">
+      <c r="G13" s="41" t="n">
         <f aca="false">IF(E13&gt;0,F13*E13/100,F13*100/ABS(E13))</f>
         <v>1050</v>
       </c>
-      <c r="H13" s="47" t="n">
+      <c r="H13" s="41" t="n">
         <f aca="false">F13+G13</f>
         <v>1125</v>
       </c>
-      <c r="I13" s="64" t="s">
+      <c r="I13" s="57" t="s">
         <v>98</v>
       </c>
-      <c r="J13" s="47" t="n">
+      <c r="J13" s="41" t="n">
         <f aca="false">IF(I13="Win",F13+G13,IF(I13="Push",F13,IF(I13="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K13" s="49" t="n">
+      <c r="K13" s="43" t="n">
         <f aca="false">IF(I13="Pending",0,J13-F13)</f>
         <v>-75</v>
       </c>
-      <c r="L13" s="81" t="n">
+      <c r="L13" s="73" t="n">
         <v>0.07</v>
       </c>
-      <c r="M13" s="69" t="s">
+      <c r="M13" s="62" t="s">
         <v>441</v>
       </c>
     </row>

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="785" uniqueCount="465">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="803" uniqueCount="473">
   <si>
     <t xml:space="preserve">BETTING TEST ACCOUNT — ROLL-UP DASHBOARD</t>
   </si>
@@ -1231,13 +1231,13 @@
     <t xml:space="preserve">TEST 6 — THE 154th OPEN CHAMPIONSHIP · ROYAL BIRKDALE · JULY 16-19, 2026</t>
   </si>
   <si>
-    <t xml:space="preserve">STATUS: ACTIVE — first tee Thu Jul 16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Source: open2026-betting-card.html · Odds: DraftKings/consensus + Golf Digest, locked Sun Jul 12 · Phase 2 props ($400) added Wed Jul 15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Outright basket is mutually exclusive — max one cashes. Basket coverage ≈ 44%. $600 deployed now; $400 reserved (not yet at risk).</t>
+    <t xml:space="preserve">STATUS: ACTIVE — first tee Thu Jul 16 · $1,000 fully deployed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source: open2026-betting-card.html · Outrights locked Sun Jul 12 · Phase 2 top-10 props deployed Wed Jul 15 (reserved $400 now at risk)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Outright basket (rows 7-12) mutually exclusive — max one cashes. Phase 2 = 5 top-10 props (rows 13-17). Full $1,000 now deployed.</t>
   </si>
   <si>
     <t xml:space="preserve">Scottie Scheffler</t>
@@ -1276,13 +1276,37 @@
     <t xml:space="preserve">5 majors, career-long price · counts in longshot record</t>
   </si>
   <si>
-    <t xml:space="preserve">RESERVED — Phase 2 props (Wed)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Top-10s / H2H matchups / make-cut — lines post midweek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$400 reserved, not yet at risk; converts Wed Jul 15</t>
+    <t xml:space="preserve">Scottie Scheffler Top-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Top-10 finish</t>
+  </si>
+  <si>
+    <t xml:space="preserve">World #1 / +620 favorite; safest of the basket</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tommy Fleetwood Top-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Southport native, home links; strong value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jon Rahm Top-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elite wind player; value vs field</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matt Fitzpatrick Top-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">English; 6 straight Open cuts made</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Collin Morikawa Top-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021 Open champ, elite ballstriker</t>
   </si>
   <si>
     <t xml:space="preserve">TOTALS (deployed)</t>
@@ -1430,7 +1454,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="11">
+  <numFmts count="13">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="\$#,##0"/>
     <numFmt numFmtId="166" formatCode="\$#,##0.00;&quot;($&quot;#,##0.00\);\-"/>
@@ -1441,7 +1465,9 @@
     <numFmt numFmtId="171" formatCode="0%"/>
     <numFmt numFmtId="172" formatCode="0.0&quot; exp. wins&quot;"/>
     <numFmt numFmtId="173" formatCode="0.0"/>
-    <numFmt numFmtId="174" formatCode="0.00&quot; exp. wins&quot;"/>
+    <numFmt numFmtId="174" formatCode="\$#,##0"/>
+    <numFmt numFmtId="175" formatCode="\$#,##0.00"/>
+    <numFmt numFmtId="176" formatCode="\$#,##0.00;&quot;($&quot;#,##0.00\);\-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -1743,7 +1769,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="90">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2040,11 +2066,59 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="174" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="175" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="176" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="174" fontId="7" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="174" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="175" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="176" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="175" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2065,7 +2139,35 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="4">
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <family val="0"/>
+        <b val="1"/>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <family val="0"/>
+        <b val="1"/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <name val="Arial"/>
@@ -2399,7 +2501,7 @@
       </c>
       <c r="B8" s="9" t="n">
         <f aca="false">F25</f>
-        <v>2600</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2408,7 +2510,7 @@
       </c>
       <c r="B9" s="8" t="n">
         <f aca="false">B7-B8</f>
-        <v>1159.67586625339</v>
+        <v>759.675866253387</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2551,19 +2653,19 @@
         <v>22</v>
       </c>
       <c r="E18" s="17" t="n">
-        <f aca="false">SUM('The Open'!F7:F12)</f>
-        <v>600</v>
+        <f aca="false">SUM('The Open'!F7:F17)</f>
+        <v>1000</v>
       </c>
       <c r="F18" s="17" t="n">
-        <f aca="false">SUMIF('The Open'!I7:I12,"Pending",'The Open'!F7:F12)</f>
-        <v>600</v>
+        <f aca="false">SUMIF('The Open'!I7:I17,"Pending",'The Open'!F7:F17)</f>
+        <v>1000</v>
       </c>
       <c r="G18" s="17" t="n">
-        <f aca="false">SUM('The Open'!J7:J12)</f>
+        <f aca="false">SUM('The Open'!J7:J17)</f>
         <v>0</v>
       </c>
       <c r="H18" s="17" t="n">
-        <f aca="false">SUM('The Open'!K7:K12)</f>
+        <f aca="false">SUM('The Open'!K7:K17)</f>
         <v>0</v>
       </c>
       <c r="I18" s="18"/>
@@ -2783,11 +2885,11 @@
       </c>
       <c r="E25" s="8" t="n">
         <f aca="false">SUM(E16:E24)</f>
-        <v>7650</v>
+        <v>8050</v>
       </c>
       <c r="F25" s="8" t="n">
         <f aca="false">SUM(F16:F24)</f>
-        <v>2600</v>
+        <v>3000</v>
       </c>
       <c r="G25" s="8" t="n">
         <f aca="false">SUM(G16:G24)</f>
@@ -3128,20 +3230,20 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="35" t="s">
-        <v>442</v>
-      </c>
-      <c r="H1" s="77" t="s">
-        <v>443</v>
+        <v>450</v>
+      </c>
+      <c r="H1" s="89" t="s">
+        <v>451</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>444</v>
+        <v>452</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>445</v>
+        <v>453</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3195,10 +3297,10 @@
         <v>1</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="C7" s="32" t="s">
-        <v>447</v>
+        <v>455</v>
       </c>
       <c r="D7" s="33" t="s">
         <v>378</v>
@@ -3232,7 +3334,7 @@
         <v>0.57</v>
       </c>
       <c r="M7" s="62" t="s">
-        <v>448</v>
+        <v>456</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3240,10 +3342,10 @@
         <v>2</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>449</v>
+        <v>457</v>
       </c>
       <c r="C8" s="32" t="s">
-        <v>450</v>
+        <v>458</v>
       </c>
       <c r="D8" s="33" t="s">
         <v>179</v>
@@ -3277,7 +3379,7 @@
         <v>0.54</v>
       </c>
       <c r="M8" s="62" t="s">
-        <v>451</v>
+        <v>459</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3285,10 +3387,10 @@
         <v>3</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="C9" s="32" t="s">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="D9" s="33" t="s">
         <v>179</v>
@@ -3322,7 +3424,7 @@
         <v>0.55</v>
       </c>
       <c r="M9" s="62" t="s">
-        <v>454</v>
+        <v>462</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3330,7 +3432,7 @@
         <v>4</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="C10" s="32" t="s">
         <v>393</v>
@@ -3367,7 +3469,7 @@
         <v>0.54</v>
       </c>
       <c r="M10" s="62" t="s">
-        <v>456</v>
+        <v>464</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3375,10 +3477,10 @@
         <v>5</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="C11" s="32" t="s">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="D11" s="33" t="s">
         <v>89</v>
@@ -3412,7 +3514,7 @@
         <v>0.58</v>
       </c>
       <c r="M11" s="62" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3420,10 +3522,10 @@
         <v>6</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>460</v>
+        <v>468</v>
       </c>
       <c r="C12" s="32" t="s">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="D12" s="33" t="s">
         <v>378</v>
@@ -3457,7 +3559,7 @@
         <v>0.52</v>
       </c>
       <c r="M12" s="62" t="s">
-        <v>462</v>
+        <v>470</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3468,7 +3570,7 @@
         <v>395</v>
       </c>
       <c r="C13" s="32" t="s">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="D13" s="33" t="s">
         <v>117</v>
@@ -3502,7 +3604,7 @@
         <v>0.1</v>
       </c>
       <c r="M13" s="62" t="s">
-        <v>464</v>
+        <v>472</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7684,7 +7786,7 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="74" t="n">
+      <c r="A13" s="20" t="n">
         <v>7</v>
       </c>
       <c r="B13" s="21" t="s">
@@ -7693,77 +7795,252 @@
       <c r="C13" s="74" t="s">
         <v>416</v>
       </c>
-      <c r="D13" s="74" t="s">
-        <v>63</v>
-      </c>
-      <c r="E13" s="74"/>
-      <c r="F13" s="74"/>
-      <c r="G13" s="74"/>
-      <c r="H13" s="74"/>
-      <c r="I13" s="74"/>
-      <c r="J13" s="74"/>
-      <c r="K13" s="74"/>
-      <c r="L13" s="74"/>
-      <c r="M13" s="74" t="s">
+      <c r="D13" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="E13" s="75" t="n">
+        <v>-146</v>
+      </c>
+      <c r="F13" s="76" t="n">
+        <v>120</v>
+      </c>
+      <c r="G13" s="77" t="n">
+        <f aca="false">IF(E13&gt;0,F13*E13/100,F13*100/ABS(E13))</f>
+        <v>82.1917808219178</v>
+      </c>
+      <c r="H13" s="77" t="n">
+        <f aca="false">F13+G13</f>
+        <v>202.191780821918</v>
+      </c>
+      <c r="I13" s="57" t="s">
+        <v>123</v>
+      </c>
+      <c r="J13" s="77" t="n">
+        <f aca="false">IF(I13="Win",F13+G13,IF(I13="Push",F13,IF(I13="Loss",0,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="K13" s="78" t="n">
+        <f aca="false">IF(I13="Pending",0,J13-F13)</f>
+        <v>0</v>
+      </c>
+      <c r="L13" s="79" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="M13" s="80" t="s">
         <v>417</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="63"/>
-      <c r="B14" s="64" t="s">
+      <c r="A14" s="33" t="n">
+        <v>8</v>
+      </c>
+      <c r="B14" s="5" t="s">
         <v>418</v>
       </c>
-      <c r="C14" s="63"/>
-      <c r="D14" s="63"/>
-      <c r="E14" s="63"/>
-      <c r="F14" s="48" t="n">
-        <f aca="false">SUM(F7:F13)</f>
-        <v>600</v>
-      </c>
-      <c r="G14" s="49" t="n">
-        <f aca="false">SUM(G7:G12)</f>
-        <v>10160</v>
-      </c>
-      <c r="H14" s="49" t="n">
-        <f aca="false">SUM(H7:H12)</f>
-        <v>10760</v>
-      </c>
-      <c r="I14" s="63"/>
-      <c r="J14" s="49" t="n">
-        <f aca="false">SUM(J7:J12)</f>
-        <v>0</v>
-      </c>
-      <c r="K14" s="50" t="n">
-        <f aca="false">SUM(K7:K12)</f>
-        <v>0</v>
-      </c>
-      <c r="L14" s="75" t="n">
-        <f aca="false">SUM(L7:L12)</f>
-        <v>0.445</v>
-      </c>
-      <c r="M14" s="63"/>
+      <c r="C14" s="32" t="s">
+        <v>416</v>
+      </c>
+      <c r="D14" s="33" t="s">
+        <v>94</v>
+      </c>
+      <c r="E14" s="39" t="n">
+        <v>158</v>
+      </c>
+      <c r="F14" s="81" t="n">
+        <v>90</v>
+      </c>
+      <c r="G14" s="82" t="n">
+        <f aca="false">IF(E14&gt;0,F14*E14/100,F14*100/ABS(E14))</f>
+        <v>142.2</v>
+      </c>
+      <c r="H14" s="82" t="n">
+        <f aca="false">F14+G14</f>
+        <v>232.2</v>
+      </c>
+      <c r="I14" s="57" t="s">
+        <v>123</v>
+      </c>
+      <c r="J14" s="82" t="n">
+        <f aca="false">IF(I14="Win",F14+G14,IF(I14="Push",F14,IF(I14="Loss",0,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="K14" s="83" t="n">
+        <f aca="false">IF(I14="Pending",0,J14-F14)</f>
+        <v>0</v>
+      </c>
+      <c r="L14" s="73" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="M14" s="62" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="33" t="n">
+        <v>9</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>420</v>
+      </c>
+      <c r="C15" s="32" t="s">
+        <v>416</v>
+      </c>
+      <c r="D15" s="33" t="s">
+        <v>94</v>
+      </c>
+      <c r="E15" s="39" t="n">
+        <v>172</v>
+      </c>
+      <c r="F15" s="81" t="n">
+        <v>80</v>
+      </c>
+      <c r="G15" s="82" t="n">
+        <f aca="false">IF(E15&gt;0,F15*E15/100,F15*100/ABS(E15))</f>
+        <v>137.6</v>
+      </c>
+      <c r="H15" s="82" t="n">
+        <f aca="false">F15+G15</f>
+        <v>217.6</v>
+      </c>
+      <c r="I15" s="57" t="s">
+        <v>123</v>
+      </c>
+      <c r="J15" s="82" t="n">
+        <f aca="false">IF(I15="Win",F15+G15,IF(I15="Push",F15,IF(I15="Loss",0,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="K15" s="83" t="n">
+        <f aca="false">IF(I15="Pending",0,J15-F15)</f>
+        <v>0</v>
+      </c>
+      <c r="L15" s="73" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="M15" s="62" t="s">
+        <v>421</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="4" t="s">
-        <v>119</v>
+      <c r="A16" s="33" t="n">
+        <v>10</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>422</v>
+      </c>
+      <c r="C16" s="32" t="s">
+        <v>416</v>
+      </c>
+      <c r="D16" s="33" t="s">
+        <v>94</v>
+      </c>
+      <c r="E16" s="39" t="n">
+        <v>164</v>
+      </c>
+      <c r="F16" s="81" t="n">
+        <v>70</v>
+      </c>
+      <c r="G16" s="82" t="n">
+        <f aca="false">IF(E16&gt;0,F16*E16/100,F16*100/ABS(E16))</f>
+        <v>114.8</v>
+      </c>
+      <c r="H16" s="82" t="n">
+        <f aca="false">F16+G16</f>
+        <v>184.8</v>
+      </c>
+      <c r="I16" s="57" t="s">
+        <v>123</v>
+      </c>
+      <c r="J16" s="82" t="n">
+        <f aca="false">IF(I16="Win",F16+G16,IF(I16="Push",F16,IF(I16="Loss",0,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="K16" s="83" t="n">
+        <f aca="false">IF(I16="Pending",0,J16-F16)</f>
+        <v>0</v>
+      </c>
+      <c r="L16" s="73" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="M16" s="62" t="s">
+        <v>423</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="33" t="n">
+        <v>11</v>
+      </c>
       <c r="B17" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="C17" s="51" t="n">
-        <f aca="false">COUNTIF(I7:I12,"Win")</f>
-        <v>0</v>
+        <v>424</v>
+      </c>
+      <c r="C17" s="84" t="s">
+        <v>416</v>
+      </c>
+      <c r="D17" s="33" t="s">
+        <v>94</v>
+      </c>
+      <c r="E17" s="39" t="n">
+        <v>280</v>
+      </c>
+      <c r="F17" s="81" t="n">
+        <v>40</v>
+      </c>
+      <c r="G17" s="82" t="n">
+        <f aca="false">IF(E17&gt;0,F17*E17/100,F17*100/ABS(E17))</f>
+        <v>112</v>
+      </c>
+      <c r="H17" s="82" t="n">
+        <f aca="false">F17+G17</f>
+        <v>152</v>
+      </c>
+      <c r="I17" s="57" t="s">
+        <v>123</v>
+      </c>
+      <c r="J17" s="82" t="n">
+        <f aca="false">IF(I17="Win",F17+G17,IF(I17="Push",F17,IF(I17="Loss",0,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="K17" s="83" t="n">
+        <f aca="false">IF(I17="Pending",0,J17-F17)</f>
+        <v>0</v>
+      </c>
+      <c r="L17" s="73" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M17" s="62" t="s">
+        <v>425</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="5" t="s">
-        <v>121</v>
+      <c r="B18" s="85" t="s">
+        <v>426</v>
       </c>
       <c r="C18" s="51" t="n">
         <f aca="false">COUNTIF(I7:I12,"Loss")</f>
         <v>0</v>
+      </c>
+      <c r="F18" s="86" t="n">
+        <f aca="false">SUM(F7:F17)</f>
+        <v>1000</v>
+      </c>
+      <c r="G18" s="86" t="n">
+        <f aca="false">SUM(G7:G17)</f>
+        <v>10748.7917808219</v>
+      </c>
+      <c r="H18" s="86" t="n">
+        <f aca="false">SUM(H7:H17)</f>
+        <v>11748.7917808219</v>
+      </c>
+      <c r="J18" s="86" t="n">
+        <f aca="false">SUM(J7:J17)</f>
+        <v>0</v>
+      </c>
+      <c r="K18" s="86" t="n">
+        <f aca="false">SUM(K7:K17)</f>
+        <v>0</v>
+      </c>
+      <c r="L18" s="87" t="n">
+        <f aca="false">SUM(L7:L17)</f>
+        <v>2.645</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7786,7 +8063,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="5" t="s">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c r="C21" s="34" t="n">
         <f aca="false">SUM(F7:F12)</f>
@@ -7813,7 +8090,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="5" t="s">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c r="C24" s="52" t="n">
         <f aca="false">SUM(L7:L12)</f>
@@ -7837,8 +8114,20 @@
       <formula>AND(ISNUMBER(C23),C23&lt;0)</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="1">
+  <conditionalFormatting sqref="K7:K18">
+    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+      <formula>AND(ISNUMBER(K7),K7&gt;0)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+      <formula>AND(ISNUMBER(K7),K7&lt;0)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="2">
     <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="I7:I12" type="list">
+      <formula1>"Pending,Win,Loss,Push"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="I13:I17" type="list">
       <formula1>"Pending,Win,Loss,Push"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -7878,20 +8167,20 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="35" t="s">
-        <v>421</v>
-      </c>
-      <c r="H1" s="76" t="s">
-        <v>422</v>
+        <v>429</v>
+      </c>
+      <c r="H1" s="88" t="s">
+        <v>430</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>423</v>
+        <v>431</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>424</v>
+        <v>432</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7945,7 +8234,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c r="C7" s="32" t="s">
         <v>287</v>
@@ -7982,7 +8271,7 @@
         <v>0.27</v>
       </c>
       <c r="M7" s="62" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7990,7 +8279,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>427</v>
+        <v>435</v>
       </c>
       <c r="C8" s="32" t="s">
         <v>287</v>
@@ -8027,7 +8316,7 @@
         <v>0.18</v>
       </c>
       <c r="M8" s="62" t="s">
-        <v>428</v>
+        <v>436</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8035,10 +8324,10 @@
         <v>3</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="C9" s="32" t="s">
-        <v>430</v>
+        <v>438</v>
       </c>
       <c r="D9" s="33" t="s">
         <v>94</v>
@@ -8072,7 +8361,7 @@
         <v>0.6</v>
       </c>
       <c r="M9" s="62" t="s">
-        <v>431</v>
+        <v>439</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8080,10 +8369,10 @@
         <v>4</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>432</v>
+        <v>440</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>433</v>
+        <v>441</v>
       </c>
       <c r="D10" s="33" t="s">
         <v>94</v>
@@ -8117,7 +8406,7 @@
         <v>0.58</v>
       </c>
       <c r="M10" s="62" t="s">
-        <v>434</v>
+        <v>442</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8125,10 +8414,10 @@
         <v>5</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="C11" s="32" t="s">
-        <v>430</v>
+        <v>438</v>
       </c>
       <c r="D11" s="33" t="s">
         <v>94</v>
@@ -8162,7 +8451,7 @@
         <v>0.57</v>
       </c>
       <c r="M11" s="62" t="s">
-        <v>436</v>
+        <v>444</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8170,10 +8459,10 @@
         <v>6</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="C12" s="32" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="D12" s="33" t="s">
         <v>94</v>
@@ -8207,7 +8496,7 @@
         <v>0.56</v>
       </c>
       <c r="M12" s="62" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8215,7 +8504,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="C13" s="32" t="s">
         <v>287</v>
@@ -8252,7 +8541,7 @@
         <v>0.07</v>
       </c>
       <c r="M13" s="62" t="s">
-        <v>441</v>
+        <v>449</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -1231,7 +1231,7 @@
     <t xml:space="preserve">TEST 6 — THE 154th OPEN CHAMPIONSHIP · ROYAL BIRKDALE · JULY 16-19, 2026</t>
   </si>
   <si>
-    <t xml:space="preserve">STATUS: ACTIVE — R1 LIVE Thu Jul 16 (began 6:35 AM UK) · $1,000 fully deployed</t>
+    <t xml:space="preserve">STATUS: ACTIVE — R1 COMPLETE Thu Jul 16: Suber leads −5 (65); Morikawa −3 best on card · $1,000 fully deployed</t>
   </si>
   <si>
     <t xml:space="preserve">Source: open2026-betting-card.html · Outrights locked Sun Jul 12 · Phase 2 top-10 props deployed Wed Jul 15 (reserved $400 now at risk)</t>

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -1231,7 +1231,7 @@
     <t xml:space="preserve">TEST 6 — THE 154th OPEN CHAMPIONSHIP · ROYAL BIRKDALE · JULY 16-19, 2026</t>
   </si>
   <si>
-    <t xml:space="preserve">STATUS: ACTIVE — R1 COMPLETE Thu Jul 16: Suber leads −5 (65); Morikawa −3 best on card · $1,000 fully deployed</t>
+    <t xml:space="preserve">STATUS: ACTIVE — R1 COMPLETE Thu Jul 16: Suber leads −5 (65); Morikawa −3 best on card; Fitzpatrick +2 confirmed (T93, cut watch) · $1,000 fully deployed</t>
   </si>
   <si>
     <t xml:space="preserve">Source: open2026-betting-card.html · Outrights locked Sun Jul 12 · Phase 2 top-10 props deployed Wed Jul 15 (reserved $400 now at risk)</t>

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -1231,7 +1231,7 @@
     <t xml:space="preserve">TEST 6 — THE 154th OPEN CHAMPIONSHIP · ROYAL BIRKDALE · JULY 16-19, 2026</t>
   </si>
   <si>
-    <t xml:space="preserve">STATUS: ACTIVE — R1 COMPLETE Thu Jul 16: Suber leads −5 (65); Morikawa −3 best on card; Fitzpatrick +2 confirmed (T93, cut watch) · $1,000 fully deployed</t>
+    <t xml:space="preserve">STATUS: ACTIVE — R2 IN PROGRESS Fri Jul 17 (10 AM UK): morning wave away — Morikawa 9:36, Koepka 9:47, Fitzpatrick 10:09; Suber (−5 leader) mid-round. Overnight board stands; projected cut +1 (~40% to +2), Fitzpatrick +2 on the number · $1,000 fully deployed</t>
   </si>
   <si>
     <t xml:space="preserve">Source: open2026-betting-card.html · Outrights locked Sun Jul 12 · Phase 2 top-10 props deployed Wed Jul 15 (reserved $400 now at risk)</t>

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -1231,7 +1231,7 @@
     <t xml:space="preserve">TEST 6 — THE 154th OPEN CHAMPIONSHIP · ROYAL BIRKDALE · JULY 16-19, 2026</t>
   </si>
   <si>
-    <t xml:space="preserve">STATUS: ACTIVE — R2 IN PROGRESS Fri Jul 17 (10 AM UK): morning wave away — Morikawa 9:36, Koepka 9:47, Fitzpatrick 10:09; Suber (−5 leader) mid-round. Overnight board stands; projected cut +1 (~40% to +2), Fitzpatrick +2 on the number · $1,000 fully deployed</t>
+    <t xml:space="preserve">STATUS: ACTIVE — R2 IN PROGRESS Fri Jul 17 (11 AM UK): Suber holds -5 thru 11 (E today); Morikawa -3 thru 3, T8, best on card; Koepka/Fitzpatrick early, no in-play numbers yet. Cut firming at +1 (~51%). Grade Sunday night only.</t>
   </si>
   <si>
     <t xml:space="preserve">Source: open2026-betting-card.html · Outrights locked Sun Jul 12 · Phase 2 top-10 props deployed Wed Jul 15 (reserved $400 now at risk)</t>

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -1231,7 +1231,7 @@
     <t xml:space="preserve">TEST 6 — THE 154th OPEN CHAMPIONSHIP · ROYAL BIRKDALE · JULY 16-19, 2026</t>
   </si>
   <si>
-    <t xml:space="preserve">STATUS: ACTIVE — R2 IN PROGRESS Fri Jul 17 (11 AM UK): Suber holds -5 thru 11 (E today); Morikawa -3 thru 3, T8, best on card; Koepka/Fitzpatrick early, no in-play numbers yet. Cut firming at +1 (~51%). Grade Sunday night only.</t>
+    <t xml:space="preserve">STATUS: ACTIVE — R2 IN PROGRESS Fri Jul 17 (1:30 PM UK): NEW LEADER Herbert -8 thru 12 (record 28 front nine); Suber 2nd -6 thru 17; Morikawa -5 thru 9, best on card, 3 back; Koepka/Fitzpatrick no in-play numbers (E / +2 overnight, cut watch). Cut ~+1 (53%). Grade Sunday night only.</t>
   </si>
   <si>
     <t xml:space="preserve">Source: open2026-betting-card.html · Outrights locked Sun Jul 12 · Phase 2 top-10 props deployed Wed Jul 15 (reserved $400 now at risk)</t>

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -18,6 +18,7 @@
     <sheet name="The Open" sheetId="8" state="visible" r:id="rId10"/>
     <sheet name="HR Derby" sheetId="9" state="visible" r:id="rId11"/>
     <sheet name="WNBA Jul 15" sheetId="10" state="visible" r:id="rId12"/>
+    <sheet name="Rugby Jul 18" sheetId="11" state="visible" r:id="rId13"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="803" uniqueCount="473">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="838" uniqueCount="486">
   <si>
     <t xml:space="preserve">BETTING TEST ACCOUNT — ROLL-UP DASHBOARD</t>
   </si>
@@ -121,9 +122,6 @@
     <t xml:space="preserve">2026-07-18</t>
   </si>
   <si>
-    <t xml:space="preserve">QUEUED</t>
-  </si>
-  <si>
     <t xml:space="preserve">MLB Home Run Derby</t>
   </si>
   <si>
@@ -217,13 +215,10 @@
     <t xml:space="preserve">Test 7 · Rugby Jul 18</t>
   </si>
   <si>
-    <t xml:space="preserve">TBD at finalization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TBD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Queued</t>
+    <t xml:space="preserve">Georgia -12.5 + USA -3.5 parlay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+263</t>
   </si>
   <si>
     <t xml:space="preserve">Test 8 · HR Derby</t>
@@ -1147,6 +1142,9 @@
     <t xml:space="preserve">covers.com (Fever-Valkyries odds); dratings.com (slate, projections); actionnetwork.com (Sparks-Lynx); fantasyalarm.com (Fever preview); espn.com (records)</t>
   </si>
   <si>
+    <t xml:space="preserve">freetips.com (Chile-Georgia -12.5, USA-Spain -3.5 handicaps); all.rugby (fixtures/form); world.rugby (tournament); skysports.com (previews)</t>
+  </si>
+  <si>
     <t xml:space="preserve">TEST 5 — WNBA SUNDAY NIGHT DOUBLEHEADER · JULY 12, 2026</t>
   </si>
   <si>
@@ -1448,13 +1446,55 @@
   </si>
   <si>
     <t xml:space="preserve">Cross-game stack; counts in longshot record · RESULT: Fever -3.5 leg dead at the first hurdle → parlay dead (longshot MISS, 0-for-6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEST 7 — WORLD RUGBY NATIONS CUP · FINAL ROUND · JULY 18, 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STATUS: ACTIVE — settles Sat night Jul 18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source: cards/rugby-jul18-betting-card.html · Lines: freetips.com / Stake.com handicaps, finalized Fri Jul 17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Only 2 of 6 matches drew clean lines (tier-2 markets thin). $550 deployed on priced handicaps + longshot; $450 kept in the account, not at risk.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Georgia -12.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chile vs Georgia · ~2 PM CT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Handicap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anchor — Georgia unbeaten, class of field; tipster 3-unit high play</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USA -3.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USA vs Spain · ~6:30 PM CT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Centerpiece — USA 2-0, backed to cover vs inconsistent Spain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LONGSHOT: Georgia -12.5 + USA -3.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2-leg cross-match parlay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Round's longshot (modest — only 2 markets priced); counts in longshot record</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="10">
+  <numFmts count="13">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="\$#,##0"/>
     <numFmt numFmtId="166" formatCode="\$#,##0.00;&quot;($&quot;#,##0.00\);\-"/>
@@ -1465,6 +1505,9 @@
     <numFmt numFmtId="171" formatCode="0%"/>
     <numFmt numFmtId="172" formatCode="0.0&quot; exp. wins&quot;"/>
     <numFmt numFmtId="173" formatCode="0.0"/>
+    <numFmt numFmtId="174" formatCode="\$#,##0"/>
+    <numFmt numFmtId="175" formatCode="\$#,##0.00"/>
+    <numFmt numFmtId="176" formatCode="\$#,##0.00;&quot;($&quot;#,##0.00\);\-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -1637,7 +1680,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1660,12 +1703,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFE2F0D9"/>
         <bgColor rgb="FFE7E6E6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFF2F2F2"/>
       </patternFill>
     </fill>
     <fill>
@@ -1706,6 +1743,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFE81828"/>
         <bgColor rgb="FFC00000"/>
       </patternFill>
@@ -1714,6 +1757,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFF6B00"/>
         <bgColor rgb="FFFF9900"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7A2E8D"/>
+        <bgColor rgb="FF993366"/>
       </patternFill>
     </fill>
   </fills>
@@ -1766,7 +1815,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="93">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1863,22 +1912,6 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1911,7 +1944,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1935,7 +1968,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1947,27 +1980,27 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1983,7 +2016,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1991,11 +2024,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2003,7 +2036,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="7" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="172" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2019,11 +2052,11 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2051,7 +2084,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="22" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2059,31 +2092,47 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="170" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="13" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="13" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="10" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="10" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="13" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2105,6 +2154,38 @@
     </xf>
     <xf numFmtId="164" fontId="9" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="14" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="174" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="175" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="176" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="175" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -2116,7 +2197,35 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="4">
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <family val="0"/>
+        <b val="1"/>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <family val="0"/>
+        <b val="1"/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <name val="Arial"/>
@@ -2165,7 +2274,7 @@
       <rgbColor rgb="FFB0B0B0"/>
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FF7A2E8D"/>
       <rgbColor rgb="FFFFF2CC"/>
       <rgbColor rgb="FFE2F0D9"/>
       <rgbColor rgb="FF660066"/>
@@ -2450,7 +2559,7 @@
       </c>
       <c r="B8" s="9" t="n">
         <f aca="false">F25</f>
-        <v>1000</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2459,7 +2568,7 @@
       </c>
       <c r="B9" s="8" t="n">
         <f aca="false">B7-B8</f>
-        <v>1943.68337513795</v>
+        <v>1393.68337513795</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2468,7 +2577,7 @@
       </c>
       <c r="B10" s="10" t="str">
         <f aca="false">COUNTIF(D16:D24,"ACTIVE")&amp;" of 4 max"</f>
-        <v>1 of 4 max</v>
+        <v>2 of 4 max</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2624,28 +2733,32 @@
       <c r="M18" s="1"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="24" t="n">
+      <c r="A19" s="20" t="n">
         <v>7</v>
       </c>
-      <c r="B19" s="25" t="s">
+      <c r="B19" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="C19" s="24" t="s">
+      <c r="C19" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="D19" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="E19" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="27" t="n">
+      <c r="D19" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="E19" s="23" t="n">
+        <f aca="false">SUM('Rugby Jul 18'!F7:F9)</f>
+        <v>550</v>
+      </c>
+      <c r="F19" s="23" t="n">
+        <f aca="false">SUMIF('Rugby Jul 18'!I7:I9,"Pending",'Rugby Jul 18'!F7:F9)</f>
+        <v>550</v>
+      </c>
+      <c r="G19" s="23" t="n">
+        <f aca="false">SUM('Rugby Jul 18'!J7:J9)</f>
+        <v>0</v>
+      </c>
+      <c r="H19" s="23" t="n">
+        <f aca="false">SUM('Rugby Jul 18'!K7:K9)</f>
         <v>0</v>
       </c>
       <c r="I19" s="18"/>
@@ -2659,10 +2772,10 @@
         <v>8</v>
       </c>
       <c r="B20" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20" s="14" t="s">
         <v>31</v>
-      </c>
-      <c r="C20" s="14" t="s">
-        <v>32</v>
       </c>
       <c r="D20" s="16" t="s">
         <v>22</v>
@@ -2694,10 +2807,10 @@
         <v>4</v>
       </c>
       <c r="B21" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="C21" s="14" t="s">
         <v>33</v>
-      </c>
-      <c r="C21" s="14" t="s">
-        <v>34</v>
       </c>
       <c r="D21" s="16" t="s">
         <v>22</v>
@@ -2729,10 +2842,10 @@
         <v>5</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D22" s="16" t="s">
         <v>22</v>
@@ -2764,10 +2877,10 @@
         <v>3</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D23" s="16" t="s">
         <v>22</v>
@@ -2788,8 +2901,8 @@
         <f aca="false">SUM('MLB Jul 12'!K7:K14)</f>
         <v>-197.767741935484</v>
       </c>
-      <c r="I23" s="28"/>
-      <c r="J23" s="28"/>
+      <c r="I23" s="24"/>
+      <c r="J23" s="24"/>
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
       <c r="M23" s="1"/>
@@ -2799,10 +2912,10 @@
         <v>1</v>
       </c>
       <c r="B24" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="C24" s="14" t="s">
         <v>37</v>
-      </c>
-      <c r="C24" s="14" t="s">
-        <v>38</v>
       </c>
       <c r="D24" s="16" t="s">
         <v>22</v>
@@ -2830,15 +2943,15 @@
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="4"/>
       <c r="B25" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E25" s="8" t="n">
         <f aca="false">SUM(E16:E24)</f>
-        <v>8050</v>
+        <v>8600</v>
       </c>
       <c r="F25" s="8" t="n">
         <f aca="false">SUM(F16:F24)</f>
-        <v>1000</v>
+        <v>1550</v>
       </c>
       <c r="G25" s="8" t="n">
         <f aca="false">SUM(G16:G24)</f>
@@ -2853,7 +2966,7 @@
       <c r="M25" s="1"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="29"/>
+      <c r="A26" s="25"/>
       <c r="B26" s="13"/>
       <c r="C26" s="13"/>
       <c r="D26" s="13"/>
@@ -2863,12 +2976,12 @@
       <c r="M26" s="1"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="29" t="s">
-        <v>40</v>
+      <c r="A27" s="25" t="s">
+        <v>39</v>
       </c>
       <c r="B27" s="13"/>
       <c r="C27" s="13"/>
-      <c r="D27" s="30"/>
+      <c r="D27" s="26"/>
       <c r="E27" s="13"/>
       <c r="K27" s="1"/>
       <c r="L27" s="1"/>
@@ -2876,16 +2989,16 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="B28" s="12" t="s">
+      <c r="C28" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="C28" s="12" t="s">
+      <c r="D28" s="27" t="s">
         <v>43</v>
-      </c>
-      <c r="D28" s="31" t="s">
-        <v>44</v>
       </c>
       <c r="E28" s="12" t="s">
         <v>15</v>
@@ -2895,36 +3008,36 @@
       <c r="M28" s="1"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="32" t="s">
+      <c r="A29" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="B29" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="B29" s="32" t="s">
+      <c r="C29" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="C29" s="33" t="s">
+      <c r="D29" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="10" t="s">
         <v>47</v>
-      </c>
-      <c r="D29" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" s="10" t="s">
-        <v>48</v>
       </c>
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
       <c r="M29" s="1"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="32" t="s">
+      <c r="A30" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="B30" s="28" t="s">
         <v>49</v>
       </c>
-      <c r="B30" s="32" t="s">
+      <c r="C30" s="29" t="s">
         <v>50</v>
       </c>
-      <c r="C30" s="33" t="s">
-        <v>51</v>
-      </c>
-      <c r="D30" s="34" t="n">
+      <c r="D30" s="30" t="n">
         <v>50</v>
       </c>
       <c r="E30" s="10" t="str">
@@ -2936,16 +3049,16 @@
       <c r="M30" s="1"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="32" t="s">
+      <c r="A31" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="B31" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="B31" s="32" t="s">
+      <c r="C31" s="29" t="s">
         <v>53</v>
       </c>
-      <c r="C31" s="33" t="s">
-        <v>54</v>
-      </c>
-      <c r="D31" s="34" t="n">
+      <c r="D31" s="30" t="n">
         <v>40</v>
       </c>
       <c r="E31" s="10" t="str">
@@ -2957,16 +3070,16 @@
       <c r="M31" s="1"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="32" t="s">
+      <c r="A32" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="B32" s="28" t="s">
         <v>55</v>
       </c>
-      <c r="B32" s="32" t="s">
+      <c r="C32" s="29" t="s">
         <v>56</v>
       </c>
-      <c r="C32" s="33" t="s">
-        <v>57</v>
-      </c>
-      <c r="D32" s="34" t="n">
+      <c r="D32" s="30" t="n">
         <v>100</v>
       </c>
       <c r="E32" s="10" t="str">
@@ -2978,16 +3091,16 @@
       <c r="M32" s="1"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="32" t="s">
+      <c r="A33" s="28" t="s">
+        <v>57</v>
+      </c>
+      <c r="B33" s="28" t="s">
         <v>58</v>
       </c>
-      <c r="B33" s="32" t="s">
+      <c r="C33" s="29" t="s">
         <v>59</v>
       </c>
-      <c r="C33" s="33" t="s">
-        <v>60</v>
-      </c>
-      <c r="D33" s="34" t="n">
+      <c r="D33" s="30" t="n">
         <v>50</v>
       </c>
       <c r="E33" s="10" t="str">
@@ -2999,36 +3112,37 @@
       <c r="M33" s="1"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="32" t="s">
+      <c r="A34" s="28" t="s">
+        <v>60</v>
+      </c>
+      <c r="B34" s="28" t="s">
         <v>61</v>
       </c>
-      <c r="B34" s="32" t="s">
+      <c r="C34" s="29" t="s">
         <v>62</v>
       </c>
-      <c r="C34" s="33" t="s">
-        <v>63</v>
-      </c>
-      <c r="D34" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" s="10" t="s">
-        <v>64</v>
+      <c r="D34" s="30" t="n">
+        <v>60</v>
+      </c>
+      <c r="E34" s="10" t="str">
+        <f aca="false">IF('Rugby Jul 18'!I9="Win","HIT",IF('Rugby Jul 18'!I9="Loss","MISS","Pending"))</f>
+        <v>Pending</v>
       </c>
       <c r="K34" s="1"/>
       <c r="L34" s="1"/>
       <c r="M34" s="1"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="32" t="s">
+      <c r="A35" s="28" t="s">
+        <v>63</v>
+      </c>
+      <c r="B35" s="28" t="s">
+        <v>64</v>
+      </c>
+      <c r="C35" s="29" t="s">
         <v>65</v>
       </c>
-      <c r="B35" s="32" t="s">
-        <v>66</v>
-      </c>
-      <c r="C35" s="33" t="s">
-        <v>67</v>
-      </c>
-      <c r="D35" s="34" t="n">
+      <c r="D35" s="30" t="n">
         <v>75</v>
       </c>
       <c r="E35" s="10" t="str">
@@ -3040,16 +3154,16 @@
       <c r="M35" s="1"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="32" t="s">
-        <v>68</v>
-      </c>
-      <c r="B36" s="32" t="s">
-        <v>56</v>
-      </c>
-      <c r="C36" s="33" t="s">
-        <v>69</v>
-      </c>
-      <c r="D36" s="34" t="n">
+      <c r="A36" s="28" t="s">
+        <v>66</v>
+      </c>
+      <c r="B36" s="28" t="s">
+        <v>55</v>
+      </c>
+      <c r="C36" s="29" t="s">
+        <v>67</v>
+      </c>
+      <c r="D36" s="30" t="n">
         <v>75</v>
       </c>
       <c r="E36" s="10" t="str">
@@ -3062,7 +3176,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E37" s="10" t="str">
         <f aca="false">IF(COUNTIF(E29:E36,"HIT")+COUNTIF(E29:E36,"MISS")=0,"—",COUNTIF(E29:E36,"HIT")&amp;"-for-"&amp;(COUNTIF(E29:E36,"HIT")+COUNTIF(E29:E36,"MISS"))&amp;" ("&amp;TEXT(COUNTIF(E29:E36,"HIT")/(COUNTIF(E29:E36,"HIT")+COUNTIF(E29:E36,"MISS")),"0%")&amp;")")</f>
@@ -3074,7 +3188,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="K38" s="1"/>
       <c r="L38" s="1"/>
@@ -3178,26 +3292,26 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="31" t="s">
+        <v>449</v>
+      </c>
+      <c r="H1" s="84" t="s">
         <v>450</v>
-      </c>
-      <c r="H1" s="84" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3205,360 +3319,360 @@
         <v>12</v>
       </c>
       <c r="B6" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>198</v>
+      </c>
+      <c r="D6" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="C6" s="12" t="s">
-        <v>200</v>
-      </c>
-      <c r="D6" s="12" t="s">
+      <c r="E6" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="G6" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="H6" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="F6" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="G6" s="12" t="s">
+      <c r="I6" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="H6" s="12" t="s">
+      <c r="J6" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="I6" s="12" t="s">
+      <c r="K6" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="J6" s="12" t="s">
+      <c r="L6" s="12" t="s">
+        <v>218</v>
+      </c>
+      <c r="M6" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="K6" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="L6" s="12" t="s">
-        <v>220</v>
-      </c>
-      <c r="M6" s="12" t="s">
-        <v>86</v>
-      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="33" t="n">
+      <c r="A7" s="29" t="n">
         <v>1</v>
       </c>
       <c r="B7" s="5" t="s">
+        <v>453</v>
+      </c>
+      <c r="C7" s="28" t="s">
         <v>454</v>
       </c>
-      <c r="C7" s="32" t="s">
-        <v>455</v>
-      </c>
-      <c r="D7" s="33" t="s">
-        <v>378</v>
-      </c>
-      <c r="E7" s="39" t="n">
+      <c r="D7" s="29" t="s">
+        <v>377</v>
+      </c>
+      <c r="E7" s="35" t="n">
         <v>-105</v>
       </c>
-      <c r="F7" s="40" t="n">
+      <c r="F7" s="36" t="n">
         <v>185</v>
       </c>
-      <c r="G7" s="41" t="n">
+      <c r="G7" s="37" t="n">
         <f aca="false">IF(E7&gt;0,F7*E7/100,F7*100/ABS(E7))</f>
         <v>176.190476190476</v>
       </c>
-      <c r="H7" s="41" t="n">
+      <c r="H7" s="37" t="n">
         <f aca="false">F7+G7</f>
         <v>361.190476190476</v>
       </c>
-      <c r="I7" s="57" t="s">
-        <v>98</v>
-      </c>
-      <c r="J7" s="41" t="n">
+      <c r="I7" s="53" t="s">
+        <v>96</v>
+      </c>
+      <c r="J7" s="37" t="n">
         <f aca="false">IF(I7="Win",F7+G7,IF(I7="Push",F7,IF(I7="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K7" s="43" t="n">
+      <c r="K7" s="39" t="n">
         <f aca="false">IF(I7="Pending",0,J7-F7)</f>
         <v>-185</v>
       </c>
-      <c r="L7" s="73" t="n">
+      <c r="L7" s="70" t="n">
         <v>0.57</v>
       </c>
-      <c r="M7" s="62" t="s">
+      <c r="M7" s="58" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>456</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="33" t="n">
-        <v>2</v>
-      </c>
-      <c r="B8" s="5" t="s">
+      <c r="C8" s="28" t="s">
         <v>457</v>
       </c>
-      <c r="C8" s="32" t="s">
-        <v>458</v>
-      </c>
-      <c r="D8" s="33" t="s">
-        <v>179</v>
-      </c>
-      <c r="E8" s="39" t="n">
+      <c r="D8" s="29" t="s">
+        <v>177</v>
+      </c>
+      <c r="E8" s="35" t="n">
         <v>-115</v>
       </c>
-      <c r="F8" s="40" t="n">
+      <c r="F8" s="36" t="n">
         <v>175</v>
       </c>
-      <c r="G8" s="41" t="n">
+      <c r="G8" s="37" t="n">
         <f aca="false">IF(E8&gt;0,F8*E8/100,F8*100/ABS(E8))</f>
         <v>152.173913043478</v>
       </c>
-      <c r="H8" s="41" t="n">
+      <c r="H8" s="37" t="n">
         <f aca="false">F8+G8</f>
         <v>327.173913043478</v>
       </c>
-      <c r="I8" s="57" t="s">
-        <v>98</v>
-      </c>
-      <c r="J8" s="41" t="n">
+      <c r="I8" s="53" t="s">
+        <v>96</v>
+      </c>
+      <c r="J8" s="37" t="n">
         <f aca="false">IF(I8="Win",F8+G8,IF(I8="Push",F8,IF(I8="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K8" s="43" t="n">
+      <c r="K8" s="39" t="n">
         <f aca="false">IF(I8="Pending",0,J8-F8)</f>
         <v>-175</v>
       </c>
-      <c r="L8" s="73" t="n">
+      <c r="L8" s="70" t="n">
         <v>0.54</v>
       </c>
-      <c r="M8" s="62" t="s">
+      <c r="M8" s="58" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" s="5" t="s">
         <v>459</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="33" t="n">
-        <v>3</v>
-      </c>
-      <c r="B9" s="5" t="s">
+      <c r="C9" s="28" t="s">
         <v>460</v>
       </c>
-      <c r="C9" s="32" t="s">
-        <v>461</v>
-      </c>
-      <c r="D9" s="33" t="s">
-        <v>179</v>
-      </c>
-      <c r="E9" s="39" t="n">
+      <c r="D9" s="29" t="s">
+        <v>177</v>
+      </c>
+      <c r="E9" s="35" t="n">
         <v>-110</v>
       </c>
-      <c r="F9" s="40" t="n">
+      <c r="F9" s="36" t="n">
         <v>160</v>
       </c>
-      <c r="G9" s="41" t="n">
+      <c r="G9" s="37" t="n">
         <f aca="false">IF(E9&gt;0,F9*E9/100,F9*100/ABS(E9))</f>
         <v>145.454545454545</v>
       </c>
-      <c r="H9" s="41" t="n">
+      <c r="H9" s="37" t="n">
         <f aca="false">F9+G9</f>
         <v>305.454545454546</v>
       </c>
-      <c r="I9" s="57" t="s">
-        <v>90</v>
-      </c>
-      <c r="J9" s="41" t="n">
+      <c r="I9" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="J9" s="37" t="n">
         <f aca="false">IF(I9="Win",F9+G9,IF(I9="Push",F9,IF(I9="Loss",0,0)))</f>
         <v>305.454545454546</v>
       </c>
-      <c r="K9" s="43" t="n">
+      <c r="K9" s="39" t="n">
         <f aca="false">IF(I9="Pending",0,J9-F9)</f>
         <v>145.454545454546</v>
       </c>
-      <c r="L9" s="73" t="n">
+      <c r="L9" s="70" t="n">
         <v>0.55</v>
       </c>
-      <c r="M9" s="62" t="s">
+      <c r="M9" s="58" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="B10" s="5" t="s">
         <v>462</v>
       </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="33" t="n">
-        <v>4</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>463</v>
-      </c>
-      <c r="C10" s="32" t="s">
-        <v>393</v>
-      </c>
-      <c r="D10" s="33" t="s">
-        <v>94</v>
-      </c>
-      <c r="E10" s="39" t="n">
+      <c r="C10" s="28" t="s">
+        <v>392</v>
+      </c>
+      <c r="D10" s="29" t="s">
+        <v>92</v>
+      </c>
+      <c r="E10" s="35" t="n">
         <v>-110</v>
       </c>
-      <c r="F10" s="40" t="n">
+      <c r="F10" s="36" t="n">
         <v>150</v>
       </c>
-      <c r="G10" s="41" t="n">
+      <c r="G10" s="37" t="n">
         <f aca="false">IF(E10&gt;0,F10*E10/100,F10*100/ABS(E10))</f>
         <v>136.363636363636</v>
       </c>
-      <c r="H10" s="41" t="n">
+      <c r="H10" s="37" t="n">
         <f aca="false">F10+G10</f>
         <v>286.363636363636</v>
       </c>
-      <c r="I10" s="57" t="s">
-        <v>98</v>
-      </c>
-      <c r="J10" s="41" t="n">
+      <c r="I10" s="53" t="s">
+        <v>96</v>
+      </c>
+      <c r="J10" s="37" t="n">
         <f aca="false">IF(I10="Win",F10+G10,IF(I10="Push",F10,IF(I10="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K10" s="43" t="n">
+      <c r="K10" s="39" t="n">
         <f aca="false">IF(I10="Pending",0,J10-F10)</f>
         <v>-150</v>
       </c>
-      <c r="L10" s="73" t="n">
+      <c r="L10" s="70" t="n">
         <v>0.54</v>
       </c>
-      <c r="M10" s="62" t="s">
+      <c r="M10" s="58" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" s="5" t="s">
         <v>464</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="33" t="n">
-        <v>5</v>
-      </c>
-      <c r="B11" s="5" t="s">
+      <c r="C11" s="28" t="s">
         <v>465</v>
       </c>
-      <c r="C11" s="32" t="s">
-        <v>466</v>
-      </c>
-      <c r="D11" s="33" t="s">
-        <v>89</v>
-      </c>
-      <c r="E11" s="39" t="n">
+      <c r="D11" s="29" t="s">
+        <v>87</v>
+      </c>
+      <c r="E11" s="35" t="n">
         <v>-130</v>
       </c>
-      <c r="F11" s="40" t="n">
+      <c r="F11" s="36" t="n">
         <v>140</v>
       </c>
-      <c r="G11" s="41" t="n">
+      <c r="G11" s="37" t="n">
         <f aca="false">IF(E11&gt;0,F11*E11/100,F11*100/ABS(E11))</f>
         <v>107.692307692308</v>
       </c>
-      <c r="H11" s="41" t="n">
+      <c r="H11" s="37" t="n">
         <f aca="false">F11+G11</f>
         <v>247.692307692308</v>
       </c>
-      <c r="I11" s="57" t="s">
-        <v>90</v>
-      </c>
-      <c r="J11" s="41" t="n">
+      <c r="I11" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="J11" s="37" t="n">
         <f aca="false">IF(I11="Win",F11+G11,IF(I11="Push",F11,IF(I11="Loss",0,0)))</f>
         <v>247.692307692308</v>
       </c>
-      <c r="K11" s="43" t="n">
+      <c r="K11" s="39" t="n">
         <f aca="false">IF(I11="Pending",0,J11-F11)</f>
         <v>107.692307692308</v>
       </c>
-      <c r="L11" s="73" t="n">
+      <c r="L11" s="70" t="n">
         <v>0.58</v>
       </c>
-      <c r="M11" s="62" t="s">
+      <c r="M11" s="58" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" s="5" t="s">
         <v>467</v>
       </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="33" t="n">
-        <v>6</v>
-      </c>
-      <c r="B12" s="5" t="s">
+      <c r="C12" s="28" t="s">
         <v>468</v>
       </c>
-      <c r="C12" s="32" t="s">
-        <v>469</v>
-      </c>
-      <c r="D12" s="33" t="s">
-        <v>378</v>
-      </c>
-      <c r="E12" s="39" t="n">
+      <c r="D12" s="29" t="s">
+        <v>377</v>
+      </c>
+      <c r="E12" s="35" t="n">
         <v>-110</v>
       </c>
-      <c r="F12" s="40" t="n">
+      <c r="F12" s="36" t="n">
         <v>115</v>
       </c>
-      <c r="G12" s="41" t="n">
+      <c r="G12" s="37" t="n">
         <f aca="false">IF(E12&gt;0,F12*E12/100,F12*100/ABS(E12))</f>
         <v>104.545454545455</v>
       </c>
-      <c r="H12" s="41" t="n">
+      <c r="H12" s="37" t="n">
         <f aca="false">F12+G12</f>
         <v>219.545454545455</v>
       </c>
-      <c r="I12" s="57" t="s">
-        <v>98</v>
-      </c>
-      <c r="J12" s="41" t="n">
+      <c r="I12" s="53" t="s">
+        <v>96</v>
+      </c>
+      <c r="J12" s="37" t="n">
         <f aca="false">IF(I12="Win",F12+G12,IF(I12="Push",F12,IF(I12="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K12" s="43" t="n">
+      <c r="K12" s="39" t="n">
         <f aca="false">IF(I12="Pending",0,J12-F12)</f>
         <v>-115</v>
       </c>
-      <c r="L12" s="73" t="n">
+      <c r="L12" s="70" t="n">
         <v>0.52</v>
       </c>
-      <c r="M12" s="62" t="s">
+      <c r="M12" s="58" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="29" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="C13" s="28" t="s">
         <v>470</v>
       </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="33" t="n">
-        <v>7</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>395</v>
-      </c>
-      <c r="C13" s="32" t="s">
-        <v>471</v>
-      </c>
-      <c r="D13" s="33" t="s">
-        <v>117</v>
-      </c>
-      <c r="E13" s="39" t="n">
+      <c r="D13" s="29" t="s">
+        <v>115</v>
+      </c>
+      <c r="E13" s="35" t="n">
         <v>1133</v>
       </c>
-      <c r="F13" s="40" t="n">
+      <c r="F13" s="36" t="n">
         <v>75</v>
       </c>
-      <c r="G13" s="41" t="n">
+      <c r="G13" s="37" t="n">
         <f aca="false">IF(E13&gt;0,F13*E13/100,F13*100/ABS(E13))</f>
         <v>849.75</v>
       </c>
-      <c r="H13" s="41" t="n">
+      <c r="H13" s="37" t="n">
         <f aca="false">F13+G13</f>
         <v>924.75</v>
       </c>
-      <c r="I13" s="57" t="s">
-        <v>98</v>
-      </c>
-      <c r="J13" s="41" t="n">
+      <c r="I13" s="53" t="s">
+        <v>96</v>
+      </c>
+      <c r="J13" s="37" t="n">
         <f aca="false">IF(I13="Win",F13+G13,IF(I13="Push",F13,IF(I13="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K13" s="43" t="n">
+      <c r="K13" s="39" t="n">
         <f aca="false">IF(I13="Pending",0,J13-F13)</f>
         <v>-75</v>
       </c>
-      <c r="L13" s="73" t="n">
+      <c r="L13" s="70" t="n">
         <v>0.1</v>
       </c>
-      <c r="M13" s="62" t="s">
-        <v>472</v>
+      <c r="M13" s="58" t="s">
+        <v>471</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F14" s="8" t="n">
         <f aca="false">SUM(F7:F13)</f>
@@ -3592,6 +3706,278 @@
   </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="I7:I13" type="list">
+      <formula1>"Pending,Win,Loss,Push"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FF7A2E8D"/>
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:M10"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="50"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="85" t="s">
+        <v>472</v>
+      </c>
+      <c r="H1" s="86" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="87" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="87" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="88" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>198</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="G6" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="H6" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="I6" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="J6" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="K6" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="L6" s="12" t="s">
+        <v>218</v>
+      </c>
+      <c r="M6" s="12" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>476</v>
+      </c>
+      <c r="C7" s="28" t="s">
+        <v>477</v>
+      </c>
+      <c r="D7" s="29" t="s">
+        <v>478</v>
+      </c>
+      <c r="E7" s="35" t="n">
+        <v>-111</v>
+      </c>
+      <c r="F7" s="89" t="n">
+        <v>340</v>
+      </c>
+      <c r="G7" s="90" t="n">
+        <f aca="false">IF(E7&gt;0,F7*E7/100,F7*100/ABS(E7))</f>
+        <v>306.306306306306</v>
+      </c>
+      <c r="H7" s="90" t="n">
+        <f aca="false">F7+G7</f>
+        <v>646.306306306306</v>
+      </c>
+      <c r="I7" s="53" t="s">
+        <v>121</v>
+      </c>
+      <c r="J7" s="90" t="n">
+        <f aca="false">IF(I7="Win",F7+G7,IF(I7="Push",F7,IF(I7="Loss",0,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="K7" s="91" t="n">
+        <f aca="false">IF(I7="Pending",0,J7-F7)</f>
+        <v>0</v>
+      </c>
+      <c r="L7" s="70" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M7" s="58" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>480</v>
+      </c>
+      <c r="C8" s="28" t="s">
+        <v>481</v>
+      </c>
+      <c r="D8" s="29" t="s">
+        <v>478</v>
+      </c>
+      <c r="E8" s="35" t="n">
+        <v>-110</v>
+      </c>
+      <c r="F8" s="89" t="n">
+        <v>150</v>
+      </c>
+      <c r="G8" s="90" t="n">
+        <f aca="false">IF(E8&gt;0,F8*E8/100,F8*100/ABS(E8))</f>
+        <v>136.363636363636</v>
+      </c>
+      <c r="H8" s="90" t="n">
+        <f aca="false">F8+G8</f>
+        <v>286.363636363636</v>
+      </c>
+      <c r="I8" s="53" t="s">
+        <v>121</v>
+      </c>
+      <c r="J8" s="90" t="n">
+        <f aca="false">IF(I8="Win",F8+G8,IF(I8="Push",F8,IF(I8="Loss",0,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="K8" s="91" t="n">
+        <f aca="false">IF(I8="Pending",0,J8-F8)</f>
+        <v>0</v>
+      </c>
+      <c r="L8" s="70" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="M8" s="58" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>483</v>
+      </c>
+      <c r="C9" s="28" t="s">
+        <v>484</v>
+      </c>
+      <c r="D9" s="29" t="s">
+        <v>115</v>
+      </c>
+      <c r="E9" s="35" t="n">
+        <v>263</v>
+      </c>
+      <c r="F9" s="89" t="n">
+        <v>60</v>
+      </c>
+      <c r="G9" s="90" t="n">
+        <f aca="false">IF(E9&gt;0,F9*E9/100,F9*100/ABS(E9))</f>
+        <v>157.8</v>
+      </c>
+      <c r="H9" s="90" t="n">
+        <f aca="false">F9+G9</f>
+        <v>217.8</v>
+      </c>
+      <c r="I9" s="53" t="s">
+        <v>121</v>
+      </c>
+      <c r="J9" s="90" t="n">
+        <f aca="false">IF(I9="Win",F9+G9,IF(I9="Push",F9,IF(I9="Loss",0,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="K9" s="91" t="n">
+        <f aca="false">IF(I9="Pending",0,J9-F9)</f>
+        <v>0</v>
+      </c>
+      <c r="L9" s="70" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="M9" s="58" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="88" t="s">
+        <v>425</v>
+      </c>
+      <c r="F10" s="92" t="n">
+        <f aca="false">SUM(F7:F9)</f>
+        <v>550</v>
+      </c>
+      <c r="G10" s="92" t="n">
+        <f aca="false">SUM(G7:G9)</f>
+        <v>600.469942669943</v>
+      </c>
+      <c r="H10" s="92" t="n">
+        <f aca="false">SUM(H7:H9)</f>
+        <v>1150.46994266994</v>
+      </c>
+      <c r="J10" s="92" t="n">
+        <f aca="false">SUM(J7:J9)</f>
+        <v>0</v>
+      </c>
+      <c r="K10" s="92" t="n">
+        <f aca="false">SUM(K7:K9)</f>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="K7:K10">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+      <formula>AND(ISNUMBER(K7),K7&gt;0)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+      <formula>AND(ISNUMBER(K7),K7&lt;0)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="I7:I9" type="list">
       <formula1>"Pending,Win,Loss,Push"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -3628,26 +4014,26 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="35" t="s">
-        <v>72</v>
-      </c>
-      <c r="H1" s="36" t="s">
-        <v>73</v>
+      <c r="A1" s="31" t="s">
+        <v>70</v>
+      </c>
+      <c r="H1" s="32" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3655,546 +4041,546 @@
         <v>12</v>
       </c>
       <c r="B6" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="D6" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="E6" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="F6" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="G6" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="H6" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="F6" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="G6" s="12" t="s">
+      <c r="I6" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="H6" s="12" t="s">
+      <c r="J6" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="I6" s="12" t="s">
+      <c r="K6" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="J6" s="12" t="s">
+      <c r="L6" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="K6" s="12" t="s">
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="33" t="s">
         <v>85</v>
       </c>
-      <c r="L6" s="12" t="s">
+      <c r="C7" s="34" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="B7" s="37" t="s">
+      <c r="D7" s="29" t="s">
         <v>87</v>
       </c>
-      <c r="C7" s="38" t="s">
-        <v>88</v>
-      </c>
-      <c r="D7" s="33" t="s">
-        <v>89</v>
-      </c>
-      <c r="E7" s="39" t="n">
+      <c r="E7" s="35" t="n">
         <v>-265</v>
       </c>
-      <c r="F7" s="40" t="n">
+      <c r="F7" s="36" t="n">
         <v>265</v>
       </c>
-      <c r="G7" s="41" t="n">
+      <c r="G7" s="37" t="n">
         <f aca="false">IF(E7&gt;0,F7*E7/100,F7*100/ABS(E7))</f>
         <v>100</v>
       </c>
-      <c r="H7" s="41" t="n">
+      <c r="H7" s="37" t="n">
         <f aca="false">F7+G7</f>
         <v>365</v>
       </c>
-      <c r="I7" s="42" t="s">
-        <v>90</v>
-      </c>
-      <c r="J7" s="41" t="n">
+      <c r="I7" s="38" t="s">
+        <v>88</v>
+      </c>
+      <c r="J7" s="37" t="n">
         <f aca="false">IF(I7="Win",F7+G7,IF(I7="Push",F7,IF(I7="Loss",0,0)))</f>
         <v>365</v>
       </c>
-      <c r="K7" s="43" t="n">
+      <c r="K7" s="39" t="n">
         <f aca="false">IF(I7="Pending",0,J7-F7)</f>
         <v>100</v>
       </c>
-      <c r="L7" s="44" t="s">
+      <c r="L7" s="40" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="33" t="s">
+        <v>90</v>
+      </c>
+      <c r="C8" s="34" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="33" t="n">
-        <v>2</v>
-      </c>
-      <c r="B8" s="37" t="s">
+      <c r="D8" s="29" t="s">
         <v>92</v>
       </c>
-      <c r="C8" s="38" t="s">
-        <v>93</v>
-      </c>
-      <c r="D8" s="33" t="s">
-        <v>94</v>
-      </c>
-      <c r="E8" s="39" t="n">
+      <c r="E8" s="35" t="n">
         <v>-140</v>
       </c>
-      <c r="F8" s="40" t="n">
+      <c r="F8" s="36" t="n">
         <v>200</v>
       </c>
-      <c r="G8" s="41" t="n">
+      <c r="G8" s="37" t="n">
         <f aca="false">IF(E8&gt;0,F8*E8/100,F8*100/ABS(E8))</f>
         <v>142.857142857143</v>
       </c>
-      <c r="H8" s="41" t="n">
+      <c r="H8" s="37" t="n">
         <f aca="false">F8+G8</f>
         <v>342.857142857143</v>
       </c>
-      <c r="I8" s="42" t="s">
-        <v>90</v>
-      </c>
-      <c r="J8" s="41" t="n">
+      <c r="I8" s="38" t="s">
+        <v>88</v>
+      </c>
+      <c r="J8" s="37" t="n">
         <f aca="false">IF(I8="Win",F8+G8,IF(I8="Push",F8,IF(I8="Loss",0,0)))</f>
         <v>342.857142857143</v>
       </c>
-      <c r="K8" s="43" t="n">
+      <c r="K8" s="39" t="n">
         <f aca="false">IF(I8="Pending",0,J8-F8)</f>
         <v>142.857142857143</v>
       </c>
-      <c r="L8" s="44" t="s">
+      <c r="L8" s="40" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" s="33" t="s">
+        <v>94</v>
+      </c>
+      <c r="C9" s="34" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="33" t="n">
-        <v>3</v>
-      </c>
-      <c r="B9" s="37" t="s">
-        <v>96</v>
-      </c>
-      <c r="C9" s="38" t="s">
-        <v>97</v>
-      </c>
-      <c r="D9" s="33" t="s">
-        <v>89</v>
-      </c>
-      <c r="E9" s="39" t="n">
+      <c r="D9" s="29" t="s">
+        <v>87</v>
+      </c>
+      <c r="E9" s="35" t="n">
         <v>-148</v>
       </c>
-      <c r="F9" s="40" t="n">
+      <c r="F9" s="36" t="n">
         <v>148</v>
       </c>
-      <c r="G9" s="41" t="n">
+      <c r="G9" s="37" t="n">
         <f aca="false">IF(E9&gt;0,F9*E9/100,F9*100/ABS(E9))</f>
         <v>100</v>
       </c>
-      <c r="H9" s="41" t="n">
+      <c r="H9" s="37" t="n">
         <f aca="false">F9+G9</f>
         <v>248</v>
       </c>
-      <c r="I9" s="45" t="s">
-        <v>98</v>
-      </c>
-      <c r="J9" s="41" t="n">
+      <c r="I9" s="41" t="s">
+        <v>96</v>
+      </c>
+      <c r="J9" s="37" t="n">
         <f aca="false">IF(I9="Win",F9+G9,IF(I9="Push",F9,IF(I9="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K9" s="43" t="n">
+      <c r="K9" s="39" t="n">
         <f aca="false">IF(I9="Pending",0,J9-F9)</f>
         <v>-148</v>
       </c>
-      <c r="L9" s="44" t="s">
+      <c r="L9" s="40" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="B10" s="33" t="s">
+        <v>98</v>
+      </c>
+      <c r="C10" s="34" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="33" t="n">
-        <v>4</v>
-      </c>
-      <c r="B10" s="37" t="s">
+      <c r="D10" s="29" t="s">
+        <v>87</v>
+      </c>
+      <c r="E10" s="35" t="n">
+        <v>114</v>
+      </c>
+      <c r="F10" s="36" t="n">
         <v>100</v>
       </c>
-      <c r="C10" s="38" t="s">
-        <v>101</v>
-      </c>
-      <c r="D10" s="33" t="s">
-        <v>89</v>
-      </c>
-      <c r="E10" s="39" t="n">
-        <v>114</v>
-      </c>
-      <c r="F10" s="40" t="n">
-        <v>100</v>
-      </c>
-      <c r="G10" s="41" t="n">
+      <c r="G10" s="37" t="n">
         <f aca="false">IF(E10&gt;0,F10*E10/100,F10*100/ABS(E10))</f>
         <v>114</v>
       </c>
-      <c r="H10" s="41" t="n">
+      <c r="H10" s="37" t="n">
         <f aca="false">F10+G10</f>
         <v>214</v>
       </c>
-      <c r="I10" s="42" t="s">
-        <v>90</v>
-      </c>
-      <c r="J10" s="41" t="n">
+      <c r="I10" s="38" t="s">
+        <v>88</v>
+      </c>
+      <c r="J10" s="37" t="n">
         <f aca="false">IF(I10="Win",F10+G10,IF(I10="Push",F10,IF(I10="Loss",0,0)))</f>
         <v>214</v>
       </c>
-      <c r="K10" s="43" t="n">
+      <c r="K10" s="39" t="n">
         <f aca="false">IF(I10="Pending",0,J10-F10)</f>
         <v>114</v>
       </c>
-      <c r="L10" s="44" t="s">
+      <c r="L10" s="40" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" s="33" t="s">
+        <v>101</v>
+      </c>
+      <c r="C11" s="34" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="33" t="n">
-        <v>5</v>
-      </c>
-      <c r="B11" s="37" t="s">
-        <v>103</v>
-      </c>
-      <c r="C11" s="38" t="s">
-        <v>104</v>
-      </c>
-      <c r="D11" s="33" t="s">
-        <v>89</v>
-      </c>
-      <c r="E11" s="39" t="n">
+      <c r="D11" s="29" t="s">
+        <v>87</v>
+      </c>
+      <c r="E11" s="35" t="n">
         <v>-218</v>
       </c>
-      <c r="F11" s="40" t="n">
+      <c r="F11" s="36" t="n">
         <v>100</v>
       </c>
-      <c r="G11" s="41" t="n">
+      <c r="G11" s="37" t="n">
         <f aca="false">IF(E11&gt;0,F11*E11/100,F11*100/ABS(E11))</f>
         <v>45.8715596330275</v>
       </c>
-      <c r="H11" s="41" t="n">
+      <c r="H11" s="37" t="n">
         <f aca="false">F11+G11</f>
         <v>145.871559633028</v>
       </c>
-      <c r="I11" s="45" t="s">
-        <v>98</v>
-      </c>
-      <c r="J11" s="41" t="n">
+      <c r="I11" s="41" t="s">
+        <v>96</v>
+      </c>
+      <c r="J11" s="37" t="n">
         <f aca="false">IF(I11="Win",F11+G11,IF(I11="Push",F11,IF(I11="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K11" s="43" t="n">
+      <c r="K11" s="39" t="n">
         <f aca="false">IF(I11="Pending",0,J11-F11)</f>
         <v>-100</v>
       </c>
-      <c r="L11" s="44" t="s">
+      <c r="L11" s="40" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" s="33" t="s">
+        <v>104</v>
+      </c>
+      <c r="C12" s="34" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="33" t="n">
-        <v>6</v>
-      </c>
-      <c r="B12" s="37" t="s">
-        <v>106</v>
-      </c>
-      <c r="C12" s="38" t="s">
-        <v>107</v>
-      </c>
-      <c r="D12" s="33" t="s">
-        <v>89</v>
-      </c>
-      <c r="E12" s="39" t="n">
+      <c r="D12" s="29" t="s">
+        <v>87</v>
+      </c>
+      <c r="E12" s="35" t="n">
         <v>-125</v>
       </c>
-      <c r="F12" s="40" t="n">
+      <c r="F12" s="36" t="n">
         <v>75</v>
       </c>
-      <c r="G12" s="41" t="n">
+      <c r="G12" s="37" t="n">
         <f aca="false">IF(E12&gt;0,F12*E12/100,F12*100/ABS(E12))</f>
         <v>60</v>
       </c>
-      <c r="H12" s="41" t="n">
+      <c r="H12" s="37" t="n">
         <f aca="false">F12+G12</f>
         <v>135</v>
       </c>
-      <c r="I12" s="42" t="s">
-        <v>90</v>
-      </c>
-      <c r="J12" s="41" t="n">
+      <c r="I12" s="38" t="s">
+        <v>88</v>
+      </c>
+      <c r="J12" s="37" t="n">
         <f aca="false">IF(I12="Win",F12+G12,IF(I12="Push",F12,IF(I12="Loss",0,0)))</f>
         <v>135</v>
       </c>
-      <c r="K12" s="43" t="n">
+      <c r="K12" s="39" t="n">
         <f aca="false">IF(I12="Pending",0,J12-F12)</f>
         <v>60</v>
       </c>
-      <c r="L12" s="44" t="s">
+      <c r="L12" s="40" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="29" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" s="33" t="s">
+        <v>107</v>
+      </c>
+      <c r="C13" s="34" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="33" t="n">
-        <v>7</v>
-      </c>
-      <c r="B13" s="37" t="s">
-        <v>109</v>
-      </c>
-      <c r="C13" s="38" t="s">
-        <v>110</v>
-      </c>
-      <c r="D13" s="33" t="s">
-        <v>89</v>
-      </c>
-      <c r="E13" s="39" t="n">
+      <c r="D13" s="29" t="s">
+        <v>87</v>
+      </c>
+      <c r="E13" s="35" t="n">
         <v>-225</v>
       </c>
-      <c r="F13" s="40" t="n">
+      <c r="F13" s="36" t="n">
         <v>50</v>
       </c>
-      <c r="G13" s="41" t="n">
+      <c r="G13" s="37" t="n">
         <f aca="false">IF(E13&gt;0,F13*E13/100,F13*100/ABS(E13))</f>
         <v>22.2222222222222</v>
       </c>
-      <c r="H13" s="41" t="n">
+      <c r="H13" s="37" t="n">
         <f aca="false">F13+G13</f>
         <v>72.2222222222222</v>
       </c>
-      <c r="I13" s="42" t="s">
-        <v>90</v>
-      </c>
-      <c r="J13" s="41" t="n">
+      <c r="I13" s="38" t="s">
+        <v>88</v>
+      </c>
+      <c r="J13" s="37" t="n">
         <f aca="false">IF(I13="Win",F13+G13,IF(I13="Push",F13,IF(I13="Loss",0,0)))</f>
         <v>72.2222222222222</v>
       </c>
-      <c r="K13" s="43" t="n">
+      <c r="K13" s="39" t="n">
         <f aca="false">IF(I13="Pending",0,J13-F13)</f>
         <v>22.2222222222222</v>
       </c>
-      <c r="L13" s="44" t="s">
+      <c r="L13" s="40" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="29" t="n">
+        <v>8</v>
+      </c>
+      <c r="B14" s="33" t="s">
+        <v>110</v>
+      </c>
+      <c r="C14" s="34" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="33" t="n">
-        <v>8</v>
-      </c>
-      <c r="B14" s="37" t="s">
-        <v>112</v>
-      </c>
-      <c r="C14" s="38" t="s">
-        <v>113</v>
-      </c>
-      <c r="D14" s="33" t="s">
-        <v>89</v>
-      </c>
-      <c r="E14" s="39" t="n">
+      <c r="D14" s="29" t="s">
+        <v>87</v>
+      </c>
+      <c r="E14" s="35" t="n">
         <v>-258</v>
       </c>
-      <c r="F14" s="40" t="n">
+      <c r="F14" s="36" t="n">
         <v>62</v>
       </c>
-      <c r="G14" s="41" t="n">
+      <c r="G14" s="37" t="n">
         <f aca="false">IF(E14&gt;0,F14*E14/100,F14*100/ABS(E14))</f>
         <v>24.031007751938</v>
       </c>
-      <c r="H14" s="41" t="n">
+      <c r="H14" s="37" t="n">
         <f aca="false">F14+G14</f>
         <v>86.031007751938</v>
       </c>
-      <c r="I14" s="42" t="s">
-        <v>90</v>
-      </c>
-      <c r="J14" s="41" t="n">
+      <c r="I14" s="38" t="s">
+        <v>88</v>
+      </c>
+      <c r="J14" s="37" t="n">
         <f aca="false">IF(I14="Win",F14+G14,IF(I14="Push",F14,IF(I14="Loss",0,0)))</f>
         <v>86.031007751938</v>
       </c>
-      <c r="K14" s="43" t="n">
+      <c r="K14" s="39" t="n">
         <f aca="false">IF(I14="Pending",0,J14-F14)</f>
         <v>24.031007751938</v>
       </c>
-      <c r="L14" s="44" t="s">
+      <c r="L14" s="40" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="29" t="n">
+        <v>9</v>
+      </c>
+      <c r="B15" s="33" t="s">
+        <v>113</v>
+      </c>
+      <c r="C15" s="34" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="33" t="n">
-        <v>9</v>
-      </c>
-      <c r="B15" s="37" t="s">
+      <c r="D15" s="29" t="s">
         <v>115</v>
       </c>
-      <c r="C15" s="38" t="s">
-        <v>116</v>
-      </c>
-      <c r="D15" s="33" t="s">
-        <v>117</v>
-      </c>
-      <c r="E15" s="39" t="n">
+      <c r="E15" s="35" t="n">
         <v>443</v>
       </c>
-      <c r="F15" s="40" t="n">
+      <c r="F15" s="36" t="n">
         <v>50</v>
       </c>
-      <c r="G15" s="41" t="n">
+      <c r="G15" s="37" t="n">
         <f aca="false">IF(E15&gt;0,F15*E15/100,F15*100/ABS(E15))</f>
         <v>221.5</v>
       </c>
-      <c r="H15" s="41" t="n">
+      <c r="H15" s="37" t="n">
         <f aca="false">F15+G15</f>
         <v>271.5</v>
       </c>
-      <c r="I15" s="45" t="s">
-        <v>98</v>
-      </c>
-      <c r="J15" s="41" t="n">
+      <c r="I15" s="41" t="s">
+        <v>96</v>
+      </c>
+      <c r="J15" s="37" t="n">
         <f aca="false">IF(I15="Win",F15+G15,IF(I15="Push",F15,IF(I15="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K15" s="43" t="n">
+      <c r="K15" s="39" t="n">
         <f aca="false">IF(I15="Pending",0,J15-F15)</f>
         <v>-50</v>
       </c>
-      <c r="L15" s="44" t="s">
-        <v>118</v>
+      <c r="L15" s="40" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="46"/>
-      <c r="B16" s="47" t="s">
-        <v>39</v>
-      </c>
-      <c r="C16" s="46"/>
-      <c r="D16" s="46"/>
-      <c r="E16" s="46"/>
-      <c r="F16" s="48" t="n">
+      <c r="A16" s="42"/>
+      <c r="B16" s="43" t="s">
+        <v>38</v>
+      </c>
+      <c r="C16" s="42"/>
+      <c r="D16" s="42"/>
+      <c r="E16" s="42"/>
+      <c r="F16" s="44" t="n">
         <f aca="false">SUM(F7:F15)</f>
         <v>1050</v>
       </c>
-      <c r="G16" s="49" t="n">
+      <c r="G16" s="45" t="n">
         <f aca="false">SUM(G7:G15)</f>
         <v>830.481932464331</v>
       </c>
-      <c r="H16" s="49" t="n">
+      <c r="H16" s="45" t="n">
         <f aca="false">SUM(H7:H15)</f>
         <v>1880.48193246433</v>
       </c>
-      <c r="I16" s="46"/>
-      <c r="J16" s="49" t="n">
+      <c r="I16" s="42"/>
+      <c r="J16" s="45" t="n">
         <f aca="false">SUM(J7:J15)</f>
         <v>1215.1103728313</v>
       </c>
-      <c r="K16" s="50" t="n">
+      <c r="K16" s="46" t="n">
         <f aca="false">SUM(K7:K15)</f>
         <v>165.110372831303</v>
       </c>
-      <c r="L16" s="46"/>
+      <c r="L16" s="42"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="37" t="s">
-        <v>120</v>
-      </c>
-      <c r="C19" s="51" t="n">
+      <c r="B19" s="33" t="s">
+        <v>118</v>
+      </c>
+      <c r="C19" s="47" t="n">
         <f aca="false">COUNTIF(I7:I15,"Win")</f>
         <v>6</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="37" t="s">
-        <v>121</v>
-      </c>
-      <c r="C20" s="51" t="n">
+      <c r="B20" s="33" t="s">
+        <v>119</v>
+      </c>
+      <c r="C20" s="47" t="n">
         <f aca="false">COUNTIF(I7:I15,"Loss")</f>
         <v>3</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="37" t="s">
+      <c r="B21" s="33" t="s">
+        <v>120</v>
+      </c>
+      <c r="C21" s="47" t="n">
+        <f aca="false">COUNTIF(I7:I15,"Push")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B22" s="33" t="s">
+        <v>121</v>
+      </c>
+      <c r="C22" s="47" t="n">
+        <f aca="false">COUNTIF(I7:I15,"Pending")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B23" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="C21" s="51" t="n">
-        <f aca="false">COUNTIF(I7:I15,"Push")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="37" t="s">
-        <v>123</v>
-      </c>
-      <c r="C22" s="51" t="n">
-        <f aca="false">COUNTIF(I7:I15,"Pending")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="37" t="s">
-        <v>124</v>
-      </c>
-      <c r="C23" s="52" t="n">
+      <c r="C23" s="48" t="n">
         <f aca="false">IF(COUNTIF(I7:I15,"Win")+COUNTIF(I7:I15,"Loss")=0,"—",COUNTIF(I7:I15,"Win")/(COUNTIF(I7:I15,"Win")+COUNTIF(I7:I15,"Loss")))</f>
         <v>0.666666666666667</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="37" t="s">
-        <v>125</v>
-      </c>
-      <c r="C24" s="34" t="n">
+      <c r="B24" s="33" t="s">
+        <v>123</v>
+      </c>
+      <c r="C24" s="30" t="n">
         <f aca="false">SUM(F7:F15)</f>
         <v>1050</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="37" t="s">
-        <v>126</v>
-      </c>
-      <c r="C25" s="41" t="n">
+      <c r="B25" s="33" t="s">
+        <v>124</v>
+      </c>
+      <c r="C25" s="37" t="n">
         <f aca="false">SUM(J7:J15)</f>
         <v>1215.1103728313</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="37" t="s">
-        <v>127</v>
-      </c>
-      <c r="C26" s="43" t="n">
+      <c r="B26" s="33" t="s">
+        <v>125</v>
+      </c>
+      <c r="C26" s="39" t="n">
         <f aca="false">SUM(K7:K15)</f>
         <v>165.110372831303</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="37" t="s">
-        <v>128</v>
-      </c>
-      <c r="C27" s="52" t="n">
+      <c r="B27" s="33" t="s">
+        <v>126</v>
+      </c>
+      <c r="C27" s="48" t="n">
         <f aca="false">IF(SUM(F7:F15)=0,"—",SUM(K7:K15)/SUM(F7:F15))</f>
         <v>0.157247974125051</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="37" t="s">
-        <v>129</v>
-      </c>
-      <c r="C28" s="41" t="n">
+      <c r="B28" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="C28" s="37" t="n">
         <f aca="false">SUM(H7:H15)</f>
         <v>1880.48193246433</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4202,154 +4588,154 @@
         <v>12</v>
       </c>
       <c r="B31" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="C31" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="D31" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="C31" s="12" t="s">
+      <c r="E31" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="D31" s="12" t="s">
+      <c r="F31" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="E31" s="12" t="s">
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="B32" s="33" t="s">
         <v>134</v>
       </c>
-      <c r="F31" s="12" t="s">
+      <c r="C32" s="40" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="B32" s="37" t="s">
+      <c r="D32" s="49" t="s">
         <v>136</v>
       </c>
-      <c r="C32" s="44" t="s">
+      <c r="E32" s="50" t="s">
         <v>137</v>
       </c>
-      <c r="D32" s="53" t="s">
+      <c r="F32" s="50" t="s">
         <v>138</v>
       </c>
-      <c r="E32" s="54" t="s">
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="B33" s="33" t="s">
         <v>139</v>
       </c>
-      <c r="F32" s="54" t="s">
+      <c r="C33" s="40" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="33" t="n">
-        <v>2</v>
-      </c>
-      <c r="B33" s="37" t="s">
+      <c r="D33" s="49" t="s">
         <v>141</v>
       </c>
-      <c r="C33" s="44" t="s">
+      <c r="E33" s="50" t="s">
         <v>142</v>
       </c>
-      <c r="D33" s="53" t="s">
+      <c r="F33" s="50" t="s">
         <v>143</v>
       </c>
-      <c r="E33" s="54" t="s">
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="B34" s="33" t="s">
         <v>144</v>
       </c>
-      <c r="F33" s="54" t="s">
+      <c r="C34" s="40" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="33" t="n">
-        <v>3</v>
-      </c>
-      <c r="B34" s="37" t="s">
+      <c r="D34" s="49" t="s">
         <v>146</v>
       </c>
-      <c r="C34" s="44" t="s">
+      <c r="E34" s="50" t="s">
         <v>147</v>
       </c>
-      <c r="D34" s="53" t="s">
+      <c r="F34" s="50" t="s">
         <v>148</v>
       </c>
-      <c r="E34" s="54" t="s">
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="B35" s="33" t="s">
         <v>149</v>
       </c>
-      <c r="F34" s="54" t="s">
+      <c r="C35" s="40" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="33" t="n">
-        <v>4</v>
-      </c>
-      <c r="B35" s="37" t="s">
+      <c r="D35" s="49" t="s">
         <v>151</v>
       </c>
-      <c r="C35" s="44" t="s">
+      <c r="E35" s="50" t="s">
         <v>152</v>
       </c>
-      <c r="D35" s="53" t="s">
+      <c r="F35" s="50" t="s">
         <v>153</v>
       </c>
-      <c r="E35" s="54" t="s">
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="B36" s="33" t="s">
         <v>154</v>
       </c>
-      <c r="F35" s="54" t="s">
+      <c r="C36" s="40" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="33" t="n">
-        <v>5</v>
-      </c>
-      <c r="B36" s="37" t="s">
+      <c r="D36" s="49" t="s">
         <v>156</v>
       </c>
-      <c r="C36" s="44" t="s">
+      <c r="E36" s="50" t="s">
         <v>157</v>
       </c>
-      <c r="D36" s="53" t="s">
+      <c r="F36" s="50" t="s">
         <v>158</v>
       </c>
-      <c r="E36" s="54" t="s">
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="B37" s="33" t="s">
         <v>159</v>
       </c>
-      <c r="F36" s="54" t="s">
+      <c r="C37" s="40" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="33" t="n">
-        <v>6</v>
-      </c>
-      <c r="B37" s="37" t="s">
+      <c r="D37" s="49" t="s">
+        <v>46</v>
+      </c>
+      <c r="E37" s="50" t="s">
         <v>161</v>
       </c>
-      <c r="C37" s="44" t="s">
+      <c r="F37" s="50" t="s">
         <v>162</v>
       </c>
-      <c r="D37" s="53" t="s">
-        <v>47</v>
-      </c>
-      <c r="E37" s="54" t="s">
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="51" t="s">
         <v>163</v>
       </c>
-      <c r="F37" s="54" t="s">
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="51" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="55" t="s">
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="51" t="s">
         <v>165</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="55" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="55" t="s">
-        <v>167</v>
       </c>
     </row>
   </sheetData>
@@ -4406,26 +4792,26 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="35" t="s">
-        <v>168</v>
-      </c>
-      <c r="H1" s="56" t="s">
-        <v>169</v>
+      <c r="A1" s="31" t="s">
+        <v>166</v>
+      </c>
+      <c r="H1" s="52" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4433,462 +4819,462 @@
         <v>12</v>
       </c>
       <c r="B6" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="D6" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="E6" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="G6" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="H6" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="I6" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="J6" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="K6" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="L6" s="12" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="33" t="s">
+        <v>171</v>
+      </c>
+      <c r="C7" s="34" t="s">
         <v>172</v>
       </c>
-      <c r="D6" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="E6" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="F6" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="G6" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="H6" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="I6" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="J6" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="K6" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="L6" s="12" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="B7" s="37" t="s">
+      <c r="D7" s="29" t="s">
         <v>173</v>
       </c>
-      <c r="C7" s="38" t="s">
-        <v>174</v>
-      </c>
-      <c r="D7" s="33" t="s">
-        <v>175</v>
-      </c>
-      <c r="E7" s="39" t="n">
+      <c r="E7" s="35" t="n">
         <v>-144</v>
       </c>
-      <c r="F7" s="40" t="n">
+      <c r="F7" s="36" t="n">
         <v>300</v>
       </c>
-      <c r="G7" s="41" t="n">
+      <c r="G7" s="37" t="n">
         <f aca="false">IF(E7&gt;0,F7*E7/100,F7*100/ABS(E7))</f>
         <v>208.333333333333</v>
       </c>
-      <c r="H7" s="41" t="n">
+      <c r="H7" s="37" t="n">
         <f aca="false">F7+G7</f>
         <v>508.333333333333</v>
       </c>
-      <c r="I7" s="57" t="s">
-        <v>98</v>
-      </c>
-      <c r="J7" s="41" t="n">
+      <c r="I7" s="53" t="s">
+        <v>96</v>
+      </c>
+      <c r="J7" s="37" t="n">
         <f aca="false">IF(I7="Win",F7+G7,IF(I7="Push",F7,IF(I7="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K7" s="43" t="n">
+      <c r="K7" s="39" t="n">
         <f aca="false">IF(I7="Pending",0,J7-F7)</f>
         <v>-300</v>
       </c>
-      <c r="L7" s="44" t="s">
+      <c r="L7" s="40" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="33" t="s">
+        <v>175</v>
+      </c>
+      <c r="C8" s="34" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="33" t="n">
-        <v>2</v>
-      </c>
-      <c r="B8" s="37" t="s">
+      <c r="D8" s="29" t="s">
         <v>177</v>
       </c>
-      <c r="C8" s="38" t="s">
-        <v>178</v>
-      </c>
-      <c r="D8" s="33" t="s">
-        <v>179</v>
-      </c>
-      <c r="E8" s="39" t="n">
+      <c r="E8" s="35" t="n">
         <v>-122</v>
       </c>
-      <c r="F8" s="40" t="n">
+      <c r="F8" s="36" t="n">
         <v>120</v>
       </c>
-      <c r="G8" s="41" t="n">
+      <c r="G8" s="37" t="n">
         <f aca="false">IF(E8&gt;0,F8*E8/100,F8*100/ABS(E8))</f>
         <v>98.3606557377049</v>
       </c>
-      <c r="H8" s="41" t="n">
+      <c r="H8" s="37" t="n">
         <f aca="false">F8+G8</f>
         <v>218.360655737705</v>
       </c>
-      <c r="I8" s="57" t="s">
-        <v>90</v>
-      </c>
-      <c r="J8" s="41" t="n">
+      <c r="I8" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="J8" s="37" t="n">
         <f aca="false">IF(I8="Win",F8+G8,IF(I8="Push",F8,IF(I8="Loss",0,0)))</f>
         <v>218.360655737705</v>
       </c>
-      <c r="K8" s="43" t="n">
+      <c r="K8" s="39" t="n">
         <f aca="false">IF(I8="Pending",0,J8-F8)</f>
         <v>98.3606557377049</v>
       </c>
-      <c r="L8" s="44" t="s">
+      <c r="L8" s="40" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" s="33" t="s">
+        <v>179</v>
+      </c>
+      <c r="C9" s="34" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="33" t="n">
-        <v>3</v>
-      </c>
-      <c r="B9" s="37" t="s">
+      <c r="D9" s="29" t="s">
         <v>181</v>
       </c>
-      <c r="C9" s="38" t="s">
-        <v>182</v>
-      </c>
-      <c r="D9" s="33" t="s">
-        <v>183</v>
-      </c>
-      <c r="E9" s="39" t="n">
+      <c r="E9" s="35" t="n">
         <v>175</v>
       </c>
-      <c r="F9" s="40" t="n">
+      <c r="F9" s="36" t="n">
         <v>150</v>
       </c>
-      <c r="G9" s="41" t="n">
+      <c r="G9" s="37" t="n">
         <f aca="false">IF(E9&gt;0,F9*E9/100,F9*100/ABS(E9))</f>
         <v>262.5</v>
       </c>
-      <c r="H9" s="41" t="n">
+      <c r="H9" s="37" t="n">
         <f aca="false">F9+G9</f>
         <v>412.5</v>
       </c>
-      <c r="I9" s="57" t="s">
-        <v>90</v>
-      </c>
-      <c r="J9" s="41" t="n">
+      <c r="I9" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="J9" s="37" t="n">
         <f aca="false">IF(I9="Win",F9+G9,IF(I9="Push",F9,IF(I9="Loss",0,0)))</f>
         <v>412.5</v>
       </c>
-      <c r="K9" s="43" t="n">
+      <c r="K9" s="39" t="n">
         <f aca="false">IF(I9="Pending",0,J9-F9)</f>
         <v>262.5</v>
       </c>
-      <c r="L9" s="44" t="s">
+      <c r="L9" s="40" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="B10" s="33" t="s">
+        <v>183</v>
+      </c>
+      <c r="C10" s="34" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="33" t="n">
-        <v>4</v>
-      </c>
-      <c r="B10" s="37" t="s">
-        <v>185</v>
-      </c>
-      <c r="C10" s="38" t="s">
-        <v>186</v>
-      </c>
-      <c r="D10" s="33" t="s">
-        <v>183</v>
-      </c>
-      <c r="E10" s="39" t="n">
+      <c r="D10" s="29" t="s">
+        <v>181</v>
+      </c>
+      <c r="E10" s="35" t="n">
         <v>205</v>
       </c>
-      <c r="F10" s="40" t="n">
+      <c r="F10" s="36" t="n">
         <v>80</v>
       </c>
-      <c r="G10" s="41" t="n">
+      <c r="G10" s="37" t="n">
         <f aca="false">IF(E10&gt;0,F10*E10/100,F10*100/ABS(E10))</f>
         <v>164</v>
       </c>
-      <c r="H10" s="41" t="n">
+      <c r="H10" s="37" t="n">
         <f aca="false">F10+G10</f>
         <v>244</v>
       </c>
-      <c r="I10" s="57" t="s">
-        <v>98</v>
-      </c>
-      <c r="J10" s="41" t="n">
+      <c r="I10" s="53" t="s">
+        <v>96</v>
+      </c>
+      <c r="J10" s="37" t="n">
         <f aca="false">IF(I10="Win",F10+G10,IF(I10="Push",F10,IF(I10="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K10" s="43" t="n">
+      <c r="K10" s="39" t="n">
         <f aca="false">IF(I10="Pending",0,J10-F10)</f>
         <v>-80</v>
       </c>
-      <c r="L10" s="44" t="s">
+      <c r="L10" s="40" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" s="33" t="s">
+        <v>186</v>
+      </c>
+      <c r="C11" s="34" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="33" t="n">
-        <v>5</v>
-      </c>
-      <c r="B11" s="37" t="s">
+      <c r="D11" s="29" t="s">
         <v>188</v>
       </c>
-      <c r="C11" s="38" t="s">
-        <v>189</v>
-      </c>
-      <c r="D11" s="33" t="s">
-        <v>190</v>
-      </c>
-      <c r="E11" s="39" t="n">
+      <c r="E11" s="35" t="n">
         <v>160</v>
       </c>
-      <c r="F11" s="40" t="n">
+      <c r="F11" s="36" t="n">
         <v>250</v>
       </c>
-      <c r="G11" s="41" t="n">
+      <c r="G11" s="37" t="n">
         <f aca="false">IF(E11&gt;0,F11*E11/100,F11*100/ABS(E11))</f>
         <v>400</v>
       </c>
-      <c r="H11" s="41" t="n">
+      <c r="H11" s="37" t="n">
         <f aca="false">F11+G11</f>
         <v>650</v>
       </c>
-      <c r="I11" s="57" t="s">
-        <v>98</v>
-      </c>
-      <c r="J11" s="41" t="n">
+      <c r="I11" s="53" t="s">
+        <v>96</v>
+      </c>
+      <c r="J11" s="37" t="n">
         <f aca="false">IF(I11="Win",F11+G11,IF(I11="Push",F11,IF(I11="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K11" s="43" t="n">
+      <c r="K11" s="39" t="n">
         <f aca="false">IF(I11="Pending",0,J11-F11)</f>
         <v>-250</v>
       </c>
-      <c r="L11" s="44" t="s">
+      <c r="L11" s="40" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" s="33" t="s">
+        <v>190</v>
+      </c>
+      <c r="C12" s="34" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="33" t="n">
-        <v>6</v>
-      </c>
-      <c r="B12" s="37" t="s">
-        <v>192</v>
-      </c>
-      <c r="C12" s="38" t="s">
-        <v>193</v>
-      </c>
-      <c r="D12" s="33" t="s">
-        <v>190</v>
-      </c>
-      <c r="E12" s="39" t="n">
+      <c r="D12" s="29" t="s">
+        <v>188</v>
+      </c>
+      <c r="E12" s="35" t="n">
         <v>500</v>
       </c>
-      <c r="F12" s="40" t="n">
+      <c r="F12" s="36" t="n">
         <v>50</v>
       </c>
-      <c r="G12" s="41" t="n">
+      <c r="G12" s="37" t="n">
         <f aca="false">IF(E12&gt;0,F12*E12/100,F12*100/ABS(E12))</f>
         <v>250</v>
       </c>
-      <c r="H12" s="41" t="n">
+      <c r="H12" s="37" t="n">
         <f aca="false">F12+G12</f>
         <v>300</v>
       </c>
-      <c r="I12" s="57" t="s">
-        <v>98</v>
-      </c>
-      <c r="J12" s="41" t="n">
+      <c r="I12" s="53" t="s">
+        <v>96</v>
+      </c>
+      <c r="J12" s="37" t="n">
         <f aca="false">IF(I12="Win",F12+G12,IF(I12="Push",F12,IF(I12="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K12" s="43" t="n">
+      <c r="K12" s="39" t="n">
         <f aca="false">IF(I12="Pending",0,J12-F12)</f>
         <v>-50</v>
       </c>
-      <c r="L12" s="44" t="s">
+      <c r="L12" s="40" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="29" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" s="33" t="s">
+        <v>193</v>
+      </c>
+      <c r="C13" s="34" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="33" t="n">
-        <v>7</v>
-      </c>
-      <c r="B13" s="37" t="s">
-        <v>195</v>
-      </c>
-      <c r="C13" s="38" t="s">
-        <v>196</v>
-      </c>
-      <c r="D13" s="33" t="s">
-        <v>117</v>
-      </c>
-      <c r="E13" s="39" t="n">
+      <c r="D13" s="29" t="s">
+        <v>115</v>
+      </c>
+      <c r="E13" s="35" t="n">
         <v>179</v>
       </c>
-      <c r="F13" s="40" t="n">
+      <c r="F13" s="36" t="n">
         <v>50</v>
       </c>
-      <c r="G13" s="41" t="n">
+      <c r="G13" s="37" t="n">
         <f aca="false">IF(E13&gt;0,F13*E13/100,F13*100/ABS(E13))</f>
         <v>89.5</v>
       </c>
-      <c r="H13" s="41" t="n">
+      <c r="H13" s="37" t="n">
         <f aca="false">F13+G13</f>
         <v>139.5</v>
       </c>
-      <c r="I13" s="57" t="s">
-        <v>98</v>
-      </c>
-      <c r="J13" s="41" t="n">
+      <c r="I13" s="53" t="s">
+        <v>96</v>
+      </c>
+      <c r="J13" s="37" t="n">
         <f aca="false">IF(I13="Win",F13+G13,IF(I13="Push",F13,IF(I13="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K13" s="43" t="n">
+      <c r="K13" s="39" t="n">
         <f aca="false">IF(I13="Pending",0,J13-F13)</f>
         <v>-50</v>
       </c>
-      <c r="L13" s="44" t="s">
-        <v>197</v>
+      <c r="L13" s="40" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="46"/>
-      <c r="B14" s="47" t="s">
-        <v>39</v>
-      </c>
-      <c r="C14" s="46"/>
-      <c r="D14" s="46"/>
-      <c r="E14" s="46"/>
-      <c r="F14" s="48" t="n">
+      <c r="A14" s="42"/>
+      <c r="B14" s="43" t="s">
+        <v>38</v>
+      </c>
+      <c r="C14" s="42"/>
+      <c r="D14" s="42"/>
+      <c r="E14" s="42"/>
+      <c r="F14" s="44" t="n">
         <f aca="false">SUM(F7:F13)</f>
         <v>1000</v>
       </c>
-      <c r="G14" s="49" t="n">
+      <c r="G14" s="45" t="n">
         <f aca="false">SUM(G7:G13)</f>
         <v>1472.69398907104</v>
       </c>
-      <c r="H14" s="49" t="n">
+      <c r="H14" s="45" t="n">
         <f aca="false">SUM(H7:H13)</f>
         <v>2472.69398907104</v>
       </c>
-      <c r="I14" s="46"/>
-      <c r="J14" s="49" t="n">
+      <c r="I14" s="42"/>
+      <c r="J14" s="45" t="n">
         <f aca="false">SUM(J7:J13)</f>
         <v>630.860655737705</v>
       </c>
-      <c r="K14" s="50" t="n">
+      <c r="K14" s="46" t="n">
         <f aca="false">SUM(K7:K13)</f>
         <v>-369.139344262295</v>
       </c>
-      <c r="L14" s="46"/>
+      <c r="L14" s="42"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="37" t="s">
-        <v>120</v>
-      </c>
-      <c r="C17" s="51" t="n">
+      <c r="B17" s="33" t="s">
+        <v>118</v>
+      </c>
+      <c r="C17" s="47" t="n">
         <f aca="false">COUNTIF(I7:I13,"Win")</f>
         <v>2</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="37" t="s">
-        <v>121</v>
-      </c>
-      <c r="C18" s="51" t="n">
+      <c r="B18" s="33" t="s">
+        <v>119</v>
+      </c>
+      <c r="C18" s="47" t="n">
         <f aca="false">COUNTIF(I7:I13,"Loss")</f>
         <v>5</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="37" t="s">
+      <c r="B19" s="33" t="s">
+        <v>120</v>
+      </c>
+      <c r="C19" s="47" t="n">
+        <f aca="false">COUNTIF(I7:I13,"Push")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B20" s="33" t="s">
+        <v>121</v>
+      </c>
+      <c r="C20" s="47" t="n">
+        <f aca="false">COUNTIF(I7:I13,"Pending")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B21" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="C19" s="51" t="n">
-        <f aca="false">COUNTIF(I7:I13,"Push")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="37" t="s">
-        <v>123</v>
-      </c>
-      <c r="C20" s="51" t="n">
-        <f aca="false">COUNTIF(I7:I13,"Pending")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="37" t="s">
-        <v>124</v>
-      </c>
-      <c r="C21" s="52" t="n">
+      <c r="C21" s="48" t="n">
         <f aca="false">IF(COUNTIF(I7:I13,"Win")+COUNTIF(I7:I13,"Loss")=0,"—",COUNTIF(I7:I13,"Win")/(COUNTIF(I7:I13,"Win")+COUNTIF(I7:I13,"Loss")))</f>
         <v>0.285714285714286</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="37" t="s">
-        <v>125</v>
-      </c>
-      <c r="C22" s="34" t="n">
+      <c r="B22" s="33" t="s">
+        <v>123</v>
+      </c>
+      <c r="C22" s="30" t="n">
         <f aca="false">SUM(F7:F13)</f>
         <v>1000</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="37" t="s">
-        <v>126</v>
-      </c>
-      <c r="C23" s="41" t="n">
+      <c r="B23" s="33" t="s">
+        <v>124</v>
+      </c>
+      <c r="C23" s="37" t="n">
         <f aca="false">SUM(J7:J13)</f>
         <v>630.860655737705</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="37" t="s">
-        <v>127</v>
-      </c>
-      <c r="C24" s="43" t="n">
+      <c r="B24" s="33" t="s">
+        <v>125</v>
+      </c>
+      <c r="C24" s="39" t="n">
         <f aca="false">SUM(K7:K13)</f>
         <v>-369.139344262295</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="37" t="s">
-        <v>128</v>
-      </c>
-      <c r="C25" s="52" t="n">
+      <c r="B25" s="33" t="s">
+        <v>126</v>
+      </c>
+      <c r="C25" s="48" t="n">
         <f aca="false">IF(SUM(F7:F13)=0,"—",SUM(K7:K13)/SUM(F7:F13))</f>
         <v>-0.369139344262295</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="37" t="s">
-        <v>198</v>
-      </c>
-      <c r="C26" s="34" t="n">
+      <c r="B26" s="33" t="s">
+        <v>196</v>
+      </c>
+      <c r="C26" s="30" t="n">
         <f aca="false">929</f>
         <v>929</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4896,88 +5282,88 @@
         <v>12</v>
       </c>
       <c r="B29" s="12" t="s">
+        <v>198</v>
+      </c>
+      <c r="C29" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="D29" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="E29" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="F29" s="12" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="B30" s="33" t="s">
         <v>200</v>
       </c>
-      <c r="C29" s="12" t="s">
-        <v>132</v>
-      </c>
-      <c r="D29" s="12" t="s">
-        <v>133</v>
-      </c>
-      <c r="E29" s="12" t="s">
+      <c r="C30" s="40" t="s">
         <v>201</v>
       </c>
-      <c r="F29" s="12" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="B30" s="37" t="s">
+      <c r="D30" s="49" t="s">
         <v>202</v>
       </c>
-      <c r="C30" s="44" t="s">
+      <c r="E30" s="53"/>
+      <c r="F30" s="53"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="B31" s="33" t="s">
         <v>203</v>
       </c>
-      <c r="D30" s="53" t="s">
+      <c r="C31" s="40" t="s">
         <v>204</v>
       </c>
-      <c r="E30" s="57"/>
-      <c r="F30" s="57"/>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="33" t="n">
-        <v>2</v>
-      </c>
-      <c r="B31" s="37" t="s">
+      <c r="D31" s="49" t="s">
         <v>205</v>
       </c>
-      <c r="C31" s="44" t="s">
+      <c r="E31" s="53"/>
+      <c r="F31" s="53"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="B32" s="33" t="s">
         <v>206</v>
       </c>
-      <c r="D31" s="53" t="s">
+      <c r="C32" s="40" t="s">
         <v>207</v>
       </c>
-      <c r="E31" s="57"/>
-      <c r="F31" s="57"/>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="33" t="n">
-        <v>3</v>
-      </c>
-      <c r="B32" s="37" t="s">
+      <c r="D32" s="49" t="s">
         <v>208</v>
       </c>
-      <c r="C32" s="44" t="s">
+      <c r="E32" s="53"/>
+      <c r="F32" s="53"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="B33" s="33" t="s">
         <v>209</v>
       </c>
-      <c r="D32" s="53" t="s">
+      <c r="C33" s="40" t="s">
         <v>210</v>
       </c>
-      <c r="E32" s="57"/>
-      <c r="F32" s="57"/>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="33" t="n">
-        <v>4</v>
-      </c>
-      <c r="B33" s="37" t="s">
+      <c r="D33" s="49" t="s">
         <v>211</v>
       </c>
-      <c r="C33" s="44" t="s">
+      <c r="E33" s="53"/>
+      <c r="F33" s="53"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="51" t="s">
         <v>212</v>
-      </c>
-      <c r="D33" s="53" t="s">
-        <v>213</v>
-      </c>
-      <c r="E33" s="57"/>
-      <c r="F33" s="57"/>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="55" t="s">
-        <v>214</v>
       </c>
     </row>
   </sheetData>
@@ -5035,26 +5421,26 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="35" t="s">
-        <v>215</v>
-      </c>
-      <c r="H1" s="36" t="s">
-        <v>216</v>
+      <c r="A1" s="31" t="s">
+        <v>213</v>
+      </c>
+      <c r="H1" s="32" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5062,553 +5448,553 @@
         <v>12</v>
       </c>
       <c r="B6" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="D6" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="E6" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="G6" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="H6" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="I6" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="J6" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="K6" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="L6" s="12" t="s">
+        <v>218</v>
+      </c>
+      <c r="M6" s="12" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="33" t="s">
         <v>219</v>
       </c>
-      <c r="D6" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="E6" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="F6" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="G6" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="H6" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="I6" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="J6" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="K6" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="L6" s="12" t="s">
+      <c r="C7" s="34" t="s">
         <v>220</v>
       </c>
-      <c r="M6" s="12" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="B7" s="37" t="s">
-        <v>221</v>
-      </c>
-      <c r="C7" s="38" t="s">
-        <v>222</v>
-      </c>
-      <c r="D7" s="33" t="s">
-        <v>89</v>
-      </c>
-      <c r="E7" s="39" t="n">
+      <c r="D7" s="29" t="s">
+        <v>87</v>
+      </c>
+      <c r="E7" s="35" t="n">
         <v>-155</v>
       </c>
-      <c r="F7" s="40" t="n">
+      <c r="F7" s="36" t="n">
         <v>200</v>
       </c>
-      <c r="G7" s="41" t="n">
+      <c r="G7" s="37" t="n">
         <f aca="false">IF(E7&gt;0,F7*E7/100,F7*100/ABS(E7))</f>
         <v>129.032258064516</v>
       </c>
-      <c r="H7" s="41" t="n">
+      <c r="H7" s="37" t="n">
         <f aca="false">F7+G7</f>
         <v>329.032258064516</v>
       </c>
-      <c r="I7" s="42" t="s">
-        <v>90</v>
-      </c>
-      <c r="J7" s="41" t="n">
+      <c r="I7" s="38" t="s">
+        <v>88</v>
+      </c>
+      <c r="J7" s="37" t="n">
         <f aca="false">IF(I7="Win",F7+G7,IF(I7="Push",F7,IF(I7="Loss",0,0)))</f>
         <v>329.032258064516</v>
       </c>
-      <c r="K7" s="43" t="n">
+      <c r="K7" s="39" t="n">
         <f aca="false">IF(I7="Pending",0,J7-F7)</f>
         <v>129.032258064516</v>
       </c>
-      <c r="L7" s="58" t="n">
+      <c r="L7" s="54" t="n">
         <v>0.62</v>
       </c>
-      <c r="M7" s="44" t="s">
+      <c r="M7" s="40" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="33" t="s">
+        <v>222</v>
+      </c>
+      <c r="C8" s="34" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="33" t="n">
-        <v>2</v>
-      </c>
-      <c r="B8" s="37" t="s">
-        <v>224</v>
-      </c>
-      <c r="C8" s="38" t="s">
-        <v>225</v>
-      </c>
-      <c r="D8" s="33" t="s">
-        <v>89</v>
-      </c>
-      <c r="E8" s="39" t="n">
+      <c r="D8" s="29" t="s">
+        <v>87</v>
+      </c>
+      <c r="E8" s="35" t="n">
         <v>-104</v>
       </c>
-      <c r="F8" s="40" t="n">
+      <c r="F8" s="36" t="n">
         <v>150</v>
       </c>
-      <c r="G8" s="41" t="n">
+      <c r="G8" s="37" t="n">
         <f aca="false">IF(E8&gt;0,F8*E8/100,F8*100/ABS(E8))</f>
         <v>144.230769230769</v>
       </c>
-      <c r="H8" s="41" t="n">
+      <c r="H8" s="37" t="n">
         <f aca="false">F8+G8</f>
         <v>294.230769230769</v>
       </c>
-      <c r="I8" s="45" t="s">
-        <v>98</v>
-      </c>
-      <c r="J8" s="41" t="n">
+      <c r="I8" s="41" t="s">
+        <v>96</v>
+      </c>
+      <c r="J8" s="37" t="n">
         <f aca="false">IF(I8="Win",F8+G8,IF(I8="Push",F8,IF(I8="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K8" s="43" t="n">
+      <c r="K8" s="39" t="n">
         <f aca="false">IF(I8="Pending",0,J8-F8)</f>
         <v>-150</v>
       </c>
-      <c r="L8" s="58" t="n">
+      <c r="L8" s="54" t="n">
         <v>0.54</v>
       </c>
-      <c r="M8" s="44" t="s">
+      <c r="M8" s="40" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" s="33" t="s">
+        <v>225</v>
+      </c>
+      <c r="C9" s="34" t="s">
         <v>226</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="33" t="n">
-        <v>3</v>
-      </c>
-      <c r="B9" s="37" t="s">
-        <v>227</v>
-      </c>
-      <c r="C9" s="38" t="s">
-        <v>228</v>
-      </c>
-      <c r="D9" s="33" t="s">
-        <v>89</v>
-      </c>
-      <c r="E9" s="39" t="n">
+      <c r="D9" s="29" t="s">
+        <v>87</v>
+      </c>
+      <c r="E9" s="35" t="n">
         <v>-115</v>
       </c>
-      <c r="F9" s="40" t="n">
+      <c r="F9" s="36" t="n">
         <v>150</v>
       </c>
-      <c r="G9" s="41" t="n">
+      <c r="G9" s="37" t="n">
         <f aca="false">IF(E9&gt;0,F9*E9/100,F9*100/ABS(E9))</f>
         <v>130.434782608696</v>
       </c>
-      <c r="H9" s="41" t="n">
+      <c r="H9" s="37" t="n">
         <f aca="false">F9+G9</f>
         <v>280.434782608696</v>
       </c>
-      <c r="I9" s="45" t="s">
-        <v>98</v>
-      </c>
-      <c r="J9" s="41" t="n">
+      <c r="I9" s="41" t="s">
+        <v>96</v>
+      </c>
+      <c r="J9" s="37" t="n">
         <f aca="false">IF(I9="Win",F9+G9,IF(I9="Push",F9,IF(I9="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K9" s="43" t="n">
+      <c r="K9" s="39" t="n">
         <f aca="false">IF(I9="Pending",0,J9-F9)</f>
         <v>-150</v>
       </c>
-      <c r="L9" s="58" t="n">
+      <c r="L9" s="54" t="n">
         <v>0.55</v>
       </c>
-      <c r="M9" s="44" t="s">
+      <c r="M9" s="40" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="B10" s="33" t="s">
+        <v>228</v>
+      </c>
+      <c r="C10" s="34" t="s">
         <v>229</v>
       </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="33" t="n">
-        <v>4</v>
-      </c>
-      <c r="B10" s="37" t="s">
-        <v>230</v>
-      </c>
-      <c r="C10" s="38" t="s">
-        <v>231</v>
-      </c>
-      <c r="D10" s="33" t="s">
-        <v>179</v>
-      </c>
-      <c r="E10" s="39" t="n">
+      <c r="D10" s="29" t="s">
+        <v>177</v>
+      </c>
+      <c r="E10" s="35" t="n">
         <v>-114</v>
       </c>
-      <c r="F10" s="40" t="n">
+      <c r="F10" s="36" t="n">
         <v>120</v>
       </c>
-      <c r="G10" s="41" t="n">
+      <c r="G10" s="37" t="n">
         <f aca="false">IF(E10&gt;0,F10*E10/100,F10*100/ABS(E10))</f>
         <v>105.263157894737</v>
       </c>
-      <c r="H10" s="41" t="n">
+      <c r="H10" s="37" t="n">
         <f aca="false">F10+G10</f>
         <v>225.263157894737</v>
       </c>
-      <c r="I10" s="45" t="s">
-        <v>98</v>
-      </c>
-      <c r="J10" s="41" t="n">
+      <c r="I10" s="41" t="s">
+        <v>96</v>
+      </c>
+      <c r="J10" s="37" t="n">
         <f aca="false">IF(I10="Win",F10+G10,IF(I10="Push",F10,IF(I10="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K10" s="43" t="n">
+      <c r="K10" s="39" t="n">
         <f aca="false">IF(I10="Pending",0,J10-F10)</f>
         <v>-120</v>
       </c>
-      <c r="L10" s="58" t="n">
+      <c r="L10" s="54" t="n">
         <v>0.55</v>
       </c>
-      <c r="M10" s="44" t="s">
+      <c r="M10" s="40" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" s="33" t="s">
+        <v>231</v>
+      </c>
+      <c r="C11" s="34" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="33" t="n">
-        <v>5</v>
-      </c>
-      <c r="B11" s="37" t="s">
-        <v>233</v>
-      </c>
-      <c r="C11" s="38" t="s">
-        <v>234</v>
-      </c>
-      <c r="D11" s="33" t="s">
-        <v>89</v>
-      </c>
-      <c r="E11" s="39" t="n">
+      <c r="D11" s="29" t="s">
+        <v>87</v>
+      </c>
+      <c r="E11" s="35" t="n">
         <v>104</v>
       </c>
-      <c r="F11" s="40" t="n">
+      <c r="F11" s="36" t="n">
         <v>130</v>
       </c>
-      <c r="G11" s="41" t="n">
+      <c r="G11" s="37" t="n">
         <f aca="false">IF(E11&gt;0,F11*E11/100,F11*100/ABS(E11))</f>
         <v>135.2</v>
       </c>
-      <c r="H11" s="41" t="n">
+      <c r="H11" s="37" t="n">
         <f aca="false">F11+G11</f>
         <v>265.2</v>
       </c>
-      <c r="I11" s="42" t="s">
-        <v>90</v>
-      </c>
-      <c r="J11" s="41" t="n">
+      <c r="I11" s="38" t="s">
+        <v>88</v>
+      </c>
+      <c r="J11" s="37" t="n">
         <f aca="false">IF(I11="Win",F11+G11,IF(I11="Push",F11,IF(I11="Loss",0,0)))</f>
         <v>265.2</v>
       </c>
-      <c r="K11" s="43" t="n">
+      <c r="K11" s="39" t="n">
         <f aca="false">IF(I11="Pending",0,J11-F11)</f>
         <v>135.2</v>
       </c>
-      <c r="L11" s="58" t="n">
+      <c r="L11" s="54" t="n">
         <v>0.52</v>
       </c>
-      <c r="M11" s="44" t="s">
+      <c r="M11" s="40" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" s="33" t="s">
+        <v>234</v>
+      </c>
+      <c r="C12" s="34" t="s">
         <v>235</v>
       </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="33" t="n">
-        <v>6</v>
-      </c>
-      <c r="B12" s="37" t="s">
-        <v>236</v>
-      </c>
-      <c r="C12" s="38" t="s">
-        <v>237</v>
-      </c>
-      <c r="D12" s="33" t="s">
-        <v>89</v>
-      </c>
-      <c r="E12" s="39" t="n">
+      <c r="D12" s="29" t="s">
+        <v>87</v>
+      </c>
+      <c r="E12" s="35" t="n">
         <v>108</v>
       </c>
-      <c r="F12" s="40" t="n">
+      <c r="F12" s="36" t="n">
         <v>100</v>
       </c>
-      <c r="G12" s="41" t="n">
+      <c r="G12" s="37" t="n">
         <f aca="false">IF(E12&gt;0,F12*E12/100,F12*100/ABS(E12))</f>
         <v>108</v>
       </c>
-      <c r="H12" s="41" t="n">
+      <c r="H12" s="37" t="n">
         <f aca="false">F12+G12</f>
         <v>208</v>
       </c>
-      <c r="I12" s="45" t="s">
-        <v>98</v>
-      </c>
-      <c r="J12" s="41" t="n">
+      <c r="I12" s="41" t="s">
+        <v>96</v>
+      </c>
+      <c r="J12" s="37" t="n">
         <f aca="false">IF(I12="Win",F12+G12,IF(I12="Push",F12,IF(I12="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K12" s="43" t="n">
+      <c r="K12" s="39" t="n">
         <f aca="false">IF(I12="Pending",0,J12-F12)</f>
         <v>-100</v>
       </c>
-      <c r="L12" s="58" t="n">
+      <c r="L12" s="54" t="n">
         <v>0.5</v>
       </c>
-      <c r="M12" s="44" t="s">
+      <c r="M12" s="40" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="29" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" s="33" t="s">
+        <v>237</v>
+      </c>
+      <c r="C13" s="34" t="s">
         <v>238</v>
       </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="33" t="n">
-        <v>7</v>
-      </c>
-      <c r="B13" s="37" t="s">
-        <v>239</v>
-      </c>
-      <c r="C13" s="38" t="s">
-        <v>240</v>
-      </c>
-      <c r="D13" s="33" t="s">
-        <v>89</v>
-      </c>
-      <c r="E13" s="39" t="n">
+      <c r="D13" s="29" t="s">
+        <v>87</v>
+      </c>
+      <c r="E13" s="35" t="n">
         <v>108</v>
       </c>
-      <c r="F13" s="40" t="n">
+      <c r="F13" s="36" t="n">
         <v>100</v>
       </c>
-      <c r="G13" s="41" t="n">
+      <c r="G13" s="37" t="n">
         <f aca="false">IF(E13&gt;0,F13*E13/100,F13*100/ABS(E13))</f>
         <v>108</v>
       </c>
-      <c r="H13" s="41" t="n">
+      <c r="H13" s="37" t="n">
         <f aca="false">F13+G13</f>
         <v>208</v>
       </c>
-      <c r="I13" s="42" t="s">
-        <v>90</v>
-      </c>
-      <c r="J13" s="41" t="n">
+      <c r="I13" s="38" t="s">
+        <v>88</v>
+      </c>
+      <c r="J13" s="37" t="n">
         <f aca="false">IF(I13="Win",F13+G13,IF(I13="Push",F13,IF(I13="Loss",0,0)))</f>
         <v>208</v>
       </c>
-      <c r="K13" s="43" t="n">
+      <c r="K13" s="39" t="n">
         <f aca="false">IF(I13="Pending",0,J13-F13)</f>
         <v>108</v>
       </c>
-      <c r="L13" s="58" t="n">
+      <c r="L13" s="54" t="n">
         <v>0.5</v>
       </c>
-      <c r="M13" s="44" t="s">
+      <c r="M13" s="40" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="29" t="n">
+        <v>8</v>
+      </c>
+      <c r="B14" s="33" t="s">
+        <v>240</v>
+      </c>
+      <c r="C14" s="34" t="s">
         <v>241</v>
       </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="33" t="n">
-        <v>8</v>
-      </c>
-      <c r="B14" s="37" t="s">
-        <v>242</v>
-      </c>
-      <c r="C14" s="38" t="s">
-        <v>243</v>
-      </c>
-      <c r="D14" s="33" t="s">
-        <v>117</v>
-      </c>
-      <c r="E14" s="39" t="n">
+      <c r="D14" s="29" t="s">
+        <v>115</v>
+      </c>
+      <c r="E14" s="35" t="n">
         <v>732</v>
       </c>
-      <c r="F14" s="40" t="n">
+      <c r="F14" s="36" t="n">
         <v>50</v>
       </c>
-      <c r="G14" s="41" t="n">
+      <c r="G14" s="37" t="n">
         <f aca="false">IF(E14&gt;0,F14*E14/100,F14*100/ABS(E14))</f>
         <v>366</v>
       </c>
-      <c r="H14" s="41" t="n">
+      <c r="H14" s="37" t="n">
         <f aca="false">F14+G14</f>
         <v>416</v>
       </c>
-      <c r="I14" s="45" t="s">
-        <v>98</v>
-      </c>
-      <c r="J14" s="41" t="n">
+      <c r="I14" s="41" t="s">
+        <v>96</v>
+      </c>
+      <c r="J14" s="37" t="n">
         <f aca="false">IF(I14="Win",F14+G14,IF(I14="Push",F14,IF(I14="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K14" s="43" t="n">
+      <c r="K14" s="39" t="n">
         <f aca="false">IF(I14="Pending",0,J14-F14)</f>
         <v>-50</v>
       </c>
-      <c r="L14" s="58" t="n">
+      <c r="L14" s="54" t="n">
         <v>0.14</v>
       </c>
-      <c r="M14" s="44" t="s">
-        <v>244</v>
+      <c r="M14" s="40" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="46"/>
-      <c r="B15" s="47" t="s">
-        <v>39</v>
-      </c>
-      <c r="C15" s="46"/>
-      <c r="D15" s="46"/>
-      <c r="E15" s="46"/>
-      <c r="F15" s="48" t="n">
+      <c r="A15" s="42"/>
+      <c r="B15" s="43" t="s">
+        <v>38</v>
+      </c>
+      <c r="C15" s="42"/>
+      <c r="D15" s="42"/>
+      <c r="E15" s="42"/>
+      <c r="F15" s="44" t="n">
         <f aca="false">SUM(F7:F14)</f>
         <v>1000</v>
       </c>
-      <c r="G15" s="49" t="n">
+      <c r="G15" s="45" t="n">
         <f aca="false">SUM(G7:G14)</f>
         <v>1226.16096779872</v>
       </c>
-      <c r="H15" s="49" t="n">
+      <c r="H15" s="45" t="n">
         <f aca="false">SUM(H7:H14)</f>
         <v>2226.16096779872</v>
       </c>
-      <c r="I15" s="46"/>
-      <c r="J15" s="49" t="n">
+      <c r="I15" s="42"/>
+      <c r="J15" s="45" t="n">
         <f aca="false">SUM(J7:J14)</f>
         <v>802.232258064516</v>
       </c>
-      <c r="K15" s="50" t="n">
+      <c r="K15" s="46" t="n">
         <f aca="false">SUM(K7:K14)</f>
         <v>-197.767741935484</v>
       </c>
-      <c r="L15" s="59" t="n">
+      <c r="L15" s="55" t="n">
         <f aca="false">SUM(L7:L14)</f>
         <v>3.92</v>
       </c>
-      <c r="M15" s="46"/>
+      <c r="M15" s="42"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="37" t="s">
-        <v>120</v>
-      </c>
-      <c r="C18" s="51" t="n">
+      <c r="B18" s="33" t="s">
+        <v>118</v>
+      </c>
+      <c r="C18" s="47" t="n">
         <f aca="false">COUNTIF(I7:I14,"Win")</f>
         <v>3</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="37" t="s">
-        <v>121</v>
-      </c>
-      <c r="C19" s="51" t="n">
+      <c r="B19" s="33" t="s">
+        <v>119</v>
+      </c>
+      <c r="C19" s="47" t="n">
         <f aca="false">COUNTIF(I7:I14,"Loss")</f>
         <v>5</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="37" t="s">
+      <c r="B20" s="33" t="s">
+        <v>120</v>
+      </c>
+      <c r="C20" s="47" t="n">
+        <f aca="false">COUNTIF(I7:I14,"Push")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B21" s="33" t="s">
+        <v>121</v>
+      </c>
+      <c r="C21" s="47" t="n">
+        <f aca="false">COUNTIF(I7:I14,"Pending")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B22" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="C20" s="51" t="n">
-        <f aca="false">COUNTIF(I7:I14,"Push")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="37" t="s">
-        <v>123</v>
-      </c>
-      <c r="C21" s="51" t="n">
-        <f aca="false">COUNTIF(I7:I14,"Pending")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="37" t="s">
-        <v>124</v>
-      </c>
-      <c r="C22" s="52" t="n">
+      <c r="C22" s="48" t="n">
         <f aca="false">IF(COUNTIF(I7:I14,"Win")+COUNTIF(I7:I14,"Loss")=0,"—",COUNTIF(I7:I14,"Win")/(COUNTIF(I7:I14,"Win")+COUNTIF(I7:I14,"Loss")))</f>
         <v>0.375</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="37" t="s">
-        <v>125</v>
-      </c>
-      <c r="C23" s="34" t="n">
+      <c r="B23" s="33" t="s">
+        <v>123</v>
+      </c>
+      <c r="C23" s="30" t="n">
         <f aca="false">SUM(F7:F14)</f>
         <v>1000</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="37" t="s">
-        <v>126</v>
-      </c>
-      <c r="C24" s="41" t="n">
+      <c r="B24" s="33" t="s">
+        <v>124</v>
+      </c>
+      <c r="C24" s="37" t="n">
         <f aca="false">SUM(J7:J14)</f>
         <v>802.232258064516</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="37" t="s">
-        <v>127</v>
-      </c>
-      <c r="C25" s="43" t="n">
+      <c r="B25" s="33" t="s">
+        <v>125</v>
+      </c>
+      <c r="C25" s="39" t="n">
         <f aca="false">SUM(K7:K14)</f>
         <v>-197.767741935484</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="37" t="s">
-        <v>128</v>
-      </c>
-      <c r="C26" s="52" t="n">
+      <c r="B26" s="33" t="s">
+        <v>126</v>
+      </c>
+      <c r="C26" s="48" t="n">
         <f aca="false">IF(SUM(F7:F14)=0,"—",SUM(K7:K14)/SUM(F7:F14))</f>
         <v>-0.197767741935484</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="37" t="s">
-        <v>129</v>
-      </c>
-      <c r="C27" s="41" t="n">
+      <c r="B27" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="C27" s="37" t="n">
         <f aca="false">SUM(H7:H14)</f>
         <v>2226.16096779872</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="37" t="s">
-        <v>245</v>
-      </c>
-      <c r="C28" s="60" t="n">
+      <c r="B28" s="33" t="s">
+        <v>243</v>
+      </c>
+      <c r="C28" s="56" t="n">
         <f aca="false">SUM(L7:L14)</f>
         <v>3.92</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="37" t="s">
-        <v>246</v>
-      </c>
-      <c r="C29" s="43" t="n">
+      <c r="B29" s="33" t="s">
+        <v>244</v>
+      </c>
+      <c r="C29" s="39" t="n">
         <f aca="false">SUMPRODUCT(L7:L14,G7:G14)-SUMPRODUCT(1-L7:L14,F7:F14)</f>
         <v>45.1624826615033</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5616,152 +6002,152 @@
         <v>12</v>
       </c>
       <c r="B32" s="12" t="s">
+        <v>246</v>
+      </c>
+      <c r="C32" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="D32" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="E32" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="F32" s="12" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="B33" s="33" t="s">
         <v>248</v>
       </c>
-      <c r="C32" s="12" t="s">
-        <v>132</v>
-      </c>
-      <c r="D32" s="12" t="s">
+      <c r="C33" s="40" t="s">
         <v>249</v>
       </c>
-      <c r="E32" s="12" t="s">
-        <v>134</v>
-      </c>
-      <c r="F32" s="12" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="B33" s="37" t="s">
+      <c r="D33" s="49" t="s">
         <v>250</v>
       </c>
-      <c r="C33" s="44" t="s">
+      <c r="E33" s="53"/>
+      <c r="F33" s="53"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="B34" s="33" t="s">
         <v>251</v>
       </c>
-      <c r="D33" s="53" t="s">
+      <c r="C34" s="40" t="s">
         <v>252</v>
       </c>
-      <c r="E33" s="57"/>
-      <c r="F33" s="57"/>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="33" t="n">
-        <v>2</v>
-      </c>
-      <c r="B34" s="37" t="s">
+      <c r="D34" s="49" t="s">
         <v>253</v>
       </c>
-      <c r="C34" s="44" t="s">
+      <c r="E34" s="53"/>
+      <c r="F34" s="53"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="B35" s="33" t="s">
         <v>254</v>
       </c>
-      <c r="D34" s="53" t="s">
+      <c r="C35" s="40" t="s">
         <v>255</v>
       </c>
-      <c r="E34" s="57"/>
-      <c r="F34" s="57"/>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="33" t="n">
-        <v>3</v>
-      </c>
-      <c r="B35" s="37" t="s">
+      <c r="D35" s="49" t="s">
         <v>256</v>
       </c>
-      <c r="C35" s="44" t="s">
+      <c r="E35" s="53"/>
+      <c r="F35" s="53"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="B36" s="33" t="s">
         <v>257</v>
       </c>
-      <c r="D35" s="53" t="s">
+      <c r="C36" s="40" t="s">
         <v>258</v>
       </c>
-      <c r="E35" s="57"/>
-      <c r="F35" s="57"/>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="33" t="n">
-        <v>4</v>
-      </c>
-      <c r="B36" s="37" t="s">
+      <c r="D36" s="49" t="s">
         <v>259</v>
       </c>
-      <c r="C36" s="44" t="s">
+      <c r="E36" s="53"/>
+      <c r="F36" s="53"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="B37" s="33" t="s">
         <v>260</v>
       </c>
-      <c r="D36" s="53" t="s">
+      <c r="C37" s="40" t="s">
         <v>261</v>
       </c>
-      <c r="E36" s="57"/>
-      <c r="F36" s="57"/>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="33" t="n">
-        <v>5</v>
-      </c>
-      <c r="B37" s="37" t="s">
+      <c r="D37" s="49" t="s">
         <v>262</v>
       </c>
-      <c r="C37" s="44" t="s">
+      <c r="E37" s="53"/>
+      <c r="F37" s="53"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="B38" s="33" t="s">
         <v>263</v>
       </c>
-      <c r="D37" s="53" t="s">
+      <c r="C38" s="40" t="s">
         <v>264</v>
       </c>
-      <c r="E37" s="57"/>
-      <c r="F37" s="57"/>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="33" t="n">
-        <v>6</v>
-      </c>
-      <c r="B38" s="37" t="s">
+      <c r="D38" s="49" t="s">
         <v>265</v>
       </c>
-      <c r="C38" s="44" t="s">
+      <c r="E38" s="53"/>
+      <c r="F38" s="53"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="29" t="n">
+        <v>7</v>
+      </c>
+      <c r="B39" s="33" t="s">
         <v>266</v>
       </c>
-      <c r="D38" s="53" t="s">
+      <c r="C39" s="40" t="s">
         <v>267</v>
       </c>
-      <c r="E38" s="57"/>
-      <c r="F38" s="57"/>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="33" t="n">
-        <v>7</v>
-      </c>
-      <c r="B39" s="37" t="s">
+      <c r="D39" s="49" t="s">
         <v>268</v>
       </c>
-      <c r="C39" s="44" t="s">
+      <c r="E39" s="53"/>
+      <c r="F39" s="53"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="29" t="n">
+        <v>8</v>
+      </c>
+      <c r="B40" s="33" t="s">
         <v>269</v>
       </c>
-      <c r="D39" s="53" t="s">
+      <c r="C40" s="40" t="s">
         <v>270</v>
       </c>
-      <c r="E39" s="57"/>
-      <c r="F39" s="57"/>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="33" t="n">
-        <v>8</v>
-      </c>
-      <c r="B40" s="37" t="s">
+      <c r="D40" s="49" t="s">
         <v>271</v>
       </c>
-      <c r="C40" s="44" t="s">
+      <c r="E40" s="53"/>
+      <c r="F40" s="53"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="51" t="s">
         <v>272</v>
-      </c>
-      <c r="D40" s="53" t="s">
-        <v>273</v>
-      </c>
-      <c r="E40" s="57"/>
-      <c r="F40" s="57"/>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="55" t="s">
-        <v>274</v>
       </c>
     </row>
   </sheetData>
@@ -5827,26 +6213,26 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="35" t="s">
-        <v>275</v>
-      </c>
-      <c r="H1" s="56" t="s">
-        <v>276</v>
+      <c r="A1" s="31" t="s">
+        <v>273</v>
+      </c>
+      <c r="H1" s="52" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="61" t="s">
-        <v>278</v>
+      <c r="A3" s="57" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5854,499 +6240,499 @@
         <v>12</v>
       </c>
       <c r="B6" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>198</v>
+      </c>
+      <c r="D6" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="C6" s="12" t="s">
-        <v>200</v>
-      </c>
-      <c r="D6" s="12" t="s">
+      <c r="E6" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="G6" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="H6" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="F6" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="G6" s="12" t="s">
+      <c r="I6" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="H6" s="12" t="s">
+      <c r="J6" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="I6" s="12" t="s">
+      <c r="K6" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="J6" s="12" t="s">
+      <c r="L6" s="12" t="s">
+        <v>218</v>
+      </c>
+      <c r="M6" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="K6" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="L6" s="12" t="s">
-        <v>220</v>
-      </c>
-      <c r="M6" s="12" t="s">
-        <v>86</v>
-      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="33" t="n">
+      <c r="A7" s="29" t="n">
         <v>1</v>
       </c>
       <c r="B7" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="C7" s="28" t="s">
+        <v>278</v>
+      </c>
+      <c r="D7" s="29" t="s">
         <v>279</v>
       </c>
-      <c r="C7" s="32" t="s">
-        <v>280</v>
-      </c>
-      <c r="D7" s="33" t="s">
-        <v>281</v>
-      </c>
-      <c r="E7" s="39" t="n">
+      <c r="E7" s="35" t="n">
         <v>-113</v>
       </c>
-      <c r="F7" s="40" t="n">
+      <c r="F7" s="36" t="n">
         <v>300</v>
       </c>
-      <c r="G7" s="41" t="n">
+      <c r="G7" s="37" t="n">
         <f aca="false">IF(E7&gt;0,F7*E7/100,F7*100/ABS(E7))</f>
         <v>265.486725663717</v>
       </c>
-      <c r="H7" s="41" t="n">
+      <c r="H7" s="37" t="n">
         <f aca="false">F7+G7</f>
         <v>565.486725663717</v>
       </c>
-      <c r="I7" s="57" t="s">
-        <v>90</v>
-      </c>
-      <c r="J7" s="41" t="n">
+      <c r="I7" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="J7" s="37" t="n">
         <f aca="false">IF(I7="Win",F7+G7,IF(I7="Push",F7,IF(I7="Loss",0,0)))</f>
         <v>565.486725663717</v>
       </c>
-      <c r="K7" s="43" t="n">
+      <c r="K7" s="39" t="n">
         <f aca="false">IF(I7="Pending",0,J7-F7)</f>
         <v>265.486725663717</v>
       </c>
-      <c r="L7" s="58" t="n">
+      <c r="L7" s="54" t="n">
         <v>0.58</v>
       </c>
-      <c r="M7" s="62" t="s">
+      <c r="M7" s="58" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="C8" s="28" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="33" t="n">
-        <v>2</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>283</v>
-      </c>
-      <c r="C8" s="32" t="s">
-        <v>284</v>
-      </c>
-      <c r="D8" s="33" t="s">
-        <v>94</v>
-      </c>
-      <c r="E8" s="39" t="n">
+      <c r="D8" s="29" t="s">
+        <v>92</v>
+      </c>
+      <c r="E8" s="35" t="n">
         <v>456</v>
       </c>
-      <c r="F8" s="40" t="n">
+      <c r="F8" s="36" t="n">
         <v>200</v>
       </c>
-      <c r="G8" s="41" t="n">
+      <c r="G8" s="37" t="n">
         <f aca="false">IF(E8&gt;0,F8*E8/100,F8*100/ABS(E8))</f>
         <v>912</v>
       </c>
-      <c r="H8" s="41" t="n">
+      <c r="H8" s="37" t="n">
         <f aca="false">F8+G8</f>
         <v>1112</v>
       </c>
-      <c r="I8" s="57" t="s">
-        <v>98</v>
-      </c>
-      <c r="J8" s="41" t="n">
+      <c r="I8" s="53" t="s">
+        <v>96</v>
+      </c>
+      <c r="J8" s="37" t="n">
         <f aca="false">IF(I8="Win",F8+G8,IF(I8="Push",F8,IF(I8="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K8" s="43" t="n">
+      <c r="K8" s="39" t="n">
         <f aca="false">IF(I8="Pending",0,J8-F8)</f>
         <v>-200</v>
       </c>
-      <c r="L8" s="58" t="n">
+      <c r="L8" s="54" t="n">
         <v>0.24</v>
       </c>
-      <c r="M8" s="62" t="s">
+      <c r="M8" s="58" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>284</v>
+      </c>
+      <c r="C9" s="28" t="s">
         <v>285</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="33" t="n">
-        <v>3</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>286</v>
-      </c>
-      <c r="C9" s="32" t="s">
-        <v>287</v>
-      </c>
-      <c r="D9" s="33" t="s">
-        <v>190</v>
-      </c>
-      <c r="E9" s="39" t="n">
+      <c r="D9" s="29" t="s">
+        <v>188</v>
+      </c>
+      <c r="E9" s="35" t="n">
         <v>1150</v>
       </c>
-      <c r="F9" s="40" t="n">
+      <c r="F9" s="36" t="n">
         <v>150</v>
       </c>
-      <c r="G9" s="41" t="n">
+      <c r="G9" s="37" t="n">
         <f aca="false">IF(E9&gt;0,F9*E9/100,F9*100/ABS(E9))</f>
         <v>1725</v>
       </c>
-      <c r="H9" s="41" t="n">
+      <c r="H9" s="37" t="n">
         <f aca="false">F9+G9</f>
         <v>1875</v>
       </c>
-      <c r="I9" s="57" t="s">
-        <v>98</v>
-      </c>
-      <c r="J9" s="41" t="n">
+      <c r="I9" s="53" t="s">
+        <v>96</v>
+      </c>
+      <c r="J9" s="37" t="n">
         <f aca="false">IF(I9="Win",F9+G9,IF(I9="Push",F9,IF(I9="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K9" s="43" t="n">
+      <c r="K9" s="39" t="n">
         <f aca="false">IF(I9="Pending",0,J9-F9)</f>
         <v>-150</v>
       </c>
-      <c r="L9" s="58" t="n">
+      <c r="L9" s="54" t="n">
         <v>0.1</v>
       </c>
-      <c r="M9" s="62" t="s">
-        <v>288</v>
+      <c r="M9" s="58" t="s">
+        <v>286</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="33" t="n">
+      <c r="A10" s="29" t="n">
         <v>4</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>289</v>
-      </c>
-      <c r="C10" s="32" t="s">
         <v>287</v>
       </c>
-      <c r="D10" s="33" t="s">
-        <v>190</v>
-      </c>
-      <c r="E10" s="39" t="n">
+      <c r="C10" s="28" t="s">
+        <v>285</v>
+      </c>
+      <c r="D10" s="29" t="s">
+        <v>188</v>
+      </c>
+      <c r="E10" s="35" t="n">
         <v>1567</v>
       </c>
-      <c r="F10" s="40" t="n">
+      <c r="F10" s="36" t="n">
         <v>120</v>
       </c>
-      <c r="G10" s="41" t="n">
+      <c r="G10" s="37" t="n">
         <f aca="false">IF(E10&gt;0,F10*E10/100,F10*100/ABS(E10))</f>
         <v>1880.4</v>
       </c>
-      <c r="H10" s="41" t="n">
+      <c r="H10" s="37" t="n">
         <f aca="false">F10+G10</f>
         <v>2000.4</v>
       </c>
-      <c r="I10" s="57" t="s">
-        <v>98</v>
-      </c>
-      <c r="J10" s="41" t="n">
+      <c r="I10" s="53" t="s">
+        <v>96</v>
+      </c>
+      <c r="J10" s="37" t="n">
         <f aca="false">IF(I10="Win",F10+G10,IF(I10="Push",F10,IF(I10="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K10" s="43" t="n">
+      <c r="K10" s="39" t="n">
         <f aca="false">IF(I10="Pending",0,J10-F10)</f>
         <v>-120</v>
       </c>
-      <c r="L10" s="58" t="n">
+      <c r="L10" s="54" t="n">
         <v>0.08</v>
       </c>
-      <c r="M10" s="62" t="s">
-        <v>290</v>
+      <c r="M10" s="58" t="s">
+        <v>288</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="33" t="n">
+      <c r="A11" s="29" t="n">
         <v>5</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>291</v>
-      </c>
-      <c r="C11" s="32" t="s">
-        <v>287</v>
-      </c>
-      <c r="D11" s="33" t="s">
-        <v>190</v>
-      </c>
-      <c r="E11" s="39" t="n">
+        <v>289</v>
+      </c>
+      <c r="C11" s="28" t="s">
+        <v>285</v>
+      </c>
+      <c r="D11" s="29" t="s">
+        <v>188</v>
+      </c>
+      <c r="E11" s="35" t="n">
         <v>1800</v>
       </c>
-      <c r="F11" s="40" t="n">
+      <c r="F11" s="36" t="n">
         <v>100</v>
       </c>
-      <c r="G11" s="41" t="n">
+      <c r="G11" s="37" t="n">
         <f aca="false">IF(E11&gt;0,F11*E11/100,F11*100/ABS(E11))</f>
         <v>1800</v>
       </c>
-      <c r="H11" s="41" t="n">
+      <c r="H11" s="37" t="n">
         <f aca="false">F11+G11</f>
         <v>1900</v>
       </c>
-      <c r="I11" s="57" t="s">
-        <v>98</v>
-      </c>
-      <c r="J11" s="41" t="n">
+      <c r="I11" s="53" t="s">
+        <v>96</v>
+      </c>
+      <c r="J11" s="37" t="n">
         <f aca="false">IF(I11="Win",F11+G11,IF(I11="Push",F11,IF(I11="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K11" s="43" t="n">
+      <c r="K11" s="39" t="n">
         <f aca="false">IF(I11="Pending",0,J11-F11)</f>
         <v>-100</v>
       </c>
-      <c r="L11" s="58" t="n">
+      <c r="L11" s="54" t="n">
         <v>0.07</v>
       </c>
-      <c r="M11" s="62" t="s">
-        <v>292</v>
+      <c r="M11" s="58" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="33" t="n">
+      <c r="A12" s="29" t="n">
         <v>6</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>293</v>
-      </c>
-      <c r="C12" s="32" t="s">
-        <v>287</v>
-      </c>
-      <c r="D12" s="33" t="s">
-        <v>190</v>
-      </c>
-      <c r="E12" s="39" t="n">
+        <v>291</v>
+      </c>
+      <c r="C12" s="28" t="s">
+        <v>285</v>
+      </c>
+      <c r="D12" s="29" t="s">
+        <v>188</v>
+      </c>
+      <c r="E12" s="35" t="n">
         <v>1150</v>
       </c>
-      <c r="F12" s="40" t="n">
+      <c r="F12" s="36" t="n">
         <v>90</v>
       </c>
-      <c r="G12" s="41" t="n">
+      <c r="G12" s="37" t="n">
         <f aca="false">IF(E12&gt;0,F12*E12/100,F12*100/ABS(E12))</f>
         <v>1035</v>
       </c>
-      <c r="H12" s="41" t="n">
+      <c r="H12" s="37" t="n">
         <f aca="false">F12+G12</f>
         <v>1125</v>
       </c>
-      <c r="I12" s="57" t="s">
-        <v>98</v>
-      </c>
-      <c r="J12" s="41" t="n">
+      <c r="I12" s="53" t="s">
+        <v>96</v>
+      </c>
+      <c r="J12" s="37" t="n">
         <f aca="false">IF(I12="Win",F12+G12,IF(I12="Push",F12,IF(I12="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K12" s="43" t="n">
+      <c r="K12" s="39" t="n">
         <f aca="false">IF(I12="Pending",0,J12-F12)</f>
         <v>-90</v>
       </c>
-      <c r="L12" s="58" t="n">
+      <c r="L12" s="54" t="n">
         <v>0.08</v>
       </c>
-      <c r="M12" s="62" t="s">
-        <v>294</v>
+      <c r="M12" s="58" t="s">
+        <v>292</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="33" t="n">
+      <c r="A13" s="29" t="n">
         <v>7</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>295</v>
-      </c>
-      <c r="C13" s="32" t="s">
-        <v>287</v>
-      </c>
-      <c r="D13" s="33" t="s">
-        <v>190</v>
-      </c>
-      <c r="E13" s="39" t="n">
+        <v>293</v>
+      </c>
+      <c r="C13" s="28" t="s">
+        <v>285</v>
+      </c>
+      <c r="D13" s="29" t="s">
+        <v>188</v>
+      </c>
+      <c r="E13" s="35" t="n">
         <v>1900</v>
       </c>
-      <c r="F13" s="40" t="n">
+      <c r="F13" s="36" t="n">
         <v>40</v>
       </c>
-      <c r="G13" s="41" t="n">
+      <c r="G13" s="37" t="n">
         <f aca="false">IF(E13&gt;0,F13*E13/100,F13*100/ABS(E13))</f>
         <v>760</v>
       </c>
-      <c r="H13" s="41" t="n">
+      <c r="H13" s="37" t="n">
         <f aca="false">F13+G13</f>
         <v>800</v>
       </c>
-      <c r="I13" s="57" t="s">
-        <v>98</v>
-      </c>
-      <c r="J13" s="41" t="n">
+      <c r="I13" s="53" t="s">
+        <v>96</v>
+      </c>
+      <c r="J13" s="37" t="n">
         <f aca="false">IF(I13="Win",F13+G13,IF(I13="Push",F13,IF(I13="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K13" s="43" t="n">
+      <c r="K13" s="39" t="n">
         <f aca="false">IF(I13="Pending",0,J13-F13)</f>
         <v>-40</v>
       </c>
-      <c r="L13" s="58" t="n">
+      <c r="L13" s="54" t="n">
         <v>0.05</v>
       </c>
-      <c r="M13" s="62" t="s">
-        <v>296</v>
+      <c r="M13" s="58" t="s">
+        <v>294</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="63"/>
-      <c r="B14" s="64" t="s">
-        <v>39</v>
-      </c>
-      <c r="C14" s="63"/>
-      <c r="D14" s="63"/>
-      <c r="E14" s="63"/>
-      <c r="F14" s="48" t="n">
+      <c r="A14" s="59"/>
+      <c r="B14" s="60" t="s">
+        <v>38</v>
+      </c>
+      <c r="C14" s="59"/>
+      <c r="D14" s="59"/>
+      <c r="E14" s="59"/>
+      <c r="F14" s="44" t="n">
         <f aca="false">SUM(F7:F13)</f>
         <v>1000</v>
       </c>
-      <c r="G14" s="49" t="n">
+      <c r="G14" s="45" t="n">
         <f aca="false">SUM(G7:G13)</f>
         <v>8377.88672566372</v>
       </c>
-      <c r="H14" s="49" t="n">
+      <c r="H14" s="45" t="n">
         <f aca="false">SUM(H7:H13)</f>
         <v>9377.88672566372</v>
       </c>
-      <c r="I14" s="63"/>
-      <c r="J14" s="49" t="n">
+      <c r="I14" s="59"/>
+      <c r="J14" s="45" t="n">
         <f aca="false">SUM(J7:J13)</f>
         <v>565.486725663717</v>
       </c>
-      <c r="K14" s="50" t="n">
+      <c r="K14" s="46" t="n">
         <f aca="false">SUM(K7:K13)</f>
         <v>-434.513274336283</v>
       </c>
-      <c r="L14" s="59" t="n">
+      <c r="L14" s="55" t="n">
         <f aca="false">SUM(L7:L13)</f>
         <v>1.2</v>
       </c>
-      <c r="M14" s="63"/>
+      <c r="M14" s="59"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="C17" s="51" t="n">
+        <v>118</v>
+      </c>
+      <c r="C17" s="47" t="n">
         <f aca="false">COUNTIF(I7:I13,"Win")</f>
         <v>1</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="C18" s="51" t="n">
+        <v>119</v>
+      </c>
+      <c r="C18" s="47" t="n">
         <f aca="false">COUNTIF(I7:I13,"Loss")</f>
         <v>6</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="C19" s="51" t="n">
+        <v>120</v>
+      </c>
+      <c r="C19" s="47" t="n">
         <f aca="false">COUNTIF(I7:I13,"Push")</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="C20" s="51" t="n">
+        <v>121</v>
+      </c>
+      <c r="C20" s="47" t="n">
         <f aca="false">COUNTIF(I7:I13,"Pending")</f>
         <v>0</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="C21" s="52" t="n">
+        <v>122</v>
+      </c>
+      <c r="C21" s="48" t="n">
         <f aca="false">IF(COUNTIF(I7:I13,"Win")+COUNTIF(I7:I13,"Loss")=0,"—",COUNTIF(I7:I13,"Win")/(COUNTIF(I7:I13,"Win")+COUNTIF(I7:I13,"Loss")))</f>
         <v>0.142857142857143</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="C22" s="34" t="n">
+        <v>123</v>
+      </c>
+      <c r="C22" s="30" t="n">
         <f aca="false">SUM(F7:F13)</f>
         <v>1000</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="C23" s="41" t="n">
+        <v>124</v>
+      </c>
+      <c r="C23" s="37" t="n">
         <f aca="false">SUM(J7:J13)</f>
         <v>565.486725663717</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="C24" s="43" t="n">
+        <v>125</v>
+      </c>
+      <c r="C24" s="39" t="n">
         <f aca="false">SUM(K7:K13)</f>
         <v>-434.513274336283</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="C25" s="52" t="n">
+        <v>126</v>
+      </c>
+      <c r="C25" s="48" t="n">
         <f aca="false">IF(SUM(F7:F13)=0,"—",SUM(K7:K13)/SUM(F7:F13))</f>
         <v>-0.434513274336283</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="5" t="s">
-        <v>245</v>
-      </c>
-      <c r="C26" s="60" t="n">
+        <v>243</v>
+      </c>
+      <c r="C26" s="56" t="n">
         <f aca="false">SUM(L7:L13)</f>
         <v>1.2</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="5" t="s">
-        <v>297</v>
-      </c>
-      <c r="C27" s="34" t="n">
+        <v>295</v>
+      </c>
+      <c r="C27" s="30" t="n">
         <f aca="false">2678</f>
         <v>2678</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="55" t="s">
-        <v>298</v>
+      <c r="A29" s="51" t="s">
+        <v>296</v>
       </c>
     </row>
   </sheetData>
@@ -6387,7 +6773,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="26"/>
@@ -6398,388 +6784,396 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="35" t="s">
-        <v>299</v>
+      <c r="A1" s="31" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
+        <v>299</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>300</v>
+      </c>
+      <c r="C4" s="12" t="s">
         <v>301</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="D4" s="12" t="s">
         <v>302</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="E4" s="12" t="s">
         <v>303</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="F4" s="12" t="s">
         <v>304</v>
       </c>
-      <c r="E4" s="12" t="s">
-        <v>305</v>
-      </c>
-      <c r="F4" s="12" t="s">
-        <v>306</v>
-      </c>
       <c r="G4" s="12" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
+        <v>305</v>
+      </c>
+      <c r="B5" s="61" t="s">
+        <v>306</v>
+      </c>
+      <c r="C5" s="62"/>
+      <c r="D5" s="62" t="s">
         <v>307</v>
       </c>
-      <c r="B5" s="65" t="s">
+      <c r="E5" s="62" t="s">
+        <v>307</v>
+      </c>
+      <c r="F5" s="62"/>
+      <c r="G5" s="63" t="s">
         <v>308</v>
-      </c>
-      <c r="C5" s="66"/>
-      <c r="D5" s="66" t="s">
-        <v>309</v>
-      </c>
-      <c r="E5" s="66" t="s">
-        <v>309</v>
-      </c>
-      <c r="F5" s="66"/>
-      <c r="G5" s="67" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="B6" s="61" t="s">
+        <v>310</v>
+      </c>
+      <c r="C6" s="62" t="s">
+        <v>307</v>
+      </c>
+      <c r="D6" s="62"/>
+      <c r="E6" s="62"/>
+      <c r="F6" s="62"/>
+      <c r="G6" s="63" t="s">
         <v>311</v>
-      </c>
-      <c r="B6" s="65" t="s">
-        <v>312</v>
-      </c>
-      <c r="C6" s="66" t="s">
-        <v>309</v>
-      </c>
-      <c r="D6" s="66"/>
-      <c r="E6" s="66"/>
-      <c r="F6" s="66"/>
-      <c r="G6" s="67" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="B7" s="61" t="s">
+        <v>313</v>
+      </c>
+      <c r="C7" s="62" t="s">
+        <v>307</v>
+      </c>
+      <c r="D7" s="62"/>
+      <c r="E7" s="62"/>
+      <c r="F7" s="62"/>
+      <c r="G7" s="63" t="s">
         <v>314</v>
-      </c>
-      <c r="B7" s="65" t="s">
-        <v>315</v>
-      </c>
-      <c r="C7" s="66" t="s">
-        <v>309</v>
-      </c>
-      <c r="D7" s="66"/>
-      <c r="E7" s="66"/>
-      <c r="F7" s="66"/>
-      <c r="G7" s="67" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="B8" s="61" t="s">
+        <v>316</v>
+      </c>
+      <c r="C8" s="62"/>
+      <c r="D8" s="62" t="s">
+        <v>307</v>
+      </c>
+      <c r="E8" s="62"/>
+      <c r="F8" s="62"/>
+      <c r="G8" s="63" t="s">
         <v>317</v>
-      </c>
-      <c r="B8" s="65" t="s">
-        <v>318</v>
-      </c>
-      <c r="C8" s="66"/>
-      <c r="D8" s="66" t="s">
-        <v>309</v>
-      </c>
-      <c r="E8" s="66"/>
-      <c r="F8" s="66"/>
-      <c r="G8" s="67" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="B9" s="61" t="s">
+        <v>319</v>
+      </c>
+      <c r="C9" s="62"/>
+      <c r="D9" s="62" t="s">
+        <v>307</v>
+      </c>
+      <c r="E9" s="62"/>
+      <c r="F9" s="62" t="s">
+        <v>307</v>
+      </c>
+      <c r="G9" s="63" t="s">
         <v>320</v>
-      </c>
-      <c r="B9" s="65" t="s">
-        <v>321</v>
-      </c>
-      <c r="C9" s="66"/>
-      <c r="D9" s="66" t="s">
-        <v>309</v>
-      </c>
-      <c r="E9" s="66"/>
-      <c r="F9" s="66" t="s">
-        <v>309</v>
-      </c>
-      <c r="G9" s="67" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
+        <v>321</v>
+      </c>
+      <c r="B10" s="61" t="s">
+        <v>322</v>
+      </c>
+      <c r="C10" s="62"/>
+      <c r="D10" s="62" t="s">
+        <v>307</v>
+      </c>
+      <c r="E10" s="62" t="s">
+        <v>307</v>
+      </c>
+      <c r="F10" s="62"/>
+      <c r="G10" s="63" t="s">
         <v>323</v>
-      </c>
-      <c r="B10" s="65" t="s">
-        <v>324</v>
-      </c>
-      <c r="C10" s="66"/>
-      <c r="D10" s="66" t="s">
-        <v>309</v>
-      </c>
-      <c r="E10" s="66" t="s">
-        <v>309</v>
-      </c>
-      <c r="F10" s="66"/>
-      <c r="G10" s="67" t="s">
-        <v>325</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
+        <v>324</v>
+      </c>
+      <c r="B11" s="61" t="s">
+        <v>325</v>
+      </c>
+      <c r="C11" s="62"/>
+      <c r="D11" s="62" t="s">
+        <v>307</v>
+      </c>
+      <c r="E11" s="62"/>
+      <c r="F11" s="62" t="s">
+        <v>307</v>
+      </c>
+      <c r="G11" s="63" t="s">
         <v>326</v>
-      </c>
-      <c r="B11" s="65" t="s">
-        <v>327</v>
-      </c>
-      <c r="C11" s="66"/>
-      <c r="D11" s="66" t="s">
-        <v>309</v>
-      </c>
-      <c r="E11" s="66"/>
-      <c r="F11" s="66" t="s">
-        <v>309</v>
-      </c>
-      <c r="G11" s="67" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
+        <v>327</v>
+      </c>
+      <c r="B12" s="61" t="s">
+        <v>328</v>
+      </c>
+      <c r="C12" s="62"/>
+      <c r="D12" s="62" t="s">
+        <v>307</v>
+      </c>
+      <c r="E12" s="62"/>
+      <c r="F12" s="62"/>
+      <c r="G12" s="63" t="s">
         <v>329</v>
-      </c>
-      <c r="B12" s="65" t="s">
-        <v>330</v>
-      </c>
-      <c r="C12" s="66"/>
-      <c r="D12" s="66" t="s">
-        <v>309</v>
-      </c>
-      <c r="E12" s="66"/>
-      <c r="F12" s="66"/>
-      <c r="G12" s="67" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
+        <v>330</v>
+      </c>
+      <c r="B13" s="61" t="s">
+        <v>331</v>
+      </c>
+      <c r="C13" s="62"/>
+      <c r="D13" s="62" t="s">
+        <v>307</v>
+      </c>
+      <c r="E13" s="62"/>
+      <c r="F13" s="62"/>
+      <c r="G13" s="63" t="s">
         <v>332</v>
-      </c>
-      <c r="B13" s="65" t="s">
-        <v>333</v>
-      </c>
-      <c r="C13" s="66"/>
-      <c r="D13" s="66" t="s">
-        <v>309</v>
-      </c>
-      <c r="E13" s="66"/>
-      <c r="F13" s="66"/>
-      <c r="G13" s="67" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="B14" s="61" t="s">
+        <v>334</v>
+      </c>
+      <c r="C14" s="62"/>
+      <c r="D14" s="62" t="s">
+        <v>307</v>
+      </c>
+      <c r="E14" s="62"/>
+      <c r="F14" s="62"/>
+      <c r="G14" s="63" t="s">
         <v>335</v>
-      </c>
-      <c r="B14" s="65" t="s">
-        <v>336</v>
-      </c>
-      <c r="C14" s="66"/>
-      <c r="D14" s="66" t="s">
-        <v>309</v>
-      </c>
-      <c r="E14" s="66"/>
-      <c r="F14" s="66"/>
-      <c r="G14" s="67" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
+        <v>336</v>
+      </c>
+      <c r="B15" s="61" t="s">
+        <v>337</v>
+      </c>
+      <c r="C15" s="62"/>
+      <c r="D15" s="62" t="s">
+        <v>307</v>
+      </c>
+      <c r="E15" s="62"/>
+      <c r="F15" s="62"/>
+      <c r="G15" s="63" t="s">
         <v>338</v>
-      </c>
-      <c r="B15" s="65" t="s">
-        <v>339</v>
-      </c>
-      <c r="C15" s="66"/>
-      <c r="D15" s="66" t="s">
-        <v>309</v>
-      </c>
-      <c r="E15" s="66"/>
-      <c r="F15" s="66"/>
-      <c r="G15" s="67" t="s">
-        <v>340</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="B16" s="61" t="s">
+        <v>340</v>
+      </c>
+      <c r="C16" s="62"/>
+      <c r="D16" s="62"/>
+      <c r="E16" s="62" t="s">
+        <v>307</v>
+      </c>
+      <c r="F16" s="62" t="s">
+        <v>307</v>
+      </c>
+      <c r="G16" s="63" t="s">
         <v>341</v>
-      </c>
-      <c r="B16" s="65" t="s">
-        <v>342</v>
-      </c>
-      <c r="C16" s="66"/>
-      <c r="D16" s="66"/>
-      <c r="E16" s="66" t="s">
-        <v>309</v>
-      </c>
-      <c r="F16" s="66" t="s">
-        <v>309</v>
-      </c>
-      <c r="G16" s="67" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="B17" s="61" t="s">
+        <v>343</v>
+      </c>
+      <c r="C17" s="62"/>
+      <c r="D17" s="62"/>
+      <c r="E17" s="62" t="s">
+        <v>307</v>
+      </c>
+      <c r="F17" s="62"/>
+      <c r="G17" s="63" t="s">
         <v>344</v>
-      </c>
-      <c r="B17" s="65" t="s">
-        <v>345</v>
-      </c>
-      <c r="C17" s="66"/>
-      <c r="D17" s="66"/>
-      <c r="E17" s="66" t="s">
-        <v>309</v>
-      </c>
-      <c r="F17" s="66"/>
-      <c r="G17" s="67" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="B18" s="61" t="s">
+        <v>346</v>
+      </c>
+      <c r="C18" s="62"/>
+      <c r="D18" s="62"/>
+      <c r="E18" s="62" t="s">
+        <v>307</v>
+      </c>
+      <c r="F18" s="62"/>
+      <c r="G18" s="63" t="s">
         <v>347</v>
-      </c>
-      <c r="B18" s="65" t="s">
-        <v>348</v>
-      </c>
-      <c r="C18" s="66"/>
-      <c r="D18" s="66"/>
-      <c r="E18" s="66" t="s">
-        <v>309</v>
-      </c>
-      <c r="F18" s="66"/>
-      <c r="G18" s="67" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
+        <v>348</v>
+      </c>
+      <c r="B19" s="61" t="s">
+        <v>349</v>
+      </c>
+      <c r="C19" s="62"/>
+      <c r="D19" s="62"/>
+      <c r="E19" s="62"/>
+      <c r="F19" s="62" t="s">
+        <v>307</v>
+      </c>
+      <c r="G19" s="63" t="s">
         <v>350</v>
       </c>
-      <c r="B19" s="65" t="s">
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="64" t="s">
         <v>351</v>
       </c>
-      <c r="C19" s="66"/>
-      <c r="D19" s="66"/>
-      <c r="E19" s="66"/>
-      <c r="F19" s="66" t="s">
-        <v>309</v>
-      </c>
-      <c r="G19" s="67" t="s">
+      <c r="B20" s="65" t="s">
         <v>352</v>
       </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="68" t="s">
+      <c r="D20" s="66" t="s">
+        <v>307</v>
+      </c>
+      <c r="F20" s="66" t="s">
+        <v>307</v>
+      </c>
+      <c r="G20" s="51" t="s">
         <v>353</v>
       </c>
-      <c r="B20" s="69" t="s">
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="64" t="s">
         <v>354</v>
       </c>
-      <c r="D20" s="70" t="s">
-        <v>309</v>
-      </c>
-      <c r="F20" s="70" t="s">
-        <v>309</v>
-      </c>
-      <c r="G20" s="55" t="s">
+      <c r="B21" s="65" t="s">
         <v>355</v>
       </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="68" t="s">
+      <c r="G21" s="51" t="s">
         <v>356</v>
       </c>
-      <c r="B21" s="69" t="s">
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="64" t="s">
         <v>357</v>
       </c>
-      <c r="G21" s="55" t="s">
+      <c r="B22" s="65" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="68" t="s">
+      <c r="G22" s="51" t="s">
         <v>359</v>
       </c>
-      <c r="B22" s="69" t="s">
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="64" t="s">
         <v>360</v>
       </c>
-      <c r="G22" s="55" t="s">
+      <c r="B23" s="65" t="s">
         <v>361</v>
       </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="68" t="s">
+      <c r="G23" s="51" t="s">
         <v>362</v>
-      </c>
-      <c r="B23" s="69" t="s">
-        <v>363</v>
-      </c>
-      <c r="G23" s="55" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="71" t="s">
-        <v>365</v>
+      <c r="A25" s="67" t="s">
+        <v>363</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="3" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="68" t="s">
+        <v>367</v>
+      </c>
+      <c r="B29" s="68" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="72" t="s">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="68" t="s">
+        <v>66</v>
+      </c>
+      <c r="B30" s="68" t="s">
         <v>369</v>
       </c>
-      <c r="B29" s="72" t="s">
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="69" t="s">
+        <v>60</v>
+      </c>
+      <c r="B31" s="69" t="s">
         <v>370</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="72" t="s">
-        <v>68</v>
-      </c>
-      <c r="B30" s="72" t="s">
-        <v>371</v>
       </c>
     </row>
   </sheetData>
@@ -6815,26 +7209,26 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="31" t="s">
+        <v>371</v>
+      </c>
+      <c r="H1" s="52" t="s">
         <v>372</v>
-      </c>
-      <c r="H1" s="56" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6842,508 +7236,508 @@
         <v>12</v>
       </c>
       <c r="B6" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="D6" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="C6" s="12" t="s">
-        <v>219</v>
-      </c>
-      <c r="D6" s="12" t="s">
+      <c r="E6" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="G6" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="H6" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="F6" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="G6" s="12" t="s">
+      <c r="I6" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="H6" s="12" t="s">
+      <c r="J6" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="I6" s="12" t="s">
+      <c r="K6" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="J6" s="12" t="s">
+      <c r="L6" s="12" t="s">
+        <v>218</v>
+      </c>
+      <c r="M6" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="K6" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="L6" s="12" t="s">
-        <v>220</v>
-      </c>
-      <c r="M6" s="12" t="s">
-        <v>86</v>
-      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="33" t="n">
+      <c r="A7" s="29" t="n">
         <v>1</v>
       </c>
       <c r="B7" s="5" t="s">
+        <v>375</v>
+      </c>
+      <c r="C7" s="28" t="s">
         <v>376</v>
       </c>
-      <c r="C7" s="32" t="s">
+      <c r="D7" s="29" t="s">
         <v>377</v>
       </c>
-      <c r="D7" s="33" t="s">
-        <v>378</v>
-      </c>
-      <c r="E7" s="39" t="n">
+      <c r="E7" s="35" t="n">
         <v>-115</v>
       </c>
-      <c r="F7" s="40" t="n">
+      <c r="F7" s="36" t="n">
         <v>200</v>
       </c>
-      <c r="G7" s="41" t="n">
+      <c r="G7" s="37" t="n">
         <f aca="false">IF(E7&gt;0,F7*E7/100,F7*100/ABS(E7))</f>
         <v>173.913043478261</v>
       </c>
-      <c r="H7" s="41" t="n">
+      <c r="H7" s="37" t="n">
         <f aca="false">F7+G7</f>
         <v>373.913043478261</v>
       </c>
-      <c r="I7" s="45" t="s">
-        <v>98</v>
-      </c>
-      <c r="J7" s="41" t="n">
+      <c r="I7" s="41" t="s">
+        <v>96</v>
+      </c>
+      <c r="J7" s="37" t="n">
         <f aca="false">IF(I7="Win",F7+G7,IF(I7="Push",F7,IF(I7="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K7" s="43" t="n">
+      <c r="K7" s="39" t="n">
         <f aca="false">IF(I7="Pending",0,J7-F7)</f>
         <v>-200</v>
       </c>
-      <c r="L7" s="58" t="n">
+      <c r="L7" s="54" t="n">
         <v>0.56</v>
       </c>
-      <c r="M7" s="62" t="s">
+      <c r="M7" s="58" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>379</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="33" t="n">
-        <v>2</v>
-      </c>
-      <c r="B8" s="5" t="s">
+      <c r="C8" s="28" t="s">
         <v>380</v>
       </c>
-      <c r="C8" s="32" t="s">
-        <v>381</v>
-      </c>
-      <c r="D8" s="33" t="s">
-        <v>179</v>
-      </c>
-      <c r="E8" s="39" t="n">
+      <c r="D8" s="29" t="s">
+        <v>177</v>
+      </c>
+      <c r="E8" s="35" t="n">
         <v>-112</v>
       </c>
-      <c r="F8" s="40" t="n">
+      <c r="F8" s="36" t="n">
         <v>150</v>
       </c>
-      <c r="G8" s="41" t="n">
+      <c r="G8" s="37" t="n">
         <f aca="false">IF(E8&gt;0,F8*E8/100,F8*100/ABS(E8))</f>
         <v>133.928571428571</v>
       </c>
-      <c r="H8" s="41" t="n">
+      <c r="H8" s="37" t="n">
         <f aca="false">F8+G8</f>
         <v>283.928571428571</v>
       </c>
-      <c r="I8" s="45" t="s">
-        <v>98</v>
-      </c>
-      <c r="J8" s="41" t="n">
+      <c r="I8" s="41" t="s">
+        <v>96</v>
+      </c>
+      <c r="J8" s="37" t="n">
         <f aca="false">IF(I8="Win",F8+G8,IF(I8="Push",F8,IF(I8="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K8" s="43" t="n">
+      <c r="K8" s="39" t="n">
         <f aca="false">IF(I8="Pending",0,J8-F8)</f>
         <v>-150</v>
       </c>
-      <c r="L8" s="58" t="n">
+      <c r="L8" s="54" t="n">
         <v>0.56</v>
       </c>
-      <c r="M8" s="62" t="s">
+      <c r="M8" s="58" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" s="5" t="s">
         <v>382</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="33" t="n">
-        <v>3</v>
-      </c>
-      <c r="B9" s="5" t="s">
+      <c r="C9" s="28" t="s">
         <v>383</v>
       </c>
-      <c r="C9" s="32" t="s">
-        <v>384</v>
-      </c>
-      <c r="D9" s="33" t="s">
-        <v>94</v>
-      </c>
-      <c r="E9" s="39" t="n">
+      <c r="D9" s="29" t="s">
+        <v>92</v>
+      </c>
+      <c r="E9" s="35" t="n">
         <v>-159</v>
       </c>
-      <c r="F9" s="40" t="n">
+      <c r="F9" s="36" t="n">
         <v>150</v>
       </c>
-      <c r="G9" s="41" t="n">
+      <c r="G9" s="37" t="n">
         <f aca="false">IF(E9&gt;0,F9*E9/100,F9*100/ABS(E9))</f>
         <v>94.3396226415094</v>
       </c>
-      <c r="H9" s="41" t="n">
+      <c r="H9" s="37" t="n">
         <f aca="false">F9+G9</f>
         <v>244.339622641509</v>
       </c>
-      <c r="I9" s="42" t="s">
-        <v>90</v>
-      </c>
-      <c r="J9" s="41" t="n">
+      <c r="I9" s="38" t="s">
+        <v>88</v>
+      </c>
+      <c r="J9" s="37" t="n">
         <f aca="false">IF(I9="Win",F9+G9,IF(I9="Push",F9,IF(I9="Loss",0,0)))</f>
         <v>244.339622641509</v>
       </c>
-      <c r="K9" s="43" t="n">
+      <c r="K9" s="39" t="n">
         <f aca="false">IF(I9="Pending",0,J9-F9)</f>
         <v>94.3396226415094</v>
       </c>
-      <c r="L9" s="58" t="n">
+      <c r="L9" s="54" t="n">
         <v>0.65</v>
       </c>
-      <c r="M9" s="62" t="s">
+      <c r="M9" s="58" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="B10" s="5" t="s">
         <v>385</v>
       </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="33" t="n">
-        <v>4</v>
-      </c>
-      <c r="B10" s="5" t="s">
+      <c r="C10" s="28" t="s">
         <v>386</v>
       </c>
-      <c r="C10" s="32" t="s">
-        <v>387</v>
-      </c>
-      <c r="D10" s="33" t="s">
-        <v>378</v>
-      </c>
-      <c r="E10" s="39" t="n">
+      <c r="D10" s="29" t="s">
+        <v>377</v>
+      </c>
+      <c r="E10" s="35" t="n">
         <v>-108</v>
       </c>
-      <c r="F10" s="40" t="n">
+      <c r="F10" s="36" t="n">
         <v>150</v>
       </c>
-      <c r="G10" s="41" t="n">
+      <c r="G10" s="37" t="n">
         <f aca="false">IF(E10&gt;0,F10*E10/100,F10*100/ABS(E10))</f>
         <v>138.888888888889</v>
       </c>
-      <c r="H10" s="41" t="n">
+      <c r="H10" s="37" t="n">
         <f aca="false">F10+G10</f>
         <v>288.888888888889</v>
       </c>
-      <c r="I10" s="57" t="s">
-        <v>98</v>
-      </c>
-      <c r="J10" s="41" t="n">
+      <c r="I10" s="53" t="s">
+        <v>96</v>
+      </c>
+      <c r="J10" s="37" t="n">
         <f aca="false">IF(I10="Win",F10+G10,IF(I10="Push",F10,IF(I10="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K10" s="43" t="n">
+      <c r="K10" s="39" t="n">
         <f aca="false">IF(I10="Pending",0,J10-F10)</f>
         <v>-150</v>
       </c>
-      <c r="L10" s="58" t="n">
+      <c r="L10" s="54" t="n">
         <v>0.55</v>
       </c>
-      <c r="M10" s="62" t="s">
+      <c r="M10" s="58" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" s="5" t="s">
         <v>388</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="33" t="n">
-        <v>5</v>
-      </c>
-      <c r="B11" s="5" t="s">
+      <c r="C11" s="28" t="s">
         <v>389</v>
       </c>
-      <c r="C11" s="32" t="s">
-        <v>390</v>
-      </c>
-      <c r="D11" s="33" t="s">
-        <v>94</v>
-      </c>
-      <c r="E11" s="39" t="n">
+      <c r="D11" s="29" t="s">
+        <v>92</v>
+      </c>
+      <c r="E11" s="35" t="n">
         <v>-120</v>
       </c>
-      <c r="F11" s="40" t="n">
+      <c r="F11" s="36" t="n">
         <v>130</v>
       </c>
-      <c r="G11" s="41" t="n">
+      <c r="G11" s="37" t="n">
         <f aca="false">IF(E11&gt;0,F11*E11/100,F11*100/ABS(E11))</f>
         <v>108.333333333333</v>
       </c>
-      <c r="H11" s="41" t="n">
+      <c r="H11" s="37" t="n">
         <f aca="false">F11+G11</f>
         <v>238.333333333333</v>
       </c>
-      <c r="I11" s="57" t="s">
-        <v>90</v>
-      </c>
-      <c r="J11" s="41" t="n">
+      <c r="I11" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="J11" s="37" t="n">
         <f aca="false">IF(I11="Win",F11+G11,IF(I11="Push",F11,IF(I11="Loss",0,0)))</f>
         <v>238.333333333333</v>
       </c>
-      <c r="K11" s="43" t="n">
+      <c r="K11" s="39" t="n">
         <f aca="false">IF(I11="Pending",0,J11-F11)</f>
         <v>108.333333333333</v>
       </c>
-      <c r="L11" s="58" t="n">
+      <c r="L11" s="54" t="n">
         <v>0.6</v>
       </c>
-      <c r="M11" s="62" t="s">
+      <c r="M11" s="58" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" s="5" t="s">
         <v>391</v>
       </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="33" t="n">
-        <v>6</v>
-      </c>
-      <c r="B12" s="5" t="s">
+      <c r="C12" s="28" t="s">
         <v>392</v>
       </c>
-      <c r="C12" s="32" t="s">
-        <v>393</v>
-      </c>
-      <c r="D12" s="33" t="s">
-        <v>94</v>
-      </c>
-      <c r="E12" s="39" t="n">
+      <c r="D12" s="29" t="s">
+        <v>92</v>
+      </c>
+      <c r="E12" s="35" t="n">
         <v>-121</v>
       </c>
-      <c r="F12" s="40" t="n">
+      <c r="F12" s="36" t="n">
         <v>120</v>
       </c>
-      <c r="G12" s="41" t="n">
+      <c r="G12" s="37" t="n">
         <f aca="false">IF(E12&gt;0,F12*E12/100,F12*100/ABS(E12))</f>
         <v>99.1735537190083</v>
       </c>
-      <c r="H12" s="41" t="n">
+      <c r="H12" s="37" t="n">
         <f aca="false">F12+G12</f>
         <v>219.173553719008</v>
       </c>
-      <c r="I12" s="57" t="s">
-        <v>90</v>
-      </c>
-      <c r="J12" s="41" t="n">
+      <c r="I12" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="J12" s="37" t="n">
         <f aca="false">IF(I12="Win",F12+G12,IF(I12="Push",F12,IF(I12="Loss",0,0)))</f>
         <v>219.173553719008</v>
       </c>
-      <c r="K12" s="43" t="n">
+      <c r="K12" s="39" t="n">
         <f aca="false">IF(I12="Pending",0,J12-F12)</f>
         <v>99.1735537190083</v>
       </c>
-      <c r="L12" s="58" t="n">
+      <c r="L12" s="54" t="n">
         <v>0.58</v>
       </c>
-      <c r="M12" s="62" t="s">
+      <c r="M12" s="58" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="29" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" s="5" t="s">
         <v>394</v>
       </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="33" t="n">
-        <v>7</v>
-      </c>
-      <c r="B13" s="5" t="s">
+      <c r="C13" s="28" t="s">
         <v>395</v>
       </c>
-      <c r="C13" s="32" t="s">
-        <v>396</v>
-      </c>
-      <c r="D13" s="33" t="s">
-        <v>117</v>
-      </c>
-      <c r="E13" s="39" t="n">
+      <c r="D13" s="29" t="s">
+        <v>115</v>
+      </c>
+      <c r="E13" s="35" t="n">
         <v>971</v>
       </c>
-      <c r="F13" s="40" t="n">
+      <c r="F13" s="36" t="n">
         <v>100</v>
       </c>
-      <c r="G13" s="41" t="n">
+      <c r="G13" s="37" t="n">
         <f aca="false">IF(E13&gt;0,F13*E13/100,F13*100/ABS(E13))</f>
         <v>971</v>
       </c>
-      <c r="H13" s="41" t="n">
+      <c r="H13" s="37" t="n">
         <f aca="false">F13+G13</f>
         <v>1071</v>
       </c>
-      <c r="I13" s="45" t="s">
-        <v>98</v>
-      </c>
-      <c r="J13" s="41" t="n">
+      <c r="I13" s="41" t="s">
+        <v>96</v>
+      </c>
+      <c r="J13" s="37" t="n">
         <f aca="false">IF(I13="Win",F13+G13,IF(I13="Push",F13,IF(I13="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K13" s="43" t="n">
+      <c r="K13" s="39" t="n">
         <f aca="false">IF(I13="Pending",0,J13-F13)</f>
         <v>-100</v>
       </c>
-      <c r="L13" s="58" t="n">
+      <c r="L13" s="54" t="n">
         <v>0.12</v>
       </c>
-      <c r="M13" s="62" t="s">
-        <v>397</v>
+      <c r="M13" s="58" t="s">
+        <v>396</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="63"/>
-      <c r="B14" s="64" t="s">
-        <v>39</v>
-      </c>
-      <c r="C14" s="63"/>
-      <c r="D14" s="63"/>
-      <c r="E14" s="63"/>
-      <c r="F14" s="48" t="n">
+      <c r="A14" s="59"/>
+      <c r="B14" s="60" t="s">
+        <v>38</v>
+      </c>
+      <c r="C14" s="59"/>
+      <c r="D14" s="59"/>
+      <c r="E14" s="59"/>
+      <c r="F14" s="44" t="n">
         <f aca="false">SUM(F7:F13)</f>
         <v>1000</v>
       </c>
-      <c r="G14" s="49" t="n">
+      <c r="G14" s="45" t="n">
         <f aca="false">SUM(G7:G13)</f>
         <v>1719.57701348957</v>
       </c>
-      <c r="H14" s="49" t="n">
+      <c r="H14" s="45" t="n">
         <f aca="false">SUM(H7:H13)</f>
         <v>2719.57701348957</v>
       </c>
-      <c r="I14" s="63"/>
-      <c r="J14" s="49" t="n">
+      <c r="I14" s="59"/>
+      <c r="J14" s="45" t="n">
         <f aca="false">SUM(J7:J13)</f>
         <v>701.846509693851</v>
       </c>
-      <c r="K14" s="50" t="n">
+      <c r="K14" s="46" t="n">
         <f aca="false">SUM(K7:K13)</f>
         <v>-298.153490306149</v>
       </c>
-      <c r="L14" s="59" t="n">
+      <c r="L14" s="55" t="n">
         <f aca="false">SUM(L7:L13)</f>
         <v>3.62</v>
       </c>
-      <c r="M14" s="63"/>
+      <c r="M14" s="59"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="C17" s="51" t="n">
+        <v>118</v>
+      </c>
+      <c r="C17" s="47" t="n">
         <f aca="false">COUNTIF(I7:I13,"Win")</f>
         <v>3</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="C18" s="51" t="n">
+        <v>119</v>
+      </c>
+      <c r="C18" s="47" t="n">
         <f aca="false">COUNTIF(I7:I13,"Loss")</f>
         <v>4</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="C19" s="51" t="n">
+        <v>120</v>
+      </c>
+      <c r="C19" s="47" t="n">
         <f aca="false">COUNTIF(I7:I13,"Push")</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="C20" s="51" t="n">
+        <v>121</v>
+      </c>
+      <c r="C20" s="47" t="n">
         <f aca="false">COUNTIF(I7:I13,"Pending")</f>
         <v>0</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="C21" s="52" t="n">
+        <v>122</v>
+      </c>
+      <c r="C21" s="48" t="n">
         <f aca="false">IF(COUNTIF(I7:I13,"Win")+COUNTIF(I7:I13,"Loss")=0,"—",COUNTIF(I7:I13,"Win")/(COUNTIF(I7:I13,"Win")+COUNTIF(I7:I13,"Loss")))</f>
         <v>0.428571428571429</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="C22" s="34" t="n">
+        <v>123</v>
+      </c>
+      <c r="C22" s="30" t="n">
         <f aca="false">SUM(F7:F13)</f>
         <v>1000</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="C23" s="41" t="n">
+        <v>124</v>
+      </c>
+      <c r="C23" s="37" t="n">
         <f aca="false">SUM(J7:J13)</f>
         <v>701.846509693851</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="C24" s="43" t="n">
+        <v>125</v>
+      </c>
+      <c r="C24" s="39" t="n">
         <f aca="false">SUM(K7:K13)</f>
         <v>-298.153490306149</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="C25" s="52" t="n">
+        <v>126</v>
+      </c>
+      <c r="C25" s="48" t="n">
         <f aca="false">IF(SUM(F7:F13)=0,"—",SUM(K7:K13)/SUM(F7:F13))</f>
         <v>-0.298153490306149</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="C26" s="41" t="n">
+        <v>127</v>
+      </c>
+      <c r="C26" s="37" t="n">
         <f aca="false">SUM(H7:H13)</f>
         <v>2719.57701348957</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="5" t="s">
-        <v>245</v>
-      </c>
-      <c r="C27" s="60" t="n">
+        <v>243</v>
+      </c>
+      <c r="C27" s="56" t="n">
         <f aca="false">SUM(L7:L13)</f>
         <v>3.62</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="5" t="s">
-        <v>246</v>
-      </c>
-      <c r="C28" s="43" t="n">
+        <v>244</v>
+      </c>
+      <c r="C28" s="39" t="n">
         <f aca="false">SUMPRODUCT(L7:L13,G7:G13)-SUMPRODUCT(1-L7:L13,F7:F13)</f>
         <v>84.7416091107209</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="55" t="s">
-        <v>398</v>
+      <c r="A30" s="51" t="s">
+        <v>397</v>
       </c>
     </row>
   </sheetData>
@@ -7401,26 +7795,26 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="31" t="s">
+        <v>398</v>
+      </c>
+      <c r="H1" s="52" t="s">
         <v>399</v>
-      </c>
-      <c r="H1" s="56" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7428,343 +7822,343 @@
         <v>12</v>
       </c>
       <c r="B6" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>198</v>
+      </c>
+      <c r="D6" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="E6" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="G6" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="H6" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="I6" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="J6" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="K6" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="L6" s="12" t="s">
+        <v>218</v>
+      </c>
+      <c r="M6" s="12" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>402</v>
+      </c>
+      <c r="C7" s="28" t="s">
+        <v>285</v>
+      </c>
+      <c r="D7" s="29" t="s">
+        <v>188</v>
+      </c>
+      <c r="E7" s="35" t="n">
+        <v>450</v>
+      </c>
+      <c r="F7" s="36" t="n">
         <v>200</v>
       </c>
-      <c r="D6" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="E6" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="F6" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="G6" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="H6" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="I6" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="J6" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="K6" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="L6" s="12" t="s">
-        <v>220</v>
-      </c>
-      <c r="M6" s="12" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>403</v>
-      </c>
-      <c r="C7" s="32" t="s">
-        <v>287</v>
-      </c>
-      <c r="D7" s="33" t="s">
-        <v>190</v>
-      </c>
-      <c r="E7" s="39" t="n">
-        <v>450</v>
-      </c>
-      <c r="F7" s="40" t="n">
-        <v>200</v>
-      </c>
-      <c r="G7" s="41" t="n">
+      <c r="G7" s="37" t="n">
         <f aca="false">IF(E7&gt;0,F7*E7/100,F7*100/ABS(E7))</f>
         <v>900</v>
       </c>
-      <c r="H7" s="41" t="n">
+      <c r="H7" s="37" t="n">
         <f aca="false">F7+G7</f>
         <v>1100</v>
       </c>
-      <c r="I7" s="57" t="s">
-        <v>123</v>
-      </c>
-      <c r="J7" s="41" t="n">
+      <c r="I7" s="53" t="s">
+        <v>121</v>
+      </c>
+      <c r="J7" s="37" t="n">
         <f aca="false">IF(I7="Win",F7+G7,IF(I7="Push",F7,IF(I7="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K7" s="43" t="n">
+      <c r="K7" s="39" t="n">
         <f aca="false">IF(I7="Pending",0,J7-F7)</f>
         <v>0</v>
       </c>
-      <c r="L7" s="73" t="n">
+      <c r="L7" s="70" t="n">
         <v>0.18</v>
       </c>
-      <c r="M7" s="62" t="s">
+      <c r="M7" s="58" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>404</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="33" t="n">
-        <v>2</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>405</v>
-      </c>
-      <c r="C8" s="32" t="s">
-        <v>287</v>
-      </c>
-      <c r="D8" s="33" t="s">
-        <v>190</v>
-      </c>
-      <c r="E8" s="39" t="n">
+      <c r="C8" s="28" t="s">
+        <v>285</v>
+      </c>
+      <c r="D8" s="29" t="s">
+        <v>188</v>
+      </c>
+      <c r="E8" s="35" t="n">
         <v>1600</v>
       </c>
-      <c r="F8" s="40" t="n">
+      <c r="F8" s="36" t="n">
         <v>100</v>
       </c>
-      <c r="G8" s="41" t="n">
+      <c r="G8" s="37" t="n">
         <f aca="false">IF(E8&gt;0,F8*E8/100,F8*100/ABS(E8))</f>
         <v>1600</v>
       </c>
-      <c r="H8" s="41" t="n">
+      <c r="H8" s="37" t="n">
         <f aca="false">F8+G8</f>
         <v>1700</v>
       </c>
-      <c r="I8" s="57" t="s">
-        <v>123</v>
-      </c>
-      <c r="J8" s="41" t="n">
+      <c r="I8" s="53" t="s">
+        <v>121</v>
+      </c>
+      <c r="J8" s="37" t="n">
         <f aca="false">IF(I8="Win",F8+G8,IF(I8="Push",F8,IF(I8="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K8" s="43" t="n">
+      <c r="K8" s="39" t="n">
         <f aca="false">IF(I8="Pending",0,J8-F8)</f>
         <v>0</v>
       </c>
-      <c r="L8" s="73" t="n">
+      <c r="L8" s="70" t="n">
         <v>0.07</v>
       </c>
-      <c r="M8" s="62" t="s">
+      <c r="M8" s="58" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" s="5" t="s">
         <v>406</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="33" t="n">
-        <v>3</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>407</v>
-      </c>
-      <c r="C9" s="32" t="s">
-        <v>287</v>
-      </c>
-      <c r="D9" s="33" t="s">
-        <v>190</v>
-      </c>
-      <c r="E9" s="39" t="n">
+      <c r="C9" s="28" t="s">
+        <v>285</v>
+      </c>
+      <c r="D9" s="29" t="s">
+        <v>188</v>
+      </c>
+      <c r="E9" s="35" t="n">
         <v>1600</v>
       </c>
-      <c r="F9" s="40" t="n">
+      <c r="F9" s="36" t="n">
         <v>100</v>
       </c>
-      <c r="G9" s="41" t="n">
+      <c r="G9" s="37" t="n">
         <f aca="false">IF(E9&gt;0,F9*E9/100,F9*100/ABS(E9))</f>
         <v>1600</v>
       </c>
-      <c r="H9" s="41" t="n">
+      <c r="H9" s="37" t="n">
         <f aca="false">F9+G9</f>
         <v>1700</v>
       </c>
-      <c r="I9" s="57" t="s">
-        <v>123</v>
-      </c>
-      <c r="J9" s="41" t="n">
+      <c r="I9" s="53" t="s">
+        <v>121</v>
+      </c>
+      <c r="J9" s="37" t="n">
         <f aca="false">IF(I9="Win",F9+G9,IF(I9="Push",F9,IF(I9="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K9" s="43" t="n">
+      <c r="K9" s="39" t="n">
         <f aca="false">IF(I9="Pending",0,J9-F9)</f>
         <v>0</v>
       </c>
-      <c r="L9" s="73" t="n">
+      <c r="L9" s="70" t="n">
         <v>0.07</v>
       </c>
-      <c r="M9" s="62" t="s">
+      <c r="M9" s="58" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="B10" s="5" t="s">
         <v>408</v>
       </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="33" t="n">
-        <v>4</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="C10" s="32" t="s">
-        <v>287</v>
-      </c>
-      <c r="D10" s="33" t="s">
-        <v>190</v>
-      </c>
-      <c r="E10" s="39" t="n">
+      <c r="C10" s="28" t="s">
+        <v>285</v>
+      </c>
+      <c r="D10" s="29" t="s">
+        <v>188</v>
+      </c>
+      <c r="E10" s="35" t="n">
         <v>2000</v>
       </c>
-      <c r="F10" s="40" t="n">
+      <c r="F10" s="36" t="n">
         <v>80</v>
       </c>
-      <c r="G10" s="41" t="n">
+      <c r="G10" s="37" t="n">
         <f aca="false">IF(E10&gt;0,F10*E10/100,F10*100/ABS(E10))</f>
         <v>1600</v>
       </c>
-      <c r="H10" s="41" t="n">
+      <c r="H10" s="37" t="n">
         <f aca="false">F10+G10</f>
         <v>1680</v>
       </c>
-      <c r="I10" s="57" t="s">
-        <v>123</v>
-      </c>
-      <c r="J10" s="41" t="n">
+      <c r="I10" s="53" t="s">
+        <v>121</v>
+      </c>
+      <c r="J10" s="37" t="n">
         <f aca="false">IF(I10="Win",F10+G10,IF(I10="Push",F10,IF(I10="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K10" s="43" t="n">
+      <c r="K10" s="39" t="n">
         <f aca="false">IF(I10="Pending",0,J10-F10)</f>
         <v>0</v>
       </c>
-      <c r="L10" s="73" t="n">
+      <c r="L10" s="70" t="n">
         <v>0.055</v>
       </c>
-      <c r="M10" s="62" t="s">
+      <c r="M10" s="58" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" s="5" t="s">
         <v>410</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="33" t="n">
-        <v>5</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>411</v>
-      </c>
-      <c r="C11" s="32" t="s">
-        <v>287</v>
-      </c>
-      <c r="D11" s="33" t="s">
-        <v>190</v>
-      </c>
-      <c r="E11" s="39" t="n">
+      <c r="C11" s="28" t="s">
+        <v>285</v>
+      </c>
+      <c r="D11" s="29" t="s">
+        <v>188</v>
+      </c>
+      <c r="E11" s="35" t="n">
         <v>2800</v>
       </c>
-      <c r="F11" s="40" t="n">
+      <c r="F11" s="36" t="n">
         <v>70</v>
       </c>
-      <c r="G11" s="41" t="n">
+      <c r="G11" s="37" t="n">
         <f aca="false">IF(E11&gt;0,F11*E11/100,F11*100/ABS(E11))</f>
         <v>1960</v>
       </c>
-      <c r="H11" s="41" t="n">
+      <c r="H11" s="37" t="n">
         <f aca="false">F11+G11</f>
         <v>2030</v>
       </c>
-      <c r="I11" s="57" t="s">
-        <v>123</v>
-      </c>
-      <c r="J11" s="41" t="n">
+      <c r="I11" s="53" t="s">
+        <v>121</v>
+      </c>
+      <c r="J11" s="37" t="n">
         <f aca="false">IF(I11="Win",F11+G11,IF(I11="Push",F11,IF(I11="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K11" s="43" t="n">
+      <c r="K11" s="39" t="n">
         <f aca="false">IF(I11="Pending",0,J11-F11)</f>
         <v>0</v>
       </c>
-      <c r="L11" s="73" t="n">
+      <c r="L11" s="70" t="n">
         <v>0.045</v>
       </c>
-      <c r="M11" s="62" t="s">
+      <c r="M11" s="58" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" s="5" t="s">
         <v>412</v>
       </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="33" t="n">
-        <v>6</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>413</v>
-      </c>
-      <c r="C12" s="32" t="s">
-        <v>287</v>
-      </c>
-      <c r="D12" s="33" t="s">
-        <v>190</v>
-      </c>
-      <c r="E12" s="39" t="n">
+      <c r="C12" s="28" t="s">
+        <v>285</v>
+      </c>
+      <c r="D12" s="29" t="s">
+        <v>188</v>
+      </c>
+      <c r="E12" s="35" t="n">
         <v>5000</v>
       </c>
-      <c r="F12" s="40" t="n">
+      <c r="F12" s="36" t="n">
         <v>50</v>
       </c>
-      <c r="G12" s="41" t="n">
+      <c r="G12" s="37" t="n">
         <f aca="false">IF(E12&gt;0,F12*E12/100,F12*100/ABS(E12))</f>
         <v>2500</v>
       </c>
-      <c r="H12" s="41" t="n">
+      <c r="H12" s="37" t="n">
         <f aca="false">F12+G12</f>
         <v>2550</v>
       </c>
-      <c r="I12" s="57" t="s">
-        <v>123</v>
-      </c>
-      <c r="J12" s="41" t="n">
+      <c r="I12" s="53" t="s">
+        <v>121</v>
+      </c>
+      <c r="J12" s="37" t="n">
         <f aca="false">IF(I12="Win",F12+G12,IF(I12="Push",F12,IF(I12="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K12" s="43" t="n">
+      <c r="K12" s="39" t="n">
         <f aca="false">IF(I12="Pending",0,J12-F12)</f>
         <v>0</v>
       </c>
-      <c r="L12" s="73" t="n">
+      <c r="L12" s="70" t="n">
         <v>0.025</v>
       </c>
-      <c r="M12" s="62" t="s">
+      <c r="M12" s="58" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="71" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" s="72" t="s">
         <v>414</v>
       </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="24" t="n">
-        <v>7</v>
-      </c>
-      <c r="B13" s="25" t="s">
+      <c r="C13" s="73" t="s">
         <v>415</v>
       </c>
-      <c r="C13" s="74" t="s">
-        <v>416</v>
-      </c>
-      <c r="D13" s="24" t="s">
-        <v>94</v>
-      </c>
-      <c r="E13" s="75" t="n">
+      <c r="D13" s="71" t="s">
+        <v>92</v>
+      </c>
+      <c r="E13" s="74" t="n">
         <v>-146</v>
       </c>
-      <c r="F13" s="76" t="n">
+      <c r="F13" s="75" t="n">
         <v>120</v>
       </c>
-      <c r="G13" s="27" t="n">
+      <c r="G13" s="76" t="n">
         <f aca="false">IF(E13&gt;0,F13*E13/100,F13*100/ABS(E13))</f>
         <v>82.1917808219178</v>
       </c>
-      <c r="H13" s="27" t="n">
+      <c r="H13" s="76" t="n">
         <f aca="false">F13+G13</f>
         <v>202.191780821918</v>
       </c>
-      <c r="I13" s="57" t="s">
-        <v>123</v>
-      </c>
-      <c r="J13" s="27" t="n">
+      <c r="I13" s="53" t="s">
+        <v>121</v>
+      </c>
+      <c r="J13" s="76" t="n">
         <f aca="false">IF(I13="Win",F13+G13,IF(I13="Push",F13,IF(I13="Loss",0,0)))</f>
         <v>0</v>
       </c>
@@ -7776,194 +8170,194 @@
         <v>0.62</v>
       </c>
       <c r="M13" s="79" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="29" t="n">
+        <v>8</v>
+      </c>
+      <c r="B14" s="5" t="s">
         <v>417</v>
       </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="33" t="n">
-        <v>8</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>418</v>
-      </c>
-      <c r="C14" s="32" t="s">
-        <v>416</v>
-      </c>
-      <c r="D14" s="33" t="s">
-        <v>94</v>
-      </c>
-      <c r="E14" s="39" t="n">
+      <c r="C14" s="28" t="s">
+        <v>415</v>
+      </c>
+      <c r="D14" s="29" t="s">
+        <v>92</v>
+      </c>
+      <c r="E14" s="35" t="n">
         <v>158</v>
       </c>
-      <c r="F14" s="40" t="n">
+      <c r="F14" s="36" t="n">
         <v>90</v>
       </c>
-      <c r="G14" s="41" t="n">
+      <c r="G14" s="37" t="n">
         <f aca="false">IF(E14&gt;0,F14*E14/100,F14*100/ABS(E14))</f>
         <v>142.2</v>
       </c>
-      <c r="H14" s="41" t="n">
+      <c r="H14" s="37" t="n">
         <f aca="false">F14+G14</f>
         <v>232.2</v>
       </c>
-      <c r="I14" s="57" t="s">
-        <v>123</v>
-      </c>
-      <c r="J14" s="41" t="n">
+      <c r="I14" s="53" t="s">
+        <v>121</v>
+      </c>
+      <c r="J14" s="37" t="n">
         <f aca="false">IF(I14="Win",F14+G14,IF(I14="Push",F14,IF(I14="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K14" s="43" t="n">
+      <c r="K14" s="39" t="n">
         <f aca="false">IF(I14="Pending",0,J14-F14)</f>
         <v>0</v>
       </c>
-      <c r="L14" s="73" t="n">
+      <c r="L14" s="70" t="n">
         <v>0.44</v>
       </c>
-      <c r="M14" s="62" t="s">
+      <c r="M14" s="58" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="29" t="n">
+        <v>9</v>
+      </c>
+      <c r="B15" s="5" t="s">
         <v>419</v>
       </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="33" t="n">
-        <v>9</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>420</v>
-      </c>
-      <c r="C15" s="32" t="s">
-        <v>416</v>
-      </c>
-      <c r="D15" s="33" t="s">
-        <v>94</v>
-      </c>
-      <c r="E15" s="39" t="n">
+      <c r="C15" s="28" t="s">
+        <v>415</v>
+      </c>
+      <c r="D15" s="29" t="s">
+        <v>92</v>
+      </c>
+      <c r="E15" s="35" t="n">
         <v>172</v>
       </c>
-      <c r="F15" s="40" t="n">
+      <c r="F15" s="36" t="n">
         <v>80</v>
       </c>
-      <c r="G15" s="41" t="n">
+      <c r="G15" s="37" t="n">
         <f aca="false">IF(E15&gt;0,F15*E15/100,F15*100/ABS(E15))</f>
         <v>137.6</v>
       </c>
-      <c r="H15" s="41" t="n">
+      <c r="H15" s="37" t="n">
         <f aca="false">F15+G15</f>
         <v>217.6</v>
       </c>
-      <c r="I15" s="57" t="s">
-        <v>123</v>
-      </c>
-      <c r="J15" s="41" t="n">
+      <c r="I15" s="53" t="s">
+        <v>121</v>
+      </c>
+      <c r="J15" s="37" t="n">
         <f aca="false">IF(I15="Win",F15+G15,IF(I15="Push",F15,IF(I15="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K15" s="43" t="n">
+      <c r="K15" s="39" t="n">
         <f aca="false">IF(I15="Pending",0,J15-F15)</f>
         <v>0</v>
       </c>
-      <c r="L15" s="73" t="n">
+      <c r="L15" s="70" t="n">
         <v>0.42</v>
       </c>
-      <c r="M15" s="62" t="s">
+      <c r="M15" s="58" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B16" s="5" t="s">
         <v>421</v>
       </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="33" t="n">
-        <v>10</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>422</v>
-      </c>
-      <c r="C16" s="32" t="s">
-        <v>416</v>
-      </c>
-      <c r="D16" s="33" t="s">
-        <v>94</v>
-      </c>
-      <c r="E16" s="39" t="n">
+      <c r="C16" s="28" t="s">
+        <v>415</v>
+      </c>
+      <c r="D16" s="29" t="s">
+        <v>92</v>
+      </c>
+      <c r="E16" s="35" t="n">
         <v>164</v>
       </c>
-      <c r="F16" s="40" t="n">
+      <c r="F16" s="36" t="n">
         <v>70</v>
       </c>
-      <c r="G16" s="41" t="n">
+      <c r="G16" s="37" t="n">
         <f aca="false">IF(E16&gt;0,F16*E16/100,F16*100/ABS(E16))</f>
         <v>114.8</v>
       </c>
-      <c r="H16" s="41" t="n">
+      <c r="H16" s="37" t="n">
         <f aca="false">F16+G16</f>
         <v>184.8</v>
       </c>
-      <c r="I16" s="57" t="s">
-        <v>123</v>
-      </c>
-      <c r="J16" s="41" t="n">
+      <c r="I16" s="53" t="s">
+        <v>121</v>
+      </c>
+      <c r="J16" s="37" t="n">
         <f aca="false">IF(I16="Win",F16+G16,IF(I16="Push",F16,IF(I16="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K16" s="43" t="n">
+      <c r="K16" s="39" t="n">
         <f aca="false">IF(I16="Pending",0,J16-F16)</f>
         <v>0</v>
       </c>
-      <c r="L16" s="73" t="n">
+      <c r="L16" s="70" t="n">
         <v>0.42</v>
       </c>
-      <c r="M16" s="62" t="s">
+      <c r="M16" s="58" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="29" t="n">
+        <v>11</v>
+      </c>
+      <c r="B17" s="5" t="s">
         <v>423</v>
       </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="33" t="n">
-        <v>11</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>424</v>
-      </c>
       <c r="C17" s="80" t="s">
-        <v>416</v>
-      </c>
-      <c r="D17" s="33" t="s">
-        <v>94</v>
-      </c>
-      <c r="E17" s="39" t="n">
+        <v>415</v>
+      </c>
+      <c r="D17" s="29" t="s">
+        <v>92</v>
+      </c>
+      <c r="E17" s="35" t="n">
         <v>280</v>
       </c>
-      <c r="F17" s="40" t="n">
+      <c r="F17" s="36" t="n">
         <v>40</v>
       </c>
-      <c r="G17" s="41" t="n">
+      <c r="G17" s="37" t="n">
         <f aca="false">IF(E17&gt;0,F17*E17/100,F17*100/ABS(E17))</f>
         <v>112</v>
       </c>
-      <c r="H17" s="41" t="n">
+      <c r="H17" s="37" t="n">
         <f aca="false">F17+G17</f>
         <v>152</v>
       </c>
-      <c r="I17" s="57" t="s">
-        <v>123</v>
-      </c>
-      <c r="J17" s="41" t="n">
+      <c r="I17" s="53" t="s">
+        <v>121</v>
+      </c>
+      <c r="J17" s="37" t="n">
         <f aca="false">IF(I17="Win",F17+G17,IF(I17="Push",F17,IF(I17="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K17" s="43" t="n">
+      <c r="K17" s="39" t="n">
         <f aca="false">IF(I17="Pending",0,J17-F17)</f>
         <v>0</v>
       </c>
-      <c r="L17" s="73" t="n">
+      <c r="L17" s="70" t="n">
         <v>0.3</v>
       </c>
-      <c r="M17" s="62" t="s">
-        <v>425</v>
+      <c r="M17" s="58" t="s">
+        <v>424</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="81" t="s">
-        <v>426</v>
-      </c>
-      <c r="C18" s="51" t="n">
+        <v>425</v>
+      </c>
+      <c r="C18" s="47" t="n">
         <f aca="false">COUNTIF(I7:I12,"Loss")</f>
         <v>0</v>
       </c>
@@ -7994,54 +8388,54 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="C19" s="51" t="n">
+        <v>121</v>
+      </c>
+      <c r="C19" s="47" t="n">
         <f aca="false">COUNTIF(I7:I12,"Pending")</f>
         <v>6</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="C20" s="52" t="str">
+        <v>122</v>
+      </c>
+      <c r="C20" s="48" t="str">
         <f aca="false">IF(COUNTIF(I7:I12,"Win")+COUNTIF(I7:I12,"Loss")=0,"—",COUNTIF(I7:I12,"Win")/(COUNTIF(I7:I12,"Win")+COUNTIF(I7:I12,"Loss")))</f>
         <v>—</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="5" t="s">
-        <v>427</v>
-      </c>
-      <c r="C21" s="34" t="n">
+        <v>426</v>
+      </c>
+      <c r="C21" s="30" t="n">
         <f aca="false">SUM(F7:F12)</f>
         <v>600</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="C22" s="41" t="n">
+        <v>124</v>
+      </c>
+      <c r="C22" s="37" t="n">
         <f aca="false">SUM(J7:J12)</f>
         <v>0</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="C23" s="43" t="n">
+        <v>125</v>
+      </c>
+      <c r="C23" s="39" t="n">
         <f aca="false">SUM(K7:K12)</f>
         <v>0</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="5" t="s">
-        <v>428</v>
-      </c>
-      <c r="C24" s="52" t="n">
+        <v>427</v>
+      </c>
+      <c r="C24" s="48" t="n">
         <f aca="false">SUM(L7:L12)</f>
         <v>0.445</v>
       </c>
@@ -8115,26 +8509,26 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="31" t="s">
+        <v>428</v>
+      </c>
+      <c r="H1" s="83" t="s">
         <v>429</v>
-      </c>
-      <c r="H1" s="83" t="s">
-        <v>430</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8142,360 +8536,360 @@
         <v>12</v>
       </c>
       <c r="B6" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>198</v>
+      </c>
+      <c r="D6" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="C6" s="12" t="s">
-        <v>200</v>
-      </c>
-      <c r="D6" s="12" t="s">
+      <c r="E6" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="G6" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="H6" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="F6" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="G6" s="12" t="s">
+      <c r="I6" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="H6" s="12" t="s">
+      <c r="J6" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="I6" s="12" t="s">
+      <c r="K6" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="J6" s="12" t="s">
+      <c r="L6" s="12" t="s">
+        <v>218</v>
+      </c>
+      <c r="M6" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="K6" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="L6" s="12" t="s">
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>432</v>
+      </c>
+      <c r="C7" s="28" t="s">
+        <v>285</v>
+      </c>
+      <c r="D7" s="29" t="s">
+        <v>188</v>
+      </c>
+      <c r="E7" s="35" t="n">
+        <v>310</v>
+      </c>
+      <c r="F7" s="36" t="n">
         <v>220</v>
       </c>
-      <c r="M6" s="12" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>433</v>
-      </c>
-      <c r="C7" s="32" t="s">
-        <v>287</v>
-      </c>
-      <c r="D7" s="33" t="s">
-        <v>190</v>
-      </c>
-      <c r="E7" s="39" t="n">
-        <v>310</v>
-      </c>
-      <c r="F7" s="40" t="n">
-        <v>220</v>
-      </c>
-      <c r="G7" s="41" t="n">
+      <c r="G7" s="37" t="n">
         <f aca="false">IF(E7&gt;0,F7*E7/100,F7*100/ABS(E7))</f>
         <v>682</v>
       </c>
-      <c r="H7" s="41" t="n">
+      <c r="H7" s="37" t="n">
         <f aca="false">F7+G7</f>
         <v>902</v>
       </c>
-      <c r="I7" s="57" t="s">
-        <v>98</v>
-      </c>
-      <c r="J7" s="41" t="n">
+      <c r="I7" s="53" t="s">
+        <v>96</v>
+      </c>
+      <c r="J7" s="37" t="n">
         <f aca="false">IF(I7="Win",F7+G7,IF(I7="Push",F7,IF(I7="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K7" s="43" t="n">
+      <c r="K7" s="39" t="n">
         <f aca="false">IF(I7="Pending",0,J7-F7)</f>
         <v>-220</v>
       </c>
-      <c r="L7" s="73" t="n">
+      <c r="L7" s="70" t="n">
         <v>0.27</v>
       </c>
-      <c r="M7" s="62" t="s">
+      <c r="M7" s="58" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>434</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="33" t="n">
-        <v>2</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>435</v>
-      </c>
-      <c r="C8" s="32" t="s">
-        <v>287</v>
-      </c>
-      <c r="D8" s="33" t="s">
-        <v>190</v>
-      </c>
-      <c r="E8" s="39" t="n">
+      <c r="C8" s="28" t="s">
+        <v>285</v>
+      </c>
+      <c r="D8" s="29" t="s">
+        <v>188</v>
+      </c>
+      <c r="E8" s="35" t="n">
         <v>425</v>
       </c>
-      <c r="F8" s="40" t="n">
+      <c r="F8" s="36" t="n">
         <v>130</v>
       </c>
-      <c r="G8" s="41" t="n">
+      <c r="G8" s="37" t="n">
         <f aca="false">IF(E8&gt;0,F8*E8/100,F8*100/ABS(E8))</f>
         <v>552.5</v>
       </c>
-      <c r="H8" s="41" t="n">
+      <c r="H8" s="37" t="n">
         <f aca="false">F8+G8</f>
         <v>682.5</v>
       </c>
-      <c r="I8" s="57" t="s">
-        <v>98</v>
-      </c>
-      <c r="J8" s="41" t="n">
+      <c r="I8" s="53" t="s">
+        <v>96</v>
+      </c>
+      <c r="J8" s="37" t="n">
         <f aca="false">IF(I8="Win",F8+G8,IF(I8="Push",F8,IF(I8="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K8" s="43" t="n">
+      <c r="K8" s="39" t="n">
         <f aca="false">IF(I8="Pending",0,J8-F8)</f>
         <v>-130</v>
       </c>
-      <c r="L8" s="73" t="n">
+      <c r="L8" s="70" t="n">
         <v>0.18</v>
       </c>
-      <c r="M8" s="62" t="s">
+      <c r="M8" s="58" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" s="5" t="s">
         <v>436</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="33" t="n">
-        <v>3</v>
-      </c>
-      <c r="B9" s="5" t="s">
+      <c r="C9" s="28" t="s">
         <v>437</v>
       </c>
-      <c r="C9" s="32" t="s">
-        <v>438</v>
-      </c>
-      <c r="D9" s="33" t="s">
-        <v>94</v>
-      </c>
-      <c r="E9" s="39" t="n">
+      <c r="D9" s="29" t="s">
+        <v>92</v>
+      </c>
+      <c r="E9" s="35" t="n">
         <v>-110</v>
       </c>
-      <c r="F9" s="40" t="n">
+      <c r="F9" s="36" t="n">
         <v>180</v>
       </c>
-      <c r="G9" s="41" t="n">
+      <c r="G9" s="37" t="n">
         <f aca="false">IF(E9&gt;0,F9*E9/100,F9*100/ABS(E9))</f>
         <v>163.636363636364</v>
       </c>
-      <c r="H9" s="41" t="n">
+      <c r="H9" s="37" t="n">
         <f aca="false">F9+G9</f>
         <v>343.636363636364</v>
       </c>
-      <c r="I9" s="57" t="s">
-        <v>98</v>
-      </c>
-      <c r="J9" s="41" t="n">
+      <c r="I9" s="53" t="s">
+        <v>96</v>
+      </c>
+      <c r="J9" s="37" t="n">
         <f aca="false">IF(I9="Win",F9+G9,IF(I9="Push",F9,IF(I9="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K9" s="43" t="n">
+      <c r="K9" s="39" t="n">
         <f aca="false">IF(I9="Pending",0,J9-F9)</f>
         <v>-180</v>
       </c>
-      <c r="L9" s="73" t="n">
+      <c r="L9" s="70" t="n">
         <v>0.6</v>
       </c>
-      <c r="M9" s="62" t="s">
+      <c r="M9" s="58" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="B10" s="5" t="s">
         <v>439</v>
       </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="33" t="n">
-        <v>4</v>
-      </c>
-      <c r="B10" s="5" t="s">
+      <c r="C10" s="28" t="s">
         <v>440</v>
       </c>
-      <c r="C10" s="32" t="s">
-        <v>441</v>
-      </c>
-      <c r="D10" s="33" t="s">
-        <v>94</v>
-      </c>
-      <c r="E10" s="39" t="n">
+      <c r="D10" s="29" t="s">
+        <v>92</v>
+      </c>
+      <c r="E10" s="35" t="n">
         <v>-110</v>
       </c>
-      <c r="F10" s="40" t="n">
+      <c r="F10" s="36" t="n">
         <v>150</v>
       </c>
-      <c r="G10" s="41" t="n">
+      <c r="G10" s="37" t="n">
         <f aca="false">IF(E10&gt;0,F10*E10/100,F10*100/ABS(E10))</f>
         <v>136.363636363636</v>
       </c>
-      <c r="H10" s="41" t="n">
+      <c r="H10" s="37" t="n">
         <f aca="false">F10+G10</f>
         <v>286.363636363636</v>
       </c>
-      <c r="I10" s="57" t="s">
-        <v>90</v>
-      </c>
-      <c r="J10" s="41" t="n">
+      <c r="I10" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="J10" s="37" t="n">
         <f aca="false">IF(I10="Win",F10+G10,IF(I10="Push",F10,IF(I10="Loss",0,0)))</f>
         <v>286.363636363636</v>
       </c>
-      <c r="K10" s="43" t="n">
+      <c r="K10" s="39" t="n">
         <f aca="false">IF(I10="Pending",0,J10-F10)</f>
         <v>136.363636363636</v>
       </c>
-      <c r="L10" s="73" t="n">
+      <c r="L10" s="70" t="n">
         <v>0.58</v>
       </c>
-      <c r="M10" s="62" t="s">
+      <c r="M10" s="58" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" s="5" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="33" t="n">
-        <v>5</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>443</v>
-      </c>
-      <c r="C11" s="32" t="s">
-        <v>438</v>
-      </c>
-      <c r="D11" s="33" t="s">
-        <v>94</v>
-      </c>
-      <c r="E11" s="39" t="n">
+      <c r="C11" s="28" t="s">
+        <v>437</v>
+      </c>
+      <c r="D11" s="29" t="s">
+        <v>92</v>
+      </c>
+      <c r="E11" s="35" t="n">
         <v>-110</v>
       </c>
-      <c r="F11" s="40" t="n">
+      <c r="F11" s="36" t="n">
         <v>120</v>
       </c>
-      <c r="G11" s="41" t="n">
+      <c r="G11" s="37" t="n">
         <f aca="false">IF(E11&gt;0,F11*E11/100,F11*100/ABS(E11))</f>
         <v>109.090909090909</v>
       </c>
-      <c r="H11" s="41" t="n">
+      <c r="H11" s="37" t="n">
         <f aca="false">F11+G11</f>
         <v>229.090909090909</v>
       </c>
-      <c r="I11" s="57" t="s">
-        <v>98</v>
-      </c>
-      <c r="J11" s="41" t="n">
+      <c r="I11" s="53" t="s">
+        <v>96</v>
+      </c>
+      <c r="J11" s="37" t="n">
         <f aca="false">IF(I11="Win",F11+G11,IF(I11="Push",F11,IF(I11="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K11" s="43" t="n">
+      <c r="K11" s="39" t="n">
         <f aca="false">IF(I11="Pending",0,J11-F11)</f>
         <v>-120</v>
       </c>
-      <c r="L11" s="73" t="n">
+      <c r="L11" s="70" t="n">
         <v>0.57</v>
       </c>
-      <c r="M11" s="62" t="s">
+      <c r="M11" s="58" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" s="5" t="s">
         <v>444</v>
       </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="33" t="n">
-        <v>6</v>
-      </c>
-      <c r="B12" s="5" t="s">
+      <c r="C12" s="28" t="s">
         <v>445</v>
       </c>
-      <c r="C12" s="32" t="s">
-        <v>446</v>
-      </c>
-      <c r="D12" s="33" t="s">
-        <v>94</v>
-      </c>
-      <c r="E12" s="39" t="n">
+      <c r="D12" s="29" t="s">
+        <v>92</v>
+      </c>
+      <c r="E12" s="35" t="n">
         <v>-110</v>
       </c>
-      <c r="F12" s="40" t="n">
+      <c r="F12" s="36" t="n">
         <v>125</v>
       </c>
-      <c r="G12" s="41" t="n">
+      <c r="G12" s="37" t="n">
         <f aca="false">IF(E12&gt;0,F12*E12/100,F12*100/ABS(E12))</f>
         <v>113.636363636364</v>
       </c>
-      <c r="H12" s="41" t="n">
+      <c r="H12" s="37" t="n">
         <f aca="false">F12+G12</f>
         <v>238.636363636364</v>
       </c>
-      <c r="I12" s="57" t="s">
-        <v>90</v>
-      </c>
-      <c r="J12" s="41" t="n">
+      <c r="I12" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="J12" s="37" t="n">
         <f aca="false">IF(I12="Win",F12+G12,IF(I12="Push",F12,IF(I12="Loss",0,0)))</f>
         <v>238.636363636364</v>
       </c>
-      <c r="K12" s="43" t="n">
+      <c r="K12" s="39" t="n">
         <f aca="false">IF(I12="Pending",0,J12-F12)</f>
         <v>113.636363636364</v>
       </c>
-      <c r="L12" s="73" t="n">
+      <c r="L12" s="70" t="n">
         <v>0.56</v>
       </c>
-      <c r="M12" s="62" t="s">
+      <c r="M12" s="58" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="29" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" s="5" t="s">
         <v>447</v>
       </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="33" t="n">
-        <v>7</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>448</v>
-      </c>
-      <c r="C13" s="32" t="s">
-        <v>287</v>
-      </c>
-      <c r="D13" s="33" t="s">
-        <v>190</v>
-      </c>
-      <c r="E13" s="39" t="n">
+      <c r="C13" s="28" t="s">
+        <v>285</v>
+      </c>
+      <c r="D13" s="29" t="s">
+        <v>188</v>
+      </c>
+      <c r="E13" s="35" t="n">
         <v>1400</v>
       </c>
-      <c r="F13" s="40" t="n">
+      <c r="F13" s="36" t="n">
         <v>75</v>
       </c>
-      <c r="G13" s="41" t="n">
+      <c r="G13" s="37" t="n">
         <f aca="false">IF(E13&gt;0,F13*E13/100,F13*100/ABS(E13))</f>
         <v>1050</v>
       </c>
-      <c r="H13" s="41" t="n">
+      <c r="H13" s="37" t="n">
         <f aca="false">F13+G13</f>
         <v>1125</v>
       </c>
-      <c r="I13" s="57" t="s">
-        <v>98</v>
-      </c>
-      <c r="J13" s="41" t="n">
+      <c r="I13" s="53" t="s">
+        <v>96</v>
+      </c>
+      <c r="J13" s="37" t="n">
         <f aca="false">IF(I13="Win",F13+G13,IF(I13="Push",F13,IF(I13="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K13" s="43" t="n">
+      <c r="K13" s="39" t="n">
         <f aca="false">IF(I13="Pending",0,J13-F13)</f>
         <v>-75</v>
       </c>
-      <c r="L13" s="73" t="n">
+      <c r="L13" s="70" t="n">
         <v>0.07</v>
       </c>
-      <c r="M13" s="62" t="s">
-        <v>449</v>
+      <c r="M13" s="58" t="s">
+        <v>448</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F14" s="8" t="n">
         <f aca="false">SUM(F7:F13)</f>

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -1229,7 +1229,7 @@
     <t xml:space="preserve">TEST 6 — THE 154th OPEN CHAMPIONSHIP · ROYAL BIRKDALE · JULY 16-19, 2026</t>
   </si>
   <si>
-    <t xml:space="preserve">STATUS: ACTIVE — R2 IN PROGRESS Fri Jul 17 (3:10 PM UK): TWO record 62s — Herbert leads -8; The Open official feed: "Sam Burns also cards an impressive 62 at Royal Birkdale" (Yahoo headline: both tie record for lowest major score ever; Burns total pending). Suber clubhouse -6. Morikawa no fresher number (last -5 thru 9, best on card). Koepka/Fitzpatrick no in-play numbers (E / +2 overnight, cut watch). Cut ~+1 (Yahoo 53%, Data Golf 50.9%). Scheffler off 3:04, Rahm/Fleetwood off 3:15 PM UK — $760 of card on course. Grade Sunday night only.</t>
+    <t xml:space="preserve">STATUS: ACTIVE — R2 IN PROGRESS Fri Jul 17 (4:10 PM UK): Both 62 totals now verified — TSN: Herbert finished -8 (62) and leads (9-under thru 16, missed par putt on 18); Burns total -5 (62, holed greenside bunker shot at 18). Suber clubhouse -6; Cam Young 67-67 -6. CUT ALARM: Golf Monthly reports Fitzpatrick +4 with 3 to play, in danger of missing cut (~+1) — one-source, confirm next check. Morikawa no fresher than -5 thru 9. Koepka no in-play number (E overnight). Scheffler (-2), Rahm/Fleetwood (-1) on course since 3:04/3:15 PM UK, no syndicated numbers yet. Grade Sunday night only.</t>
   </si>
   <si>
     <t xml:space="preserve">Source: open2026-betting-card.html · Outrights locked Sun Jul 12 · Phase 2 top-10 props deployed Wed Jul 15 (reserved $400 now at risk)</t>
@@ -1494,7 +1494,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="13">
+  <numFmts count="10">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="\$#,##0"/>
     <numFmt numFmtId="166" formatCode="\$#,##0.00;&quot;($&quot;#,##0.00\);\-"/>
@@ -1505,9 +1505,6 @@
     <numFmt numFmtId="171" formatCode="0%"/>
     <numFmt numFmtId="172" formatCode="0.0&quot; exp. wins&quot;"/>
     <numFmt numFmtId="173" formatCode="0.0"/>
-    <numFmt numFmtId="174" formatCode="\$#,##0"/>
-    <numFmt numFmtId="175" formatCode="\$#,##0.00"/>
-    <numFmt numFmtId="176" formatCode="\$#,##0.00;&quot;($&quot;#,##0.00\);\-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -1815,7 +1812,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="93">
+  <cellXfs count="85">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2092,10 +2089,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="170" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2156,36 +2149,8 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="14" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="14" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="174" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="175" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="176" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="175" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -2197,35 +2162,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="4">
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <charset val="1"/>
-        <family val="0"/>
-        <b val="1"/>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <charset val="1"/>
-        <family val="0"/>
-        <b val="1"/>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="2">
     <dxf>
       <font>
         <name val="Arial"/>
@@ -3295,7 +3232,7 @@
       <c r="A1" s="31" t="s">
         <v>449</v>
       </c>
-      <c r="H1" s="84" t="s">
+      <c r="H1" s="83" t="s">
         <v>450</v>
       </c>
     </row>
@@ -3393,7 +3330,7 @@
         <f aca="false">IF(I7="Pending",0,J7-F7)</f>
         <v>-185</v>
       </c>
-      <c r="L7" s="70" t="n">
+      <c r="L7" s="69" t="n">
         <v>0.57</v>
       </c>
       <c r="M7" s="58" t="s">
@@ -3438,7 +3375,7 @@
         <f aca="false">IF(I8="Pending",0,J8-F8)</f>
         <v>-175</v>
       </c>
-      <c r="L8" s="70" t="n">
+      <c r="L8" s="69" t="n">
         <v>0.54</v>
       </c>
       <c r="M8" s="58" t="s">
@@ -3483,7 +3420,7 @@
         <f aca="false">IF(I9="Pending",0,J9-F9)</f>
         <v>145.454545454546</v>
       </c>
-      <c r="L9" s="70" t="n">
+      <c r="L9" s="69" t="n">
         <v>0.55</v>
       </c>
       <c r="M9" s="58" t="s">
@@ -3528,7 +3465,7 @@
         <f aca="false">IF(I10="Pending",0,J10-F10)</f>
         <v>-150</v>
       </c>
-      <c r="L10" s="70" t="n">
+      <c r="L10" s="69" t="n">
         <v>0.54</v>
       </c>
       <c r="M10" s="58" t="s">
@@ -3573,7 +3510,7 @@
         <f aca="false">IF(I11="Pending",0,J11-F11)</f>
         <v>107.692307692308</v>
       </c>
-      <c r="L11" s="70" t="n">
+      <c r="L11" s="69" t="n">
         <v>0.58</v>
       </c>
       <c r="M11" s="58" t="s">
@@ -3618,7 +3555,7 @@
         <f aca="false">IF(I12="Pending",0,J12-F12)</f>
         <v>-115</v>
       </c>
-      <c r="L12" s="70" t="n">
+      <c r="L12" s="69" t="n">
         <v>0.52</v>
       </c>
       <c r="M12" s="58" t="s">
@@ -3663,7 +3600,7 @@
         <f aca="false">IF(I13="Pending",0,J13-F13)</f>
         <v>-75</v>
       </c>
-      <c r="L13" s="70" t="n">
+      <c r="L13" s="69" t="n">
         <v>0.1</v>
       </c>
       <c r="M13" s="58" t="s">
@@ -3729,44 +3666,44 @@
   <dimension ref="A1:M10"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="50"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="50"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="85" t="s">
+    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="31" t="s">
         <v>472</v>
       </c>
-      <c r="H1" s="86" t="s">
+      <c r="H1" s="84" t="s">
         <v>473</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="87" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>474</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="87" t="s">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
         <v>475</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="88" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="4" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
         <v>12</v>
       </c>
@@ -3807,7 +3744,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="29" t="n">
         <v>1</v>
       </c>
@@ -3823,36 +3760,36 @@
       <c r="E7" s="35" t="n">
         <v>-111</v>
       </c>
-      <c r="F7" s="89" t="n">
+      <c r="F7" s="36" t="n">
         <v>340</v>
       </c>
-      <c r="G7" s="90" t="n">
+      <c r="G7" s="37" t="n">
         <f aca="false">IF(E7&gt;0,F7*E7/100,F7*100/ABS(E7))</f>
         <v>306.306306306306</v>
       </c>
-      <c r="H7" s="90" t="n">
+      <c r="H7" s="37" t="n">
         <f aca="false">F7+G7</f>
         <v>646.306306306306</v>
       </c>
       <c r="I7" s="53" t="s">
         <v>121</v>
       </c>
-      <c r="J7" s="90" t="n">
+      <c r="J7" s="37" t="n">
         <f aca="false">IF(I7="Win",F7+G7,IF(I7="Push",F7,IF(I7="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K7" s="91" t="n">
+      <c r="K7" s="39" t="n">
         <f aca="false">IF(I7="Pending",0,J7-F7)</f>
         <v>0</v>
       </c>
-      <c r="L7" s="70" t="n">
+      <c r="L7" s="69" t="n">
         <v>0.6</v>
       </c>
       <c r="M7" s="58" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="29" t="n">
         <v>2</v>
       </c>
@@ -3868,36 +3805,36 @@
       <c r="E8" s="35" t="n">
         <v>-110</v>
       </c>
-      <c r="F8" s="89" t="n">
+      <c r="F8" s="36" t="n">
         <v>150</v>
       </c>
-      <c r="G8" s="90" t="n">
+      <c r="G8" s="37" t="n">
         <f aca="false">IF(E8&gt;0,F8*E8/100,F8*100/ABS(E8))</f>
         <v>136.363636363636</v>
       </c>
-      <c r="H8" s="90" t="n">
+      <c r="H8" s="37" t="n">
         <f aca="false">F8+G8</f>
         <v>286.363636363636</v>
       </c>
       <c r="I8" s="53" t="s">
         <v>121</v>
       </c>
-      <c r="J8" s="90" t="n">
+      <c r="J8" s="37" t="n">
         <f aca="false">IF(I8="Win",F8+G8,IF(I8="Push",F8,IF(I8="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K8" s="91" t="n">
+      <c r="K8" s="39" t="n">
         <f aca="false">IF(I8="Pending",0,J8-F8)</f>
         <v>0</v>
       </c>
-      <c r="L8" s="70" t="n">
+      <c r="L8" s="69" t="n">
         <v>0.54</v>
       </c>
       <c r="M8" s="58" t="s">
         <v>482</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="29" t="n">
         <v>3</v>
       </c>
@@ -3913,66 +3850,66 @@
       <c r="E9" s="35" t="n">
         <v>263</v>
       </c>
-      <c r="F9" s="89" t="n">
+      <c r="F9" s="36" t="n">
         <v>60</v>
       </c>
-      <c r="G9" s="90" t="n">
+      <c r="G9" s="37" t="n">
         <f aca="false">IF(E9&gt;0,F9*E9/100,F9*100/ABS(E9))</f>
         <v>157.8</v>
       </c>
-      <c r="H9" s="90" t="n">
+      <c r="H9" s="37" t="n">
         <f aca="false">F9+G9</f>
         <v>217.8</v>
       </c>
       <c r="I9" s="53" t="s">
         <v>121</v>
       </c>
-      <c r="J9" s="90" t="n">
+      <c r="J9" s="37" t="n">
         <f aca="false">IF(I9="Win",F9+G9,IF(I9="Push",F9,IF(I9="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K9" s="91" t="n">
+      <c r="K9" s="39" t="n">
         <f aca="false">IF(I9="Pending",0,J9-F9)</f>
         <v>0</v>
       </c>
-      <c r="L9" s="70" t="n">
+      <c r="L9" s="69" t="n">
         <v>0.32</v>
       </c>
       <c r="M9" s="58" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="88" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B10" s="4" t="s">
         <v>425</v>
       </c>
-      <c r="F10" s="92" t="n">
+      <c r="F10" s="8" t="n">
         <f aca="false">SUM(F7:F9)</f>
         <v>550</v>
       </c>
-      <c r="G10" s="92" t="n">
+      <c r="G10" s="8" t="n">
         <f aca="false">SUM(G7:G9)</f>
         <v>600.469942669943</v>
       </c>
-      <c r="H10" s="92" t="n">
+      <c r="H10" s="8" t="n">
         <f aca="false">SUM(H7:H9)</f>
         <v>1150.46994266994</v>
       </c>
-      <c r="J10" s="92" t="n">
+      <c r="J10" s="8" t="n">
         <f aca="false">SUM(J7:J9)</f>
         <v>0</v>
       </c>
-      <c r="K10" s="92" t="n">
+      <c r="K10" s="8" t="n">
         <f aca="false">SUM(K7:K9)</f>
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="K7:K10">
-    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>AND(ISNUMBER(K7),K7&gt;0)</formula>
     </cfRule>
-    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>AND(ISNUMBER(K7),K7&lt;0)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7168,11 +7105,11 @@
         <v>369</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="69" t="s">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="68" t="s">
         <v>60</v>
       </c>
-      <c r="B31" s="69" t="s">
+      <c r="B31" s="68" t="s">
         <v>370</v>
       </c>
     </row>
@@ -7896,7 +7833,7 @@
         <f aca="false">IF(I7="Pending",0,J7-F7)</f>
         <v>0</v>
       </c>
-      <c r="L7" s="70" t="n">
+      <c r="L7" s="69" t="n">
         <v>0.18</v>
       </c>
       <c r="M7" s="58" t="s">
@@ -7941,7 +7878,7 @@
         <f aca="false">IF(I8="Pending",0,J8-F8)</f>
         <v>0</v>
       </c>
-      <c r="L8" s="70" t="n">
+      <c r="L8" s="69" t="n">
         <v>0.07</v>
       </c>
       <c r="M8" s="58" t="s">
@@ -7986,7 +7923,7 @@
         <f aca="false">IF(I9="Pending",0,J9-F9)</f>
         <v>0</v>
       </c>
-      <c r="L9" s="70" t="n">
+      <c r="L9" s="69" t="n">
         <v>0.07</v>
       </c>
       <c r="M9" s="58" t="s">
@@ -8031,7 +7968,7 @@
         <f aca="false">IF(I10="Pending",0,J10-F10)</f>
         <v>0</v>
       </c>
-      <c r="L10" s="70" t="n">
+      <c r="L10" s="69" t="n">
         <v>0.055</v>
       </c>
       <c r="M10" s="58" t="s">
@@ -8076,7 +8013,7 @@
         <f aca="false">IF(I11="Pending",0,J11-F11)</f>
         <v>0</v>
       </c>
-      <c r="L11" s="70" t="n">
+      <c r="L11" s="69" t="n">
         <v>0.045</v>
       </c>
       <c r="M11" s="58" t="s">
@@ -8121,7 +8058,7 @@
         <f aca="false">IF(I12="Pending",0,J12-F12)</f>
         <v>0</v>
       </c>
-      <c r="L12" s="70" t="n">
+      <c r="L12" s="69" t="n">
         <v>0.025</v>
       </c>
       <c r="M12" s="58" t="s">
@@ -8129,47 +8066,47 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="71" t="n">
+      <c r="A13" s="70" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="72" t="s">
+      <c r="B13" s="71" t="s">
         <v>414</v>
       </c>
-      <c r="C13" s="73" t="s">
+      <c r="C13" s="72" t="s">
         <v>415</v>
       </c>
-      <c r="D13" s="71" t="s">
+      <c r="D13" s="70" t="s">
         <v>92</v>
       </c>
-      <c r="E13" s="74" t="n">
+      <c r="E13" s="73" t="n">
         <v>-146</v>
       </c>
-      <c r="F13" s="75" t="n">
+      <c r="F13" s="74" t="n">
         <v>120</v>
       </c>
-      <c r="G13" s="76" t="n">
+      <c r="G13" s="75" t="n">
         <f aca="false">IF(E13&gt;0,F13*E13/100,F13*100/ABS(E13))</f>
         <v>82.1917808219178</v>
       </c>
-      <c r="H13" s="76" t="n">
+      <c r="H13" s="75" t="n">
         <f aca="false">F13+G13</f>
         <v>202.191780821918</v>
       </c>
       <c r="I13" s="53" t="s">
         <v>121</v>
       </c>
-      <c r="J13" s="76" t="n">
+      <c r="J13" s="75" t="n">
         <f aca="false">IF(I13="Win",F13+G13,IF(I13="Push",F13,IF(I13="Loss",0,0)))</f>
         <v>0</v>
       </c>
-      <c r="K13" s="77" t="n">
+      <c r="K13" s="76" t="n">
         <f aca="false">IF(I13="Pending",0,J13-F13)</f>
         <v>0</v>
       </c>
-      <c r="L13" s="78" t="n">
+      <c r="L13" s="77" t="n">
         <v>0.62</v>
       </c>
-      <c r="M13" s="79" t="s">
+      <c r="M13" s="78" t="s">
         <v>416</v>
       </c>
     </row>
@@ -8211,7 +8148,7 @@
         <f aca="false">IF(I14="Pending",0,J14-F14)</f>
         <v>0</v>
       </c>
-      <c r="L14" s="70" t="n">
+      <c r="L14" s="69" t="n">
         <v>0.44</v>
       </c>
       <c r="M14" s="58" t="s">
@@ -8256,7 +8193,7 @@
         <f aca="false">IF(I15="Pending",0,J15-F15)</f>
         <v>0</v>
       </c>
-      <c r="L15" s="70" t="n">
+      <c r="L15" s="69" t="n">
         <v>0.42</v>
       </c>
       <c r="M15" s="58" t="s">
@@ -8301,7 +8238,7 @@
         <f aca="false">IF(I16="Pending",0,J16-F16)</f>
         <v>0</v>
       </c>
-      <c r="L16" s="70" t="n">
+      <c r="L16" s="69" t="n">
         <v>0.42</v>
       </c>
       <c r="M16" s="58" t="s">
@@ -8315,7 +8252,7 @@
       <c r="B17" s="5" t="s">
         <v>423</v>
       </c>
-      <c r="C17" s="80" t="s">
+      <c r="C17" s="79" t="s">
         <v>415</v>
       </c>
       <c r="D17" s="29" t="s">
@@ -8346,7 +8283,7 @@
         <f aca="false">IF(I17="Pending",0,J17-F17)</f>
         <v>0</v>
       </c>
-      <c r="L17" s="70" t="n">
+      <c r="L17" s="69" t="n">
         <v>0.3</v>
       </c>
       <c r="M17" s="58" t="s">
@@ -8354,7 +8291,7 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="81" t="s">
+      <c r="B18" s="80" t="s">
         <v>425</v>
       </c>
       <c r="C18" s="47" t="n">
@@ -8381,7 +8318,7 @@
         <f aca="false">SUM(K7:K17)</f>
         <v>0</v>
       </c>
-      <c r="L18" s="82" t="n">
+      <c r="L18" s="81" t="n">
         <f aca="false">SUM(L7:L17)</f>
         <v>2.645</v>
       </c>
@@ -8512,7 +8449,7 @@
       <c r="A1" s="31" t="s">
         <v>428</v>
       </c>
-      <c r="H1" s="83" t="s">
+      <c r="H1" s="82" t="s">
         <v>429</v>
       </c>
     </row>
@@ -8610,7 +8547,7 @@
         <f aca="false">IF(I7="Pending",0,J7-F7)</f>
         <v>-220</v>
       </c>
-      <c r="L7" s="70" t="n">
+      <c r="L7" s="69" t="n">
         <v>0.27</v>
       </c>
       <c r="M7" s="58" t="s">
@@ -8655,7 +8592,7 @@
         <f aca="false">IF(I8="Pending",0,J8-F8)</f>
         <v>-130</v>
       </c>
-      <c r="L8" s="70" t="n">
+      <c r="L8" s="69" t="n">
         <v>0.18</v>
       </c>
       <c r="M8" s="58" t="s">
@@ -8700,7 +8637,7 @@
         <f aca="false">IF(I9="Pending",0,J9-F9)</f>
         <v>-180</v>
       </c>
-      <c r="L9" s="70" t="n">
+      <c r="L9" s="69" t="n">
         <v>0.6</v>
       </c>
       <c r="M9" s="58" t="s">
@@ -8745,7 +8682,7 @@
         <f aca="false">IF(I10="Pending",0,J10-F10)</f>
         <v>136.363636363636</v>
       </c>
-      <c r="L10" s="70" t="n">
+      <c r="L10" s="69" t="n">
         <v>0.58</v>
       </c>
       <c r="M10" s="58" t="s">
@@ -8790,7 +8727,7 @@
         <f aca="false">IF(I11="Pending",0,J11-F11)</f>
         <v>-120</v>
       </c>
-      <c r="L11" s="70" t="n">
+      <c r="L11" s="69" t="n">
         <v>0.57</v>
       </c>
       <c r="M11" s="58" t="s">
@@ -8835,7 +8772,7 @@
         <f aca="false">IF(I12="Pending",0,J12-F12)</f>
         <v>113.636363636364</v>
       </c>
-      <c r="L12" s="70" t="n">
+      <c r="L12" s="69" t="n">
         <v>0.56</v>
       </c>
       <c r="M12" s="58" t="s">
@@ -8880,7 +8817,7 @@
         <f aca="false">IF(I13="Pending",0,J13-F13)</f>
         <v>-75</v>
       </c>
-      <c r="L13" s="70" t="n">
+      <c r="L13" s="69" t="n">
         <v>0.07</v>
       </c>
       <c r="M13" s="58" t="s">

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -1229,7 +1229,7 @@
     <t xml:space="preserve">TEST 6 — THE 154th OPEN CHAMPIONSHIP · ROYAL BIRKDALE · JULY 16-19, 2026</t>
   </si>
   <si>
-    <t xml:space="preserve">STATUS: ACTIVE — R2 IN PROGRESS Fri Jul 17 (4:10 PM UK): Both 62 totals now verified — TSN: Herbert finished -8 (62) and leads (9-under thru 16, missed par putt on 18); Burns total -5 (62, holed greenside bunker shot at 18). Suber clubhouse -6; Cam Young 67-67 -6. CUT ALARM: Golf Monthly reports Fitzpatrick +4 with 3 to play, in danger of missing cut (~+1) — one-source, confirm next check. Morikawa no fresher than -5 thru 9. Koepka no in-play number (E overnight). Scheffler (-2), Rahm/Fleetwood (-1) on course since 3:04/3:15 PM UK, no syndicated numbers yet. Grade Sunday night only.</t>
+    <t xml:space="preserve">STATUS: ACTIVE — R2 IN PROGRESS Fri Jul 17 (5:10 PM UK): Herbert lead now wire-verified two-source (Field Level Media: 8-under 132, rounds 70-62; ESPN wire: record-tying 62). Burns -5 (62), Suber -6, Cam Young -6 clubhouse. CUT ALARM CONFIRMED WORSE: Golf Monthly notables board now shows Fitzpatrick FINISHED +4 (F) — cut projecting +1 (Data Golf 10am: +1 at 50.9%) — barring the line sliding to +4 he misses; $150 exposure (rows 10+16) effectively dead, grade Sunday only. Morikawa no fresher than -5 thru 9 (Yahoo live, late morning). Koepka still no in-play number (E overnight). Scheffler/Rahm/Fleetwood ~2 hrs on course (off 3:04/3:15 PM UK) — no R2 numbers syndicated to wires yet; next check. NOTE: NBC clip of Scheffler '4-under thru 6' verified as a THURSDAY R1 highlight (Golf Channel) — do not treat as live R2. Grade Sunday night only.</t>
   </si>
   <si>
     <t xml:space="preserve">Source: open2026-betting-card.html · Outrights locked Sun Jul 12 · Phase 2 top-10 props deployed Wed Jul 15 (reserved $400 now at risk)</t>

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -1229,7 +1229,7 @@
     <t xml:space="preserve">TEST 6 — THE 154th OPEN CHAMPIONSHIP · ROYAL BIRKDALE · JULY 16-19, 2026</t>
   </si>
   <si>
-    <t xml:space="preserve">STATUS: ACTIVE — R2 IN PROGRESS Fri Jul 17 (5:10 PM UK): Herbert lead now wire-verified two-source (Field Level Media: 8-under 132, rounds 70-62; ESPN wire: record-tying 62). Burns -5 (62), Suber -6, Cam Young -6 clubhouse. CUT ALARM CONFIRMED WORSE: Golf Monthly notables board now shows Fitzpatrick FINISHED +4 (F) — cut projecting +1 (Data Golf 10am: +1 at 50.9%) — barring the line sliding to +4 he misses; $150 exposure (rows 10+16) effectively dead, grade Sunday only. Morikawa no fresher than -5 thru 9 (Yahoo live, late morning). Koepka still no in-play number (E overnight). Scheffler/Rahm/Fleetwood ~2 hrs on course (off 3:04/3:15 PM UK) — no R2 numbers syndicated to wires yet; next check. NOTE: NBC clip of Scheffler '4-under thru 6' verified as a THURSDAY R1 highlight (Golf Channel) — do not treat as live R2. Grade Sunday night only.</t>
+    <t xml:space="preserve">STATUS: ACTIVE — R2 LATE WAVE FINISHING Fri Jul 17 (8:20 PM UK): AP wire now confirms Herbert 8-under 132 (70-62) leads by two (missed 5-footer at 18 for 61); Burns 62 (-5) alongside — matches Field Level/ESPN. Suber -6 (69), Young -6 clubhouse; McIlroy 67 (-1) safely inside. Cut still projecting +1 (Data Golf 50.9%); AP expects it back at least one from even — Fitzpatrick +4 (F) misses either way, $150 (rows 10+16) dead money, grade Sunday only. Morikawa no fresher than -5 thru 9. Koepka no in-play number. Scheffler/Rahm/Fleetwood ~5 hrs in (off 3:04/3:15 PM UK), finishing now — NO late-wave numbers syndicated to wires yet (five outlets checked, all serving morning board); R2 finals expected next check. Grade Sunday night only.</t>
   </si>
   <si>
     <t xml:space="preserve">Source: open2026-betting-card.html · Outrights locked Sun Jul 12 · Phase 2 top-10 props deployed Wed Jul 15 (reserved $400 now at risk)</t>

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -1229,7 +1229,7 @@
     <t xml:space="preserve">TEST 6 — THE 154th OPEN CHAMPIONSHIP · ROYAL BIRKDALE · JULY 16-19, 2026</t>
   </si>
   <si>
-    <t xml:space="preserve">STATUS: ACTIVE — R2 LATE WAVE FINISHING Fri Jul 17 (8:20 PM UK): AP wire now confirms Herbert 8-under 132 (70-62) leads by two (missed 5-footer at 18 for 61); Burns 62 (-5) alongside — matches Field Level/ESPN. Suber -6 (69), Young -6 clubhouse; McIlroy 67 (-1) safely inside. Cut still projecting +1 (Data Golf 50.9%); AP expects it back at least one from even — Fitzpatrick +4 (F) misses either way, $150 (rows 10+16) dead money, grade Sunday only. Morikawa no fresher than -5 thru 9. Koepka no in-play number. Scheffler/Rahm/Fleetwood ~5 hrs in (off 3:04/3:15 PM UK), finishing now — NO late-wave numbers syndicated to wires yet (five outlets checked, all serving morning board); R2 finals expected next check. Grade Sunday night only.</t>
+    <t xml:space="preserve">STATUS: ACTIVE — R2 late wave hitting wires Fri Jul 17 (9:15 PM UK): Herbert −8 leads; Fleetwood/Rahm −5, Scheffler −4 T7 (GM, single-source); Fitzpatrick +4 missed cut. Grades Sunday.</t>
   </si>
   <si>
     <t xml:space="preserve">Source: open2026-betting-card.html · Outrights locked Sun Jul 12 · Phase 2 top-10 props deployed Wed Jul 15 (reserved $400 now at risk)</t>

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -1229,7 +1229,7 @@
     <t xml:space="preserve">TEST 6 — THE 154th OPEN CHAMPIONSHIP · ROYAL BIRKDALE · JULY 16-19, 2026</t>
   </si>
   <si>
-    <t xml:space="preserve">STATUS: ACTIVE — R2 late wave hitting wires Fri Jul 17 (9:15 PM UK): Herbert −8 leads; Fleetwood/Rahm −5, Scheffler −4 T7 (GM, single-source); Fitzpatrick +4 missed cut. Grades Sunday.</t>
+    <t xml:space="preserve">STATUS: ACTIVE — R2 COMPLETE Fri Jul 17 (10:20 PM UK): Herbert −8 leads (70-62); DeChambeau −7 solo 2nd after 2-stroke penalty; Suber/Young −6, Burns −5. Our card: Scheffler −4 four back (2-source); Rahm −4, Fleetwood −3 (GM, single-source); cut +1 — Fitzpatrick +4 MISSED CUT ($150 dead). Morikawa/Koepka unconfirmed. Grades Sunday.</t>
   </si>
   <si>
     <t xml:space="preserve">Source: open2026-betting-card.html · Outrights locked Sun Jul 12 · Phase 2 top-10 props deployed Wed Jul 15 (reserved $400 now at risk)</t>

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -7801,9 +7801,9 @@
           <t>TEST 6 — THE 154th OPEN CHAMPIONSHIP · ROYAL BIRKDALE · JULY 16-19, 2026</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>STATUS: ACTIVE — R2 COMPLETE Fri Jul 17 (11:08 PM UK): Herbert −8 leads; Sat final pairing Herbert/DeChambeau (−7) official per Yahoo. Our card: Scheffler −4 four back (2-source); Rahm −4, Fleetwood −3 (GM; Yahoo has both in Sat last groups); cut +1 — Fitzpatrick +4 MISSED CUT ($150 dead). NEW: Koepka MADE CUT per Yahoo (single-source) — +5000 longshot alive. Morikawa unconfirmed. Grades Sunday.</t>
+      <c r="B1" s="85" t="inlineStr">
+        <is>
+          <t>STATUS: ACTIVE — R3 TEE SHEET OFFICIAL Sat Jul 18 (3:08 AM UK): Herbert −8 leads Suber/Young/Gerard by 2 (Golf Channel verbatim); final twosome Herbert–Suber 10:50 ET — DeChambeau revised out of final pairing (10:30 w/ Burns). Our card: Scheffler −4 tees 9:45 ET; Rahm &amp; Fleetwood paired 9:35 ET; Fitzpatrick +4 MISSED CUT ($150 dead). Koepka thru cut TWO-SOURCE (4:50 ET tee time, GC+Yahoo) — +5000 alive. Morikawa CONFIRMED thru cut (PGA Tour + 8:10 ET tee time). All 5 surviving outrights play weekend. Grades Sunday.</t>
         </is>
       </c>
       <c r="H1" s="137" t="inlineStr">

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -1229,7 +1229,7 @@
     <t xml:space="preserve">TEST 6 — THE 154th OPEN CHAMPIONSHIP · ROYAL BIRKDALE · JULY 16-19, 2026</t>
   </si>
   <si>
-    <t xml:space="preserve">STATUS: ACTIVE — R3 UNDERWAY Sat Jul 18 (12:20 PM UK): Herbert −8 leads Suber/Young/Gerard by 2; Burns/DeChambeau/Kim −5 (DeChambeau 2-shot penalty confirmed, playing on). Our card: Scheffler/Rahm/Fleetwood all −4 T8 (Yahoo + Central Oregon Daily agree); Morikawa ~−2, Koepka made cut on the number — +5000 alive. Fitzpatrick MC. Grades Sunday only.</t>
+    <t xml:space="preserve">STATUS: ACTIVE — R3 MID-ROUND Sat Jul 18 (2:10 PM UK): Herbert −8 still leads, leaders tee 3:50 PM UK. Ryan Fox charging — 6-under thru 15 today, within two of the lead (Golf Monthly); JT to −4. Our card: Scheffler/Rahm/Fleetwood start −4, teeing off mid-afternoon; Morikawa −2; Koepka +1 mid-round (single source) — +5000 alive but needs a run. McIlroy back to ~level. Grades Sunday only. (Golfmagic + Golf Monthly R3 live blogs agree)</t>
   </si>
   <si>
     <t xml:space="preserve">STATUS: ACTIVE — R2 COMPLETE Fri Jul 17 (10:20 PM UK): Herbert −8 leads (70-62); DeChambeau −7 solo 2nd after 2-stroke penalty; Suber/Young −6, Burns −5. Our card: Scheffler −4 four back (2-source); Rahm −4, Fleetwood −3 (GM, single-source); cut +1 — Fitzpatrick +4 MISSED CUT ($150 dead). Morikawa/Koepka unconfirmed. Grades Sunday.</t>

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -1229,7 +1229,7 @@
     <t xml:space="preserve">TEST 6 — THE 154th OPEN CHAMPIONSHIP · ROYAL BIRKDALE · JULY 16-19, 2026</t>
   </si>
   <si>
-    <t xml:space="preserve">STATUS: ACTIVE — R3 MID-ROUND Sat Jul 18 (2:10 PM UK): Herbert −8 still leads, leaders tee 3:50 PM UK. Ryan Fox charging — 6-under thru 15 today, within two of the lead (Golf Monthly); JT to −4. Our card: Scheffler/Rahm/Fleetwood start −4, teeing off mid-afternoon; Morikawa −2; Koepka +1 mid-round (single source) — +5000 alive but needs a run. McIlroy back to ~level. Grades Sunday only. (Golfmagic + Golf Monthly R3 live blogs agree)</t>
+    <t xml:space="preserve">STATUS: ACTIVE — R3 MID-ROUND Sat Jul 18 (3:10 PM UK): Ryan Fox posts a record-tying 62 (nine birdies, one bogey) — now −8 with a SHARE OF THE LEAD; Herbert −8 tees off 3:50 PM UK (Yahoo Sports + Central Oregon Daily live board agree). DeChambeau −5. Our card: Scheffler/Rahm/Fleetwood all −4 (T10), just teed off 2:35–2:45 PM UK; JT also −4 thru 10; Morikawa and Koepka outside the live top 10 — Koepka +5000 needs a big weekend. Fitzpatrick MC $150 dead. Grades Sunday only.</t>
   </si>
   <si>
     <t xml:space="preserve">STATUS: ACTIVE — R2 COMPLETE Fri Jul 17 (10:20 PM UK): Herbert −8 leads (70-62); DeChambeau −7 solo 2nd after 2-stroke penalty; Suber/Young −6, Burns −5. Our card: Scheffler −4 four back (2-source); Rahm −4, Fleetwood −3 (GM, single-source); cut +1 — Fitzpatrick +4 MISSED CUT ($150 dead). Morikawa/Koepka unconfirmed. Grades Sunday.</t>

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -1229,10 +1229,10 @@
     <t xml:space="preserve">TEST 6 — THE 154th OPEN CHAMPIONSHIP · ROYAL BIRKDALE · JULY 16-19, 2026</t>
   </si>
   <si>
+    <t xml:space="preserve">STATUS: ACTIVE — R3 MID-ROUND Sat Jul 18 (4:10 PM UK): Ryan Fox IN THE CLUBHOUSE at −8 after a record-tying 62 (nine birdies, one bogey) — shares the lead with Herbert −8, who teed off 3:50 PM UK (Central Oregon Daily + Golfmagic live boards agree). Suber/Young −6; DeChambeau −5. Our card: Scheffler/Rahm/Fleetwood all −4 (T10), an hour into Moving Day; JT also −4; Morikawa −2; Koepka +1 — nine back, +5000 on life support. Fitzpatrick MC $150 dead. Grades Sunday only.</t>
+  </si>
+  <si>
     <t xml:space="preserve">STATUS: ACTIVE — R3 MID-ROUND Sat Jul 18 (3:10 PM UK): Ryan Fox posts a record-tying 62 (nine birdies, one bogey) — now −8 with a SHARE OF THE LEAD; Herbert −8 tees off 3:50 PM UK (Yahoo Sports + Central Oregon Daily live board agree). DeChambeau −5. Our card: Scheffler/Rahm/Fleetwood all −4 (T10), just teed off 2:35–2:45 PM UK; JT also −4 thru 10; Morikawa and Koepka outside the live top 10 — Koepka +5000 needs a big weekend. Fitzpatrick MC $150 dead. Grades Sunday only.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STATUS: ACTIVE — R2 COMPLETE Fri Jul 17 (10:20 PM UK): Herbert −8 leads (70-62); DeChambeau −7 solo 2nd after 2-stroke penalty; Suber/Young −6, Burns −5. Our card: Scheffler −4 four back (2-source); Rahm −4, Fleetwood −3 (GM, single-source); cut +1 — Fitzpatrick +4 MISSED CUT ($150 dead). Morikawa/Koepka unconfirmed. Grades Sunday.</t>
   </si>
   <si>
     <t xml:space="preserve">Source: open2026-betting-card.html · Outrights locked Sun Jul 12 · Phase 2 top-10 props deployed Wed Jul 15 (reserved $400 now at risk)</t>

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="839" uniqueCount="486">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="839" uniqueCount="487">
   <si>
     <t xml:space="preserve">BETTING TEST ACCOUNT — ROLL-UP DASHBOARD</t>
   </si>
@@ -1227,6 +1227,9 @@
   </si>
   <si>
     <t xml:space="preserve">TEST 6 — THE 154th OPEN CHAMPIONSHIP · ROYAL BIRKDALE · JULY 16-19, 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STATUS: ACTIVE — R3 LATE Sat Jul 18 (7:30 PM UK): four-way tie at −8 — Fox (record-tying 62, in the clubhouse), Herbert, Burns (touched −9 before a bogey at 9) and Si Woo Kim (Golf Monthly liveblog 5:33 PM UK + Central Oregon Daily liveblog agree; feeds lag the course ~1-2h). Young −7. OUR CARD: Fleetwood finally moving — birdies at 5, 7 and 11 have him −6/−7 and within two (PGA Tour calls it a 'storybook run'); Scheffler grinding at −5; Rahm flat around −3/−4; no R3 move reported for Morikawa (−2 start) or Koepka (+1 start — +5000 still on life support). Fitzpatrick MC $150 dead. Grades Sunday only.</t>
   </si>
   <si>
     <t xml:space="preserve">STATUS: ACTIVE — R3 MID-ROUND Sat Jul 18 (6:15 PM UK): Fox in the clubhouse at −8 (record-tying 62) and Herbert −8 still share the lead (Central Oregon Daily liveblog 1:27 PM ET + Golf Channel liveblog agree). Chase: Suber/Young/Gerard −6; Burns/DeChambeau/Si Woo Kim −5. Our card: Scheffler/Rahm/Fleetwood all −4 (T10) mid-round; JT −4 thru 9; Schauffele in at −4 (66); Morikawa −2; Koepka +1 — nine back, +5000 on life support. Fitzpatrick MC $150 dead. Grades Sunday only.</t>
@@ -3230,20 +3233,20 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="31" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H1" s="83" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3297,10 +3300,10 @@
         <v>1</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C7" s="28" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="D7" s="29" t="s">
         <v>377</v>
@@ -3334,7 +3337,7 @@
         <v>0.57</v>
       </c>
       <c r="M7" s="58" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3342,10 +3345,10 @@
         <v>2</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C8" s="28" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D8" s="29" t="s">
         <v>177</v>
@@ -3379,7 +3382,7 @@
         <v>0.54</v>
       </c>
       <c r="M8" s="58" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3387,10 +3390,10 @@
         <v>3</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C9" s="28" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D9" s="29" t="s">
         <v>177</v>
@@ -3424,7 +3427,7 @@
         <v>0.55</v>
       </c>
       <c r="M9" s="58" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3432,7 +3435,7 @@
         <v>4</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C10" s="28" t="s">
         <v>392</v>
@@ -3469,7 +3472,7 @@
         <v>0.54</v>
       </c>
       <c r="M10" s="58" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3477,10 +3480,10 @@
         <v>5</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C11" s="28" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D11" s="29" t="s">
         <v>87</v>
@@ -3514,7 +3517,7 @@
         <v>0.58</v>
       </c>
       <c r="M11" s="58" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3522,10 +3525,10 @@
         <v>6</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C12" s="28" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D12" s="29" t="s">
         <v>377</v>
@@ -3559,7 +3562,7 @@
         <v>0.52</v>
       </c>
       <c r="M12" s="58" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3570,7 +3573,7 @@
         <v>394</v>
       </c>
       <c r="C13" s="28" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D13" s="29" t="s">
         <v>115</v>
@@ -3604,7 +3607,7 @@
         <v>0.1</v>
       </c>
       <c r="M13" s="58" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3682,20 +3685,20 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="31" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1" s="84" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3749,13 +3752,13 @@
         <v>1</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C7" s="28" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="D7" s="29" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="E7" s="35" t="n">
         <v>-111</v>
@@ -3786,7 +3789,7 @@
         <v>0.6</v>
       </c>
       <c r="M7" s="58" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3794,13 +3797,13 @@
         <v>2</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C8" s="28" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="D8" s="29" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="E8" s="35" t="n">
         <v>-110</v>
@@ -3831,7 +3834,7 @@
         <v>0.54</v>
       </c>
       <c r="M8" s="58" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3839,10 +3842,10 @@
         <v>3</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C9" s="28" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="D9" s="29" t="s">
         <v>115</v>
@@ -3876,12 +3879,12 @@
         <v>0.32</v>
       </c>
       <c r="M9" s="58" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="4" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F10" s="8" t="n">
         <f aca="false">SUM(F7:F9)</f>
@@ -7739,17 +7742,17 @@
         <v>399</v>
       </c>
       <c r="H1" s="52" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7803,7 +7806,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C7" s="28" t="s">
         <v>285</v>
@@ -7840,7 +7843,7 @@
         <v>0.18</v>
       </c>
       <c r="M7" s="58" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7848,7 +7851,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C8" s="28" t="s">
         <v>285</v>
@@ -7885,7 +7888,7 @@
         <v>0.07</v>
       </c>
       <c r="M8" s="58" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7893,7 +7896,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C9" s="28" t="s">
         <v>285</v>
@@ -7930,7 +7933,7 @@
         <v>0.07</v>
       </c>
       <c r="M9" s="58" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7938,7 +7941,7 @@
         <v>4</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C10" s="28" t="s">
         <v>285</v>
@@ -7975,7 +7978,7 @@
         <v>0.055</v>
       </c>
       <c r="M10" s="58" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7983,7 +7986,7 @@
         <v>5</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C11" s="28" t="s">
         <v>285</v>
@@ -8020,7 +8023,7 @@
         <v>0.045</v>
       </c>
       <c r="M11" s="58" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8028,7 +8031,7 @@
         <v>6</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C12" s="28" t="s">
         <v>285</v>
@@ -8065,7 +8068,7 @@
         <v>0.025</v>
       </c>
       <c r="M12" s="58" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8073,10 +8076,10 @@
         <v>7</v>
       </c>
       <c r="B13" s="71" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C13" s="72" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D13" s="70" t="s">
         <v>92</v>
@@ -8110,7 +8113,7 @@
         <v>0.62</v>
       </c>
       <c r="M13" s="78" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8118,10 +8121,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C14" s="28" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D14" s="29" t="s">
         <v>92</v>
@@ -8155,7 +8158,7 @@
         <v>0.44</v>
       </c>
       <c r="M14" s="58" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8163,10 +8166,10 @@
         <v>9</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C15" s="28" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D15" s="29" t="s">
         <v>92</v>
@@ -8200,7 +8203,7 @@
         <v>0.42</v>
       </c>
       <c r="M15" s="58" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8208,10 +8211,10 @@
         <v>10</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C16" s="28" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D16" s="29" t="s">
         <v>92</v>
@@ -8245,7 +8248,7 @@
         <v>0.42</v>
       </c>
       <c r="M16" s="58" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8253,10 +8256,10 @@
         <v>11</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C17" s="79" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D17" s="29" t="s">
         <v>92</v>
@@ -8290,12 +8293,12 @@
         <v>0.3</v>
       </c>
       <c r="M17" s="58" t="s">
-        <